--- a/analyse-prix-composants.xlsx
+++ b/analyse-prix-composants.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Feuille1" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Feuille1!$A:$AA</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Feuille1!$A:$AB</definedName>
     <definedName name="Print_Titles" localSheetId="0">Feuille1!$7:$7</definedName>
   </definedNames>
   <calcPr/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="145">
   <si>
     <t xml:space="preserve">Le prix des composants IT</t>
   </si>
@@ -118,6 +118,9 @@
   </si>
   <si>
     <t xml:space="preserve">28 fev 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 mar 2026</t>
   </si>
   <si>
     <t>Min</t>
@@ -468,7 +471,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
@@ -559,6 +562,10 @@
       <u/>
       <sz val="11.000000"/>
       <color theme="10"/>
+      <name val="Tahoma"/>
+    </font>
+    <font>
+      <sz val="12.000000"/>
       <name val="Tahoma"/>
     </font>
   </fonts>
@@ -684,7 +691,7 @@
     <xf fontId="2" fillId="3" borderId="2" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="4" borderId="0" numFmtId="43" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="3" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -789,6 +796,10 @@
       <protection locked="1"/>
     </xf>
     <xf fontId="10" fillId="12" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="1"/>
+    </xf>
+    <xf fontId="16" fillId="0" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="1"/>
     </xf>
@@ -1315,12 +1326,12 @@
     <col bestFit="1" min="12" max="12" style="4" width="11.7109375"/>
     <col bestFit="1" min="13" max="13" style="4" width="13.00390625"/>
     <col bestFit="1" min="14" max="15" style="4" width="14.140625"/>
-    <col customWidth="1" min="16" max="20" style="1" width="12.7109375"/>
-    <col customWidth="1" min="21" max="24" style="2" width="12.7109375"/>
-    <col customWidth="1" min="25" max="25" style="2" width="14.140625"/>
-    <col customWidth="1" min="26" max="27" style="2" width="12.7109375"/>
-    <col customWidth="1" min="28" max="28" style="5" width="42.28125"/>
-    <col min="29" max="16384" style="1" width="9.140625"/>
+    <col customWidth="1" min="16" max="21" style="1" width="12.7109375"/>
+    <col customWidth="1" min="22" max="25" style="2" width="12.7109375"/>
+    <col customWidth="1" min="26" max="26" style="2" width="14.140625"/>
+    <col customWidth="1" min="27" max="28" style="2" width="12.7109375"/>
+    <col customWidth="1" min="29" max="29" style="5" width="42.28125"/>
+    <col min="30" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" ht="33">
@@ -1333,28 +1344,29 @@
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
-      <c r="U1" s="7" t="s">
+      <c r="U1" s="1"/>
+      <c r="V1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="V1" s="7" t="s">
+      <c r="W1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="W1" s="7" t="s">
+      <c r="X1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="X1" s="7" t="s">
+      <c r="Y1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="Y1" s="7" t="s">
+      <c r="Z1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="Z1" s="7" t="s">
+      <c r="AA1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="AA1" s="7" t="s">
+      <c r="AB1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="AB1" s="5"/>
+      <c r="AC1" s="5"/>
     </row>
     <row r="2" ht="23.25">
       <c r="A2" s="2"/>
@@ -1366,13 +1378,14 @@
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
       <c r="T2" s="1"/>
-      <c r="U2" s="7"/>
+      <c r="U2" s="1"/>
       <c r="V2" s="7"/>
       <c r="W2" s="7"/>
       <c r="X2" s="7"/>
       <c r="Y2" s="7"/>
       <c r="Z2" s="7"/>
       <c r="AA2" s="7"/>
+      <c r="AB2" s="7"/>
     </row>
     <row r="3" ht="18">
       <c r="A3" s="2"/>
@@ -1382,13 +1395,14 @@
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
       <c r="T3" s="1"/>
-      <c r="U3" s="7"/>
+      <c r="U3" s="1"/>
       <c r="V3" s="7"/>
       <c r="W3" s="7"/>
       <c r="X3" s="7"/>
       <c r="Y3" s="7"/>
       <c r="Z3" s="7"/>
       <c r="AA3" s="7"/>
+      <c r="AB3" s="7"/>
     </row>
     <row r="4" ht="54">
       <c r="A4" s="2"/>
@@ -1401,13 +1415,14 @@
       <c r="R4" s="1"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1"/>
-      <c r="U4" s="7"/>
+      <c r="U4" s="1"/>
       <c r="V4" s="7"/>
       <c r="W4" s="7"/>
       <c r="X4" s="7"/>
       <c r="Y4" s="7"/>
       <c r="Z4" s="7"/>
       <c r="AA4" s="7"/>
+      <c r="AB4" s="7"/>
     </row>
     <row r="5" ht="23.25">
       <c r="A5" s="2"/>
@@ -1419,13 +1434,14 @@
       <c r="R5" s="1"/>
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
-      <c r="U5" s="7"/>
+      <c r="U5" s="1"/>
       <c r="V5" s="7"/>
       <c r="W5" s="7"/>
       <c r="X5" s="7"/>
       <c r="Y5" s="7"/>
       <c r="Z5" s="7"/>
       <c r="AA5" s="7"/>
+      <c r="AB5" s="7"/>
     </row>
     <row r="6" ht="37.5" customHeight="1">
       <c r="A6" s="2"/>
@@ -1434,13 +1450,14 @@
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
       <c r="T6" s="1"/>
-      <c r="U6" s="7"/>
+      <c r="U6" s="1"/>
       <c r="V6" s="7"/>
       <c r="W6" s="7"/>
       <c r="X6" s="7"/>
       <c r="Y6" s="7"/>
       <c r="Z6" s="7"/>
       <c r="AA6" s="7"/>
+      <c r="AB6" s="7"/>
     </row>
     <row r="7" ht="18">
       <c r="A7" s="10" t="s">
@@ -1503,7 +1520,7 @@
       <c r="T7" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="U7" s="13" t="s">
+      <c r="U7" s="12" t="s">
         <v>31</v>
       </c>
       <c r="V7" s="13" t="s">
@@ -1524,16 +1541,19 @@
       <c r="AA7" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="AB7" s="5" t="s">
+      <c r="AB7" s="13" t="s">
         <v>38</v>
+      </c>
+      <c r="AC7" s="5" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="8" ht="36">
       <c r="A8" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C8" s="15">
         <v>171.88</v>
@@ -1560,7 +1580,7 @@
         <v>341.57999999999998</v>
       </c>
       <c r="M8" s="17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N8" s="18">
         <v>321.14999999999998</v>
@@ -1583,48 +1603,51 @@
       <c r="T8" s="18">
         <v>366.26999999999998</v>
       </c>
-      <c r="U8" s="19">
-        <f>MIN(C8:T8)</f>
+      <c r="U8" s="18">
+        <v>366.26999999999998</v>
+      </c>
+      <c r="V8" s="19">
+        <f>MIN(C8:U8)</f>
         <v>171.88</v>
       </c>
-      <c r="V8" s="20">
-        <f>MAX(C8:T8)</f>
+      <c r="W8" s="20">
+        <f>MAX(C8:U8)</f>
         <v>367.56</v>
       </c>
-      <c r="W8" s="20">
-        <f>AVERAGE(C8:T8)</f>
-        <v>331.99214285714294</v>
-      </c>
       <c r="X8" s="20">
-        <f>AVERAGE(Q8:T8)</f>
-        <v>366.75</v>
-      </c>
-      <c r="Y8" s="21">
-        <f>(X8/W8)-1</f>
-        <v>0.10469481850904372</v>
+        <f>AVERAGE(C8:U8)</f>
+        <v>334.27733333333344</v>
+      </c>
+      <c r="Y8" s="20">
+        <f>AVERAGE(Q8:U8)</f>
+        <v>366.654</v>
       </c>
       <c r="Z8" s="21">
-        <f>(X8/U8)-1</f>
-        <v>1.1337561089131953</v>
+        <f>(Y8/X8)-1</f>
+        <v>9.6855704644446483e-002</v>
       </c>
       <c r="AA8" s="21">
-        <f>(V8/U8)-1</f>
+        <f>(Y8/V8)-1</f>
+        <v>1.1331975797067724</v>
+      </c>
+      <c r="AB8" s="21">
+        <f>(W8/V8)-1</f>
         <v>1.1384686990923902</v>
       </c>
-      <c r="AB8" s="22" t="s">
-        <v>42</v>
-      </c>
-      <c r="AC8" s="23">
+      <c r="AC8" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="AD8" s="23">
         <f>C2*1</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" ht="36">
       <c r="A9" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C9" s="16"/>
       <c r="D9" s="24">
@@ -1636,7 +1659,7 @@
         <v>686</v>
       </c>
       <c r="H9" s="17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I9" s="17">
         <v>613.99000000000001</v>
@@ -1674,44 +1697,47 @@
       <c r="T9" s="18">
         <v>823.84000000000003</v>
       </c>
-      <c r="U9" s="19">
-        <f>MIN(C9:T9)</f>
+      <c r="U9" s="18">
+        <v>823.84000000000003</v>
+      </c>
+      <c r="V9" s="19">
+        <f>MIN(C9:U9)</f>
         <v>200.47999999999999</v>
       </c>
-      <c r="V9" s="20">
-        <f>MAX(C9:T9)</f>
+      <c r="W9" s="20">
+        <f>MAX(C9:U9)</f>
         <v>861.65999999999997</v>
       </c>
-      <c r="W9" s="20">
-        <f>AVERAGE(C9:T9)</f>
-        <v>760.96642857142865</v>
-      </c>
       <c r="X9" s="20">
-        <f>AVERAGE(Q9:T9)</f>
-        <v>823.84000000000003</v>
-      </c>
-      <c r="Y9" s="21">
-        <f>(X9/W9)-1</f>
-        <v>8.2623318280419689e-002</v>
+        <f>AVERAGE(C9:U9)</f>
+        <v>765.15800000000002</v>
+      </c>
+      <c r="Y9" s="20">
+        <f>AVERAGE(Q9:U9)</f>
+        <v>823.83999999999992</v>
       </c>
       <c r="Z9" s="21">
-        <f>(X9/U9)-1</f>
+        <f>(Y9/X9)-1</f>
+        <v>7.6692656941442117e-002</v>
+      </c>
+      <c r="AA9" s="21">
+        <f>(Y9/V9)-1</f>
         <v>3.1093375897845172</v>
       </c>
-      <c r="AA9" s="21">
-        <f>(V9/U9)-1</f>
+      <c r="AB9" s="21">
+        <f>(W9/V9)-1</f>
         <v>3.2979848363926578</v>
       </c>
-      <c r="AB9" s="22" t="s">
-        <v>44</v>
+      <c r="AC9" s="22" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="10" ht="36">
       <c r="A10" s="25" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C10" s="27"/>
       <c r="D10" s="24">
@@ -1761,44 +1787,47 @@
       <c r="T10" s="18">
         <v>639</v>
       </c>
-      <c r="U10" s="19">
-        <f>MIN(C10:T10)</f>
+      <c r="U10" s="18">
+        <v>640</v>
+      </c>
+      <c r="V10" s="19">
+        <f>MIN(C10:U10)</f>
         <v>284.13</v>
       </c>
-      <c r="V10" s="20">
-        <f>MAX(C10:T10)</f>
+      <c r="W10" s="20">
+        <f>MAX(C10:U10)</f>
         <v>700</v>
       </c>
-      <c r="W10" s="20">
-        <f>AVERAGE(C10:T10)</f>
-        <v>574.19266666666658</v>
-      </c>
       <c r="X10" s="20">
-        <f>AVERAGE(Q10:T10)</f>
-        <v>632.005</v>
-      </c>
-      <c r="Y10" s="21">
-        <f>(X10/W10)-1</f>
-        <v>0.10068455535830623</v>
+        <f>AVERAGE(C10:U10)</f>
+        <v>578.30562499999996</v>
+      </c>
+      <c r="Y10" s="20">
+        <f>AVERAGE(Q10:U10)</f>
+        <v>633.60400000000004</v>
       </c>
       <c r="Z10" s="21">
-        <f>(X10/U10)-1</f>
-        <v>1.2243515292295779</v>
+        <f>(Y10/X10)-1</f>
+        <v>9.5621368026638232e-002</v>
       </c>
       <c r="AA10" s="21">
-        <f>(V10/U10)-1</f>
+        <f>(Y10/V10)-1</f>
+        <v>1.229979234857284</v>
+      </c>
+      <c r="AB10" s="21">
+        <f>(W10/V10)-1</f>
         <v>1.4636610002463661</v>
       </c>
-      <c r="AB10" s="22" t="s">
-        <v>46</v>
+      <c r="AC10" s="22" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="11" ht="36">
       <c r="A11" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C11" s="16"/>
       <c r="D11" s="16"/>
@@ -1842,44 +1871,47 @@
       <c r="T11" s="18">
         <v>749.99000000000001</v>
       </c>
-      <c r="U11" s="19">
-        <f>MIN(C11:T11)</f>
+      <c r="U11" s="18">
+        <v>783.70000000000005</v>
+      </c>
+      <c r="V11" s="19">
+        <f>MIN(C11:U11)</f>
         <v>685.71000000000004</v>
       </c>
-      <c r="V11" s="20">
-        <f>MAX(C11:T11)</f>
+      <c r="W11" s="20">
+        <f>MAX(C11:U11)</f>
         <v>863.60000000000002</v>
       </c>
-      <c r="W11" s="20">
-        <f>AVERAGE(C11:T11)</f>
-        <v>777.26249999999993</v>
-      </c>
       <c r="X11" s="20">
-        <f>AVERAGE(Q11:T11)</f>
-        <v>807.53999999999996</v>
-      </c>
-      <c r="Y11" s="21">
-        <f>(X11/W11)-1</f>
-        <v>3.8954021324842047e-002</v>
+        <f>AVERAGE(C11:U11)</f>
+        <v>777.75769230769231</v>
+      </c>
+      <c r="Y11" s="20">
+        <f>AVERAGE(Q11:U11)</f>
+        <v>802.77199999999993</v>
       </c>
       <c r="Z11" s="21">
-        <f>(X11/U11)-1</f>
-        <v>0.17766986043662758</v>
+        <f>(Y11/X11)-1</f>
+        <v>3.2162083306546796e-002</v>
       </c>
       <c r="AA11" s="21">
-        <f>(V11/U11)-1</f>
+        <f>(Y11/V11)-1</f>
+        <v>0.17071648364468928</v>
+      </c>
+      <c r="AB11" s="21">
+        <f>(W11/V11)-1</f>
         <v>0.25942453807002952</v>
       </c>
-      <c r="AB11" s="22" t="s">
-        <v>48</v>
+      <c r="AC11" s="22" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="12" ht="18">
       <c r="A12" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C12" s="16"/>
       <c r="D12" s="17">
@@ -1920,7 +1952,7 @@
       <c r="Q12" s="17">
         <v>554.98000000000002</v>
       </c>
-      <c r="R12" s="17">
+      <c r="R12" s="18">
         <v>575.98000000000002</v>
       </c>
       <c r="S12" s="24">
@@ -1929,44 +1961,47 @@
       <c r="T12" s="24">
         <v>465</v>
       </c>
-      <c r="U12" s="19">
-        <f>MIN(C12:T12)</f>
+      <c r="U12" s="18">
+        <v>573.98000000000002</v>
+      </c>
+      <c r="V12" s="19">
+        <f>MIN(C12:U12)</f>
         <v>465</v>
       </c>
-      <c r="V12" s="20">
-        <f>MAX(C12:T12)</f>
+      <c r="W12" s="20">
+        <f>MAX(C12:U12)</f>
         <v>623.12</v>
       </c>
-      <c r="W12" s="20">
-        <f>AVERAGE(C12:T12)</f>
-        <v>549.85866666666652</v>
-      </c>
       <c r="X12" s="20">
-        <f>AVERAGE(Q12:T12)</f>
-        <v>518.74000000000001</v>
-      </c>
-      <c r="Y12" s="21">
-        <f>(X12/W12)-1</f>
-        <v>-5.6593936866200512e-002</v>
+        <f>AVERAGE(C12:U12)</f>
+        <v>551.36624999999981</v>
+      </c>
+      <c r="Y12" s="20">
+        <f>AVERAGE(Q12:U12)</f>
+        <v>529.78800000000001</v>
       </c>
       <c r="Z12" s="21">
-        <f>(X12/U12)-1</f>
-        <v>0.11556989247311833</v>
+        <f>(Y12/X12)-1</f>
+        <v>-3.9135964524487643e-002</v>
       </c>
       <c r="AA12" s="21">
-        <f>(V12/U12)-1</f>
+        <f>(Y12/V12)-1</f>
+        <v>0.13932903225806448</v>
+      </c>
+      <c r="AB12" s="21">
+        <f>(W12/V12)-1</f>
         <v>0.34004301075268817</v>
       </c>
-      <c r="AB12" s="22" t="s">
-        <v>51</v>
+      <c r="AC12" s="22" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="13" ht="36">
       <c r="A13" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C13" s="27"/>
       <c r="D13" s="24">
@@ -2002,58 +2037,61 @@
         <v>1084.8299999999999</v>
       </c>
       <c r="P13" s="17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q13" s="17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R13" s="17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="S13" s="30">
         <v>1426.5699999999999</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="U13" s="19">
-        <f>MIN(C13:T13)</f>
-        <v>684.98000000000002</v>
-      </c>
-      <c r="V13" s="20">
-        <f>MAX(C13:T13)</f>
+        <v>42</v>
+      </c>
+      <c r="U13" s="24">
+        <v>592.17999999999995</v>
+      </c>
+      <c r="V13" s="19">
+        <f>MIN(C13:U13)</f>
+        <v>592.17999999999995</v>
+      </c>
+      <c r="W13" s="20">
+        <f>MAX(C13:U13)</f>
         <v>1426.5699999999999</v>
       </c>
-      <c r="W13" s="20">
-        <f>AVERAGE(C13:T13)</f>
-        <v>943.53909090909099</v>
-      </c>
       <c r="X13" s="20">
-        <f>AVERAGE(Q13:T13)</f>
-        <v>1426.5699999999999</v>
-      </c>
-      <c r="Y13" s="21">
-        <f>(X13/W13)-1</f>
-        <v>0.51193523802549956</v>
+        <f>AVERAGE(C13:U13)</f>
+        <v>914.25916666666672</v>
+      </c>
+      <c r="Y13" s="20">
+        <f>AVERAGE(Q13:U13)</f>
+        <v>1009.375</v>
       </c>
       <c r="Z13" s="21">
-        <f>(X13/U13)-1</f>
-        <v>1.0826447487517883</v>
+        <f>(Y13/X13)-1</f>
+        <v>0.10403596354425382</v>
       </c>
       <c r="AA13" s="21">
-        <f>(V13/U13)-1</f>
-        <v>1.0826447487517883</v>
-      </c>
-      <c r="AB13" s="22" t="s">
-        <v>54</v>
+        <f>(Y13/V13)-1</f>
+        <v>0.70450707555135272</v>
+      </c>
+      <c r="AB13" s="21">
+        <f>(W13/V13)-1</f>
+        <v>1.4090141511027054</v>
+      </c>
+      <c r="AC13" s="22" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="14" ht="18">
       <c r="A14" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
@@ -2095,44 +2133,47 @@
       <c r="T14" s="18">
         <v>699</v>
       </c>
-      <c r="U14" s="19">
-        <f>MIN(C14:T14)</f>
+      <c r="U14" s="18">
+        <v>679</v>
+      </c>
+      <c r="V14" s="19">
+        <f>MIN(C14:U14)</f>
         <v>580.98000000000002</v>
       </c>
-      <c r="V14" s="20">
-        <f>MAX(C14:T14)</f>
+      <c r="W14" s="20">
+        <f>MAX(C14:U14)</f>
         <v>709.99000000000001</v>
       </c>
-      <c r="W14" s="20">
-        <f>AVERAGE(C14:T14)</f>
-        <v>650.470909090909</v>
-      </c>
       <c r="X14" s="20">
-        <f>AVERAGE(Q14:T14)</f>
-        <v>696.72250000000008</v>
-      </c>
-      <c r="Y14" s="21">
-        <f>(X14/W14)-1</f>
-        <v>7.1104780033486525e-002</v>
+        <f>AVERAGE(C14:U14)</f>
+        <v>652.84833333333324</v>
+      </c>
+      <c r="Y14" s="20">
+        <f>AVERAGE(Q14:U14)</f>
+        <v>693.17800000000011</v>
       </c>
       <c r="Z14" s="21">
-        <f>(X14/U14)-1</f>
-        <v>0.19921942235533074</v>
+        <f>(Y14/X14)-1</f>
+        <v>6.1774940070307593e-002</v>
       </c>
       <c r="AA14" s="21">
-        <f>(V14/U14)-1</f>
+        <f>(Y14/V14)-1</f>
+        <v>0.19311852387345541</v>
+      </c>
+      <c r="AB14" s="21">
+        <f>(W14/V14)-1</f>
         <v>0.22205583668973117</v>
       </c>
-      <c r="AB14" s="22" t="s">
-        <v>56</v>
+      <c r="AC14" s="22" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="15" ht="18">
       <c r="A15" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C15" s="16"/>
       <c r="D15" s="16"/>
@@ -2174,44 +2215,47 @@
       <c r="T15" s="17">
         <v>705.61000000000001</v>
       </c>
-      <c r="U15" s="19">
-        <f>MIN(C15:T15)</f>
+      <c r="U15" s="17">
+        <v>700.36000000000001</v>
+      </c>
+      <c r="V15" s="19">
+        <f>MIN(C15:U15)</f>
         <v>622.63</v>
       </c>
-      <c r="V15" s="20">
-        <f>MAX(C15:T15)</f>
+      <c r="W15" s="20">
+        <f>MAX(C15:U15)</f>
         <v>728.61000000000001</v>
       </c>
-      <c r="W15" s="20">
-        <f>AVERAGE(C15:T15)</f>
-        <v>680.08636363636356</v>
-      </c>
       <c r="X15" s="20">
-        <f>AVERAGE(Q15:T15)</f>
-        <v>704.02250000000004</v>
-      </c>
-      <c r="Y15" s="21">
-        <f>(X15/W15)-1</f>
-        <v>3.519573048877489e-002</v>
+        <f>AVERAGE(C15:U15)</f>
+        <v>681.77583333333325</v>
+      </c>
+      <c r="Y15" s="20">
+        <f>AVERAGE(Q15:U15)</f>
+        <v>703.29000000000008</v>
       </c>
       <c r="Z15" s="21">
-        <f>(X15/U15)-1</f>
-        <v>0.13072370428665514</v>
+        <f>(Y15/X15)-1</f>
+        <v>3.1556071093749249e-002</v>
       </c>
       <c r="AA15" s="21">
-        <f>(V15/U15)-1</f>
+        <f>(Y15/V15)-1</f>
+        <v>0.12954724314600985</v>
+      </c>
+      <c r="AB15" s="21">
+        <f>(W15/V15)-1</f>
         <v>0.17021344940012528</v>
       </c>
-      <c r="AB15" s="22" t="s">
-        <v>58</v>
+      <c r="AC15" s="22" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="16" ht="18">
       <c r="A16" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C16" s="27"/>
       <c r="D16" s="28"/>
@@ -2259,44 +2303,47 @@
       <c r="T16" s="17">
         <v>11004</v>
       </c>
-      <c r="U16" s="19">
-        <f>MIN(C16:T16)</f>
+      <c r="U16" s="17">
+        <v>11315.18</v>
+      </c>
+      <c r="V16" s="19">
+        <f>MIN(C16:U16)</f>
         <v>9100</v>
       </c>
-      <c r="V16" s="20">
-        <f>MAX(C16:T16)</f>
-        <v>11230</v>
-      </c>
       <c r="W16" s="20">
-        <f>AVERAGE(C16:T16)</f>
-        <v>9464.613571428572</v>
+        <f>MAX(C16:U16)</f>
+        <v>11315.18</v>
       </c>
       <c r="X16" s="20">
-        <f>AVERAGE(Q16:T16)</f>
-        <v>10278.887500000001</v>
-      </c>
-      <c r="Y16" s="21">
-        <f>(X16/W16)-1</f>
-        <v>8.6033510235381305e-002</v>
+        <f>AVERAGE(C16:U16)</f>
+        <v>9587.9846666666654</v>
+      </c>
+      <c r="Y16" s="20">
+        <f>AVERAGE(Q16:U16)</f>
+        <v>10486.146000000001</v>
       </c>
       <c r="Z16" s="21">
-        <f>(X16/U16)-1</f>
-        <v>0.12954807692307702</v>
+        <f>(Y16/X16)-1</f>
+        <v>9.3675716488769378e-002</v>
       </c>
       <c r="AA16" s="21">
-        <f>(V16/U16)-1</f>
-        <v>0.23406593406593412</v>
-      </c>
-      <c r="AB16" s="22" t="s">
-        <v>60</v>
+        <f>(Y16/V16)-1</f>
+        <v>0.15232373626373641</v>
+      </c>
+      <c r="AB16" s="21">
+        <f>(W16/V16)-1</f>
+        <v>0.24342637362637376</v>
+      </c>
+      <c r="AC16" s="22" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="17" ht="36">
       <c r="A17" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C17" s="16"/>
       <c r="D17" s="16"/>
@@ -2336,44 +2383,47 @@
       <c r="T17" s="18">
         <v>1544.76</v>
       </c>
-      <c r="U17" s="19">
-        <f>MIN(C17:T17)</f>
+      <c r="U17" s="18">
+        <v>1544.76</v>
+      </c>
+      <c r="V17" s="19">
+        <f>MIN(C17:U17)</f>
         <v>1297.6199999999999</v>
       </c>
-      <c r="V17" s="20">
-        <f>MAX(C17:T17)</f>
+      <c r="W17" s="20">
+        <f>MAX(C17:U17)</f>
         <v>1697.6199999999999</v>
       </c>
-      <c r="W17" s="20">
-        <f>AVERAGE(C17:T17)</f>
-        <v>1509.2909999999997</v>
-      </c>
       <c r="X17" s="20">
-        <f>AVERAGE(Q17:T17)</f>
-        <v>1568.595</v>
-      </c>
-      <c r="Y17" s="21">
-        <f>(X17/W17)-1</f>
-        <v>3.9292621502414304e-002</v>
+        <f>AVERAGE(C17:U17)</f>
+        <v>1512.5154545454543</v>
+      </c>
+      <c r="Y17" s="20">
+        <f>AVERAGE(Q17:U17)</f>
+        <v>1563.828</v>
       </c>
       <c r="Z17" s="21">
-        <f>(X17/U17)-1</f>
-        <v>0.20882461737642766</v>
+        <f>(Y17/X17)-1</f>
+        <v>3.3925303242581695e-002</v>
       </c>
       <c r="AA17" s="21">
-        <f>(V17/U17)-1</f>
+        <f>(Y17/V17)-1</f>
+        <v>0.20515096869653693</v>
+      </c>
+      <c r="AB17" s="21">
+        <f>(W17/V17)-1</f>
         <v>0.30825665449052875</v>
       </c>
-      <c r="AB17" s="22" t="s">
-        <v>62</v>
+      <c r="AC17" s="22" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="18" ht="18">
       <c r="A18" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B18" s="26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C18" s="27"/>
       <c r="D18" s="28"/>
@@ -2382,85 +2432,88 @@
         <v>2279</v>
       </c>
       <c r="G18" s="28" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H18" s="28" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="I18" s="28" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="J18" s="28" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K18" s="28" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L18" s="28" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M18" s="28" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N18" s="28" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="O18" s="28" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="P18" s="17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="Q18" s="17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="R18" s="17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="S18" s="17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>64</v>
-      </c>
-      <c r="U18" s="19">
-        <f>MIN(C18:T18)</f>
+        <v>65</v>
+      </c>
+      <c r="U18" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="V18" s="19">
+        <f>MIN(C18:U18)</f>
         <v>2279</v>
       </c>
-      <c r="V18" s="20">
-        <f>MAX(C18:T18)</f>
+      <c r="W18" s="20">
+        <f>MAX(C18:U18)</f>
         <v>2279</v>
       </c>
-      <c r="W18" s="20">
-        <f>AVERAGE(C18:T18)</f>
+      <c r="X18" s="20">
+        <f>AVERAGE(C18:U18)</f>
         <v>2279</v>
       </c>
-      <c r="X18" s="20" t="e">
-        <f>AVERAGE(Q18:T18)</f>
+      <c r="Y18" s="20" t="e">
+        <f>AVERAGE(Q18:U18)</f>
         <v>#NUM!</v>
       </c>
-      <c r="Y18" s="21" t="e">
-        <f>(X18/W18)-1</f>
+      <c r="Z18" s="21" t="e">
+        <f>(Y18/X18)-1</f>
         <v>#NUM!</v>
       </c>
-      <c r="Z18" s="21" t="e">
-        <f>(X18/U18)-1</f>
+      <c r="AA18" s="21" t="e">
+        <f>(Y18/V18)-1</f>
         <v>#NUM!</v>
       </c>
-      <c r="AA18" s="21">
-        <f>(V18/U18)-1</f>
+      <c r="AB18" s="21">
+        <f>(W18/V18)-1</f>
         <v>0</v>
       </c>
-      <c r="AB18" s="22" t="s">
-        <v>65</v>
+      <c r="AC18" s="22" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="19" ht="18">
       <c r="A19" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C19" s="24">
         <v>176.69</v>
@@ -2510,44 +2563,47 @@
       <c r="T19" s="30">
         <v>237.69999999999999</v>
       </c>
-      <c r="U19" s="19">
-        <f>MIN(C19:T19)</f>
+      <c r="U19" s="30">
+        <v>237.69999999999999</v>
+      </c>
+      <c r="V19" s="19">
+        <f>MIN(C19:U19)</f>
         <v>145</v>
       </c>
-      <c r="V19" s="20">
-        <f>MAX(C19:T19)</f>
+      <c r="W19" s="20">
+        <f>MAX(C19:U19)</f>
         <v>237.69999999999999</v>
       </c>
-      <c r="W19" s="20">
-        <f>AVERAGE(C19:T19)</f>
-        <v>189.14866666666663</v>
-      </c>
       <c r="X19" s="20">
-        <f>AVERAGE(Q19:T19)</f>
+        <f>AVERAGE(C19:U19)</f>
+        <v>192.18312499999996</v>
+      </c>
+      <c r="Y19" s="20">
+        <f>AVERAGE(Q19:U19)</f>
         <v>237.69999999999999</v>
       </c>
-      <c r="Y19" s="21">
-        <f>(X19/W19)-1</f>
-        <v>0.25668345534200632</v>
-      </c>
       <c r="Z19" s="21">
-        <f>(X19/U19)-1</f>
+        <f>(Y19/X19)-1</f>
+        <v>0.23684116386389298</v>
+      </c>
+      <c r="AA19" s="21">
+        <f>(Y19/V19)-1</f>
         <v>0.63931034482758609</v>
       </c>
-      <c r="AA19" s="21">
-        <f>(V19/U19)-1</f>
+      <c r="AB19" s="21">
+        <f>(W19/V19)-1</f>
         <v>0.63931034482758609</v>
       </c>
-      <c r="AB19" s="22" t="s">
-        <v>67</v>
+      <c r="AC19" s="22" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="20" ht="18">
       <c r="A20" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C20" s="17"/>
       <c r="D20" s="17"/>
@@ -2595,44 +2651,47 @@
       <c r="T20" s="18">
         <v>212.31</v>
       </c>
-      <c r="U20" s="19">
-        <f>MIN(C20:T20)</f>
+      <c r="U20" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="V20" s="19">
+        <f>MIN(C20:U20)</f>
         <v>176.91999999999999</v>
       </c>
-      <c r="V20" s="20">
-        <f>MAX(C20:T20)</f>
+      <c r="W20" s="20">
+        <f>MAX(C20:U20)</f>
         <v>212.31</v>
       </c>
-      <c r="W20" s="20">
-        <f>AVERAGE(C20:T20)</f>
+      <c r="X20" s="20">
+        <f>AVERAGE(C20:U20)</f>
         <v>188.63428571428571</v>
       </c>
-      <c r="X20" s="20">
-        <f>AVERAGE(Q20:T20)</f>
+      <c r="Y20" s="20">
+        <f>AVERAGE(Q20:U20)</f>
         <v>209.32499999999999</v>
       </c>
-      <c r="Y20" s="21">
-        <f>(X20/W20)-1</f>
+      <c r="Z20" s="21">
+        <f>(Y20/X20)-1</f>
         <v>0.10968692254097112</v>
       </c>
-      <c r="Z20" s="21">
-        <f>(X20/U20)-1</f>
+      <c r="AA20" s="21">
+        <f>(Y20/V20)-1</f>
         <v>0.18316188107619258</v>
       </c>
-      <c r="AA20" s="21">
-        <f>(V20/U20)-1</f>
+      <c r="AB20" s="21">
+        <f>(W20/V20)-1</f>
         <v>0.20003391363328071</v>
       </c>
-      <c r="AB20" s="22" t="s">
-        <v>69</v>
+      <c r="AC20" s="22" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="21" ht="18">
       <c r="A21" s="25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C21" s="28"/>
       <c r="D21" s="28"/>
@@ -2645,31 +2704,31 @@
         <v>396.77999999999997</v>
       </c>
       <c r="I21" s="28" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J21" s="28" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K21" s="28" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L21" s="28" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M21" s="28" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="N21" s="28" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O21" s="28" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="P21" s="17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="Q21" s="17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R21" s="17">
         <v>413</v>
@@ -2680,44 +2739,47 @@
       <c r="T21" s="17">
         <v>408.87</v>
       </c>
-      <c r="U21" s="19">
-        <f>MIN(C21:T21)</f>
+      <c r="U21" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="V21" s="19">
+        <f>MIN(C21:U21)</f>
         <v>396.77999999999997</v>
       </c>
-      <c r="V21" s="20">
-        <f>MAX(C21:T21)</f>
+      <c r="W21" s="20">
+        <f>MAX(C21:U21)</f>
         <v>453.01999999999998</v>
       </c>
-      <c r="W21" s="20">
-        <f>AVERAGE(C21:T21)</f>
+      <c r="X21" s="20">
+        <f>AVERAGE(C21:U21)</f>
         <v>413.68999999999994</v>
       </c>
-      <c r="X21" s="20">
-        <f>AVERAGE(Q21:T21)</f>
+      <c r="Y21" s="20">
+        <f>AVERAGE(Q21:U21)</f>
         <v>424.96333333333331</v>
       </c>
-      <c r="Y21" s="21">
-        <f>(X21/W21)-1</f>
+      <c r="Z21" s="21">
+        <f>(Y21/X21)-1</f>
         <v>2.7250678849702448e-002</v>
       </c>
-      <c r="Z21" s="21">
-        <f>(X21/U21)-1</f>
+      <c r="AA21" s="21">
+        <f>(Y21/V21)-1</f>
         <v>7.1030125846396786e-002</v>
       </c>
-      <c r="AA21" s="21">
-        <f>(V21/U21)-1</f>
+      <c r="AB21" s="21">
+        <f>(W21/V21)-1</f>
         <v>0.14174101517213566</v>
       </c>
-      <c r="AB21" s="22" t="s">
-        <v>71</v>
+      <c r="AC21" s="22" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="22" ht="54">
       <c r="A22" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C22" s="17"/>
       <c r="D22" s="17"/>
@@ -2765,44 +2827,47 @@
       <c r="T22" s="17">
         <v>600</v>
       </c>
-      <c r="U22" s="19">
-        <f>MIN(C22:T22)</f>
+      <c r="U22" s="17">
+        <v>600</v>
+      </c>
+      <c r="V22" s="19">
+        <f>MIN(C22:U22)</f>
         <v>550</v>
       </c>
-      <c r="V22" s="20">
-        <f>MAX(C22:T22)</f>
+      <c r="W22" s="20">
+        <f>MAX(C22:U22)</f>
         <v>600</v>
       </c>
-      <c r="W22" s="20">
-        <f>AVERAGE(C22:T22)</f>
-        <v>562.85714285714289</v>
-      </c>
       <c r="X22" s="20">
-        <f>AVERAGE(Q22:T22)</f>
-        <v>595</v>
-      </c>
-      <c r="Y22" s="21">
-        <f>(X22/W22)-1</f>
-        <v>5.7106598984771439e-002</v>
+        <f>AVERAGE(C22:U22)</f>
+        <v>565.33333333333337</v>
+      </c>
+      <c r="Y22" s="20">
+        <f>AVERAGE(Q22:U22)</f>
+        <v>596</v>
       </c>
       <c r="Z22" s="21">
-        <f>(X22/U22)-1</f>
-        <v>8.181818181818179e-002</v>
+        <f>(Y22/X22)-1</f>
+        <v>5.4245283018867774e-002</v>
       </c>
       <c r="AA22" s="21">
-        <f>(V22/U22)-1</f>
+        <f>(Y22/V22)-1</f>
+        <v>8.3636363636363731e-002</v>
+      </c>
+      <c r="AB22" s="21">
+        <f>(W22/V22)-1</f>
         <v>9.0909090909090828e-002</v>
       </c>
-      <c r="AB22" s="22" t="s">
-        <v>74</v>
+      <c r="AC22" s="22" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="23" ht="18">
       <c r="A23" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C23" s="17"/>
       <c r="D23" s="17"/>
@@ -2850,44 +2915,47 @@
       <c r="T23" s="18">
         <v>529.95000000000005</v>
       </c>
-      <c r="U23" s="19">
-        <f>MIN(C23:T23)</f>
+      <c r="U23" s="18">
+        <v>518</v>
+      </c>
+      <c r="V23" s="19">
+        <f>MIN(C23:U23)</f>
         <v>329</v>
       </c>
-      <c r="V23" s="20">
-        <f>MAX(C23:T23)</f>
+      <c r="W23" s="20">
+        <f>MAX(C23:U23)</f>
         <v>529.95000000000005</v>
       </c>
-      <c r="W23" s="20">
-        <f>AVERAGE(C23:T23)</f>
-        <v>464.05357142857139</v>
-      </c>
       <c r="X23" s="20">
-        <f>AVERAGE(Q23:T23)</f>
-        <v>515.46250000000009</v>
-      </c>
-      <c r="Y23" s="21">
-        <f>(X23/W23)-1</f>
-        <v>0.11078231423404028</v>
+        <f>AVERAGE(C23:U23)</f>
+        <v>467.64999999999992</v>
+      </c>
+      <c r="Y23" s="20">
+        <f>AVERAGE(Q23:U23)</f>
+        <v>515.97000000000003</v>
       </c>
       <c r="Z23" s="21">
-        <f>(X23/U23)-1</f>
-        <v>0.56675531914893651</v>
+        <f>(Y23/X23)-1</f>
+        <v>0.1033251363198977</v>
       </c>
       <c r="AA23" s="21">
-        <f>(V23/U23)-1</f>
+        <f>(Y23/V23)-1</f>
+        <v>0.56829787234042572</v>
+      </c>
+      <c r="AB23" s="21">
+        <f>(W23/V23)-1</f>
         <v>0.61079027355623117</v>
       </c>
-      <c r="AB23" s="22" t="s">
-        <v>77</v>
+      <c r="AC23" s="22" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="24" ht="18">
       <c r="A24" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C24" s="17"/>
       <c r="D24" s="17"/>
@@ -2935,44 +3003,47 @@
       <c r="T24" s="18">
         <v>476.07999999999998</v>
       </c>
-      <c r="U24" s="19">
-        <f>MIN(C24:T24)</f>
+      <c r="U24" s="18">
+        <v>475.56</v>
+      </c>
+      <c r="V24" s="19">
+        <f>MIN(C24:U24)</f>
         <v>371.14999999999998</v>
       </c>
-      <c r="V24" s="20">
-        <f>MAX(C24:T24)</f>
+      <c r="W24" s="20">
+        <f>MAX(C24:U24)</f>
         <v>513.71000000000004</v>
       </c>
-      <c r="W24" s="20">
-        <f>AVERAGE(C24:T24)</f>
-        <v>441.87428571428563</v>
-      </c>
       <c r="X24" s="20">
-        <f>AVERAGE(Q24:T24)</f>
-        <v>491.88</v>
-      </c>
-      <c r="Y24" s="21">
-        <f>(X24/W24)-1</f>
-        <v>0.11316728739913118</v>
+        <f>AVERAGE(C24:U24)</f>
+        <v>444.11999999999995</v>
+      </c>
+      <c r="Y24" s="20">
+        <f>AVERAGE(Q24:U24)</f>
+        <v>488.61599999999999</v>
       </c>
       <c r="Z24" s="21">
-        <f>(X24/U24)-1</f>
-        <v>0.32528627239660524</v>
+        <f>(Y24/X24)-1</f>
+        <v>0.10018913807079177</v>
       </c>
       <c r="AA24" s="21">
-        <f>(V24/U24)-1</f>
+        <f>(Y24/V24)-1</f>
+        <v>0.31649198437289505</v>
+      </c>
+      <c r="AB24" s="21">
+        <f>(W24/V24)-1</f>
         <v>0.38410346221204383</v>
       </c>
-      <c r="AB24" s="22" t="s">
-        <v>79</v>
+      <c r="AC24" s="22" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="25" ht="36">
       <c r="A25" s="25" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B25" s="26" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C25" s="28"/>
       <c r="D25" s="28"/>
@@ -3024,44 +3095,47 @@
       <c r="T25" s="17">
         <v>559.45000000000005</v>
       </c>
-      <c r="U25" s="19">
-        <f>MIN(C25:T25)</f>
+      <c r="U25" s="17">
+        <v>492.13999999999999</v>
+      </c>
+      <c r="V25" s="19">
+        <f>MIN(C25:U25)</f>
         <v>396</v>
       </c>
-      <c r="V25" s="20">
-        <f>MAX(C25:T25)</f>
+      <c r="W25" s="20">
+        <f>MAX(C25:U25)</f>
         <v>568.66999999999996</v>
       </c>
-      <c r="W25" s="20">
-        <f>AVERAGE(C25:T25)</f>
-        <v>517.614375</v>
-      </c>
       <c r="X25" s="20">
-        <f>AVERAGE(Q25:T25)</f>
-        <v>558.26999999999998</v>
-      </c>
-      <c r="Y25" s="21">
-        <f>(X25/W25)-1</f>
-        <v>7.8544234788687994e-002</v>
+        <f>AVERAGE(C25:U25)</f>
+        <v>516.11588235294118</v>
+      </c>
+      <c r="Y25" s="20">
+        <f>AVERAGE(Q25:U25)</f>
+        <v>545.04399999999998</v>
       </c>
       <c r="Z25" s="21">
-        <f>(X25/U25)-1</f>
-        <v>0.40977272727272718</v>
+        <f>(Y25/X25)-1</f>
+        <v>5.604965597101419e-002</v>
       </c>
       <c r="AA25" s="21">
-        <f>(V25/U25)-1</f>
+        <f>(Y25/V25)-1</f>
+        <v>0.37637373737373725</v>
+      </c>
+      <c r="AB25" s="21">
+        <f>(W25/V25)-1</f>
         <v>0.43603535353535339</v>
       </c>
-      <c r="AB25" s="22" t="s">
-        <v>82</v>
+      <c r="AC25" s="22" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="26" ht="18">
       <c r="A26" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C26" s="17"/>
       <c r="D26" s="24">
@@ -3111,44 +3185,47 @@
       <c r="T26" s="32">
         <v>370</v>
       </c>
-      <c r="U26" s="19">
-        <f>MIN(C26:T26)</f>
+      <c r="U26" s="30">
+        <v>1655.4000000000001</v>
+      </c>
+      <c r="V26" s="19">
+        <f>MIN(C26:U26)</f>
         <v>370</v>
       </c>
-      <c r="V26" s="20">
-        <f>MAX(C26:T26)</f>
-        <v>1552.5699999999999</v>
-      </c>
       <c r="W26" s="20">
-        <f>AVERAGE(C26:T26)</f>
-        <v>1079.8293333333334</v>
+        <f>MAX(C26:U26)</f>
+        <v>1655.4000000000001</v>
       </c>
       <c r="X26" s="20">
-        <f>AVERAGE(Q26:T26)</f>
-        <v>1211.2525000000001</v>
-      </c>
-      <c r="Y26" s="21">
-        <f>(X26/W26)-1</f>
-        <v>0.12170735005037847</v>
+        <f>AVERAGE(C26:U26)</f>
+        <v>1115.8025</v>
+      </c>
+      <c r="Y26" s="20">
+        <f>AVERAGE(Q26:U26)</f>
+        <v>1300.0819999999999</v>
       </c>
       <c r="Z26" s="21">
-        <f>(X26/U26)-1</f>
-        <v>2.2736554054054054</v>
+        <f>(Y26/X26)-1</f>
+        <v>0.16515422756267339</v>
       </c>
       <c r="AA26" s="21">
-        <f>(V26/U26)-1</f>
-        <v>3.196135135135135</v>
-      </c>
-      <c r="AB26" s="22" t="s">
-        <v>84</v>
+        <f>(Y26/V26)-1</f>
+        <v>2.5137351351351347</v>
+      </c>
+      <c r="AB26" s="21">
+        <f>(W26/V26)-1</f>
+        <v>3.4740540540540543</v>
+      </c>
+      <c r="AC26" s="22" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="27" ht="18">
       <c r="A27" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C27" s="17"/>
       <c r="D27" s="17"/>
@@ -3188,44 +3265,47 @@
       <c r="T27" s="29">
         <v>159.99000000000001</v>
       </c>
-      <c r="U27" s="19">
-        <f>MIN(C27:T27)</f>
+      <c r="U27" s="29">
+        <v>159.99000000000001</v>
+      </c>
+      <c r="V27" s="19">
+        <f>MIN(C27:U27)</f>
         <v>109.98999999999999</v>
       </c>
-      <c r="V27" s="20">
-        <f>MAX(C27:T27)</f>
+      <c r="W27" s="20">
+        <f>MAX(C27:U27)</f>
         <v>165.72999999999999</v>
       </c>
-      <c r="W27" s="20">
-        <f>AVERAGE(C27:T27)</f>
-        <v>139.56400000000002</v>
-      </c>
       <c r="X27" s="20">
-        <f>AVERAGE(Q27:T27)</f>
-        <v>152.49000000000001</v>
-      </c>
-      <c r="Y27" s="21">
-        <f>(X27/W27)-1</f>
-        <v>9.2617007251153405e-002</v>
+        <f>AVERAGE(C27:U27)</f>
+        <v>141.42090909090911</v>
+      </c>
+      <c r="Y27" s="20">
+        <f>AVERAGE(Q27:U27)</f>
+        <v>153.99000000000001</v>
       </c>
       <c r="Z27" s="21">
-        <f>(X27/U27)-1</f>
-        <v>0.38639876352395697</v>
+        <f>(Y27/X27)-1</f>
+        <v>8.8877175163760036e-002</v>
       </c>
       <c r="AA27" s="21">
-        <f>(V27/U27)-1</f>
+        <f>(Y27/V27)-1</f>
+        <v>0.40003636694244937</v>
+      </c>
+      <c r="AB27" s="21">
+        <f>(W27/V27)-1</f>
         <v>0.50677334303118471</v>
       </c>
-      <c r="AB27" s="22" t="s">
-        <v>86</v>
+      <c r="AC27" s="22" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="28" ht="18">
       <c r="A28" s="25" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B28" s="26" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C28" s="28"/>
       <c r="D28" s="28"/>
@@ -3265,44 +3345,47 @@
       <c r="T28" s="17">
         <v>83</v>
       </c>
-      <c r="U28" s="19">
-        <f>MIN(C28:T28)</f>
+      <c r="U28" s="17">
+        <v>81</v>
+      </c>
+      <c r="V28" s="19">
+        <f>MIN(C28:U28)</f>
         <v>68</v>
       </c>
-      <c r="V28" s="20">
-        <f>MAX(C28:T28)</f>
+      <c r="W28" s="20">
+        <f>MAX(C28:U28)</f>
         <v>83</v>
       </c>
-      <c r="W28" s="20">
-        <f>AVERAGE(C28:T28)</f>
-        <v>76.912000000000006</v>
-      </c>
       <c r="X28" s="20">
-        <f>AVERAGE(Q28:T28)</f>
-        <v>81.579999999999998</v>
-      </c>
-      <c r="Y28" s="21">
-        <f>(X28/W28)-1</f>
-        <v>6.0692739754524494e-002</v>
+        <f>AVERAGE(C28:U28)</f>
+        <v>77.283636363636361</v>
+      </c>
+      <c r="Y28" s="20">
+        <f>AVERAGE(Q28:U28)</f>
+        <v>81.463999999999999</v>
       </c>
       <c r="Z28" s="21">
-        <f>(X28/U28)-1</f>
-        <v>0.19970588235294118</v>
+        <f>(Y28/X28)-1</f>
+        <v>5.4091187126523277e-002</v>
       </c>
       <c r="AA28" s="21">
-        <f>(V28/U28)-1</f>
+        <f>(Y28/V28)-1</f>
+        <v>0.19799999999999995</v>
+      </c>
+      <c r="AB28" s="21">
+        <f>(W28/V28)-1</f>
         <v>0.22058823529411775</v>
       </c>
-      <c r="AB28" s="22" t="s">
-        <v>88</v>
+      <c r="AC28" s="22" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="29" ht="18">
       <c r="A29" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C29" s="17"/>
       <c r="D29" s="17"/>
@@ -3342,44 +3425,47 @@
       <c r="T29" s="30">
         <v>104.5</v>
       </c>
-      <c r="U29" s="19">
-        <f>MIN(C29:T29)</f>
+      <c r="U29" s="30">
+        <v>111</v>
+      </c>
+      <c r="V29" s="19">
+        <f>MIN(C29:U29)</f>
         <v>55</v>
       </c>
-      <c r="V29" s="20">
-        <f>MAX(C29:T29)</f>
-        <v>108</v>
-      </c>
       <c r="W29" s="20">
-        <f>AVERAGE(C29:T29)</f>
-        <v>80.562000000000012</v>
+        <f>MAX(C29:U29)</f>
+        <v>111</v>
       </c>
       <c r="X29" s="20">
-        <f>AVERAGE(Q29:T29)</f>
-        <v>93.965000000000003</v>
-      </c>
-      <c r="Y29" s="21">
-        <f>(X29/W29)-1</f>
-        <v>0.16636875946476004</v>
+        <f>AVERAGE(C29:U29)</f>
+        <v>83.329090909090922</v>
+      </c>
+      <c r="Y29" s="20">
+        <f>AVERAGE(Q29:U29)</f>
+        <v>97.372</v>
       </c>
       <c r="Z29" s="21">
-        <f>(X29/U29)-1</f>
-        <v>0.70845454545454545</v>
+        <f>(Y29/X29)-1</f>
+        <v>0.16852348846850362</v>
       </c>
       <c r="AA29" s="21">
-        <f>(V29/U29)-1</f>
-        <v>0.96363636363636362</v>
-      </c>
-      <c r="AB29" s="22" t="s">
-        <v>90</v>
+        <f>(Y29/V29)-1</f>
+        <v>0.77039999999999997</v>
+      </c>
+      <c r="AB29" s="21">
+        <f>(W29/V29)-1</f>
+        <v>1.0181818181818181</v>
+      </c>
+      <c r="AC29" s="22" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="30" ht="18">
       <c r="A30" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
@@ -3417,44 +3503,47 @@
       <c r="T30" s="29">
         <v>100.68000000000001</v>
       </c>
-      <c r="U30" s="19">
-        <f>MIN(C30:T30)</f>
+      <c r="U30" s="29">
+        <v>92.530000000000001</v>
+      </c>
+      <c r="V30" s="19">
+        <f>MIN(C30:U30)</f>
         <v>47.359999999999999</v>
       </c>
-      <c r="V30" s="20">
-        <f>MAX(C30:T30)</f>
+      <c r="W30" s="20">
+        <f>MAX(C30:U30)</f>
         <v>100.68000000000001</v>
       </c>
-      <c r="W30" s="20">
-        <f>AVERAGE(C30:T30)</f>
-        <v>66.832222222222228</v>
-      </c>
       <c r="X30" s="20">
-        <f>AVERAGE(Q30:T30)</f>
-        <v>82.260000000000005</v>
-      </c>
-      <c r="Y30" s="21">
-        <f>(X30/W30)-1</f>
-        <v>0.23084340554290184</v>
+        <f>AVERAGE(C30:U30)</f>
+        <v>69.402000000000001</v>
+      </c>
+      <c r="Y30" s="20">
+        <f>AVERAGE(Q30:U30)</f>
+        <v>84.314000000000007</v>
       </c>
       <c r="Z30" s="21">
-        <f>(X30/U30)-1</f>
-        <v>0.73690878378378399</v>
+        <f>(Y30/X30)-1</f>
+        <v>0.21486412495317153</v>
       </c>
       <c r="AA30" s="21">
-        <f>(V30/U30)-1</f>
+        <f>(Y30/V30)-1</f>
+        <v>0.78027871621621636</v>
+      </c>
+      <c r="AB30" s="21">
+        <f>(W30/V30)-1</f>
         <v>1.1258445945945947</v>
       </c>
-      <c r="AB30" s="22" t="s">
-        <v>92</v>
+      <c r="AC30" s="22" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="31" ht="18">
       <c r="A31" s="25" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B31" s="26" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C31" s="28"/>
       <c r="D31" s="28"/>
@@ -3490,46 +3579,49 @@
         <v>132.33000000000001</v>
       </c>
       <c r="T31" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="U31" s="19">
-        <f>MIN(C31:T31)</f>
+        <v>42</v>
+      </c>
+      <c r="U31" s="18">
+        <v>156</v>
+      </c>
+      <c r="V31" s="19">
+        <f>MIN(C31:U31)</f>
         <v>92.5</v>
       </c>
-      <c r="V31" s="20">
-        <f>MAX(C31:T31)</f>
-        <v>132.33000000000001</v>
-      </c>
       <c r="W31" s="20">
-        <f>AVERAGE(C31:T31)</f>
-        <v>110.58500000000002</v>
+        <f>MAX(C31:U31)</f>
+        <v>156</v>
       </c>
       <c r="X31" s="20">
-        <f>AVERAGE(Q31:T31)</f>
-        <v>118.39666666666669</v>
-      </c>
-      <c r="Y31" s="21">
-        <f>(X31/W31)-1</f>
-        <v>7.0639477927989081e-002</v>
+        <f>AVERAGE(C31:U31)</f>
+        <v>115.63111111111114</v>
+      </c>
+      <c r="Y31" s="20">
+        <f>AVERAGE(Q31:U31)</f>
+        <v>127.79750000000001</v>
       </c>
       <c r="Z31" s="21">
-        <f>(X31/U31)-1</f>
-        <v>0.27996396396396417</v>
+        <f>(Y31/X31)-1</f>
+        <v>0.10521726179036772</v>
       </c>
       <c r="AA31" s="21">
-        <f>(V31/U31)-1</f>
-        <v>0.43059459459459482</v>
-      </c>
-      <c r="AB31" s="22" t="s">
-        <v>94</v>
+        <f>(Y31/V31)-1</f>
+        <v>0.38159459459459466</v>
+      </c>
+      <c r="AB31" s="21">
+        <f>(W31/V31)-1</f>
+        <v>0.68648648648648658</v>
+      </c>
+      <c r="AC31" s="22" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="32" ht="18">
       <c r="A32" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C32" s="17"/>
       <c r="D32" s="17"/>
@@ -3565,44 +3657,47 @@
       <c r="T32" s="17">
         <v>210.08000000000001</v>
       </c>
-      <c r="U32" s="19">
-        <f>MIN(C32:T32)</f>
+      <c r="U32" s="18">
+        <v>238.24000000000001</v>
+      </c>
+      <c r="V32" s="19">
+        <f>MIN(C32:U32)</f>
         <v>148.88</v>
       </c>
-      <c r="V32" s="20">
-        <f t="shared" ref="V32:V52" si="0">MAX(C32:T32)</f>
+      <c r="W32" s="20">
+        <f>MAX(C32:U32)</f>
         <v>257.87</v>
       </c>
-      <c r="W32" s="20">
-        <f>AVERAGE(C32:T32)</f>
-        <v>214.23375000000001</v>
-      </c>
       <c r="X32" s="20">
-        <f>AVERAGE(Q32:T32)</f>
-        <v>233.19750000000002</v>
-      </c>
-      <c r="Y32" s="21">
-        <f>(X32/W32)-1</f>
-        <v>8.8518965849218478e-002</v>
+        <f>AVERAGE(C32:U32)</f>
+        <v>216.90111111111113</v>
+      </c>
+      <c r="Y32" s="20">
+        <f>AVERAGE(Q32:U32)</f>
+        <v>234.20600000000005</v>
       </c>
       <c r="Z32" s="21">
-        <f>(X32/U32)-1</f>
-        <v>0.56634537882858704</v>
+        <f>(Y32/X32)-1</f>
+        <v>7.9782389312077706e-002</v>
       </c>
       <c r="AA32" s="21">
-        <f>(V32/U32)-1</f>
+        <f>(Y32/V32)-1</f>
+        <v>0.57311929070392287</v>
+      </c>
+      <c r="AB32" s="21">
+        <f>(W32/V32)-1</f>
         <v>0.73206609349811935</v>
       </c>
-      <c r="AB32" s="22" t="s">
-        <v>96</v>
+      <c r="AC32" s="22" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="33" ht="18">
       <c r="A33" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C33" s="17"/>
       <c r="D33" s="17"/>
@@ -3634,44 +3729,47 @@
       <c r="T33" s="17">
         <v>147.44999999999999</v>
       </c>
-      <c r="U33" s="19">
-        <f>MIN(C33:T33)</f>
+      <c r="U33" s="18">
+        <v>162.63999999999999</v>
+      </c>
+      <c r="V33" s="19">
+        <f>MIN(C33:U33)</f>
         <v>144.94999999999999</v>
       </c>
-      <c r="V33" s="20">
-        <f t="shared" si="0"/>
-        <v>155</v>
-      </c>
       <c r="W33" s="20">
-        <f>AVERAGE(C33:T33)</f>
-        <v>150.36833333333334</v>
+        <f>MAX(C33:U33)</f>
+        <v>162.63999999999999</v>
       </c>
       <c r="X33" s="20">
-        <f>AVERAGE(Q33:T33)</f>
-        <v>148.4425</v>
-      </c>
-      <c r="Y33" s="21">
-        <f>(X33/W33)-1</f>
-        <v>-1.2807439509648577e-002</v>
+        <f>AVERAGE(C33:U33)</f>
+        <v>152.12142857142857</v>
+      </c>
+      <c r="Y33" s="20">
+        <f>AVERAGE(Q33:U33)</f>
+        <v>151.28199999999998</v>
       </c>
       <c r="Z33" s="21">
-        <f>(X33/U33)-1</f>
-        <v>2.409451535012086e-002</v>
+        <f>(Y33/X33)-1</f>
+        <v>-5.5181480959760609e-003</v>
       </c>
       <c r="AA33" s="21">
-        <f>(V33/U33)-1</f>
-        <v>6.9334253190755479e-002</v>
-      </c>
-      <c r="AB33" s="22" t="s">
-        <v>98</v>
+        <f>(Y33/V33)-1</f>
+        <v>4.3684028975508715e-002</v>
+      </c>
+      <c r="AB33" s="21">
+        <f>(W33/V33)-1</f>
+        <v>0.12204208347706103</v>
+      </c>
+      <c r="AC33" s="22" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="34" ht="18">
       <c r="A34" s="25" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B34" s="26" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C34" s="28"/>
       <c r="D34" s="28"/>
@@ -3703,44 +3801,47 @@
       <c r="T34" s="29">
         <v>189.99000000000001</v>
       </c>
-      <c r="U34" s="19">
-        <f>MIN(C34:T34)</f>
+      <c r="U34" s="29">
+        <v>199.94999999999999</v>
+      </c>
+      <c r="V34" s="19">
+        <f>MIN(C34:U34)</f>
         <v>144</v>
       </c>
-      <c r="V34" s="20">
-        <f t="shared" si="0"/>
-        <v>199.93000000000001</v>
-      </c>
       <c r="W34" s="20">
-        <f>AVERAGE(C34:T34)</f>
-        <v>178.535</v>
+        <f>MAX(C34:U34)</f>
+        <v>199.94999999999999</v>
       </c>
       <c r="X34" s="20">
-        <f>AVERAGE(Q34:T34)</f>
-        <v>177.345</v>
-      </c>
-      <c r="Y34" s="21">
-        <f>(X34/W34)-1</f>
-        <v>-6.6653597333855563e-003</v>
+        <f>AVERAGE(C34:U34)</f>
+        <v>181.59428571428572</v>
+      </c>
+      <c r="Y34" s="20">
+        <f>AVERAGE(Q34:U34)</f>
+        <v>181.86599999999999</v>
       </c>
       <c r="Z34" s="21">
-        <f>(X34/U34)-1</f>
-        <v>0.23156249999999989</v>
+        <f>(Y34/X34)-1</f>
+        <v>1.4962711224393299e-003</v>
       </c>
       <c r="AA34" s="21">
-        <f>(V34/U34)-1</f>
-        <v>0.38840277777777787</v>
-      </c>
-      <c r="AB34" s="22" t="s">
-        <v>100</v>
+        <f>(Y34/V34)-1</f>
+        <v>0.26295833333333318</v>
+      </c>
+      <c r="AB34" s="21">
+        <f>(W34/V34)-1</f>
+        <v>0.38854166666666656</v>
+      </c>
+      <c r="AC34" s="22" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="35" ht="18">
       <c r="A35" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C35" s="17"/>
       <c r="D35" s="17"/>
@@ -3765,7 +3866,7 @@
         <v>31941.080000000002</v>
       </c>
       <c r="M35" s="17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N35" s="18"/>
       <c r="O35" s="17"/>
@@ -3774,44 +3875,45 @@
       <c r="R35" s="17"/>
       <c r="S35" s="17"/>
       <c r="T35" s="17"/>
-      <c r="U35" s="19">
-        <f>MIN(C35:T35)</f>
+      <c r="U35" s="17"/>
+      <c r="V35" s="19">
+        <f>MIN(C35:U35)</f>
         <v>30731.380000000001</v>
       </c>
-      <c r="V35" s="20">
-        <f t="shared" si="0"/>
+      <c r="W35" s="20">
+        <f>MAX(C35:U35)</f>
         <v>32790.889999999999</v>
       </c>
-      <c r="W35" s="20">
-        <f>AVERAGE(C35:T35)</f>
+      <c r="X35" s="20">
+        <f>AVERAGE(C35:U35)</f>
         <v>31912.133333333331</v>
       </c>
-      <c r="X35" s="20" t="e">
-        <f>AVERAGE(Q35:T35)</f>
+      <c r="Y35" s="20" t="e">
+        <f>AVERAGE(Q35:U35)</f>
         <v>#NUM!</v>
       </c>
-      <c r="Y35" s="21" t="e">
-        <f>(X35/W35)-1</f>
+      <c r="Z35" s="21" t="e">
+        <f>(Y35/X35)-1</f>
         <v>#NUM!</v>
       </c>
-      <c r="Z35" s="21" t="e">
-        <f>(X35/U35)-1</f>
+      <c r="AA35" s="21" t="e">
+        <f>(Y35/V35)-1</f>
         <v>#NUM!</v>
       </c>
-      <c r="AA35" s="21">
-        <f>(V35/U35)-1</f>
+      <c r="AB35" s="21">
+        <f>(W35/V35)-1</f>
         <v>6.7016515366377982e-002</v>
       </c>
-      <c r="AB35" s="22" t="s">
-        <v>103</v>
+      <c r="AC35" s="22" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="36" ht="18">
       <c r="A36" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C36" s="17"/>
       <c r="D36" s="17"/>
@@ -3843,46 +3945,49 @@
         <v>721.67999999999995</v>
       </c>
       <c r="T36" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="U36" s="19">
-        <f>MIN(C36:T36)</f>
+        <v>42</v>
+      </c>
+      <c r="U36" s="17">
+        <v>1164</v>
+      </c>
+      <c r="V36" s="19">
+        <f>MIN(C36:U36)</f>
         <v>642.82000000000005</v>
       </c>
-      <c r="V36" s="20">
-        <f t="shared" si="0"/>
-        <v>721.67999999999995</v>
-      </c>
       <c r="W36" s="20">
-        <f>AVERAGE(C36:T36)</f>
-        <v>695.39333333333332</v>
+        <f>MAX(C36:U36)</f>
+        <v>1164</v>
       </c>
       <c r="X36" s="20">
-        <f>AVERAGE(Q36:T36)</f>
-        <v>721.67999999999995</v>
-      </c>
-      <c r="Y36" s="21">
-        <f>(X36/W36)-1</f>
-        <v>3.7801148510675064e-002</v>
+        <f>AVERAGE(C36:U36)</f>
+        <v>762.33714285714279</v>
+      </c>
+      <c r="Y36" s="20">
+        <f>AVERAGE(Q36:U36)</f>
+        <v>832.25999999999999</v>
       </c>
       <c r="Z36" s="21">
-        <f>(X36/U36)-1</f>
-        <v>0.12267819918484157</v>
+        <f>(Y36/X36)-1</f>
+        <v>9.1721697936421265e-002</v>
       </c>
       <c r="AA36" s="21">
-        <f>(V36/U36)-1</f>
-        <v>0.12267819918484157</v>
-      </c>
-      <c r="AB36" s="22" t="s">
-        <v>106</v>
+        <f>(Y36/V36)-1</f>
+        <v>0.29470147164058358</v>
+      </c>
+      <c r="AB36" s="21">
+        <f>(W36/V36)-1</f>
+        <v>0.81077128900780915</v>
+      </c>
+      <c r="AC36" s="22" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="37" ht="18">
       <c r="A37" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C37" s="17"/>
       <c r="D37" s="17"/>
@@ -3916,44 +4021,47 @@
       <c r="T37" s="30">
         <v>2064</v>
       </c>
-      <c r="U37" s="19">
-        <f>MIN(C37:T37)</f>
+      <c r="U37" s="30">
+        <v>2064</v>
+      </c>
+      <c r="V37" s="19">
+        <f>MIN(C37:U37)</f>
         <v>1151.71</v>
       </c>
-      <c r="V37" s="20">
-        <f t="shared" si="0"/>
+      <c r="W37" s="20">
+        <f>MAX(C37:U37)</f>
         <v>2064</v>
       </c>
-      <c r="W37" s="20">
-        <f>AVERAGE(C37:T37)</f>
-        <v>1355.1628571428573</v>
-      </c>
       <c r="X37" s="20">
-        <f>AVERAGE(Q37:T37)</f>
-        <v>1475.76</v>
-      </c>
-      <c r="Y37" s="21">
-        <f>(X37/W37)-1</f>
-        <v>8.8990885650011231e-002</v>
+        <f>AVERAGE(C37:U37)</f>
+        <v>1443.7675000000002</v>
+      </c>
+      <c r="Y37" s="20">
+        <f>AVERAGE(Q37:U37)</f>
+        <v>1593.4079999999999</v>
       </c>
       <c r="Z37" s="21">
-        <f>(X37/U37)-1</f>
-        <v>0.28136423231542662</v>
+        <f>(Y37/X37)-1</f>
+        <v>0.10364584325384785</v>
       </c>
       <c r="AA37" s="21">
-        <f>(V37/U37)-1</f>
+        <f>(Y37/V37)-1</f>
+        <v>0.38351494733917368</v>
+      </c>
+      <c r="AB37" s="21">
+        <f>(W37/V37)-1</f>
         <v>0.79211780743416305</v>
       </c>
-      <c r="AB37" s="22" t="s">
-        <v>106</v>
+      <c r="AC37" s="22" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="38" ht="18">
       <c r="A38" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C38" s="17"/>
       <c r="D38" s="17"/>
@@ -3987,44 +4095,47 @@
       <c r="T38" s="30">
         <v>3876</v>
       </c>
-      <c r="U38" s="19">
-        <f>MIN(C38:T38)</f>
+      <c r="U38" s="33" t="s">
+        <v>42</v>
+      </c>
+      <c r="V38" s="19">
+        <f>MIN(C38:U38)</f>
         <v>2159.8299999999999</v>
       </c>
-      <c r="V38" s="20">
-        <f t="shared" si="0"/>
+      <c r="W38" s="20">
+        <f>MAX(C38:U38)</f>
         <v>3876</v>
       </c>
-      <c r="W38" s="20">
-        <f>AVERAGE(C38:T38)</f>
+      <c r="X38" s="20">
+        <f>AVERAGE(C38:U38)</f>
         <v>2544.02</v>
       </c>
-      <c r="X38" s="20">
-        <f>AVERAGE(Q38:T38)</f>
+      <c r="Y38" s="20">
+        <f>AVERAGE(Q38:U38)</f>
         <v>2771.3400000000001</v>
       </c>
-      <c r="Y38" s="21">
-        <f>(X38/W38)-1</f>
+      <c r="Z38" s="21">
+        <f>(Y38/X38)-1</f>
         <v>8.9354643438337877e-002</v>
       </c>
-      <c r="Z38" s="21">
-        <f>(X38/U38)-1</f>
+      <c r="AA38" s="21">
+        <f>(Y38/V38)-1</f>
         <v>0.28312876476389359</v>
       </c>
-      <c r="AA38" s="21">
-        <f>(V38/U38)-1</f>
+      <c r="AB38" s="21">
+        <f>(W38/V38)-1</f>
         <v>0.79458568498446636</v>
       </c>
-      <c r="AB38" s="22" t="s">
-        <v>106</v>
+      <c r="AC38" s="22" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="39" ht="18">
       <c r="A39" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C39" s="17"/>
       <c r="D39" s="17"/>
@@ -4058,44 +4169,47 @@
       <c r="T39" s="30">
         <v>2130</v>
       </c>
-      <c r="U39" s="19">
-        <f>MIN(C39:T39)</f>
+      <c r="U39" s="30">
+        <v>2130</v>
+      </c>
+      <c r="V39" s="19">
+        <f>MIN(C39:U39)</f>
         <v>1310.1800000000001</v>
       </c>
-      <c r="V39" s="20">
-        <f t="shared" si="0"/>
+      <c r="W39" s="20">
+        <f>MAX(C39:U39)</f>
         <v>2130</v>
       </c>
-      <c r="W39" s="20">
-        <f>AVERAGE(C39:T39)</f>
-        <v>1434.74</v>
-      </c>
       <c r="X39" s="20">
-        <f>AVERAGE(Q39:T39)</f>
-        <v>1522.9499999999998</v>
-      </c>
-      <c r="Y39" s="21">
-        <f>(X39/W39)-1</f>
-        <v>6.1481522784615938e-002</v>
+        <f>AVERAGE(C39:U39)</f>
+        <v>1521.6475</v>
+      </c>
+      <c r="Y39" s="20">
+        <f>AVERAGE(Q39:U39)</f>
+        <v>1644.3599999999999</v>
       </c>
       <c r="Z39" s="21">
-        <f>(X39/U39)-1</f>
-        <v>0.16239753316338201</v>
+        <f>(Y39/X39)-1</f>
+        <v>8.0644498808035259e-002</v>
       </c>
       <c r="AA39" s="21">
-        <f>(V39/U39)-1</f>
+        <f>(Y39/V39)-1</f>
+        <v>0.25506418965332989</v>
+      </c>
+      <c r="AB39" s="21">
+        <f>(W39/V39)-1</f>
         <v>0.62573081561312183</v>
       </c>
-      <c r="AB39" s="22" t="s">
-        <v>106</v>
+      <c r="AC39" s="22" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="40" ht="18">
       <c r="A40" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C40" s="17"/>
       <c r="D40" s="17"/>
@@ -4117,44 +4231,47 @@
       <c r="T40" s="29">
         <v>1896</v>
       </c>
-      <c r="U40" s="19">
-        <f>MIN(C40:T40)</f>
+      <c r="U40" s="29">
         <v>1896</v>
       </c>
-      <c r="V40" s="20">
-        <f t="shared" si="0"/>
+      <c r="V40" s="19">
+        <f>MIN(C40:U40)</f>
         <v>1896</v>
       </c>
       <c r="W40" s="20">
-        <f>AVERAGE(C40:T40)</f>
+        <f>MAX(C40:U40)</f>
         <v>1896</v>
       </c>
       <c r="X40" s="20">
-        <f>AVERAGE(Q40:T40)</f>
+        <f>AVERAGE(C40:U40)</f>
         <v>1896</v>
       </c>
-      <c r="Y40" s="21">
-        <f>(X40/W40)-1</f>
+      <c r="Y40" s="20">
+        <f>AVERAGE(Q40:U40)</f>
+        <v>1896</v>
+      </c>
+      <c r="Z40" s="21">
+        <f>(Y40/X40)-1</f>
         <v>0</v>
       </c>
-      <c r="Z40" s="21">
-        <f>(X40/U40)-1</f>
+      <c r="AA40" s="21">
+        <f>(Y40/V40)-1</f>
         <v>0</v>
       </c>
-      <c r="AA40" s="21">
-        <f>(V40/U40)-1</f>
+      <c r="AB40" s="21">
+        <f>(W40/V40)-1</f>
         <v>0</v>
       </c>
-      <c r="AB40" s="22" t="s">
-        <v>106</v>
+      <c r="AC40" s="22" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="41" ht="18">
       <c r="A41" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C41" s="17"/>
       <c r="D41" s="17"/>
@@ -4186,102 +4303,106 @@
         <v>1628.6199999999999</v>
       </c>
       <c r="T41" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="U41" s="19">
-        <f>MIN(C41:T41)</f>
+        <v>42</v>
+      </c>
+      <c r="U41" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="V41" s="19">
+        <f>MIN(C41:U41)</f>
         <v>1480.5599999999999</v>
       </c>
-      <c r="V41" s="20">
-        <f t="shared" si="0"/>
+      <c r="W41" s="20">
+        <f>MAX(C41:U41)</f>
         <v>1628.6199999999999</v>
       </c>
-      <c r="W41" s="20">
-        <f>AVERAGE(C41:T41)</f>
+      <c r="X41" s="20">
+        <f>AVERAGE(C41:U41)</f>
         <v>1579.2666666666664</v>
       </c>
-      <c r="X41" s="20">
-        <f>AVERAGE(Q41:T41)</f>
+      <c r="Y41" s="20">
+        <f>AVERAGE(Q41:U41)</f>
         <v>1628.6199999999999</v>
       </c>
-      <c r="Y41" s="21">
-        <f>(X41/W41)-1</f>
+      <c r="Z41" s="21">
+        <f>(Y41/X41)-1</f>
         <v>3.1250791506606479e-002</v>
       </c>
-      <c r="Z41" s="21">
-        <f>(X41/U41)-1</f>
+      <c r="AA41" s="21">
+        <f>(Y41/V41)-1</f>
         <v>0.10000270168044523</v>
       </c>
-      <c r="AA41" s="21">
-        <f>(V41/U41)-1</f>
+      <c r="AB41" s="21">
+        <f>(W41/V41)-1</f>
         <v>0.10000270168044523</v>
       </c>
-      <c r="AB41" s="22" t="s">
-        <v>106</v>
+      <c r="AC41" s="22" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="42" ht="18">
       <c r="A42" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C42" s="17"/>
       <c r="D42" s="17">
         <v>339.45999999999998</v>
       </c>
-      <c r="E42" s="33"/>
-      <c r="F42" s="33"/>
-      <c r="G42" s="33"/>
-      <c r="H42" s="33"/>
-      <c r="I42" s="33"/>
-      <c r="J42" s="33"/>
-      <c r="K42" s="33"/>
-      <c r="L42" s="33"/>
-      <c r="M42" s="33"/>
-      <c r="N42" s="33"/>
+      <c r="E42" s="34"/>
+      <c r="F42" s="34"/>
+      <c r="G42" s="34"/>
+      <c r="H42" s="34"/>
+      <c r="I42" s="34"/>
+      <c r="J42" s="34"/>
+      <c r="K42" s="34"/>
+      <c r="L42" s="34"/>
+      <c r="M42" s="34"/>
+      <c r="N42" s="34"/>
       <c r="O42" s="17"/>
       <c r="P42" s="17"/>
       <c r="Q42" s="17"/>
       <c r="R42" s="17"/>
       <c r="S42" s="17"/>
       <c r="T42" s="17"/>
-      <c r="U42" s="19">
-        <f>MIN(C42:T42)</f>
+      <c r="U42" s="17"/>
+      <c r="V42" s="19">
+        <f>MIN(C42:U42)</f>
         <v>339.45999999999998</v>
       </c>
-      <c r="V42" s="20">
-        <f t="shared" si="0"/>
+      <c r="W42" s="20">
+        <f>MAX(C42:U42)</f>
         <v>339.45999999999998</v>
       </c>
-      <c r="W42" s="20">
-        <f>AVERAGE(C42:T42)</f>
+      <c r="X42" s="20">
+        <f>AVERAGE(C42:U42)</f>
         <v>339.45999999999998</v>
       </c>
-      <c r="X42" s="20" t="e">
-        <f>AVERAGE(Q42:T42)</f>
+      <c r="Y42" s="20" t="e">
+        <f>AVERAGE(Q42:U42)</f>
         <v>#NUM!</v>
       </c>
-      <c r="Y42" s="21" t="e">
-        <f>(X42/W42)-1</f>
+      <c r="Z42" s="21" t="e">
+        <f>(Y42/X42)-1</f>
         <v>#NUM!</v>
       </c>
-      <c r="Z42" s="21" t="e">
-        <f>(X42/U42)-1</f>
+      <c r="AA42" s="21" t="e">
+        <f>(Y42/V42)-1</f>
         <v>#NUM!</v>
       </c>
-      <c r="AA42" s="21">
-        <f>(V42/U42)-1</f>
+      <c r="AB42" s="21">
+        <f>(W42/V42)-1</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" ht="18">
       <c r="A43" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C43" s="17"/>
       <c r="D43" s="17"/>
@@ -4329,44 +4450,47 @@
       <c r="T43" s="17">
         <v>378.99000000000001</v>
       </c>
-      <c r="U43" s="19">
-        <f>MIN(C43:T43)</f>
+      <c r="U43" s="17">
         <v>378.99000000000001</v>
       </c>
-      <c r="V43" s="20">
-        <f t="shared" si="0"/>
+      <c r="V43" s="19">
+        <f>MIN(C43:U43)</f>
         <v>378.99000000000001</v>
       </c>
       <c r="W43" s="20">
-        <f>AVERAGE(C43:T43)</f>
+        <f>MAX(C43:U43)</f>
+        <v>378.99000000000001</v>
+      </c>
+      <c r="X43" s="20">
+        <f>AVERAGE(C43:U43)</f>
         <v>378.9899999999999</v>
       </c>
-      <c r="X43" s="20">
-        <f>AVERAGE(Q43:T43)</f>
+      <c r="Y43" s="20">
+        <f>AVERAGE(Q43:U43)</f>
         <v>378.99000000000001</v>
       </c>
-      <c r="Y43" s="21">
-        <f>(X43/W43)-1</f>
+      <c r="Z43" s="21">
+        <f>(Y43/X43)-1</f>
         <v>2.2204460492503131e-016</v>
       </c>
-      <c r="Z43" s="21">
-        <f>(X43/U43)-1</f>
+      <c r="AA43" s="21">
+        <f>(Y43/V43)-1</f>
         <v>0</v>
       </c>
-      <c r="AA43" s="21">
-        <f>(V43/U43)-1</f>
+      <c r="AB43" s="21">
+        <f>(W43/V43)-1</f>
         <v>0</v>
       </c>
-      <c r="AB43" s="22" t="s">
-        <v>117</v>
+      <c r="AC43" s="22" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="44" ht="18">
       <c r="A44" s="25" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B44" s="26" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C44" s="28"/>
       <c r="D44" s="28"/>
@@ -4414,44 +4538,47 @@
       <c r="T44" s="18">
         <v>117.58</v>
       </c>
-      <c r="U44" s="19">
-        <f>MIN(C44:T44)</f>
+      <c r="U44" s="18">
+        <v>117.58</v>
+      </c>
+      <c r="V44" s="19">
+        <f>MIN(C44:U44)</f>
         <v>88.329999999999998</v>
       </c>
-      <c r="V44" s="20">
-        <f t="shared" si="0"/>
+      <c r="W44" s="20">
+        <f>MAX(C44:U44)</f>
         <v>118.58</v>
       </c>
-      <c r="W44" s="20">
-        <f>AVERAGE(C44:T44)</f>
-        <v>96.901428571428582</v>
-      </c>
       <c r="X44" s="20">
-        <f>AVERAGE(Q44:T44)</f>
-        <v>118.33</v>
-      </c>
-      <c r="Y44" s="21">
-        <f>(X44/W44)-1</f>
-        <v>0.22113782783682967</v>
+        <f>AVERAGE(C44:U44)</f>
+        <v>98.280000000000001</v>
+      </c>
+      <c r="Y44" s="20">
+        <f>AVERAGE(Q44:U44)</f>
+        <v>118.17999999999999</v>
       </c>
       <c r="Z44" s="21">
-        <f>(X44/U44)-1</f>
-        <v>0.33963545794180905</v>
+        <f>(Y44/X44)-1</f>
+        <v>0.2024827024827025</v>
       </c>
       <c r="AA44" s="21">
-        <f>(V44/U44)-1</f>
+        <f>(Y44/V44)-1</f>
+        <v>0.33793728065209994</v>
+      </c>
+      <c r="AB44" s="21">
+        <f>(W44/V44)-1</f>
         <v>0.34246575342465757</v>
       </c>
-      <c r="AB44" s="22" t="s">
-        <v>120</v>
+      <c r="AC44" s="22" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="45" ht="18">
       <c r="A45" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C45" s="17"/>
       <c r="D45" s="17">
@@ -4501,44 +4628,47 @@
       <c r="T45" s="17">
         <v>44.979999999999997</v>
       </c>
-      <c r="U45" s="19">
-        <f>MIN(C45:T45)</f>
+      <c r="U45" s="17">
+        <v>39.990000000000002</v>
+      </c>
+      <c r="V45" s="19">
+        <f>MIN(C45:U45)</f>
         <v>29.989999999999998</v>
       </c>
-      <c r="V45" s="20">
-        <f t="shared" si="0"/>
+      <c r="W45" s="20">
+        <f>MAX(C45:U45)</f>
         <v>44.979999999999997</v>
       </c>
-      <c r="W45" s="20">
-        <f>AVERAGE(C45:T45)</f>
-        <v>36.752000000000002</v>
-      </c>
       <c r="X45" s="20">
-        <f>AVERAGE(Q45:T45)</f>
-        <v>37.484999999999999</v>
-      </c>
-      <c r="Y45" s="21">
-        <f>(X45/W45)-1</f>
-        <v>1.9944492816717396e-002</v>
+        <f>AVERAGE(C45:U45)</f>
+        <v>36.954375000000006</v>
+      </c>
+      <c r="Y45" s="20">
+        <f>AVERAGE(Q45:U45)</f>
+        <v>37.986000000000004</v>
       </c>
       <c r="Z45" s="21">
-        <f>(X45/U45)-1</f>
-        <v>0.24991663887962656</v>
+        <f>(Y45/X45)-1</f>
+        <v>2.7916180425186399e-002</v>
       </c>
       <c r="AA45" s="21">
-        <f>(V45/U45)-1</f>
+        <f>(Y45/V45)-1</f>
+        <v>0.26662220740246778</v>
+      </c>
+      <c r="AB45" s="21">
+        <f>(W45/V45)-1</f>
         <v>0.49983327775925313</v>
       </c>
-      <c r="AB45" s="22" t="s">
-        <v>123</v>
+      <c r="AC45" s="22" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="46" ht="18">
       <c r="A46" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C46" s="17"/>
       <c r="D46" s="17">
@@ -4588,44 +4718,47 @@
       <c r="T46" s="32">
         <v>27.989999999999998</v>
       </c>
-      <c r="U46" s="19">
-        <f>MIN(C46:T46)</f>
+      <c r="U46" s="32">
+        <v>27.989999999999998</v>
+      </c>
+      <c r="V46" s="19">
+        <f>MIN(C46:U46)</f>
         <v>25.989999999999998</v>
       </c>
-      <c r="V46" s="20">
-        <f t="shared" si="0"/>
+      <c r="W46" s="20">
+        <f>MAX(C46:U46)</f>
         <v>42</v>
       </c>
-      <c r="W46" s="20">
-        <f>AVERAGE(C46:T46)</f>
-        <v>32.018000000000001</v>
-      </c>
       <c r="X46" s="20">
-        <f>AVERAGE(Q46:T46)</f>
-        <v>34.012500000000003</v>
-      </c>
-      <c r="Y46" s="21">
-        <f>(X46/W46)-1</f>
-        <v>6.2293085139609072e-002</v>
+        <f>AVERAGE(C46:U46)</f>
+        <v>31.766249999999999</v>
+      </c>
+      <c r="Y46" s="20">
+        <f>AVERAGE(Q46:U46)</f>
+        <v>32.808000000000007</v>
       </c>
       <c r="Z46" s="21">
-        <f>(X46/U46)-1</f>
-        <v>0.30867641400538681</v>
+        <f>(Y46/X46)-1</f>
+        <v>3.279423916892954e-002</v>
       </c>
       <c r="AA46" s="21">
-        <f>(V46/U46)-1</f>
+        <f>(Y46/V46)-1</f>
+        <v>0.26233166602539471</v>
+      </c>
+      <c r="AB46" s="21">
+        <f>(W46/V46)-1</f>
         <v>0.61600615621392851</v>
       </c>
-      <c r="AB46" s="22" t="s">
-        <v>126</v>
+      <c r="AC46" s="22" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="47" ht="18">
       <c r="A47" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C47" s="17"/>
       <c r="D47" s="17">
@@ -4675,44 +4808,47 @@
       <c r="T47" s="17">
         <v>24.899999999999999</v>
       </c>
-      <c r="U47" s="19">
-        <f>MIN(C47:T47)</f>
+      <c r="U47" s="17">
+        <v>24.899999999999999</v>
+      </c>
+      <c r="V47" s="19">
+        <f>MIN(C47:U47)</f>
         <v>21.690000000000001</v>
       </c>
-      <c r="V47" s="20">
-        <f t="shared" si="0"/>
+      <c r="W47" s="20">
+        <f>MAX(C47:U47)</f>
         <v>43.990000000000002</v>
       </c>
-      <c r="W47" s="20">
-        <f>AVERAGE(C47:T47)</f>
-        <v>30.332666666666661</v>
-      </c>
       <c r="X47" s="20">
-        <f>AVERAGE(Q47:T47)</f>
-        <v>29.795000000000002</v>
-      </c>
-      <c r="Y47" s="21">
-        <f>(X47/W47)-1</f>
-        <v>-1.7725664300314081e-002</v>
+        <f>AVERAGE(C47:U47)</f>
+        <v>29.993124999999992</v>
+      </c>
+      <c r="Y47" s="20">
+        <f>AVERAGE(Q47:U47)</f>
+        <v>28.816000000000003</v>
       </c>
       <c r="Z47" s="21">
-        <f>(X47/U47)-1</f>
-        <v>0.37367450437989858</v>
+        <f>(Y47/X47)-1</f>
+        <v>-3.9246493988205344e-002</v>
       </c>
       <c r="AA47" s="21">
-        <f>(V47/U47)-1</f>
+        <f>(Y47/V47)-1</f>
+        <v>0.32853849700322724</v>
+      </c>
+      <c r="AB47" s="21">
+        <f>(W47/V47)-1</f>
         <v>1.0281235592438911</v>
       </c>
-      <c r="AB47" s="22" t="s">
-        <v>129</v>
+      <c r="AC47" s="22" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="48" ht="54">
       <c r="A48" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C48" s="17"/>
       <c r="D48" s="17"/>
@@ -4733,10 +4869,10 @@
         <v>1714.0799999999999</v>
       </c>
       <c r="K48" s="17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L48" s="17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M48" s="24">
         <v>1449.28</v>
@@ -4762,44 +4898,47 @@
       <c r="T48" s="17">
         <v>1669.76</v>
       </c>
-      <c r="U48" s="19">
-        <f>MIN(C48:T48)</f>
+      <c r="U48" s="17">
+        <v>1611.6900000000001</v>
+      </c>
+      <c r="V48" s="19">
+        <f>MIN(C48:U48)</f>
         <v>1449.28</v>
       </c>
-      <c r="V48" s="20">
-        <f t="shared" si="0"/>
+      <c r="W48" s="20">
+        <f>MAX(C48:U48)</f>
         <v>1820.77</v>
       </c>
-      <c r="W48" s="20">
-        <f>AVERAGE(C48:T48)</f>
-        <v>1716.3269230769231</v>
-      </c>
       <c r="X48" s="20">
-        <f>AVERAGE(Q48:T48)</f>
-        <v>1707.5650000000001</v>
-      </c>
-      <c r="Y48" s="21">
-        <f>(X48/W48)-1</f>
-        <v>-5.1050431937612606e-003</v>
+        <f>AVERAGE(C48:U48)</f>
+        <v>1708.8528571428571</v>
+      </c>
+      <c r="Y48" s="20">
+        <f>AVERAGE(Q48:U48)</f>
+        <v>1688.3900000000001</v>
       </c>
       <c r="Z48" s="21">
-        <f>(X48/U48)-1</f>
-        <v>0.17821607970854503</v>
+        <f>(Y48/X48)-1</f>
+        <v>-1.1974616221241074e-002</v>
       </c>
       <c r="AA48" s="21">
-        <f>(V48/U48)-1</f>
+        <f>(Y48/V48)-1</f>
+        <v>0.16498537204680952</v>
+      </c>
+      <c r="AB48" s="21">
+        <f>(W48/V48)-1</f>
         <v>0.25632727975270475</v>
       </c>
-      <c r="AB48" s="1" t="s">
-        <v>131</v>
+      <c r="AC48" s="1" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="49" ht="18">
       <c r="A49" s="25" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B49" s="26" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C49" s="28"/>
       <c r="D49" s="28"/>
@@ -4847,44 +4986,47 @@
       <c r="T49" s="17">
         <v>43.210000000000001</v>
       </c>
-      <c r="U49" s="19">
-        <f>MIN(C49:T49)</f>
+      <c r="U49" s="17">
+        <v>39.899999999999999</v>
+      </c>
+      <c r="V49" s="19">
+        <f>MIN(C49:U49)</f>
         <v>33.890000000000001</v>
       </c>
-      <c r="V49" s="20">
-        <f t="shared" si="0"/>
+      <c r="W49" s="20">
+        <f>MAX(C49:U49)</f>
         <v>43.210000000000001</v>
       </c>
-      <c r="W49" s="20">
-        <f>AVERAGE(C49:T49)</f>
-        <v>37.237857142857138</v>
-      </c>
       <c r="X49" s="20">
-        <f>AVERAGE(Q49:T49)</f>
-        <v>40.089999999999996</v>
-      </c>
-      <c r="Y49" s="21">
-        <f>(X49/W49)-1</f>
-        <v>7.6592561333512332e-002</v>
+        <f>AVERAGE(C49:U49)</f>
+        <v>37.415333333333329</v>
+      </c>
+      <c r="Y49" s="20">
+        <f>AVERAGE(Q49:U49)</f>
+        <v>40.052</v>
       </c>
       <c r="Z49" s="21">
-        <f>(X49/U49)-1</f>
-        <v>0.18294482148126279</v>
+        <f>(Y49/X49)-1</f>
+        <v>7.0470217201503926e-002</v>
       </c>
       <c r="AA49" s="21">
-        <f>(V49/U49)-1</f>
+        <f>(Y49/V49)-1</f>
+        <v>0.1818235467689584</v>
+      </c>
+      <c r="AB49" s="21">
+        <f>(W49/V49)-1</f>
         <v>0.27500737680731779</v>
       </c>
-      <c r="AB49" s="22" t="s">
-        <v>134</v>
+      <c r="AC49" s="22" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="50" ht="18">
       <c r="A50" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C50" s="17"/>
       <c r="D50" s="17"/>
@@ -4932,44 +5074,47 @@
       <c r="T50" s="18">
         <v>89.650000000000006</v>
       </c>
-      <c r="U50" s="19">
-        <f>MIN(C50:T50)</f>
+      <c r="U50" s="17">
+        <v>84.900000000000006</v>
+      </c>
+      <c r="V50" s="19">
+        <f>MIN(C50:U50)</f>
         <v>81.689999999999998</v>
       </c>
-      <c r="V50" s="20">
-        <f t="shared" si="0"/>
+      <c r="W50" s="20">
+        <f>MAX(C50:U50)</f>
         <v>93.280000000000001</v>
       </c>
-      <c r="W50" s="20">
-        <f>AVERAGE(C50:T50)</f>
-        <v>89.343571428571451</v>
-      </c>
       <c r="X50" s="20">
-        <f>AVERAGE(Q50:T50)</f>
-        <v>86.547500000000014</v>
-      </c>
-      <c r="Y50" s="21">
-        <f>(X50/W50)-1</f>
-        <v>-3.1295720373198277e-002</v>
+        <f>AVERAGE(C50:U50)</f>
+        <v>89.04733333333337</v>
+      </c>
+      <c r="Y50" s="20">
+        <f>AVERAGE(Q50:U50)</f>
+        <v>86.218000000000004</v>
       </c>
       <c r="Z50" s="21">
-        <f>(X50/U50)-1</f>
-        <v>5.9462602521728636e-002</v>
+        <f>(Y50/X50)-1</f>
+        <v>-3.1773363978708336e-002</v>
       </c>
       <c r="AA50" s="21">
-        <f>(V50/U50)-1</f>
+        <f>(Y50/V50)-1</f>
+        <v>5.5429061084588227e-002</v>
+      </c>
+      <c r="AB50" s="21">
+        <f>(W50/V50)-1</f>
         <v>0.1418778308238462</v>
       </c>
-      <c r="AB50" s="1" t="s">
-        <v>137</v>
+      <c r="AC50" s="1" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="51" ht="18">
       <c r="A51" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C51" s="17"/>
       <c r="D51" s="17"/>
@@ -5019,44 +5164,47 @@
       <c r="T51" s="17">
         <v>309.05000000000001</v>
       </c>
-      <c r="U51" s="19">
-        <f>MIN(C51:T51)</f>
+      <c r="U51" s="17">
         <v>309.05000000000001</v>
       </c>
-      <c r="V51" s="20">
-        <f t="shared" si="0"/>
+      <c r="V51" s="19">
+        <f>MIN(C51:U51)</f>
         <v>309.05000000000001</v>
       </c>
       <c r="W51" s="20">
-        <f>AVERAGE(C51:T51)</f>
+        <f>MAX(C51:U51)</f>
+        <v>309.05000000000001</v>
+      </c>
+      <c r="X51" s="20">
+        <f>AVERAGE(C51:U51)</f>
         <v>309.05000000000007</v>
       </c>
-      <c r="X51" s="20">
-        <f>AVERAGE(Q51:T51)</f>
+      <c r="Y51" s="20">
+        <f>AVERAGE(Q51:U51)</f>
         <v>309.05000000000001</v>
       </c>
-      <c r="Y51" s="21">
-        <f>(X51/W51)-1</f>
+      <c r="Z51" s="21">
+        <f>(Y51/X51)-1</f>
         <v>-2.2204460492503131e-016</v>
       </c>
-      <c r="Z51" s="21">
-        <f>(X51/U51)-1</f>
+      <c r="AA51" s="21">
+        <f>(Y51/V51)-1</f>
         <v>0</v>
       </c>
-      <c r="AA51" s="21">
-        <f>(V51/U51)-1</f>
+      <c r="AB51" s="21">
+        <f>(W51/V51)-1</f>
         <v>0</v>
       </c>
-      <c r="AB51" s="22" t="s">
-        <v>140</v>
+      <c r="AC51" s="22" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="52" ht="18">
       <c r="A52" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C52" s="17"/>
       <c r="D52" s="17"/>
@@ -5104,41 +5252,44 @@
       <c r="T52" s="17">
         <v>108.98999999999999</v>
       </c>
-      <c r="U52" s="19">
-        <f>MIN(C52:T52)</f>
+      <c r="U52" s="17">
         <v>108.98999999999999</v>
       </c>
-      <c r="V52" s="20">
-        <f t="shared" si="0"/>
+      <c r="V52" s="19">
+        <f>MIN(C52:U52)</f>
         <v>108.98999999999999</v>
       </c>
       <c r="W52" s="20">
-        <f>AVERAGE(C52:T52)</f>
+        <f>MAX(C52:U52)</f>
         <v>108.98999999999999</v>
       </c>
       <c r="X52" s="20">
-        <f>AVERAGE(Q52:T52)</f>
+        <f>AVERAGE(C52:U52)</f>
         <v>108.98999999999999</v>
       </c>
-      <c r="Y52" s="21">
-        <f>(X52/W52)-1</f>
+      <c r="Y52" s="20">
+        <f>AVERAGE(Q52:U52)</f>
+        <v>108.98999999999998</v>
+      </c>
+      <c r="Z52" s="21">
+        <f>(Y52/X52)-1</f>
+        <v>-1.1102230246251565e-016</v>
+      </c>
+      <c r="AA52" s="21">
+        <f>(Y52/V52)-1</f>
+        <v>-1.1102230246251565e-016</v>
+      </c>
+      <c r="AB52" s="21">
+        <f>(W52/V52)-1</f>
         <v>0</v>
       </c>
-      <c r="Z52" s="21">
-        <f>(X52/U52)-1</f>
-        <v>0</v>
-      </c>
-      <c r="AA52" s="21">
-        <f>(V52/U52)-1</f>
-        <v>0</v>
-      </c>
-      <c r="AB52" s="34" t="s">
-        <v>142</v>
+      <c r="AC52" s="35" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="53" ht="18">
       <c r="B53" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O53" s="17">
         <v>1.49</v>
@@ -5158,89 +5309,92 @@
       <c r="T53" s="17">
         <v>1.99</v>
       </c>
-      <c r="U53" s="19">
-        <f>MIN(C53:T53)</f>
+      <c r="U53" s="17">
+        <v>1.99</v>
+      </c>
+      <c r="V53" s="19">
+        <f>MIN(C53:U53)</f>
         <v>1.49</v>
       </c>
-      <c r="V53" s="20">
-        <f>MAX(C53:T53)</f>
+      <c r="W53" s="20">
+        <f>MAX(C53:U53)</f>
         <v>1.99</v>
       </c>
-      <c r="W53" s="20">
-        <f>AVERAGE(C53:T53)</f>
-        <v>1.5733333333333333</v>
-      </c>
       <c r="X53" s="20">
-        <f>AVERAGE(Q53:T53)</f>
-        <v>1.615</v>
-      </c>
-      <c r="Y53" s="21">
-        <f>(X53/W53)-1</f>
-        <v>2.6483050847457612e-002</v>
+        <f>AVERAGE(C53:U53)</f>
+        <v>1.6328571428571428</v>
+      </c>
+      <c r="Y53" s="20">
+        <f>AVERAGE(Q53:U53)</f>
+        <v>1.6899999999999999</v>
       </c>
       <c r="Z53" s="21">
-        <f>(X53/U53)-1</f>
-        <v>8.3892617449664364e-002</v>
+        <f>(Y53/X53)-1</f>
+        <v>3.4995625546806686e-002</v>
       </c>
       <c r="AA53" s="21">
-        <f>(V53/U53)-1</f>
+        <f>(Y53/V53)-1</f>
+        <v>0.13422818791946312</v>
+      </c>
+      <c r="AB53" s="21">
+        <f>(W53/V53)-1</f>
         <v>0.33557046979865768</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="U1:U6"/>
     <mergeCell ref="V1:V6"/>
     <mergeCell ref="W1:W6"/>
     <mergeCell ref="X1:X6"/>
     <mergeCell ref="Y1:Y6"/>
     <mergeCell ref="Z1:Z6"/>
     <mergeCell ref="AA1:AA6"/>
+    <mergeCell ref="AB1:AB6"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="B5"/>
-    <hyperlink r:id="rId2" ref="AB8"/>
-    <hyperlink r:id="rId3" ref="AB9"/>
-    <hyperlink r:id="rId4" ref="AB10"/>
-    <hyperlink r:id="rId5" ref="AB11"/>
-    <hyperlink r:id="rId6" ref="AB12"/>
-    <hyperlink r:id="rId7" ref="AB13"/>
-    <hyperlink r:id="rId8" ref="AB14"/>
-    <hyperlink r:id="rId9" ref="AB15"/>
-    <hyperlink r:id="rId10" ref="AB16"/>
-    <hyperlink r:id="rId11" ref="AB17"/>
-    <hyperlink r:id="rId12" ref="AB18"/>
-    <hyperlink r:id="rId13" ref="AB19"/>
-    <hyperlink r:id="rId14" ref="AB20"/>
-    <hyperlink r:id="rId15" ref="AB21"/>
-    <hyperlink r:id="rId16" ref="AB22"/>
-    <hyperlink r:id="rId17" ref="AB23"/>
-    <hyperlink r:id="rId18" ref="AB24"/>
-    <hyperlink r:id="rId19" ref="AB25"/>
-    <hyperlink r:id="rId20" ref="AB26"/>
-    <hyperlink r:id="rId21" ref="AB27"/>
-    <hyperlink r:id="rId22" ref="AB28"/>
-    <hyperlink r:id="rId23" ref="AB29"/>
-    <hyperlink r:id="rId24" ref="AB30"/>
-    <hyperlink r:id="rId25" ref="AB31"/>
-    <hyperlink r:id="rId26" ref="AB32"/>
-    <hyperlink r:id="rId27" ref="AB33"/>
-    <hyperlink r:id="rId28" ref="AB34"/>
-    <hyperlink r:id="rId29" ref="AB35"/>
-    <hyperlink r:id="rId30" ref="AB36"/>
-    <hyperlink r:id="rId30" ref="AB37"/>
-    <hyperlink r:id="rId30" ref="AB38"/>
-    <hyperlink r:id="rId30" ref="AB39"/>
-    <hyperlink r:id="rId30" ref="AB40"/>
-    <hyperlink r:id="rId30" ref="AB41"/>
-    <hyperlink r:id="rId31" ref="AB43"/>
-    <hyperlink r:id="rId32" ref="AB44"/>
-    <hyperlink r:id="rId33" ref="AB45"/>
-    <hyperlink r:id="rId34" ref="AB46"/>
-    <hyperlink r:id="rId35" ref="AB47"/>
-    <hyperlink r:id="rId36" ref="AB49"/>
-    <hyperlink r:id="rId37" ref="AB51"/>
-    <hyperlink r:id="rId38" ref="AB52"/>
+    <hyperlink r:id="rId2" ref="AC8"/>
+    <hyperlink r:id="rId3" ref="AC9"/>
+    <hyperlink r:id="rId4" ref="AC10"/>
+    <hyperlink r:id="rId5" ref="AC11"/>
+    <hyperlink r:id="rId6" ref="AC12"/>
+    <hyperlink r:id="rId7" ref="AC13"/>
+    <hyperlink r:id="rId8" ref="AC14"/>
+    <hyperlink r:id="rId9" ref="AC15"/>
+    <hyperlink r:id="rId10" ref="AC16"/>
+    <hyperlink r:id="rId11" ref="AC17"/>
+    <hyperlink r:id="rId12" ref="AC18"/>
+    <hyperlink r:id="rId13" ref="AC19"/>
+    <hyperlink r:id="rId14" ref="AC20"/>
+    <hyperlink r:id="rId15" ref="AC21"/>
+    <hyperlink r:id="rId16" ref="AC22"/>
+    <hyperlink r:id="rId17" ref="AC23"/>
+    <hyperlink r:id="rId18" ref="AC24"/>
+    <hyperlink r:id="rId19" ref="AC25"/>
+    <hyperlink r:id="rId20" ref="AC26"/>
+    <hyperlink r:id="rId21" ref="AC27"/>
+    <hyperlink r:id="rId22" ref="AC28"/>
+    <hyperlink r:id="rId23" ref="AC29"/>
+    <hyperlink r:id="rId24" ref="AC30"/>
+    <hyperlink r:id="rId25" ref="AC31"/>
+    <hyperlink r:id="rId26" ref="AC32"/>
+    <hyperlink r:id="rId27" ref="AC33"/>
+    <hyperlink r:id="rId28" ref="AC34"/>
+    <hyperlink r:id="rId29" ref="AC35"/>
+    <hyperlink r:id="rId30" ref="AC36"/>
+    <hyperlink r:id="rId30" ref="AC37"/>
+    <hyperlink r:id="rId30" ref="AC38"/>
+    <hyperlink r:id="rId30" ref="AC39"/>
+    <hyperlink r:id="rId30" ref="AC40"/>
+    <hyperlink r:id="rId30" ref="AC41"/>
+    <hyperlink r:id="rId31" ref="AC43"/>
+    <hyperlink r:id="rId32" ref="AC44"/>
+    <hyperlink r:id="rId33" ref="AC45"/>
+    <hyperlink r:id="rId34" ref="AC46"/>
+    <hyperlink r:id="rId35" ref="AC47"/>
+    <hyperlink r:id="rId36" ref="AC49"/>
+    <hyperlink r:id="rId37" ref="AC51"/>
+    <hyperlink r:id="rId38" ref="AC52"/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>

--- a/analyse-prix-composants.xlsx
+++ b/analyse-prix-composants.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Feuille1" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Feuille1!$A:$AB</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Feuille1!$A:$AC</definedName>
     <definedName name="Print_Titles" localSheetId="0">Feuille1!$7:$7</definedName>
   </definedNames>
   <calcPr/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="146">
   <si>
     <t xml:space="preserve">Le prix des composants IT</t>
   </si>
@@ -123,6 +123,9 @@
     <t xml:space="preserve">7 mar 2026</t>
   </si>
   <si>
+    <t xml:space="preserve">14 mar 2026</t>
+  </si>
+  <si>
     <t>Min</t>
   </si>
   <si>
@@ -247,7 +250,7 @@
     <t xml:space="preserve">PNY nVidia T600 4GB (40W)</t>
   </si>
   <si>
-    <t>https://www.amazon.fr/Nvidia-Quadro-T600-graphique-Single/dp/B0F2J9D8WV</t>
+    <t>https://www.amazon.fr/PNY-Carte-graphique-NVIDIA-Quadro/dp/B09S6RMJ8B</t>
   </si>
   <si>
     <t>Laptop</t>
@@ -431,7 +434,7 @@
     <t>Dell</t>
   </si>
   <si>
-    <t>Keybord</t>
+    <t>Keyboard</t>
   </si>
   <si>
     <t xml:space="preserve">Clavier Cherry Stream Keyboard</t>
@@ -471,7 +474,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <sz val="11.000000"/>
       <color theme="1"/>
@@ -563,6 +566,12 @@
       <sz val="11.000000"/>
       <color theme="10"/>
       <name val="Tahoma"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11.000000"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <sz val="12.000000"/>
@@ -691,7 +700,7 @@
     <xf fontId="2" fillId="3" borderId="2" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="4" borderId="0" numFmtId="43" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="38">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="3" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -795,11 +804,18 @@
       <alignment horizontal="right" vertical="center"/>
       <protection locked="1"/>
     </xf>
+    <xf fontId="16" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf fontId="10" fillId="12" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="1"/>
     </xf>
-    <xf fontId="16" fillId="0" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf fontId="17" fillId="7" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="1"/>
+    </xf>
+    <xf fontId="17" fillId="0" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="1"/>
     </xf>
@@ -1326,12 +1342,12 @@
     <col bestFit="1" min="12" max="12" style="4" width="11.7109375"/>
     <col bestFit="1" min="13" max="13" style="4" width="13.00390625"/>
     <col bestFit="1" min="14" max="15" style="4" width="14.140625"/>
-    <col customWidth="1" min="16" max="21" style="1" width="12.7109375"/>
-    <col customWidth="1" min="22" max="25" style="2" width="12.7109375"/>
-    <col customWidth="1" min="26" max="26" style="2" width="14.140625"/>
-    <col customWidth="1" min="27" max="28" style="2" width="12.7109375"/>
-    <col customWidth="1" min="29" max="29" style="5" width="42.28125"/>
-    <col min="30" max="16384" style="1" width="9.140625"/>
+    <col customWidth="1" min="16" max="22" style="1" width="12.7109375"/>
+    <col customWidth="1" min="23" max="26" style="2" width="12.7109375"/>
+    <col customWidth="1" min="27" max="27" style="2" width="14.140625"/>
+    <col customWidth="1" min="28" max="29" style="2" width="12.7109375"/>
+    <col customWidth="1" min="30" max="30" style="5" width="42.28125"/>
+    <col min="31" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" ht="33">
@@ -1345,28 +1361,29 @@
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
-      <c r="V1" s="7" t="s">
+      <c r="V1" s="1"/>
+      <c r="W1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="W1" s="7" t="s">
+      <c r="X1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="X1" s="7" t="s">
+      <c r="Y1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="Y1" s="7" t="s">
+      <c r="Z1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="Z1" s="7" t="s">
+      <c r="AA1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="AA1" s="7" t="s">
+      <c r="AB1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="AB1" s="7" t="s">
+      <c r="AC1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="AC1" s="5"/>
+      <c r="AD1" s="5"/>
     </row>
     <row r="2" ht="23.25">
       <c r="A2" s="2"/>
@@ -1379,13 +1396,14 @@
       <c r="S2" s="1"/>
       <c r="T2" s="1"/>
       <c r="U2" s="1"/>
-      <c r="V2" s="7"/>
+      <c r="V2" s="1"/>
       <c r="W2" s="7"/>
       <c r="X2" s="7"/>
       <c r="Y2" s="7"/>
       <c r="Z2" s="7"/>
       <c r="AA2" s="7"/>
       <c r="AB2" s="7"/>
+      <c r="AC2" s="7"/>
     </row>
     <row r="3" ht="18">
       <c r="A3" s="2"/>
@@ -1396,13 +1414,14 @@
       <c r="S3" s="1"/>
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
-      <c r="V3" s="7"/>
+      <c r="V3" s="1"/>
       <c r="W3" s="7"/>
       <c r="X3" s="7"/>
       <c r="Y3" s="7"/>
       <c r="Z3" s="7"/>
       <c r="AA3" s="7"/>
       <c r="AB3" s="7"/>
+      <c r="AC3" s="7"/>
     </row>
     <row r="4" ht="54">
       <c r="A4" s="2"/>
@@ -1416,13 +1435,14 @@
       <c r="S4" s="1"/>
       <c r="T4" s="1"/>
       <c r="U4" s="1"/>
-      <c r="V4" s="7"/>
+      <c r="V4" s="1"/>
       <c r="W4" s="7"/>
       <c r="X4" s="7"/>
       <c r="Y4" s="7"/>
       <c r="Z4" s="7"/>
       <c r="AA4" s="7"/>
       <c r="AB4" s="7"/>
+      <c r="AC4" s="7"/>
     </row>
     <row r="5" ht="23.25">
       <c r="A5" s="2"/>
@@ -1435,13 +1455,14 @@
       <c r="S5" s="1"/>
       <c r="T5" s="1"/>
       <c r="U5" s="1"/>
-      <c r="V5" s="7"/>
+      <c r="V5" s="1"/>
       <c r="W5" s="7"/>
       <c r="X5" s="7"/>
       <c r="Y5" s="7"/>
       <c r="Z5" s="7"/>
       <c r="AA5" s="7"/>
       <c r="AB5" s="7"/>
+      <c r="AC5" s="7"/>
     </row>
     <row r="6" ht="37.5" customHeight="1">
       <c r="A6" s="2"/>
@@ -1451,13 +1472,14 @@
       <c r="S6" s="1"/>
       <c r="T6" s="1"/>
       <c r="U6" s="1"/>
-      <c r="V6" s="7"/>
+      <c r="V6" s="1"/>
       <c r="W6" s="7"/>
       <c r="X6" s="7"/>
       <c r="Y6" s="7"/>
       <c r="Z6" s="7"/>
       <c r="AA6" s="7"/>
       <c r="AB6" s="7"/>
+      <c r="AC6" s="7"/>
     </row>
     <row r="7" ht="18">
       <c r="A7" s="10" t="s">
@@ -1523,7 +1545,7 @@
       <c r="U7" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="V7" s="13" t="s">
+      <c r="V7" s="12" t="s">
         <v>32</v>
       </c>
       <c r="W7" s="13" t="s">
@@ -1544,16 +1566,19 @@
       <c r="AB7" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="AC7" s="5" t="s">
+      <c r="AC7" s="13" t="s">
         <v>39</v>
+      </c>
+      <c r="AD7" s="5" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="8" ht="36">
       <c r="A8" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C8" s="15">
         <v>171.88</v>
@@ -1580,7 +1605,7 @@
         <v>341.57999999999998</v>
       </c>
       <c r="M8" s="17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N8" s="18">
         <v>321.14999999999998</v>
@@ -1606,48 +1631,51 @@
       <c r="U8" s="18">
         <v>366.26999999999998</v>
       </c>
-      <c r="V8" s="19">
-        <f>MIN(C8:U8)</f>
+      <c r="V8" s="18">
+        <v>366.26999999999998</v>
+      </c>
+      <c r="W8" s="19">
+        <f>MIN(C8:V8)</f>
         <v>171.88</v>
       </c>
-      <c r="W8" s="20">
-        <f>MAX(C8:U8)</f>
+      <c r="X8" s="20">
+        <f>MAX(C8:V8)</f>
         <v>367.56</v>
       </c>
-      <c r="X8" s="20">
-        <f>AVERAGE(C8:U8)</f>
-        <v>334.27733333333344</v>
-      </c>
       <c r="Y8" s="20">
-        <f>AVERAGE(Q8:U8)</f>
-        <v>366.654</v>
-      </c>
-      <c r="Z8" s="21">
-        <f>(Y8/X8)-1</f>
-        <v>9.6855704644446483e-002</v>
+        <f>AVERAGE(C8:V8)</f>
+        <v>336.27687500000013</v>
+      </c>
+      <c r="Z8" s="20">
+        <f>AVERAGE(Q8:V8)</f>
+        <v>366.58999999999997</v>
       </c>
       <c r="AA8" s="21">
-        <f>(Y8/V8)-1</f>
-        <v>1.1331975797067724</v>
+        <f>(Z8/Y8)-1</f>
+        <v>9.0143352854696879e-002</v>
       </c>
       <c r="AB8" s="21">
-        <f>(W8/V8)-1</f>
+        <f>(Z8/W8)-1</f>
+        <v>1.1328252269024901</v>
+      </c>
+      <c r="AC8" s="21">
+        <f>(X8/W8)-1</f>
         <v>1.1384686990923902</v>
       </c>
-      <c r="AC8" s="22" t="s">
-        <v>43</v>
-      </c>
-      <c r="AD8" s="23">
+      <c r="AD8" s="22" t="s">
+        <v>44</v>
+      </c>
+      <c r="AE8" s="23">
         <f>C2*1</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" ht="36">
       <c r="A9" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C9" s="16"/>
       <c r="D9" s="24">
@@ -1659,7 +1687,7 @@
         <v>686</v>
       </c>
       <c r="H9" s="17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I9" s="17">
         <v>613.99000000000001</v>
@@ -1700,44 +1728,47 @@
       <c r="U9" s="18">
         <v>823.84000000000003</v>
       </c>
-      <c r="V9" s="19">
-        <f>MIN(C9:U9)</f>
+      <c r="V9" s="18">
+        <v>978.75</v>
+      </c>
+      <c r="W9" s="19">
+        <f>MIN(C9:V9)</f>
         <v>200.47999999999999</v>
       </c>
-      <c r="W9" s="20">
-        <f>MAX(C9:U9)</f>
-        <v>861.65999999999997</v>
-      </c>
       <c r="X9" s="20">
-        <f>AVERAGE(C9:U9)</f>
-        <v>765.15800000000002</v>
+        <f>MAX(C9:V9)</f>
+        <v>978.75</v>
       </c>
       <c r="Y9" s="20">
-        <f>AVERAGE(Q9:U9)</f>
-        <v>823.83999999999992</v>
-      </c>
-      <c r="Z9" s="21">
-        <f>(Y9/X9)-1</f>
-        <v>7.6692656941442117e-002</v>
+        <f>AVERAGE(C9:V9)</f>
+        <v>778.50750000000005</v>
+      </c>
+      <c r="Z9" s="20">
+        <f>AVERAGE(Q9:V9)</f>
+        <v>849.6583333333333</v>
       </c>
       <c r="AA9" s="21">
-        <f>(Y9/V9)-1</f>
-        <v>3.1093375897845172</v>
+        <f>(Z9/Y9)-1</f>
+        <v>9.1393895798477454e-002</v>
       </c>
       <c r="AB9" s="21">
-        <f>(W9/V9)-1</f>
-        <v>3.2979848363926578</v>
-      </c>
-      <c r="AC9" s="22" t="s">
-        <v>45</v>
+        <f>(Z9/W9)-1</f>
+        <v>3.2381201782388933</v>
+      </c>
+      <c r="AC9" s="21">
+        <f>(X9/W9)-1</f>
+        <v>3.8820331205107745</v>
+      </c>
+      <c r="AD9" s="22" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="10" ht="36">
       <c r="A10" s="25" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C10" s="27"/>
       <c r="D10" s="24">
@@ -1790,44 +1821,47 @@
       <c r="U10" s="18">
         <v>640</v>
       </c>
-      <c r="V10" s="19">
-        <f>MIN(C10:U10)</f>
+      <c r="V10" s="18">
+        <v>696.10000000000002</v>
+      </c>
+      <c r="W10" s="19">
+        <f>MIN(C10:V10)</f>
         <v>284.13</v>
       </c>
-      <c r="W10" s="20">
-        <f>MAX(C10:U10)</f>
+      <c r="X10" s="20">
+        <f>MAX(C10:V10)</f>
         <v>700</v>
       </c>
-      <c r="X10" s="20">
-        <f>AVERAGE(C10:U10)</f>
-        <v>578.30562499999996</v>
-      </c>
       <c r="Y10" s="20">
-        <f>AVERAGE(Q10:U10)</f>
-        <v>633.60400000000004</v>
-      </c>
-      <c r="Z10" s="21">
-        <f>(Y10/X10)-1</f>
-        <v>9.5621368026638232e-002</v>
+        <f>AVERAGE(C10:V10)</f>
+        <v>585.23470588235296</v>
+      </c>
+      <c r="Z10" s="20">
+        <f>AVERAGE(Q10:V10)</f>
+        <v>644.01999999999998</v>
       </c>
       <c r="AA10" s="21">
-        <f>(Y10/V10)-1</f>
-        <v>1.229979234857284</v>
+        <f>(Z10/Y10)-1</f>
+        <v>0.10044738209607207</v>
       </c>
       <c r="AB10" s="21">
-        <f>(W10/V10)-1</f>
+        <f>(Z10/W10)-1</f>
+        <v>1.2666385105409494</v>
+      </c>
+      <c r="AC10" s="21">
+        <f>(X10/W10)-1</f>
         <v>1.4636610002463661</v>
       </c>
-      <c r="AC10" s="22" t="s">
-        <v>47</v>
+      <c r="AD10" s="22" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="11" ht="36">
       <c r="A11" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C11" s="16"/>
       <c r="D11" s="16"/>
@@ -1874,44 +1908,47 @@
       <c r="U11" s="18">
         <v>783.70000000000005</v>
       </c>
-      <c r="V11" s="19">
-        <f>MIN(C11:U11)</f>
+      <c r="V11" s="18">
+        <v>807.03999999999996</v>
+      </c>
+      <c r="W11" s="19">
+        <f>MIN(C11:V11)</f>
         <v>685.71000000000004</v>
       </c>
-      <c r="W11" s="20">
-        <f>MAX(C11:U11)</f>
+      <c r="X11" s="20">
+        <f>MAX(C11:V11)</f>
         <v>863.60000000000002</v>
       </c>
-      <c r="X11" s="20">
-        <f>AVERAGE(C11:U11)</f>
-        <v>777.75769230769231</v>
-      </c>
       <c r="Y11" s="20">
-        <f>AVERAGE(Q11:U11)</f>
-        <v>802.77199999999993</v>
-      </c>
-      <c r="Z11" s="21">
-        <f>(Y11/X11)-1</f>
-        <v>3.2162083306546796e-002</v>
+        <f>AVERAGE(C11:V11)</f>
+        <v>779.84928571428566</v>
+      </c>
+      <c r="Z11" s="20">
+        <f>AVERAGE(Q11:V11)</f>
+        <v>803.48333333333323</v>
       </c>
       <c r="AA11" s="21">
-        <f>(Y11/V11)-1</f>
-        <v>0.17071648364468928</v>
+        <f>(Z11/Y11)-1</f>
+        <v>3.0305916863667459e-002</v>
       </c>
       <c r="AB11" s="21">
-        <f>(W11/V11)-1</f>
+        <f>(Z11/W11)-1</f>
+        <v>0.17175385123934772</v>
+      </c>
+      <c r="AC11" s="21">
+        <f>(X11/W11)-1</f>
         <v>0.25942453807002952</v>
       </c>
-      <c r="AC11" s="22" t="s">
-        <v>49</v>
+      <c r="AD11" s="22" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="12" ht="18">
       <c r="A12" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C12" s="16"/>
       <c r="D12" s="17">
@@ -1964,44 +2001,47 @@
       <c r="U12" s="18">
         <v>573.98000000000002</v>
       </c>
-      <c r="V12" s="19">
-        <f>MIN(C12:U12)</f>
+      <c r="V12" s="18">
+        <v>573.98000000000002</v>
+      </c>
+      <c r="W12" s="19">
+        <f>MIN(C12:V12)</f>
         <v>465</v>
       </c>
-      <c r="W12" s="20">
-        <f>MAX(C12:U12)</f>
+      <c r="X12" s="20">
+        <f>MAX(C12:V12)</f>
         <v>623.12</v>
       </c>
-      <c r="X12" s="20">
-        <f>AVERAGE(C12:U12)</f>
-        <v>551.36624999999981</v>
-      </c>
       <c r="Y12" s="20">
-        <f>AVERAGE(Q12:U12)</f>
-        <v>529.78800000000001</v>
-      </c>
-      <c r="Z12" s="21">
-        <f>(Y12/X12)-1</f>
-        <v>-3.9135964524487643e-002</v>
+        <f>AVERAGE(C12:V12)</f>
+        <v>552.69647058823512</v>
+      </c>
+      <c r="Z12" s="20">
+        <f>AVERAGE(Q12:V12)</f>
+        <v>537.15333333333331</v>
       </c>
       <c r="AA12" s="21">
-        <f>(Y12/V12)-1</f>
-        <v>0.13932903225806448</v>
+        <f>(Z12/Y12)-1</f>
+        <v>-2.8122374724700583e-002</v>
       </c>
       <c r="AB12" s="21">
-        <f>(W12/V12)-1</f>
+        <f>(Z12/W12)-1</f>
+        <v>0.15516845878136198</v>
+      </c>
+      <c r="AC12" s="21">
+        <f>(X12/W12)-1</f>
         <v>0.34004301075268817</v>
       </c>
-      <c r="AC12" s="22" t="s">
-        <v>52</v>
+      <c r="AD12" s="22" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="13" ht="36">
       <c r="A13" s="25" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C13" s="27"/>
       <c r="D13" s="24">
@@ -2037,61 +2077,64 @@
         <v>1084.8299999999999</v>
       </c>
       <c r="P13" s="17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q13" s="17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="R13" s="17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="S13" s="30">
         <v>1426.5699999999999</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="U13" s="24">
         <v>592.17999999999995</v>
       </c>
-      <c r="V13" s="19">
-        <f>MIN(C13:U13)</f>
+      <c r="V13" s="24">
+        <v>606.50999999999999</v>
+      </c>
+      <c r="W13" s="19">
+        <f>MIN(C13:V13)</f>
         <v>592.17999999999995</v>
       </c>
-      <c r="W13" s="20">
-        <f>MAX(C13:U13)</f>
+      <c r="X13" s="20">
+        <f>MAX(C13:V13)</f>
         <v>1426.5699999999999</v>
       </c>
-      <c r="X13" s="20">
-        <f>AVERAGE(C13:U13)</f>
-        <v>914.25916666666672</v>
-      </c>
       <c r="Y13" s="20">
-        <f>AVERAGE(Q13:U13)</f>
-        <v>1009.375</v>
-      </c>
-      <c r="Z13" s="21">
-        <f>(Y13/X13)-1</f>
-        <v>0.10403596354425382</v>
+        <f>AVERAGE(C13:V13)</f>
+        <v>890.58615384615393</v>
+      </c>
+      <c r="Z13" s="20">
+        <f>AVERAGE(Q13:V13)</f>
+        <v>875.0866666666667</v>
       </c>
       <c r="AA13" s="21">
-        <f>(Y13/V13)-1</f>
-        <v>0.70450707555135272</v>
+        <f>(Z13/Y13)-1</f>
+        <v>-1.7403692065669274e-002</v>
       </c>
       <c r="AB13" s="21">
-        <f>(W13/V13)-1</f>
+        <f>(Z13/W13)-1</f>
+        <v>0.4777376248212819</v>
+      </c>
+      <c r="AC13" s="21">
+        <f>(X13/W13)-1</f>
         <v>1.4090141511027054</v>
       </c>
-      <c r="AC13" s="22" t="s">
-        <v>55</v>
+      <c r="AD13" s="22" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="14" ht="18">
       <c r="A14" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
@@ -2136,44 +2179,47 @@
       <c r="U14" s="18">
         <v>679</v>
       </c>
-      <c r="V14" s="19">
-        <f>MIN(C14:U14)</f>
+      <c r="V14" s="18">
+        <v>669.10000000000002</v>
+      </c>
+      <c r="W14" s="19">
+        <f>MIN(C14:V14)</f>
         <v>580.98000000000002</v>
       </c>
-      <c r="W14" s="20">
-        <f>MAX(C14:U14)</f>
+      <c r="X14" s="20">
+        <f>MAX(C14:V14)</f>
         <v>709.99000000000001</v>
       </c>
-      <c r="X14" s="20">
-        <f>AVERAGE(C14:U14)</f>
-        <v>652.84833333333324</v>
-      </c>
       <c r="Y14" s="20">
-        <f>AVERAGE(Q14:U14)</f>
-        <v>693.17800000000011</v>
-      </c>
-      <c r="Z14" s="21">
-        <f>(Y14/X14)-1</f>
-        <v>6.1774940070307593e-002</v>
+        <f>AVERAGE(C14:V14)</f>
+        <v>654.09846153846149</v>
+      </c>
+      <c r="Z14" s="20">
+        <f>AVERAGE(Q14:V14)</f>
+        <v>689.16500000000008</v>
       </c>
       <c r="AA14" s="21">
-        <f>(Y14/V14)-1</f>
-        <v>0.19311852387345541</v>
+        <f>(Z14/Y14)-1</f>
+        <v>5.3610489128901095e-002</v>
       </c>
       <c r="AB14" s="21">
-        <f>(W14/V14)-1</f>
+        <f>(Z14/W14)-1</f>
+        <v>0.18621122930221357</v>
+      </c>
+      <c r="AC14" s="21">
+        <f>(X14/W14)-1</f>
         <v>0.22205583668973117</v>
       </c>
-      <c r="AC14" s="22" t="s">
-        <v>57</v>
+      <c r="AD14" s="22" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="15" ht="18">
       <c r="A15" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C15" s="16"/>
       <c r="D15" s="16"/>
@@ -2218,44 +2264,47 @@
       <c r="U15" s="17">
         <v>700.36000000000001</v>
       </c>
-      <c r="V15" s="19">
-        <f>MIN(C15:U15)</f>
+      <c r="V15" s="17">
+        <v>684.46000000000004</v>
+      </c>
+      <c r="W15" s="19">
+        <f>MIN(C15:V15)</f>
         <v>622.63</v>
       </c>
-      <c r="W15" s="20">
-        <f>MAX(C15:U15)</f>
+      <c r="X15" s="20">
+        <f>MAX(C15:V15)</f>
         <v>728.61000000000001</v>
       </c>
-      <c r="X15" s="20">
-        <f>AVERAGE(C15:U15)</f>
-        <v>681.77583333333325</v>
-      </c>
       <c r="Y15" s="20">
-        <f>AVERAGE(Q15:U15)</f>
-        <v>703.29000000000008</v>
-      </c>
-      <c r="Z15" s="21">
-        <f>(Y15/X15)-1</f>
-        <v>3.1556071093749249e-002</v>
+        <f>AVERAGE(C15:V15)</f>
+        <v>681.98230769230759</v>
+      </c>
+      <c r="Z15" s="20">
+        <f>AVERAGE(Q15:V15)</f>
+        <v>700.15166666666664</v>
       </c>
       <c r="AA15" s="21">
-        <f>(Y15/V15)-1</f>
-        <v>0.12954724314600985</v>
+        <f>(Z15/Y15)-1</f>
+        <v>2.6641979959627582e-002</v>
       </c>
       <c r="AB15" s="21">
-        <f>(W15/V15)-1</f>
+        <f>(Z15/W15)-1</f>
+        <v>0.1245067964387625</v>
+      </c>
+      <c r="AC15" s="21">
+        <f>(X15/W15)-1</f>
         <v>0.17021344940012528</v>
       </c>
-      <c r="AC15" s="22" t="s">
-        <v>59</v>
+      <c r="AD15" s="22" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="16" ht="18">
       <c r="A16" s="25" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C16" s="27"/>
       <c r="D16" s="28"/>
@@ -2306,44 +2355,47 @@
       <c r="U16" s="17">
         <v>11315.18</v>
       </c>
-      <c r="V16" s="19">
-        <f>MIN(C16:U16)</f>
+      <c r="V16" s="17">
+        <v>10867.4</v>
+      </c>
+      <c r="W16" s="19">
+        <f>MIN(C16:V16)</f>
         <v>9100</v>
       </c>
-      <c r="W16" s="20">
-        <f>MAX(C16:U16)</f>
+      <c r="X16" s="20">
+        <f>MAX(C16:V16)</f>
         <v>11315.18</v>
       </c>
-      <c r="X16" s="20">
-        <f>AVERAGE(C16:U16)</f>
-        <v>9587.9846666666654</v>
-      </c>
       <c r="Y16" s="20">
-        <f>AVERAGE(Q16:U16)</f>
-        <v>10486.146000000001</v>
-      </c>
-      <c r="Z16" s="21">
-        <f>(Y16/X16)-1</f>
-        <v>9.3675716488769378e-002</v>
+        <f>AVERAGE(C16:V16)</f>
+        <v>9667.948124999999</v>
+      </c>
+      <c r="Z16" s="20">
+        <f>AVERAGE(Q16:V16)</f>
+        <v>10549.688333333334</v>
       </c>
       <c r="AA16" s="21">
-        <f>(Y16/V16)-1</f>
-        <v>0.15232373626373641</v>
+        <f>(Z16/Y16)-1</f>
+        <v>9.1202414093769724e-002</v>
       </c>
       <c r="AB16" s="21">
-        <f>(W16/V16)-1</f>
+        <f>(Z16/W16)-1</f>
+        <v>0.15930641025641035</v>
+      </c>
+      <c r="AC16" s="21">
+        <f>(X16/W16)-1</f>
         <v>0.24342637362637376</v>
       </c>
-      <c r="AC16" s="22" t="s">
-        <v>61</v>
+      <c r="AD16" s="22" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="17" ht="36">
       <c r="A17" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C17" s="16"/>
       <c r="D17" s="16"/>
@@ -2386,44 +2438,47 @@
       <c r="U17" s="18">
         <v>1544.76</v>
       </c>
-      <c r="V17" s="19">
-        <f>MIN(C17:U17)</f>
+      <c r="V17" s="18">
+        <v>1611.1400000000001</v>
+      </c>
+      <c r="W17" s="19">
+        <f>MIN(C17:V17)</f>
         <v>1297.6199999999999</v>
       </c>
-      <c r="W17" s="20">
-        <f>MAX(C17:U17)</f>
+      <c r="X17" s="20">
+        <f>MAX(C17:V17)</f>
         <v>1697.6199999999999</v>
       </c>
-      <c r="X17" s="20">
-        <f>AVERAGE(C17:U17)</f>
-        <v>1512.5154545454543</v>
-      </c>
       <c r="Y17" s="20">
-        <f>AVERAGE(Q17:U17)</f>
-        <v>1563.828</v>
-      </c>
-      <c r="Z17" s="21">
-        <f>(Y17/X17)-1</f>
-        <v>3.3925303242581695e-002</v>
+        <f>AVERAGE(C17:V17)</f>
+        <v>1520.7341666666664</v>
+      </c>
+      <c r="Z17" s="20">
+        <f>AVERAGE(Q17:V17)</f>
+        <v>1571.7133333333334</v>
       </c>
       <c r="AA17" s="21">
-        <f>(Y17/V17)-1</f>
-        <v>0.20515096869653693</v>
+        <f>(Z17/Y17)-1</f>
+        <v>3.3522733811136352e-002</v>
       </c>
       <c r="AB17" s="21">
-        <f>(W17/V17)-1</f>
+        <f>(Z17/W17)-1</f>
+        <v>0.21122773487872681</v>
+      </c>
+      <c r="AC17" s="21">
+        <f>(X17/W17)-1</f>
         <v>0.30825665449052875</v>
       </c>
-      <c r="AC17" s="22" t="s">
-        <v>63</v>
+      <c r="AD17" s="22" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="18" ht="18">
       <c r="A18" s="25" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B18" s="26" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C18" s="27"/>
       <c r="D18" s="28"/>
@@ -2432,88 +2487,91 @@
         <v>2279</v>
       </c>
       <c r="G18" s="28" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H18" s="28" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I18" s="28" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J18" s="28" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K18" s="28" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="L18" s="28" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="M18" s="28" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="N18" s="28" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="O18" s="28" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P18" s="17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="Q18" s="17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="R18" s="17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="S18" s="17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="V18" s="19">
-        <f>MIN(C18:U18)</f>
+        <v>66</v>
+      </c>
+      <c r="V18" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="W18" s="19">
+        <f>MIN(C18:V18)</f>
         <v>2279</v>
       </c>
-      <c r="W18" s="20">
-        <f>MAX(C18:U18)</f>
+      <c r="X18" s="20">
+        <f>MAX(C18:V18)</f>
         <v>2279</v>
       </c>
-      <c r="X18" s="20">
-        <f>AVERAGE(C18:U18)</f>
+      <c r="Y18" s="20">
+        <f>AVERAGE(C18:V18)</f>
         <v>2279</v>
       </c>
-      <c r="Y18" s="20" t="e">
-        <f>AVERAGE(Q18:U18)</f>
+      <c r="Z18" s="20" t="e">
+        <f>AVERAGE(Q18:V18)</f>
         <v>#NUM!</v>
       </c>
-      <c r="Z18" s="21" t="e">
-        <f>(Y18/X18)-1</f>
+      <c r="AA18" s="21" t="e">
+        <f>(Z18/Y18)-1</f>
         <v>#NUM!</v>
       </c>
-      <c r="AA18" s="21" t="e">
-        <f>(Y18/V18)-1</f>
+      <c r="AB18" s="21" t="e">
+        <f>(Z18/W18)-1</f>
         <v>#NUM!</v>
       </c>
-      <c r="AB18" s="21">
-        <f>(W18/V18)-1</f>
+      <c r="AC18" s="21">
+        <f>(X18/W18)-1</f>
         <v>0</v>
       </c>
-      <c r="AC18" s="22" t="s">
-        <v>66</v>
+      <c r="AD18" s="22" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="19" ht="18">
       <c r="A19" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C19" s="24">
         <v>176.69</v>
@@ -2566,44 +2624,47 @@
       <c r="U19" s="30">
         <v>237.69999999999999</v>
       </c>
-      <c r="V19" s="19">
-        <f>MIN(C19:U19)</f>
+      <c r="V19" s="30">
+        <v>228</v>
+      </c>
+      <c r="W19" s="19">
+        <f>MIN(C19:V19)</f>
         <v>145</v>
       </c>
-      <c r="W19" s="20">
-        <f>MAX(C19:U19)</f>
+      <c r="X19" s="20">
+        <f>MAX(C19:V19)</f>
         <v>237.69999999999999</v>
       </c>
-      <c r="X19" s="20">
-        <f>AVERAGE(C19:U19)</f>
-        <v>192.18312499999996</v>
-      </c>
       <c r="Y19" s="20">
-        <f>AVERAGE(Q19:U19)</f>
-        <v>237.69999999999999</v>
-      </c>
-      <c r="Z19" s="21">
-        <f>(Y19/X19)-1</f>
-        <v>0.23684116386389298</v>
+        <f>AVERAGE(C19:V19)</f>
+        <v>194.28999999999996</v>
+      </c>
+      <c r="Z19" s="20">
+        <f>AVERAGE(Q19:V19)</f>
+        <v>236.08333333333334</v>
       </c>
       <c r="AA19" s="21">
-        <f>(Y19/V19)-1</f>
+        <f>(Z19/Y19)-1</f>
+        <v>0.21510800006862629</v>
+      </c>
+      <c r="AB19" s="21">
+        <f>(Z19/W19)-1</f>
+        <v>0.62816091954023001</v>
+      </c>
+      <c r="AC19" s="21">
+        <f>(X19/W19)-1</f>
         <v>0.63931034482758609</v>
       </c>
-      <c r="AB19" s="21">
-        <f>(W19/V19)-1</f>
-        <v>0.63931034482758609</v>
-      </c>
-      <c r="AC19" s="22" t="s">
-        <v>68</v>
+      <c r="AD19" s="22" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="20" ht="18">
       <c r="A20" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C20" s="17"/>
       <c r="D20" s="17"/>
@@ -2652,46 +2713,49 @@
         <v>212.31</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="V20" s="19">
-        <f>MIN(C20:U20)</f>
+        <v>43</v>
+      </c>
+      <c r="V20" s="17">
+        <v>229.94999999999999</v>
+      </c>
+      <c r="W20" s="19">
+        <f>MIN(C20:V20)</f>
         <v>176.91999999999999</v>
       </c>
-      <c r="W20" s="20">
-        <f>MAX(C20:U20)</f>
-        <v>212.31</v>
-      </c>
       <c r="X20" s="20">
-        <f>AVERAGE(C20:U20)</f>
-        <v>188.63428571428571</v>
+        <f>MAX(C20:V20)</f>
+        <v>229.94999999999999</v>
       </c>
       <c r="Y20" s="20">
-        <f>AVERAGE(Q20:U20)</f>
-        <v>209.32499999999999</v>
-      </c>
-      <c r="Z20" s="21">
-        <f>(Y20/X20)-1</f>
-        <v>0.10968692254097112</v>
+        <f>AVERAGE(C20:V20)</f>
+        <v>191.38866666666667</v>
+      </c>
+      <c r="Z20" s="20">
+        <f>AVERAGE(Q20:V20)</f>
+        <v>213.44999999999999</v>
       </c>
       <c r="AA20" s="21">
-        <f>(Y20/V20)-1</f>
-        <v>0.18316188107619258</v>
+        <f>(Z20/Y20)-1</f>
+        <v>0.11526980002298992</v>
       </c>
       <c r="AB20" s="21">
-        <f>(W20/V20)-1</f>
-        <v>0.20003391363328071</v>
-      </c>
-      <c r="AC20" s="22" t="s">
-        <v>70</v>
+        <f>(Z20/W20)-1</f>
+        <v>0.20647750395659048</v>
+      </c>
+      <c r="AC20" s="21">
+        <f>(X20/W20)-1</f>
+        <v>0.29973999547818231</v>
+      </c>
+      <c r="AD20" s="22" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="21" ht="18">
       <c r="A21" s="25" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C21" s="28"/>
       <c r="D21" s="28"/>
@@ -2704,31 +2768,31 @@
         <v>396.77999999999997</v>
       </c>
       <c r="I21" s="28" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="J21" s="28" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K21" s="28" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L21" s="28" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M21" s="28" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N21" s="28" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O21" s="28" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="P21" s="17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="Q21" s="17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="R21" s="17">
         <v>413</v>
@@ -2740,46 +2804,49 @@
         <v>408.87</v>
       </c>
       <c r="U21" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="V21" s="19">
-        <f>MIN(C21:U21)</f>
+        <v>43</v>
+      </c>
+      <c r="V21" s="17">
+        <v>453.04000000000002</v>
+      </c>
+      <c r="W21" s="19">
+        <f>MIN(C21:V21)</f>
         <v>396.77999999999997</v>
       </c>
-      <c r="W21" s="20">
-        <f>MAX(C21:U21)</f>
-        <v>453.01999999999998</v>
-      </c>
       <c r="X21" s="20">
-        <f>AVERAGE(C21:U21)</f>
-        <v>413.68999999999994</v>
+        <f>MAX(C21:V21)</f>
+        <v>453.04000000000002</v>
       </c>
       <c r="Y21" s="20">
-        <f>AVERAGE(Q21:U21)</f>
-        <v>424.96333333333331</v>
-      </c>
-      <c r="Z21" s="21">
-        <f>(Y21/X21)-1</f>
-        <v>2.7250678849702448e-002</v>
+        <f>AVERAGE(C21:V21)</f>
+        <v>420.24833333333328</v>
+      </c>
+      <c r="Z21" s="20">
+        <f>AVERAGE(Q21:V21)</f>
+        <v>431.98249999999996</v>
       </c>
       <c r="AA21" s="21">
-        <f>(Y21/V21)-1</f>
-        <v>7.1030125846396786e-002</v>
+        <f>(Z21/Y21)-1</f>
+        <v>2.792198263725032e-002</v>
       </c>
       <c r="AB21" s="21">
-        <f>(W21/V21)-1</f>
-        <v>0.14174101517213566</v>
-      </c>
-      <c r="AC21" s="22" t="s">
-        <v>72</v>
+        <f>(Z21/W21)-1</f>
+        <v>8.8720449619436481e-002</v>
+      </c>
+      <c r="AC21" s="21">
+        <f>(X21/W21)-1</f>
+        <v>0.14179142093855557</v>
+      </c>
+      <c r="AD21" s="32" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="22" ht="54">
       <c r="A22" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C22" s="17"/>
       <c r="D22" s="17"/>
@@ -2830,44 +2897,47 @@
       <c r="U22" s="17">
         <v>600</v>
       </c>
-      <c r="V22" s="19">
-        <f>MIN(C22:U22)</f>
+      <c r="V22" s="17">
+        <v>600</v>
+      </c>
+      <c r="W22" s="19">
+        <f>MIN(C22:V22)</f>
         <v>550</v>
       </c>
-      <c r="W22" s="20">
-        <f>MAX(C22:U22)</f>
+      <c r="X22" s="20">
+        <f>MAX(C22:V22)</f>
         <v>600</v>
       </c>
-      <c r="X22" s="20">
-        <f>AVERAGE(C22:U22)</f>
-        <v>565.33333333333337</v>
-      </c>
       <c r="Y22" s="20">
-        <f>AVERAGE(Q22:U22)</f>
-        <v>596</v>
-      </c>
-      <c r="Z22" s="21">
-        <f>(Y22/X22)-1</f>
-        <v>5.4245283018867774e-002</v>
+        <f>AVERAGE(C22:V22)</f>
+        <v>567.5</v>
+      </c>
+      <c r="Z22" s="20">
+        <f>AVERAGE(Q22:V22)</f>
+        <v>596.66666666666663</v>
       </c>
       <c r="AA22" s="21">
-        <f>(Y22/V22)-1</f>
-        <v>8.3636363636363731e-002</v>
+        <f>(Z22/Y22)-1</f>
+        <v>5.1395007342143861e-002</v>
       </c>
       <c r="AB22" s="21">
-        <f>(W22/V22)-1</f>
+        <f>(Z22/W22)-1</f>
+        <v>8.4848484848484729e-002</v>
+      </c>
+      <c r="AC22" s="21">
+        <f>(X22/W22)-1</f>
         <v>9.0909090909090828e-002</v>
       </c>
-      <c r="AC22" s="22" t="s">
-        <v>75</v>
+      <c r="AD22" s="22" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="23" ht="18">
       <c r="A23" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C23" s="17"/>
       <c r="D23" s="17"/>
@@ -2918,44 +2988,47 @@
       <c r="U23" s="18">
         <v>518</v>
       </c>
-      <c r="V23" s="19">
-        <f>MIN(C23:U23)</f>
+      <c r="V23" s="18">
+        <v>518</v>
+      </c>
+      <c r="W23" s="19">
+        <f>MIN(C23:V23)</f>
         <v>329</v>
       </c>
-      <c r="W23" s="20">
-        <f>MAX(C23:U23)</f>
+      <c r="X23" s="20">
+        <f>MAX(C23:V23)</f>
         <v>529.95000000000005</v>
       </c>
-      <c r="X23" s="20">
-        <f>AVERAGE(C23:U23)</f>
-        <v>467.64999999999992</v>
-      </c>
       <c r="Y23" s="20">
-        <f>AVERAGE(Q23:U23)</f>
-        <v>515.97000000000003</v>
-      </c>
-      <c r="Z23" s="21">
-        <f>(Y23/X23)-1</f>
-        <v>0.1033251363198977</v>
+        <f>AVERAGE(C23:V23)</f>
+        <v>470.79687499999994</v>
+      </c>
+      <c r="Z23" s="20">
+        <f>AVERAGE(Q23:V23)</f>
+        <v>516.30833333333339</v>
       </c>
       <c r="AA23" s="21">
-        <f>(Y23/V23)-1</f>
-        <v>0.56829787234042572</v>
+        <f>(Z23/Y23)-1</f>
+        <v>9.6668989855409393e-002</v>
       </c>
       <c r="AB23" s="21">
-        <f>(W23/V23)-1</f>
+        <f>(Z23/W23)-1</f>
+        <v>0.56932624113475194</v>
+      </c>
+      <c r="AC23" s="21">
+        <f>(X23/W23)-1</f>
         <v>0.61079027355623117</v>
       </c>
-      <c r="AC23" s="22" t="s">
-        <v>78</v>
+      <c r="AD23" s="22" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="24" ht="18">
       <c r="A24" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C24" s="17"/>
       <c r="D24" s="17"/>
@@ -3006,44 +3079,47 @@
       <c r="U24" s="18">
         <v>475.56</v>
       </c>
-      <c r="V24" s="19">
-        <f>MIN(C24:U24)</f>
+      <c r="V24" s="18">
+        <v>435.14999999999998</v>
+      </c>
+      <c r="W24" s="19">
+        <f>MIN(C24:V24)</f>
         <v>371.14999999999998</v>
       </c>
-      <c r="W24" s="20">
-        <f>MAX(C24:U24)</f>
+      <c r="X24" s="20">
+        <f>MAX(C24:V24)</f>
         <v>513.71000000000004</v>
       </c>
-      <c r="X24" s="20">
-        <f>AVERAGE(C24:U24)</f>
-        <v>444.11999999999995</v>
-      </c>
       <c r="Y24" s="20">
-        <f>AVERAGE(Q24:U24)</f>
-        <v>488.61599999999999</v>
-      </c>
-      <c r="Z24" s="21">
-        <f>(Y24/X24)-1</f>
-        <v>0.10018913807079177</v>
+        <f>AVERAGE(C24:V24)</f>
+        <v>443.55937499999993</v>
+      </c>
+      <c r="Z24" s="20">
+        <f>AVERAGE(Q24:V24)</f>
+        <v>479.70499999999998</v>
       </c>
       <c r="AA24" s="21">
-        <f>(Y24/V24)-1</f>
-        <v>0.31649198437289505</v>
+        <f>(Z24/Y24)-1</f>
+        <v>8.1489935817499193e-002</v>
       </c>
       <c r="AB24" s="21">
-        <f>(W24/V24)-1</f>
+        <f>(Z24/W24)-1</f>
+        <v>0.29248282365620382</v>
+      </c>
+      <c r="AC24" s="21">
+        <f>(X24/W24)-1</f>
         <v>0.38410346221204383</v>
       </c>
-      <c r="AC24" s="22" t="s">
-        <v>80</v>
+      <c r="AD24" s="22" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="25" ht="36">
       <c r="A25" s="25" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B25" s="26" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C25" s="28"/>
       <c r="D25" s="28"/>
@@ -3098,44 +3174,47 @@
       <c r="U25" s="17">
         <v>492.13999999999999</v>
       </c>
-      <c r="V25" s="19">
-        <f>MIN(C25:U25)</f>
+      <c r="V25" s="30">
+        <v>609.25</v>
+      </c>
+      <c r="W25" s="19">
+        <f>MIN(C25:V25)</f>
         <v>396</v>
       </c>
-      <c r="W25" s="20">
-        <f>MAX(C25:U25)</f>
-        <v>568.66999999999996</v>
-      </c>
       <c r="X25" s="20">
-        <f>AVERAGE(C25:U25)</f>
-        <v>516.11588235294118</v>
+        <f>MAX(C25:V25)</f>
+        <v>609.25</v>
       </c>
       <c r="Y25" s="20">
-        <f>AVERAGE(Q25:U25)</f>
-        <v>545.04399999999998</v>
-      </c>
-      <c r="Z25" s="21">
-        <f>(Y25/X25)-1</f>
-        <v>5.604965597101419e-002</v>
+        <f>AVERAGE(C25:V25)</f>
+        <v>521.28999999999996</v>
+      </c>
+      <c r="Z25" s="20">
+        <f>AVERAGE(Q25:V25)</f>
+        <v>555.745</v>
       </c>
       <c r="AA25" s="21">
-        <f>(Y25/V25)-1</f>
-        <v>0.37637373737373725</v>
+        <f>(Z25/Y25)-1</f>
+        <v>6.6095647336415597e-002</v>
       </c>
       <c r="AB25" s="21">
-        <f>(W25/V25)-1</f>
-        <v>0.43603535353535339</v>
-      </c>
-      <c r="AC25" s="22" t="s">
-        <v>83</v>
+        <f>(Z25/W25)-1</f>
+        <v>0.40339646464646473</v>
+      </c>
+      <c r="AC25" s="21">
+        <f>(X25/W25)-1</f>
+        <v>0.53851010101010099</v>
+      </c>
+      <c r="AD25" s="22" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="26" ht="18">
       <c r="A26" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C26" s="17"/>
       <c r="D26" s="24">
@@ -3182,50 +3261,53 @@
       <c r="S26" s="29">
         <v>1534.8399999999999</v>
       </c>
-      <c r="T26" s="32">
+      <c r="T26" s="33">
         <v>370</v>
       </c>
       <c r="U26" s="30">
         <v>1655.4000000000001</v>
       </c>
-      <c r="V26" s="19">
-        <f>MIN(C26:U26)</f>
+      <c r="V26" s="34">
+        <v>700</v>
+      </c>
+      <c r="W26" s="19">
+        <f>MIN(C26:V26)</f>
         <v>370</v>
       </c>
-      <c r="W26" s="20">
-        <f>MAX(C26:U26)</f>
+      <c r="X26" s="20">
+        <f>MAX(C26:V26)</f>
         <v>1655.4000000000001</v>
       </c>
-      <c r="X26" s="20">
-        <f>AVERAGE(C26:U26)</f>
-        <v>1115.8025</v>
-      </c>
       <c r="Y26" s="20">
-        <f>AVERAGE(Q26:U26)</f>
-        <v>1300.0819999999999</v>
-      </c>
-      <c r="Z26" s="21">
-        <f>(Y26/X26)-1</f>
-        <v>0.16515422756267339</v>
+        <f>AVERAGE(C26:V26)</f>
+        <v>1091.3435294117646</v>
+      </c>
+      <c r="Z26" s="20">
+        <f>AVERAGE(Q26:V26)</f>
+        <v>1200.0683333333334</v>
       </c>
       <c r="AA26" s="21">
-        <f>(Y26/V26)-1</f>
-        <v>2.5137351351351347</v>
+        <f>(Z26/Y26)-1</f>
+        <v>9.962472951131307e-002</v>
       </c>
       <c r="AB26" s="21">
-        <f>(W26/V26)-1</f>
+        <f>(Z26/W26)-1</f>
+        <v>2.2434279279279279</v>
+      </c>
+      <c r="AC26" s="21">
+        <f>(X26/W26)-1</f>
         <v>3.4740540540540543</v>
       </c>
-      <c r="AC26" s="22" t="s">
-        <v>85</v>
+      <c r="AD26" s="22" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="27" ht="18">
       <c r="A27" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C27" s="17"/>
       <c r="D27" s="17"/>
@@ -3268,44 +3350,47 @@
       <c r="U27" s="29">
         <v>159.99000000000001</v>
       </c>
-      <c r="V27" s="19">
-        <f>MIN(C27:U27)</f>
+      <c r="V27" s="29">
+        <v>164.99000000000001</v>
+      </c>
+      <c r="W27" s="19">
+        <f>MIN(C27:V27)</f>
         <v>109.98999999999999</v>
       </c>
-      <c r="W27" s="20">
-        <f>MAX(C27:U27)</f>
+      <c r="X27" s="20">
+        <f>MAX(C27:V27)</f>
         <v>165.72999999999999</v>
       </c>
-      <c r="X27" s="20">
-        <f>AVERAGE(C27:U27)</f>
-        <v>141.42090909090911</v>
-      </c>
       <c r="Y27" s="20">
-        <f>AVERAGE(Q27:U27)</f>
-        <v>153.99000000000001</v>
-      </c>
-      <c r="Z27" s="21">
-        <f>(Y27/X27)-1</f>
-        <v>8.8877175163760036e-002</v>
+        <f>AVERAGE(C27:V27)</f>
+        <v>143.38500000000002</v>
+      </c>
+      <c r="Z27" s="20">
+        <f>AVERAGE(Q27:V27)</f>
+        <v>155.82333333333335</v>
       </c>
       <c r="AA27" s="21">
-        <f>(Y27/V27)-1</f>
-        <v>0.40003636694244937</v>
+        <f>(Z27/Y27)-1</f>
+        <v>8.6747800211551596e-002</v>
       </c>
       <c r="AB27" s="21">
-        <f>(W27/V27)-1</f>
+        <f>(Z27/W27)-1</f>
+        <v>0.41670454889838493</v>
+      </c>
+      <c r="AC27" s="21">
+        <f>(X27/W27)-1</f>
         <v>0.50677334303118471</v>
       </c>
-      <c r="AC27" s="22" t="s">
-        <v>87</v>
+      <c r="AD27" s="22" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="28" ht="18">
       <c r="A28" s="25" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B28" s="26" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C28" s="28"/>
       <c r="D28" s="28"/>
@@ -3348,44 +3433,47 @@
       <c r="U28" s="17">
         <v>81</v>
       </c>
-      <c r="V28" s="19">
-        <f>MIN(C28:U28)</f>
+      <c r="V28" s="18">
+        <v>85.700000000000003</v>
+      </c>
+      <c r="W28" s="19">
+        <f>MIN(C28:V28)</f>
         <v>68</v>
       </c>
-      <c r="W28" s="20">
-        <f>MAX(C28:U28)</f>
-        <v>83</v>
-      </c>
       <c r="X28" s="20">
-        <f>AVERAGE(C28:U28)</f>
-        <v>77.283636363636361</v>
+        <f>MAX(C28:V28)</f>
+        <v>85.700000000000003</v>
       </c>
       <c r="Y28" s="20">
-        <f>AVERAGE(Q28:U28)</f>
-        <v>81.463999999999999</v>
-      </c>
-      <c r="Z28" s="21">
-        <f>(Y28/X28)-1</f>
-        <v>5.4091187126523277e-002</v>
+        <f>AVERAGE(C28:V28)</f>
+        <v>77.984999999999999</v>
+      </c>
+      <c r="Z28" s="20">
+        <f>AVERAGE(Q28:V28)</f>
+        <v>82.170000000000002</v>
       </c>
       <c r="AA28" s="21">
-        <f>(Y28/V28)-1</f>
-        <v>0.19799999999999995</v>
+        <f>(Z28/Y28)-1</f>
+        <v>5.3664166185805051e-002</v>
       </c>
       <c r="AB28" s="21">
-        <f>(W28/V28)-1</f>
-        <v>0.22058823529411775</v>
-      </c>
-      <c r="AC28" s="22" t="s">
-        <v>89</v>
+        <f>(Z28/W28)-1</f>
+        <v>0.20838235294117657</v>
+      </c>
+      <c r="AC28" s="21">
+        <f>(X28/W28)-1</f>
+        <v>0.26029411764705879</v>
+      </c>
+      <c r="AD28" s="22" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="29" ht="18">
       <c r="A29" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C29" s="17"/>
       <c r="D29" s="17"/>
@@ -3428,44 +3516,47 @@
       <c r="U29" s="30">
         <v>111</v>
       </c>
-      <c r="V29" s="19">
-        <f>MIN(C29:U29)</f>
+      <c r="V29" s="33">
+        <v>65.530000000000001</v>
+      </c>
+      <c r="W29" s="19">
+        <f>MIN(C29:V29)</f>
         <v>55</v>
       </c>
-      <c r="W29" s="20">
-        <f>MAX(C29:U29)</f>
+      <c r="X29" s="20">
+        <f>MAX(C29:V29)</f>
         <v>111</v>
       </c>
-      <c r="X29" s="20">
-        <f>AVERAGE(C29:U29)</f>
-        <v>83.329090909090922</v>
-      </c>
       <c r="Y29" s="20">
-        <f>AVERAGE(Q29:U29)</f>
-        <v>97.372</v>
-      </c>
-      <c r="Z29" s="21">
-        <f>(Y29/X29)-1</f>
-        <v>0.16852348846850362</v>
+        <f>AVERAGE(C29:V29)</f>
+        <v>81.845833333333346</v>
+      </c>
+      <c r="Z29" s="20">
+        <f>AVERAGE(Q29:V29)</f>
+        <v>92.064999999999998</v>
       </c>
       <c r="AA29" s="21">
-        <f>(Y29/V29)-1</f>
-        <v>0.77039999999999997</v>
+        <f>(Z29/Y29)-1</f>
+        <v>0.12485872830015765</v>
       </c>
       <c r="AB29" s="21">
-        <f>(W29/V29)-1</f>
+        <f>(Z29/W29)-1</f>
+        <v>0.67390909090909079</v>
+      </c>
+      <c r="AC29" s="21">
+        <f>(X29/W29)-1</f>
         <v>1.0181818181818181</v>
       </c>
-      <c r="AC29" s="22" t="s">
-        <v>91</v>
+      <c r="AD29" s="22" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="30" ht="18">
       <c r="A30" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
@@ -3506,44 +3597,47 @@
       <c r="U30" s="29">
         <v>92.530000000000001</v>
       </c>
-      <c r="V30" s="19">
-        <f>MIN(C30:U30)</f>
+      <c r="V30" s="18">
+        <v>89.090000000000003</v>
+      </c>
+      <c r="W30" s="19">
+        <f>MIN(C30:V30)</f>
         <v>47.359999999999999</v>
       </c>
-      <c r="W30" s="20">
-        <f>MAX(C30:U30)</f>
+      <c r="X30" s="20">
+        <f>MAX(C30:V30)</f>
         <v>100.68000000000001</v>
       </c>
-      <c r="X30" s="20">
-        <f>AVERAGE(C30:U30)</f>
-        <v>69.402000000000001</v>
-      </c>
       <c r="Y30" s="20">
-        <f>AVERAGE(Q30:U30)</f>
-        <v>84.314000000000007</v>
-      </c>
-      <c r="Z30" s="21">
-        <f>(Y30/X30)-1</f>
-        <v>0.21486412495317153</v>
+        <f>AVERAGE(C30:V30)</f>
+        <v>71.191818181818178</v>
+      </c>
+      <c r="Z30" s="20">
+        <f>AVERAGE(Q30:V30)</f>
+        <v>85.110000000000014</v>
       </c>
       <c r="AA30" s="21">
-        <f>(Y30/V30)-1</f>
-        <v>0.78027871621621636</v>
+        <f>(Z30/Y30)-1</f>
+        <v>0.19550254753482932</v>
       </c>
       <c r="AB30" s="21">
-        <f>(W30/V30)-1</f>
+        <f>(Z30/W30)-1</f>
+        <v>0.79708614864864891</v>
+      </c>
+      <c r="AC30" s="21">
+        <f>(X30/W30)-1</f>
         <v>1.1258445945945947</v>
       </c>
-      <c r="AC30" s="22" t="s">
-        <v>93</v>
+      <c r="AD30" s="22" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="31" ht="18">
       <c r="A31" s="25" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B31" s="26" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C31" s="28"/>
       <c r="D31" s="28"/>
@@ -3579,49 +3673,52 @@
         <v>132.33000000000001</v>
       </c>
       <c r="T31" s="17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="U31" s="18">
         <v>156</v>
       </c>
-      <c r="V31" s="19">
-        <f>MIN(C31:U31)</f>
+      <c r="V31" s="18">
+        <v>156</v>
+      </c>
+      <c r="W31" s="19">
+        <f>MIN(C31:V31)</f>
         <v>92.5</v>
       </c>
-      <c r="W31" s="20">
-        <f>MAX(C31:U31)</f>
+      <c r="X31" s="20">
+        <f>MAX(C31:V31)</f>
         <v>156</v>
       </c>
-      <c r="X31" s="20">
-        <f>AVERAGE(C31:U31)</f>
-        <v>115.63111111111114</v>
-      </c>
       <c r="Y31" s="20">
-        <f>AVERAGE(Q31:U31)</f>
-        <v>127.79750000000001</v>
-      </c>
-      <c r="Z31" s="21">
-        <f>(Y31/X31)-1</f>
-        <v>0.10521726179036772</v>
+        <f>AVERAGE(C31:V31)</f>
+        <v>119.66800000000003</v>
+      </c>
+      <c r="Z31" s="20">
+        <f>AVERAGE(Q31:V31)</f>
+        <v>133.43800000000002</v>
       </c>
       <c r="AA31" s="21">
-        <f>(Y31/V31)-1</f>
-        <v>0.38159459459459466</v>
+        <f>(Z31/Y31)-1</f>
+        <v>0.11506835578433638</v>
       </c>
       <c r="AB31" s="21">
-        <f>(W31/V31)-1</f>
+        <f>(Z31/W31)-1</f>
+        <v>0.44257297297297304</v>
+      </c>
+      <c r="AC31" s="21">
+        <f>(X31/W31)-1</f>
         <v>0.68648648648648658</v>
       </c>
-      <c r="AC31" s="22" t="s">
-        <v>95</v>
+      <c r="AD31" s="22" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="32" ht="18">
       <c r="A32" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C32" s="17"/>
       <c r="D32" s="17"/>
@@ -3660,44 +3757,47 @@
       <c r="U32" s="18">
         <v>238.24000000000001</v>
       </c>
-      <c r="V32" s="19">
-        <f>MIN(C32:U32)</f>
+      <c r="V32" s="18">
+        <v>238.24000000000001</v>
+      </c>
+      <c r="W32" s="19">
+        <f>MIN(C32:V32)</f>
         <v>148.88</v>
       </c>
-      <c r="W32" s="20">
-        <f>MAX(C32:U32)</f>
+      <c r="X32" s="20">
+        <f>MAX(C32:V32)</f>
         <v>257.87</v>
       </c>
-      <c r="X32" s="20">
-        <f>AVERAGE(C32:U32)</f>
-        <v>216.90111111111113</v>
-      </c>
       <c r="Y32" s="20">
-        <f>AVERAGE(Q32:U32)</f>
-        <v>234.20600000000005</v>
-      </c>
-      <c r="Z32" s="21">
-        <f>(Y32/X32)-1</f>
-        <v>7.9782389312077706e-002</v>
+        <f>AVERAGE(C32:V32)</f>
+        <v>219.03500000000003</v>
+      </c>
+      <c r="Z32" s="20">
+        <f>AVERAGE(Q32:V32)</f>
+        <v>234.87833333333336</v>
       </c>
       <c r="AA32" s="21">
-        <f>(Y32/V32)-1</f>
-        <v>0.57311929070392287</v>
+        <f>(Z32/Y32)-1</f>
+        <v>7.2332427846386826e-002</v>
       </c>
       <c r="AB32" s="21">
-        <f>(W32/V32)-1</f>
+        <f>(Z32/W32)-1</f>
+        <v>0.57763523195414668</v>
+      </c>
+      <c r="AC32" s="21">
+        <f>(X32/W32)-1</f>
         <v>0.73206609349811935</v>
       </c>
-      <c r="AC32" s="22" t="s">
-        <v>97</v>
+      <c r="AD32" s="22" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="33" ht="18">
       <c r="A33" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C33" s="17"/>
       <c r="D33" s="17"/>
@@ -3732,44 +3832,47 @@
       <c r="U33" s="18">
         <v>162.63999999999999</v>
       </c>
-      <c r="V33" s="19">
-        <f>MIN(C33:U33)</f>
+      <c r="V33" s="18">
+        <v>164.93000000000001</v>
+      </c>
+      <c r="W33" s="19">
+        <f>MIN(C33:V33)</f>
         <v>144.94999999999999</v>
       </c>
-      <c r="W33" s="20">
-        <f>MAX(C33:U33)</f>
-        <v>162.63999999999999</v>
-      </c>
       <c r="X33" s="20">
-        <f>AVERAGE(C33:U33)</f>
-        <v>152.12142857142857</v>
+        <f>MAX(C33:V33)</f>
+        <v>164.93000000000001</v>
       </c>
       <c r="Y33" s="20">
-        <f>AVERAGE(Q33:U33)</f>
-        <v>151.28199999999998</v>
-      </c>
-      <c r="Z33" s="21">
-        <f>(Y33/X33)-1</f>
-        <v>-5.5181480959760609e-003</v>
+        <f>AVERAGE(C33:V33)</f>
+        <v>153.7225</v>
+      </c>
+      <c r="Z33" s="20">
+        <f>AVERAGE(Q33:V33)</f>
+        <v>153.55666666666664</v>
       </c>
       <c r="AA33" s="21">
-        <f>(Y33/V33)-1</f>
-        <v>4.3684028975508715e-002</v>
+        <f>(Z33/Y33)-1</f>
+        <v>-1.0787837390970889e-003</v>
       </c>
       <c r="AB33" s="21">
-        <f>(W33/V33)-1</f>
-        <v>0.12204208347706103</v>
-      </c>
-      <c r="AC33" s="22" t="s">
-        <v>99</v>
+        <f>(Z33/W33)-1</f>
+        <v>5.9376796596527504e-002</v>
+      </c>
+      <c r="AC33" s="21">
+        <f>(X33/W33)-1</f>
+        <v>0.13784063470162145</v>
+      </c>
+      <c r="AD33" s="22" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="34" ht="18">
       <c r="A34" s="25" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B34" s="26" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C34" s="28"/>
       <c r="D34" s="28"/>
@@ -3804,44 +3907,47 @@
       <c r="U34" s="29">
         <v>199.94999999999999</v>
       </c>
-      <c r="V34" s="19">
-        <f>MIN(C34:U34)</f>
+      <c r="V34" s="18">
+        <v>169</v>
+      </c>
+      <c r="W34" s="19">
+        <f>MIN(C34:V34)</f>
         <v>144</v>
       </c>
-      <c r="W34" s="20">
-        <f>MAX(C34:U34)</f>
+      <c r="X34" s="20">
+        <f>MAX(C34:V34)</f>
         <v>199.94999999999999</v>
       </c>
-      <c r="X34" s="20">
-        <f>AVERAGE(C34:U34)</f>
-        <v>181.59428571428572</v>
-      </c>
       <c r="Y34" s="20">
-        <f>AVERAGE(Q34:U34)</f>
-        <v>181.86599999999999</v>
-      </c>
-      <c r="Z34" s="21">
-        <f>(Y34/X34)-1</f>
-        <v>1.4962711224393299e-003</v>
+        <f>AVERAGE(C34:V34)</f>
+        <v>180.02000000000001</v>
+      </c>
+      <c r="Z34" s="20">
+        <f>AVERAGE(Q34:V34)</f>
+        <v>179.72166666666666</v>
       </c>
       <c r="AA34" s="21">
-        <f>(Y34/V34)-1</f>
-        <v>0.26295833333333318</v>
+        <f>(Z34/Y34)-1</f>
+        <v>-1.6572232714884283e-003</v>
       </c>
       <c r="AB34" s="21">
-        <f>(W34/V34)-1</f>
+        <f>(Z34/W34)-1</f>
+        <v>0.24806712962962951</v>
+      </c>
+      <c r="AC34" s="21">
+        <f>(X34/W34)-1</f>
         <v>0.38854166666666656</v>
       </c>
-      <c r="AC34" s="22" t="s">
-        <v>101</v>
+      <c r="AD34" s="22" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="35" ht="18">
       <c r="A35" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C35" s="17"/>
       <c r="D35" s="17"/>
@@ -3866,7 +3972,7 @@
         <v>31941.080000000002</v>
       </c>
       <c r="M35" s="17" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="N35" s="18"/>
       <c r="O35" s="17"/>
@@ -3876,44 +3982,45 @@
       <c r="S35" s="17"/>
       <c r="T35" s="17"/>
       <c r="U35" s="17"/>
-      <c r="V35" s="19">
-        <f>MIN(C35:U35)</f>
+      <c r="V35" s="17"/>
+      <c r="W35" s="19">
+        <f>MIN(C35:V35)</f>
         <v>30731.380000000001</v>
       </c>
-      <c r="W35" s="20">
-        <f>MAX(C35:U35)</f>
+      <c r="X35" s="20">
+        <f>MAX(C35:V35)</f>
         <v>32790.889999999999</v>
       </c>
-      <c r="X35" s="20">
-        <f>AVERAGE(C35:U35)</f>
+      <c r="Y35" s="20">
+        <f>AVERAGE(C35:V35)</f>
         <v>31912.133333333331</v>
       </c>
-      <c r="Y35" s="20" t="e">
-        <f>AVERAGE(Q35:U35)</f>
+      <c r="Z35" s="20" t="e">
+        <f>AVERAGE(Q35:V35)</f>
         <v>#NUM!</v>
       </c>
-      <c r="Z35" s="21" t="e">
-        <f>(Y35/X35)-1</f>
+      <c r="AA35" s="21" t="e">
+        <f>(Z35/Y35)-1</f>
         <v>#NUM!</v>
       </c>
-      <c r="AA35" s="21" t="e">
-        <f>(Y35/V35)-1</f>
+      <c r="AB35" s="21" t="e">
+        <f>(Z35/W35)-1</f>
         <v>#NUM!</v>
       </c>
-      <c r="AB35" s="21">
-        <f>(W35/V35)-1</f>
+      <c r="AC35" s="21">
+        <f>(X35/W35)-1</f>
         <v>6.7016515366377982e-002</v>
       </c>
-      <c r="AC35" s="22" t="s">
-        <v>104</v>
+      <c r="AD35" s="22" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="36" ht="18">
       <c r="A36" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C36" s="17"/>
       <c r="D36" s="17"/>
@@ -3945,49 +4052,52 @@
         <v>721.67999999999995</v>
       </c>
       <c r="T36" s="17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="U36" s="17">
         <v>1164</v>
       </c>
-      <c r="V36" s="19">
-        <f>MIN(C36:U36)</f>
+      <c r="V36" s="17">
+        <v>1150.8</v>
+      </c>
+      <c r="W36" s="19">
+        <f>MIN(C36:V36)</f>
         <v>642.82000000000005</v>
       </c>
-      <c r="W36" s="20">
-        <f>MAX(C36:U36)</f>
+      <c r="X36" s="20">
+        <f>MAX(C36:V36)</f>
         <v>1164</v>
       </c>
-      <c r="X36" s="20">
-        <f>AVERAGE(C36:U36)</f>
-        <v>762.33714285714279</v>
-      </c>
       <c r="Y36" s="20">
-        <f>AVERAGE(Q36:U36)</f>
-        <v>832.25999999999999</v>
-      </c>
-      <c r="Z36" s="21">
-        <f>(Y36/X36)-1</f>
-        <v>9.1721697936421265e-002</v>
+        <f>AVERAGE(C36:V36)</f>
+        <v>810.89499999999998</v>
+      </c>
+      <c r="Z36" s="20">
+        <f>AVERAGE(Q36:V36)</f>
+        <v>895.96800000000007</v>
       </c>
       <c r="AA36" s="21">
-        <f>(Y36/V36)-1</f>
-        <v>0.29470147164058358</v>
+        <f>(Z36/Y36)-1</f>
+        <v>0.10491247325486053</v>
       </c>
       <c r="AB36" s="21">
-        <f>(W36/V36)-1</f>
+        <f>(Z36/W36)-1</f>
+        <v>0.39380853115957803</v>
+      </c>
+      <c r="AC36" s="21">
+        <f>(X36/W36)-1</f>
         <v>0.81077128900780915</v>
       </c>
-      <c r="AC36" s="22" t="s">
-        <v>107</v>
+      <c r="AD36" s="22" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="37" ht="18">
       <c r="A37" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C37" s="17"/>
       <c r="D37" s="17"/>
@@ -4024,44 +4134,47 @@
       <c r="U37" s="30">
         <v>2064</v>
       </c>
-      <c r="V37" s="19">
-        <f>MIN(C37:U37)</f>
+      <c r="V37" s="30">
+        <v>2016</v>
+      </c>
+      <c r="W37" s="19">
+        <f>MIN(C37:V37)</f>
         <v>1151.71</v>
       </c>
-      <c r="W37" s="20">
-        <f>MAX(C37:U37)</f>
+      <c r="X37" s="20">
+        <f>MAX(C37:V37)</f>
         <v>2064</v>
       </c>
-      <c r="X37" s="20">
-        <f>AVERAGE(C37:U37)</f>
-        <v>1443.7675000000002</v>
-      </c>
       <c r="Y37" s="20">
-        <f>AVERAGE(Q37:U37)</f>
-        <v>1593.4079999999999</v>
-      </c>
-      <c r="Z37" s="21">
-        <f>(Y37/X37)-1</f>
-        <v>0.10364584325384785</v>
+        <f>AVERAGE(C37:V37)</f>
+        <v>1507.348888888889</v>
+      </c>
+      <c r="Z37" s="20">
+        <f>AVERAGE(Q37:V37)</f>
+        <v>1663.8400000000001</v>
       </c>
       <c r="AA37" s="21">
-        <f>(Y37/V37)-1</f>
-        <v>0.38351494733917368</v>
+        <f>(Z37/Y37)-1</f>
+        <v>0.10381877232580528</v>
       </c>
       <c r="AB37" s="21">
-        <f>(W37/V37)-1</f>
+        <f>(Z37/W37)-1</f>
+        <v>0.44466923096960187</v>
+      </c>
+      <c r="AC37" s="21">
+        <f>(X37/W37)-1</f>
         <v>0.79211780743416305</v>
       </c>
-      <c r="AC37" s="22" t="s">
-        <v>107</v>
+      <c r="AD37" s="22" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="38" ht="18">
       <c r="A38" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C38" s="17"/>
       <c r="D38" s="17"/>
@@ -4095,47 +4208,50 @@
       <c r="T38" s="30">
         <v>3876</v>
       </c>
-      <c r="U38" s="33" t="s">
-        <v>42</v>
-      </c>
-      <c r="V38" s="19">
-        <f>MIN(C38:U38)</f>
+      <c r="U38" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="V38" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="W38" s="19">
+        <f>MIN(C38:V38)</f>
         <v>2159.8299999999999</v>
       </c>
-      <c r="W38" s="20">
-        <f>MAX(C38:U38)</f>
+      <c r="X38" s="20">
+        <f>MAX(C38:V38)</f>
         <v>3876</v>
       </c>
-      <c r="X38" s="20">
-        <f>AVERAGE(C38:U38)</f>
+      <c r="Y38" s="20">
+        <f>AVERAGE(C38:V38)</f>
         <v>2544.02</v>
       </c>
-      <c r="Y38" s="20">
-        <f>AVERAGE(Q38:U38)</f>
+      <c r="Z38" s="20">
+        <f>AVERAGE(Q38:V38)</f>
         <v>2771.3400000000001</v>
       </c>
-      <c r="Z38" s="21">
-        <f>(Y38/X38)-1</f>
+      <c r="AA38" s="21">
+        <f>(Z38/Y38)-1</f>
         <v>8.9354643438337877e-002</v>
       </c>
-      <c r="AA38" s="21">
-        <f>(Y38/V38)-1</f>
+      <c r="AB38" s="21">
+        <f>(Z38/W38)-1</f>
         <v>0.28312876476389359</v>
       </c>
-      <c r="AB38" s="21">
-        <f>(W38/V38)-1</f>
+      <c r="AC38" s="21">
+        <f>(X38/W38)-1</f>
         <v>0.79458568498446636</v>
       </c>
-      <c r="AC38" s="22" t="s">
-        <v>107</v>
+      <c r="AD38" s="22" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="39" ht="18">
       <c r="A39" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C39" s="17"/>
       <c r="D39" s="17"/>
@@ -4172,44 +4288,47 @@
       <c r="U39" s="30">
         <v>2130</v>
       </c>
-      <c r="V39" s="19">
-        <f>MIN(C39:U39)</f>
+      <c r="V39" s="30">
+        <v>2218.4400000000001</v>
+      </c>
+      <c r="W39" s="19">
+        <f>MIN(C39:V39)</f>
         <v>1310.1800000000001</v>
       </c>
-      <c r="W39" s="20">
-        <f>MAX(C39:U39)</f>
-        <v>2130</v>
-      </c>
       <c r="X39" s="20">
-        <f>AVERAGE(C39:U39)</f>
-        <v>1521.6475</v>
+        <f>MAX(C39:V39)</f>
+        <v>2218.4400000000001</v>
       </c>
       <c r="Y39" s="20">
-        <f>AVERAGE(Q39:U39)</f>
-        <v>1644.3599999999999</v>
-      </c>
-      <c r="Z39" s="21">
-        <f>(Y39/X39)-1</f>
-        <v>8.0644498808035259e-002</v>
+        <f>AVERAGE(C39:V39)</f>
+        <v>1599.068888888889</v>
+      </c>
+      <c r="Z39" s="20">
+        <f>AVERAGE(Q39:V39)</f>
+        <v>1740.04</v>
       </c>
       <c r="AA39" s="21">
-        <f>(Y39/V39)-1</f>
-        <v>0.25506418965332989</v>
+        <f>(Z39/Y39)-1</f>
+        <v>8.8158247646894505e-002</v>
       </c>
       <c r="AB39" s="21">
-        <f>(W39/V39)-1</f>
-        <v>0.62573081561312183</v>
-      </c>
-      <c r="AC39" s="22" t="s">
-        <v>107</v>
+        <f>(Z39/W39)-1</f>
+        <v>0.32809232319223303</v>
+      </c>
+      <c r="AC39" s="21">
+        <f>(X39/W39)-1</f>
+        <v>0.69323299088674828</v>
+      </c>
+      <c r="AD39" s="22" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="40" ht="18">
       <c r="A40" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C40" s="17"/>
       <c r="D40" s="17"/>
@@ -4234,44 +4353,47 @@
       <c r="U40" s="29">
         <v>1896</v>
       </c>
-      <c r="V40" s="19">
-        <f>MIN(C40:U40)</f>
+      <c r="V40" s="29">
+        <v>1592.6400000000001</v>
+      </c>
+      <c r="W40" s="19">
+        <f>MIN(C40:V40)</f>
+        <v>1592.6400000000001</v>
+      </c>
+      <c r="X40" s="20">
+        <f>MAX(C40:V40)</f>
         <v>1896</v>
       </c>
-      <c r="W40" s="20">
-        <f>MAX(C40:U40)</f>
-        <v>1896</v>
-      </c>
-      <c r="X40" s="20">
-        <f>AVERAGE(C40:U40)</f>
-        <v>1896</v>
-      </c>
       <c r="Y40" s="20">
-        <f>AVERAGE(Q40:U40)</f>
-        <v>1896</v>
-      </c>
-      <c r="Z40" s="21">
-        <f>(Y40/X40)-1</f>
+        <f>AVERAGE(C40:V40)</f>
+        <v>1794.8800000000001</v>
+      </c>
+      <c r="Z40" s="20">
+        <f>AVERAGE(Q40:V40)</f>
+        <v>1794.8800000000001</v>
+      </c>
+      <c r="AA40" s="21">
+        <f>(Z40/Y40)-1</f>
         <v>0</v>
       </c>
-      <c r="AA40" s="21">
-        <f>(Y40/V40)-1</f>
-        <v>0</v>
-      </c>
       <c r="AB40" s="21">
-        <f>(W40/V40)-1</f>
-        <v>0</v>
-      </c>
-      <c r="AC40" s="22" t="s">
-        <v>107</v>
+        <f>(Z40/W40)-1</f>
+        <v>0.12698412698412698</v>
+      </c>
+      <c r="AC40" s="21">
+        <f>(X40/W40)-1</f>
+        <v>0.19047619047619047</v>
+      </c>
+      <c r="AD40" s="22" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="41" ht="18">
       <c r="A41" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C41" s="17"/>
       <c r="D41" s="17"/>
@@ -4303,64 +4425,67 @@
         <v>1628.6199999999999</v>
       </c>
       <c r="T41" s="17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="U41" s="17" t="s">
-        <v>42</v>
-      </c>
-      <c r="V41" s="19">
-        <f>MIN(C41:U41)</f>
+        <v>43</v>
+      </c>
+      <c r="V41" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="W41" s="19">
+        <f>MIN(C41:V41)</f>
         <v>1480.5599999999999</v>
       </c>
-      <c r="W41" s="20">
-        <f>MAX(C41:U41)</f>
+      <c r="X41" s="20">
+        <f>MAX(C41:V41)</f>
         <v>1628.6199999999999</v>
       </c>
-      <c r="X41" s="20">
-        <f>AVERAGE(C41:U41)</f>
+      <c r="Y41" s="20">
+        <f>AVERAGE(C41:V41)</f>
         <v>1579.2666666666664</v>
       </c>
-      <c r="Y41" s="20">
-        <f>AVERAGE(Q41:U41)</f>
+      <c r="Z41" s="20">
+        <f>AVERAGE(Q41:V41)</f>
         <v>1628.6199999999999</v>
       </c>
-      <c r="Z41" s="21">
-        <f>(Y41/X41)-1</f>
+      <c r="AA41" s="21">
+        <f>(Z41/Y41)-1</f>
         <v>3.1250791506606479e-002</v>
       </c>
-      <c r="AA41" s="21">
-        <f>(Y41/V41)-1</f>
+      <c r="AB41" s="21">
+        <f>(Z41/W41)-1</f>
         <v>0.10000270168044523</v>
       </c>
-      <c r="AB41" s="21">
-        <f>(W41/V41)-1</f>
+      <c r="AC41" s="21">
+        <f>(X41/W41)-1</f>
         <v>0.10000270168044523</v>
       </c>
-      <c r="AC41" s="22" t="s">
-        <v>107</v>
+      <c r="AD41" s="22" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="42" ht="18">
       <c r="A42" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C42" s="17"/>
       <c r="D42" s="17">
         <v>339.45999999999998</v>
       </c>
-      <c r="E42" s="34"/>
-      <c r="F42" s="34"/>
-      <c r="G42" s="34"/>
-      <c r="H42" s="34"/>
-      <c r="I42" s="34"/>
-      <c r="J42" s="34"/>
-      <c r="K42" s="34"/>
-      <c r="L42" s="34"/>
-      <c r="M42" s="34"/>
-      <c r="N42" s="34"/>
+      <c r="E42" s="36"/>
+      <c r="F42" s="36"/>
+      <c r="G42" s="36"/>
+      <c r="H42" s="36"/>
+      <c r="I42" s="36"/>
+      <c r="J42" s="36"/>
+      <c r="K42" s="36"/>
+      <c r="L42" s="36"/>
+      <c r="M42" s="36"/>
+      <c r="N42" s="36"/>
       <c r="O42" s="17"/>
       <c r="P42" s="17"/>
       <c r="Q42" s="17"/>
@@ -4368,41 +4493,42 @@
       <c r="S42" s="17"/>
       <c r="T42" s="17"/>
       <c r="U42" s="17"/>
-      <c r="V42" s="19">
-        <f>MIN(C42:U42)</f>
+      <c r="V42" s="17"/>
+      <c r="W42" s="19">
+        <f>MIN(C42:V42)</f>
         <v>339.45999999999998</v>
       </c>
-      <c r="W42" s="20">
-        <f>MAX(C42:U42)</f>
+      <c r="X42" s="20">
+        <f>MAX(C42:V42)</f>
         <v>339.45999999999998</v>
       </c>
-      <c r="X42" s="20">
-        <f>AVERAGE(C42:U42)</f>
+      <c r="Y42" s="20">
+        <f>AVERAGE(C42:V42)</f>
         <v>339.45999999999998</v>
       </c>
-      <c r="Y42" s="20" t="e">
-        <f>AVERAGE(Q42:U42)</f>
+      <c r="Z42" s="20" t="e">
+        <f>AVERAGE(Q42:V42)</f>
         <v>#NUM!</v>
       </c>
-      <c r="Z42" s="21" t="e">
-        <f>(Y42/X42)-1</f>
+      <c r="AA42" s="21" t="e">
+        <f>(Z42/Y42)-1</f>
         <v>#NUM!</v>
       </c>
-      <c r="AA42" s="21" t="e">
-        <f>(Y42/V42)-1</f>
+      <c r="AB42" s="21" t="e">
+        <f>(Z42/W42)-1</f>
         <v>#NUM!</v>
       </c>
-      <c r="AB42" s="21">
-        <f>(W42/V42)-1</f>
+      <c r="AC42" s="21">
+        <f>(X42/W42)-1</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" ht="18">
       <c r="A43" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C43" s="17"/>
       <c r="D43" s="17"/>
@@ -4453,44 +4579,47 @@
       <c r="U43" s="17">
         <v>378.99000000000001</v>
       </c>
-      <c r="V43" s="19">
-        <f>MIN(C43:U43)</f>
+      <c r="V43" s="17">
         <v>378.99000000000001</v>
       </c>
-      <c r="W43" s="20">
-        <f>MAX(C43:U43)</f>
+      <c r="W43" s="19">
+        <f>MIN(C43:V43)</f>
         <v>378.99000000000001</v>
       </c>
       <c r="X43" s="20">
-        <f>AVERAGE(C43:U43)</f>
+        <f>MAX(C43:V43)</f>
+        <v>378.99000000000001</v>
+      </c>
+      <c r="Y43" s="20">
+        <f>AVERAGE(C43:V43)</f>
         <v>378.9899999999999</v>
       </c>
-      <c r="Y43" s="20">
-        <f>AVERAGE(Q43:U43)</f>
+      <c r="Z43" s="20">
+        <f>AVERAGE(Q43:V43)</f>
         <v>378.99000000000001</v>
       </c>
-      <c r="Z43" s="21">
-        <f>(Y43/X43)-1</f>
+      <c r="AA43" s="21">
+        <f>(Z43/Y43)-1</f>
         <v>2.2204460492503131e-016</v>
       </c>
-      <c r="AA43" s="21">
-        <f>(Y43/V43)-1</f>
+      <c r="AB43" s="21">
+        <f>(Z43/W43)-1</f>
         <v>0</v>
       </c>
-      <c r="AB43" s="21">
-        <f>(W43/V43)-1</f>
+      <c r="AC43" s="21">
+        <f>(X43/W43)-1</f>
         <v>0</v>
       </c>
-      <c r="AC43" s="22" t="s">
-        <v>118</v>
+      <c r="AD43" s="22" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="44" ht="18">
       <c r="A44" s="25" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B44" s="26" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C44" s="28"/>
       <c r="D44" s="28"/>
@@ -4541,44 +4670,47 @@
       <c r="U44" s="18">
         <v>117.58</v>
       </c>
-      <c r="V44" s="19">
-        <f>MIN(C44:U44)</f>
+      <c r="V44" s="18">
+        <v>119.59</v>
+      </c>
+      <c r="W44" s="19">
+        <f>MIN(C44:V44)</f>
         <v>88.329999999999998</v>
       </c>
-      <c r="W44" s="20">
-        <f>MAX(C44:U44)</f>
-        <v>118.58</v>
-      </c>
       <c r="X44" s="20">
-        <f>AVERAGE(C44:U44)</f>
-        <v>98.280000000000001</v>
+        <f>MAX(C44:V44)</f>
+        <v>119.59</v>
       </c>
       <c r="Y44" s="20">
-        <f>AVERAGE(Q44:U44)</f>
-        <v>118.17999999999999</v>
-      </c>
-      <c r="Z44" s="21">
-        <f>(Y44/X44)-1</f>
-        <v>0.2024827024827025</v>
+        <f>AVERAGE(C44:V44)</f>
+        <v>99.611874999999998</v>
+      </c>
+      <c r="Z44" s="20">
+        <f>AVERAGE(Q44:V44)</f>
+        <v>118.41500000000001</v>
       </c>
       <c r="AA44" s="21">
-        <f>(Y44/V44)-1</f>
-        <v>0.33793728065209994</v>
+        <f>(Z44/Y44)-1</f>
+        <v>0.18876388984747061</v>
       </c>
       <c r="AB44" s="21">
-        <f>(W44/V44)-1</f>
-        <v>0.34246575342465757</v>
-      </c>
-      <c r="AC44" s="22" t="s">
-        <v>121</v>
+        <f>(Z44/W44)-1</f>
+        <v>0.34059775840597761</v>
+      </c>
+      <c r="AC44" s="21">
+        <f>(X44/W44)-1</f>
+        <v>0.35390014717536511</v>
+      </c>
+      <c r="AD44" s="22" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="45" ht="18">
       <c r="A45" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C45" s="17"/>
       <c r="D45" s="17">
@@ -4631,44 +4763,47 @@
       <c r="U45" s="17">
         <v>39.990000000000002</v>
       </c>
-      <c r="V45" s="19">
-        <f>MIN(C45:U45)</f>
+      <c r="V45" s="33">
+        <v>32.990000000000002</v>
+      </c>
+      <c r="W45" s="19">
+        <f>MIN(C45:V45)</f>
         <v>29.989999999999998</v>
       </c>
-      <c r="W45" s="20">
-        <f>MAX(C45:U45)</f>
+      <c r="X45" s="20">
+        <f>MAX(C45:V45)</f>
         <v>44.979999999999997</v>
       </c>
-      <c r="X45" s="20">
-        <f>AVERAGE(C45:U45)</f>
-        <v>36.954375000000006</v>
-      </c>
       <c r="Y45" s="20">
-        <f>AVERAGE(Q45:U45)</f>
-        <v>37.986000000000004</v>
-      </c>
-      <c r="Z45" s="21">
-        <f>(Y45/X45)-1</f>
-        <v>2.7916180425186399e-002</v>
+        <f>AVERAGE(C45:V45)</f>
+        <v>36.72117647058824</v>
+      </c>
+      <c r="Z45" s="20">
+        <f>AVERAGE(Q45:V45)</f>
+        <v>37.153333333333336</v>
       </c>
       <c r="AA45" s="21">
-        <f>(Y45/V45)-1</f>
-        <v>0.26662220740246778</v>
+        <f>(Z45/Y45)-1</f>
+        <v>1.1768600689883391e-002</v>
       </c>
       <c r="AB45" s="21">
-        <f>(W45/V45)-1</f>
+        <f>(Z45/W45)-1</f>
+        <v>0.23885739691008134</v>
+      </c>
+      <c r="AC45" s="21">
+        <f>(X45/W45)-1</f>
         <v>0.49983327775925313</v>
       </c>
-      <c r="AC45" s="22" t="s">
-        <v>124</v>
+      <c r="AD45" s="22" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="46" ht="18">
       <c r="A46" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C46" s="17"/>
       <c r="D46" s="17">
@@ -4676,7 +4811,7 @@
       </c>
       <c r="E46" s="17"/>
       <c r="F46" s="17"/>
-      <c r="G46" s="32">
+      <c r="G46" s="33">
         <v>27.489999999999998</v>
       </c>
       <c r="H46" s="17">
@@ -4685,16 +4820,16 @@
       <c r="I46" s="17">
         <v>35.990000000000002</v>
       </c>
-      <c r="J46" s="32">
+      <c r="J46" s="33">
         <v>25.989999999999998</v>
       </c>
-      <c r="K46" s="32">
+      <c r="K46" s="33">
         <v>25.989999999999998</v>
       </c>
-      <c r="L46" s="32">
+      <c r="L46" s="33">
         <v>25.989999999999998</v>
       </c>
-      <c r="M46" s="32">
+      <c r="M46" s="33">
         <v>25.989999999999998</v>
       </c>
       <c r="N46" s="17">
@@ -4715,50 +4850,53 @@
       <c r="S46" s="17">
         <v>36.530000000000001</v>
       </c>
-      <c r="T46" s="32">
+      <c r="T46" s="33">
         <v>27.989999999999998</v>
       </c>
-      <c r="U46" s="32">
+      <c r="U46" s="33">
         <v>27.989999999999998</v>
       </c>
-      <c r="V46" s="19">
-        <f>MIN(C46:U46)</f>
+      <c r="V46" s="35">
+        <v>30.989999999999998</v>
+      </c>
+      <c r="W46" s="19">
+        <f>MIN(C46:V46)</f>
         <v>25.989999999999998</v>
       </c>
-      <c r="W46" s="20">
-        <f>MAX(C46:U46)</f>
+      <c r="X46" s="20">
+        <f>MAX(C46:V46)</f>
         <v>42</v>
       </c>
-      <c r="X46" s="20">
-        <f>AVERAGE(C46:U46)</f>
-        <v>31.766249999999999</v>
-      </c>
       <c r="Y46" s="20">
-        <f>AVERAGE(Q46:U46)</f>
-        <v>32.808000000000007</v>
-      </c>
-      <c r="Z46" s="21">
-        <f>(Y46/X46)-1</f>
-        <v>3.279423916892954e-002</v>
+        <f>AVERAGE(C46:V46)</f>
+        <v>31.720588235294116</v>
+      </c>
+      <c r="Z46" s="20">
+        <f>AVERAGE(Q46:V46)</f>
+        <v>32.505000000000003</v>
       </c>
       <c r="AA46" s="21">
-        <f>(Y46/V46)-1</f>
-        <v>0.26233166602539471</v>
+        <f>(Z46/Y46)-1</f>
+        <v>2.4728789986091959e-002</v>
       </c>
       <c r="AB46" s="21">
-        <f>(W46/V46)-1</f>
+        <f>(Z46/W46)-1</f>
+        <v>0.25067333589842256</v>
+      </c>
+      <c r="AC46" s="21">
+        <f>(X46/W46)-1</f>
         <v>0.61600615621392851</v>
       </c>
-      <c r="AC46" s="22" t="s">
-        <v>127</v>
+      <c r="AD46" s="22" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="47" ht="18">
       <c r="A47" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C47" s="17"/>
       <c r="D47" s="17">
@@ -4811,44 +4949,47 @@
       <c r="U47" s="17">
         <v>24.899999999999999</v>
       </c>
-      <c r="V47" s="19">
-        <f>MIN(C47:U47)</f>
+      <c r="V47" s="33">
         <v>21.690000000000001</v>
       </c>
-      <c r="W47" s="20">
-        <f>MAX(C47:U47)</f>
+      <c r="W47" s="19">
+        <f>MIN(C47:V47)</f>
+        <v>21.690000000000001</v>
+      </c>
+      <c r="X47" s="20">
+        <f>MAX(C47:V47)</f>
         <v>43.990000000000002</v>
       </c>
-      <c r="X47" s="20">
-        <f>AVERAGE(C47:U47)</f>
-        <v>29.993124999999992</v>
-      </c>
       <c r="Y47" s="20">
-        <f>AVERAGE(Q47:U47)</f>
-        <v>28.816000000000003</v>
-      </c>
-      <c r="Z47" s="21">
-        <f>(Y47/X47)-1</f>
-        <v>-3.9246493988205344e-002</v>
+        <f>AVERAGE(C47:V47)</f>
+        <v>29.504705882352933</v>
+      </c>
+      <c r="Z47" s="20">
+        <f>AVERAGE(Q47:V47)</f>
+        <v>27.628333333333334</v>
       </c>
       <c r="AA47" s="21">
-        <f>(Y47/V47)-1</f>
-        <v>0.32853849700322724</v>
+        <f>(Z47/Y47)-1</f>
+        <v>-6.3595704241264039e-002</v>
       </c>
       <c r="AB47" s="21">
-        <f>(W47/V47)-1</f>
+        <f>(Z47/W47)-1</f>
+        <v>0.27378208083602273</v>
+      </c>
+      <c r="AC47" s="21">
+        <f>(X47/W47)-1</f>
         <v>1.0281235592438911</v>
       </c>
-      <c r="AC47" s="22" t="s">
-        <v>130</v>
+      <c r="AD47" s="22" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="48" ht="54">
       <c r="A48" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C48" s="17"/>
       <c r="D48" s="17"/>
@@ -4869,10 +5010,10 @@
         <v>1714.0799999999999</v>
       </c>
       <c r="K48" s="17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L48" s="17" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M48" s="24">
         <v>1449.28</v>
@@ -4901,44 +5042,47 @@
       <c r="U48" s="17">
         <v>1611.6900000000001</v>
       </c>
-      <c r="V48" s="19">
-        <f>MIN(C48:U48)</f>
+      <c r="V48" s="17">
+        <v>1611.4100000000001</v>
+      </c>
+      <c r="W48" s="19">
+        <f>MIN(C48:V48)</f>
         <v>1449.28</v>
       </c>
-      <c r="W48" s="20">
-        <f>MAX(C48:U48)</f>
+      <c r="X48" s="20">
+        <f>MAX(C48:V48)</f>
         <v>1820.77</v>
       </c>
-      <c r="X48" s="20">
-        <f>AVERAGE(C48:U48)</f>
-        <v>1708.8528571428571</v>
-      </c>
       <c r="Y48" s="20">
-        <f>AVERAGE(Q48:U48)</f>
-        <v>1688.3900000000001</v>
-      </c>
-      <c r="Z48" s="21">
-        <f>(Y48/X48)-1</f>
-        <v>-1.1974616221241074e-002</v>
+        <f>AVERAGE(C48:V48)</f>
+        <v>1702.3566666666666</v>
+      </c>
+      <c r="Z48" s="20">
+        <f>AVERAGE(Q48:V48)</f>
+        <v>1675.5600000000002</v>
       </c>
       <c r="AA48" s="21">
-        <f>(Y48/V48)-1</f>
-        <v>0.16498537204680952</v>
+        <f>(Z48/Y48)-1</f>
+        <v>-1.5740923856536027e-002</v>
       </c>
       <c r="AB48" s="21">
-        <f>(W48/V48)-1</f>
+        <f>(Z48/W48)-1</f>
+        <v>0.15613270037535898</v>
+      </c>
+      <c r="AC48" s="21">
+        <f>(X48/W48)-1</f>
         <v>0.25632727975270475</v>
       </c>
-      <c r="AC48" s="1" t="s">
-        <v>132</v>
+      <c r="AD48" s="1" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="49" ht="18">
       <c r="A49" s="25" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B49" s="26" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C49" s="28"/>
       <c r="D49" s="28"/>
@@ -4989,44 +5133,47 @@
       <c r="U49" s="17">
         <v>39.899999999999999</v>
       </c>
-      <c r="V49" s="19">
-        <f>MIN(C49:U49)</f>
-        <v>33.890000000000001</v>
-      </c>
-      <c r="W49" s="20">
-        <f>MAX(C49:U49)</f>
+      <c r="V49" s="33">
+        <v>31.989999999999998</v>
+      </c>
+      <c r="W49" s="19">
+        <f>MIN(C49:V49)</f>
+        <v>31.989999999999998</v>
+      </c>
+      <c r="X49" s="20">
+        <f>MAX(C49:V49)</f>
         <v>43.210000000000001</v>
       </c>
-      <c r="X49" s="20">
-        <f>AVERAGE(C49:U49)</f>
-        <v>37.415333333333329</v>
-      </c>
       <c r="Y49" s="20">
-        <f>AVERAGE(Q49:U49)</f>
-        <v>40.052</v>
-      </c>
-      <c r="Z49" s="21">
-        <f>(Y49/X49)-1</f>
-        <v>7.0470217201503926e-002</v>
+        <f>AVERAGE(C49:V49)</f>
+        <v>37.076249999999995</v>
+      </c>
+      <c r="Z49" s="20">
+        <f>AVERAGE(Q49:V49)</f>
+        <v>38.708333333333336</v>
       </c>
       <c r="AA49" s="21">
-        <f>(Y49/V49)-1</f>
-        <v>0.1818235467689584</v>
+        <f>(Z49/Y49)-1</f>
+        <v>4.4019644201701569e-002</v>
       </c>
       <c r="AB49" s="21">
-        <f>(W49/V49)-1</f>
-        <v>0.27500737680731779</v>
-      </c>
-      <c r="AC49" s="22" t="s">
-        <v>135</v>
+        <f>(Z49/W49)-1</f>
+        <v>0.21001354589976051</v>
+      </c>
+      <c r="AC49" s="21">
+        <f>(X49/W49)-1</f>
+        <v>0.35073460456392636</v>
+      </c>
+      <c r="AD49" s="22" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="50" ht="18">
       <c r="A50" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C50" s="17"/>
       <c r="D50" s="17"/>
@@ -5077,44 +5224,47 @@
       <c r="U50" s="17">
         <v>84.900000000000006</v>
       </c>
-      <c r="V50" s="19">
-        <f>MIN(C50:U50)</f>
+      <c r="V50" s="17">
+        <v>83.079999999999998</v>
+      </c>
+      <c r="W50" s="19">
+        <f>MIN(C50:V50)</f>
         <v>81.689999999999998</v>
       </c>
-      <c r="W50" s="20">
-        <f>MAX(C50:U50)</f>
+      <c r="X50" s="20">
+        <f>MAX(C50:V50)</f>
         <v>93.280000000000001</v>
       </c>
-      <c r="X50" s="20">
-        <f>AVERAGE(C50:U50)</f>
-        <v>89.04733333333337</v>
-      </c>
       <c r="Y50" s="20">
-        <f>AVERAGE(Q50:U50)</f>
-        <v>86.218000000000004</v>
-      </c>
-      <c r="Z50" s="21">
-        <f>(Y50/X50)-1</f>
-        <v>-3.1773363978708336e-002</v>
+        <f>AVERAGE(C50:V50)</f>
+        <v>88.674375000000026</v>
+      </c>
+      <c r="Z50" s="20">
+        <f>AVERAGE(Q50:V50)</f>
+        <v>85.695000000000007</v>
       </c>
       <c r="AA50" s="21">
-        <f>(Y50/V50)-1</f>
-        <v>5.5429061084588227e-002</v>
+        <f>(Z50/Y50)-1</f>
+        <v>-3.3599052713932487e-002</v>
       </c>
       <c r="AB50" s="21">
-        <f>(W50/V50)-1</f>
+        <f>(Z50/W50)-1</f>
+        <v>4.902680866691167e-002</v>
+      </c>
+      <c r="AC50" s="21">
+        <f>(X50/W50)-1</f>
         <v>0.1418778308238462</v>
       </c>
-      <c r="AC50" s="1" t="s">
-        <v>138</v>
+      <c r="AD50" s="1" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="51" ht="18">
       <c r="A51" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C51" s="17"/>
       <c r="D51" s="17"/>
@@ -5167,44 +5317,47 @@
       <c r="U51" s="17">
         <v>309.05000000000001</v>
       </c>
-      <c r="V51" s="19">
-        <f>MIN(C51:U51)</f>
+      <c r="V51" s="17">
         <v>309.05000000000001</v>
       </c>
-      <c r="W51" s="20">
-        <f>MAX(C51:U51)</f>
+      <c r="W51" s="19">
+        <f>MIN(C51:V51)</f>
         <v>309.05000000000001</v>
       </c>
       <c r="X51" s="20">
-        <f>AVERAGE(C51:U51)</f>
+        <f>MAX(C51:V51)</f>
+        <v>309.05000000000001</v>
+      </c>
+      <c r="Y51" s="20">
+        <f>AVERAGE(C51:V51)</f>
         <v>309.05000000000007</v>
       </c>
-      <c r="Y51" s="20">
-        <f>AVERAGE(Q51:U51)</f>
+      <c r="Z51" s="20">
+        <f>AVERAGE(Q51:V51)</f>
         <v>309.05000000000001</v>
       </c>
-      <c r="Z51" s="21">
-        <f>(Y51/X51)-1</f>
+      <c r="AA51" s="21">
+        <f>(Z51/Y51)-1</f>
         <v>-2.2204460492503131e-016</v>
       </c>
-      <c r="AA51" s="21">
-        <f>(Y51/V51)-1</f>
+      <c r="AB51" s="21">
+        <f>(Z51/W51)-1</f>
         <v>0</v>
       </c>
-      <c r="AB51" s="21">
-        <f>(W51/V51)-1</f>
+      <c r="AC51" s="21">
+        <f>(X51/W51)-1</f>
         <v>0</v>
       </c>
-      <c r="AC51" s="22" t="s">
-        <v>141</v>
+      <c r="AD51" s="22" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="52" ht="18">
       <c r="A52" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C52" s="17"/>
       <c r="D52" s="17"/>
@@ -5255,41 +5408,44 @@
       <c r="U52" s="17">
         <v>108.98999999999999</v>
       </c>
-      <c r="V52" s="19">
-        <f>MIN(C52:U52)</f>
+      <c r="V52" s="17">
         <v>108.98999999999999</v>
       </c>
-      <c r="W52" s="20">
-        <f>MAX(C52:U52)</f>
+      <c r="W52" s="19">
+        <f>MIN(C52:V52)</f>
         <v>108.98999999999999</v>
       </c>
       <c r="X52" s="20">
-        <f>AVERAGE(C52:U52)</f>
+        <f>MAX(C52:V52)</f>
         <v>108.98999999999999</v>
       </c>
       <c r="Y52" s="20">
-        <f>AVERAGE(Q52:U52)</f>
-        <v>108.98999999999998</v>
-      </c>
-      <c r="Z52" s="21">
-        <f>(Y52/X52)-1</f>
-        <v>-1.1102230246251565e-016</v>
+        <f>AVERAGE(C52:V52)</f>
+        <v>108.98999999999999</v>
+      </c>
+      <c r="Z52" s="20">
+        <f>AVERAGE(Q52:V52)</f>
+        <v>108.98999999999999</v>
       </c>
       <c r="AA52" s="21">
-        <f>(Y52/V52)-1</f>
-        <v>-1.1102230246251565e-016</v>
+        <f>(Z52/Y52)-1</f>
+        <v>0</v>
       </c>
       <c r="AB52" s="21">
-        <f>(W52/V52)-1</f>
+        <f>(Z52/W52)-1</f>
         <v>0</v>
       </c>
-      <c r="AC52" s="35" t="s">
-        <v>143</v>
+      <c r="AC52" s="21">
+        <f>(X52/W52)-1</f>
+        <v>0</v>
+      </c>
+      <c r="AD52" s="37" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="53" ht="18">
       <c r="B53" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="O53" s="17">
         <v>1.49</v>
@@ -5312,93 +5468,96 @@
       <c r="U53" s="17">
         <v>1.99</v>
       </c>
-      <c r="V53" s="19">
-        <f>MIN(C53:U53)</f>
+      <c r="V53" s="17">
+        <v>1.99</v>
+      </c>
+      <c r="W53" s="19">
+        <f>MIN(C53:V53)</f>
         <v>1.49</v>
       </c>
-      <c r="W53" s="20">
-        <f>MAX(C53:U53)</f>
+      <c r="X53" s="20">
+        <f>MAX(C53:V53)</f>
         <v>1.99</v>
       </c>
-      <c r="X53" s="20">
-        <f>AVERAGE(C53:U53)</f>
-        <v>1.6328571428571428</v>
-      </c>
       <c r="Y53" s="20">
-        <f>AVERAGE(Q53:U53)</f>
-        <v>1.6899999999999999</v>
-      </c>
-      <c r="Z53" s="21">
-        <f>(Y53/X53)-1</f>
-        <v>3.4995625546806686e-002</v>
+        <f>AVERAGE(C53:V53)</f>
+        <v>1.6775</v>
+      </c>
+      <c r="Z53" s="20">
+        <f>AVERAGE(Q53:V53)</f>
+        <v>1.74</v>
       </c>
       <c r="AA53" s="21">
-        <f>(Y53/V53)-1</f>
-        <v>0.13422818791946312</v>
+        <f>(Z53/Y53)-1</f>
+        <v>3.7257824143070106e-002</v>
       </c>
       <c r="AB53" s="21">
-        <f>(W53/V53)-1</f>
+        <f>(Z53/W53)-1</f>
+        <v>0.16778523489932895</v>
+      </c>
+      <c r="AC53" s="21">
+        <f>(X53/W53)-1</f>
         <v>0.33557046979865768</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="V1:V6"/>
     <mergeCell ref="W1:W6"/>
     <mergeCell ref="X1:X6"/>
     <mergeCell ref="Y1:Y6"/>
     <mergeCell ref="Z1:Z6"/>
     <mergeCell ref="AA1:AA6"/>
     <mergeCell ref="AB1:AB6"/>
+    <mergeCell ref="AC1:AC6"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="B5"/>
-    <hyperlink r:id="rId2" ref="AC8"/>
-    <hyperlink r:id="rId3" ref="AC9"/>
-    <hyperlink r:id="rId4" ref="AC10"/>
-    <hyperlink r:id="rId5" ref="AC11"/>
-    <hyperlink r:id="rId6" ref="AC12"/>
-    <hyperlink r:id="rId7" ref="AC13"/>
-    <hyperlink r:id="rId8" ref="AC14"/>
-    <hyperlink r:id="rId9" ref="AC15"/>
-    <hyperlink r:id="rId10" ref="AC16"/>
-    <hyperlink r:id="rId11" ref="AC17"/>
-    <hyperlink r:id="rId12" ref="AC18"/>
-    <hyperlink r:id="rId13" ref="AC19"/>
-    <hyperlink r:id="rId14" ref="AC20"/>
-    <hyperlink r:id="rId15" ref="AC21"/>
-    <hyperlink r:id="rId16" ref="AC22"/>
-    <hyperlink r:id="rId17" ref="AC23"/>
-    <hyperlink r:id="rId18" ref="AC24"/>
-    <hyperlink r:id="rId19" ref="AC25"/>
-    <hyperlink r:id="rId20" ref="AC26"/>
-    <hyperlink r:id="rId21" ref="AC27"/>
-    <hyperlink r:id="rId22" ref="AC28"/>
-    <hyperlink r:id="rId23" ref="AC29"/>
-    <hyperlink r:id="rId24" ref="AC30"/>
-    <hyperlink r:id="rId25" ref="AC31"/>
-    <hyperlink r:id="rId26" ref="AC32"/>
-    <hyperlink r:id="rId27" ref="AC33"/>
-    <hyperlink r:id="rId28" ref="AC34"/>
-    <hyperlink r:id="rId29" ref="AC35"/>
-    <hyperlink r:id="rId30" ref="AC36"/>
-    <hyperlink r:id="rId30" ref="AC37"/>
-    <hyperlink r:id="rId30" ref="AC38"/>
-    <hyperlink r:id="rId30" ref="AC39"/>
-    <hyperlink r:id="rId30" ref="AC40"/>
-    <hyperlink r:id="rId30" ref="AC41"/>
-    <hyperlink r:id="rId31" ref="AC43"/>
-    <hyperlink r:id="rId32" ref="AC44"/>
-    <hyperlink r:id="rId33" ref="AC45"/>
-    <hyperlink r:id="rId34" ref="AC46"/>
-    <hyperlink r:id="rId35" ref="AC47"/>
-    <hyperlink r:id="rId36" ref="AC49"/>
-    <hyperlink r:id="rId37" ref="AC51"/>
-    <hyperlink r:id="rId38" ref="AC52"/>
+    <hyperlink r:id="rId2" ref="AD8"/>
+    <hyperlink r:id="rId3" ref="AD9"/>
+    <hyperlink r:id="rId4" ref="AD10"/>
+    <hyperlink r:id="rId5" ref="AD11"/>
+    <hyperlink r:id="rId6" ref="AD12"/>
+    <hyperlink r:id="rId7" ref="AD13"/>
+    <hyperlink r:id="rId8" ref="AD14"/>
+    <hyperlink r:id="rId9" ref="AD15"/>
+    <hyperlink r:id="rId10" ref="AD16"/>
+    <hyperlink r:id="rId11" ref="AD17"/>
+    <hyperlink r:id="rId12" ref="AD18"/>
+    <hyperlink r:id="rId13" ref="AD19"/>
+    <hyperlink r:id="rId14" ref="AD20"/>
+    <hyperlink r:id="rId15" ref="AD21"/>
+    <hyperlink r:id="rId16" ref="AD22"/>
+    <hyperlink r:id="rId17" ref="AD23"/>
+    <hyperlink r:id="rId18" ref="AD24"/>
+    <hyperlink r:id="rId19" ref="AD25"/>
+    <hyperlink r:id="rId20" ref="AD26"/>
+    <hyperlink r:id="rId21" ref="AD27"/>
+    <hyperlink r:id="rId22" ref="AD28"/>
+    <hyperlink r:id="rId23" ref="AD29"/>
+    <hyperlink r:id="rId24" ref="AD30"/>
+    <hyperlink r:id="rId25" ref="AD31"/>
+    <hyperlink r:id="rId26" ref="AD32"/>
+    <hyperlink r:id="rId27" ref="AD33"/>
+    <hyperlink r:id="rId28" ref="AD34"/>
+    <hyperlink r:id="rId29" ref="AD35"/>
+    <hyperlink r:id="rId30" ref="AD36"/>
+    <hyperlink r:id="rId30" ref="AD37"/>
+    <hyperlink r:id="rId30" ref="AD38"/>
+    <hyperlink r:id="rId30" ref="AD39"/>
+    <hyperlink r:id="rId30" ref="AD40"/>
+    <hyperlink r:id="rId30" ref="AD41"/>
+    <hyperlink r:id="rId31" ref="AD43"/>
+    <hyperlink r:id="rId32" ref="AD44"/>
+    <hyperlink r:id="rId33" ref="AD45"/>
+    <hyperlink r:id="rId34" ref="AD46"/>
+    <hyperlink r:id="rId35" ref="AD47"/>
+    <hyperlink r:id="rId36" ref="AD49"/>
+    <hyperlink r:id="rId37" ref="AD51"/>
+    <hyperlink r:id="rId38" ref="AD52"/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0"/>
-  <pageMargins left="0.70078740157480324" right="0.70078740157480324" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="35" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="0" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <pageMargins left="0.25196850393700787" right="0.25196850393700787" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
+  <pageSetup paperSize="9" scale="37" firstPageNumber="1" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="1" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/analyse-prix-composants.xlsx
+++ b/analyse-prix-composants.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Feuille1" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Feuille1!$A:$AC</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Feuille1!$A:$AE</definedName>
     <definedName name="Print_Titles" localSheetId="0">Feuille1!$7:$7</definedName>
   </definedNames>
   <calcPr/>
@@ -54,12 +54,6 @@
     <t xml:space="preserve">(c) 2025, 2026 Alexia Gossa</t>
   </si>
   <si>
-    <t xml:space="preserve">Chaque samedi sur Twitch, depuis le 6 décembre 2025, on fait le point sur les prix de l'IT en regardant quelques composants.</t>
-  </si>
-  <si>
-    <t>https://www.twitch.tv/alexia_vassiliki</t>
-  </si>
-  <si>
     <t>Type</t>
   </si>
   <si>
@@ -124,6 +118,12 @@
   </si>
   <si>
     <t xml:space="preserve">14 mar 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21 mar 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28 mar 2026</t>
   </si>
   <si>
     <t>Min</t>
@@ -620,6 +620,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor rgb="FFFFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor theme="4" tint="0.79998168889431442"/>
       </patternFill>
@@ -628,12 +634,6 @@
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.049989318521683403"/>
         <bgColor theme="0" tint="-0.049989318521683403"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor rgb="FFFFC000"/>
       </patternFill>
     </fill>
     <fill>
@@ -700,7 +700,7 @@
     <xf fontId="2" fillId="3" borderId="2" numFmtId="0" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf fontId="0" fillId="4" borderId="0" numFmtId="43" applyNumberFormat="1" applyFont="0" applyFill="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
     <xf fontId="3" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -758,14 +758,18 @@
       <alignment horizontal="right" vertical="center"/>
       <protection locked="1"/>
     </xf>
-    <xf fontId="3" fillId="8" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf fontId="5" fillId="8" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="1"/>
+    </xf>
+    <xf fontId="3" fillId="9" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="1"/>
     </xf>
-    <xf fontId="3" fillId="8" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf fontId="3" fillId="9" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="3" fillId="8" borderId="0" numFmtId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf fontId="3" fillId="9" borderId="0" numFmtId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf fontId="15" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -778,18 +782,14 @@
       <alignment horizontal="right" vertical="center"/>
       <protection locked="1"/>
     </xf>
-    <xf fontId="3" fillId="9" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf fontId="3" fillId="10" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf fontId="4" fillId="9" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf fontId="4" fillId="10" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf fontId="14" fillId="9" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf fontId="14" fillId="10" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="1"/>
-    </xf>
-    <xf fontId="5" fillId="9" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
       <protection locked="1"/>
     </xf>
     <xf fontId="5" fillId="10" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -800,12 +800,16 @@
       <alignment horizontal="right" vertical="center"/>
       <protection locked="1"/>
     </xf>
-    <xf fontId="5" fillId="9" borderId="0" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf fontId="5" fillId="10" borderId="0" numFmtId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
       <protection locked="1"/>
     </xf>
     <xf fontId="16" fillId="0" borderId="0" numFmtId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf fontId="17" fillId="8" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="1"/>
     </xf>
     <xf fontId="10" fillId="12" borderId="0" numFmtId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1342,12 +1346,12 @@
     <col bestFit="1" min="12" max="12" style="4" width="11.7109375"/>
     <col bestFit="1" min="13" max="13" style="4" width="13.00390625"/>
     <col bestFit="1" min="14" max="15" style="4" width="14.140625"/>
-    <col customWidth="1" min="16" max="22" style="1" width="12.7109375"/>
-    <col customWidth="1" min="23" max="26" style="2" width="12.7109375"/>
-    <col customWidth="1" min="27" max="27" style="2" width="14.140625"/>
-    <col customWidth="1" min="28" max="29" style="2" width="12.7109375"/>
-    <col customWidth="1" min="30" max="30" style="5" width="42.28125"/>
-    <col min="31" max="16384" style="1" width="9.140625"/>
+    <col customWidth="1" min="16" max="24" style="1" width="12.7109375"/>
+    <col customWidth="1" min="25" max="28" style="2" width="12.7109375"/>
+    <col customWidth="1" min="29" max="29" style="2" width="14.140625"/>
+    <col customWidth="1" min="30" max="31" style="2" width="12.7109375"/>
+    <col customWidth="1" min="32" max="32" style="5" width="42.28125"/>
+    <col min="33" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" ht="33">
@@ -1362,28 +1366,30 @@
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
-      <c r="W1" s="7" t="s">
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="X1" s="7" t="s">
+      <c r="Z1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="Y1" s="7" t="s">
+      <c r="AA1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="Z1" s="7" t="s">
+      <c r="AB1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="AA1" s="7" t="s">
+      <c r="AC1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="AB1" s="7" t="s">
+      <c r="AD1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="AC1" s="7" t="s">
+      <c r="AE1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="AD1" s="5"/>
+      <c r="AF1" s="5"/>
     </row>
     <row r="2" ht="23.25">
       <c r="A2" s="2"/>
@@ -1397,13 +1403,15 @@
       <c r="T2" s="1"/>
       <c r="U2" s="1"/>
       <c r="V2" s="1"/>
-      <c r="W2" s="7"/>
-      <c r="X2" s="7"/>
+      <c r="W2" s="1"/>
+      <c r="X2" s="1"/>
       <c r="Y2" s="7"/>
       <c r="Z2" s="7"/>
       <c r="AA2" s="7"/>
       <c r="AB2" s="7"/>
       <c r="AC2" s="7"/>
+      <c r="AD2" s="7"/>
+      <c r="AE2" s="7"/>
     </row>
     <row r="3" ht="18">
       <c r="A3" s="2"/>
@@ -1415,19 +1423,19 @@
       <c r="T3" s="1"/>
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
-      <c r="W3" s="7"/>
-      <c r="X3" s="7"/>
+      <c r="W3" s="1"/>
+      <c r="X3" s="1"/>
       <c r="Y3" s="7"/>
       <c r="Z3" s="7"/>
       <c r="AA3" s="7"/>
       <c r="AB3" s="7"/>
       <c r="AC3" s="7"/>
+      <c r="AD3" s="7"/>
+      <c r="AE3" s="7"/>
     </row>
     <row r="4" ht="54">
       <c r="A4" s="2"/>
-      <c r="B4" s="3" t="s">
-        <v>9</v>
-      </c>
+      <c r="B4" s="3"/>
       <c r="G4" s="4"/>
       <c r="N4" s="4"/>
       <c r="Q4" s="1"/>
@@ -1436,19 +1444,19 @@
       <c r="T4" s="1"/>
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
-      <c r="W4" s="7"/>
-      <c r="X4" s="7"/>
+      <c r="W4" s="1"/>
+      <c r="X4" s="1"/>
       <c r="Y4" s="7"/>
       <c r="Z4" s="7"/>
       <c r="AA4" s="7"/>
       <c r="AB4" s="7"/>
       <c r="AC4" s="7"/>
+      <c r="AD4" s="7"/>
+      <c r="AE4" s="7"/>
     </row>
     <row r="5" ht="23.25">
       <c r="A5" s="2"/>
-      <c r="B5" s="9" t="s">
-        <v>10</v>
-      </c>
+      <c r="B5" s="9"/>
       <c r="N5" s="4"/>
       <c r="Q5" s="1"/>
       <c r="R5" s="1"/>
@@ -1456,15 +1464,17 @@
       <c r="T5" s="1"/>
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
-      <c r="W5" s="7"/>
-      <c r="X5" s="7"/>
+      <c r="W5" s="1"/>
+      <c r="X5" s="1"/>
       <c r="Y5" s="7"/>
       <c r="Z5" s="7"/>
       <c r="AA5" s="7"/>
       <c r="AB5" s="7"/>
       <c r="AC5" s="7"/>
+      <c r="AD5" s="7"/>
+      <c r="AE5" s="7"/>
     </row>
-    <row r="6" ht="37.5" customHeight="1">
+    <row r="6" ht="24" customHeight="1">
       <c r="A6" s="2"/>
       <c r="N6" s="4"/>
       <c r="Q6" s="1"/>
@@ -1473,103 +1483,111 @@
       <c r="T6" s="1"/>
       <c r="U6" s="1"/>
       <c r="V6" s="1"/>
-      <c r="W6" s="7"/>
-      <c r="X6" s="7"/>
+      <c r="W6" s="1"/>
+      <c r="X6" s="1"/>
       <c r="Y6" s="7"/>
       <c r="Z6" s="7"/>
       <c r="AA6" s="7"/>
       <c r="AB6" s="7"/>
       <c r="AC6" s="7"/>
+      <c r="AD6" s="7"/>
+      <c r="AE6" s="7"/>
     </row>
     <row r="7" ht="18">
       <c r="A7" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="11" t="s">
+      <c r="D7" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="E7" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="F7" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="G7" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="H7" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="I7" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="H7" s="12" t="s">
+      <c r="J7" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="I7" s="12" t="s">
+      <c r="K7" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="J7" s="12" t="s">
+      <c r="L7" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="K7" s="12" t="s">
+      <c r="M7" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="L7" s="12" t="s">
+      <c r="N7" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="M7" s="12" t="s">
+      <c r="O7" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="N7" s="12" t="s">
+      <c r="P7" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="O7" s="12" t="s">
+      <c r="Q7" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="P7" s="12" t="s">
+      <c r="R7" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="Q7" s="12" t="s">
+      <c r="S7" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="R7" s="12" t="s">
+      <c r="T7" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="S7" s="12" t="s">
+      <c r="U7" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="T7" s="12" t="s">
+      <c r="V7" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="U7" s="12" t="s">
+      <c r="W7" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="V7" s="12" t="s">
+      <c r="X7" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="W7" s="13" t="s">
+      <c r="Y7" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="X7" s="13" t="s">
+      <c r="Z7" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="Y7" s="13" t="s">
+      <c r="AA7" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="Z7" s="13" t="s">
+      <c r="AB7" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="AA7" s="13" t="s">
+      <c r="AC7" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="AB7" s="13" t="s">
+      <c r="AD7" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="AC7" s="13" t="s">
+      <c r="AE7" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="AD7" s="5" t="s">
+      <c r="AF7" s="5" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1634,38 +1652,44 @@
       <c r="V8" s="18">
         <v>366.26999999999998</v>
       </c>
-      <c r="W8" s="19">
-        <f>MIN(C8:V8)</f>
+      <c r="W8" s="18">
+        <v>370.38999999999999</v>
+      </c>
+      <c r="X8" s="19">
+        <v>415.97000000000003</v>
+      </c>
+      <c r="Y8" s="20">
+        <f>MIN(C8:X8)</f>
         <v>171.88</v>
       </c>
-      <c r="X8" s="20">
-        <f>MAX(C8:V8)</f>
-        <v>367.56</v>
-      </c>
-      <c r="Y8" s="20">
-        <f>AVERAGE(C8:V8)</f>
-        <v>336.27687500000013</v>
-      </c>
-      <c r="Z8" s="20">
-        <f>AVERAGE(Q8:V8)</f>
-        <v>366.58999999999997</v>
+      <c r="Z8" s="21">
+        <f>MAX(C8:X8)</f>
+        <v>415.97000000000003</v>
       </c>
       <c r="AA8" s="21">
+        <f>AVERAGE(C8:X8)</f>
+        <v>342.5994444444446</v>
+      </c>
+      <c r="AB8" s="21">
+        <f>AVERAGE(Q8:X8)</f>
+        <v>373.23749999999995</v>
+      </c>
+      <c r="AC8" s="22">
+        <f>(AB8/AA8)-1</f>
+        <v>8.9428211435770733e-002</v>
+      </c>
+      <c r="AD8" s="22">
+        <f>(AB8/Y8)-1</f>
+        <v>1.1715004654410053</v>
+      </c>
+      <c r="AE8" s="22">
         <f>(Z8/Y8)-1</f>
-        <v>9.0143352854696879e-002</v>
-      </c>
-      <c r="AB8" s="21">
-        <f>(Z8/W8)-1</f>
-        <v>1.1328252269024901</v>
-      </c>
-      <c r="AC8" s="21">
-        <f>(X8/W8)-1</f>
-        <v>1.1384686990923902</v>
-      </c>
-      <c r="AD8" s="22" t="s">
+        <v>1.4201186874563652</v>
+      </c>
+      <c r="AF8" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="AE8" s="23">
+      <c r="AG8" s="24">
         <f>C2*1</f>
         <v>0</v>
       </c>
@@ -1678,7 +1702,7 @@
         <v>45</v>
       </c>
       <c r="C9" s="16"/>
-      <c r="D9" s="24">
+      <c r="D9" s="25">
         <v>200.47999999999999</v>
       </c>
       <c r="E9" s="16"/>
@@ -1731,58 +1755,64 @@
       <c r="V9" s="18">
         <v>978.75</v>
       </c>
-      <c r="W9" s="19">
-        <f>MIN(C9:V9)</f>
+      <c r="W9" s="18">
+        <v>978.75</v>
+      </c>
+      <c r="X9" s="18">
+        <v>978.75</v>
+      </c>
+      <c r="Y9" s="20">
+        <f>MIN(C9:X9)</f>
         <v>200.47999999999999</v>
       </c>
-      <c r="X9" s="20">
-        <f>MAX(C9:V9)</f>
+      <c r="Z9" s="21">
+        <f>MAX(C9:X9)</f>
         <v>978.75</v>
       </c>
-      <c r="Y9" s="20">
-        <f>AVERAGE(C9:V9)</f>
-        <v>778.50750000000005</v>
-      </c>
-      <c r="Z9" s="20">
-        <f>AVERAGE(Q9:V9)</f>
-        <v>849.6583333333333</v>
-      </c>
       <c r="AA9" s="21">
+        <f>AVERAGE(C9:X9)</f>
+        <v>800.75666666666666</v>
+      </c>
+      <c r="AB9" s="21">
+        <f>AVERAGE(Q9:X9)</f>
+        <v>881.93124999999998</v>
+      </c>
+      <c r="AC9" s="22">
+        <f>(AB9/AA9)-1</f>
+        <v>0.10137234782101934</v>
+      </c>
+      <c r="AD9" s="22">
+        <f>(AB9/Y9)-1</f>
+        <v>3.3990984138068638</v>
+      </c>
+      <c r="AE9" s="22">
         <f>(Z9/Y9)-1</f>
-        <v>9.1393895798477454e-002</v>
-      </c>
-      <c r="AB9" s="21">
-        <f>(Z9/W9)-1</f>
-        <v>3.2381201782388933</v>
-      </c>
-      <c r="AC9" s="21">
-        <f>(X9/W9)-1</f>
         <v>3.8820331205107745</v>
       </c>
-      <c r="AD9" s="22" t="s">
+      <c r="AF9" s="23" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="10" ht="36">
-      <c r="A10" s="25" t="s">
+      <c r="A10" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="26" t="s">
+      <c r="B10" s="27" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="27"/>
-      <c r="D10" s="24">
+      <c r="C10" s="28"/>
+      <c r="D10" s="25">
         <v>284.13</v>
       </c>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="28">
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="29">
         <v>403.11000000000001</v>
       </c>
-      <c r="H10" s="28">
+      <c r="H10" s="29">
         <v>325.23000000000002</v>
       </c>
-      <c r="I10" s="28">
+      <c r="I10" s="29">
         <v>647.89999999999998</v>
       </c>
       <c r="J10" s="18">
@@ -1824,35 +1854,41 @@
       <c r="V10" s="18">
         <v>696.10000000000002</v>
       </c>
-      <c r="W10" s="19">
-        <f>MIN(C10:V10)</f>
+      <c r="W10" s="18">
+        <v>710</v>
+      </c>
+      <c r="X10" s="19">
+        <v>717.78999999999996</v>
+      </c>
+      <c r="Y10" s="20">
+        <f>MIN(C10:X10)</f>
         <v>284.13</v>
       </c>
-      <c r="X10" s="20">
-        <f>MAX(C10:V10)</f>
-        <v>700</v>
-      </c>
-      <c r="Y10" s="20">
-        <f>AVERAGE(C10:V10)</f>
-        <v>585.23470588235296</v>
-      </c>
-      <c r="Z10" s="20">
-        <f>AVERAGE(Q10:V10)</f>
-        <v>644.01999999999998</v>
+      <c r="Z10" s="21">
+        <f>MAX(C10:X10)</f>
+        <v>717.78999999999996</v>
       </c>
       <c r="AA10" s="21">
+        <f>AVERAGE(C10:X10)</f>
+        <v>598.77789473684209</v>
+      </c>
+      <c r="AB10" s="21">
+        <f>AVERAGE(Q10:X10)</f>
+        <v>661.48874999999998</v>
+      </c>
+      <c r="AC10" s="22">
+        <f>(AB10/AA10)-1</f>
+        <v>0.10473141345793802</v>
+      </c>
+      <c r="AD10" s="22">
+        <f>(AB10/Y10)-1</f>
+        <v>1.3281200506810262</v>
+      </c>
+      <c r="AE10" s="22">
         <f>(Z10/Y10)-1</f>
-        <v>0.10044738209607207</v>
-      </c>
-      <c r="AB10" s="21">
-        <f>(Z10/W10)-1</f>
-        <v>1.2666385105409494</v>
-      </c>
-      <c r="AC10" s="21">
-        <f>(X10/W10)-1</f>
-        <v>1.4636610002463661</v>
-      </c>
-      <c r="AD10" s="22" t="s">
+        <v>1.5262731848097699</v>
+      </c>
+      <c r="AF10" s="23" t="s">
         <v>48</v>
       </c>
     </row>
@@ -1890,13 +1926,13 @@
       <c r="O11" s="18">
         <v>731.50999999999999</v>
       </c>
-      <c r="P11" s="29">
+      <c r="P11" s="19">
         <v>863.05999999999995</v>
       </c>
-      <c r="Q11" s="29">
+      <c r="Q11" s="19">
         <v>863.60000000000002</v>
       </c>
-      <c r="R11" s="29">
+      <c r="R11" s="19">
         <v>822.25</v>
       </c>
       <c r="S11" s="18">
@@ -1912,34 +1948,40 @@
         <v>807.03999999999996</v>
       </c>
       <c r="W11" s="19">
-        <f>MIN(C11:V11)</f>
+        <v>824.09000000000003</v>
+      </c>
+      <c r="X11" s="19">
+        <v>827.74000000000001</v>
+      </c>
+      <c r="Y11" s="20">
+        <f>MIN(C11:X11)</f>
         <v>685.71000000000004</v>
       </c>
-      <c r="X11" s="20">
-        <f>MAX(C11:V11)</f>
+      <c r="Z11" s="21">
+        <f>MAX(C11:X11)</f>
         <v>863.60000000000002</v>
       </c>
-      <c r="Y11" s="20">
-        <f>AVERAGE(C11:V11)</f>
-        <v>779.84928571428566</v>
-      </c>
-      <c r="Z11" s="20">
-        <f>AVERAGE(Q11:V11)</f>
-        <v>803.48333333333323</v>
-      </c>
       <c r="AA11" s="21">
+        <f>AVERAGE(C11:X11)</f>
+        <v>785.60749999999996</v>
+      </c>
+      <c r="AB11" s="21">
+        <f>AVERAGE(Q11:X11)</f>
+        <v>809.09124999999995</v>
+      </c>
+      <c r="AC11" s="22">
+        <f>(AB11/AA11)-1</f>
+        <v>2.989247174956966e-002</v>
+      </c>
+      <c r="AD11" s="22">
+        <f>(AB11/Y11)-1</f>
+        <v>0.17993211415904664</v>
+      </c>
+      <c r="AE11" s="22">
         <f>(Z11/Y11)-1</f>
-        <v>3.0305916863667459e-002</v>
-      </c>
-      <c r="AB11" s="21">
-        <f>(Z11/W11)-1</f>
-        <v>0.17175385123934772</v>
-      </c>
-      <c r="AC11" s="21">
-        <f>(X11/W11)-1</f>
         <v>0.25942453807002952</v>
       </c>
-      <c r="AD11" s="22" t="s">
+      <c r="AF11" s="23" t="s">
         <v>50</v>
       </c>
     </row>
@@ -1965,7 +2007,7 @@
       <c r="I12" s="17">
         <v>550.98000000000002</v>
       </c>
-      <c r="J12" s="24">
+      <c r="J12" s="25">
         <v>546.98000000000002</v>
       </c>
       <c r="K12" s="17">
@@ -1992,10 +2034,10 @@
       <c r="R12" s="18">
         <v>575.98000000000002</v>
       </c>
-      <c r="S12" s="24">
+      <c r="S12" s="25">
         <v>479</v>
       </c>
-      <c r="T12" s="24">
+      <c r="T12" s="25">
         <v>465</v>
       </c>
       <c r="U12" s="18">
@@ -2004,76 +2046,82 @@
       <c r="V12" s="18">
         <v>573.98000000000002</v>
       </c>
-      <c r="W12" s="19">
-        <f>MIN(C12:V12)</f>
+      <c r="W12" s="18">
+        <v>552.98000000000002</v>
+      </c>
+      <c r="X12" s="18">
+        <v>555.91999999999996</v>
+      </c>
+      <c r="Y12" s="20">
+        <f>MIN(C12:X12)</f>
         <v>465</v>
       </c>
-      <c r="X12" s="20">
-        <f>MAX(C12:V12)</f>
+      <c r="Z12" s="21">
+        <f>MAX(C12:X12)</f>
         <v>623.12</v>
       </c>
-      <c r="Y12" s="20">
-        <f>AVERAGE(C12:V12)</f>
-        <v>552.69647058823512</v>
-      </c>
-      <c r="Z12" s="20">
-        <f>AVERAGE(Q12:V12)</f>
-        <v>537.15333333333331</v>
-      </c>
       <c r="AA12" s="21">
+        <f>AVERAGE(C12:X12)</f>
+        <v>552.88105263157877</v>
+      </c>
+      <c r="AB12" s="21">
+        <f>AVERAGE(Q12:X12)</f>
+        <v>541.47749999999996</v>
+      </c>
+      <c r="AC12" s="22">
+        <f>(AB12/AA12)-1</f>
+        <v>-2.0625688974691192e-002</v>
+      </c>
+      <c r="AD12" s="22">
+        <f>(AB12/Y12)-1</f>
+        <v>0.16446774193548386</v>
+      </c>
+      <c r="AE12" s="22">
         <f>(Z12/Y12)-1</f>
-        <v>-2.8122374724700583e-002</v>
-      </c>
-      <c r="AB12" s="21">
-        <f>(Z12/W12)-1</f>
-        <v>0.15516845878136198</v>
-      </c>
-      <c r="AC12" s="21">
-        <f>(X12/W12)-1</f>
         <v>0.34004301075268817</v>
       </c>
-      <c r="AD12" s="22" t="s">
+      <c r="AF12" s="23" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="13" ht="36">
-      <c r="A13" s="25" t="s">
+      <c r="A13" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="B13" s="26" t="s">
+      <c r="B13" s="27" t="s">
         <v>55</v>
       </c>
-      <c r="C13" s="27"/>
-      <c r="D13" s="24">
+      <c r="C13" s="28"/>
+      <c r="D13" s="25">
         <v>684.98000000000002</v>
       </c>
-      <c r="E13" s="27"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="28">
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="29">
         <v>839</v>
       </c>
-      <c r="H13" s="28">
+      <c r="H13" s="29">
         <v>857.05999999999995</v>
       </c>
-      <c r="I13" s="28">
+      <c r="I13" s="29">
         <v>826.44000000000005</v>
       </c>
-      <c r="J13" s="28">
+      <c r="J13" s="29">
         <v>853.54999999999995</v>
       </c>
-      <c r="K13" s="28">
+      <c r="K13" s="29">
         <v>853.20000000000005</v>
       </c>
-      <c r="L13" s="28">
+      <c r="L13" s="29">
         <v>940.37</v>
       </c>
-      <c r="M13" s="28">
+      <c r="M13" s="29">
         <v>928.10000000000002</v>
       </c>
-      <c r="N13" s="28">
+      <c r="N13" s="29">
         <v>1084.8299999999999</v>
       </c>
-      <c r="O13" s="28">
+      <c r="O13" s="29">
         <v>1084.8299999999999</v>
       </c>
       <c r="P13" s="17" t="s">
@@ -2091,41 +2139,47 @@
       <c r="T13" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="U13" s="24">
+      <c r="U13" s="25">
         <v>592.17999999999995</v>
       </c>
-      <c r="V13" s="24">
+      <c r="V13" s="25">
         <v>606.50999999999999</v>
       </c>
-      <c r="W13" s="19">
-        <f>MIN(C13:V13)</f>
+      <c r="W13" s="25">
+        <v>608.62</v>
+      </c>
+      <c r="X13" s="25">
+        <v>623.23000000000002</v>
+      </c>
+      <c r="Y13" s="20">
+        <f>MIN(C13:X13)</f>
         <v>592.17999999999995</v>
       </c>
-      <c r="X13" s="20">
-        <f>MAX(C13:V13)</f>
+      <c r="Z13" s="21">
+        <f>MAX(C13:X13)</f>
         <v>1426.5699999999999</v>
       </c>
-      <c r="Y13" s="20">
-        <f>AVERAGE(C13:V13)</f>
-        <v>890.58615384615393</v>
-      </c>
-      <c r="Z13" s="20">
-        <f>AVERAGE(Q13:V13)</f>
-        <v>875.0866666666667</v>
-      </c>
       <c r="AA13" s="21">
+        <f>AVERAGE(C13:X13)</f>
+        <v>853.96466666666674</v>
+      </c>
+      <c r="AB13" s="21">
+        <f>AVERAGE(Q13:X13)</f>
+        <v>771.42200000000003</v>
+      </c>
+      <c r="AC13" s="22">
+        <f>(AB13/AA13)-1</f>
+        <v>-9.665817555293077e-002</v>
+      </c>
+      <c r="AD13" s="22">
+        <f>(AB13/Y13)-1</f>
+        <v>0.30268161707588925</v>
+      </c>
+      <c r="AE13" s="22">
         <f>(Z13/Y13)-1</f>
-        <v>-1.7403692065669274e-002</v>
-      </c>
-      <c r="AB13" s="21">
-        <f>(Z13/W13)-1</f>
-        <v>0.4777376248212819</v>
-      </c>
-      <c r="AC13" s="21">
-        <f>(X13/W13)-1</f>
         <v>1.4090141511027054</v>
       </c>
-      <c r="AD13" s="22" t="s">
+      <c r="AF13" s="23" t="s">
         <v>56</v>
       </c>
     </row>
@@ -2182,35 +2236,41 @@
       <c r="V14" s="18">
         <v>669.10000000000002</v>
       </c>
-      <c r="W14" s="19">
-        <f>MIN(C14:V14)</f>
+      <c r="W14" s="18">
+        <v>678.97000000000003</v>
+      </c>
+      <c r="X14" s="18">
+        <v>599.99000000000001</v>
+      </c>
+      <c r="Y14" s="20">
+        <f>MIN(C14:X14)</f>
         <v>580.98000000000002</v>
       </c>
-      <c r="X14" s="20">
-        <f>MAX(C14:V14)</f>
+      <c r="Z14" s="21">
+        <f>MAX(C14:X14)</f>
         <v>709.99000000000001</v>
       </c>
-      <c r="Y14" s="20">
-        <f>AVERAGE(C14:V14)</f>
-        <v>654.09846153846149</v>
-      </c>
-      <c r="Z14" s="20">
-        <f>AVERAGE(Q14:V14)</f>
-        <v>689.16500000000008</v>
-      </c>
       <c r="AA14" s="21">
+        <f>AVERAGE(C14:X14)</f>
+        <v>652.14933333333317</v>
+      </c>
+      <c r="AB14" s="21">
+        <f>AVERAGE(Q14:X14)</f>
+        <v>676.74375000000009</v>
+      </c>
+      <c r="AC14" s="22">
+        <f>(AB14/AA14)-1</f>
+        <v>3.7712860244688784e-002</v>
+      </c>
+      <c r="AD14" s="22">
+        <f>(AB14/Y14)-1</f>
+        <v>0.16483140555612952</v>
+      </c>
+      <c r="AE14" s="22">
         <f>(Z14/Y14)-1</f>
-        <v>5.3610489128901095e-002</v>
-      </c>
-      <c r="AB14" s="21">
-        <f>(Z14/W14)-1</f>
-        <v>0.18621122930221357</v>
-      </c>
-      <c r="AC14" s="21">
-        <f>(X14/W14)-1</f>
         <v>0.22205583668973117</v>
       </c>
-      <c r="AD14" s="22" t="s">
+      <c r="AF14" s="23" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2267,49 +2327,55 @@
       <c r="V15" s="17">
         <v>684.46000000000004</v>
       </c>
-      <c r="W15" s="19">
-        <f>MIN(C15:V15)</f>
+      <c r="W15" s="17">
+        <v>689</v>
+      </c>
+      <c r="X15" s="17">
+        <v>679</v>
+      </c>
+      <c r="Y15" s="20">
+        <f>MIN(C15:X15)</f>
         <v>622.63</v>
       </c>
-      <c r="X15" s="20">
-        <f>MAX(C15:V15)</f>
+      <c r="Z15" s="21">
+        <f>MAX(C15:X15)</f>
         <v>728.61000000000001</v>
       </c>
-      <c r="Y15" s="20">
-        <f>AVERAGE(C15:V15)</f>
-        <v>681.98230769230759</v>
-      </c>
-      <c r="Z15" s="20">
-        <f>AVERAGE(Q15:V15)</f>
-        <v>700.15166666666664</v>
-      </c>
       <c r="AA15" s="21">
+        <f>AVERAGE(C15:X15)</f>
+        <v>682.25133333333326</v>
+      </c>
+      <c r="AB15" s="21">
+        <f>AVERAGE(Q15:X15)</f>
+        <v>696.11374999999998</v>
+      </c>
+      <c r="AC15" s="22">
+        <f>(AB15/AA15)-1</f>
+        <v>2.0318636240603594e-002</v>
+      </c>
+      <c r="AD15" s="22">
+        <f>(AB15/Y15)-1</f>
+        <v>0.11802153767084778</v>
+      </c>
+      <c r="AE15" s="22">
         <f>(Z15/Y15)-1</f>
-        <v>2.6641979959627582e-002</v>
-      </c>
-      <c r="AB15" s="21">
-        <f>(Z15/W15)-1</f>
-        <v>0.1245067964387625</v>
-      </c>
-      <c r="AC15" s="21">
-        <f>(X15/W15)-1</f>
         <v>0.17021344940012528</v>
       </c>
-      <c r="AD15" s="22" t="s">
+      <c r="AF15" s="23" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="16" ht="18">
-      <c r="A16" s="25" t="s">
+      <c r="A16" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="B16" s="26" t="s">
+      <c r="B16" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="C16" s="27"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
+      <c r="C16" s="28"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
       <c r="G16" s="31">
         <v>9100</v>
       </c>
@@ -2358,35 +2424,41 @@
       <c r="V16" s="17">
         <v>10867.4</v>
       </c>
-      <c r="W16" s="19">
-        <f>MIN(C16:V16)</f>
+      <c r="W16" s="17">
+        <v>10757.610000000001</v>
+      </c>
+      <c r="X16" s="17">
+        <v>10790.610000000001</v>
+      </c>
+      <c r="Y16" s="20">
+        <f>MIN(C16:X16)</f>
         <v>9100</v>
       </c>
-      <c r="X16" s="20">
-        <f>MAX(C16:V16)</f>
+      <c r="Z16" s="21">
+        <f>MAX(C16:X16)</f>
         <v>11315.18</v>
       </c>
-      <c r="Y16" s="20">
-        <f>AVERAGE(C16:V16)</f>
-        <v>9667.948124999999</v>
-      </c>
-      <c r="Z16" s="20">
-        <f>AVERAGE(Q16:V16)</f>
-        <v>10549.688333333334</v>
-      </c>
       <c r="AA16" s="21">
+        <f>AVERAGE(C16:X16)</f>
+        <v>9790.8549999999977</v>
+      </c>
+      <c r="AB16" s="21">
+        <f>AVERAGE(Q16:X16)</f>
+        <v>10605.793750000001</v>
+      </c>
+      <c r="AC16" s="22">
+        <f>(AB16/AA16)-1</f>
+        <v>8.3234686858298268e-002</v>
+      </c>
+      <c r="AD16" s="22">
+        <f>(AB16/Y16)-1</f>
+        <v>0.16547184065934073</v>
+      </c>
+      <c r="AE16" s="22">
         <f>(Z16/Y16)-1</f>
-        <v>9.1202414093769724e-002</v>
-      </c>
-      <c r="AB16" s="21">
-        <f>(Z16/W16)-1</f>
-        <v>0.15930641025641035</v>
-      </c>
-      <c r="AC16" s="21">
-        <f>(X16/W16)-1</f>
         <v>0.24342637362637376</v>
       </c>
-      <c r="AD16" s="22" t="s">
+      <c r="AF16" s="23" t="s">
         <v>62</v>
       </c>
     </row>
@@ -2441,76 +2513,82 @@
       <c r="V17" s="18">
         <v>1611.1400000000001</v>
       </c>
-      <c r="W17" s="19">
-        <f>MIN(C17:V17)</f>
+      <c r="W17" s="18">
+        <v>1610.1400000000001</v>
+      </c>
+      <c r="X17" s="18">
+        <v>1610.8900000000001</v>
+      </c>
+      <c r="Y17" s="20">
+        <f>MIN(C17:X17)</f>
         <v>1297.6199999999999</v>
       </c>
-      <c r="X17" s="20">
-        <f>MAX(C17:V17)</f>
+      <c r="Z17" s="21">
+        <f>MAX(C17:X17)</f>
         <v>1697.6199999999999</v>
       </c>
-      <c r="Y17" s="20">
-        <f>AVERAGE(C17:V17)</f>
-        <v>1520.7341666666664</v>
-      </c>
-      <c r="Z17" s="20">
-        <f>AVERAGE(Q17:V17)</f>
-        <v>1571.7133333333334</v>
-      </c>
       <c r="AA17" s="21">
+        <f>AVERAGE(C17:X17)</f>
+        <v>1533.5599999999997</v>
+      </c>
+      <c r="AB17" s="21">
+        <f>AVERAGE(Q17:X17)</f>
+        <v>1581.4137499999999</v>
+      </c>
+      <c r="AC17" s="22">
+        <f>(AB17/AA17)-1</f>
+        <v>3.1204354573671766e-002</v>
+      </c>
+      <c r="AD17" s="22">
+        <f>(AB17/Y17)-1</f>
+        <v>0.21870327985080373</v>
+      </c>
+      <c r="AE17" s="22">
         <f>(Z17/Y17)-1</f>
-        <v>3.3522733811136352e-002</v>
-      </c>
-      <c r="AB17" s="21">
-        <f>(Z17/W17)-1</f>
-        <v>0.21122773487872681</v>
-      </c>
-      <c r="AC17" s="21">
-        <f>(X17/W17)-1</f>
         <v>0.30825665449052875</v>
       </c>
-      <c r="AD17" s="22" t="s">
+      <c r="AF17" s="23" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="18" ht="18">
-      <c r="A18" s="25" t="s">
+      <c r="A18" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="B18" s="26" t="s">
+      <c r="B18" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="C18" s="27"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28">
+      <c r="C18" s="28"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="29">
         <v>2279</v>
       </c>
-      <c r="G18" s="28" t="s">
+      <c r="G18" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="H18" s="28" t="s">
+      <c r="H18" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="I18" s="28" t="s">
+      <c r="I18" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="J18" s="28" t="s">
+      <c r="J18" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="K18" s="28" t="s">
+      <c r="K18" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="L18" s="28" t="s">
+      <c r="L18" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="M18" s="28" t="s">
+      <c r="M18" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="N18" s="28" t="s">
+      <c r="N18" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="O18" s="28" t="s">
+      <c r="O18" s="29" t="s">
         <v>66</v>
       </c>
       <c r="P18" s="17" t="s">
@@ -2534,35 +2612,41 @@
       <c r="V18" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="W18" s="19">
-        <f>MIN(C18:V18)</f>
+      <c r="W18" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="X18" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y18" s="20">
+        <f>MIN(C18:X18)</f>
         <v>2279</v>
       </c>
-      <c r="X18" s="20">
-        <f>MAX(C18:V18)</f>
+      <c r="Z18" s="21">
+        <f>MAX(C18:X18)</f>
         <v>2279</v>
       </c>
-      <c r="Y18" s="20">
-        <f>AVERAGE(C18:V18)</f>
+      <c r="AA18" s="21">
+        <f>AVERAGE(C18:X18)</f>
         <v>2279</v>
       </c>
-      <c r="Z18" s="20" t="e">
-        <f>AVERAGE(Q18:V18)</f>
+      <c r="AB18" s="21" t="e">
+        <f>AVERAGE(Q18:X18)</f>
         <v>#NUM!</v>
       </c>
-      <c r="AA18" s="21" t="e">
+      <c r="AC18" s="22" t="e">
+        <f>(AB18/AA18)-1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AD18" s="22" t="e">
+        <f>(AB18/Y18)-1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AE18" s="22">
         <f>(Z18/Y18)-1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AB18" s="21" t="e">
-        <f>(Z18/W18)-1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AC18" s="21">
-        <f>(X18/W18)-1</f>
         <v>0</v>
       </c>
-      <c r="AD18" s="22" t="s">
+      <c r="AF18" s="23" t="s">
         <v>67</v>
       </c>
     </row>
@@ -2573,13 +2657,13 @@
       <c r="B19" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="C19" s="24">
+      <c r="C19" s="25">
         <v>176.69</v>
       </c>
       <c r="D19" s="17"/>
       <c r="E19" s="17"/>
       <c r="F19" s="17"/>
-      <c r="G19" s="24">
+      <c r="G19" s="25">
         <v>150</v>
       </c>
       <c r="H19" s="17">
@@ -2594,19 +2678,19 @@
       <c r="K19" s="17">
         <v>199</v>
       </c>
-      <c r="L19" s="24">
+      <c r="L19" s="25">
         <v>145</v>
       </c>
-      <c r="M19" s="24">
+      <c r="M19" s="25">
         <v>150</v>
       </c>
-      <c r="N19" s="24">
+      <c r="N19" s="25">
         <v>150</v>
       </c>
-      <c r="O19" s="24">
+      <c r="O19" s="25">
         <v>148.05000000000001</v>
       </c>
-      <c r="P19" s="29">
+      <c r="P19" s="19">
         <v>219.69</v>
       </c>
       <c r="Q19" s="30">
@@ -2627,35 +2711,41 @@
       <c r="V19" s="30">
         <v>228</v>
       </c>
-      <c r="W19" s="19">
-        <f>MIN(C19:V19)</f>
+      <c r="W19" s="30">
+        <v>228</v>
+      </c>
+      <c r="X19" s="30">
+        <v>228</v>
+      </c>
+      <c r="Y19" s="20">
+        <f>MIN(C19:X19)</f>
         <v>145</v>
       </c>
-      <c r="X19" s="20">
-        <f>MAX(C19:V19)</f>
+      <c r="Z19" s="21">
+        <f>MAX(C19:X19)</f>
         <v>237.69999999999999</v>
       </c>
-      <c r="Y19" s="20">
-        <f>AVERAGE(C19:V19)</f>
-        <v>194.28999999999996</v>
-      </c>
-      <c r="Z19" s="20">
-        <f>AVERAGE(Q19:V19)</f>
-        <v>236.08333333333334</v>
-      </c>
       <c r="AA19" s="21">
+        <f>AVERAGE(C19:X19)</f>
+        <v>197.83842105263156</v>
+      </c>
+      <c r="AB19" s="21">
+        <f>AVERAGE(Q19:X19)</f>
+        <v>234.0625</v>
+      </c>
+      <c r="AC19" s="22">
+        <f>(AB19/AA19)-1</f>
+        <v>0.18309931283636582</v>
+      </c>
+      <c r="AD19" s="22">
+        <f>(AB19/Y19)-1</f>
+        <v>0.61422413793103448</v>
+      </c>
+      <c r="AE19" s="22">
         <f>(Z19/Y19)-1</f>
-        <v>0.21510800006862629</v>
-      </c>
-      <c r="AB19" s="21">
-        <f>(Z19/W19)-1</f>
-        <v>0.62816091954023001</v>
-      </c>
-      <c r="AC19" s="21">
-        <f>(X19/W19)-1</f>
         <v>0.63931034482758609</v>
       </c>
-      <c r="AD19" s="22" t="s">
+      <c r="AF19" s="23" t="s">
         <v>69</v>
       </c>
     </row>
@@ -2679,22 +2769,22 @@
       <c r="I20" s="17">
         <v>180</v>
       </c>
-      <c r="J20" s="24">
+      <c r="J20" s="25">
         <v>176.91999999999999</v>
       </c>
-      <c r="K20" s="24">
+      <c r="K20" s="25">
         <v>176.91999999999999</v>
       </c>
-      <c r="L20" s="24">
+      <c r="L20" s="25">
         <v>176.91999999999999</v>
       </c>
-      <c r="M20" s="24">
+      <c r="M20" s="25">
         <v>176.91999999999999</v>
       </c>
-      <c r="N20" s="24">
+      <c r="N20" s="25">
         <v>179</v>
       </c>
-      <c r="O20" s="24">
+      <c r="O20" s="25">
         <v>180</v>
       </c>
       <c r="P20" s="18">
@@ -2718,74 +2808,80 @@
       <c r="V20" s="17">
         <v>229.94999999999999</v>
       </c>
-      <c r="W20" s="19">
-        <f>MIN(C20:V20)</f>
+      <c r="W20" s="17">
+        <v>229.94</v>
+      </c>
+      <c r="X20" s="17">
+        <v>230</v>
+      </c>
+      <c r="Y20" s="20">
+        <f>MIN(C20:X20)</f>
         <v>176.91999999999999</v>
       </c>
-      <c r="X20" s="20">
-        <f>MAX(C20:V20)</f>
-        <v>229.94999999999999</v>
-      </c>
-      <c r="Y20" s="20">
-        <f>AVERAGE(C20:V20)</f>
-        <v>191.38866666666667</v>
-      </c>
-      <c r="Z20" s="20">
-        <f>AVERAGE(Q20:V20)</f>
-        <v>213.44999999999999</v>
+      <c r="Z20" s="21">
+        <f>MAX(C20:X20)</f>
+        <v>230</v>
       </c>
       <c r="AA20" s="21">
+        <f>AVERAGE(C20:X20)</f>
+        <v>195.92764705882354</v>
+      </c>
+      <c r="AB20" s="21">
+        <f>AVERAGE(Q20:X20)</f>
+        <v>218.17000000000002</v>
+      </c>
+      <c r="AC20" s="22">
+        <f>(AB20/AA20)-1</f>
+        <v>0.11352329941725192</v>
+      </c>
+      <c r="AD20" s="22">
+        <f>(AB20/Y20)-1</f>
+        <v>0.23315622880397946</v>
+      </c>
+      <c r="AE20" s="22">
         <f>(Z20/Y20)-1</f>
-        <v>0.11526980002298992</v>
-      </c>
-      <c r="AB20" s="21">
-        <f>(Z20/W20)-1</f>
-        <v>0.20647750395659048</v>
-      </c>
-      <c r="AC20" s="21">
-        <f>(X20/W20)-1</f>
-        <v>0.29973999547818231</v>
-      </c>
-      <c r="AD20" s="22" t="s">
+        <v>0.30002260908885381</v>
+      </c>
+      <c r="AF20" s="23" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="21" ht="18">
-      <c r="A21" s="25" t="s">
+      <c r="A21" s="26" t="s">
         <v>54</v>
       </c>
-      <c r="B21" s="26" t="s">
+      <c r="B21" s="27" t="s">
         <v>72</v>
       </c>
-      <c r="C21" s="28"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="28"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="28">
+      <c r="C21" s="29"/>
+      <c r="D21" s="29"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="29"/>
+      <c r="G21" s="29">
         <v>396.77999999999997</v>
       </c>
-      <c r="H21" s="28">
+      <c r="H21" s="29">
         <v>396.77999999999997</v>
       </c>
-      <c r="I21" s="28" t="s">
+      <c r="I21" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="J21" s="28" t="s">
+      <c r="J21" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="K21" s="28" t="s">
+      <c r="K21" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="L21" s="28" t="s">
+      <c r="L21" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="M21" s="28" t="s">
+      <c r="M21" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="N21" s="28" t="s">
+      <c r="N21" s="29" t="s">
         <v>43</v>
       </c>
-      <c r="O21" s="28" t="s">
+      <c r="O21" s="29" t="s">
         <v>43</v>
       </c>
       <c r="P21" s="17" t="s">
@@ -2809,35 +2905,41 @@
       <c r="V21" s="17">
         <v>453.04000000000002</v>
       </c>
-      <c r="W21" s="19">
-        <f>MIN(C21:V21)</f>
-        <v>396.77999999999997</v>
-      </c>
-      <c r="X21" s="20">
-        <f>MAX(C21:V21)</f>
+      <c r="W21" s="17">
         <v>453.04000000000002</v>
       </c>
+      <c r="X21" s="17">
+        <v>349</v>
+      </c>
       <c r="Y21" s="20">
-        <f>AVERAGE(C21:V21)</f>
-        <v>420.24833333333328</v>
-      </c>
-      <c r="Z21" s="20">
-        <f>AVERAGE(Q21:V21)</f>
-        <v>431.98249999999996</v>
+        <f>MIN(C21:X21)</f>
+        <v>349</v>
+      </c>
+      <c r="Z21" s="21">
+        <f>MAX(C21:X21)</f>
+        <v>453.04000000000002</v>
       </c>
       <c r="AA21" s="21">
+        <f>AVERAGE(C21:X21)</f>
+        <v>415.44124999999997</v>
+      </c>
+      <c r="AB21" s="21">
+        <f>AVERAGE(Q21:X21)</f>
+        <v>421.66166666666663</v>
+      </c>
+      <c r="AC21" s="22">
+        <f>(AB21/AA21)-1</f>
+        <v>1.4973035697987802e-002</v>
+      </c>
+      <c r="AD21" s="22">
+        <f>(AB21/Y21)-1</f>
+        <v>0.20819961795606479</v>
+      </c>
+      <c r="AE21" s="22">
         <f>(Z21/Y21)-1</f>
-        <v>2.792198263725032e-002</v>
-      </c>
-      <c r="AB21" s="21">
-        <f>(Z21/W21)-1</f>
-        <v>8.8720449619436481e-002</v>
-      </c>
-      <c r="AC21" s="21">
-        <f>(X21/W21)-1</f>
-        <v>0.14179142093855557</v>
-      </c>
-      <c r="AD21" s="32" t="s">
+        <v>0.29810888252148993</v>
+      </c>
+      <c r="AF21" s="32" t="s">
         <v>73</v>
       </c>
     </row>
@@ -2900,35 +3002,41 @@
       <c r="V22" s="17">
         <v>600</v>
       </c>
-      <c r="W22" s="19">
-        <f>MIN(C22:V22)</f>
+      <c r="W22" s="17">
+        <v>600</v>
+      </c>
+      <c r="X22" s="17">
+        <v>600</v>
+      </c>
+      <c r="Y22" s="20">
+        <f>MIN(C22:X22)</f>
         <v>550</v>
       </c>
-      <c r="X22" s="20">
-        <f>MAX(C22:V22)</f>
+      <c r="Z22" s="21">
+        <f>MAX(C22:X22)</f>
         <v>600</v>
       </c>
-      <c r="Y22" s="20">
-        <f>AVERAGE(C22:V22)</f>
-        <v>567.5</v>
-      </c>
-      <c r="Z22" s="20">
-        <f>AVERAGE(Q22:V22)</f>
-        <v>596.66666666666663</v>
-      </c>
       <c r="AA22" s="21">
+        <f>AVERAGE(C22:X22)</f>
+        <v>571.11111111111109</v>
+      </c>
+      <c r="AB22" s="21">
+        <f>AVERAGE(Q22:X22)</f>
+        <v>597.5</v>
+      </c>
+      <c r="AC22" s="22">
+        <f>(AB22/AA22)-1</f>
+        <v>4.620622568093391e-002</v>
+      </c>
+      <c r="AD22" s="22">
+        <f>(AB22/Y22)-1</f>
+        <v>8.636363636363642e-002</v>
+      </c>
+      <c r="AE22" s="22">
         <f>(Z22/Y22)-1</f>
-        <v>5.1395007342143861e-002</v>
-      </c>
-      <c r="AB22" s="21">
-        <f>(Z22/W22)-1</f>
-        <v>8.4848484848484729e-002</v>
-      </c>
-      <c r="AC22" s="21">
-        <f>(X22/W22)-1</f>
         <v>9.0909090909090828e-002</v>
       </c>
-      <c r="AD22" s="22" t="s">
+      <c r="AF22" s="23" t="s">
         <v>76</v>
       </c>
     </row>
@@ -2943,7 +3051,7 @@
       <c r="D23" s="17"/>
       <c r="E23" s="17"/>
       <c r="F23" s="17"/>
-      <c r="G23" s="24">
+      <c r="G23" s="25">
         <v>329</v>
       </c>
       <c r="H23" s="17">
@@ -2992,34 +3100,40 @@
         <v>518</v>
       </c>
       <c r="W23" s="19">
-        <f>MIN(C23:V23)</f>
+        <v>549</v>
+      </c>
+      <c r="X23" s="19">
+        <v>549</v>
+      </c>
+      <c r="Y23" s="20">
+        <f>MIN(C23:X23)</f>
         <v>329</v>
       </c>
-      <c r="X23" s="20">
-        <f>MAX(C23:V23)</f>
-        <v>529.95000000000005</v>
-      </c>
-      <c r="Y23" s="20">
-        <f>AVERAGE(C23:V23)</f>
-        <v>470.79687499999994</v>
-      </c>
-      <c r="Z23" s="20">
-        <f>AVERAGE(Q23:V23)</f>
-        <v>516.30833333333339</v>
+      <c r="Z23" s="21">
+        <f>MAX(C23:X23)</f>
+        <v>549</v>
       </c>
       <c r="AA23" s="21">
+        <f>AVERAGE(C23:X23)</f>
+        <v>479.48611111111109</v>
+      </c>
+      <c r="AB23" s="21">
+        <f>AVERAGE(Q23:X23)</f>
+        <v>524.48125000000005</v>
+      </c>
+      <c r="AC23" s="22">
+        <f>(AB23/AA23)-1</f>
+        <v>9.3840338325174688e-002</v>
+      </c>
+      <c r="AD23" s="22">
+        <f>(AB23/Y23)-1</f>
+        <v>0.59416793313069927</v>
+      </c>
+      <c r="AE23" s="22">
         <f>(Z23/Y23)-1</f>
-        <v>9.6668989855409393e-002</v>
-      </c>
-      <c r="AB23" s="21">
-        <f>(Z23/W23)-1</f>
-        <v>0.56932624113475194</v>
-      </c>
-      <c r="AC23" s="21">
-        <f>(X23/W23)-1</f>
-        <v>0.61079027355623117</v>
-      </c>
-      <c r="AD23" s="22" t="s">
+        <v>0.66869300911854102</v>
+      </c>
+      <c r="AF23" s="23" t="s">
         <v>79</v>
       </c>
     </row>
@@ -3034,7 +3148,7 @@
       <c r="D24" s="17"/>
       <c r="E24" s="17"/>
       <c r="F24" s="17"/>
-      <c r="G24" s="24">
+      <c r="G24" s="25">
         <v>371.14999999999998</v>
       </c>
       <c r="H24" s="17">
@@ -3070,7 +3184,7 @@
       <c r="R24" s="18">
         <v>504.73000000000002</v>
       </c>
-      <c r="S24" s="18">
+      <c r="S24" s="19">
         <v>513.71000000000004</v>
       </c>
       <c r="T24" s="18">
@@ -3082,78 +3196,84 @@
       <c r="V24" s="18">
         <v>435.14999999999998</v>
       </c>
-      <c r="W24" s="19">
-        <f>MIN(C24:V24)</f>
+      <c r="W24" s="18">
+        <v>483.99000000000001</v>
+      </c>
+      <c r="X24" s="18">
+        <v>435.14999999999998</v>
+      </c>
+      <c r="Y24" s="20">
+        <f>MIN(C24:X24)</f>
         <v>371.14999999999998</v>
       </c>
-      <c r="X24" s="20">
-        <f>MAX(C24:V24)</f>
+      <c r="Z24" s="21">
+        <f>MAX(C24:X24)</f>
         <v>513.71000000000004</v>
       </c>
-      <c r="Y24" s="20">
-        <f>AVERAGE(C24:V24)</f>
-        <v>443.55937499999993</v>
-      </c>
-      <c r="Z24" s="20">
-        <f>AVERAGE(Q24:V24)</f>
-        <v>479.70499999999998</v>
-      </c>
       <c r="AA24" s="21">
+        <f>AVERAGE(C24:X24)</f>
+        <v>445.33833333333325</v>
+      </c>
+      <c r="AB24" s="21">
+        <f>AVERAGE(Q24:X24)</f>
+        <v>474.67125000000004</v>
+      </c>
+      <c r="AC24" s="22">
+        <f>(AB24/AA24)-1</f>
+        <v>6.5866588324233089e-002</v>
+      </c>
+      <c r="AD24" s="22">
+        <f>(AB24/Y24)-1</f>
+        <v>0.27892024787821645</v>
+      </c>
+      <c r="AE24" s="22">
         <f>(Z24/Y24)-1</f>
-        <v>8.1489935817499193e-002</v>
-      </c>
-      <c r="AB24" s="21">
-        <f>(Z24/W24)-1</f>
-        <v>0.29248282365620382</v>
-      </c>
-      <c r="AC24" s="21">
-        <f>(X24/W24)-1</f>
         <v>0.38410346221204383</v>
       </c>
-      <c r="AD24" s="22" t="s">
+      <c r="AF24" s="23" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="25" ht="36">
-      <c r="A25" s="25" t="s">
+      <c r="A25" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="B25" s="26" t="s">
+      <c r="B25" s="27" t="s">
         <v>83</v>
       </c>
-      <c r="C25" s="28"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="28">
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="29">
         <v>433.49000000000001</v>
       </c>
-      <c r="F25" s="24">
+      <c r="F25" s="25">
         <v>396</v>
       </c>
-      <c r="G25" s="28">
+      <c r="G25" s="29">
         <v>541.24000000000001</v>
       </c>
-      <c r="H25" s="28">
+      <c r="H25" s="29">
         <v>531.65999999999997</v>
       </c>
-      <c r="I25" s="28">
+      <c r="I25" s="29">
         <v>524.17999999999995</v>
       </c>
-      <c r="J25" s="28">
+      <c r="J25" s="29">
         <v>519.91999999999996</v>
       </c>
-      <c r="K25" s="28">
+      <c r="K25" s="29">
         <v>519.74000000000001</v>
       </c>
-      <c r="L25" s="28">
+      <c r="L25" s="29">
         <v>429.80000000000001</v>
       </c>
-      <c r="M25" s="28">
+      <c r="M25" s="29">
         <v>534.13</v>
       </c>
-      <c r="N25" s="28">
+      <c r="N25" s="29">
         <v>525.30999999999995</v>
       </c>
-      <c r="O25" s="28">
+      <c r="O25" s="29">
         <v>524.61000000000001</v>
       </c>
       <c r="P25" s="17">
@@ -3177,35 +3297,41 @@
       <c r="V25" s="30">
         <v>609.25</v>
       </c>
-      <c r="W25" s="19">
-        <f>MIN(C25:V25)</f>
+      <c r="W25" s="33">
+        <v>587.11000000000001</v>
+      </c>
+      <c r="X25" s="33">
+        <v>587.11000000000001</v>
+      </c>
+      <c r="Y25" s="20">
+        <f>MIN(C25:X25)</f>
         <v>396</v>
       </c>
-      <c r="X25" s="20">
-        <f>MAX(C25:V25)</f>
+      <c r="Z25" s="21">
+        <f>MAX(C25:X25)</f>
         <v>609.25</v>
       </c>
-      <c r="Y25" s="20">
-        <f>AVERAGE(C25:V25)</f>
-        <v>521.28999999999996</v>
-      </c>
-      <c r="Z25" s="20">
-        <f>AVERAGE(Q25:V25)</f>
-        <v>555.745</v>
-      </c>
       <c r="AA25" s="21">
+        <f>AVERAGE(C25:X25)</f>
+        <v>527.87200000000007</v>
+      </c>
+      <c r="AB25" s="21">
+        <f>AVERAGE(Q25:X25)</f>
+        <v>563.58624999999995</v>
+      </c>
+      <c r="AC25" s="22">
+        <f>(AB25/AA25)-1</f>
+        <v>6.7657026703443091e-002</v>
+      </c>
+      <c r="AD25" s="22">
+        <f>(AB25/Y25)-1</f>
+        <v>0.42319760101010084</v>
+      </c>
+      <c r="AE25" s="22">
         <f>(Z25/Y25)-1</f>
-        <v>6.6095647336415597e-002</v>
-      </c>
-      <c r="AB25" s="21">
-        <f>(Z25/W25)-1</f>
-        <v>0.40339646464646473</v>
-      </c>
-      <c r="AC25" s="21">
-        <f>(X25/W25)-1</f>
         <v>0.53851010101010099</v>
       </c>
-      <c r="AD25" s="22" t="s">
+      <c r="AF25" s="23" t="s">
         <v>84</v>
       </c>
     </row>
@@ -3217,7 +3343,7 @@
         <v>85</v>
       </c>
       <c r="C26" s="17"/>
-      <c r="D26" s="24">
+      <c r="D26" s="25">
         <v>381.82999999999998</v>
       </c>
       <c r="E26" s="17"/>
@@ -3246,59 +3372,65 @@
       <c r="N26" s="18">
         <v>988.74000000000001</v>
       </c>
-      <c r="O26" s="29">
+      <c r="O26" s="19">
         <v>1543.1300000000001</v>
       </c>
-      <c r="P26" s="29">
+      <c r="P26" s="19">
         <v>1552.5699999999999</v>
       </c>
-      <c r="Q26" s="29">
+      <c r="Q26" s="19">
         <v>1542.1700000000001</v>
       </c>
-      <c r="R26" s="29">
+      <c r="R26" s="19">
         <v>1398</v>
       </c>
-      <c r="S26" s="29">
+      <c r="S26" s="19">
         <v>1534.8399999999999</v>
       </c>
-      <c r="T26" s="33">
+      <c r="T26" s="34">
         <v>370</v>
       </c>
       <c r="U26" s="30">
         <v>1655.4000000000001</v>
       </c>
-      <c r="V26" s="34">
+      <c r="V26" s="35">
         <v>700</v>
       </c>
-      <c r="W26" s="19">
-        <f>MIN(C26:V26)</f>
+      <c r="W26" s="30">
+        <v>1678.0799999999999</v>
+      </c>
+      <c r="X26" s="30">
+        <v>1565.48</v>
+      </c>
+      <c r="Y26" s="20">
+        <f>MIN(C26:X26)</f>
         <v>370</v>
       </c>
-      <c r="X26" s="20">
-        <f>MAX(C26:V26)</f>
-        <v>1655.4000000000001</v>
-      </c>
-      <c r="Y26" s="20">
-        <f>AVERAGE(C26:V26)</f>
-        <v>1091.3435294117646</v>
-      </c>
-      <c r="Z26" s="20">
-        <f>AVERAGE(Q26:V26)</f>
-        <v>1200.0683333333334</v>
+      <c r="Z26" s="21">
+        <f>MAX(C26:X26)</f>
+        <v>1678.0799999999999</v>
       </c>
       <c r="AA26" s="21">
+        <f>AVERAGE(C26:X26)</f>
+        <v>1147.1789473684209</v>
+      </c>
+      <c r="AB26" s="21">
+        <f>AVERAGE(Q26:X26)</f>
+        <v>1305.4962499999999</v>
+      </c>
+      <c r="AC26" s="22">
+        <f>(AB26/AA26)-1</f>
+        <v>0.13800576012552535</v>
+      </c>
+      <c r="AD26" s="22">
+        <f>(AB26/Y26)-1</f>
+        <v>2.5283682432432428</v>
+      </c>
+      <c r="AE26" s="22">
         <f>(Z26/Y26)-1</f>
-        <v>9.962472951131307e-002</v>
-      </c>
-      <c r="AB26" s="21">
-        <f>(Z26/W26)-1</f>
-        <v>2.2434279279279279</v>
-      </c>
-      <c r="AC26" s="21">
-        <f>(X26/W26)-1</f>
-        <v>3.4740540540540543</v>
-      </c>
-      <c r="AD26" s="22" t="s">
+        <v>3.535351351351351</v>
+      </c>
+      <c r="AF26" s="23" t="s">
         <v>86</v>
       </c>
     </row>
@@ -3344,75 +3476,81 @@
       <c r="S27" s="18">
         <v>149.99000000000001</v>
       </c>
-      <c r="T27" s="29">
+      <c r="T27" s="19">
         <v>159.99000000000001</v>
       </c>
-      <c r="U27" s="29">
+      <c r="U27" s="19">
         <v>159.99000000000001</v>
       </c>
-      <c r="V27" s="29">
+      <c r="V27" s="19">
         <v>164.99000000000001</v>
       </c>
       <c r="W27" s="19">
-        <f>MIN(C27:V27)</f>
+        <v>164.99000000000001</v>
+      </c>
+      <c r="X27" s="19">
+        <v>164.99000000000001</v>
+      </c>
+      <c r="Y27" s="20">
+        <f>MIN(C27:X27)</f>
         <v>109.98999999999999</v>
       </c>
-      <c r="X27" s="20">
-        <f>MAX(C27:V27)</f>
+      <c r="Z27" s="21">
+        <f>MAX(C27:X27)</f>
         <v>165.72999999999999</v>
       </c>
-      <c r="Y27" s="20">
-        <f>AVERAGE(C27:V27)</f>
-        <v>143.38500000000002</v>
-      </c>
-      <c r="Z27" s="20">
-        <f>AVERAGE(Q27:V27)</f>
-        <v>155.82333333333335</v>
-      </c>
       <c r="AA27" s="21">
+        <f>AVERAGE(C27:X27)</f>
+        <v>146.47142857142859</v>
+      </c>
+      <c r="AB27" s="21">
+        <f>AVERAGE(Q27:X27)</f>
+        <v>158.11500000000001</v>
+      </c>
+      <c r="AC27" s="22">
+        <f>(AB27/AA27)-1</f>
+        <v>7.94938066907247e-002</v>
+      </c>
+      <c r="AD27" s="22">
+        <f>(AB27/Y27)-1</f>
+        <v>0.43753977634330399</v>
+      </c>
+      <c r="AE27" s="22">
         <f>(Z27/Y27)-1</f>
-        <v>8.6747800211551596e-002</v>
-      </c>
-      <c r="AB27" s="21">
-        <f>(Z27/W27)-1</f>
-        <v>0.41670454889838493</v>
-      </c>
-      <c r="AC27" s="21">
-        <f>(X27/W27)-1</f>
         <v>0.50677334303118471</v>
       </c>
-      <c r="AD27" s="22" t="s">
+      <c r="AF27" s="23" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="28" ht="18">
-      <c r="A28" s="25" t="s">
+      <c r="A28" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="B28" s="26" t="s">
+      <c r="B28" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="C28" s="28"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="28"/>
-      <c r="F28" s="28"/>
-      <c r="G28" s="28"/>
-      <c r="H28" s="28"/>
-      <c r="I28" s="28"/>
-      <c r="J28" s="28"/>
-      <c r="K28" s="28">
+      <c r="C28" s="29"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="29"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="29"/>
+      <c r="H28" s="29"/>
+      <c r="I28" s="29"/>
+      <c r="J28" s="29"/>
+      <c r="K28" s="29">
         <v>69</v>
       </c>
-      <c r="L28" s="28">
+      <c r="L28" s="29">
         <v>68</v>
       </c>
-      <c r="M28" s="28">
+      <c r="M28" s="29">
         <v>80.060000000000002</v>
       </c>
-      <c r="N28" s="28">
+      <c r="N28" s="29">
         <v>74.560000000000002</v>
       </c>
-      <c r="O28" s="28">
+      <c r="O28" s="29">
         <v>76.189999999999998</v>
       </c>
       <c r="P28" s="17">
@@ -3436,35 +3574,41 @@
       <c r="V28" s="18">
         <v>85.700000000000003</v>
       </c>
-      <c r="W28" s="19">
-        <f>MIN(C28:V28)</f>
+      <c r="W28" s="18">
+        <v>82</v>
+      </c>
+      <c r="X28" s="18">
+        <v>82.890000000000001</v>
+      </c>
+      <c r="Y28" s="20">
+        <f>MIN(C28:X28)</f>
         <v>68</v>
       </c>
-      <c r="X28" s="20">
-        <f>MAX(C28:V28)</f>
+      <c r="Z28" s="21">
+        <f>MAX(C28:X28)</f>
         <v>85.700000000000003</v>
       </c>
-      <c r="Y28" s="20">
-        <f>AVERAGE(C28:V28)</f>
-        <v>77.984999999999999</v>
-      </c>
-      <c r="Z28" s="20">
-        <f>AVERAGE(Q28:V28)</f>
-        <v>82.170000000000002</v>
-      </c>
       <c r="AA28" s="21">
+        <f>AVERAGE(C28:X28)</f>
+        <v>78.622142857142862</v>
+      </c>
+      <c r="AB28" s="21">
+        <f>AVERAGE(Q28:X28)</f>
+        <v>82.238749999999996</v>
+      </c>
+      <c r="AC28" s="22">
+        <f>(AB28/AA28)-1</f>
+        <v>4.5999854639278137e-002</v>
+      </c>
+      <c r="AD28" s="22">
+        <f>(AB28/Y28)-1</f>
+        <v>0.20939338235294103</v>
+      </c>
+      <c r="AE28" s="22">
         <f>(Z28/Y28)-1</f>
-        <v>5.3664166185805051e-002</v>
-      </c>
-      <c r="AB28" s="21">
-        <f>(Z28/W28)-1</f>
-        <v>0.20838235294117657</v>
-      </c>
-      <c r="AC28" s="21">
-        <f>(X28/W28)-1</f>
         <v>0.26029411764705879</v>
       </c>
-      <c r="AD28" s="22" t="s">
+      <c r="AF28" s="23" t="s">
         <v>90</v>
       </c>
     </row>
@@ -3516,38 +3660,44 @@
       <c r="U29" s="30">
         <v>111</v>
       </c>
-      <c r="V29" s="33">
+      <c r="V29" s="34">
         <v>65.530000000000001</v>
       </c>
-      <c r="W29" s="19">
-        <f>MIN(C29:V29)</f>
+      <c r="W29" s="33">
+        <v>99.989999999999995</v>
+      </c>
+      <c r="X29" s="30">
+        <v>107</v>
+      </c>
+      <c r="Y29" s="20">
+        <f>MIN(C29:X29)</f>
         <v>55</v>
       </c>
-      <c r="X29" s="20">
-        <f>MAX(C29:V29)</f>
+      <c r="Z29" s="21">
+        <f>MAX(C29:X29)</f>
         <v>111</v>
       </c>
-      <c r="Y29" s="20">
-        <f>AVERAGE(C29:V29)</f>
-        <v>81.845833333333346</v>
-      </c>
-      <c r="Z29" s="20">
-        <f>AVERAGE(Q29:V29)</f>
-        <v>92.064999999999998</v>
-      </c>
       <c r="AA29" s="21">
+        <f>AVERAGE(C29:X29)</f>
+        <v>84.938571428571436</v>
+      </c>
+      <c r="AB29" s="21">
+        <f>AVERAGE(Q29:X29)</f>
+        <v>94.922499999999999</v>
+      </c>
+      <c r="AC29" s="22">
+        <f>(AB29/AA29)-1</f>
+        <v>0.11754293018483941</v>
+      </c>
+      <c r="AD29" s="22">
+        <f>(AB29/Y29)-1</f>
+        <v>0.72586363636363638</v>
+      </c>
+      <c r="AE29" s="22">
         <f>(Z29/Y29)-1</f>
-        <v>0.12485872830015765</v>
-      </c>
-      <c r="AB29" s="21">
-        <f>(Z29/W29)-1</f>
-        <v>0.67390909090909079</v>
-      </c>
-      <c r="AC29" s="21">
-        <f>(X29/W29)-1</f>
         <v>1.0181818181818181</v>
       </c>
-      <c r="AD29" s="22" t="s">
+      <c r="AF29" s="23" t="s">
         <v>92</v>
       </c>
     </row>
@@ -3591,73 +3741,79 @@
       <c r="S30" s="18">
         <v>90.579999999999998</v>
       </c>
-      <c r="T30" s="29">
+      <c r="T30" s="19">
         <v>100.68000000000001</v>
       </c>
-      <c r="U30" s="29">
+      <c r="U30" s="19">
         <v>92.530000000000001</v>
       </c>
       <c r="V30" s="18">
         <v>89.090000000000003</v>
       </c>
-      <c r="W30" s="19">
-        <f>MIN(C30:V30)</f>
+      <c r="W30" s="18">
+        <v>86.700000000000003</v>
+      </c>
+      <c r="X30" s="18">
+        <v>86.700000000000003</v>
+      </c>
+      <c r="Y30" s="20">
+        <f>MIN(C30:X30)</f>
         <v>47.359999999999999</v>
       </c>
-      <c r="X30" s="20">
-        <f>MAX(C30:V30)</f>
+      <c r="Z30" s="21">
+        <f>MAX(C30:X30)</f>
         <v>100.68000000000001</v>
       </c>
-      <c r="Y30" s="20">
-        <f>AVERAGE(C30:V30)</f>
-        <v>71.191818181818178</v>
-      </c>
-      <c r="Z30" s="20">
-        <f>AVERAGE(Q30:V30)</f>
-        <v>85.110000000000014</v>
-      </c>
       <c r="AA30" s="21">
+        <f>AVERAGE(C30:X30)</f>
+        <v>73.577692307692317</v>
+      </c>
+      <c r="AB30" s="21">
+        <f>AVERAGE(Q30:X30)</f>
+        <v>85.507500000000022</v>
+      </c>
+      <c r="AC30" s="22">
+        <f>(AB30/AA30)-1</f>
+        <v>0.16213892170494826</v>
+      </c>
+      <c r="AD30" s="22">
+        <f>(AB30/Y30)-1</f>
+        <v>0.8054793074324329</v>
+      </c>
+      <c r="AE30" s="22">
         <f>(Z30/Y30)-1</f>
-        <v>0.19550254753482932</v>
-      </c>
-      <c r="AB30" s="21">
-        <f>(Z30/W30)-1</f>
-        <v>0.79708614864864891</v>
-      </c>
-      <c r="AC30" s="21">
-        <f>(X30/W30)-1</f>
         <v>1.1258445945945947</v>
       </c>
-      <c r="AD30" s="22" t="s">
+      <c r="AF30" s="23" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="31" ht="18">
-      <c r="A31" s="25" t="s">
+      <c r="A31" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="B31" s="26" t="s">
+      <c r="B31" s="27" t="s">
         <v>95</v>
       </c>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="28"/>
-      <c r="H31" s="28"/>
-      <c r="I31" s="28"/>
-      <c r="J31" s="28"/>
-      <c r="K31" s="28"/>
-      <c r="L31" s="28">
+      <c r="C31" s="29"/>
+      <c r="D31" s="29"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="29"/>
+      <c r="H31" s="29"/>
+      <c r="I31" s="29"/>
+      <c r="J31" s="29"/>
+      <c r="K31" s="29"/>
+      <c r="L31" s="29">
         <v>92.5</v>
       </c>
-      <c r="M31" s="28">
+      <c r="M31" s="29">
         <v>110.91</v>
       </c>
-      <c r="N31" s="28">
+      <c r="N31" s="29">
         <v>107.04000000000001</v>
       </c>
-      <c r="O31" s="28">
+      <c r="O31" s="29">
         <v>112</v>
       </c>
       <c r="P31" s="17">
@@ -3681,35 +3837,41 @@
       <c r="V31" s="18">
         <v>156</v>
       </c>
-      <c r="W31" s="19">
-        <f>MIN(C31:V31)</f>
+      <c r="W31" s="18">
+        <v>156</v>
+      </c>
+      <c r="X31" s="18">
+        <v>156</v>
+      </c>
+      <c r="Y31" s="20">
+        <f>MIN(C31:X31)</f>
         <v>92.5</v>
       </c>
-      <c r="X31" s="20">
-        <f>MAX(C31:V31)</f>
+      <c r="Z31" s="21">
+        <f>MAX(C31:X31)</f>
         <v>156</v>
       </c>
-      <c r="Y31" s="20">
-        <f>AVERAGE(C31:V31)</f>
-        <v>119.66800000000003</v>
-      </c>
-      <c r="Z31" s="20">
-        <f>AVERAGE(Q31:V31)</f>
-        <v>133.43800000000002</v>
-      </c>
       <c r="AA31" s="21">
+        <f>AVERAGE(C31:X31)</f>
+        <v>125.72333333333336</v>
+      </c>
+      <c r="AB31" s="21">
+        <f>AVERAGE(Q31:X31)</f>
+        <v>139.88428571428571</v>
+      </c>
+      <c r="AC31" s="22">
+        <f>(AB31/AA31)-1</f>
+        <v>0.11263583302716818</v>
+      </c>
+      <c r="AD31" s="22">
+        <f>(AB31/Y31)-1</f>
+        <v>0.51226254826254825</v>
+      </c>
+      <c r="AE31" s="22">
         <f>(Z31/Y31)-1</f>
-        <v>0.11506835578433638</v>
-      </c>
-      <c r="AB31" s="21">
-        <f>(Z31/W31)-1</f>
-        <v>0.44257297297297304</v>
-      </c>
-      <c r="AC31" s="21">
-        <f>(X31/W31)-1</f>
         <v>0.68648648648648658</v>
       </c>
-      <c r="AD31" s="22" t="s">
+      <c r="AF31" s="23" t="s">
         <v>96</v>
       </c>
     </row>
@@ -3736,7 +3898,7 @@
       <c r="N32" s="17">
         <v>165.36000000000001</v>
       </c>
-      <c r="O32" s="29">
+      <c r="O32" s="19">
         <v>241.99000000000001</v>
       </c>
       <c r="P32" s="18">
@@ -3745,7 +3907,7 @@
       <c r="Q32" s="18">
         <v>224.84999999999999</v>
       </c>
-      <c r="R32" s="29">
+      <c r="R32" s="19">
         <v>257.87</v>
       </c>
       <c r="S32" s="18">
@@ -3760,35 +3922,41 @@
       <c r="V32" s="18">
         <v>238.24000000000001</v>
       </c>
-      <c r="W32" s="19">
-        <f>MIN(C32:V32)</f>
+      <c r="W32" s="18">
+        <v>235.97999999999999</v>
+      </c>
+      <c r="X32" s="18">
+        <v>238.24000000000001</v>
+      </c>
+      <c r="Y32" s="20">
+        <f>MIN(C32:X32)</f>
         <v>148.88</v>
       </c>
-      <c r="X32" s="20">
-        <f>MAX(C32:V32)</f>
+      <c r="Z32" s="21">
+        <f>MAX(C32:X32)</f>
         <v>257.87</v>
       </c>
-      <c r="Y32" s="20">
-        <f>AVERAGE(C32:V32)</f>
-        <v>219.03500000000003</v>
-      </c>
-      <c r="Z32" s="20">
-        <f>AVERAGE(Q32:V32)</f>
-        <v>234.87833333333336</v>
-      </c>
       <c r="AA32" s="21">
+        <f>AVERAGE(C32:X32)</f>
+        <v>222.04750000000004</v>
+      </c>
+      <c r="AB32" s="21">
+        <f>AVERAGE(Q32:X32)</f>
+        <v>235.43625000000003</v>
+      </c>
+      <c r="AC32" s="22">
+        <f>(AB32/AA32)-1</f>
+        <v>6.0296783345905602e-002</v>
+      </c>
+      <c r="AD32" s="22">
+        <f>(AB32/Y32)-1</f>
+        <v>0.58138265717356274</v>
+      </c>
+      <c r="AE32" s="22">
         <f>(Z32/Y32)-1</f>
-        <v>7.2332427846386826e-002</v>
-      </c>
-      <c r="AB32" s="21">
-        <f>(Z32/W32)-1</f>
-        <v>0.57763523195414668</v>
-      </c>
-      <c r="AC32" s="21">
-        <f>(X32/W32)-1</f>
         <v>0.73206609349811935</v>
       </c>
-      <c r="AD32" s="22" t="s">
+      <c r="AF32" s="23" t="s">
         <v>98</v>
       </c>
     </row>
@@ -3835,58 +4003,64 @@
       <c r="V33" s="18">
         <v>164.93000000000001</v>
       </c>
-      <c r="W33" s="19">
-        <f>MIN(C33:V33)</f>
+      <c r="W33" s="18">
+        <v>161.65000000000001</v>
+      </c>
+      <c r="X33" s="18">
+        <v>164.38999999999999</v>
+      </c>
+      <c r="Y33" s="20">
+        <f>MIN(C33:X33)</f>
         <v>144.94999999999999</v>
       </c>
-      <c r="X33" s="20">
-        <f>MAX(C33:V33)</f>
+      <c r="Z33" s="21">
+        <f>MAX(C33:X33)</f>
         <v>164.93000000000001</v>
       </c>
-      <c r="Y33" s="20">
-        <f>AVERAGE(C33:V33)</f>
-        <v>153.7225</v>
-      </c>
-      <c r="Z33" s="20">
-        <f>AVERAGE(Q33:V33)</f>
-        <v>153.55666666666664</v>
-      </c>
       <c r="AA33" s="21">
+        <f>AVERAGE(C33:X33)</f>
+        <v>155.58200000000002</v>
+      </c>
+      <c r="AB33" s="21">
+        <f>AVERAGE(Q33:X33)</f>
+        <v>155.92250000000001</v>
+      </c>
+      <c r="AC33" s="22">
+        <f>(AB33/AA33)-1</f>
+        <v>2.1885565168207055e-003</v>
+      </c>
+      <c r="AD33" s="22">
+        <f>(AB33/Y33)-1</f>
+        <v>7.5698516729907128e-002</v>
+      </c>
+      <c r="AE33" s="22">
         <f>(Z33/Y33)-1</f>
-        <v>-1.0787837390970889e-003</v>
-      </c>
-      <c r="AB33" s="21">
-        <f>(Z33/W33)-1</f>
-        <v>5.9376796596527504e-002</v>
-      </c>
-      <c r="AC33" s="21">
-        <f>(X33/W33)-1</f>
         <v>0.13784063470162145</v>
       </c>
-      <c r="AD33" s="22" t="s">
+      <c r="AF33" s="23" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="34" ht="18">
-      <c r="A34" s="25" t="s">
+      <c r="A34" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="B34" s="26" t="s">
+      <c r="B34" s="27" t="s">
         <v>101</v>
       </c>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="28"/>
-      <c r="F34" s="28"/>
-      <c r="G34" s="28"/>
-      <c r="H34" s="28"/>
-      <c r="I34" s="28"/>
-      <c r="J34" s="28"/>
-      <c r="K34" s="28"/>
-      <c r="L34" s="28"/>
-      <c r="M34" s="28"/>
-      <c r="N34" s="28"/>
-      <c r="O34" s="29">
+      <c r="C34" s="29"/>
+      <c r="D34" s="29"/>
+      <c r="E34" s="29"/>
+      <c r="F34" s="29"/>
+      <c r="G34" s="29"/>
+      <c r="H34" s="29"/>
+      <c r="I34" s="29"/>
+      <c r="J34" s="29"/>
+      <c r="K34" s="29"/>
+      <c r="L34" s="29"/>
+      <c r="M34" s="29"/>
+      <c r="N34" s="29"/>
+      <c r="O34" s="19">
         <v>199.93000000000001</v>
       </c>
       <c r="P34" s="17">
@@ -3895,50 +4069,56 @@
       <c r="Q34" s="17">
         <v>175.99000000000001</v>
       </c>
-      <c r="R34" s="24">
+      <c r="R34" s="25">
         <v>144</v>
       </c>
-      <c r="S34" s="29">
+      <c r="S34" s="19">
         <v>199.40000000000001</v>
       </c>
-      <c r="T34" s="29">
+      <c r="T34" s="19">
         <v>189.99000000000001</v>
       </c>
-      <c r="U34" s="29">
+      <c r="U34" s="19">
         <v>199.94999999999999</v>
       </c>
       <c r="V34" s="18">
         <v>169</v>
       </c>
       <c r="W34" s="19">
-        <f>MIN(C34:V34)</f>
+        <v>181.33000000000001</v>
+      </c>
+      <c r="X34" s="18">
+        <v>169</v>
+      </c>
+      <c r="Y34" s="20">
+        <f>MIN(C34:X34)</f>
         <v>144</v>
       </c>
-      <c r="X34" s="20">
-        <f>MAX(C34:V34)</f>
+      <c r="Z34" s="21">
+        <f>MAX(C34:X34)</f>
         <v>199.94999999999999</v>
       </c>
-      <c r="Y34" s="20">
-        <f>AVERAGE(C34:V34)</f>
-        <v>180.02000000000001</v>
-      </c>
-      <c r="Z34" s="20">
-        <f>AVERAGE(Q34:V34)</f>
-        <v>179.72166666666666</v>
-      </c>
       <c r="AA34" s="21">
+        <f>AVERAGE(C34:X34)</f>
+        <v>179.04900000000001</v>
+      </c>
+      <c r="AB34" s="21">
+        <f>AVERAGE(Q34:X34)</f>
+        <v>178.58249999999998</v>
+      </c>
+      <c r="AC34" s="22">
+        <f>(AB34/AA34)-1</f>
+        <v>-2.6054320325722413e-003</v>
+      </c>
+      <c r="AD34" s="22">
+        <f>(AB34/Y34)-1</f>
+        <v>0.24015624999999985</v>
+      </c>
+      <c r="AE34" s="22">
         <f>(Z34/Y34)-1</f>
-        <v>-1.6572232714884283e-003</v>
-      </c>
-      <c r="AB34" s="21">
-        <f>(Z34/W34)-1</f>
-        <v>0.24806712962962951</v>
-      </c>
-      <c r="AC34" s="21">
-        <f>(X34/W34)-1</f>
         <v>0.38854166666666656</v>
       </c>
-      <c r="AD34" s="22" t="s">
+      <c r="AF34" s="23" t="s">
         <v>102</v>
       </c>
     </row>
@@ -3953,7 +4133,7 @@
       <c r="D35" s="17"/>
       <c r="E35" s="17"/>
       <c r="F35" s="17"/>
-      <c r="G35" s="24">
+      <c r="G35" s="25">
         <v>30731.380000000001</v>
       </c>
       <c r="H35" s="18">
@@ -3983,35 +4163,37 @@
       <c r="T35" s="17"/>
       <c r="U35" s="17"/>
       <c r="V35" s="17"/>
-      <c r="W35" s="19">
-        <f>MIN(C35:V35)</f>
+      <c r="W35" s="17"/>
+      <c r="X35" s="17"/>
+      <c r="Y35" s="20">
+        <f>MIN(C35:X35)</f>
         <v>30731.380000000001</v>
       </c>
-      <c r="X35" s="20">
-        <f>MAX(C35:V35)</f>
+      <c r="Z35" s="21">
+        <f>MAX(C35:X35)</f>
         <v>32790.889999999999</v>
       </c>
-      <c r="Y35" s="20">
-        <f>AVERAGE(C35:V35)</f>
+      <c r="AA35" s="21">
+        <f>AVERAGE(C35:X35)</f>
         <v>31912.133333333331</v>
       </c>
-      <c r="Z35" s="20" t="e">
-        <f>AVERAGE(Q35:V35)</f>
+      <c r="AB35" s="21" t="e">
+        <f>AVERAGE(Q35:X35)</f>
         <v>#NUM!</v>
       </c>
-      <c r="AA35" s="21" t="e">
+      <c r="AC35" s="22" t="e">
+        <f>(AB35/AA35)-1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AD35" s="22" t="e">
+        <f>(AB35/Y35)-1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AE35" s="22">
         <f>(Z35/Y35)-1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AB35" s="21" t="e">
-        <f>(Z35/W35)-1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AC35" s="21">
-        <f>(X35/W35)-1</f>
         <v>6.7016515366377982e-002</v>
       </c>
-      <c r="AD35" s="22" t="s">
+      <c r="AF35" s="23" t="s">
         <v>105</v>
       </c>
     </row>
@@ -4026,7 +4208,7 @@
       <c r="D36" s="17"/>
       <c r="E36" s="17"/>
       <c r="F36" s="17"/>
-      <c r="G36" s="24"/>
+      <c r="G36" s="25"/>
       <c r="H36" s="18"/>
       <c r="I36" s="18"/>
       <c r="J36" s="18"/>
@@ -4039,16 +4221,16 @@
       <c r="O36" s="18">
         <v>642.82000000000005</v>
       </c>
-      <c r="P36" s="29">
+      <c r="P36" s="19">
         <v>721.67999999999995</v>
       </c>
-      <c r="Q36" s="29">
+      <c r="Q36" s="19">
         <v>721.67999999999995</v>
       </c>
-      <c r="R36" s="29">
+      <c r="R36" s="19">
         <v>721.67999999999995</v>
       </c>
-      <c r="S36" s="29">
+      <c r="S36" s="19">
         <v>721.67999999999995</v>
       </c>
       <c r="T36" s="17" t="s">
@@ -4060,35 +4242,41 @@
       <c r="V36" s="17">
         <v>1150.8</v>
       </c>
-      <c r="W36" s="19">
-        <f>MIN(C36:V36)</f>
+      <c r="W36" s="17">
+        <v>1150.8</v>
+      </c>
+      <c r="X36" s="17">
+        <v>1150.8</v>
+      </c>
+      <c r="Y36" s="20">
+        <f>MIN(C36:X36)</f>
         <v>642.82000000000005</v>
       </c>
-      <c r="X36" s="20">
-        <f>MAX(C36:V36)</f>
+      <c r="Z36" s="21">
+        <f>MAX(C36:X36)</f>
         <v>1164</v>
       </c>
-      <c r="Y36" s="20">
-        <f>AVERAGE(C36:V36)</f>
-        <v>810.89499999999998</v>
-      </c>
-      <c r="Z36" s="20">
-        <f>AVERAGE(Q36:V36)</f>
-        <v>895.96800000000007</v>
-      </c>
       <c r="AA36" s="21">
+        <f>AVERAGE(C36:X36)</f>
+        <v>878.87599999999998</v>
+      </c>
+      <c r="AB36" s="21">
+        <f>AVERAGE(Q36:X36)</f>
+        <v>968.77714285714296</v>
+      </c>
+      <c r="AC36" s="22">
+        <f>(AB36/AA36)-1</f>
+        <v>0.1022910431700752</v>
+      </c>
+      <c r="AD36" s="22">
+        <f>(AB36/Y36)-1</f>
+        <v>0.50707374203842903</v>
+      </c>
+      <c r="AE36" s="22">
         <f>(Z36/Y36)-1</f>
-        <v>0.10491247325486053</v>
-      </c>
-      <c r="AB36" s="21">
-        <f>(Z36/W36)-1</f>
-        <v>0.39380853115957803</v>
-      </c>
-      <c r="AC36" s="21">
-        <f>(X36/W36)-1</f>
         <v>0.81077128900780915</v>
       </c>
-      <c r="AD36" s="22" t="s">
+      <c r="AF36" s="23" t="s">
         <v>108</v>
       </c>
     </row>
@@ -4103,7 +4291,7 @@
       <c r="D37" s="17"/>
       <c r="E37" s="17"/>
       <c r="F37" s="17"/>
-      <c r="G37" s="24"/>
+      <c r="G37" s="25"/>
       <c r="H37" s="18"/>
       <c r="I37" s="18"/>
       <c r="J37" s="18"/>
@@ -4116,16 +4304,16 @@
       <c r="O37" s="18">
         <v>1151.71</v>
       </c>
-      <c r="P37" s="29">
+      <c r="P37" s="19">
         <v>1279.6800000000001</v>
       </c>
-      <c r="Q37" s="29">
+      <c r="Q37" s="19">
         <v>1279.6800000000001</v>
       </c>
-      <c r="R37" s="29">
+      <c r="R37" s="19">
         <v>1279.6800000000001</v>
       </c>
-      <c r="S37" s="29">
+      <c r="S37" s="19">
         <v>1279.6800000000001</v>
       </c>
       <c r="T37" s="30">
@@ -4137,35 +4325,41 @@
       <c r="V37" s="30">
         <v>2016</v>
       </c>
-      <c r="W37" s="19">
-        <f>MIN(C37:V37)</f>
+      <c r="W37" s="30">
+        <v>2016</v>
+      </c>
+      <c r="X37" s="30">
+        <v>2016</v>
+      </c>
+      <c r="Y37" s="20">
+        <f>MIN(C37:X37)</f>
         <v>1151.71</v>
       </c>
-      <c r="X37" s="20">
-        <f>MAX(C37:V37)</f>
+      <c r="Z37" s="21">
+        <f>MAX(C37:X37)</f>
         <v>2064</v>
       </c>
-      <c r="Y37" s="20">
-        <f>AVERAGE(C37:V37)</f>
-        <v>1507.348888888889</v>
-      </c>
-      <c r="Z37" s="20">
-        <f>AVERAGE(Q37:V37)</f>
-        <v>1663.8400000000001</v>
-      </c>
       <c r="AA37" s="21">
+        <f>AVERAGE(C37:X37)</f>
+        <v>1599.830909090909</v>
+      </c>
+      <c r="AB37" s="21">
+        <f>AVERAGE(Q37:X37)</f>
+        <v>1751.8800000000001</v>
+      </c>
+      <c r="AC37" s="22">
+        <f>(AB37/AA37)-1</f>
+        <v>9.5040725894895761e-002</v>
+      </c>
+      <c r="AD37" s="22">
+        <f>(AB37/Y37)-1</f>
+        <v>0.52111208550763655</v>
+      </c>
+      <c r="AE37" s="22">
         <f>(Z37/Y37)-1</f>
-        <v>0.10381877232580528</v>
-      </c>
-      <c r="AB37" s="21">
-        <f>(Z37/W37)-1</f>
-        <v>0.44466923096960187</v>
-      </c>
-      <c r="AC37" s="21">
-        <f>(X37/W37)-1</f>
         <v>0.79211780743416305</v>
       </c>
-      <c r="AD37" s="22" t="s">
+      <c r="AF37" s="23" t="s">
         <v>108</v>
       </c>
     </row>
@@ -4180,7 +4374,7 @@
       <c r="D38" s="17"/>
       <c r="E38" s="17"/>
       <c r="F38" s="17"/>
-      <c r="G38" s="24"/>
+      <c r="G38" s="25"/>
       <c r="H38" s="18"/>
       <c r="I38" s="18"/>
       <c r="J38" s="18"/>
@@ -4193,56 +4387,62 @@
       <c r="O38" s="18">
         <v>2159.8299999999999</v>
       </c>
-      <c r="P38" s="29">
+      <c r="P38" s="19">
         <v>2403.1199999999999</v>
       </c>
-      <c r="Q38" s="29">
+      <c r="Q38" s="19">
         <v>2403.1199999999999</v>
       </c>
-      <c r="R38" s="29">
+      <c r="R38" s="19">
         <v>2403.1199999999999</v>
       </c>
-      <c r="S38" s="29">
+      <c r="S38" s="19">
         <v>2403.1199999999999</v>
       </c>
       <c r="T38" s="30">
         <v>3876</v>
       </c>
-      <c r="U38" s="35" t="s">
+      <c r="U38" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="V38" s="35" t="s">
+      <c r="V38" s="36" t="s">
         <v>43</v>
       </c>
-      <c r="W38" s="19">
-        <f>MIN(C38:V38)</f>
+      <c r="W38" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="X38" s="36" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y38" s="20">
+        <f>MIN(C38:X38)</f>
         <v>2159.8299999999999</v>
       </c>
-      <c r="X38" s="20">
-        <f>MAX(C38:V38)</f>
+      <c r="Z38" s="21">
+        <f>MAX(C38:X38)</f>
         <v>3876</v>
       </c>
-      <c r="Y38" s="20">
-        <f>AVERAGE(C38:V38)</f>
+      <c r="AA38" s="21">
+        <f>AVERAGE(C38:X38)</f>
         <v>2544.02</v>
       </c>
-      <c r="Z38" s="20">
-        <f>AVERAGE(Q38:V38)</f>
+      <c r="AB38" s="21">
+        <f>AVERAGE(Q38:X38)</f>
         <v>2771.3400000000001</v>
       </c>
-      <c r="AA38" s="21">
+      <c r="AC38" s="22">
+        <f>(AB38/AA38)-1</f>
+        <v>8.9354643438337877e-002</v>
+      </c>
+      <c r="AD38" s="22">
+        <f>(AB38/Y38)-1</f>
+        <v>0.28312876476389359</v>
+      </c>
+      <c r="AE38" s="22">
         <f>(Z38/Y38)-1</f>
-        <v>8.9354643438337877e-002</v>
-      </c>
-      <c r="AB38" s="21">
-        <f>(Z38/W38)-1</f>
-        <v>0.28312876476389359</v>
-      </c>
-      <c r="AC38" s="21">
-        <f>(X38/W38)-1</f>
         <v>0.79458568498446636</v>
       </c>
-      <c r="AD38" s="22" t="s">
+      <c r="AF38" s="23" t="s">
         <v>108</v>
       </c>
     </row>
@@ -4257,7 +4457,7 @@
       <c r="D39" s="17"/>
       <c r="E39" s="17"/>
       <c r="F39" s="17"/>
-      <c r="G39" s="24"/>
+      <c r="G39" s="25"/>
       <c r="H39" s="18"/>
       <c r="I39" s="18"/>
       <c r="J39" s="18"/>
@@ -4270,16 +4470,16 @@
       <c r="O39" s="18">
         <v>1320.5999999999999</v>
       </c>
-      <c r="P39" s="29">
+      <c r="P39" s="19">
         <v>1320.5999999999999</v>
       </c>
-      <c r="Q39" s="29">
+      <c r="Q39" s="19">
         <v>1320.5999999999999</v>
       </c>
-      <c r="R39" s="29">
+      <c r="R39" s="19">
         <v>1320.5999999999999</v>
       </c>
-      <c r="S39" s="29">
+      <c r="S39" s="19">
         <v>1320.5999999999999</v>
       </c>
       <c r="T39" s="30">
@@ -4291,35 +4491,41 @@
       <c r="V39" s="30">
         <v>2218.4400000000001</v>
       </c>
-      <c r="W39" s="19">
-        <f>MIN(C39:V39)</f>
+      <c r="W39" s="30">
+        <v>2218.4400000000001</v>
+      </c>
+      <c r="X39" s="30">
+        <v>2218.4400000000001</v>
+      </c>
+      <c r="Y39" s="20">
+        <f>MIN(C39:X39)</f>
         <v>1310.1800000000001</v>
       </c>
-      <c r="X39" s="20">
-        <f>MAX(C39:V39)</f>
+      <c r="Z39" s="21">
+        <f>MAX(C39:X39)</f>
         <v>2218.4400000000001</v>
       </c>
-      <c r="Y39" s="20">
-        <f>AVERAGE(C39:V39)</f>
-        <v>1599.068888888889</v>
-      </c>
-      <c r="Z39" s="20">
-        <f>AVERAGE(Q39:V39)</f>
-        <v>1740.04</v>
-      </c>
       <c r="AA39" s="21">
+        <f>AVERAGE(C39:X39)</f>
+        <v>1711.6818181818182</v>
+      </c>
+      <c r="AB39" s="21">
+        <f>AVERAGE(Q39:X39)</f>
+        <v>1859.6400000000001</v>
+      </c>
+      <c r="AC39" s="22">
+        <f>(AB39/AA39)-1</f>
+        <v>8.6440236874950171e-002</v>
+      </c>
+      <c r="AD39" s="22">
+        <f>(AB39/Y39)-1</f>
+        <v>0.41937749011586201</v>
+      </c>
+      <c r="AE39" s="22">
         <f>(Z39/Y39)-1</f>
-        <v>8.8158247646894505e-002</v>
-      </c>
-      <c r="AB39" s="21">
-        <f>(Z39/W39)-1</f>
-        <v>0.32809232319223303</v>
-      </c>
-      <c r="AC39" s="21">
-        <f>(X39/W39)-1</f>
         <v>0.69323299088674828</v>
       </c>
-      <c r="AD39" s="22" t="s">
+      <c r="AF39" s="23" t="s">
         <v>108</v>
       </c>
     </row>
@@ -4347,44 +4553,50 @@
       <c r="Q40" s="17"/>
       <c r="R40" s="17"/>
       <c r="S40" s="17"/>
-      <c r="T40" s="29">
+      <c r="T40" s="19">
         <v>1896</v>
       </c>
-      <c r="U40" s="29">
+      <c r="U40" s="19">
         <v>1896</v>
       </c>
-      <c r="V40" s="29">
+      <c r="V40" s="19">
         <v>1592.6400000000001</v>
       </c>
       <c r="W40" s="19">
-        <f>MIN(C40:V40)</f>
         <v>1592.6400000000001</v>
       </c>
-      <c r="X40" s="20">
-        <f>MAX(C40:V40)</f>
+      <c r="X40" s="19">
+        <v>1592.6400000000001</v>
+      </c>
+      <c r="Y40" s="20">
+        <f>MIN(C40:X40)</f>
+        <v>1592.6400000000001</v>
+      </c>
+      <c r="Z40" s="21">
+        <f>MAX(C40:X40)</f>
         <v>1896</v>
       </c>
-      <c r="Y40" s="20">
-        <f>AVERAGE(C40:V40)</f>
-        <v>1794.8800000000001</v>
-      </c>
-      <c r="Z40" s="20">
-        <f>AVERAGE(Q40:V40)</f>
-        <v>1794.8800000000001</v>
-      </c>
       <c r="AA40" s="21">
+        <f>AVERAGE(C40:X40)</f>
+        <v>1713.9839999999999</v>
+      </c>
+      <c r="AB40" s="21">
+        <f>AVERAGE(Q40:X40)</f>
+        <v>1713.9839999999999</v>
+      </c>
+      <c r="AC40" s="22">
+        <f>(AB40/AA40)-1</f>
+        <v>0</v>
+      </c>
+      <c r="AD40" s="22">
+        <f>(AB40/Y40)-1</f>
+        <v>7.6190476190476142e-002</v>
+      </c>
+      <c r="AE40" s="22">
         <f>(Z40/Y40)-1</f>
-        <v>0</v>
-      </c>
-      <c r="AB40" s="21">
-        <f>(Z40/W40)-1</f>
-        <v>0.12698412698412698</v>
-      </c>
-      <c r="AC40" s="21">
-        <f>(X40/W40)-1</f>
         <v>0.19047619047619047</v>
       </c>
-      <c r="AD40" s="22" t="s">
+      <c r="AF40" s="23" t="s">
         <v>108</v>
       </c>
     </row>
@@ -4399,7 +4611,7 @@
       <c r="D41" s="17"/>
       <c r="E41" s="17"/>
       <c r="F41" s="17"/>
-      <c r="G41" s="24"/>
+      <c r="G41" s="25"/>
       <c r="H41" s="18"/>
       <c r="I41" s="18"/>
       <c r="J41" s="18"/>
@@ -4412,16 +4624,16 @@
       <c r="O41" s="18">
         <v>1480.5599999999999</v>
       </c>
-      <c r="P41" s="29">
+      <c r="P41" s="19">
         <v>1628.6199999999999</v>
       </c>
-      <c r="Q41" s="29">
+      <c r="Q41" s="19">
         <v>1628.6199999999999</v>
       </c>
-      <c r="R41" s="29">
+      <c r="R41" s="19">
         <v>1628.6199999999999</v>
       </c>
-      <c r="S41" s="29">
+      <c r="S41" s="19">
         <v>1628.6199999999999</v>
       </c>
       <c r="T41" s="17" t="s">
@@ -4434,34 +4646,40 @@
         <v>43</v>
       </c>
       <c r="W41" s="19">
-        <f>MIN(C41:V41)</f>
+        <v>1985.76</v>
+      </c>
+      <c r="X41" s="19">
+        <v>1985.76</v>
+      </c>
+      <c r="Y41" s="20">
+        <f>MIN(C41:X41)</f>
         <v>1480.5599999999999</v>
       </c>
-      <c r="X41" s="20">
-        <f>MAX(C41:V41)</f>
-        <v>1628.6199999999999</v>
-      </c>
-      <c r="Y41" s="20">
-        <f>AVERAGE(C41:V41)</f>
-        <v>1579.2666666666664</v>
-      </c>
-      <c r="Z41" s="20">
-        <f>AVERAGE(Q41:V41)</f>
-        <v>1628.6199999999999</v>
+      <c r="Z41" s="21">
+        <f>MAX(C41:X41)</f>
+        <v>1985.76</v>
       </c>
       <c r="AA41" s="21">
+        <f>AVERAGE(C41:X41)</f>
+        <v>1680.8899999999999</v>
+      </c>
+      <c r="AB41" s="21">
+        <f>AVERAGE(Q41:X41)</f>
+        <v>1771.4759999999999</v>
+      </c>
+      <c r="AC41" s="22">
+        <f>(AB41/AA41)-1</f>
+        <v>5.3891688331776599e-002</v>
+      </c>
+      <c r="AD41" s="22">
+        <f>(AB41/Y41)-1</f>
+        <v>0.19649051710163712</v>
+      </c>
+      <c r="AE41" s="22">
         <f>(Z41/Y41)-1</f>
-        <v>3.1250791506606479e-002</v>
-      </c>
-      <c r="AB41" s="21">
-        <f>(Z41/W41)-1</f>
-        <v>0.10000270168044523</v>
-      </c>
-      <c r="AC41" s="21">
-        <f>(X41/W41)-1</f>
-        <v>0.10000270168044523</v>
-      </c>
-      <c r="AD41" s="22" t="s">
+        <v>0.34122224023342529</v>
+      </c>
+      <c r="AF41" s="23" t="s">
         <v>108</v>
       </c>
     </row>
@@ -4476,16 +4694,16 @@
       <c r="D42" s="17">
         <v>339.45999999999998</v>
       </c>
-      <c r="E42" s="36"/>
-      <c r="F42" s="36"/>
-      <c r="G42" s="36"/>
-      <c r="H42" s="36"/>
-      <c r="I42" s="36"/>
-      <c r="J42" s="36"/>
-      <c r="K42" s="36"/>
-      <c r="L42" s="36"/>
-      <c r="M42" s="36"/>
-      <c r="N42" s="36"/>
+      <c r="E42" s="37"/>
+      <c r="F42" s="37"/>
+      <c r="G42" s="37"/>
+      <c r="H42" s="37"/>
+      <c r="I42" s="37"/>
+      <c r="J42" s="37"/>
+      <c r="K42" s="37"/>
+      <c r="L42" s="37"/>
+      <c r="M42" s="37"/>
+      <c r="N42" s="37"/>
       <c r="O42" s="17"/>
       <c r="P42" s="17"/>
       <c r="Q42" s="17"/>
@@ -4494,32 +4712,34 @@
       <c r="T42" s="17"/>
       <c r="U42" s="17"/>
       <c r="V42" s="17"/>
-      <c r="W42" s="19">
-        <f>MIN(C42:V42)</f>
+      <c r="W42" s="17"/>
+      <c r="X42" s="17"/>
+      <c r="Y42" s="20">
+        <f>MIN(C42:X42)</f>
         <v>339.45999999999998</v>
       </c>
-      <c r="X42" s="20">
-        <f>MAX(C42:V42)</f>
+      <c r="Z42" s="21">
+        <f>MAX(C42:X42)</f>
         <v>339.45999999999998</v>
       </c>
-      <c r="Y42" s="20">
-        <f>AVERAGE(C42:V42)</f>
+      <c r="AA42" s="21">
+        <f>AVERAGE(C42:X42)</f>
         <v>339.45999999999998</v>
       </c>
-      <c r="Z42" s="20" t="e">
-        <f>AVERAGE(Q42:V42)</f>
+      <c r="AB42" s="21" t="e">
+        <f>AVERAGE(Q42:X42)</f>
         <v>#NUM!</v>
       </c>
-      <c r="AA42" s="21" t="e">
+      <c r="AC42" s="22" t="e">
+        <f>(AB42/AA42)-1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AD42" s="22" t="e">
+        <f>(AB42/Y42)-1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AE42" s="22">
         <f>(Z42/Y42)-1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AB42" s="21" t="e">
-        <f>(Z42/W42)-1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AC42" s="21">
-        <f>(X42/W42)-1</f>
         <v>0</v>
       </c>
     </row>
@@ -4534,7 +4754,7 @@
       <c r="D43" s="17"/>
       <c r="E43" s="17"/>
       <c r="F43" s="17"/>
-      <c r="G43" s="24">
+      <c r="G43" s="25">
         <v>378.99000000000001</v>
       </c>
       <c r="H43" s="17">
@@ -4582,74 +4802,80 @@
       <c r="V43" s="17">
         <v>378.99000000000001</v>
       </c>
-      <c r="W43" s="19">
-        <f>MIN(C43:V43)</f>
+      <c r="W43" s="17">
         <v>378.99000000000001</v>
       </c>
-      <c r="X43" s="20">
-        <f>MAX(C43:V43)</f>
+      <c r="X43" s="17">
         <v>378.99000000000001</v>
       </c>
       <c r="Y43" s="20">
-        <f>AVERAGE(C43:V43)</f>
+        <f>MIN(C43:X43)</f>
+        <v>378.99000000000001</v>
+      </c>
+      <c r="Z43" s="21">
+        <f>MAX(C43:X43)</f>
+        <v>378.99000000000001</v>
+      </c>
+      <c r="AA43" s="21">
+        <f>AVERAGE(C43:X43)</f>
         <v>378.9899999999999</v>
       </c>
-      <c r="Z43" s="20">
-        <f>AVERAGE(Q43:V43)</f>
+      <c r="AB43" s="21">
+        <f>AVERAGE(Q43:X43)</f>
         <v>378.99000000000001</v>
       </c>
-      <c r="AA43" s="21">
+      <c r="AC43" s="22">
+        <f>(AB43/AA43)-1</f>
+        <v>2.2204460492503131e-016</v>
+      </c>
+      <c r="AD43" s="22">
+        <f>(AB43/Y43)-1</f>
+        <v>0</v>
+      </c>
+      <c r="AE43" s="22">
         <f>(Z43/Y43)-1</f>
-        <v>2.2204460492503131e-016</v>
-      </c>
-      <c r="AB43" s="21">
-        <f>(Z43/W43)-1</f>
         <v>0</v>
       </c>
-      <c r="AC43" s="21">
-        <f>(X43/W43)-1</f>
-        <v>0</v>
-      </c>
-      <c r="AD43" s="22" t="s">
+      <c r="AF43" s="23" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="44" ht="18">
-      <c r="A44" s="25" t="s">
+      <c r="A44" s="26" t="s">
         <v>120</v>
       </c>
-      <c r="B44" s="26" t="s">
+      <c r="B44" s="27" t="s">
         <v>121</v>
       </c>
-      <c r="C44" s="28"/>
-      <c r="D44" s="28"/>
-      <c r="E44" s="28"/>
-      <c r="F44" s="28"/>
-      <c r="G44" s="28">
+      <c r="C44" s="29"/>
+      <c r="D44" s="29"/>
+      <c r="E44" s="29"/>
+      <c r="F44" s="29"/>
+      <c r="G44" s="29">
         <v>88.329999999999998</v>
       </c>
-      <c r="H44" s="28">
+      <c r="H44" s="29">
         <v>88.329999999999998</v>
       </c>
-      <c r="I44" s="28">
+      <c r="I44" s="29">
         <v>88.329999999999998</v>
       </c>
-      <c r="J44" s="28">
+      <c r="J44" s="29">
         <v>88.329999999999998</v>
       </c>
-      <c r="K44" s="28">
+      <c r="K44" s="29">
         <v>88.329999999999998</v>
       </c>
-      <c r="L44" s="28">
+      <c r="L44" s="29">
         <v>88.329999999999998</v>
       </c>
-      <c r="M44" s="28">
+      <c r="M44" s="29">
         <v>88.329999999999998</v>
       </c>
-      <c r="N44" s="28">
+      <c r="N44" s="29">
         <v>88.329999999999998</v>
       </c>
-      <c r="O44" s="28">
+      <c r="O44" s="29">
         <v>88.329999999999998</v>
       </c>
       <c r="P44" s="17">
@@ -4674,34 +4900,40 @@
         <v>119.59</v>
       </c>
       <c r="W44" s="19">
-        <f>MIN(C44:V44)</f>
+        <v>128.36000000000001</v>
+      </c>
+      <c r="X44" s="19">
+        <v>128.36000000000001</v>
+      </c>
+      <c r="Y44" s="20">
+        <f>MIN(C44:X44)</f>
         <v>88.329999999999998</v>
       </c>
-      <c r="X44" s="20">
-        <f>MAX(C44:V44)</f>
-        <v>119.59</v>
-      </c>
-      <c r="Y44" s="20">
-        <f>AVERAGE(C44:V44)</f>
-        <v>99.611874999999998</v>
-      </c>
-      <c r="Z44" s="20">
-        <f>AVERAGE(Q44:V44)</f>
-        <v>118.41500000000001</v>
+      <c r="Z44" s="21">
+        <f>MAX(C44:X44)</f>
+        <v>128.36000000000001</v>
       </c>
       <c r="AA44" s="21">
+        <f>AVERAGE(C44:X44)</f>
+        <v>102.80611111111112</v>
+      </c>
+      <c r="AB44" s="21">
+        <f>AVERAGE(Q44:X44)</f>
+        <v>120.90125</v>
+      </c>
+      <c r="AC44" s="22">
+        <f>(AB44/AA44)-1</f>
+        <v>0.1760122885042501</v>
+      </c>
+      <c r="AD44" s="22">
+        <f>(AB44/Y44)-1</f>
+        <v>0.368745046982905</v>
+      </c>
+      <c r="AE44" s="22">
         <f>(Z44/Y44)-1</f>
-        <v>0.18876388984747061</v>
-      </c>
-      <c r="AB44" s="21">
-        <f>(Z44/W44)-1</f>
-        <v>0.34059775840597761</v>
-      </c>
-      <c r="AC44" s="21">
-        <f>(X44/W44)-1</f>
-        <v>0.35390014717536511</v>
-      </c>
-      <c r="AD44" s="22" t="s">
+        <v>0.45318691271368738</v>
+      </c>
+      <c r="AF44" s="23" t="s">
         <v>122</v>
       </c>
     </row>
@@ -4721,7 +4953,7 @@
       <c r="G45" s="17">
         <v>39.950000000000003</v>
       </c>
-      <c r="H45" s="24">
+      <c r="H45" s="25">
         <v>29.989999999999998</v>
       </c>
       <c r="I45" s="17">
@@ -4763,38 +4995,44 @@
       <c r="U45" s="17">
         <v>39.990000000000002</v>
       </c>
-      <c r="V45" s="33">
+      <c r="V45" s="34">
         <v>32.990000000000002</v>
       </c>
-      <c r="W45" s="19">
-        <f>MIN(C45:V45)</f>
+      <c r="W45" s="34">
+        <v>32.990000000000002</v>
+      </c>
+      <c r="X45" s="36">
+        <v>34.759999999999998</v>
+      </c>
+      <c r="Y45" s="20">
+        <f>MIN(C45:X45)</f>
         <v>29.989999999999998</v>
       </c>
-      <c r="X45" s="20">
-        <f>MAX(C45:V45)</f>
+      <c r="Z45" s="21">
+        <f>MAX(C45:X45)</f>
         <v>44.979999999999997</v>
       </c>
-      <c r="Y45" s="20">
-        <f>AVERAGE(C45:V45)</f>
-        <v>36.72117647058824</v>
-      </c>
-      <c r="Z45" s="20">
-        <f>AVERAGE(Q45:V45)</f>
-        <v>37.153333333333336</v>
-      </c>
       <c r="AA45" s="21">
+        <f>AVERAGE(C45:X45)</f>
+        <v>36.421578947368424</v>
+      </c>
+      <c r="AB45" s="21">
+        <f>AVERAGE(Q45:X45)</f>
+        <v>36.333750000000002</v>
+      </c>
+      <c r="AC45" s="22">
+        <f>(AB45/AA45)-1</f>
+        <v>-2.4114535917111324e-003</v>
+      </c>
+      <c r="AD45" s="22">
+        <f>(AB45/Y45)-1</f>
+        <v>0.2115288429476494</v>
+      </c>
+      <c r="AE45" s="22">
         <f>(Z45/Y45)-1</f>
-        <v>1.1768600689883391e-002</v>
-      </c>
-      <c r="AB45" s="21">
-        <f>(Z45/W45)-1</f>
-        <v>0.23885739691008134</v>
-      </c>
-      <c r="AC45" s="21">
-        <f>(X45/W45)-1</f>
         <v>0.49983327775925313</v>
       </c>
-      <c r="AD45" s="22" t="s">
+      <c r="AF45" s="23" t="s">
         <v>125</v>
       </c>
     </row>
@@ -4811,7 +5049,7 @@
       </c>
       <c r="E46" s="17"/>
       <c r="F46" s="17"/>
-      <c r="G46" s="33">
+      <c r="G46" s="34">
         <v>27.489999999999998</v>
       </c>
       <c r="H46" s="17">
@@ -4820,74 +5058,80 @@
       <c r="I46" s="17">
         <v>35.990000000000002</v>
       </c>
-      <c r="J46" s="33">
+      <c r="J46" s="34">
         <v>25.989999999999998</v>
       </c>
-      <c r="K46" s="33">
+      <c r="K46" s="34">
         <v>25.989999999999998</v>
       </c>
-      <c r="L46" s="33">
+      <c r="L46" s="34">
         <v>25.989999999999998</v>
       </c>
-      <c r="M46" s="33">
+      <c r="M46" s="34">
         <v>25.989999999999998</v>
       </c>
-      <c r="N46" s="17">
+      <c r="N46" s="18">
         <v>36.43</v>
       </c>
-      <c r="O46" s="17">
+      <c r="O46" s="19">
         <v>42</v>
       </c>
-      <c r="P46" s="17">
+      <c r="P46" s="18">
         <v>36.369999999999997</v>
       </c>
-      <c r="Q46" s="17">
+      <c r="Q46" s="18">
         <v>35.119999999999997</v>
       </c>
-      <c r="R46" s="17">
+      <c r="R46" s="18">
         <v>36.409999999999997</v>
       </c>
-      <c r="S46" s="17">
+      <c r="S46" s="18">
         <v>36.530000000000001</v>
       </c>
-      <c r="T46" s="33">
+      <c r="T46" s="34">
         <v>27.989999999999998</v>
       </c>
-      <c r="U46" s="33">
+      <c r="U46" s="34">
         <v>27.989999999999998</v>
       </c>
-      <c r="V46" s="35">
+      <c r="V46" s="36">
         <v>30.989999999999998</v>
       </c>
-      <c r="W46" s="19">
-        <f>MIN(C46:V46)</f>
+      <c r="W46" s="36">
+        <v>30.989999999999998</v>
+      </c>
+      <c r="X46" s="35">
+        <v>36.530000000000001</v>
+      </c>
+      <c r="Y46" s="20">
+        <f>MIN(C46:X46)</f>
         <v>25.989999999999998</v>
       </c>
-      <c r="X46" s="20">
-        <f>MAX(C46:V46)</f>
+      <c r="Z46" s="21">
+        <f>MAX(C46:X46)</f>
         <v>42</v>
       </c>
-      <c r="Y46" s="20">
-        <f>AVERAGE(C46:V46)</f>
-        <v>31.720588235294116</v>
-      </c>
-      <c r="Z46" s="20">
-        <f>AVERAGE(Q46:V46)</f>
-        <v>32.505000000000003</v>
-      </c>
       <c r="AA46" s="21">
+        <f>AVERAGE(C46:X46)</f>
+        <v>31.935263157894735</v>
+      </c>
+      <c r="AB46" s="21">
+        <f>AVERAGE(Q46:X46)</f>
+        <v>32.818750000000009</v>
+      </c>
+      <c r="AC46" s="22">
+        <f>(AB46/AA46)-1</f>
+        <v>2.766493069861764e-002</v>
+      </c>
+      <c r="AD46" s="22">
+        <f>(AB46/Y46)-1</f>
+        <v>0.26274528664871144</v>
+      </c>
+      <c r="AE46" s="22">
         <f>(Z46/Y46)-1</f>
-        <v>2.4728789986091959e-002</v>
-      </c>
-      <c r="AB46" s="21">
-        <f>(Z46/W46)-1</f>
-        <v>0.25067333589842256</v>
-      </c>
-      <c r="AC46" s="21">
-        <f>(X46/W46)-1</f>
         <v>0.61600615621392851</v>
       </c>
-      <c r="AD46" s="22" t="s">
+      <c r="AF46" s="23" t="s">
         <v>128</v>
       </c>
     </row>
@@ -4907,7 +5151,7 @@
       <c r="G47" s="17">
         <v>22.989999999999998</v>
       </c>
-      <c r="H47" s="24">
+      <c r="H47" s="25">
         <v>21.690000000000001</v>
       </c>
       <c r="I47" s="17">
@@ -4949,38 +5193,44 @@
       <c r="U47" s="17">
         <v>24.899999999999999</v>
       </c>
-      <c r="V47" s="33">
+      <c r="V47" s="34">
         <v>21.690000000000001</v>
       </c>
-      <c r="W47" s="19">
-        <f>MIN(C47:V47)</f>
+      <c r="W47" s="36">
+        <v>28.899999999999999</v>
+      </c>
+      <c r="X47" s="36">
+        <v>28.899999999999999</v>
+      </c>
+      <c r="Y47" s="20">
+        <f>MIN(C47:X47)</f>
         <v>21.690000000000001</v>
       </c>
-      <c r="X47" s="20">
-        <f>MAX(C47:V47)</f>
+      <c r="Z47" s="21">
+        <f>MAX(C47:X47)</f>
         <v>43.990000000000002</v>
       </c>
-      <c r="Y47" s="20">
-        <f>AVERAGE(C47:V47)</f>
-        <v>29.504705882352933</v>
-      </c>
-      <c r="Z47" s="20">
-        <f>AVERAGE(Q47:V47)</f>
-        <v>27.628333333333334</v>
-      </c>
       <c r="AA47" s="21">
+        <f>AVERAGE(C47:X47)</f>
+        <v>29.441052631578941</v>
+      </c>
+      <c r="AB47" s="21">
+        <f>AVERAGE(Q47:X47)</f>
+        <v>27.946250000000003</v>
+      </c>
+      <c r="AC47" s="22">
+        <f>(AB47/AA47)-1</f>
+        <v>-5.0772730523078846e-002</v>
+      </c>
+      <c r="AD47" s="22">
+        <f>(AB47/Y47)-1</f>
+        <v>0.28843937298294153</v>
+      </c>
+      <c r="AE47" s="22">
         <f>(Z47/Y47)-1</f>
-        <v>-6.3595704241264039e-002</v>
-      </c>
-      <c r="AB47" s="21">
-        <f>(Z47/W47)-1</f>
-        <v>0.27378208083602273</v>
-      </c>
-      <c r="AC47" s="21">
-        <f>(X47/W47)-1</f>
         <v>1.0281235592438911</v>
       </c>
-      <c r="AD47" s="22" t="s">
+      <c r="AF47" s="23" t="s">
         <v>131</v>
       </c>
     </row>
@@ -5015,7 +5265,7 @@
       <c r="L48" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="M48" s="24">
+      <c r="M48" s="25">
         <v>1449.28</v>
       </c>
       <c r="N48" s="18">
@@ -5045,74 +5295,80 @@
       <c r="V48" s="17">
         <v>1611.4100000000001</v>
       </c>
-      <c r="W48" s="19">
-        <f>MIN(C48:V48)</f>
+      <c r="W48" s="17">
+        <v>1611.4100000000001</v>
+      </c>
+      <c r="X48" s="17">
+        <v>1611.4100000000001</v>
+      </c>
+      <c r="Y48" s="20">
+        <f>MIN(C48:X48)</f>
         <v>1449.28</v>
       </c>
-      <c r="X48" s="20">
-        <f>MAX(C48:V48)</f>
+      <c r="Z48" s="21">
+        <f>MAX(C48:X48)</f>
         <v>1820.77</v>
       </c>
-      <c r="Y48" s="20">
-        <f>AVERAGE(C48:V48)</f>
-        <v>1702.3566666666666</v>
-      </c>
-      <c r="Z48" s="20">
-        <f>AVERAGE(Q48:V48)</f>
-        <v>1675.5600000000002</v>
-      </c>
       <c r="AA48" s="21">
+        <f>AVERAGE(C48:X48)</f>
+        <v>1691.6570588235293</v>
+      </c>
+      <c r="AB48" s="21">
+        <f>AVERAGE(Q48:X48)</f>
+        <v>1659.5225</v>
+      </c>
+      <c r="AC48" s="22">
+        <f>(AB48/AA48)-1</f>
+        <v>-1.899590620682734e-002</v>
+      </c>
+      <c r="AD48" s="22">
+        <f>(AB48/Y48)-1</f>
+        <v>0.14506686078604547</v>
+      </c>
+      <c r="AE48" s="22">
         <f>(Z48/Y48)-1</f>
-        <v>-1.5740923856536027e-002</v>
-      </c>
-      <c r="AB48" s="21">
-        <f>(Z48/W48)-1</f>
-        <v>0.15613270037535898</v>
-      </c>
-      <c r="AC48" s="21">
-        <f>(X48/W48)-1</f>
         <v>0.25632727975270475</v>
       </c>
-      <c r="AD48" s="1" t="s">
+      <c r="AF48" s="1" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="49" ht="18">
-      <c r="A49" s="25" t="s">
+      <c r="A49" s="26" t="s">
         <v>134</v>
       </c>
-      <c r="B49" s="26" t="s">
+      <c r="B49" s="27" t="s">
         <v>135</v>
       </c>
-      <c r="C49" s="28"/>
-      <c r="D49" s="28"/>
-      <c r="E49" s="28"/>
-      <c r="F49" s="28"/>
-      <c r="G49" s="28">
+      <c r="C49" s="29"/>
+      <c r="D49" s="29"/>
+      <c r="E49" s="29"/>
+      <c r="F49" s="29"/>
+      <c r="G49" s="29">
         <v>33.890000000000001</v>
       </c>
-      <c r="H49" s="28">
+      <c r="H49" s="29">
         <v>33.890000000000001</v>
       </c>
-      <c r="I49" s="28">
+      <c r="I49" s="29">
         <v>33.890000000000001</v>
       </c>
-      <c r="J49" s="28">
+      <c r="J49" s="29">
         <v>33.890000000000001</v>
       </c>
-      <c r="K49" s="28">
+      <c r="K49" s="29">
         <v>33.890000000000001</v>
       </c>
-      <c r="L49" s="28">
+      <c r="L49" s="29">
         <v>38.039999999999999</v>
       </c>
-      <c r="M49" s="28">
+      <c r="M49" s="29">
         <v>38.369999999999997</v>
       </c>
-      <c r="N49" s="28">
+      <c r="N49" s="29">
         <v>38.369999999999997</v>
       </c>
-      <c r="O49" s="28">
+      <c r="O49" s="29">
         <v>38.369999999999997</v>
       </c>
       <c r="P49" s="17">
@@ -5133,38 +5389,44 @@
       <c r="U49" s="17">
         <v>39.899999999999999</v>
       </c>
-      <c r="V49" s="33">
+      <c r="V49" s="34">
         <v>31.989999999999998</v>
       </c>
-      <c r="W49" s="19">
-        <f>MIN(C49:V49)</f>
-        <v>31.989999999999998</v>
-      </c>
-      <c r="X49" s="20">
-        <f>MAX(C49:V49)</f>
+      <c r="W49" s="34">
+        <v>30.989999999999998</v>
+      </c>
+      <c r="X49" s="36">
+        <v>39.899999999999999</v>
+      </c>
+      <c r="Y49" s="20">
+        <f>MIN(C49:X49)</f>
+        <v>30.989999999999998</v>
+      </c>
+      <c r="Z49" s="21">
+        <f>MAX(C49:X49)</f>
         <v>43.210000000000001</v>
       </c>
-      <c r="Y49" s="20">
-        <f>AVERAGE(C49:V49)</f>
-        <v>37.076249999999995</v>
-      </c>
-      <c r="Z49" s="20">
-        <f>AVERAGE(Q49:V49)</f>
-        <v>38.708333333333336</v>
-      </c>
       <c r="AA49" s="21">
+        <f>AVERAGE(C49:X49)</f>
+        <v>36.894999999999996</v>
+      </c>
+      <c r="AB49" s="21">
+        <f>AVERAGE(Q49:X49)</f>
+        <v>37.892499999999998</v>
+      </c>
+      <c r="AC49" s="22">
+        <f>(AB49/AA49)-1</f>
+        <v>2.7036183764737931e-002</v>
+      </c>
+      <c r="AD49" s="22">
+        <f>(AB49/Y49)-1</f>
+        <v>0.2227331397224912</v>
+      </c>
+      <c r="AE49" s="22">
         <f>(Z49/Y49)-1</f>
-        <v>4.4019644201701569e-002</v>
-      </c>
-      <c r="AB49" s="21">
-        <f>(Z49/W49)-1</f>
-        <v>0.21001354589976051</v>
-      </c>
-      <c r="AC49" s="21">
-        <f>(X49/W49)-1</f>
-        <v>0.35073460456392636</v>
-      </c>
-      <c r="AD49" s="22" t="s">
+        <v>0.39432074862859001</v>
+      </c>
+      <c r="AF49" s="23" t="s">
         <v>136</v>
       </c>
     </row>
@@ -5185,13 +5447,13 @@
       <c r="H50" s="17">
         <v>90.739999999999995</v>
       </c>
-      <c r="I50" s="24">
+      <c r="I50" s="25">
         <v>89.950000000000003</v>
       </c>
-      <c r="J50" s="24">
+      <c r="J50" s="25">
         <v>89.950000000000003</v>
       </c>
-      <c r="K50" s="24">
+      <c r="K50" s="25">
         <v>89.950000000000003</v>
       </c>
       <c r="L50" s="17">
@@ -5227,35 +5489,41 @@
       <c r="V50" s="17">
         <v>83.079999999999998</v>
       </c>
-      <c r="W50" s="19">
-        <f>MIN(C50:V50)</f>
+      <c r="W50" s="17">
+        <v>84.099999999999994</v>
+      </c>
+      <c r="X50" s="17">
+        <v>84.680000000000007</v>
+      </c>
+      <c r="Y50" s="20">
+        <f>MIN(C50:X50)</f>
         <v>81.689999999999998</v>
       </c>
-      <c r="X50" s="20">
-        <f>MAX(C50:V50)</f>
+      <c r="Z50" s="21">
+        <f>MAX(C50:X50)</f>
         <v>93.280000000000001</v>
       </c>
-      <c r="Y50" s="20">
-        <f>AVERAGE(C50:V50)</f>
-        <v>88.674375000000026</v>
-      </c>
-      <c r="Z50" s="20">
-        <f>AVERAGE(Q50:V50)</f>
-        <v>85.695000000000007</v>
-      </c>
       <c r="AA50" s="21">
+        <f>AVERAGE(C50:X50)</f>
+        <v>88.198333333333352</v>
+      </c>
+      <c r="AB50" s="21">
+        <f>AVERAGE(Q50:X50)</f>
+        <v>85.368750000000006</v>
+      </c>
+      <c r="AC50" s="22">
+        <f>(AB50/AA50)-1</f>
+        <v>-3.2082049925357792e-002</v>
+      </c>
+      <c r="AD50" s="22">
+        <f>(AB50/Y50)-1</f>
+        <v>4.5033051781123934e-002</v>
+      </c>
+      <c r="AE50" s="22">
         <f>(Z50/Y50)-1</f>
-        <v>-3.3599052713932487e-002</v>
-      </c>
-      <c r="AB50" s="21">
-        <f>(Z50/W50)-1</f>
-        <v>4.902680866691167e-002</v>
-      </c>
-      <c r="AC50" s="21">
-        <f>(X50/W50)-1</f>
         <v>0.1418778308238462</v>
       </c>
-      <c r="AD50" s="1" t="s">
+      <c r="AF50" s="1" t="s">
         <v>139</v>
       </c>
     </row>
@@ -5320,35 +5588,41 @@
       <c r="V51" s="17">
         <v>309.05000000000001</v>
       </c>
-      <c r="W51" s="19">
-        <f>MIN(C51:V51)</f>
+      <c r="W51" s="34">
+        <v>298.80000000000001</v>
+      </c>
+      <c r="X51" s="34">
+        <v>298.80000000000001</v>
+      </c>
+      <c r="Y51" s="20">
+        <f>MIN(C51:X51)</f>
+        <v>298.80000000000001</v>
+      </c>
+      <c r="Z51" s="21">
+        <f>MAX(C51:X51)</f>
         <v>309.05000000000001</v>
       </c>
-      <c r="X51" s="20">
-        <f>MAX(C51:V51)</f>
-        <v>309.05000000000001</v>
-      </c>
-      <c r="Y51" s="20">
-        <f>AVERAGE(C51:V51)</f>
-        <v>309.05000000000007</v>
-      </c>
-      <c r="Z51" s="20">
-        <f>AVERAGE(Q51:V51)</f>
-        <v>309.05000000000001</v>
-      </c>
       <c r="AA51" s="21">
+        <f>AVERAGE(C51:X51)</f>
+        <v>307.97105263157903</v>
+      </c>
+      <c r="AB51" s="21">
+        <f>AVERAGE(Q51:X51)</f>
+        <v>306.48750000000001</v>
+      </c>
+      <c r="AC51" s="22">
+        <f>(AB51/AA51)-1</f>
+        <v>-4.817182065983916e-003</v>
+      </c>
+      <c r="AD51" s="22">
+        <f>(AB51/Y51)-1</f>
+        <v>2.5727911646586277e-002</v>
+      </c>
+      <c r="AE51" s="22">
         <f>(Z51/Y51)-1</f>
-        <v>-2.2204460492503131e-016</v>
-      </c>
-      <c r="AB51" s="21">
-        <f>(Z51/W51)-1</f>
-        <v>0</v>
-      </c>
-      <c r="AC51" s="21">
-        <f>(X51/W51)-1</f>
-        <v>0</v>
-      </c>
-      <c r="AD51" s="22" t="s">
+        <v>3.4303882195448443e-002</v>
+      </c>
+      <c r="AF51" s="23" t="s">
         <v>142</v>
       </c>
     </row>
@@ -5411,35 +5685,41 @@
       <c r="V52" s="17">
         <v>108.98999999999999</v>
       </c>
-      <c r="W52" s="19">
-        <f>MIN(C52:V52)</f>
+      <c r="W52" s="17">
         <v>108.98999999999999</v>
       </c>
-      <c r="X52" s="20">
-        <f>MAX(C52:V52)</f>
+      <c r="X52" s="17">
         <v>108.98999999999999</v>
       </c>
       <c r="Y52" s="20">
-        <f>AVERAGE(C52:V52)</f>
+        <f>MIN(C52:X52)</f>
         <v>108.98999999999999</v>
       </c>
-      <c r="Z52" s="20">
-        <f>AVERAGE(Q52:V52)</f>
+      <c r="Z52" s="21">
+        <f>MAX(C52:X52)</f>
         <v>108.98999999999999</v>
       </c>
       <c r="AA52" s="21">
+        <f>AVERAGE(C52:X52)</f>
+        <v>108.98999999999999</v>
+      </c>
+      <c r="AB52" s="21">
+        <f>AVERAGE(Q52:X52)</f>
+        <v>108.98999999999999</v>
+      </c>
+      <c r="AC52" s="22">
+        <f>(AB52/AA52)-1</f>
+        <v>0</v>
+      </c>
+      <c r="AD52" s="22">
+        <f>(AB52/Y52)-1</f>
+        <v>0</v>
+      </c>
+      <c r="AE52" s="22">
         <f>(Z52/Y52)-1</f>
         <v>0</v>
       </c>
-      <c r="AB52" s="21">
-        <f>(Z52/W52)-1</f>
-        <v>0</v>
-      </c>
-      <c r="AC52" s="21">
-        <f>(X52/W52)-1</f>
-        <v>0</v>
-      </c>
-      <c r="AD52" s="37" t="s">
+      <c r="AF52" s="38" t="s">
         <v>144</v>
       </c>
     </row>
@@ -5471,93 +5751,98 @@
       <c r="V53" s="17">
         <v>1.99</v>
       </c>
-      <c r="W53" s="19">
-        <f>MIN(C53:V53)</f>
+      <c r="W53" s="17">
+        <v>1.99</v>
+      </c>
+      <c r="X53" s="17">
+        <v>1.99</v>
+      </c>
+      <c r="Y53" s="20">
+        <f>MIN(C53:X53)</f>
         <v>1.49</v>
       </c>
-      <c r="X53" s="20">
-        <f>MAX(C53:V53)</f>
+      <c r="Z53" s="21">
+        <f>MAX(C53:X53)</f>
         <v>1.99</v>
       </c>
-      <c r="Y53" s="20">
-        <f>AVERAGE(C53:V53)</f>
-        <v>1.6775</v>
-      </c>
-      <c r="Z53" s="20">
-        <f>AVERAGE(Q53:V53)</f>
-        <v>1.74</v>
-      </c>
       <c r="AA53" s="21">
+        <f>AVERAGE(C53:X53)</f>
+        <v>1.7399999999999998</v>
+      </c>
+      <c r="AB53" s="21">
+        <f>AVERAGE(Q53:X53)</f>
+        <v>1.8025</v>
+      </c>
+      <c r="AC53" s="22">
+        <f>(AB53/AA53)-1</f>
+        <v>3.5919540229885083e-002</v>
+      </c>
+      <c r="AD53" s="22">
+        <f>(AB53/Y53)-1</f>
+        <v>0.20973154362416113</v>
+      </c>
+      <c r="AE53" s="22">
         <f>(Z53/Y53)-1</f>
-        <v>3.7257824143070106e-002</v>
-      </c>
-      <c r="AB53" s="21">
-        <f>(Z53/W53)-1</f>
-        <v>0.16778523489932895</v>
-      </c>
-      <c r="AC53" s="21">
-        <f>(X53/W53)-1</f>
         <v>0.33557046979865768</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="W1:W6"/>
-    <mergeCell ref="X1:X6"/>
     <mergeCell ref="Y1:Y6"/>
     <mergeCell ref="Z1:Z6"/>
     <mergeCell ref="AA1:AA6"/>
     <mergeCell ref="AB1:AB6"/>
     <mergeCell ref="AC1:AC6"/>
+    <mergeCell ref="AD1:AD6"/>
+    <mergeCell ref="AE1:AE6"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="B5"/>
-    <hyperlink r:id="rId2" ref="AD8"/>
-    <hyperlink r:id="rId3" ref="AD9"/>
-    <hyperlink r:id="rId4" ref="AD10"/>
-    <hyperlink r:id="rId5" ref="AD11"/>
-    <hyperlink r:id="rId6" ref="AD12"/>
-    <hyperlink r:id="rId7" ref="AD13"/>
-    <hyperlink r:id="rId8" ref="AD14"/>
-    <hyperlink r:id="rId9" ref="AD15"/>
-    <hyperlink r:id="rId10" ref="AD16"/>
-    <hyperlink r:id="rId11" ref="AD17"/>
-    <hyperlink r:id="rId12" ref="AD18"/>
-    <hyperlink r:id="rId13" ref="AD19"/>
-    <hyperlink r:id="rId14" ref="AD20"/>
-    <hyperlink r:id="rId15" ref="AD21"/>
-    <hyperlink r:id="rId16" ref="AD22"/>
-    <hyperlink r:id="rId17" ref="AD23"/>
-    <hyperlink r:id="rId18" ref="AD24"/>
-    <hyperlink r:id="rId19" ref="AD25"/>
-    <hyperlink r:id="rId20" ref="AD26"/>
-    <hyperlink r:id="rId21" ref="AD27"/>
-    <hyperlink r:id="rId22" ref="AD28"/>
-    <hyperlink r:id="rId23" ref="AD29"/>
-    <hyperlink r:id="rId24" ref="AD30"/>
-    <hyperlink r:id="rId25" ref="AD31"/>
-    <hyperlink r:id="rId26" ref="AD32"/>
-    <hyperlink r:id="rId27" ref="AD33"/>
-    <hyperlink r:id="rId28" ref="AD34"/>
-    <hyperlink r:id="rId29" ref="AD35"/>
-    <hyperlink r:id="rId30" ref="AD36"/>
-    <hyperlink r:id="rId30" ref="AD37"/>
-    <hyperlink r:id="rId30" ref="AD38"/>
-    <hyperlink r:id="rId30" ref="AD39"/>
-    <hyperlink r:id="rId30" ref="AD40"/>
-    <hyperlink r:id="rId30" ref="AD41"/>
-    <hyperlink r:id="rId31" ref="AD43"/>
-    <hyperlink r:id="rId32" ref="AD44"/>
-    <hyperlink r:id="rId33" ref="AD45"/>
-    <hyperlink r:id="rId34" ref="AD46"/>
-    <hyperlink r:id="rId35" ref="AD47"/>
-    <hyperlink r:id="rId36" ref="AD49"/>
-    <hyperlink r:id="rId37" ref="AD51"/>
-    <hyperlink r:id="rId38" ref="AD52"/>
+    <hyperlink r:id="rId1" ref="AF8"/>
+    <hyperlink r:id="rId2" ref="AF9"/>
+    <hyperlink r:id="rId3" ref="AF10"/>
+    <hyperlink r:id="rId4" ref="AF11"/>
+    <hyperlink r:id="rId5" ref="AF12"/>
+    <hyperlink r:id="rId6" ref="AF13"/>
+    <hyperlink r:id="rId7" ref="AF14"/>
+    <hyperlink r:id="rId8" ref="AF15"/>
+    <hyperlink r:id="rId9" ref="AF16"/>
+    <hyperlink r:id="rId10" ref="AF17"/>
+    <hyperlink r:id="rId11" ref="AF18"/>
+    <hyperlink r:id="rId12" ref="AF19"/>
+    <hyperlink r:id="rId13" ref="AF20"/>
+    <hyperlink r:id="rId14" ref="AF21"/>
+    <hyperlink r:id="rId15" ref="AF22"/>
+    <hyperlink r:id="rId16" ref="AF23"/>
+    <hyperlink r:id="rId17" ref="AF24"/>
+    <hyperlink r:id="rId18" ref="AF25"/>
+    <hyperlink r:id="rId19" ref="AF26"/>
+    <hyperlink r:id="rId20" ref="AF27"/>
+    <hyperlink r:id="rId21" ref="AF28"/>
+    <hyperlink r:id="rId22" ref="AF29"/>
+    <hyperlink r:id="rId23" ref="AF30"/>
+    <hyperlink r:id="rId24" ref="AF31"/>
+    <hyperlink r:id="rId25" ref="AF32"/>
+    <hyperlink r:id="rId26" ref="AF33"/>
+    <hyperlink r:id="rId27" ref="AF34"/>
+    <hyperlink r:id="rId28" ref="AF35"/>
+    <hyperlink r:id="rId29" ref="AF36"/>
+    <hyperlink r:id="rId29" ref="AF37"/>
+    <hyperlink r:id="rId29" ref="AF38"/>
+    <hyperlink r:id="rId29" ref="AF39"/>
+    <hyperlink r:id="rId29" ref="AF40"/>
+    <hyperlink r:id="rId29" ref="AF41"/>
+    <hyperlink r:id="rId30" ref="AF43"/>
+    <hyperlink r:id="rId31" ref="AF44"/>
+    <hyperlink r:id="rId32" ref="AF45"/>
+    <hyperlink r:id="rId33" ref="AF46"/>
+    <hyperlink r:id="rId34" ref="AF47"/>
+    <hyperlink r:id="rId35" ref="AF49"/>
+    <hyperlink r:id="rId36" ref="AF51"/>
+    <hyperlink r:id="rId37" ref="AF52"/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.25196850393700787" right="0.25196850393700787" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="37" firstPageNumber="1" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="1" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <pageSetup paperSize="9" scale="36" firstPageNumber="1" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="1" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/analyse-prix-composants.xlsx
+++ b/analyse-prix-composants.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Feuille1" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Feuille1!$A:$AE</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Feuille1!$A:$AF</definedName>
     <definedName name="Print_Titles" localSheetId="0">Feuille1!$7:$7</definedName>
   </definedNames>
   <calcPr/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="147">
   <si>
     <t xml:space="preserve">Le prix des composants IT</t>
   </si>
@@ -124,6 +124,9 @@
   </si>
   <si>
     <t xml:space="preserve">28 mar 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 avr 2026</t>
   </si>
   <si>
     <t>Min</t>
@@ -1346,12 +1349,12 @@
     <col bestFit="1" min="12" max="12" style="4" width="11.7109375"/>
     <col bestFit="1" min="13" max="13" style="4" width="13.00390625"/>
     <col bestFit="1" min="14" max="15" style="4" width="14.140625"/>
-    <col customWidth="1" min="16" max="24" style="1" width="12.7109375"/>
-    <col customWidth="1" min="25" max="28" style="2" width="12.7109375"/>
-    <col customWidth="1" min="29" max="29" style="2" width="14.140625"/>
-    <col customWidth="1" min="30" max="31" style="2" width="12.7109375"/>
-    <col customWidth="1" min="32" max="32" style="5" width="42.28125"/>
-    <col min="33" max="16384" style="1" width="9.140625"/>
+    <col customWidth="1" min="16" max="25" style="1" width="12.7109375"/>
+    <col customWidth="1" min="26" max="29" style="2" width="12.7109375"/>
+    <col customWidth="1" min="30" max="30" style="2" width="14.140625"/>
+    <col customWidth="1" min="31" max="32" style="2" width="12.7109375"/>
+    <col customWidth="1" min="33" max="33" style="5" width="42.28125"/>
+    <col min="34" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" ht="33">
@@ -1368,28 +1371,29 @@
       <c r="V1" s="1"/>
       <c r="W1" s="1"/>
       <c r="X1" s="1"/>
-      <c r="Y1" s="7" t="s">
+      <c r="Y1" s="1"/>
+      <c r="Z1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="Z1" s="7" t="s">
+      <c r="AA1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="AA1" s="7" t="s">
+      <c r="AB1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="AB1" s="7" t="s">
+      <c r="AC1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="AC1" s="7" t="s">
+      <c r="AD1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="AD1" s="7" t="s">
+      <c r="AE1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="AE1" s="7" t="s">
+      <c r="AF1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="AF1" s="5"/>
+      <c r="AG1" s="5"/>
     </row>
     <row r="2" ht="23.25">
       <c r="A2" s="2"/>
@@ -1405,13 +1409,14 @@
       <c r="V2" s="1"/>
       <c r="W2" s="1"/>
       <c r="X2" s="1"/>
-      <c r="Y2" s="7"/>
+      <c r="Y2" s="1"/>
       <c r="Z2" s="7"/>
       <c r="AA2" s="7"/>
       <c r="AB2" s="7"/>
       <c r="AC2" s="7"/>
       <c r="AD2" s="7"/>
       <c r="AE2" s="7"/>
+      <c r="AF2" s="7"/>
     </row>
     <row r="3" ht="18">
       <c r="A3" s="2"/>
@@ -1425,15 +1430,16 @@
       <c r="V3" s="1"/>
       <c r="W3" s="1"/>
       <c r="X3" s="1"/>
-      <c r="Y3" s="7"/>
+      <c r="Y3" s="1"/>
       <c r="Z3" s="7"/>
       <c r="AA3" s="7"/>
       <c r="AB3" s="7"/>
       <c r="AC3" s="7"/>
       <c r="AD3" s="7"/>
       <c r="AE3" s="7"/>
+      <c r="AF3" s="7"/>
     </row>
-    <row r="4" ht="54">
+    <row r="4" ht="18">
       <c r="A4" s="2"/>
       <c r="B4" s="3"/>
       <c r="G4" s="4"/>
@@ -1446,13 +1452,14 @@
       <c r="V4" s="1"/>
       <c r="W4" s="1"/>
       <c r="X4" s="1"/>
-      <c r="Y4" s="7"/>
+      <c r="Y4" s="1"/>
       <c r="Z4" s="7"/>
       <c r="AA4" s="7"/>
       <c r="AB4" s="7"/>
       <c r="AC4" s="7"/>
       <c r="AD4" s="7"/>
       <c r="AE4" s="7"/>
+      <c r="AF4" s="7"/>
     </row>
     <row r="5" ht="23.25">
       <c r="A5" s="2"/>
@@ -1466,13 +1473,14 @@
       <c r="V5" s="1"/>
       <c r="W5" s="1"/>
       <c r="X5" s="1"/>
-      <c r="Y5" s="7"/>
+      <c r="Y5" s="1"/>
       <c r="Z5" s="7"/>
       <c r="AA5" s="7"/>
       <c r="AB5" s="7"/>
       <c r="AC5" s="7"/>
       <c r="AD5" s="7"/>
       <c r="AE5" s="7"/>
+      <c r="AF5" s="7"/>
     </row>
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="2"/>
@@ -1485,13 +1493,14 @@
       <c r="V6" s="1"/>
       <c r="W6" s="1"/>
       <c r="X6" s="1"/>
-      <c r="Y6" s="7"/>
+      <c r="Y6" s="1"/>
       <c r="Z6" s="7"/>
       <c r="AA6" s="7"/>
       <c r="AB6" s="7"/>
       <c r="AC6" s="7"/>
       <c r="AD6" s="7"/>
       <c r="AE6" s="7"/>
+      <c r="AF6" s="7"/>
     </row>
     <row r="7" ht="18">
       <c r="A7" s="10" t="s">
@@ -1566,7 +1575,7 @@
       <c r="X7" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="Y7" s="13" t="s">
+      <c r="Y7" s="12" t="s">
         <v>33</v>
       </c>
       <c r="Z7" s="13" t="s">
@@ -1587,16 +1596,19 @@
       <c r="AE7" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="AF7" s="5" t="s">
+      <c r="AF7" s="13" t="s">
         <v>40</v>
+      </c>
+      <c r="AG7" s="5" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="8" ht="36">
       <c r="A8" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C8" s="15">
         <v>171.88</v>
@@ -1623,7 +1635,7 @@
         <v>341.57999999999998</v>
       </c>
       <c r="M8" s="17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N8" s="18">
         <v>321.14999999999998</v>
@@ -1658,48 +1670,51 @@
       <c r="X8" s="19">
         <v>415.97000000000003</v>
       </c>
-      <c r="Y8" s="20">
-        <f>MIN(C8:X8)</f>
+      <c r="Y8" s="19">
+        <v>418.17000000000002</v>
+      </c>
+      <c r="Z8" s="20">
+        <f>MIN(C8:Y8)</f>
         <v>171.88</v>
       </c>
-      <c r="Z8" s="21">
-        <f>MAX(C8:X8)</f>
-        <v>415.97000000000003</v>
-      </c>
       <c r="AA8" s="21">
-        <f>AVERAGE(C8:X8)</f>
-        <v>342.5994444444446</v>
+        <f>MAX(C8:Y8)</f>
+        <v>418.17000000000002</v>
       </c>
       <c r="AB8" s="21">
-        <f>AVERAGE(Q8:X8)</f>
-        <v>373.23749999999995</v>
-      </c>
-      <c r="AC8" s="22">
-        <f>(AB8/AA8)-1</f>
-        <v>8.9428211435770733e-002</v>
+        <f>AVERAGE(C8:Y8)</f>
+        <v>346.57684210526332</v>
+      </c>
+      <c r="AC8" s="21">
+        <f>AVERAGE(Q8:Y8)</f>
+        <v>378.22999999999996</v>
       </c>
       <c r="AD8" s="22">
-        <f>(AB8/Y8)-1</f>
-        <v>1.1715004654410053</v>
+        <f>(AC8/AB8)-1</f>
+        <v>9.1330850908736938e-002</v>
       </c>
       <c r="AE8" s="22">
-        <f>(Z8/Y8)-1</f>
-        <v>1.4201186874563652</v>
-      </c>
-      <c r="AF8" s="23" t="s">
-        <v>44</v>
-      </c>
-      <c r="AG8" s="24">
+        <f>(AC8/Z8)-1</f>
+        <v>1.200546893181289</v>
+      </c>
+      <c r="AF8" s="22">
+        <f>(AA8/Z8)-1</f>
+        <v>1.4329183151035609</v>
+      </c>
+      <c r="AG8" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH8" s="24">
         <f>C2*1</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" ht="36">
       <c r="A9" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C9" s="16"/>
       <c r="D9" s="25">
@@ -1711,7 +1726,7 @@
         <v>686</v>
       </c>
       <c r="H9" s="17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I9" s="17">
         <v>613.99000000000001</v>
@@ -1761,44 +1776,47 @@
       <c r="X9" s="18">
         <v>978.75</v>
       </c>
-      <c r="Y9" s="20">
-        <f>MIN(C9:X9)</f>
+      <c r="Y9" s="18">
+        <v>978.75</v>
+      </c>
+      <c r="Z9" s="20">
+        <f>MIN(C9:Y9)</f>
         <v>200.47999999999999</v>
       </c>
-      <c r="Z9" s="21">
-        <f>MAX(C9:X9)</f>
+      <c r="AA9" s="21">
+        <f>MAX(C9:Y9)</f>
         <v>978.75</v>
       </c>
-      <c r="AA9" s="21">
-        <f>AVERAGE(C9:X9)</f>
-        <v>800.75666666666666</v>
-      </c>
       <c r="AB9" s="21">
-        <f>AVERAGE(Q9:X9)</f>
-        <v>881.93124999999998</v>
-      </c>
-      <c r="AC9" s="22">
-        <f>(AB9/AA9)-1</f>
-        <v>0.10137234782101934</v>
+        <f>AVERAGE(C9:Y9)</f>
+        <v>810.12473684210534</v>
+      </c>
+      <c r="AC9" s="21">
+        <f>AVERAGE(Q9:Y9)</f>
+        <v>892.68888888888887</v>
       </c>
       <c r="AD9" s="22">
-        <f>(AB9/Y9)-1</f>
-        <v>3.3990984138068638</v>
+        <f>(AC9/AB9)-1</f>
+        <v>0.10191535734190937</v>
       </c>
       <c r="AE9" s="22">
-        <f>(Z9/Y9)-1</f>
+        <f>(AC9/Z9)-1</f>
+        <v>3.4527578256628537</v>
+      </c>
+      <c r="AF9" s="22">
+        <f>(AA9/Z9)-1</f>
         <v>3.8820331205107745</v>
       </c>
-      <c r="AF9" s="23" t="s">
-        <v>46</v>
+      <c r="AG9" s="23" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="10" ht="36">
       <c r="A10" s="26" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C10" s="28"/>
       <c r="D10" s="25">
@@ -1860,44 +1878,47 @@
       <c r="X10" s="19">
         <v>717.78999999999996</v>
       </c>
-      <c r="Y10" s="20">
-        <f>MIN(C10:X10)</f>
+      <c r="Y10" s="18">
+        <v>709.99000000000001</v>
+      </c>
+      <c r="Z10" s="20">
+        <f>MIN(C10:Y10)</f>
         <v>284.13</v>
       </c>
-      <c r="Z10" s="21">
-        <f>MAX(C10:X10)</f>
+      <c r="AA10" s="21">
+        <f>MAX(C10:Y10)</f>
         <v>717.78999999999996</v>
       </c>
-      <c r="AA10" s="21">
-        <f>AVERAGE(C10:X10)</f>
-        <v>598.77789473684209</v>
-      </c>
       <c r="AB10" s="21">
-        <f>AVERAGE(Q10:X10)</f>
-        <v>661.48874999999998</v>
-      </c>
-      <c r="AC10" s="22">
-        <f>(AB10/AA10)-1</f>
-        <v>0.10473141345793802</v>
+        <f>AVERAGE(C10:Y10)</f>
+        <v>604.33849999999995</v>
+      </c>
+      <c r="AC10" s="21">
+        <f>AVERAGE(Q10:Y10)</f>
+        <v>666.87777777777774</v>
       </c>
       <c r="AD10" s="22">
-        <f>(AB10/Y10)-1</f>
-        <v>1.3281200506810262</v>
+        <f>(AC10/AB10)-1</f>
+        <v>0.10348385512056213</v>
       </c>
       <c r="AE10" s="22">
-        <f>(Z10/Y10)-1</f>
+        <f>(AC10/Z10)-1</f>
+        <v>1.3470868186315341</v>
+      </c>
+      <c r="AF10" s="22">
+        <f>(AA10/Z10)-1</f>
         <v>1.5262731848097699</v>
       </c>
-      <c r="AF10" s="23" t="s">
-        <v>48</v>
+      <c r="AG10" s="23" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="11" ht="36">
       <c r="A11" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C11" s="16"/>
       <c r="D11" s="16"/>
@@ -1953,44 +1974,47 @@
       <c r="X11" s="19">
         <v>827.74000000000001</v>
       </c>
-      <c r="Y11" s="20">
-        <f>MIN(C11:X11)</f>
+      <c r="Y11" s="19">
+        <v>824.50999999999999</v>
+      </c>
+      <c r="Z11" s="20">
+        <f>MIN(C11:Y11)</f>
         <v>685.71000000000004</v>
       </c>
-      <c r="Z11" s="21">
-        <f>MAX(C11:X11)</f>
+      <c r="AA11" s="21">
+        <f>MAX(C11:Y11)</f>
         <v>863.60000000000002</v>
       </c>
-      <c r="AA11" s="21">
-        <f>AVERAGE(C11:X11)</f>
-        <v>785.60749999999996</v>
-      </c>
       <c r="AB11" s="21">
-        <f>AVERAGE(Q11:X11)</f>
-        <v>809.09124999999995</v>
-      </c>
-      <c r="AC11" s="22">
-        <f>(AB11/AA11)-1</f>
-        <v>2.989247174956966e-002</v>
+        <f>AVERAGE(C11:Y11)</f>
+        <v>787.89588235294116</v>
+      </c>
+      <c r="AC11" s="21">
+        <f>AVERAGE(Q11:Y11)</f>
+        <v>810.80444444444447</v>
       </c>
       <c r="AD11" s="22">
-        <f>(AB11/Y11)-1</f>
-        <v>0.17993211415904664</v>
+        <f>(AC11/AB11)-1</f>
+        <v>2.9075621036487753e-002</v>
       </c>
       <c r="AE11" s="22">
-        <f>(Z11/Y11)-1</f>
+        <f>(AC11/Z11)-1</f>
+        <v>0.18243053833901279</v>
+      </c>
+      <c r="AF11" s="22">
+        <f>(AA11/Z11)-1</f>
         <v>0.25942453807002952</v>
       </c>
-      <c r="AF11" s="23" t="s">
-        <v>50</v>
+      <c r="AG11" s="23" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="12" ht="18">
       <c r="A12" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C12" s="16"/>
       <c r="D12" s="17">
@@ -2052,44 +2076,47 @@
       <c r="X12" s="18">
         <v>555.91999999999996</v>
       </c>
-      <c r="Y12" s="20">
-        <f>MIN(C12:X12)</f>
+      <c r="Y12" s="18">
+        <v>547.98000000000002</v>
+      </c>
+      <c r="Z12" s="20">
+        <f>MIN(C12:Y12)</f>
         <v>465</v>
       </c>
-      <c r="Z12" s="21">
-        <f>MAX(C12:X12)</f>
+      <c r="AA12" s="21">
+        <f>MAX(C12:Y12)</f>
         <v>623.12</v>
       </c>
-      <c r="AA12" s="21">
-        <f>AVERAGE(C12:X12)</f>
-        <v>552.88105263157877</v>
-      </c>
       <c r="AB12" s="21">
-        <f>AVERAGE(Q12:X12)</f>
-        <v>541.47749999999996</v>
-      </c>
-      <c r="AC12" s="22">
-        <f>(AB12/AA12)-1</f>
-        <v>-2.0625688974691192e-002</v>
+        <f>AVERAGE(C12:Y12)</f>
+        <v>552.63599999999974</v>
+      </c>
+      <c r="AC12" s="21">
+        <f>AVERAGE(Q12:Y12)</f>
+        <v>542.19999999999993</v>
       </c>
       <c r="AD12" s="22">
-        <f>(AB12/Y12)-1</f>
-        <v>0.16446774193548386</v>
+        <f>(AC12/AB12)-1</f>
+        <v>-1.8884039403874953e-002</v>
       </c>
       <c r="AE12" s="22">
-        <f>(Z12/Y12)-1</f>
+        <f>(AC12/Z12)-1</f>
+        <v>0.16602150537634386</v>
+      </c>
+      <c r="AF12" s="22">
+        <f>(AA12/Z12)-1</f>
         <v>0.34004301075268817</v>
       </c>
-      <c r="AF12" s="23" t="s">
-        <v>53</v>
+      <c r="AG12" s="23" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="13" ht="36">
       <c r="A13" s="26" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C13" s="28"/>
       <c r="D13" s="25">
@@ -2125,19 +2152,19 @@
         <v>1084.8299999999999</v>
       </c>
       <c r="P13" s="17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q13" s="17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="R13" s="17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="S13" s="30">
         <v>1426.5699999999999</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="U13" s="25">
         <v>592.17999999999995</v>
@@ -2151,44 +2178,47 @@
       <c r="X13" s="25">
         <v>623.23000000000002</v>
       </c>
-      <c r="Y13" s="20">
-        <f>MIN(C13:X13)</f>
+      <c r="Y13" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z13" s="20">
+        <f>MIN(C13:Y13)</f>
         <v>592.17999999999995</v>
       </c>
-      <c r="Z13" s="21">
-        <f>MAX(C13:X13)</f>
+      <c r="AA13" s="21">
+        <f>MAX(C13:Y13)</f>
         <v>1426.5699999999999</v>
       </c>
-      <c r="AA13" s="21">
-        <f>AVERAGE(C13:X13)</f>
+      <c r="AB13" s="21">
+        <f>AVERAGE(C13:Y13)</f>
         <v>853.96466666666674</v>
       </c>
-      <c r="AB13" s="21">
-        <f>AVERAGE(Q13:X13)</f>
+      <c r="AC13" s="21">
+        <f>AVERAGE(Q13:Y13)</f>
         <v>771.42200000000003</v>
       </c>
-      <c r="AC13" s="22">
-        <f>(AB13/AA13)-1</f>
+      <c r="AD13" s="22">
+        <f>(AC13/AB13)-1</f>
         <v>-9.665817555293077e-002</v>
       </c>
-      <c r="AD13" s="22">
-        <f>(AB13/Y13)-1</f>
+      <c r="AE13" s="22">
+        <f>(AC13/Z13)-1</f>
         <v>0.30268161707588925</v>
       </c>
-      <c r="AE13" s="22">
-        <f>(Z13/Y13)-1</f>
+      <c r="AF13" s="22">
+        <f>(AA13/Z13)-1</f>
         <v>1.4090141511027054</v>
       </c>
-      <c r="AF13" s="23" t="s">
-        <v>56</v>
+      <c r="AG13" s="23" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="14" ht="18">
       <c r="A14" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
@@ -2242,44 +2272,47 @@
       <c r="X14" s="18">
         <v>599.99000000000001</v>
       </c>
-      <c r="Y14" s="20">
-        <f>MIN(C14:X14)</f>
+      <c r="Y14" s="18">
+        <v>678</v>
+      </c>
+      <c r="Z14" s="20">
+        <f>MIN(C14:Y14)</f>
         <v>580.98000000000002</v>
       </c>
-      <c r="Z14" s="21">
-        <f>MAX(C14:X14)</f>
+      <c r="AA14" s="21">
+        <f>MAX(C14:Y14)</f>
         <v>709.99000000000001</v>
       </c>
-      <c r="AA14" s="21">
-        <f>AVERAGE(C14:X14)</f>
-        <v>652.14933333333317</v>
-      </c>
       <c r="AB14" s="21">
-        <f>AVERAGE(Q14:X14)</f>
-        <v>676.74375000000009</v>
-      </c>
-      <c r="AC14" s="22">
-        <f>(AB14/AA14)-1</f>
-        <v>3.7712860244688784e-002</v>
+        <f>AVERAGE(C14:Y14)</f>
+        <v>653.76499999999987</v>
+      </c>
+      <c r="AC14" s="21">
+        <f>AVERAGE(Q14:Y14)</f>
+        <v>676.88333333333344</v>
       </c>
       <c r="AD14" s="22">
-        <f>(AB14/Y14)-1</f>
-        <v>0.16483140555612952</v>
+        <f>(AC14/AB14)-1</f>
+        <v>3.5361840008770073e-002</v>
       </c>
       <c r="AE14" s="22">
-        <f>(Z14/Y14)-1</f>
+        <f>(AC14/Z14)-1</f>
+        <v>0.16507166052761435</v>
+      </c>
+      <c r="AF14" s="22">
+        <f>(AA14/Z14)-1</f>
         <v>0.22205583668973117</v>
       </c>
-      <c r="AF14" s="23" t="s">
-        <v>58</v>
+      <c r="AG14" s="23" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="15" ht="18">
       <c r="A15" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C15" s="16"/>
       <c r="D15" s="16"/>
@@ -2333,44 +2366,47 @@
       <c r="X15" s="17">
         <v>679</v>
       </c>
-      <c r="Y15" s="20">
-        <f>MIN(C15:X15)</f>
+      <c r="Y15" s="17">
+        <v>679</v>
+      </c>
+      <c r="Z15" s="20">
+        <f>MIN(C15:Y15)</f>
         <v>622.63</v>
       </c>
-      <c r="Z15" s="21">
-        <f>MAX(C15:X15)</f>
+      <c r="AA15" s="21">
+        <f>MAX(C15:Y15)</f>
         <v>728.61000000000001</v>
       </c>
-      <c r="AA15" s="21">
-        <f>AVERAGE(C15:X15)</f>
-        <v>682.25133333333326</v>
-      </c>
       <c r="AB15" s="21">
-        <f>AVERAGE(Q15:X15)</f>
-        <v>696.11374999999998</v>
-      </c>
-      <c r="AC15" s="22">
-        <f>(AB15/AA15)-1</f>
-        <v>2.0318636240603594e-002</v>
+        <f>AVERAGE(C15:Y15)</f>
+        <v>682.04812499999991</v>
+      </c>
+      <c r="AC15" s="21">
+        <f>AVERAGE(Q15:Y15)</f>
+        <v>694.21222222222218</v>
       </c>
       <c r="AD15" s="22">
-        <f>(AB15/Y15)-1</f>
-        <v>0.11802153767084778</v>
+        <f>(AC15/AB15)-1</f>
+        <v>1.7834661186440837e-002</v>
       </c>
       <c r="AE15" s="22">
-        <f>(Z15/Y15)-1</f>
+        <f>(AC15/Z15)-1</f>
+        <v>0.11496751236243385</v>
+      </c>
+      <c r="AF15" s="22">
+        <f>(AA15/Z15)-1</f>
         <v>0.17021344940012528</v>
       </c>
-      <c r="AF15" s="23" t="s">
-        <v>60</v>
+      <c r="AG15" s="23" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="16" ht="18">
       <c r="A16" s="26" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C16" s="28"/>
       <c r="D16" s="29"/>
@@ -2430,44 +2466,47 @@
       <c r="X16" s="17">
         <v>10790.610000000001</v>
       </c>
-      <c r="Y16" s="20">
-        <f>MIN(C16:X16)</f>
+      <c r="Y16" s="17">
+        <v>10799.02</v>
+      </c>
+      <c r="Z16" s="20">
+        <f>MIN(C16:Y16)</f>
         <v>9100</v>
       </c>
-      <c r="Z16" s="21">
-        <f>MAX(C16:X16)</f>
+      <c r="AA16" s="21">
+        <f>MAX(C16:Y16)</f>
         <v>11315.18</v>
       </c>
-      <c r="AA16" s="21">
-        <f>AVERAGE(C16:X16)</f>
-        <v>9790.8549999999977</v>
-      </c>
       <c r="AB16" s="21">
-        <f>AVERAGE(Q16:X16)</f>
-        <v>10605.793750000001</v>
-      </c>
-      <c r="AC16" s="22">
-        <f>(AB16/AA16)-1</f>
-        <v>8.3234686858298268e-002</v>
+        <f>AVERAGE(C16:Y16)</f>
+        <v>9843.9163157894709</v>
+      </c>
+      <c r="AC16" s="21">
+        <f>AVERAGE(Q16:Y16)</f>
+        <v>10627.263333333334</v>
       </c>
       <c r="AD16" s="22">
-        <f>(AB16/Y16)-1</f>
-        <v>0.16547184065934073</v>
+        <f>(AC16/AB16)-1</f>
+        <v>7.9576765223754231e-002</v>
       </c>
       <c r="AE16" s="22">
-        <f>(Z16/Y16)-1</f>
+        <f>(AC16/Z16)-1</f>
+        <v>0.16783113553113571</v>
+      </c>
+      <c r="AF16" s="22">
+        <f>(AA16/Z16)-1</f>
         <v>0.24342637362637376</v>
       </c>
-      <c r="AF16" s="23" t="s">
-        <v>62</v>
+      <c r="AG16" s="23" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="17" ht="36">
       <c r="A17" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C17" s="16"/>
       <c r="D17" s="16"/>
@@ -2519,44 +2558,47 @@
       <c r="X17" s="18">
         <v>1610.8900000000001</v>
       </c>
-      <c r="Y17" s="20">
-        <f>MIN(C17:X17)</f>
+      <c r="Y17" s="18">
+        <v>1610.8900000000001</v>
+      </c>
+      <c r="Z17" s="20">
+        <f>MIN(C17:Y17)</f>
         <v>1297.6199999999999</v>
       </c>
-      <c r="Z17" s="21">
-        <f>MAX(C17:X17)</f>
+      <c r="AA17" s="21">
+        <f>MAX(C17:Y17)</f>
         <v>1697.6199999999999</v>
       </c>
-      <c r="AA17" s="21">
-        <f>AVERAGE(C17:X17)</f>
-        <v>1533.5599999999997</v>
-      </c>
       <c r="AB17" s="21">
-        <f>AVERAGE(Q17:X17)</f>
-        <v>1581.4137499999999</v>
-      </c>
-      <c r="AC17" s="22">
-        <f>(AB17/AA17)-1</f>
-        <v>3.1204354573671766e-002</v>
+        <f>AVERAGE(C17:Y17)</f>
+        <v>1538.7153333333331</v>
+      </c>
+      <c r="AC17" s="21">
+        <f>AVERAGE(Q17:Y17)</f>
+        <v>1584.6888888888889</v>
       </c>
       <c r="AD17" s="22">
-        <f>(AB17/Y17)-1</f>
-        <v>0.21870327985080373</v>
+        <f>(AC17/AB17)-1</f>
+        <v>2.9877882256468258e-002</v>
       </c>
       <c r="AE17" s="22">
-        <f>(Z17/Y17)-1</f>
+        <f>(AC17/Z17)-1</f>
+        <v>0.22122723824300561</v>
+      </c>
+      <c r="AF17" s="22">
+        <f>(AA17/Z17)-1</f>
         <v>0.30825665449052875</v>
       </c>
-      <c r="AF17" s="23" t="s">
-        <v>64</v>
+      <c r="AG17" s="23" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="18" ht="18">
       <c r="A18" s="26" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C18" s="28"/>
       <c r="D18" s="29"/>
@@ -2565,97 +2607,100 @@
         <v>2279</v>
       </c>
       <c r="G18" s="29" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H18" s="29" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I18" s="29" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J18" s="29" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L18" s="29" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="M18" s="29" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N18" s="29" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="O18" s="29" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="P18" s="17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Q18" s="17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="R18" s="17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="S18" s="17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="V18" s="17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="W18" s="17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="X18" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="Y18" s="20">
-        <f>MIN(C18:X18)</f>
+        <v>67</v>
+      </c>
+      <c r="Y18" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z18" s="20">
+        <f>MIN(C18:Y18)</f>
         <v>2279</v>
       </c>
-      <c r="Z18" s="21">
-        <f>MAX(C18:X18)</f>
+      <c r="AA18" s="21">
+        <f>MAX(C18:Y18)</f>
         <v>2279</v>
       </c>
-      <c r="AA18" s="21">
-        <f>AVERAGE(C18:X18)</f>
+      <c r="AB18" s="21">
+        <f>AVERAGE(C18:Y18)</f>
         <v>2279</v>
       </c>
-      <c r="AB18" s="21" t="e">
-        <f>AVERAGE(Q18:X18)</f>
+      <c r="AC18" s="21" t="e">
+        <f>AVERAGE(Q18:Y18)</f>
         <v>#NUM!</v>
       </c>
-      <c r="AC18" s="22" t="e">
-        <f>(AB18/AA18)-1</f>
+      <c r="AD18" s="22" t="e">
+        <f>(AC18/AB18)-1</f>
         <v>#NUM!</v>
       </c>
-      <c r="AD18" s="22" t="e">
-        <f>(AB18/Y18)-1</f>
+      <c r="AE18" s="22" t="e">
+        <f>(AC18/Z18)-1</f>
         <v>#NUM!</v>
       </c>
-      <c r="AE18" s="22">
-        <f>(Z18/Y18)-1</f>
+      <c r="AF18" s="22">
+        <f>(AA18/Z18)-1</f>
         <v>0</v>
       </c>
-      <c r="AF18" s="23" t="s">
-        <v>67</v>
+      <c r="AG18" s="23" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="19" ht="18">
       <c r="A19" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C19" s="25">
         <v>176.69</v>
@@ -2717,44 +2762,47 @@
       <c r="X19" s="30">
         <v>228</v>
       </c>
-      <c r="Y19" s="20">
-        <f>MIN(C19:X19)</f>
+      <c r="Y19" s="30">
+        <v>260</v>
+      </c>
+      <c r="Z19" s="20">
+        <f>MIN(C19:Y19)</f>
         <v>145</v>
       </c>
-      <c r="Z19" s="21">
-        <f>MAX(C19:X19)</f>
-        <v>237.69999999999999</v>
-      </c>
       <c r="AA19" s="21">
-        <f>AVERAGE(C19:X19)</f>
-        <v>197.83842105263156</v>
+        <f>MAX(C19:Y19)</f>
+        <v>260</v>
       </c>
       <c r="AB19" s="21">
-        <f>AVERAGE(Q19:X19)</f>
-        <v>234.0625</v>
-      </c>
-      <c r="AC19" s="22">
-        <f>(AB19/AA19)-1</f>
-        <v>0.18309931283636582</v>
+        <f>AVERAGE(C19:Y19)</f>
+        <v>200.94649999999996</v>
+      </c>
+      <c r="AC19" s="21">
+        <f>AVERAGE(Q19:Y19)</f>
+        <v>236.94444444444446</v>
       </c>
       <c r="AD19" s="22">
-        <f>(AB19/Y19)-1</f>
-        <v>0.61422413793103448</v>
+        <f>(AC19/AB19)-1</f>
+        <v>0.17914193302418568</v>
       </c>
       <c r="AE19" s="22">
-        <f>(Z19/Y19)-1</f>
-        <v>0.63931034482758609</v>
-      </c>
-      <c r="AF19" s="23" t="s">
-        <v>69</v>
+        <f>(AC19/Z19)-1</f>
+        <v>0.63409961685823757</v>
+      </c>
+      <c r="AF19" s="22">
+        <f>(AA19/Z19)-1</f>
+        <v>0.7931034482758621</v>
+      </c>
+      <c r="AG19" s="23" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="20" ht="18">
       <c r="A20" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C20" s="17"/>
       <c r="D20" s="17"/>
@@ -2803,55 +2851,58 @@
         <v>212.31</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="V20" s="17">
+        <v>44</v>
+      </c>
+      <c r="V20" s="19">
         <v>229.94999999999999</v>
       </c>
-      <c r="W20" s="17">
+      <c r="W20" s="19">
         <v>229.94</v>
       </c>
-      <c r="X20" s="17">
+      <c r="X20" s="19">
         <v>230</v>
       </c>
-      <c r="Y20" s="20">
-        <f>MIN(C20:X20)</f>
+      <c r="Y20" s="30">
+        <v>270</v>
+      </c>
+      <c r="Z20" s="20">
+        <f>MIN(C20:Y20)</f>
         <v>176.91999999999999</v>
       </c>
-      <c r="Z20" s="21">
-        <f>MAX(C20:X20)</f>
-        <v>230</v>
-      </c>
       <c r="AA20" s="21">
-        <f>AVERAGE(C20:X20)</f>
-        <v>195.92764705882354</v>
+        <f>MAX(C20:Y20)</f>
+        <v>270</v>
       </c>
       <c r="AB20" s="21">
-        <f>AVERAGE(Q20:X20)</f>
-        <v>218.17000000000002</v>
-      </c>
-      <c r="AC20" s="22">
-        <f>(AB20/AA20)-1</f>
-        <v>0.11352329941725192</v>
+        <f>AVERAGE(C20:Y20)</f>
+        <v>200.04277777777779</v>
+      </c>
+      <c r="AC20" s="21">
+        <f>AVERAGE(Q20:Y20)</f>
+        <v>224.64875000000001</v>
       </c>
       <c r="AD20" s="22">
-        <f>(AB20/Y20)-1</f>
-        <v>0.23315622880397946</v>
+        <f>(AC20/AB20)-1</f>
+        <v>0.12300355201804059</v>
       </c>
       <c r="AE20" s="22">
-        <f>(Z20/Y20)-1</f>
-        <v>0.30002260908885381</v>
-      </c>
-      <c r="AF20" s="23" t="s">
-        <v>71</v>
+        <f>(AC20/Z20)-1</f>
+        <v>0.26977588740673775</v>
+      </c>
+      <c r="AF20" s="22">
+        <f>(AA20/Z20)-1</f>
+        <v>0.52611349762604576</v>
+      </c>
+      <c r="AG20" s="23" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="21" ht="18">
       <c r="A21" s="26" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C21" s="29"/>
       <c r="D21" s="29"/>
@@ -2864,31 +2915,31 @@
         <v>396.77999999999997</v>
       </c>
       <c r="I21" s="29" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J21" s="29" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K21" s="29" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L21" s="29" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M21" s="29" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N21" s="29" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="O21" s="29" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="P21" s="17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="Q21" s="17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="R21" s="17">
         <v>413</v>
@@ -2900,7 +2951,7 @@
         <v>408.87</v>
       </c>
       <c r="U21" s="17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="V21" s="17">
         <v>453.04000000000002</v>
@@ -2911,44 +2962,47 @@
       <c r="X21" s="17">
         <v>349</v>
       </c>
-      <c r="Y21" s="20">
-        <f>MIN(C21:X21)</f>
+      <c r="Y21" s="17">
         <v>349</v>
       </c>
-      <c r="Z21" s="21">
-        <f>MAX(C21:X21)</f>
+      <c r="Z21" s="20">
+        <f>MIN(C21:Y21)</f>
+        <v>349</v>
+      </c>
+      <c r="AA21" s="21">
+        <f>MAX(C21:Y21)</f>
         <v>453.04000000000002</v>
       </c>
-      <c r="AA21" s="21">
-        <f>AVERAGE(C21:X21)</f>
-        <v>415.44124999999997</v>
-      </c>
       <c r="AB21" s="21">
-        <f>AVERAGE(Q21:X21)</f>
-        <v>421.66166666666663</v>
-      </c>
-      <c r="AC21" s="22">
-        <f>(AB21/AA21)-1</f>
-        <v>1.4973035697987802e-002</v>
+        <f>AVERAGE(C21:Y21)</f>
+        <v>408.05888888888887</v>
+      </c>
+      <c r="AC21" s="21">
+        <f>AVERAGE(Q21:Y21)</f>
+        <v>411.28142857142853</v>
       </c>
       <c r="AD21" s="22">
-        <f>(AB21/Y21)-1</f>
-        <v>0.20819961795606479</v>
+        <f>(AC21/AB21)-1</f>
+        <v>7.8972417224247859e-003</v>
       </c>
       <c r="AE21" s="22">
-        <f>(Z21/Y21)-1</f>
+        <f>(AC21/Z21)-1</f>
+        <v>0.17845681539091274</v>
+      </c>
+      <c r="AF21" s="22">
+        <f>(AA21/Z21)-1</f>
         <v>0.29810888252148993</v>
       </c>
-      <c r="AF21" s="32" t="s">
-        <v>73</v>
+      <c r="AG21" s="32" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="22" ht="54">
       <c r="A22" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C22" s="17"/>
       <c r="D22" s="17"/>
@@ -3008,44 +3062,47 @@
       <c r="X22" s="17">
         <v>600</v>
       </c>
-      <c r="Y22" s="20">
-        <f>MIN(C22:X22)</f>
+      <c r="Y22" s="17">
+        <v>600</v>
+      </c>
+      <c r="Z22" s="20">
+        <f>MIN(C22:Y22)</f>
         <v>550</v>
       </c>
-      <c r="Z22" s="21">
-        <f>MAX(C22:X22)</f>
+      <c r="AA22" s="21">
+        <f>MAX(C22:Y22)</f>
         <v>600</v>
       </c>
-      <c r="AA22" s="21">
-        <f>AVERAGE(C22:X22)</f>
-        <v>571.11111111111109</v>
-      </c>
       <c r="AB22" s="21">
-        <f>AVERAGE(Q22:X22)</f>
-        <v>597.5</v>
-      </c>
-      <c r="AC22" s="22">
-        <f>(AB22/AA22)-1</f>
-        <v>4.620622568093391e-002</v>
+        <f>AVERAGE(C22:Y22)</f>
+        <v>572.63157894736844</v>
+      </c>
+      <c r="AC22" s="21">
+        <f>AVERAGE(Q22:Y22)</f>
+        <v>597.77777777777783</v>
       </c>
       <c r="AD22" s="22">
-        <f>(AB22/Y22)-1</f>
-        <v>8.636363636363642e-002</v>
+        <f>(AC22/AB22)-1</f>
+        <v>4.3913398692810413e-002</v>
       </c>
       <c r="AE22" s="22">
-        <f>(Z22/Y22)-1</f>
+        <f>(AC22/Z22)-1</f>
+        <v>8.6868686868686984e-002</v>
+      </c>
+      <c r="AF22" s="22">
+        <f>(AA22/Z22)-1</f>
         <v>9.0909090909090828e-002</v>
       </c>
-      <c r="AF22" s="23" t="s">
-        <v>76</v>
+      <c r="AG22" s="23" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="23" ht="18">
       <c r="A23" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C23" s="17"/>
       <c r="D23" s="17"/>
@@ -3105,44 +3162,47 @@
       <c r="X23" s="19">
         <v>549</v>
       </c>
-      <c r="Y23" s="20">
-        <f>MIN(C23:X23)</f>
+      <c r="Y23" s="19">
+        <v>549</v>
+      </c>
+      <c r="Z23" s="20">
+        <f>MIN(C23:Y23)</f>
         <v>329</v>
       </c>
-      <c r="Z23" s="21">
-        <f>MAX(C23:X23)</f>
+      <c r="AA23" s="21">
+        <f>MAX(C23:Y23)</f>
         <v>549</v>
       </c>
-      <c r="AA23" s="21">
-        <f>AVERAGE(C23:X23)</f>
-        <v>479.48611111111109</v>
-      </c>
       <c r="AB23" s="21">
-        <f>AVERAGE(Q23:X23)</f>
-        <v>524.48125000000005</v>
-      </c>
-      <c r="AC23" s="22">
-        <f>(AB23/AA23)-1</f>
-        <v>9.3840338325174688e-002</v>
+        <f>AVERAGE(C23:Y23)</f>
+        <v>483.14473684210526</v>
+      </c>
+      <c r="AC23" s="21">
+        <f>AVERAGE(Q23:Y23)</f>
+        <v>527.20555555555563</v>
       </c>
       <c r="AD23" s="22">
-        <f>(AB23/Y23)-1</f>
-        <v>0.59416793313069927</v>
+        <f>(AC23/AB23)-1</f>
+        <v>9.1195899186313101e-002</v>
       </c>
       <c r="AE23" s="22">
-        <f>(Z23/Y23)-1</f>
+        <f>(AC23/Z23)-1</f>
+        <v>0.60244849712934845</v>
+      </c>
+      <c r="AF23" s="22">
+        <f>(AA23/Z23)-1</f>
         <v>0.66869300911854102</v>
       </c>
-      <c r="AF23" s="23" t="s">
-        <v>79</v>
+      <c r="AG23" s="23" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="24" ht="18">
       <c r="A24" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C24" s="17"/>
       <c r="D24" s="17"/>
@@ -3202,44 +3262,47 @@
       <c r="X24" s="18">
         <v>435.14999999999998</v>
       </c>
-      <c r="Y24" s="20">
-        <f>MIN(C24:X24)</f>
+      <c r="Y24" s="18">
+        <v>472.97000000000003</v>
+      </c>
+      <c r="Z24" s="20">
+        <f>MIN(C24:Y24)</f>
         <v>371.14999999999998</v>
       </c>
-      <c r="Z24" s="21">
-        <f>MAX(C24:X24)</f>
+      <c r="AA24" s="21">
+        <f>MAX(C24:Y24)</f>
         <v>513.71000000000004</v>
       </c>
-      <c r="AA24" s="21">
-        <f>AVERAGE(C24:X24)</f>
-        <v>445.33833333333325</v>
-      </c>
       <c r="AB24" s="21">
-        <f>AVERAGE(Q24:X24)</f>
-        <v>474.67125000000004</v>
-      </c>
-      <c r="AC24" s="22">
-        <f>(AB24/AA24)-1</f>
-        <v>6.5866588324233089e-002</v>
+        <f>AVERAGE(C24:Y24)</f>
+        <v>446.79263157894724</v>
+      </c>
+      <c r="AC24" s="21">
+        <f>AVERAGE(Q24:Y24)</f>
+        <v>474.48222222222222</v>
       </c>
       <c r="AD24" s="22">
-        <f>(AB24/Y24)-1</f>
-        <v>0.27892024787821645</v>
+        <f>(AC24/AB24)-1</f>
+        <v>6.1974143453129571e-002</v>
       </c>
       <c r="AE24" s="22">
-        <f>(Z24/Y24)-1</f>
+        <f>(AC24/Z24)-1</f>
+        <v>0.27841094496085739</v>
+      </c>
+      <c r="AF24" s="22">
+        <f>(AA24/Z24)-1</f>
         <v>0.38410346221204383</v>
       </c>
-      <c r="AF24" s="23" t="s">
-        <v>81</v>
+      <c r="AG24" s="23" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="25" ht="36">
       <c r="A25" s="26" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C25" s="29"/>
       <c r="D25" s="29"/>
@@ -3303,44 +3366,47 @@
       <c r="X25" s="33">
         <v>587.11000000000001</v>
       </c>
-      <c r="Y25" s="20">
-        <f>MIN(C25:X25)</f>
+      <c r="Y25" s="30">
+        <v>619.59000000000003</v>
+      </c>
+      <c r="Z25" s="20">
+        <f>MIN(C25:Y25)</f>
         <v>396</v>
       </c>
-      <c r="Z25" s="21">
-        <f>MAX(C25:X25)</f>
-        <v>609.25</v>
-      </c>
       <c r="AA25" s="21">
-        <f>AVERAGE(C25:X25)</f>
-        <v>527.87200000000007</v>
+        <f>MAX(C25:Y25)</f>
+        <v>619.59000000000003</v>
       </c>
       <c r="AB25" s="21">
-        <f>AVERAGE(Q25:X25)</f>
-        <v>563.58624999999995</v>
-      </c>
-      <c r="AC25" s="22">
-        <f>(AB25/AA25)-1</f>
-        <v>6.7657026703443091e-002</v>
+        <f>AVERAGE(C25:Y25)</f>
+        <v>532.2395238095238</v>
+      </c>
+      <c r="AC25" s="21">
+        <f>AVERAGE(Q25:Y25)</f>
+        <v>569.80888888888887</v>
       </c>
       <c r="AD25" s="22">
-        <f>(AB25/Y25)-1</f>
-        <v>0.42319760101010084</v>
+        <f>(AC25/AB25)-1</f>
+        <v>7.0587326567671971e-002</v>
       </c>
       <c r="AE25" s="22">
-        <f>(Z25/Y25)-1</f>
-        <v>0.53851010101010099</v>
-      </c>
-      <c r="AF25" s="23" t="s">
-        <v>84</v>
+        <f>(AC25/Z25)-1</f>
+        <v>0.4389113355780021</v>
+      </c>
+      <c r="AF25" s="22">
+        <f>(AA25/Z25)-1</f>
+        <v>0.56462121212121219</v>
+      </c>
+      <c r="AG25" s="23" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="26" ht="18">
       <c r="A26" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C26" s="17"/>
       <c r="D26" s="25">
@@ -3402,44 +3468,47 @@
       <c r="X26" s="30">
         <v>1565.48</v>
       </c>
-      <c r="Y26" s="20">
-        <f>MIN(C26:X26)</f>
+      <c r="Y26" s="30">
+        <v>1592.45</v>
+      </c>
+      <c r="Z26" s="20">
+        <f>MIN(C26:Y26)</f>
         <v>370</v>
       </c>
-      <c r="Z26" s="21">
-        <f>MAX(C26:X26)</f>
+      <c r="AA26" s="21">
+        <f>MAX(C26:Y26)</f>
         <v>1678.0799999999999</v>
       </c>
-      <c r="AA26" s="21">
-        <f>AVERAGE(C26:X26)</f>
-        <v>1147.1789473684209</v>
-      </c>
       <c r="AB26" s="21">
-        <f>AVERAGE(Q26:X26)</f>
-        <v>1305.4962499999999</v>
-      </c>
-      <c r="AC26" s="22">
-        <f>(AB26/AA26)-1</f>
-        <v>0.13800576012552535</v>
+        <f>AVERAGE(C26:Y26)</f>
+        <v>1169.4424999999999</v>
+      </c>
+      <c r="AC26" s="21">
+        <f>AVERAGE(Q26:Y26)</f>
+        <v>1337.3800000000001</v>
       </c>
       <c r="AD26" s="22">
-        <f>(AB26/Y26)-1</f>
-        <v>2.5283682432432428</v>
+        <f>(AC26/AB26)-1</f>
+        <v>0.14360475183687971</v>
       </c>
       <c r="AE26" s="22">
-        <f>(Z26/Y26)-1</f>
+        <f>(AC26/Z26)-1</f>
+        <v>2.6145405405405406</v>
+      </c>
+      <c r="AF26" s="22">
+        <f>(AA26/Z26)-1</f>
         <v>3.535351351351351</v>
       </c>
-      <c r="AF26" s="23" t="s">
-        <v>86</v>
+      <c r="AG26" s="23" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="27" ht="18">
       <c r="A27" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C27" s="17"/>
       <c r="D27" s="17"/>
@@ -3491,44 +3560,47 @@
       <c r="X27" s="19">
         <v>164.99000000000001</v>
       </c>
-      <c r="Y27" s="20">
-        <f>MIN(C27:X27)</f>
+      <c r="Y27" s="19">
+        <v>166.99000000000001</v>
+      </c>
+      <c r="Z27" s="20">
+        <f>MIN(C27:Y27)</f>
         <v>109.98999999999999</v>
       </c>
-      <c r="Z27" s="21">
-        <f>MAX(C27:X27)</f>
-        <v>165.72999999999999</v>
-      </c>
       <c r="AA27" s="21">
-        <f>AVERAGE(C27:X27)</f>
-        <v>146.47142857142859</v>
+        <f>MAX(C27:Y27)</f>
+        <v>166.99000000000001</v>
       </c>
       <c r="AB27" s="21">
-        <f>AVERAGE(Q27:X27)</f>
-        <v>158.11500000000001</v>
-      </c>
-      <c r="AC27" s="22">
-        <f>(AB27/AA27)-1</f>
-        <v>7.94938066907247e-002</v>
+        <f>AVERAGE(C27:Y27)</f>
+        <v>147.83933333333334</v>
+      </c>
+      <c r="AC27" s="21">
+        <f>AVERAGE(Q27:Y27)</f>
+        <v>159.10111111111112</v>
       </c>
       <c r="AD27" s="22">
-        <f>(AB27/Y27)-1</f>
-        <v>0.43753977634330399</v>
+        <f>(AC27/AB27)-1</f>
+        <v>7.6175788430984381e-002</v>
       </c>
       <c r="AE27" s="22">
-        <f>(Z27/Y27)-1</f>
-        <v>0.50677334303118471</v>
-      </c>
-      <c r="AF27" s="23" t="s">
-        <v>88</v>
+        <f>(AC27/Z27)-1</f>
+        <v>0.4465052378499057</v>
+      </c>
+      <c r="AF27" s="22">
+        <f>(AA27/Z27)-1</f>
+        <v>0.51822892990271852</v>
+      </c>
+      <c r="AG27" s="23" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="28" ht="18">
       <c r="A28" s="26" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B28" s="27" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C28" s="29"/>
       <c r="D28" s="29"/>
@@ -3580,44 +3652,47 @@
       <c r="X28" s="18">
         <v>82.890000000000001</v>
       </c>
-      <c r="Y28" s="20">
-        <f>MIN(C28:X28)</f>
+      <c r="Y28" s="18">
+        <v>81.480000000000004</v>
+      </c>
+      <c r="Z28" s="20">
+        <f>MIN(C28:Y28)</f>
         <v>68</v>
       </c>
-      <c r="Z28" s="21">
-        <f>MAX(C28:X28)</f>
+      <c r="AA28" s="21">
+        <f>MAX(C28:Y28)</f>
         <v>85.700000000000003</v>
       </c>
-      <c r="AA28" s="21">
-        <f>AVERAGE(C28:X28)</f>
-        <v>78.622142857142862</v>
-      </c>
       <c r="AB28" s="21">
-        <f>AVERAGE(Q28:X28)</f>
-        <v>82.238749999999996</v>
-      </c>
-      <c r="AC28" s="22">
-        <f>(AB28/AA28)-1</f>
-        <v>4.5999854639278137e-002</v>
+        <f>AVERAGE(C28:Y28)</f>
+        <v>78.812666666666672</v>
+      </c>
+      <c r="AC28" s="21">
+        <f>AVERAGE(Q28:Y28)</f>
+        <v>82.154444444444437</v>
       </c>
       <c r="AD28" s="22">
-        <f>(AB28/Y28)-1</f>
-        <v>0.20939338235294103</v>
+        <f>(AC28/AB28)-1</f>
+        <v>4.240153162069249e-002</v>
       </c>
       <c r="AE28" s="22">
-        <f>(Z28/Y28)-1</f>
+        <f>(AC28/Z28)-1</f>
+        <v>0.20815359477124162</v>
+      </c>
+      <c r="AF28" s="22">
+        <f>(AA28/Z28)-1</f>
         <v>0.26029411764705879</v>
       </c>
-      <c r="AF28" s="23" t="s">
-        <v>90</v>
+      <c r="AG28" s="23" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="29" ht="18">
       <c r="A29" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C29" s="17"/>
       <c r="D29" s="17"/>
@@ -3669,44 +3744,47 @@
       <c r="X29" s="30">
         <v>107</v>
       </c>
-      <c r="Y29" s="20">
-        <f>MIN(C29:X29)</f>
+      <c r="Y29" s="33">
+        <v>99.900000000000006</v>
+      </c>
+      <c r="Z29" s="20">
+        <f>MIN(C29:Y29)</f>
         <v>55</v>
       </c>
-      <c r="Z29" s="21">
-        <f>MAX(C29:X29)</f>
+      <c r="AA29" s="21">
+        <f>MAX(C29:Y29)</f>
         <v>111</v>
       </c>
-      <c r="AA29" s="21">
-        <f>AVERAGE(C29:X29)</f>
-        <v>84.938571428571436</v>
-      </c>
       <c r="AB29" s="21">
-        <f>AVERAGE(Q29:X29)</f>
-        <v>94.922499999999999</v>
-      </c>
-      <c r="AC29" s="22">
-        <f>(AB29/AA29)-1</f>
-        <v>0.11754293018483941</v>
+        <f>AVERAGE(C29:Y29)</f>
+        <v>85.936000000000007</v>
+      </c>
+      <c r="AC29" s="21">
+        <f>AVERAGE(Q29:Y29)</f>
+        <v>95.475555555555559</v>
       </c>
       <c r="AD29" s="22">
-        <f>(AB29/Y29)-1</f>
-        <v>0.72586363636363638</v>
+        <f>(AC29/AB29)-1</f>
+        <v>0.11100767496224573</v>
       </c>
       <c r="AE29" s="22">
-        <f>(Z29/Y29)-1</f>
+        <f>(AC29/Z29)-1</f>
+        <v>0.73591919191919208</v>
+      </c>
+      <c r="AF29" s="22">
+        <f>(AA29/Z29)-1</f>
         <v>1.0181818181818181</v>
       </c>
-      <c r="AF29" s="23" t="s">
-        <v>92</v>
+      <c r="AG29" s="23" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="30" ht="18">
       <c r="A30" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
@@ -3756,44 +3834,47 @@
       <c r="X30" s="18">
         <v>86.700000000000003</v>
       </c>
-      <c r="Y30" s="20">
-        <f>MIN(C30:X30)</f>
+      <c r="Y30" s="18">
+        <v>89.700000000000003</v>
+      </c>
+      <c r="Z30" s="20">
+        <f>MIN(C30:Y30)</f>
         <v>47.359999999999999</v>
       </c>
-      <c r="Z30" s="21">
-        <f>MAX(C30:X30)</f>
+      <c r="AA30" s="21">
+        <f>MAX(C30:Y30)</f>
         <v>100.68000000000001</v>
       </c>
-      <c r="AA30" s="21">
-        <f>AVERAGE(C30:X30)</f>
-        <v>73.577692307692317</v>
-      </c>
       <c r="AB30" s="21">
-        <f>AVERAGE(Q30:X30)</f>
-        <v>85.507500000000022</v>
-      </c>
-      <c r="AC30" s="22">
-        <f>(AB30/AA30)-1</f>
-        <v>0.16213892170494826</v>
+        <f>AVERAGE(C30:Y30)</f>
+        <v>74.729285714285723</v>
+      </c>
+      <c r="AC30" s="21">
+        <f>AVERAGE(Q30:Y30)</f>
+        <v>85.973333333333358</v>
       </c>
       <c r="AD30" s="22">
-        <f>(AB30/Y30)-1</f>
-        <v>0.8054793074324329</v>
+        <f>(AC30/AB30)-1</f>
+        <v>0.15046373736311724</v>
       </c>
       <c r="AE30" s="22">
-        <f>(Z30/Y30)-1</f>
+        <f>(AC30/Z30)-1</f>
+        <v>0.81531531531531587</v>
+      </c>
+      <c r="AF30" s="22">
+        <f>(AA30/Z30)-1</f>
         <v>1.1258445945945947</v>
       </c>
-      <c r="AF30" s="23" t="s">
-        <v>94</v>
+      <c r="AG30" s="23" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="31" ht="18">
       <c r="A31" s="26" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C31" s="29"/>
       <c r="D31" s="29"/>
@@ -3829,7 +3910,7 @@
         <v>132.33000000000001</v>
       </c>
       <c r="T31" s="17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="U31" s="18">
         <v>156</v>
@@ -3843,44 +3924,47 @@
       <c r="X31" s="18">
         <v>156</v>
       </c>
-      <c r="Y31" s="20">
-        <f>MIN(C31:X31)</f>
+      <c r="Y31" s="18">
+        <v>151.22</v>
+      </c>
+      <c r="Z31" s="20">
+        <f>MIN(C31:Y31)</f>
         <v>92.5</v>
       </c>
-      <c r="Z31" s="21">
-        <f>MAX(C31:X31)</f>
+      <c r="AA31" s="21">
+        <f>MAX(C31:Y31)</f>
         <v>156</v>
       </c>
-      <c r="AA31" s="21">
-        <f>AVERAGE(C31:X31)</f>
-        <v>125.72333333333336</v>
-      </c>
       <c r="AB31" s="21">
-        <f>AVERAGE(Q31:X31)</f>
-        <v>139.88428571428571</v>
-      </c>
-      <c r="AC31" s="22">
-        <f>(AB31/AA31)-1</f>
-        <v>0.11263583302716818</v>
+        <f>AVERAGE(C31:Y31)</f>
+        <v>127.68461538461541</v>
+      </c>
+      <c r="AC31" s="21">
+        <f>AVERAGE(Q31:Y31)</f>
+        <v>141.30125000000001</v>
       </c>
       <c r="AD31" s="22">
-        <f>(AB31/Y31)-1</f>
-        <v>0.51226254826254825</v>
+        <f>(AC31/AB31)-1</f>
+        <v>0.10664271944093007</v>
       </c>
       <c r="AE31" s="22">
-        <f>(Z31/Y31)-1</f>
+        <f>(AC31/Z31)-1</f>
+        <v>0.52758108108108126</v>
+      </c>
+      <c r="AF31" s="22">
+        <f>(AA31/Z31)-1</f>
         <v>0.68648648648648658</v>
       </c>
-      <c r="AF31" s="23" t="s">
-        <v>96</v>
+      <c r="AG31" s="23" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="32" ht="18">
       <c r="A32" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C32" s="17"/>
       <c r="D32" s="17"/>
@@ -3928,44 +4012,47 @@
       <c r="X32" s="18">
         <v>238.24000000000001</v>
       </c>
-      <c r="Y32" s="20">
-        <f>MIN(C32:X32)</f>
+      <c r="Y32" s="18">
+        <v>221.25</v>
+      </c>
+      <c r="Z32" s="20">
+        <f>MIN(C32:Y32)</f>
         <v>148.88</v>
       </c>
-      <c r="Z32" s="21">
-        <f>MAX(C32:X32)</f>
+      <c r="AA32" s="21">
+        <f>MAX(C32:Y32)</f>
         <v>257.87</v>
       </c>
-      <c r="AA32" s="21">
-        <f>AVERAGE(C32:X32)</f>
-        <v>222.04750000000004</v>
-      </c>
       <c r="AB32" s="21">
-        <f>AVERAGE(Q32:X32)</f>
-        <v>235.43625000000003</v>
-      </c>
-      <c r="AC32" s="22">
-        <f>(AB32/AA32)-1</f>
-        <v>6.0296783345905602e-002</v>
+        <f>AVERAGE(C32:Y32)</f>
+        <v>221.98615384615388</v>
+      </c>
+      <c r="AC32" s="21">
+        <f>AVERAGE(Q32:Y32)</f>
+        <v>233.86000000000001</v>
       </c>
       <c r="AD32" s="22">
-        <f>(AB32/Y32)-1</f>
-        <v>0.58138265717356274</v>
+        <f>(AC32/AB32)-1</f>
+        <v>5.3489129606143049e-002</v>
       </c>
       <c r="AE32" s="22">
-        <f>(Z32/Y32)-1</f>
+        <f>(AC32/Z32)-1</f>
+        <v>0.57079527135948438</v>
+      </c>
+      <c r="AF32" s="22">
+        <f>(AA32/Z32)-1</f>
         <v>0.73206609349811935</v>
       </c>
-      <c r="AF32" s="23" t="s">
-        <v>98</v>
+      <c r="AG32" s="23" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="33" ht="18">
       <c r="A33" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C33" s="17"/>
       <c r="D33" s="17"/>
@@ -4009,44 +4096,47 @@
       <c r="X33" s="18">
         <v>164.38999999999999</v>
       </c>
-      <c r="Y33" s="20">
-        <f>MIN(C33:X33)</f>
+      <c r="Y33" s="18">
+        <v>168.28999999999999</v>
+      </c>
+      <c r="Z33" s="20">
+        <f>MIN(C33:Y33)</f>
         <v>144.94999999999999</v>
       </c>
-      <c r="Z33" s="21">
-        <f>MAX(C33:X33)</f>
-        <v>164.93000000000001</v>
-      </c>
       <c r="AA33" s="21">
-        <f>AVERAGE(C33:X33)</f>
-        <v>155.58200000000002</v>
+        <f>MAX(C33:Y33)</f>
+        <v>168.28999999999999</v>
       </c>
       <c r="AB33" s="21">
-        <f>AVERAGE(Q33:X33)</f>
-        <v>155.92250000000001</v>
-      </c>
-      <c r="AC33" s="22">
-        <f>(AB33/AA33)-1</f>
-        <v>2.1885565168207055e-003</v>
+        <f>AVERAGE(C33:Y33)</f>
+        <v>156.73727272727274</v>
+      </c>
+      <c r="AC33" s="21">
+        <f>AVERAGE(Q33:Y33)</f>
+        <v>157.29666666666668</v>
       </c>
       <c r="AD33" s="22">
-        <f>(AB33/Y33)-1</f>
-        <v>7.5698516729907128e-002</v>
+        <f>(AC33/AB33)-1</f>
+        <v>3.5689911509899641e-003</v>
       </c>
       <c r="AE33" s="22">
-        <f>(Z33/Y33)-1</f>
-        <v>0.13784063470162145</v>
-      </c>
-      <c r="AF33" s="23" t="s">
-        <v>100</v>
+        <f>(AC33/Z33)-1</f>
+        <v>8.517879728642086e-002</v>
+      </c>
+      <c r="AF33" s="22">
+        <f>(AA33/Z33)-1</f>
+        <v>0.16102104173853049</v>
+      </c>
+      <c r="AG33" s="23" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="34" ht="18">
       <c r="A34" s="26" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B34" s="27" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C34" s="29"/>
       <c r="D34" s="29"/>
@@ -4090,44 +4180,47 @@
       <c r="X34" s="18">
         <v>169</v>
       </c>
-      <c r="Y34" s="20">
-        <f>MIN(C34:X34)</f>
+      <c r="Y34" s="18">
+        <v>159</v>
+      </c>
+      <c r="Z34" s="20">
+        <f>MIN(C34:Y34)</f>
         <v>144</v>
       </c>
-      <c r="Z34" s="21">
-        <f>MAX(C34:X34)</f>
+      <c r="AA34" s="21">
+        <f>MAX(C34:Y34)</f>
         <v>199.94999999999999</v>
       </c>
-      <c r="AA34" s="21">
-        <f>AVERAGE(C34:X34)</f>
-        <v>179.04900000000001</v>
-      </c>
       <c r="AB34" s="21">
-        <f>AVERAGE(Q34:X34)</f>
-        <v>178.58249999999998</v>
-      </c>
-      <c r="AC34" s="22">
-        <f>(AB34/AA34)-1</f>
-        <v>-2.6054320325722413e-003</v>
+        <f>AVERAGE(C34:Y34)</f>
+        <v>177.22636363636363</v>
+      </c>
+      <c r="AC34" s="21">
+        <f>AVERAGE(Q34:Y34)</f>
+        <v>176.40666666666664</v>
       </c>
       <c r="AD34" s="22">
-        <f>(AB34/Y34)-1</f>
-        <v>0.24015624999999985</v>
+        <f>(AC34/AB34)-1</f>
+        <v>-4.6251412762655653e-003</v>
       </c>
       <c r="AE34" s="22">
-        <f>(Z34/Y34)-1</f>
+        <f>(AC34/Z34)-1</f>
+        <v>0.22504629629629602</v>
+      </c>
+      <c r="AF34" s="22">
+        <f>(AA34/Z34)-1</f>
         <v>0.38854166666666656</v>
       </c>
-      <c r="AF34" s="23" t="s">
-        <v>102</v>
+      <c r="AG34" s="23" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="35" ht="18">
       <c r="A35" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C35" s="17"/>
       <c r="D35" s="17"/>
@@ -4152,7 +4245,7 @@
         <v>31941.080000000002</v>
       </c>
       <c r="M35" s="17" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N35" s="18"/>
       <c r="O35" s="17"/>
@@ -4165,44 +4258,45 @@
       <c r="V35" s="17"/>
       <c r="W35" s="17"/>
       <c r="X35" s="17"/>
-      <c r="Y35" s="20">
-        <f>MIN(C35:X35)</f>
+      <c r="Y35" s="17"/>
+      <c r="Z35" s="20">
+        <f>MIN(C35:Y35)</f>
         <v>30731.380000000001</v>
       </c>
-      <c r="Z35" s="21">
-        <f>MAX(C35:X35)</f>
+      <c r="AA35" s="21">
+        <f>MAX(C35:Y35)</f>
         <v>32790.889999999999</v>
       </c>
-      <c r="AA35" s="21">
-        <f>AVERAGE(C35:X35)</f>
+      <c r="AB35" s="21">
+        <f>AVERAGE(C35:Y35)</f>
         <v>31912.133333333331</v>
       </c>
-      <c r="AB35" s="21" t="e">
-        <f>AVERAGE(Q35:X35)</f>
+      <c r="AC35" s="21" t="e">
+        <f>AVERAGE(Q35:Y35)</f>
         <v>#NUM!</v>
       </c>
-      <c r="AC35" s="22" t="e">
-        <f>(AB35/AA35)-1</f>
+      <c r="AD35" s="22" t="e">
+        <f>(AC35/AB35)-1</f>
         <v>#NUM!</v>
       </c>
-      <c r="AD35" s="22" t="e">
-        <f>(AB35/Y35)-1</f>
+      <c r="AE35" s="22" t="e">
+        <f>(AC35/Z35)-1</f>
         <v>#NUM!</v>
       </c>
-      <c r="AE35" s="22">
-        <f>(Z35/Y35)-1</f>
+      <c r="AF35" s="22">
+        <f>(AA35/Z35)-1</f>
         <v>6.7016515366377982e-002</v>
       </c>
-      <c r="AF35" s="23" t="s">
-        <v>105</v>
+      <c r="AG35" s="23" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="36" ht="18">
       <c r="A36" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C36" s="17"/>
       <c r="D36" s="17"/>
@@ -4234,7 +4328,7 @@
         <v>721.67999999999995</v>
       </c>
       <c r="T36" s="17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="U36" s="17">
         <v>1164</v>
@@ -4248,44 +4342,47 @@
       <c r="X36" s="17">
         <v>1150.8</v>
       </c>
-      <c r="Y36" s="20">
-        <f>MIN(C36:X36)</f>
+      <c r="Y36" s="17">
+        <v>1150.8</v>
+      </c>
+      <c r="Z36" s="20">
+        <f>MIN(C36:Y36)</f>
         <v>642.82000000000005</v>
       </c>
-      <c r="Z36" s="21">
-        <f>MAX(C36:X36)</f>
+      <c r="AA36" s="21">
+        <f>MAX(C36:Y36)</f>
         <v>1164</v>
       </c>
-      <c r="AA36" s="21">
-        <f>AVERAGE(C36:X36)</f>
-        <v>878.87599999999998</v>
-      </c>
       <c r="AB36" s="21">
-        <f>AVERAGE(Q36:X36)</f>
-        <v>968.77714285714296</v>
-      </c>
-      <c r="AC36" s="22">
-        <f>(AB36/AA36)-1</f>
-        <v>0.1022910431700752</v>
+        <f>AVERAGE(C36:Y36)</f>
+        <v>903.59636363636355</v>
+      </c>
+      <c r="AC36" s="21">
+        <f>AVERAGE(Q36:Y36)</f>
+        <v>991.53000000000009</v>
       </c>
       <c r="AD36" s="22">
-        <f>(AB36/Y36)-1</f>
-        <v>0.50707374203842903</v>
+        <f>(AC36/AB36)-1</f>
+        <v>9.7315172905038327e-002</v>
       </c>
       <c r="AE36" s="22">
-        <f>(Z36/Y36)-1</f>
+        <f>(AC36/Z36)-1</f>
+        <v>0.54246912043806983</v>
+      </c>
+      <c r="AF36" s="22">
+        <f>(AA36/Z36)-1</f>
         <v>0.81077128900780915</v>
       </c>
-      <c r="AF36" s="23" t="s">
-        <v>108</v>
+      <c r="AG36" s="23" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="37" ht="18">
       <c r="A37" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C37" s="17"/>
       <c r="D37" s="17"/>
@@ -4331,44 +4428,47 @@
       <c r="X37" s="30">
         <v>2016</v>
       </c>
-      <c r="Y37" s="20">
-        <f>MIN(C37:X37)</f>
+      <c r="Y37" s="30">
+        <v>2016</v>
+      </c>
+      <c r="Z37" s="20">
+        <f>MIN(C37:Y37)</f>
         <v>1151.71</v>
       </c>
-      <c r="Z37" s="21">
-        <f>MAX(C37:X37)</f>
+      <c r="AA37" s="21">
+        <f>MAX(C37:Y37)</f>
         <v>2064</v>
       </c>
-      <c r="AA37" s="21">
-        <f>AVERAGE(C37:X37)</f>
-        <v>1599.830909090909</v>
-      </c>
       <c r="AB37" s="21">
-        <f>AVERAGE(Q37:X37)</f>
-        <v>1751.8800000000001</v>
-      </c>
-      <c r="AC37" s="22">
-        <f>(AB37/AA37)-1</f>
-        <v>9.5040725894895761e-002</v>
+        <f>AVERAGE(C37:Y37)</f>
+        <v>1634.5116666666665</v>
+      </c>
+      <c r="AC37" s="21">
+        <f>AVERAGE(Q37:Y37)</f>
+        <v>1781.2266666666667</v>
       </c>
       <c r="AD37" s="22">
-        <f>(AB37/Y37)-1</f>
-        <v>0.52111208550763655</v>
+        <f>(AC37/AB37)-1</f>
+        <v>8.9760754231386297e-002</v>
       </c>
       <c r="AE37" s="22">
-        <f>(Z37/Y37)-1</f>
+        <f>(AC37/Z37)-1</f>
+        <v>0.5465930370203147</v>
+      </c>
+      <c r="AF37" s="22">
+        <f>(AA37/Z37)-1</f>
         <v>0.79211780743416305</v>
       </c>
-      <c r="AF37" s="23" t="s">
-        <v>108</v>
+      <c r="AG37" s="23" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="38" ht="18">
       <c r="A38" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C38" s="17"/>
       <c r="D38" s="17"/>
@@ -4403,55 +4503,58 @@
         <v>3876</v>
       </c>
       <c r="U38" s="36" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="V38" s="36" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="W38" s="36" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="X38" s="36" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y38" s="20">
-        <f>MIN(C38:X38)</f>
+        <v>44</v>
+      </c>
+      <c r="Y38" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z38" s="20">
+        <f>MIN(C38:Y38)</f>
         <v>2159.8299999999999</v>
       </c>
-      <c r="Z38" s="21">
-        <f>MAX(C38:X38)</f>
+      <c r="AA38" s="21">
+        <f>MAX(C38:Y38)</f>
         <v>3876</v>
       </c>
-      <c r="AA38" s="21">
-        <f>AVERAGE(C38:X38)</f>
+      <c r="AB38" s="21">
+        <f>AVERAGE(C38:Y38)</f>
         <v>2544.02</v>
       </c>
-      <c r="AB38" s="21">
-        <f>AVERAGE(Q38:X38)</f>
+      <c r="AC38" s="21">
+        <f>AVERAGE(Q38:Y38)</f>
         <v>2771.3400000000001</v>
       </c>
-      <c r="AC38" s="22">
-        <f>(AB38/AA38)-1</f>
+      <c r="AD38" s="22">
+        <f>(AC38/AB38)-1</f>
         <v>8.9354643438337877e-002</v>
       </c>
-      <c r="AD38" s="22">
-        <f>(AB38/Y38)-1</f>
+      <c r="AE38" s="22">
+        <f>(AC38/Z38)-1</f>
         <v>0.28312876476389359</v>
       </c>
-      <c r="AE38" s="22">
-        <f>(Z38/Y38)-1</f>
+      <c r="AF38" s="22">
+        <f>(AA38/Z38)-1</f>
         <v>0.79458568498446636</v>
       </c>
-      <c r="AF38" s="23" t="s">
-        <v>108</v>
+      <c r="AG38" s="23" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="39" ht="18">
       <c r="A39" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C39" s="17"/>
       <c r="D39" s="17"/>
@@ -4497,44 +4600,47 @@
       <c r="X39" s="30">
         <v>2218.4400000000001</v>
       </c>
-      <c r="Y39" s="20">
-        <f>MIN(C39:X39)</f>
+      <c r="Y39" s="30">
+        <v>2218.4400000000001</v>
+      </c>
+      <c r="Z39" s="20">
+        <f>MIN(C39:Y39)</f>
         <v>1310.1800000000001</v>
       </c>
-      <c r="Z39" s="21">
-        <f>MAX(C39:X39)</f>
+      <c r="AA39" s="21">
+        <f>MAX(C39:Y39)</f>
         <v>2218.4400000000001</v>
       </c>
-      <c r="AA39" s="21">
-        <f>AVERAGE(C39:X39)</f>
-        <v>1711.6818181818182</v>
-      </c>
       <c r="AB39" s="21">
-        <f>AVERAGE(Q39:X39)</f>
-        <v>1859.6400000000001</v>
-      </c>
-      <c r="AC39" s="22">
-        <f>(AB39/AA39)-1</f>
-        <v>8.6440236874950171e-002</v>
+        <f>AVERAGE(C39:Y39)</f>
+        <v>1753.9116666666666</v>
+      </c>
+      <c r="AC39" s="21">
+        <f>AVERAGE(Q39:Y39)</f>
+        <v>1899.5066666666669</v>
       </c>
       <c r="AD39" s="22">
-        <f>(AB39/Y39)-1</f>
-        <v>0.41937749011586201</v>
+        <f>(AC39/AB39)-1</f>
+        <v>8.3011592183947158e-002</v>
       </c>
       <c r="AE39" s="22">
-        <f>(Z39/Y39)-1</f>
+        <f>(AC39/Z39)-1</f>
+        <v>0.44980587909040493</v>
+      </c>
+      <c r="AF39" s="22">
+        <f>(AA39/Z39)-1</f>
         <v>0.69323299088674828</v>
       </c>
-      <c r="AF39" s="23" t="s">
-        <v>108</v>
+      <c r="AG39" s="23" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="40" ht="18">
       <c r="A40" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C40" s="17"/>
       <c r="D40" s="17"/>
@@ -4568,44 +4674,47 @@
       <c r="X40" s="19">
         <v>1592.6400000000001</v>
       </c>
-      <c r="Y40" s="20">
-        <f>MIN(C40:X40)</f>
+      <c r="Y40" s="19">
         <v>1592.6400000000001</v>
       </c>
-      <c r="Z40" s="21">
-        <f>MAX(C40:X40)</f>
+      <c r="Z40" s="20">
+        <f>MIN(C40:Y40)</f>
+        <v>1592.6400000000001</v>
+      </c>
+      <c r="AA40" s="21">
+        <f>MAX(C40:Y40)</f>
         <v>1896</v>
       </c>
-      <c r="AA40" s="21">
-        <f>AVERAGE(C40:X40)</f>
-        <v>1713.9839999999999</v>
-      </c>
       <c r="AB40" s="21">
-        <f>AVERAGE(Q40:X40)</f>
-        <v>1713.9839999999999</v>
-      </c>
-      <c r="AC40" s="22">
-        <f>(AB40/AA40)-1</f>
+        <f>AVERAGE(C40:Y40)</f>
+        <v>1693.76</v>
+      </c>
+      <c r="AC40" s="21">
+        <f>AVERAGE(Q40:Y40)</f>
+        <v>1693.76</v>
+      </c>
+      <c r="AD40" s="22">
+        <f>(AC40/AB40)-1</f>
         <v>0</v>
       </c>
-      <c r="AD40" s="22">
-        <f>(AB40/Y40)-1</f>
-        <v>7.6190476190476142e-002</v>
-      </c>
       <c r="AE40" s="22">
-        <f>(Z40/Y40)-1</f>
+        <f>(AC40/Z40)-1</f>
+        <v>6.3492063492063489e-002</v>
+      </c>
+      <c r="AF40" s="22">
+        <f>(AA40/Z40)-1</f>
         <v>0.19047619047619047</v>
       </c>
-      <c r="AF40" s="23" t="s">
-        <v>108</v>
+      <c r="AG40" s="23" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="41" ht="18">
       <c r="A41" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C41" s="17"/>
       <c r="D41" s="17"/>
@@ -4637,13 +4746,13 @@
         <v>1628.6199999999999</v>
       </c>
       <c r="T41" s="17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="U41" s="17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="V41" s="17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="W41" s="19">
         <v>1985.76</v>
@@ -4651,44 +4760,47 @@
       <c r="X41" s="19">
         <v>1985.76</v>
       </c>
-      <c r="Y41" s="20">
-        <f>MIN(C41:X41)</f>
+      <c r="Y41" s="19">
+        <v>1985.76</v>
+      </c>
+      <c r="Z41" s="20">
+        <f>MIN(C41:Y41)</f>
         <v>1480.5599999999999</v>
       </c>
-      <c r="Z41" s="21">
-        <f>MAX(C41:X41)</f>
+      <c r="AA41" s="21">
+        <f>MAX(C41:Y41)</f>
         <v>1985.76</v>
       </c>
-      <c r="AA41" s="21">
-        <f>AVERAGE(C41:X41)</f>
-        <v>1680.8899999999999</v>
-      </c>
       <c r="AB41" s="21">
-        <f>AVERAGE(Q41:X41)</f>
-        <v>1771.4759999999999</v>
-      </c>
-      <c r="AC41" s="22">
-        <f>(AB41/AA41)-1</f>
-        <v>5.3891688331776599e-002</v>
+        <f>AVERAGE(C41:Y41)</f>
+        <v>1714.7644444444443</v>
+      </c>
+      <c r="AC41" s="21">
+        <f>AVERAGE(Q41:Y41)</f>
+        <v>1807.1899999999998</v>
       </c>
       <c r="AD41" s="22">
-        <f>(AB41/Y41)-1</f>
-        <v>0.19649051710163712</v>
+        <f>(AC41/AB41)-1</f>
+        <v>5.389985537372155e-002</v>
       </c>
       <c r="AE41" s="22">
-        <f>(Z41/Y41)-1</f>
+        <f>(AC41/Z41)-1</f>
+        <v>0.22061247095693504</v>
+      </c>
+      <c r="AF41" s="22">
+        <f>(AA41/Z41)-1</f>
         <v>0.34122224023342529</v>
       </c>
-      <c r="AF41" s="23" t="s">
-        <v>108</v>
+      <c r="AG41" s="23" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="42" ht="18">
       <c r="A42" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C42" s="17"/>
       <c r="D42" s="17">
@@ -4714,41 +4826,42 @@
       <c r="V42" s="17"/>
       <c r="W42" s="17"/>
       <c r="X42" s="17"/>
-      <c r="Y42" s="20">
-        <f>MIN(C42:X42)</f>
+      <c r="Y42" s="17"/>
+      <c r="Z42" s="20">
+        <f>MIN(C42:Y42)</f>
         <v>339.45999999999998</v>
       </c>
-      <c r="Z42" s="21">
-        <f>MAX(C42:X42)</f>
+      <c r="AA42" s="21">
+        <f>MAX(C42:Y42)</f>
         <v>339.45999999999998</v>
       </c>
-      <c r="AA42" s="21">
-        <f>AVERAGE(C42:X42)</f>
+      <c r="AB42" s="21">
+        <f>AVERAGE(C42:Y42)</f>
         <v>339.45999999999998</v>
       </c>
-      <c r="AB42" s="21" t="e">
-        <f>AVERAGE(Q42:X42)</f>
+      <c r="AC42" s="21" t="e">
+        <f>AVERAGE(Q42:Y42)</f>
         <v>#NUM!</v>
       </c>
-      <c r="AC42" s="22" t="e">
-        <f>(AB42/AA42)-1</f>
+      <c r="AD42" s="22" t="e">
+        <f>(AC42/AB42)-1</f>
         <v>#NUM!</v>
       </c>
-      <c r="AD42" s="22" t="e">
-        <f>(AB42/Y42)-1</f>
+      <c r="AE42" s="22" t="e">
+        <f>(AC42/Z42)-1</f>
         <v>#NUM!</v>
       </c>
-      <c r="AE42" s="22">
-        <f>(Z42/Y42)-1</f>
+      <c r="AF42" s="22">
+        <f>(AA42/Z42)-1</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" ht="18">
       <c r="A43" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C43" s="17"/>
       <c r="D43" s="17"/>
@@ -4808,44 +4921,47 @@
       <c r="X43" s="17">
         <v>378.99000000000001</v>
       </c>
-      <c r="Y43" s="20">
-        <f>MIN(C43:X43)</f>
+      <c r="Y43" s="17">
         <v>378.99000000000001</v>
       </c>
-      <c r="Z43" s="21">
-        <f>MAX(C43:X43)</f>
+      <c r="Z43" s="20">
+        <f>MIN(C43:Y43)</f>
         <v>378.99000000000001</v>
       </c>
       <c r="AA43" s="21">
-        <f>AVERAGE(C43:X43)</f>
+        <f>MAX(C43:Y43)</f>
+        <v>378.99000000000001</v>
+      </c>
+      <c r="AB43" s="21">
+        <f>AVERAGE(C43:Y43)</f>
         <v>378.9899999999999</v>
       </c>
-      <c r="AB43" s="21">
-        <f>AVERAGE(Q43:X43)</f>
+      <c r="AC43" s="21">
+        <f>AVERAGE(Q43:Y43)</f>
         <v>378.99000000000001</v>
       </c>
-      <c r="AC43" s="22">
-        <f>(AB43/AA43)-1</f>
+      <c r="AD43" s="22">
+        <f>(AC43/AB43)-1</f>
         <v>2.2204460492503131e-016</v>
       </c>
-      <c r="AD43" s="22">
-        <f>(AB43/Y43)-1</f>
+      <c r="AE43" s="22">
+        <f>(AC43/Z43)-1</f>
         <v>0</v>
       </c>
-      <c r="AE43" s="22">
-        <f>(Z43/Y43)-1</f>
+      <c r="AF43" s="22">
+        <f>(AA43/Z43)-1</f>
         <v>0</v>
       </c>
-      <c r="AF43" s="23" t="s">
-        <v>119</v>
+      <c r="AG43" s="23" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="44" ht="18">
       <c r="A44" s="26" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B44" s="27" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C44" s="29"/>
       <c r="D44" s="29"/>
@@ -4905,44 +5021,47 @@
       <c r="X44" s="19">
         <v>128.36000000000001</v>
       </c>
-      <c r="Y44" s="20">
-        <f>MIN(C44:X44)</f>
+      <c r="Y44" s="30">
+        <v>191.19</v>
+      </c>
+      <c r="Z44" s="20">
+        <f>MIN(C44:Y44)</f>
         <v>88.329999999999998</v>
       </c>
-      <c r="Z44" s="21">
-        <f>MAX(C44:X44)</f>
-        <v>128.36000000000001</v>
-      </c>
       <c r="AA44" s="21">
-        <f>AVERAGE(C44:X44)</f>
-        <v>102.80611111111112</v>
+        <f>MAX(C44:Y44)</f>
+        <v>191.19</v>
       </c>
       <c r="AB44" s="21">
-        <f>AVERAGE(Q44:X44)</f>
-        <v>120.90125</v>
-      </c>
-      <c r="AC44" s="22">
-        <f>(AB44/AA44)-1</f>
-        <v>0.1760122885042501</v>
+        <f>AVERAGE(C44:Y44)</f>
+        <v>107.45789473684212</v>
+      </c>
+      <c r="AC44" s="21">
+        <f>AVERAGE(Q44:Y44)</f>
+        <v>128.71111111111111</v>
       </c>
       <c r="AD44" s="22">
-        <f>(AB44/Y44)-1</f>
-        <v>0.368745046982905</v>
+        <f>(AC44/AB44)-1</f>
+        <v>0.19778180492291253</v>
       </c>
       <c r="AE44" s="22">
-        <f>(Z44/Y44)-1</f>
-        <v>0.45318691271368738</v>
-      </c>
-      <c r="AF44" s="23" t="s">
-        <v>122</v>
+        <f>(AC44/Z44)-1</f>
+        <v>0.4571619054807099</v>
+      </c>
+      <c r="AF44" s="22">
+        <f>(AA44/Z44)-1</f>
+        <v>1.1644967734631497</v>
+      </c>
+      <c r="AG44" s="23" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="45" ht="18">
       <c r="A45" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C45" s="17"/>
       <c r="D45" s="17">
@@ -5004,44 +5123,47 @@
       <c r="X45" s="36">
         <v>34.759999999999998</v>
       </c>
-      <c r="Y45" s="20">
-        <f>MIN(C45:X45)</f>
+      <c r="Y45" s="36">
+        <v>40.039999999999999</v>
+      </c>
+      <c r="Z45" s="20">
+        <f>MIN(C45:Y45)</f>
         <v>29.989999999999998</v>
       </c>
-      <c r="Z45" s="21">
-        <f>MAX(C45:X45)</f>
+      <c r="AA45" s="21">
+        <f>MAX(C45:Y45)</f>
         <v>44.979999999999997</v>
       </c>
-      <c r="AA45" s="21">
-        <f>AVERAGE(C45:X45)</f>
-        <v>36.421578947368424</v>
-      </c>
       <c r="AB45" s="21">
-        <f>AVERAGE(Q45:X45)</f>
-        <v>36.333750000000002</v>
-      </c>
-      <c r="AC45" s="22">
-        <f>(AB45/AA45)-1</f>
-        <v>-2.4114535917111324e-003</v>
+        <f>AVERAGE(C45:Y45)</f>
+        <v>36.602500000000006</v>
+      </c>
+      <c r="AC45" s="21">
+        <f>AVERAGE(Q45:Y45)</f>
+        <v>36.745555555555562</v>
       </c>
       <c r="AD45" s="22">
-        <f>(AB45/Y45)-1</f>
-        <v>0.2115288429476494</v>
+        <f>(AC45/AB45)-1</f>
+        <v>3.9083547723668399e-003</v>
       </c>
       <c r="AE45" s="22">
-        <f>(Z45/Y45)-1</f>
+        <f>(AC45/Z45)-1</f>
+        <v>0.22526027194249965</v>
+      </c>
+      <c r="AF45" s="22">
+        <f>(AA45/Z45)-1</f>
         <v>0.49983327775925313</v>
       </c>
-      <c r="AF45" s="23" t="s">
-        <v>125</v>
+      <c r="AG45" s="23" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="46" ht="18">
       <c r="A46" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C46" s="17"/>
       <c r="D46" s="17">
@@ -5103,44 +5225,47 @@
       <c r="X46" s="35">
         <v>36.530000000000001</v>
       </c>
-      <c r="Y46" s="20">
-        <f>MIN(C46:X46)</f>
+      <c r="Y46" s="36">
+        <v>30.989999999999998</v>
+      </c>
+      <c r="Z46" s="20">
+        <f>MIN(C46:Y46)</f>
         <v>25.989999999999998</v>
       </c>
-      <c r="Z46" s="21">
-        <f>MAX(C46:X46)</f>
+      <c r="AA46" s="21">
+        <f>MAX(C46:Y46)</f>
         <v>42</v>
       </c>
-      <c r="AA46" s="21">
-        <f>AVERAGE(C46:X46)</f>
-        <v>31.935263157894735</v>
-      </c>
       <c r="AB46" s="21">
-        <f>AVERAGE(Q46:X46)</f>
-        <v>32.818750000000009</v>
-      </c>
-      <c r="AC46" s="22">
-        <f>(AB46/AA46)-1</f>
-        <v>2.766493069861764e-002</v>
+        <f>AVERAGE(C46:Y46)</f>
+        <v>31.887999999999998</v>
+      </c>
+      <c r="AC46" s="21">
+        <f>AVERAGE(Q46:Y46)</f>
+        <v>32.615555555555567</v>
       </c>
       <c r="AD46" s="22">
-        <f>(AB46/Y46)-1</f>
-        <v>0.26274528664871144</v>
+        <f>(AC46/AB46)-1</f>
+        <v>2.2815966995596071e-002</v>
       </c>
       <c r="AE46" s="22">
-        <f>(Z46/Y46)-1</f>
+        <f>(AC46/Z46)-1</f>
+        <v>0.25492710871702839</v>
+      </c>
+      <c r="AF46" s="22">
+        <f>(AA46/Z46)-1</f>
         <v>0.61600615621392851</v>
       </c>
-      <c r="AF46" s="23" t="s">
-        <v>128</v>
+      <c r="AG46" s="23" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="47" ht="18">
       <c r="A47" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C47" s="17"/>
       <c r="D47" s="17">
@@ -5202,44 +5327,47 @@
       <c r="X47" s="36">
         <v>28.899999999999999</v>
       </c>
-      <c r="Y47" s="20">
-        <f>MIN(C47:X47)</f>
+      <c r="Y47" s="36">
+        <v>28.899999999999999</v>
+      </c>
+      <c r="Z47" s="20">
+        <f>MIN(C47:Y47)</f>
         <v>21.690000000000001</v>
       </c>
-      <c r="Z47" s="21">
-        <f>MAX(C47:X47)</f>
+      <c r="AA47" s="21">
+        <f>MAX(C47:Y47)</f>
         <v>43.990000000000002</v>
       </c>
-      <c r="AA47" s="21">
-        <f>AVERAGE(C47:X47)</f>
-        <v>29.441052631578941</v>
-      </c>
       <c r="AB47" s="21">
-        <f>AVERAGE(Q47:X47)</f>
-        <v>27.946250000000003</v>
-      </c>
-      <c r="AC47" s="22">
-        <f>(AB47/AA47)-1</f>
-        <v>-5.0772730523078846e-002</v>
+        <f>AVERAGE(C47:Y47)</f>
+        <v>29.413999999999994</v>
+      </c>
+      <c r="AC47" s="21">
+        <f>AVERAGE(Q47:Y47)</f>
+        <v>28.052222222222227</v>
       </c>
       <c r="AD47" s="22">
-        <f>(AB47/Y47)-1</f>
-        <v>0.28843937298294153</v>
+        <f>(AC47/AB47)-1</f>
+        <v>-4.6296925878077322e-002</v>
       </c>
       <c r="AE47" s="22">
-        <f>(Z47/Y47)-1</f>
+        <f>(AC47/Z47)-1</f>
+        <v>0.29332513703191454</v>
+      </c>
+      <c r="AF47" s="22">
+        <f>(AA47/Z47)-1</f>
         <v>1.0281235592438911</v>
       </c>
-      <c r="AF47" s="23" t="s">
-        <v>131</v>
+      <c r="AG47" s="23" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="48" ht="54">
       <c r="A48" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C48" s="17"/>
       <c r="D48" s="17"/>
@@ -5260,10 +5388,10 @@
         <v>1714.0799999999999</v>
       </c>
       <c r="K48" s="17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L48" s="17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M48" s="25">
         <v>1449.28</v>
@@ -5301,44 +5429,47 @@
       <c r="X48" s="17">
         <v>1611.4100000000001</v>
       </c>
-      <c r="Y48" s="20">
-        <f>MIN(C48:X48)</f>
+      <c r="Y48" s="18">
+        <v>1820.77</v>
+      </c>
+      <c r="Z48" s="20">
+        <f>MIN(C48:Y48)</f>
         <v>1449.28</v>
       </c>
-      <c r="Z48" s="21">
-        <f>MAX(C48:X48)</f>
+      <c r="AA48" s="21">
+        <f>MAX(C48:Y48)</f>
         <v>1820.77</v>
       </c>
-      <c r="AA48" s="21">
-        <f>AVERAGE(C48:X48)</f>
-        <v>1691.6570588235293</v>
-      </c>
       <c r="AB48" s="21">
-        <f>AVERAGE(Q48:X48)</f>
-        <v>1659.5225</v>
-      </c>
-      <c r="AC48" s="22">
-        <f>(AB48/AA48)-1</f>
-        <v>-1.899590620682734e-002</v>
+        <f>AVERAGE(C48:Y48)</f>
+        <v>1698.8299999999999</v>
+      </c>
+      <c r="AC48" s="21">
+        <f>AVERAGE(Q48:Y48)</f>
+        <v>1677.4388888888889</v>
       </c>
       <c r="AD48" s="22">
-        <f>(AB48/Y48)-1</f>
-        <v>0.14506686078604547</v>
+        <f>(AC48/AB48)-1</f>
+        <v>-1.2591672569421952e-002</v>
       </c>
       <c r="AE48" s="22">
-        <f>(Z48/Y48)-1</f>
+        <f>(AC48/Z48)-1</f>
+        <v>0.15742912956011867</v>
+      </c>
+      <c r="AF48" s="22">
+        <f>(AA48/Z48)-1</f>
         <v>0.25632727975270475</v>
       </c>
-      <c r="AF48" s="1" t="s">
-        <v>133</v>
+      <c r="AG48" s="1" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="49" ht="18">
       <c r="A49" s="26" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B49" s="27" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C49" s="29"/>
       <c r="D49" s="29"/>
@@ -5398,44 +5529,47 @@
       <c r="X49" s="36">
         <v>39.899999999999999</v>
       </c>
-      <c r="Y49" s="20">
-        <f>MIN(C49:X49)</f>
+      <c r="Y49" s="36">
+        <v>43.990000000000002</v>
+      </c>
+      <c r="Z49" s="20">
+        <f>MIN(C49:Y49)</f>
         <v>30.989999999999998</v>
       </c>
-      <c r="Z49" s="21">
-        <f>MAX(C49:X49)</f>
-        <v>43.210000000000001</v>
-      </c>
       <c r="AA49" s="21">
-        <f>AVERAGE(C49:X49)</f>
-        <v>36.894999999999996</v>
+        <f>MAX(C49:Y49)</f>
+        <v>43.990000000000002</v>
       </c>
       <c r="AB49" s="21">
-        <f>AVERAGE(Q49:X49)</f>
-        <v>37.892499999999998</v>
-      </c>
-      <c r="AC49" s="22">
-        <f>(AB49/AA49)-1</f>
-        <v>2.7036183764737931e-002</v>
+        <f>AVERAGE(C49:Y49)</f>
+        <v>37.268421052631574</v>
+      </c>
+      <c r="AC49" s="21">
+        <f>AVERAGE(Q49:Y49)</f>
+        <v>38.57</v>
       </c>
       <c r="AD49" s="22">
-        <f>(AB49/Y49)-1</f>
-        <v>0.2227331397224912</v>
+        <f>(AC49/AB49)-1</f>
+        <v>3.4924445699760165e-002</v>
       </c>
       <c r="AE49" s="22">
-        <f>(Z49/Y49)-1</f>
-        <v>0.39432074862859001</v>
-      </c>
-      <c r="AF49" s="23" t="s">
-        <v>136</v>
+        <f>(AC49/Z49)-1</f>
+        <v>0.24459503065505017</v>
+      </c>
+      <c r="AF49" s="22">
+        <f>(AA49/Z49)-1</f>
+        <v>0.41949015811552126</v>
+      </c>
+      <c r="AG49" s="23" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="50" ht="18">
       <c r="A50" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C50" s="17"/>
       <c r="D50" s="17"/>
@@ -5495,44 +5629,47 @@
       <c r="X50" s="17">
         <v>84.680000000000007</v>
       </c>
-      <c r="Y50" s="20">
-        <f>MIN(C50:X50)</f>
+      <c r="Y50" s="17">
+        <v>85.209999999999994</v>
+      </c>
+      <c r="Z50" s="20">
+        <f>MIN(C50:Y50)</f>
         <v>81.689999999999998</v>
       </c>
-      <c r="Z50" s="21">
-        <f>MAX(C50:X50)</f>
+      <c r="AA50" s="21">
+        <f>MAX(C50:Y50)</f>
         <v>93.280000000000001</v>
       </c>
-      <c r="AA50" s="21">
-        <f>AVERAGE(C50:X50)</f>
-        <v>88.198333333333352</v>
-      </c>
       <c r="AB50" s="21">
-        <f>AVERAGE(Q50:X50)</f>
-        <v>85.368750000000006</v>
-      </c>
-      <c r="AC50" s="22">
-        <f>(AB50/AA50)-1</f>
-        <v>-3.2082049925357792e-002</v>
+        <f>AVERAGE(C50:Y50)</f>
+        <v>88.041052631578964</v>
+      </c>
+      <c r="AC50" s="21">
+        <f>AVERAGE(Q50:Y50)</f>
+        <v>85.351111111111123</v>
       </c>
       <c r="AD50" s="22">
-        <f>(AB50/Y50)-1</f>
-        <v>4.5033051781123934e-002</v>
+        <f>(AC50/AB50)-1</f>
+        <v>-3.0553263961124011e-002</v>
       </c>
       <c r="AE50" s="22">
-        <f>(Z50/Y50)-1</f>
+        <f>(AC50/Z50)-1</f>
+        <v>4.4817127079338048e-002</v>
+      </c>
+      <c r="AF50" s="22">
+        <f>(AA50/Z50)-1</f>
         <v>0.1418778308238462</v>
       </c>
-      <c r="AF50" s="1" t="s">
-        <v>139</v>
+      <c r="AG50" s="1" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="51" ht="18">
       <c r="A51" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C51" s="17"/>
       <c r="D51" s="17"/>
@@ -5594,44 +5731,47 @@
       <c r="X51" s="34">
         <v>298.80000000000001</v>
       </c>
-      <c r="Y51" s="20">
-        <f>MIN(C51:X51)</f>
+      <c r="Y51" s="34">
         <v>298.80000000000001</v>
       </c>
-      <c r="Z51" s="21">
-        <f>MAX(C51:X51)</f>
+      <c r="Z51" s="20">
+        <f>MIN(C51:Y51)</f>
+        <v>298.80000000000001</v>
+      </c>
+      <c r="AA51" s="21">
+        <f>MAX(C51:Y51)</f>
         <v>309.05000000000001</v>
       </c>
-      <c r="AA51" s="21">
-        <f>AVERAGE(C51:X51)</f>
-        <v>307.97105263157903</v>
-      </c>
       <c r="AB51" s="21">
-        <f>AVERAGE(Q51:X51)</f>
-        <v>306.48750000000001</v>
-      </c>
-      <c r="AC51" s="22">
-        <f>(AB51/AA51)-1</f>
-        <v>-4.817182065983916e-003</v>
+        <f>AVERAGE(C51:Y51)</f>
+        <v>307.5125000000001</v>
+      </c>
+      <c r="AC51" s="21">
+        <f>AVERAGE(Q51:Y51)</f>
+        <v>305.63333333333338</v>
       </c>
       <c r="AD51" s="22">
-        <f>(AB51/Y51)-1</f>
-        <v>2.5727911646586277e-002</v>
+        <f>(AC51/AB51)-1</f>
+        <v>-6.1108627020584061e-003</v>
       </c>
       <c r="AE51" s="22">
-        <f>(Z51/Y51)-1</f>
+        <f>(AC51/Z51)-1</f>
+        <v>2.2869254796965777e-002</v>
+      </c>
+      <c r="AF51" s="22">
+        <f>(AA51/Z51)-1</f>
         <v>3.4303882195448443e-002</v>
       </c>
-      <c r="AF51" s="23" t="s">
-        <v>142</v>
+      <c r="AG51" s="23" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="52" ht="18">
       <c r="A52" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C52" s="17"/>
       <c r="D52" s="17"/>
@@ -5691,41 +5831,44 @@
       <c r="X52" s="17">
         <v>108.98999999999999</v>
       </c>
-      <c r="Y52" s="20">
-        <f>MIN(C52:X52)</f>
+      <c r="Y52" s="25">
+        <v>100.44</v>
+      </c>
+      <c r="Z52" s="20">
+        <f>MIN(C52:Y52)</f>
+        <v>100.44</v>
+      </c>
+      <c r="AA52" s="21">
+        <f>MAX(C52:Y52)</f>
         <v>108.98999999999999</v>
       </c>
-      <c r="Z52" s="21">
-        <f>MAX(C52:X52)</f>
-        <v>108.98999999999999</v>
-      </c>
-      <c r="AA52" s="21">
-        <f>AVERAGE(C52:X52)</f>
-        <v>108.98999999999999</v>
-      </c>
       <c r="AB52" s="21">
-        <f>AVERAGE(Q52:X52)</f>
-        <v>108.98999999999999</v>
-      </c>
-      <c r="AC52" s="22">
-        <f>(AB52/AA52)-1</f>
-        <v>0</v>
+        <f>AVERAGE(C52:Y52)</f>
+        <v>108.53999999999999</v>
+      </c>
+      <c r="AC52" s="21">
+        <f>AVERAGE(Q52:Y52)</f>
+        <v>108.03999999999999</v>
       </c>
       <c r="AD52" s="22">
-        <f>(AB52/Y52)-1</f>
-        <v>0</v>
+        <f>(AC52/AB52)-1</f>
+        <v>-4.6065966463976205e-003</v>
       </c>
       <c r="AE52" s="22">
-        <f>(Z52/Y52)-1</f>
-        <v>0</v>
-      </c>
-      <c r="AF52" s="38" t="s">
-        <v>144</v>
+        <f>(AC52/Z52)-1</f>
+        <v>7.5667064914376692e-002</v>
+      </c>
+      <c r="AF52" s="22">
+        <f>(AA52/Z52)-1</f>
+        <v>8.5125448028673834e-002</v>
+      </c>
+      <c r="AG52" s="38" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="53" ht="18">
       <c r="B53" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="O53" s="17">
         <v>1.49</v>
@@ -5757,92 +5900,95 @@
       <c r="X53" s="17">
         <v>1.99</v>
       </c>
-      <c r="Y53" s="20">
-        <f>MIN(C53:X53)</f>
+      <c r="Y53" s="17">
+        <v>1.99</v>
+      </c>
+      <c r="Z53" s="20">
+        <f>MIN(C53:Y53)</f>
         <v>1.49</v>
       </c>
-      <c r="Z53" s="21">
-        <f>MAX(C53:X53)</f>
+      <c r="AA53" s="21">
+        <f>MAX(C53:Y53)</f>
         <v>1.99</v>
       </c>
-      <c r="AA53" s="21">
-        <f>AVERAGE(C53:X53)</f>
-        <v>1.7399999999999998</v>
-      </c>
       <c r="AB53" s="21">
-        <f>AVERAGE(Q53:X53)</f>
-        <v>1.8025</v>
-      </c>
-      <c r="AC53" s="22">
-        <f>(AB53/AA53)-1</f>
-        <v>3.5919540229885083e-002</v>
+        <f>AVERAGE(C53:Y53)</f>
+        <v>1.7627272727272725</v>
+      </c>
+      <c r="AC53" s="21">
+        <f>AVERAGE(Q53:Y53)</f>
+        <v>1.8233333333333333</v>
       </c>
       <c r="AD53" s="22">
-        <f>(AB53/Y53)-1</f>
-        <v>0.20973154362416113</v>
+        <f>(AC53/AB53)-1</f>
+        <v>3.4381983840467756e-002</v>
       </c>
       <c r="AE53" s="22">
-        <f>(Z53/Y53)-1</f>
+        <f>(AC53/Z53)-1</f>
+        <v>0.22371364653243853</v>
+      </c>
+      <c r="AF53" s="22">
+        <f>(AA53/Z53)-1</f>
         <v>0.33557046979865768</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="Y1:Y6"/>
     <mergeCell ref="Z1:Z6"/>
     <mergeCell ref="AA1:AA6"/>
     <mergeCell ref="AB1:AB6"/>
     <mergeCell ref="AC1:AC6"/>
     <mergeCell ref="AD1:AD6"/>
     <mergeCell ref="AE1:AE6"/>
+    <mergeCell ref="AF1:AF6"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="AF8"/>
-    <hyperlink r:id="rId2" ref="AF9"/>
-    <hyperlink r:id="rId3" ref="AF10"/>
-    <hyperlink r:id="rId4" ref="AF11"/>
-    <hyperlink r:id="rId5" ref="AF12"/>
-    <hyperlink r:id="rId6" ref="AF13"/>
-    <hyperlink r:id="rId7" ref="AF14"/>
-    <hyperlink r:id="rId8" ref="AF15"/>
-    <hyperlink r:id="rId9" ref="AF16"/>
-    <hyperlink r:id="rId10" ref="AF17"/>
-    <hyperlink r:id="rId11" ref="AF18"/>
-    <hyperlink r:id="rId12" ref="AF19"/>
-    <hyperlink r:id="rId13" ref="AF20"/>
-    <hyperlink r:id="rId14" ref="AF21"/>
-    <hyperlink r:id="rId15" ref="AF22"/>
-    <hyperlink r:id="rId16" ref="AF23"/>
-    <hyperlink r:id="rId17" ref="AF24"/>
-    <hyperlink r:id="rId18" ref="AF25"/>
-    <hyperlink r:id="rId19" ref="AF26"/>
-    <hyperlink r:id="rId20" ref="AF27"/>
-    <hyperlink r:id="rId21" ref="AF28"/>
-    <hyperlink r:id="rId22" ref="AF29"/>
-    <hyperlink r:id="rId23" ref="AF30"/>
-    <hyperlink r:id="rId24" ref="AF31"/>
-    <hyperlink r:id="rId25" ref="AF32"/>
-    <hyperlink r:id="rId26" ref="AF33"/>
-    <hyperlink r:id="rId27" ref="AF34"/>
-    <hyperlink r:id="rId28" ref="AF35"/>
-    <hyperlink r:id="rId29" ref="AF36"/>
-    <hyperlink r:id="rId29" ref="AF37"/>
-    <hyperlink r:id="rId29" ref="AF38"/>
-    <hyperlink r:id="rId29" ref="AF39"/>
-    <hyperlink r:id="rId29" ref="AF40"/>
-    <hyperlink r:id="rId29" ref="AF41"/>
-    <hyperlink r:id="rId30" ref="AF43"/>
-    <hyperlink r:id="rId31" ref="AF44"/>
-    <hyperlink r:id="rId32" ref="AF45"/>
-    <hyperlink r:id="rId33" ref="AF46"/>
-    <hyperlink r:id="rId34" ref="AF47"/>
-    <hyperlink r:id="rId35" ref="AF49"/>
-    <hyperlink r:id="rId36" ref="AF51"/>
-    <hyperlink r:id="rId37" ref="AF52"/>
+    <hyperlink r:id="rId1" ref="AG8"/>
+    <hyperlink r:id="rId2" ref="AG9"/>
+    <hyperlink r:id="rId3" ref="AG10"/>
+    <hyperlink r:id="rId4" ref="AG11"/>
+    <hyperlink r:id="rId5" ref="AG12"/>
+    <hyperlink r:id="rId6" ref="AG13"/>
+    <hyperlink r:id="rId7" ref="AG14"/>
+    <hyperlink r:id="rId8" ref="AG15"/>
+    <hyperlink r:id="rId9" ref="AG16"/>
+    <hyperlink r:id="rId10" ref="AG17"/>
+    <hyperlink r:id="rId11" ref="AG18"/>
+    <hyperlink r:id="rId12" ref="AG19"/>
+    <hyperlink r:id="rId13" ref="AG20"/>
+    <hyperlink r:id="rId14" ref="AG21"/>
+    <hyperlink r:id="rId15" ref="AG22"/>
+    <hyperlink r:id="rId16" ref="AG23"/>
+    <hyperlink r:id="rId17" ref="AG24"/>
+    <hyperlink r:id="rId18" ref="AG25"/>
+    <hyperlink r:id="rId19" ref="AG26"/>
+    <hyperlink r:id="rId20" ref="AG27"/>
+    <hyperlink r:id="rId21" ref="AG28"/>
+    <hyperlink r:id="rId22" ref="AG29"/>
+    <hyperlink r:id="rId23" ref="AG30"/>
+    <hyperlink r:id="rId24" ref="AG31"/>
+    <hyperlink r:id="rId25" ref="AG32"/>
+    <hyperlink r:id="rId26" ref="AG33"/>
+    <hyperlink r:id="rId27" ref="AG34"/>
+    <hyperlink r:id="rId28" ref="AG35"/>
+    <hyperlink r:id="rId29" ref="AG36"/>
+    <hyperlink r:id="rId29" ref="AG37"/>
+    <hyperlink r:id="rId29" ref="AG38"/>
+    <hyperlink r:id="rId29" ref="AG39"/>
+    <hyperlink r:id="rId29" ref="AG40"/>
+    <hyperlink r:id="rId29" ref="AG41"/>
+    <hyperlink r:id="rId30" ref="AG43"/>
+    <hyperlink r:id="rId31" ref="AG44"/>
+    <hyperlink r:id="rId32" ref="AG45"/>
+    <hyperlink r:id="rId33" ref="AG46"/>
+    <hyperlink r:id="rId34" ref="AG47"/>
+    <hyperlink r:id="rId35" ref="AG49"/>
+    <hyperlink r:id="rId36" ref="AG51"/>
+    <hyperlink r:id="rId37" ref="AG52"/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.25196850393700787" right="0.25196850393700787" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="36" firstPageNumber="1" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="1" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <pageSetup paperSize="9" scale="34" firstPageNumber="1" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="1" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/analyse-prix-composants.xlsx
+++ b/analyse-prix-composants.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Feuille1" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Feuille1!$A:$AF</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Feuille1!$A:$AG</definedName>
     <definedName name="Print_Titles" localSheetId="0">Feuille1!$7:$7</definedName>
   </definedNames>
   <calcPr/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="148">
   <si>
     <t xml:space="preserve">Le prix des composants IT</t>
   </si>
@@ -127,6 +127,9 @@
   </si>
   <si>
     <t xml:space="preserve">4 avr 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11 avr 2026</t>
   </si>
   <si>
     <t>Min</t>
@@ -1349,12 +1352,12 @@
     <col bestFit="1" min="12" max="12" style="4" width="11.7109375"/>
     <col bestFit="1" min="13" max="13" style="4" width="13.00390625"/>
     <col bestFit="1" min="14" max="15" style="4" width="14.140625"/>
-    <col customWidth="1" min="16" max="25" style="1" width="12.7109375"/>
-    <col customWidth="1" min="26" max="29" style="2" width="12.7109375"/>
-    <col customWidth="1" min="30" max="30" style="2" width="14.140625"/>
-    <col customWidth="1" min="31" max="32" style="2" width="12.7109375"/>
-    <col customWidth="1" min="33" max="33" style="5" width="42.28125"/>
-    <col min="34" max="16384" style="1" width="9.140625"/>
+    <col customWidth="1" min="16" max="26" style="1" width="12.7109375"/>
+    <col customWidth="1" min="27" max="30" style="2" width="12.7109375"/>
+    <col customWidth="1" min="31" max="31" style="2" width="14.140625"/>
+    <col customWidth="1" min="32" max="33" style="2" width="12.7109375"/>
+    <col customWidth="1" min="34" max="34" style="5" width="42.28125"/>
+    <col min="35" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" ht="33">
@@ -1372,28 +1375,29 @@
       <c r="W1" s="1"/>
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
-      <c r="Z1" s="7" t="s">
+      <c r="Z1" s="1"/>
+      <c r="AA1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="AA1" s="7" t="s">
+      <c r="AB1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="AB1" s="7" t="s">
+      <c r="AC1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="AC1" s="7" t="s">
+      <c r="AD1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="AD1" s="7" t="s">
+      <c r="AE1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="AE1" s="7" t="s">
+      <c r="AF1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="AF1" s="7" t="s">
+      <c r="AG1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="AG1" s="5"/>
+      <c r="AH1" s="5"/>
     </row>
     <row r="2" ht="23.25">
       <c r="A2" s="2"/>
@@ -1410,13 +1414,14 @@
       <c r="W2" s="1"/>
       <c r="X2" s="1"/>
       <c r="Y2" s="1"/>
-      <c r="Z2" s="7"/>
+      <c r="Z2" s="1"/>
       <c r="AA2" s="7"/>
       <c r="AB2" s="7"/>
       <c r="AC2" s="7"/>
       <c r="AD2" s="7"/>
       <c r="AE2" s="7"/>
       <c r="AF2" s="7"/>
+      <c r="AG2" s="7"/>
     </row>
     <row r="3" ht="18">
       <c r="A3" s="2"/>
@@ -1431,13 +1436,14 @@
       <c r="W3" s="1"/>
       <c r="X3" s="1"/>
       <c r="Y3" s="1"/>
-      <c r="Z3" s="7"/>
+      <c r="Z3" s="1"/>
       <c r="AA3" s="7"/>
       <c r="AB3" s="7"/>
       <c r="AC3" s="7"/>
       <c r="AD3" s="7"/>
       <c r="AE3" s="7"/>
       <c r="AF3" s="7"/>
+      <c r="AG3" s="7"/>
     </row>
     <row r="4" ht="18">
       <c r="A4" s="2"/>
@@ -1453,13 +1459,14 @@
       <c r="W4" s="1"/>
       <c r="X4" s="1"/>
       <c r="Y4" s="1"/>
-      <c r="Z4" s="7"/>
+      <c r="Z4" s="1"/>
       <c r="AA4" s="7"/>
       <c r="AB4" s="7"/>
       <c r="AC4" s="7"/>
       <c r="AD4" s="7"/>
       <c r="AE4" s="7"/>
       <c r="AF4" s="7"/>
+      <c r="AG4" s="7"/>
     </row>
     <row r="5" ht="23.25">
       <c r="A5" s="2"/>
@@ -1474,13 +1481,14 @@
       <c r="W5" s="1"/>
       <c r="X5" s="1"/>
       <c r="Y5" s="1"/>
-      <c r="Z5" s="7"/>
+      <c r="Z5" s="1"/>
       <c r="AA5" s="7"/>
       <c r="AB5" s="7"/>
       <c r="AC5" s="7"/>
       <c r="AD5" s="7"/>
       <c r="AE5" s="7"/>
       <c r="AF5" s="7"/>
+      <c r="AG5" s="7"/>
     </row>
     <row r="6" ht="24" customHeight="1">
       <c r="A6" s="2"/>
@@ -1494,13 +1502,14 @@
       <c r="W6" s="1"/>
       <c r="X6" s="1"/>
       <c r="Y6" s="1"/>
-      <c r="Z6" s="7"/>
+      <c r="Z6" s="1"/>
       <c r="AA6" s="7"/>
       <c r="AB6" s="7"/>
       <c r="AC6" s="7"/>
       <c r="AD6" s="7"/>
       <c r="AE6" s="7"/>
       <c r="AF6" s="7"/>
+      <c r="AG6" s="7"/>
     </row>
     <row r="7" ht="18">
       <c r="A7" s="10" t="s">
@@ -1578,7 +1587,7 @@
       <c r="Y7" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="Z7" s="13" t="s">
+      <c r="Z7" s="12" t="s">
         <v>34</v>
       </c>
       <c r="AA7" s="13" t="s">
@@ -1599,16 +1608,19 @@
       <c r="AF7" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="AG7" s="5" t="s">
+      <c r="AG7" s="13" t="s">
         <v>41</v>
+      </c>
+      <c r="AH7" s="5" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="8" ht="36">
       <c r="A8" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C8" s="15">
         <v>171.88</v>
@@ -1635,7 +1647,7 @@
         <v>341.57999999999998</v>
       </c>
       <c r="M8" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N8" s="18">
         <v>321.14999999999998</v>
@@ -1673,48 +1685,51 @@
       <c r="Y8" s="19">
         <v>418.17000000000002</v>
       </c>
-      <c r="Z8" s="20">
-        <f>MIN(C8:Y8)</f>
+      <c r="Z8" s="18">
+        <v>397.13</v>
+      </c>
+      <c r="AA8" s="20">
+        <f>MIN(C8:Z8)</f>
         <v>171.88</v>
       </c>
-      <c r="AA8" s="21">
-        <f>MAX(C8:Y8)</f>
+      <c r="AB8" s="21">
+        <f>MAX(C8:Z8)</f>
         <v>418.17000000000002</v>
       </c>
-      <c r="AB8" s="21">
-        <f>AVERAGE(C8:Y8)</f>
-        <v>346.57684210526332</v>
-      </c>
       <c r="AC8" s="21">
-        <f>AVERAGE(Q8:Y8)</f>
-        <v>378.22999999999996</v>
-      </c>
-      <c r="AD8" s="22">
-        <f>(AC8/AB8)-1</f>
-        <v>9.1330850908736938e-002</v>
+        <f>AVERAGE(C8:Z8)</f>
+        <v>349.10450000000014</v>
+      </c>
+      <c r="AD8" s="21">
+        <f>AVERAGE(Q8:Z8)</f>
+        <v>380.12</v>
       </c>
       <c r="AE8" s="22">
-        <f>(AC8/Z8)-1</f>
-        <v>1.200546893181289</v>
+        <f>(AD8/AC8)-1</f>
+        <v>8.8843025512417739e-002</v>
       </c>
       <c r="AF8" s="22">
-        <f>(AA8/Z8)-1</f>
+        <f>(AD8/AA8)-1</f>
+        <v>1.211542936932744</v>
+      </c>
+      <c r="AG8" s="22">
+        <f>(AB8/AA8)-1</f>
         <v>1.4329183151035609</v>
       </c>
-      <c r="AG8" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="AH8" s="24">
+      <c r="AH8" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="AI8" s="24">
         <f>C2*1</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" ht="36">
       <c r="A9" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" s="16"/>
       <c r="D9" s="25">
@@ -1726,7 +1741,7 @@
         <v>686</v>
       </c>
       <c r="H9" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I9" s="17">
         <v>613.99000000000001</v>
@@ -1779,44 +1794,47 @@
       <c r="Y9" s="18">
         <v>978.75</v>
       </c>
-      <c r="Z9" s="20">
-        <f>MIN(C9:Y9)</f>
+      <c r="Z9" s="18">
+        <v>978.75</v>
+      </c>
+      <c r="AA9" s="20">
+        <f>MIN(C9:Z9)</f>
         <v>200.47999999999999</v>
       </c>
-      <c r="AA9" s="21">
-        <f>MAX(C9:Y9)</f>
+      <c r="AB9" s="21">
+        <f>MAX(C9:Z9)</f>
         <v>978.75</v>
       </c>
-      <c r="AB9" s="21">
-        <f>AVERAGE(C9:Y9)</f>
-        <v>810.12473684210534</v>
-      </c>
       <c r="AC9" s="21">
-        <f>AVERAGE(Q9:Y9)</f>
-        <v>892.68888888888887</v>
-      </c>
-      <c r="AD9" s="22">
-        <f>(AC9/AB9)-1</f>
-        <v>0.10191535734190937</v>
+        <f>AVERAGE(C9:Z9)</f>
+        <v>818.55600000000004</v>
+      </c>
+      <c r="AD9" s="21">
+        <f>AVERAGE(Q9:Z9)</f>
+        <v>901.29500000000007</v>
       </c>
       <c r="AE9" s="22">
-        <f>(AC9/Z9)-1</f>
-        <v>3.4527578256628537</v>
+        <f>(AD9/AC9)-1</f>
+        <v>0.1010792175489521</v>
       </c>
       <c r="AF9" s="22">
-        <f>(AA9/Z9)-1</f>
+        <f>(AD9/AA9)-1</f>
+        <v>3.4956853551476463</v>
+      </c>
+      <c r="AG9" s="22">
+        <f>(AB9/AA9)-1</f>
         <v>3.8820331205107745</v>
       </c>
-      <c r="AG9" s="23" t="s">
-        <v>47</v>
+      <c r="AH9" s="23" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="10" ht="36">
       <c r="A10" s="26" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C10" s="28"/>
       <c r="D10" s="25">
@@ -1881,44 +1899,47 @@
       <c r="Y10" s="18">
         <v>709.99000000000001</v>
       </c>
-      <c r="Z10" s="20">
-        <f>MIN(C10:Y10)</f>
+      <c r="Z10" s="18">
+        <v>709.99000000000001</v>
+      </c>
+      <c r="AA10" s="20">
+        <f>MIN(C10:Z10)</f>
         <v>284.13</v>
       </c>
-      <c r="AA10" s="21">
-        <f>MAX(C10:Y10)</f>
+      <c r="AB10" s="21">
+        <f>MAX(C10:Z10)</f>
         <v>717.78999999999996</v>
       </c>
-      <c r="AB10" s="21">
-        <f>AVERAGE(C10:Y10)</f>
-        <v>604.33849999999995</v>
-      </c>
       <c r="AC10" s="21">
-        <f>AVERAGE(Q10:Y10)</f>
-        <v>666.87777777777774</v>
-      </c>
-      <c r="AD10" s="22">
-        <f>(AC10/AB10)-1</f>
-        <v>0.10348385512056213</v>
+        <f>AVERAGE(C10:Z10)</f>
+        <v>609.36952380952368</v>
+      </c>
+      <c r="AD10" s="21">
+        <f>AVERAGE(Q10:Z10)</f>
+        <v>671.18899999999996</v>
       </c>
       <c r="AE10" s="22">
-        <f>(AC10/Z10)-1</f>
-        <v>1.3470868186315341</v>
+        <f>(AD10/AC10)-1</f>
+        <v>0.10144825721510764</v>
       </c>
       <c r="AF10" s="22">
-        <f>(AA10/Z10)-1</f>
+        <f>(AD10/AA10)-1</f>
+        <v>1.3622602329919404</v>
+      </c>
+      <c r="AG10" s="22">
+        <f>(AB10/AA10)-1</f>
         <v>1.5262731848097699</v>
       </c>
-      <c r="AG10" s="23" t="s">
-        <v>49</v>
+      <c r="AH10" s="23" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="11" ht="36">
       <c r="A11" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C11" s="16"/>
       <c r="D11" s="16"/>
@@ -1977,44 +1998,47 @@
       <c r="Y11" s="19">
         <v>824.50999999999999</v>
       </c>
-      <c r="Z11" s="20">
-        <f>MIN(C11:Y11)</f>
+      <c r="Z11" s="18">
+        <v>796.15999999999997</v>
+      </c>
+      <c r="AA11" s="20">
+        <f>MIN(C11:Z11)</f>
         <v>685.71000000000004</v>
       </c>
-      <c r="AA11" s="21">
-        <f>MAX(C11:Y11)</f>
+      <c r="AB11" s="21">
+        <f>MAX(C11:Z11)</f>
         <v>863.60000000000002</v>
       </c>
-      <c r="AB11" s="21">
-        <f>AVERAGE(C11:Y11)</f>
-        <v>787.89588235294116</v>
-      </c>
       <c r="AC11" s="21">
-        <f>AVERAGE(Q11:Y11)</f>
-        <v>810.80444444444447</v>
-      </c>
-      <c r="AD11" s="22">
-        <f>(AC11/AB11)-1</f>
-        <v>2.9075621036487753e-002</v>
+        <f>AVERAGE(C11:Z11)</f>
+        <v>788.35500000000002</v>
+      </c>
+      <c r="AD11" s="21">
+        <f>AVERAGE(Q11:Z11)</f>
+        <v>809.33999999999992</v>
       </c>
       <c r="AE11" s="22">
-        <f>(AC11/Z11)-1</f>
-        <v>0.18243053833901279</v>
+        <f>(AD11/AC11)-1</f>
+        <v>2.6618718724432444e-002</v>
       </c>
       <c r="AF11" s="22">
-        <f>(AA11/Z11)-1</f>
+        <f>(AD11/AA11)-1</f>
+        <v>0.18029487684298018</v>
+      </c>
+      <c r="AG11" s="22">
+        <f>(AB11/AA11)-1</f>
         <v>0.25942453807002952</v>
       </c>
-      <c r="AG11" s="23" t="s">
-        <v>51</v>
+      <c r="AH11" s="23" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="12" ht="18">
       <c r="A12" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C12" s="16"/>
       <c r="D12" s="17">
@@ -2079,44 +2103,47 @@
       <c r="Y12" s="18">
         <v>547.98000000000002</v>
       </c>
-      <c r="Z12" s="20">
-        <f>MIN(C12:Y12)</f>
+      <c r="Z12" s="18">
+        <v>547.98000000000002</v>
+      </c>
+      <c r="AA12" s="20">
+        <f>MIN(C12:Z12)</f>
         <v>465</v>
       </c>
-      <c r="AA12" s="21">
-        <f>MAX(C12:Y12)</f>
+      <c r="AB12" s="21">
+        <f>MAX(C12:Z12)</f>
         <v>623.12</v>
       </c>
-      <c r="AB12" s="21">
-        <f>AVERAGE(C12:Y12)</f>
-        <v>552.63599999999974</v>
-      </c>
       <c r="AC12" s="21">
-        <f>AVERAGE(Q12:Y12)</f>
-        <v>542.19999999999993</v>
-      </c>
-      <c r="AD12" s="22">
-        <f>(AC12/AB12)-1</f>
-        <v>-1.8884039403874953e-002</v>
+        <f>AVERAGE(C12:Z12)</f>
+        <v>552.41428571428548</v>
+      </c>
+      <c r="AD12" s="21">
+        <f>AVERAGE(Q12:Z12)</f>
+        <v>542.77799999999991</v>
       </c>
       <c r="AE12" s="22">
-        <f>(AC12/Z12)-1</f>
-        <v>0.16602150537634386</v>
+        <f>(AD12/AC12)-1</f>
+        <v>-1.7443947348004585e-002</v>
       </c>
       <c r="AF12" s="22">
-        <f>(AA12/Z12)-1</f>
+        <f>(AD12/AA12)-1</f>
+        <v>0.16726451612903204</v>
+      </c>
+      <c r="AG12" s="22">
+        <f>(AB12/AA12)-1</f>
         <v>0.34004301075268817</v>
       </c>
-      <c r="AG12" s="23" t="s">
-        <v>54</v>
+      <c r="AH12" s="23" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="13" ht="36">
       <c r="A13" s="26" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C13" s="28"/>
       <c r="D13" s="25">
@@ -2152,19 +2179,19 @@
         <v>1084.8299999999999</v>
       </c>
       <c r="P13" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Q13" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="R13" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="S13" s="30">
         <v>1426.5699999999999</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="U13" s="25">
         <v>592.17999999999995</v>
@@ -2179,46 +2206,49 @@
         <v>623.23000000000002</v>
       </c>
       <c r="Y13" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z13" s="20">
-        <f>MIN(C13:Y13)</f>
+        <v>45</v>
+      </c>
+      <c r="Z13" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA13" s="20">
+        <f>MIN(C13:Z13)</f>
         <v>592.17999999999995</v>
       </c>
-      <c r="AA13" s="21">
-        <f>MAX(C13:Y13)</f>
+      <c r="AB13" s="21">
+        <f>MAX(C13:Z13)</f>
         <v>1426.5699999999999</v>
       </c>
-      <c r="AB13" s="21">
-        <f>AVERAGE(C13:Y13)</f>
+      <c r="AC13" s="21">
+        <f>AVERAGE(C13:Z13)</f>
         <v>853.96466666666674</v>
       </c>
-      <c r="AC13" s="21">
-        <f>AVERAGE(Q13:Y13)</f>
+      <c r="AD13" s="21">
+        <f>AVERAGE(Q13:Z13)</f>
         <v>771.42200000000003</v>
       </c>
-      <c r="AD13" s="22">
-        <f>(AC13/AB13)-1</f>
+      <c r="AE13" s="22">
+        <f>(AD13/AC13)-1</f>
         <v>-9.665817555293077e-002</v>
       </c>
-      <c r="AE13" s="22">
-        <f>(AC13/Z13)-1</f>
+      <c r="AF13" s="22">
+        <f>(AD13/AA13)-1</f>
         <v>0.30268161707588925</v>
       </c>
-      <c r="AF13" s="22">
-        <f>(AA13/Z13)-1</f>
+      <c r="AG13" s="22">
+        <f>(AB13/AA13)-1</f>
         <v>1.4090141511027054</v>
       </c>
-      <c r="AG13" s="23" t="s">
-        <v>57</v>
+      <c r="AH13" s="23" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="14" ht="18">
       <c r="A14" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
@@ -2275,44 +2305,47 @@
       <c r="Y14" s="18">
         <v>678</v>
       </c>
-      <c r="Z14" s="20">
-        <f>MIN(C14:Y14)</f>
+      <c r="Z14" s="18">
+        <v>597.99000000000001</v>
+      </c>
+      <c r="AA14" s="20">
+        <f>MIN(C14:Z14)</f>
         <v>580.98000000000002</v>
       </c>
-      <c r="AA14" s="21">
-        <f>MAX(C14:Y14)</f>
+      <c r="AB14" s="21">
+        <f>MAX(C14:Z14)</f>
         <v>709.99000000000001</v>
       </c>
-      <c r="AB14" s="21">
-        <f>AVERAGE(C14:Y14)</f>
-        <v>653.76499999999987</v>
-      </c>
       <c r="AC14" s="21">
-        <f>AVERAGE(Q14:Y14)</f>
-        <v>676.88333333333344</v>
-      </c>
-      <c r="AD14" s="22">
-        <f>(AC14/AB14)-1</f>
-        <v>3.5361840008770073e-002</v>
+        <f>AVERAGE(C14:Z14)</f>
+        <v>650.48411764705872</v>
+      </c>
+      <c r="AD14" s="21">
+        <f>AVERAGE(Q14:Z14)</f>
+        <v>668.99400000000003</v>
       </c>
       <c r="AE14" s="22">
-        <f>(AC14/Z14)-1</f>
-        <v>0.16507166052761435</v>
+        <f>(AD14/AC14)-1</f>
+        <v>2.8455548491937988e-002</v>
       </c>
       <c r="AF14" s="22">
-        <f>(AA14/Z14)-1</f>
+        <f>(AD14/AA14)-1</f>
+        <v>0.1514923061034803</v>
+      </c>
+      <c r="AG14" s="22">
+        <f>(AB14/AA14)-1</f>
         <v>0.22205583668973117</v>
       </c>
-      <c r="AG14" s="23" t="s">
-        <v>59</v>
+      <c r="AH14" s="23" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="15" ht="18">
       <c r="A15" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C15" s="16"/>
       <c r="D15" s="16"/>
@@ -2369,44 +2402,47 @@
       <c r="Y15" s="17">
         <v>679</v>
       </c>
-      <c r="Z15" s="20">
-        <f>MIN(C15:Y15)</f>
+      <c r="Z15" s="17">
+        <v>679</v>
+      </c>
+      <c r="AA15" s="20">
+        <f>MIN(C15:Z15)</f>
         <v>622.63</v>
       </c>
-      <c r="AA15" s="21">
-        <f>MAX(C15:Y15)</f>
+      <c r="AB15" s="21">
+        <f>MAX(C15:Z15)</f>
         <v>728.61000000000001</v>
       </c>
-      <c r="AB15" s="21">
-        <f>AVERAGE(C15:Y15)</f>
-        <v>682.04812499999991</v>
-      </c>
       <c r="AC15" s="21">
-        <f>AVERAGE(Q15:Y15)</f>
-        <v>694.21222222222218</v>
-      </c>
-      <c r="AD15" s="22">
-        <f>(AC15/AB15)-1</f>
-        <v>1.7834661186440837e-002</v>
+        <f>AVERAGE(C15:Z15)</f>
+        <v>681.86882352941166</v>
+      </c>
+      <c r="AD15" s="21">
+        <f>AVERAGE(Q15:Z15)</f>
+        <v>692.69100000000003</v>
       </c>
       <c r="AE15" s="22">
-        <f>(AC15/Z15)-1</f>
-        <v>0.11496751236243385</v>
+        <f>(AD15/AC15)-1</f>
+        <v>1.5871346653703711e-002</v>
       </c>
       <c r="AF15" s="22">
-        <f>(AA15/Z15)-1</f>
+        <f>(AD15/AA15)-1</f>
+        <v>0.11252429211570281</v>
+      </c>
+      <c r="AG15" s="22">
+        <f>(AB15/AA15)-1</f>
         <v>0.17021344940012528</v>
       </c>
-      <c r="AG15" s="23" t="s">
-        <v>61</v>
+      <c r="AH15" s="23" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="16" ht="18">
       <c r="A16" s="26" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C16" s="28"/>
       <c r="D16" s="29"/>
@@ -2469,44 +2505,47 @@
       <c r="Y16" s="17">
         <v>10799.02</v>
       </c>
-      <c r="Z16" s="20">
-        <f>MIN(C16:Y16)</f>
+      <c r="Z16" s="17">
+        <v>10798.99</v>
+      </c>
+      <c r="AA16" s="20">
+        <f>MIN(C16:Z16)</f>
         <v>9100</v>
       </c>
-      <c r="AA16" s="21">
-        <f>MAX(C16:Y16)</f>
+      <c r="AB16" s="21">
+        <f>MAX(C16:Z16)</f>
         <v>11315.18</v>
       </c>
-      <c r="AB16" s="21">
-        <f>AVERAGE(C16:Y16)</f>
-        <v>9843.9163157894709</v>
-      </c>
       <c r="AC16" s="21">
-        <f>AVERAGE(Q16:Y16)</f>
-        <v>10627.263333333334</v>
-      </c>
-      <c r="AD16" s="22">
-        <f>(AC16/AB16)-1</f>
-        <v>7.9576765223754231e-002</v>
+        <f>AVERAGE(C16:Z16)</f>
+        <v>9891.6699999999964</v>
+      </c>
+      <c r="AD16" s="21">
+        <f>AVERAGE(Q16:Z16)</f>
+        <v>10644.436000000002</v>
       </c>
       <c r="AE16" s="22">
-        <f>(AC16/Z16)-1</f>
-        <v>0.16783113553113571</v>
+        <f>(AD16/AC16)-1</f>
+        <v>7.6101002156360398e-002</v>
       </c>
       <c r="AF16" s="22">
-        <f>(AA16/Z16)-1</f>
+        <f>(AD16/AA16)-1</f>
+        <v>0.16971824175824191</v>
+      </c>
+      <c r="AG16" s="22">
+        <f>(AB16/AA16)-1</f>
         <v>0.24342637362637376</v>
       </c>
-      <c r="AG16" s="23" t="s">
-        <v>63</v>
+      <c r="AH16" s="23" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="17" ht="36">
       <c r="A17" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C17" s="16"/>
       <c r="D17" s="16"/>
@@ -2561,44 +2600,47 @@
       <c r="Y17" s="18">
         <v>1610.8900000000001</v>
       </c>
-      <c r="Z17" s="20">
-        <f>MIN(C17:Y17)</f>
+      <c r="Z17" s="18">
+        <v>1558.77</v>
+      </c>
+      <c r="AA17" s="20">
+        <f>MIN(C17:Z17)</f>
         <v>1297.6199999999999</v>
       </c>
-      <c r="AA17" s="21">
-        <f>MAX(C17:Y17)</f>
+      <c r="AB17" s="21">
+        <f>MAX(C17:Z17)</f>
         <v>1697.6199999999999</v>
       </c>
-      <c r="AB17" s="21">
-        <f>AVERAGE(C17:Y17)</f>
-        <v>1538.7153333333331</v>
-      </c>
       <c r="AC17" s="21">
-        <f>AVERAGE(Q17:Y17)</f>
-        <v>1584.6888888888889</v>
-      </c>
-      <c r="AD17" s="22">
-        <f>(AC17/AB17)-1</f>
-        <v>2.9877882256468258e-002</v>
+        <f>AVERAGE(C17:Z17)</f>
+        <v>1539.9687499999998</v>
+      </c>
+      <c r="AD17" s="21">
+        <f>AVERAGE(Q17:Z17)</f>
+        <v>1582.097</v>
       </c>
       <c r="AE17" s="22">
-        <f>(AC17/Z17)-1</f>
-        <v>0.22122723824300561</v>
+        <f>(AD17/AC17)-1</f>
+        <v>2.7356561618539388e-002</v>
       </c>
       <c r="AF17" s="22">
-        <f>(AA17/Z17)-1</f>
+        <f>(AD17/AA17)-1</f>
+        <v>0.21922982074875552</v>
+      </c>
+      <c r="AG17" s="22">
+        <f>(AB17/AA17)-1</f>
         <v>0.30825665449052875</v>
       </c>
-      <c r="AG17" s="23" t="s">
-        <v>65</v>
+      <c r="AH17" s="23" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="18" ht="18">
       <c r="A18" s="26" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C18" s="28"/>
       <c r="D18" s="29"/>
@@ -2607,100 +2649,103 @@
         <v>2279</v>
       </c>
       <c r="G18" s="29" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H18" s="29" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I18" s="29" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J18" s="29" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K18" s="29" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L18" s="29" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M18" s="29" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="N18" s="29" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="O18" s="29" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="P18" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Q18" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="R18" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S18" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="V18" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="W18" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="X18" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Y18" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="Z18" s="20">
-        <f>MIN(C18:Y18)</f>
+        <v>68</v>
+      </c>
+      <c r="Z18" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="AA18" s="20">
+        <f>MIN(C18:Z18)</f>
         <v>2279</v>
       </c>
-      <c r="AA18" s="21">
-        <f>MAX(C18:Y18)</f>
+      <c r="AB18" s="21">
+        <f>MAX(C18:Z18)</f>
         <v>2279</v>
       </c>
-      <c r="AB18" s="21">
-        <f>AVERAGE(C18:Y18)</f>
+      <c r="AC18" s="21">
+        <f>AVERAGE(C18:Z18)</f>
         <v>2279</v>
       </c>
-      <c r="AC18" s="21" t="e">
-        <f>AVERAGE(Q18:Y18)</f>
+      <c r="AD18" s="21" t="e">
+        <f>AVERAGE(Q18:Z18)</f>
         <v>#NUM!</v>
       </c>
-      <c r="AD18" s="22" t="e">
-        <f>(AC18/AB18)-1</f>
+      <c r="AE18" s="22" t="e">
+        <f>(AD18/AC18)-1</f>
         <v>#NUM!</v>
       </c>
-      <c r="AE18" s="22" t="e">
-        <f>(AC18/Z18)-1</f>
+      <c r="AF18" s="22" t="e">
+        <f>(AD18/AA18)-1</f>
         <v>#NUM!</v>
       </c>
-      <c r="AF18" s="22">
-        <f>(AA18/Z18)-1</f>
+      <c r="AG18" s="22">
+        <f>(AB18/AA18)-1</f>
         <v>0</v>
       </c>
-      <c r="AG18" s="23" t="s">
-        <v>68</v>
+      <c r="AH18" s="23" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="19" ht="18">
       <c r="A19" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C19" s="25">
         <v>176.69</v>
@@ -2765,44 +2810,47 @@
       <c r="Y19" s="30">
         <v>260</v>
       </c>
-      <c r="Z19" s="20">
-        <f>MIN(C19:Y19)</f>
+      <c r="Z19" s="30">
+        <v>260</v>
+      </c>
+      <c r="AA19" s="20">
+        <f>MIN(C19:Z19)</f>
         <v>145</v>
       </c>
-      <c r="AA19" s="21">
-        <f>MAX(C19:Y19)</f>
+      <c r="AB19" s="21">
+        <f>MAX(C19:Z19)</f>
         <v>260</v>
       </c>
-      <c r="AB19" s="21">
-        <f>AVERAGE(C19:Y19)</f>
-        <v>200.94649999999996</v>
-      </c>
       <c r="AC19" s="21">
-        <f>AVERAGE(Q19:Y19)</f>
-        <v>236.94444444444446</v>
-      </c>
-      <c r="AD19" s="22">
-        <f>(AC19/AB19)-1</f>
-        <v>0.17914193302418568</v>
+        <f>AVERAGE(C19:Z19)</f>
+        <v>203.7585714285714</v>
+      </c>
+      <c r="AD19" s="21">
+        <f>AVERAGE(Q19:Z19)</f>
+        <v>239.25</v>
       </c>
       <c r="AE19" s="22">
-        <f>(AC19/Z19)-1</f>
-        <v>0.63409961685823757</v>
+        <f>(AD19/AC19)-1</f>
+        <v>0.17418373284910027</v>
       </c>
       <c r="AF19" s="22">
-        <f>(AA19/Z19)-1</f>
+        <f>(AD19/AA19)-1</f>
+        <v>0.64999999999999991</v>
+      </c>
+      <c r="AG19" s="22">
+        <f>(AB19/AA19)-1</f>
         <v>0.7931034482758621</v>
       </c>
-      <c r="AG19" s="23" t="s">
-        <v>70</v>
+      <c r="AH19" s="23" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="20" ht="18">
       <c r="A20" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C20" s="17"/>
       <c r="D20" s="17"/>
@@ -2851,7 +2899,7 @@
         <v>212.31</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="V20" s="19">
         <v>229.94999999999999</v>
@@ -2865,44 +2913,47 @@
       <c r="Y20" s="30">
         <v>270</v>
       </c>
-      <c r="Z20" s="20">
-        <f>MIN(C20:Y20)</f>
+      <c r="Z20" s="30">
+        <v>270</v>
+      </c>
+      <c r="AA20" s="20">
+        <f>MIN(C20:Z20)</f>
         <v>176.91999999999999</v>
       </c>
-      <c r="AA20" s="21">
-        <f>MAX(C20:Y20)</f>
+      <c r="AB20" s="21">
+        <f>MAX(C20:Z20)</f>
         <v>270</v>
       </c>
-      <c r="AB20" s="21">
-        <f>AVERAGE(C20:Y20)</f>
-        <v>200.04277777777779</v>
-      </c>
       <c r="AC20" s="21">
-        <f>AVERAGE(Q20:Y20)</f>
-        <v>224.64875000000001</v>
-      </c>
-      <c r="AD20" s="22">
-        <f>(AC20/AB20)-1</f>
-        <v>0.12300355201804059</v>
+        <f>AVERAGE(C20:Z20)</f>
+        <v>203.72473684210527</v>
+      </c>
+      <c r="AD20" s="21">
+        <f>AVERAGE(Q20:Z20)</f>
+        <v>229.6877777777778</v>
       </c>
       <c r="AE20" s="22">
-        <f>(AC20/Z20)-1</f>
-        <v>0.26977588740673775</v>
+        <f>(AD20/AC20)-1</f>
+        <v>0.12744176940964658</v>
       </c>
       <c r="AF20" s="22">
-        <f>(AA20/Z20)-1</f>
+        <f>(AD20/AA20)-1</f>
+        <v>0.2982578440977719</v>
+      </c>
+      <c r="AG20" s="22">
+        <f>(AB20/AA20)-1</f>
         <v>0.52611349762604576</v>
       </c>
-      <c r="AG20" s="23" t="s">
-        <v>72</v>
+      <c r="AH20" s="23" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="21" ht="18">
       <c r="A21" s="26" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C21" s="29"/>
       <c r="D21" s="29"/>
@@ -2915,31 +2966,31 @@
         <v>396.77999999999997</v>
       </c>
       <c r="I21" s="29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J21" s="29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K21" s="29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L21" s="29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M21" s="29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N21" s="29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="O21" s="29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P21" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Q21" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="R21" s="17">
         <v>413</v>
@@ -2951,7 +3002,7 @@
         <v>408.87</v>
       </c>
       <c r="U21" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="V21" s="17">
         <v>453.04000000000002</v>
@@ -2965,44 +3016,47 @@
       <c r="Y21" s="17">
         <v>349</v>
       </c>
-      <c r="Z21" s="20">
-        <f>MIN(C21:Y21)</f>
+      <c r="Z21" s="17">
         <v>349</v>
       </c>
-      <c r="AA21" s="21">
-        <f>MAX(C21:Y21)</f>
+      <c r="AA21" s="20">
+        <f>MIN(C21:Z21)</f>
+        <v>349</v>
+      </c>
+      <c r="AB21" s="21">
+        <f>MAX(C21:Z21)</f>
         <v>453.04000000000002</v>
       </c>
-      <c r="AB21" s="21">
-        <f>AVERAGE(C21:Y21)</f>
-        <v>408.05888888888887</v>
-      </c>
       <c r="AC21" s="21">
-        <f>AVERAGE(Q21:Y21)</f>
-        <v>411.28142857142853</v>
-      </c>
-      <c r="AD21" s="22">
-        <f>(AC21/AB21)-1</f>
-        <v>7.8972417224247859e-003</v>
+        <f>AVERAGE(C21:Z21)</f>
+        <v>402.15299999999996</v>
+      </c>
+      <c r="AD21" s="21">
+        <f>AVERAGE(Q21:Z21)</f>
+        <v>403.49624999999997</v>
       </c>
       <c r="AE21" s="22">
-        <f>(AC21/Z21)-1</f>
-        <v>0.17845681539091274</v>
+        <f>(AD21/AC21)-1</f>
+        <v>3.3401466605993413e-003</v>
       </c>
       <c r="AF21" s="22">
-        <f>(AA21/Z21)-1</f>
+        <f>(AD21/AA21)-1</f>
+        <v>0.15614971346704865</v>
+      </c>
+      <c r="AG21" s="22">
+        <f>(AB21/AA21)-1</f>
         <v>0.29810888252148993</v>
       </c>
-      <c r="AG21" s="32" t="s">
-        <v>74</v>
+      <c r="AH21" s="32" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="22" ht="54">
       <c r="A22" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C22" s="17"/>
       <c r="D22" s="17"/>
@@ -3065,44 +3119,47 @@
       <c r="Y22" s="17">
         <v>600</v>
       </c>
-      <c r="Z22" s="20">
-        <f>MIN(C22:Y22)</f>
+      <c r="Z22" s="17">
+        <v>600</v>
+      </c>
+      <c r="AA22" s="20">
+        <f>MIN(C22:Z22)</f>
         <v>550</v>
       </c>
-      <c r="AA22" s="21">
-        <f>MAX(C22:Y22)</f>
+      <c r="AB22" s="21">
+        <f>MAX(C22:Z22)</f>
         <v>600</v>
       </c>
-      <c r="AB22" s="21">
-        <f>AVERAGE(C22:Y22)</f>
-        <v>572.63157894736844</v>
-      </c>
       <c r="AC22" s="21">
-        <f>AVERAGE(Q22:Y22)</f>
-        <v>597.77777777777783</v>
-      </c>
-      <c r="AD22" s="22">
-        <f>(AC22/AB22)-1</f>
-        <v>4.3913398692810413e-002</v>
+        <f>AVERAGE(C22:Z22)</f>
+        <v>574</v>
+      </c>
+      <c r="AD22" s="21">
+        <f>AVERAGE(Q22:Z22)</f>
+        <v>598</v>
       </c>
       <c r="AE22" s="22">
-        <f>(AC22/Z22)-1</f>
-        <v>8.6868686868686984e-002</v>
+        <f>(AD22/AC22)-1</f>
+        <v>4.1811846689895571e-002</v>
       </c>
       <c r="AF22" s="22">
-        <f>(AA22/Z22)-1</f>
+        <f>(AD22/AA22)-1</f>
+        <v>8.7272727272727169e-002</v>
+      </c>
+      <c r="AG22" s="22">
+        <f>(AB22/AA22)-1</f>
         <v>9.0909090909090828e-002</v>
       </c>
-      <c r="AG22" s="23" t="s">
-        <v>77</v>
+      <c r="AH22" s="23" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="23" ht="18">
       <c r="A23" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C23" s="17"/>
       <c r="D23" s="17"/>
@@ -3165,44 +3222,47 @@
       <c r="Y23" s="19">
         <v>549</v>
       </c>
-      <c r="Z23" s="20">
-        <f>MIN(C23:Y23)</f>
+      <c r="Z23" s="19">
+        <v>549</v>
+      </c>
+      <c r="AA23" s="20">
+        <f>MIN(C23:Z23)</f>
         <v>329</v>
       </c>
-      <c r="AA23" s="21">
-        <f>MAX(C23:Y23)</f>
+      <c r="AB23" s="21">
+        <f>MAX(C23:Z23)</f>
         <v>549</v>
       </c>
-      <c r="AB23" s="21">
-        <f>AVERAGE(C23:Y23)</f>
-        <v>483.14473684210526</v>
-      </c>
       <c r="AC23" s="21">
-        <f>AVERAGE(Q23:Y23)</f>
-        <v>527.20555555555563</v>
-      </c>
-      <c r="AD23" s="22">
-        <f>(AC23/AB23)-1</f>
-        <v>9.1195899186313101e-002</v>
+        <f>AVERAGE(C23:Z23)</f>
+        <v>486.4375</v>
+      </c>
+      <c r="AD23" s="21">
+        <f>AVERAGE(Q23:Z23)</f>
+        <v>529.38499999999999</v>
       </c>
       <c r="AE23" s="22">
-        <f>(AC23/Z23)-1</f>
-        <v>0.60244849712934845</v>
+        <f>(AD23/AC23)-1</f>
+        <v>8.8289862520878781e-002</v>
       </c>
       <c r="AF23" s="22">
-        <f>(AA23/Z23)-1</f>
+        <f>(AD23/AA23)-1</f>
+        <v>0.60907294832826753</v>
+      </c>
+      <c r="AG23" s="22">
+        <f>(AB23/AA23)-1</f>
         <v>0.66869300911854102</v>
       </c>
-      <c r="AG23" s="23" t="s">
-        <v>80</v>
+      <c r="AH23" s="23" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="24" ht="18">
       <c r="A24" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C24" s="17"/>
       <c r="D24" s="17"/>
@@ -3265,44 +3325,47 @@
       <c r="Y24" s="18">
         <v>472.97000000000003</v>
       </c>
-      <c r="Z24" s="20">
-        <f>MIN(C24:Y24)</f>
+      <c r="Z24" s="18">
+        <v>435.14999999999998</v>
+      </c>
+      <c r="AA24" s="20">
+        <f>MIN(C24:Z24)</f>
         <v>371.14999999999998</v>
       </c>
-      <c r="AA24" s="21">
-        <f>MAX(C24:Y24)</f>
+      <c r="AB24" s="21">
+        <f>MAX(C24:Z24)</f>
         <v>513.71000000000004</v>
       </c>
-      <c r="AB24" s="21">
-        <f>AVERAGE(C24:Y24)</f>
-        <v>446.79263157894724</v>
-      </c>
       <c r="AC24" s="21">
-        <f>AVERAGE(Q24:Y24)</f>
-        <v>474.48222222222222</v>
-      </c>
-      <c r="AD24" s="22">
-        <f>(AC24/AB24)-1</f>
-        <v>6.1974143453129571e-002</v>
+        <f>AVERAGE(C24:Z24)</f>
+        <v>446.21049999999985</v>
+      </c>
+      <c r="AD24" s="21">
+        <f>AVERAGE(Q24:Z24)</f>
+        <v>470.54899999999998</v>
       </c>
       <c r="AE24" s="22">
-        <f>(AC24/Z24)-1</f>
-        <v>0.27841094496085739</v>
+        <f>(AD24/AC24)-1</f>
+        <v>5.454488408497804e-002</v>
       </c>
       <c r="AF24" s="22">
-        <f>(AA24/Z24)-1</f>
+        <f>(AD24/AA24)-1</f>
+        <v>0.26781355247204641</v>
+      </c>
+      <c r="AG24" s="22">
+        <f>(AB24/AA24)-1</f>
         <v>0.38410346221204383</v>
       </c>
-      <c r="AG24" s="23" t="s">
-        <v>82</v>
+      <c r="AH24" s="23" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="25" ht="36">
       <c r="A25" s="26" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C25" s="29"/>
       <c r="D25" s="29"/>
@@ -3369,44 +3432,47 @@
       <c r="Y25" s="30">
         <v>619.59000000000003</v>
       </c>
-      <c r="Z25" s="20">
-        <f>MIN(C25:Y25)</f>
+      <c r="Z25" s="30">
+        <v>619.58000000000004</v>
+      </c>
+      <c r="AA25" s="20">
+        <f>MIN(C25:Z25)</f>
         <v>396</v>
       </c>
-      <c r="AA25" s="21">
-        <f>MAX(C25:Y25)</f>
+      <c r="AB25" s="21">
+        <f>MAX(C25:Z25)</f>
         <v>619.59000000000003</v>
       </c>
-      <c r="AB25" s="21">
-        <f>AVERAGE(C25:Y25)</f>
-        <v>532.2395238095238</v>
-      </c>
       <c r="AC25" s="21">
-        <f>AVERAGE(Q25:Y25)</f>
-        <v>569.80888888888887</v>
-      </c>
-      <c r="AD25" s="22">
-        <f>(AC25/AB25)-1</f>
-        <v>7.0587326567671971e-002</v>
+        <f>AVERAGE(C25:Z25)</f>
+        <v>536.20954545454549</v>
+      </c>
+      <c r="AD25" s="21">
+        <f>AVERAGE(Q25:Z25)</f>
+        <v>574.78599999999994</v>
       </c>
       <c r="AE25" s="22">
-        <f>(AC25/Z25)-1</f>
-        <v>0.4389113355780021</v>
+        <f>(AD25/AC25)-1</f>
+        <v>7.1942871723317037e-002</v>
       </c>
       <c r="AF25" s="22">
-        <f>(AA25/Z25)-1</f>
+        <f>(AD25/AA25)-1</f>
+        <v>0.45147979797979776</v>
+      </c>
+      <c r="AG25" s="22">
+        <f>(AB25/AA25)-1</f>
         <v>0.56462121212121219</v>
       </c>
-      <c r="AG25" s="23" t="s">
-        <v>85</v>
+      <c r="AH25" s="23" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="26" ht="18">
       <c r="A26" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C26" s="17"/>
       <c r="D26" s="25">
@@ -3471,44 +3537,47 @@
       <c r="Y26" s="30">
         <v>1592.45</v>
       </c>
-      <c r="Z26" s="20">
-        <f>MIN(C26:Y26)</f>
+      <c r="Z26" s="30">
+        <v>1561.8099999999999</v>
+      </c>
+      <c r="AA26" s="20">
+        <f>MIN(C26:Z26)</f>
         <v>370</v>
       </c>
-      <c r="AA26" s="21">
-        <f>MAX(C26:Y26)</f>
+      <c r="AB26" s="21">
+        <f>MAX(C26:Z26)</f>
         <v>1678.0799999999999</v>
       </c>
-      <c r="AB26" s="21">
-        <f>AVERAGE(C26:Y26)</f>
-        <v>1169.4424999999999</v>
-      </c>
       <c r="AC26" s="21">
-        <f>AVERAGE(Q26:Y26)</f>
-        <v>1337.3800000000001</v>
-      </c>
-      <c r="AD26" s="22">
-        <f>(AC26/AB26)-1</f>
-        <v>0.14360475183687971</v>
+        <f>AVERAGE(C26:Z26)</f>
+        <v>1188.1266666666666</v>
+      </c>
+      <c r="AD26" s="21">
+        <f>AVERAGE(Q26:Z26)</f>
+        <v>1359.8229999999999</v>
       </c>
       <c r="AE26" s="22">
-        <f>(AC26/Z26)-1</f>
-        <v>2.6145405405405406</v>
+        <f>(AD26/AC26)-1</f>
+        <v>0.14451012518306139</v>
       </c>
       <c r="AF26" s="22">
-        <f>(AA26/Z26)-1</f>
+        <f>(AD26/AA26)-1</f>
+        <v>2.6751972972972968</v>
+      </c>
+      <c r="AG26" s="22">
+        <f>(AB26/AA26)-1</f>
         <v>3.535351351351351</v>
       </c>
-      <c r="AG26" s="23" t="s">
-        <v>87</v>
+      <c r="AH26" s="23" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="27" ht="18">
       <c r="A27" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C27" s="17"/>
       <c r="D27" s="17"/>
@@ -3563,44 +3632,47 @@
       <c r="Y27" s="19">
         <v>166.99000000000001</v>
       </c>
-      <c r="Z27" s="20">
-        <f>MIN(C27:Y27)</f>
+      <c r="Z27" s="19">
+        <v>166.99000000000001</v>
+      </c>
+      <c r="AA27" s="20">
+        <f>MIN(C27:Z27)</f>
         <v>109.98999999999999</v>
       </c>
-      <c r="AA27" s="21">
-        <f>MAX(C27:Y27)</f>
+      <c r="AB27" s="21">
+        <f>MAX(C27:Z27)</f>
         <v>166.99000000000001</v>
       </c>
-      <c r="AB27" s="21">
-        <f>AVERAGE(C27:Y27)</f>
-        <v>147.83933333333334</v>
-      </c>
       <c r="AC27" s="21">
-        <f>AVERAGE(Q27:Y27)</f>
-        <v>159.10111111111112</v>
-      </c>
-      <c r="AD27" s="22">
-        <f>(AC27/AB27)-1</f>
-        <v>7.6175788430984381e-002</v>
+        <f>AVERAGE(C27:Z27)</f>
+        <v>149.03625</v>
+      </c>
+      <c r="AD27" s="21">
+        <f>AVERAGE(Q27:Z27)</f>
+        <v>159.89000000000001</v>
       </c>
       <c r="AE27" s="22">
-        <f>(AC27/Z27)-1</f>
-        <v>0.4465052378499057</v>
+        <f>(AD27/AC27)-1</f>
+        <v>7.2826241937783642e-002</v>
       </c>
       <c r="AF27" s="22">
-        <f>(AA27/Z27)-1</f>
+        <f>(AD27/AA27)-1</f>
+        <v>0.45367760705518712</v>
+      </c>
+      <c r="AG27" s="22">
+        <f>(AB27/AA27)-1</f>
         <v>0.51822892990271852</v>
       </c>
-      <c r="AG27" s="23" t="s">
-        <v>89</v>
+      <c r="AH27" s="23" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="28" ht="18">
       <c r="A28" s="26" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B28" s="27" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C28" s="29"/>
       <c r="D28" s="29"/>
@@ -3655,44 +3727,47 @@
       <c r="Y28" s="18">
         <v>81.480000000000004</v>
       </c>
-      <c r="Z28" s="20">
-        <f>MIN(C28:Y28)</f>
+      <c r="Z28" s="18">
+        <v>81.480000000000004</v>
+      </c>
+      <c r="AA28" s="20">
+        <f>MIN(C28:Z28)</f>
         <v>68</v>
       </c>
-      <c r="AA28" s="21">
-        <f>MAX(C28:Y28)</f>
+      <c r="AB28" s="21">
+        <f>MAX(C28:Z28)</f>
         <v>85.700000000000003</v>
       </c>
-      <c r="AB28" s="21">
-        <f>AVERAGE(C28:Y28)</f>
-        <v>78.812666666666672</v>
-      </c>
       <c r="AC28" s="21">
-        <f>AVERAGE(Q28:Y28)</f>
-        <v>82.154444444444437</v>
-      </c>
-      <c r="AD28" s="22">
-        <f>(AC28/AB28)-1</f>
-        <v>4.240153162069249e-002</v>
+        <f>AVERAGE(C28:Z28)</f>
+        <v>78.979375000000005</v>
+      </c>
+      <c r="AD28" s="21">
+        <f>AVERAGE(Q28:Z28)</f>
+        <v>82.087000000000003</v>
       </c>
       <c r="AE28" s="22">
-        <f>(AC28/Z28)-1</f>
-        <v>0.20815359477124162</v>
+        <f>(AD28/AC28)-1</f>
+        <v>3.9347297949622995e-002</v>
       </c>
       <c r="AF28" s="22">
-        <f>(AA28/Z28)-1</f>
+        <f>(AD28/AA28)-1</f>
+        <v>0.20716176470588232</v>
+      </c>
+      <c r="AG28" s="22">
+        <f>(AB28/AA28)-1</f>
         <v>0.26029411764705879</v>
       </c>
-      <c r="AG28" s="23" t="s">
-        <v>91</v>
+      <c r="AH28" s="23" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="29" ht="18">
       <c r="A29" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C29" s="17"/>
       <c r="D29" s="17"/>
@@ -3747,44 +3822,47 @@
       <c r="Y29" s="33">
         <v>99.900000000000006</v>
       </c>
-      <c r="Z29" s="20">
-        <f>MIN(C29:Y29)</f>
+      <c r="Z29" s="33">
+        <v>99.900000000000006</v>
+      </c>
+      <c r="AA29" s="20">
+        <f>MIN(C29:Z29)</f>
         <v>55</v>
       </c>
-      <c r="AA29" s="21">
-        <f>MAX(C29:Y29)</f>
+      <c r="AB29" s="21">
+        <f>MAX(C29:Z29)</f>
         <v>111</v>
       </c>
-      <c r="AB29" s="21">
-        <f>AVERAGE(C29:Y29)</f>
-        <v>85.936000000000007</v>
-      </c>
       <c r="AC29" s="21">
-        <f>AVERAGE(Q29:Y29)</f>
-        <v>95.475555555555559</v>
-      </c>
-      <c r="AD29" s="22">
-        <f>(AC29/AB29)-1</f>
-        <v>0.11100767496224573</v>
+        <f>AVERAGE(C29:Z29)</f>
+        <v>86.808750000000018</v>
+      </c>
+      <c r="AD29" s="21">
+        <f>AVERAGE(Q29:Z29)</f>
+        <v>95.917999999999992</v>
       </c>
       <c r="AE29" s="22">
-        <f>(AC29/Z29)-1</f>
-        <v>0.73591919191919208</v>
+        <f>(AD29/AC29)-1</f>
+        <v>0.10493469840309855</v>
       </c>
       <c r="AF29" s="22">
-        <f>(AA29/Z29)-1</f>
+        <f>(AD29/AA29)-1</f>
+        <v>0.74396363636363616</v>
+      </c>
+      <c r="AG29" s="22">
+        <f>(AB29/AA29)-1</f>
         <v>1.0181818181818181</v>
       </c>
-      <c r="AG29" s="23" t="s">
-        <v>93</v>
+      <c r="AH29" s="23" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="30" ht="18">
       <c r="A30" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C30" s="17"/>
       <c r="D30" s="17"/>
@@ -3837,44 +3915,47 @@
       <c r="Y30" s="18">
         <v>89.700000000000003</v>
       </c>
-      <c r="Z30" s="20">
-        <f>MIN(C30:Y30)</f>
+      <c r="Z30" s="19">
+        <v>91</v>
+      </c>
+      <c r="AA30" s="20">
+        <f>MIN(C30:Z30)</f>
         <v>47.359999999999999</v>
       </c>
-      <c r="AA30" s="21">
-        <f>MAX(C30:Y30)</f>
+      <c r="AB30" s="21">
+        <f>MAX(C30:Z30)</f>
         <v>100.68000000000001</v>
       </c>
-      <c r="AB30" s="21">
-        <f>AVERAGE(C30:Y30)</f>
-        <v>74.729285714285723</v>
-      </c>
       <c r="AC30" s="21">
-        <f>AVERAGE(Q30:Y30)</f>
-        <v>85.973333333333358</v>
-      </c>
-      <c r="AD30" s="22">
-        <f>(AC30/AB30)-1</f>
-        <v>0.15046373736311724</v>
+        <f>AVERAGE(C30:Z30)</f>
+        <v>75.814000000000007</v>
+      </c>
+      <c r="AD30" s="21">
+        <f>AVERAGE(Q30:Z30)</f>
+        <v>86.476000000000028</v>
       </c>
       <c r="AE30" s="22">
-        <f>(AC30/Z30)-1</f>
-        <v>0.81531531531531587</v>
+        <f>(AD30/AC30)-1</f>
+        <v>0.14063365605297196</v>
       </c>
       <c r="AF30" s="22">
-        <f>(AA30/Z30)-1</f>
+        <f>(AD30/AA30)-1</f>
+        <v>0.8259290540540547</v>
+      </c>
+      <c r="AG30" s="22">
+        <f>(AB30/AA30)-1</f>
         <v>1.1258445945945947</v>
       </c>
-      <c r="AG30" s="23" t="s">
-        <v>95</v>
+      <c r="AH30" s="23" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="31" ht="18">
       <c r="A31" s="26" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C31" s="29"/>
       <c r="D31" s="29"/>
@@ -3910,7 +3991,7 @@
         <v>132.33000000000001</v>
       </c>
       <c r="T31" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="U31" s="18">
         <v>156</v>
@@ -3927,44 +4008,47 @@
       <c r="Y31" s="18">
         <v>151.22</v>
       </c>
-      <c r="Z31" s="20">
-        <f>MIN(C31:Y31)</f>
+      <c r="Z31" s="18">
+        <v>151.22</v>
+      </c>
+      <c r="AA31" s="20">
+        <f>MIN(C31:Z31)</f>
         <v>92.5</v>
       </c>
-      <c r="AA31" s="21">
-        <f>MAX(C31:Y31)</f>
+      <c r="AB31" s="21">
+        <f>MAX(C31:Z31)</f>
         <v>156</v>
       </c>
-      <c r="AB31" s="21">
-        <f>AVERAGE(C31:Y31)</f>
-        <v>127.68461538461541</v>
-      </c>
       <c r="AC31" s="21">
-        <f>AVERAGE(Q31:Y31)</f>
-        <v>141.30125000000001</v>
-      </c>
-      <c r="AD31" s="22">
-        <f>(AC31/AB31)-1</f>
-        <v>0.10664271944093007</v>
+        <f>AVERAGE(C31:Z31)</f>
+        <v>129.36571428571432</v>
+      </c>
+      <c r="AD31" s="21">
+        <f>AVERAGE(Q31:Z31)</f>
+        <v>142.40333333333334</v>
       </c>
       <c r="AE31" s="22">
-        <f>(AC31/Z31)-1</f>
-        <v>0.52758108108108126</v>
+        <f>(AD31/AC31)-1</f>
+        <v>0.10078110046085631</v>
       </c>
       <c r="AF31" s="22">
-        <f>(AA31/Z31)-1</f>
+        <f>(AD31/AA31)-1</f>
+        <v>0.53949549549549558</v>
+      </c>
+      <c r="AG31" s="22">
+        <f>(AB31/AA31)-1</f>
         <v>0.68648648648648658</v>
       </c>
-      <c r="AG31" s="23" t="s">
-        <v>97</v>
+      <c r="AH31" s="23" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="32" ht="18">
       <c r="A32" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C32" s="17"/>
       <c r="D32" s="17"/>
@@ -4015,44 +4099,47 @@
       <c r="Y32" s="18">
         <v>221.25</v>
       </c>
-      <c r="Z32" s="20">
-        <f>MIN(C32:Y32)</f>
+      <c r="Z32" s="17">
+        <v>209.99000000000001</v>
+      </c>
+      <c r="AA32" s="20">
+        <f>MIN(C32:Z32)</f>
         <v>148.88</v>
       </c>
-      <c r="AA32" s="21">
-        <f>MAX(C32:Y32)</f>
+      <c r="AB32" s="21">
+        <f>MAX(C32:Z32)</f>
         <v>257.87</v>
       </c>
-      <c r="AB32" s="21">
-        <f>AVERAGE(C32:Y32)</f>
-        <v>221.98615384615388</v>
-      </c>
       <c r="AC32" s="21">
-        <f>AVERAGE(Q32:Y32)</f>
-        <v>233.86000000000001</v>
-      </c>
-      <c r="AD32" s="22">
-        <f>(AC32/AB32)-1</f>
-        <v>5.3489129606143049e-002</v>
+        <f>AVERAGE(C32:Z32)</f>
+        <v>221.12928571428574</v>
+      </c>
+      <c r="AD32" s="21">
+        <f>AVERAGE(Q32:Z32)</f>
+        <v>231.47300000000004</v>
       </c>
       <c r="AE32" s="22">
-        <f>(AC32/Z32)-1</f>
-        <v>0.57079527135948438</v>
+        <f>(AD32/AC32)-1</f>
+        <v>4.6776772476347039e-002</v>
       </c>
       <c r="AF32" s="22">
-        <f>(AA32/Z32)-1</f>
+        <f>(AD32/AA32)-1</f>
+        <v>0.5547622246104249</v>
+      </c>
+      <c r="AG32" s="22">
+        <f>(AB32/AA32)-1</f>
         <v>0.73206609349811935</v>
       </c>
-      <c r="AG32" s="23" t="s">
-        <v>99</v>
+      <c r="AH32" s="23" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="33" ht="18">
       <c r="A33" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C33" s="17"/>
       <c r="D33" s="17"/>
@@ -4099,44 +4186,47 @@
       <c r="Y33" s="18">
         <v>168.28999999999999</v>
       </c>
-      <c r="Z33" s="20">
-        <f>MIN(C33:Y33)</f>
+      <c r="Z33" s="18">
+        <v>149.88999999999999</v>
+      </c>
+      <c r="AA33" s="20">
+        <f>MIN(C33:Z33)</f>
         <v>144.94999999999999</v>
       </c>
-      <c r="AA33" s="21">
-        <f>MAX(C33:Y33)</f>
+      <c r="AB33" s="21">
+        <f>MAX(C33:Z33)</f>
         <v>168.28999999999999</v>
       </c>
-      <c r="AB33" s="21">
-        <f>AVERAGE(C33:Y33)</f>
-        <v>156.73727272727274</v>
-      </c>
       <c r="AC33" s="21">
-        <f>AVERAGE(Q33:Y33)</f>
-        <v>157.29666666666668</v>
-      </c>
-      <c r="AD33" s="22">
-        <f>(AC33/AB33)-1</f>
-        <v>3.5689911509899641e-003</v>
+        <f>AVERAGE(C33:Z33)</f>
+        <v>156.16666666666666</v>
+      </c>
+      <c r="AD33" s="21">
+        <f>AVERAGE(Q33:Z33)</f>
+        <v>156.55599999999998</v>
       </c>
       <c r="AE33" s="22">
-        <f>(AC33/Z33)-1</f>
-        <v>8.517879728642086e-002</v>
+        <f>(AD33/AC33)-1</f>
+        <v>2.493062966915538e-003</v>
       </c>
       <c r="AF33" s="22">
-        <f>(AA33/Z33)-1</f>
+        <f>(AD33/AA33)-1</f>
+        <v>8.0068989306657512e-002</v>
+      </c>
+      <c r="AG33" s="22">
+        <f>(AB33/AA33)-1</f>
         <v>0.16102104173853049</v>
       </c>
-      <c r="AG33" s="23" t="s">
-        <v>101</v>
+      <c r="AH33" s="23" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="34" ht="18">
       <c r="A34" s="26" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B34" s="27" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C34" s="29"/>
       <c r="D34" s="29"/>
@@ -4183,44 +4273,47 @@
       <c r="Y34" s="18">
         <v>159</v>
       </c>
-      <c r="Z34" s="20">
-        <f>MIN(C34:Y34)</f>
+      <c r="Z34" s="19">
+        <v>195.22999999999999</v>
+      </c>
+      <c r="AA34" s="20">
+        <f>MIN(C34:Z34)</f>
         <v>144</v>
       </c>
-      <c r="AA34" s="21">
-        <f>MAX(C34:Y34)</f>
+      <c r="AB34" s="21">
+        <f>MAX(C34:Z34)</f>
         <v>199.94999999999999</v>
       </c>
-      <c r="AB34" s="21">
-        <f>AVERAGE(C34:Y34)</f>
-        <v>177.22636363636363</v>
-      </c>
       <c r="AC34" s="21">
-        <f>AVERAGE(Q34:Y34)</f>
-        <v>176.40666666666664</v>
-      </c>
-      <c r="AD34" s="22">
-        <f>(AC34/AB34)-1</f>
-        <v>-4.6251412762655653e-003</v>
+        <f>AVERAGE(C34:Z34)</f>
+        <v>178.72666666666666</v>
+      </c>
+      <c r="AD34" s="21">
+        <f>AVERAGE(Q34:Z34)</f>
+        <v>178.28899999999999</v>
       </c>
       <c r="AE34" s="22">
-        <f>(AC34/Z34)-1</f>
-        <v>0.22504629629629602</v>
+        <f>(AD34/AC34)-1</f>
+        <v>-2.4488045059495311e-003</v>
       </c>
       <c r="AF34" s="22">
-        <f>(AA34/Z34)-1</f>
+        <f>(AD34/AA34)-1</f>
+        <v>0.23811805555555554</v>
+      </c>
+      <c r="AG34" s="22">
+        <f>(AB34/AA34)-1</f>
         <v>0.38854166666666656</v>
       </c>
-      <c r="AG34" s="23" t="s">
-        <v>103</v>
+      <c r="AH34" s="23" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="35" ht="18">
       <c r="A35" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C35" s="17"/>
       <c r="D35" s="17"/>
@@ -4245,7 +4338,7 @@
         <v>31941.080000000002</v>
       </c>
       <c r="M35" s="17" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="N35" s="18"/>
       <c r="O35" s="17"/>
@@ -4259,44 +4352,45 @@
       <c r="W35" s="17"/>
       <c r="X35" s="17"/>
       <c r="Y35" s="17"/>
-      <c r="Z35" s="20">
-        <f>MIN(C35:Y35)</f>
+      <c r="Z35" s="17"/>
+      <c r="AA35" s="20">
+        <f>MIN(C35:Z35)</f>
         <v>30731.380000000001</v>
       </c>
-      <c r="AA35" s="21">
-        <f>MAX(C35:Y35)</f>
+      <c r="AB35" s="21">
+        <f>MAX(C35:Z35)</f>
         <v>32790.889999999999</v>
       </c>
-      <c r="AB35" s="21">
-        <f>AVERAGE(C35:Y35)</f>
+      <c r="AC35" s="21">
+        <f>AVERAGE(C35:Z35)</f>
         <v>31912.133333333331</v>
       </c>
-      <c r="AC35" s="21" t="e">
-        <f>AVERAGE(Q35:Y35)</f>
+      <c r="AD35" s="21" t="e">
+        <f>AVERAGE(Q35:Z35)</f>
         <v>#NUM!</v>
       </c>
-      <c r="AD35" s="22" t="e">
-        <f>(AC35/AB35)-1</f>
+      <c r="AE35" s="22" t="e">
+        <f>(AD35/AC35)-1</f>
         <v>#NUM!</v>
       </c>
-      <c r="AE35" s="22" t="e">
-        <f>(AC35/Z35)-1</f>
+      <c r="AF35" s="22" t="e">
+        <f>(AD35/AA35)-1</f>
         <v>#NUM!</v>
       </c>
-      <c r="AF35" s="22">
-        <f>(AA35/Z35)-1</f>
+      <c r="AG35" s="22">
+        <f>(AB35/AA35)-1</f>
         <v>6.7016515366377982e-002</v>
       </c>
-      <c r="AG35" s="23" t="s">
-        <v>106</v>
+      <c r="AH35" s="23" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="36" ht="18">
       <c r="A36" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C36" s="17"/>
       <c r="D36" s="17"/>
@@ -4328,61 +4422,64 @@
         <v>721.67999999999995</v>
       </c>
       <c r="T36" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="U36" s="17">
+        <v>45</v>
+      </c>
+      <c r="U36" s="19">
         <v>1164</v>
       </c>
-      <c r="V36" s="17">
+      <c r="V36" s="19">
         <v>1150.8</v>
       </c>
-      <c r="W36" s="17">
+      <c r="W36" s="19">
         <v>1150.8</v>
       </c>
-      <c r="X36" s="17">
+      <c r="X36" s="19">
         <v>1150.8</v>
       </c>
-      <c r="Y36" s="17">
+      <c r="Y36" s="19">
         <v>1150.8</v>
       </c>
-      <c r="Z36" s="20">
-        <f>MIN(C36:Y36)</f>
+      <c r="Z36" s="30">
+        <v>1360.8</v>
+      </c>
+      <c r="AA36" s="20">
+        <f>MIN(C36:Z36)</f>
         <v>642.82000000000005</v>
       </c>
-      <c r="AA36" s="21">
-        <f>MAX(C36:Y36)</f>
-        <v>1164</v>
-      </c>
       <c r="AB36" s="21">
-        <f>AVERAGE(C36:Y36)</f>
-        <v>903.59636363636355</v>
+        <f>MAX(C36:Z36)</f>
+        <v>1360.8</v>
       </c>
       <c r="AC36" s="21">
-        <f>AVERAGE(Q36:Y36)</f>
-        <v>991.53000000000009</v>
-      </c>
-      <c r="AD36" s="22">
-        <f>(AC36/AB36)-1</f>
-        <v>9.7315172905038327e-002</v>
+        <f>AVERAGE(C36:Z36)</f>
+        <v>941.6966666666666</v>
+      </c>
+      <c r="AD36" s="21">
+        <f>AVERAGE(Q36:Z36)</f>
+        <v>1032.5600000000002</v>
       </c>
       <c r="AE36" s="22">
-        <f>(AC36/Z36)-1</f>
-        <v>0.54246912043806983</v>
+        <f>(AD36/AC36)-1</f>
+        <v>9.6488961413618846e-002</v>
       </c>
       <c r="AF36" s="22">
-        <f>(AA36/Z36)-1</f>
-        <v>0.81077128900780915</v>
-      </c>
-      <c r="AG36" s="23" t="s">
-        <v>109</v>
+        <f>(AD36/AA36)-1</f>
+        <v>0.60629725273015778</v>
+      </c>
+      <c r="AG36" s="22">
+        <f>(AB36/AA36)-1</f>
+        <v>1.1169223110668614</v>
+      </c>
+      <c r="AH36" s="23" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="37" ht="18">
       <c r="A37" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C37" s="17"/>
       <c r="D37" s="17"/>
@@ -4431,44 +4528,47 @@
       <c r="Y37" s="30">
         <v>2016</v>
       </c>
-      <c r="Z37" s="20">
-        <f>MIN(C37:Y37)</f>
+      <c r="Z37" s="30">
+        <v>2171.4000000000001</v>
+      </c>
+      <c r="AA37" s="20">
+        <f>MIN(C37:Z37)</f>
         <v>1151.71</v>
       </c>
-      <c r="AA37" s="21">
-        <f>MAX(C37:Y37)</f>
-        <v>2064</v>
-      </c>
       <c r="AB37" s="21">
-        <f>AVERAGE(C37:Y37)</f>
-        <v>1634.5116666666665</v>
+        <f>MAX(C37:Z37)</f>
+        <v>2171.4000000000001</v>
       </c>
       <c r="AC37" s="21">
-        <f>AVERAGE(Q37:Y37)</f>
-        <v>1781.2266666666667</v>
-      </c>
-      <c r="AD37" s="22">
-        <f>(AC37/AB37)-1</f>
-        <v>8.9760754231386297e-002</v>
+        <f>AVERAGE(C37:Z37)</f>
+        <v>1675.8107692307692</v>
+      </c>
+      <c r="AD37" s="21">
+        <f>AVERAGE(Q37:Z37)</f>
+        <v>1820.2440000000001</v>
       </c>
       <c r="AE37" s="22">
-        <f>(AC37/Z37)-1</f>
-        <v>0.5465930370203147</v>
+        <f>(AD37/AC37)-1</f>
+        <v>8.6187076381857075e-002</v>
       </c>
       <c r="AF37" s="22">
-        <f>(AA37/Z37)-1</f>
-        <v>0.79211780743416305</v>
-      </c>
-      <c r="AG37" s="23" t="s">
-        <v>109</v>
+        <f>(AD37/AA37)-1</f>
+        <v>0.58047077823410409</v>
+      </c>
+      <c r="AG37" s="22">
+        <f>(AB37/AA37)-1</f>
+        <v>0.88537044915820817</v>
+      </c>
+      <c r="AH37" s="23" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="38" ht="18">
       <c r="A38" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C38" s="17"/>
       <c r="D38" s="17"/>
@@ -4503,58 +4603,61 @@
         <v>3876</v>
       </c>
       <c r="U38" s="36" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="V38" s="36" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="W38" s="36" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X38" s="36" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Y38" s="36" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z38" s="20">
-        <f>MIN(C38:Y38)</f>
+        <v>45</v>
+      </c>
+      <c r="Z38" s="36" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA38" s="20">
+        <f>MIN(C38:Z38)</f>
         <v>2159.8299999999999</v>
       </c>
-      <c r="AA38" s="21">
-        <f>MAX(C38:Y38)</f>
+      <c r="AB38" s="21">
+        <f>MAX(C38:Z38)</f>
         <v>3876</v>
       </c>
-      <c r="AB38" s="21">
-        <f>AVERAGE(C38:Y38)</f>
+      <c r="AC38" s="21">
+        <f>AVERAGE(C38:Z38)</f>
         <v>2544.02</v>
       </c>
-      <c r="AC38" s="21">
-        <f>AVERAGE(Q38:Y38)</f>
+      <c r="AD38" s="21">
+        <f>AVERAGE(Q38:Z38)</f>
         <v>2771.3400000000001</v>
       </c>
-      <c r="AD38" s="22">
-        <f>(AC38/AB38)-1</f>
+      <c r="AE38" s="22">
+        <f>(AD38/AC38)-1</f>
         <v>8.9354643438337877e-002</v>
       </c>
-      <c r="AE38" s="22">
-        <f>(AC38/Z38)-1</f>
+      <c r="AF38" s="22">
+        <f>(AD38/AA38)-1</f>
         <v>0.28312876476389359</v>
       </c>
-      <c r="AF38" s="22">
-        <f>(AA38/Z38)-1</f>
+      <c r="AG38" s="22">
+        <f>(AB38/AA38)-1</f>
         <v>0.79458568498446636</v>
       </c>
-      <c r="AG38" s="23" t="s">
-        <v>109</v>
+      <c r="AH38" s="23" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="39" ht="18">
       <c r="A39" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C39" s="17"/>
       <c r="D39" s="17"/>
@@ -4603,44 +4706,47 @@
       <c r="Y39" s="30">
         <v>2218.4400000000001</v>
       </c>
-      <c r="Z39" s="20">
-        <f>MIN(C39:Y39)</f>
+      <c r="Z39" s="30">
+        <v>2804.7600000000002</v>
+      </c>
+      <c r="AA39" s="20">
+        <f>MIN(C39:Z39)</f>
         <v>1310.1800000000001</v>
       </c>
-      <c r="AA39" s="21">
-        <f>MAX(C39:Y39)</f>
-        <v>2218.4400000000001</v>
-      </c>
       <c r="AB39" s="21">
-        <f>AVERAGE(C39:Y39)</f>
-        <v>1753.9116666666666</v>
+        <f>MAX(C39:Z39)</f>
+        <v>2804.7600000000002</v>
       </c>
       <c r="AC39" s="21">
-        <f>AVERAGE(Q39:Y39)</f>
-        <v>1899.5066666666669</v>
-      </c>
-      <c r="AD39" s="22">
-        <f>(AC39/AB39)-1</f>
-        <v>8.3011592183947158e-002</v>
+        <f>AVERAGE(C39:Z39)</f>
+        <v>1834.7461538461537</v>
+      </c>
+      <c r="AD39" s="21">
+        <f>AVERAGE(Q39:Z39)</f>
+        <v>1990.0319999999999</v>
       </c>
       <c r="AE39" s="22">
-        <f>(AC39/Z39)-1</f>
-        <v>0.44980587909040493</v>
+        <f>(AD39/AC39)-1</f>
+        <v>8.4636147528268424e-002</v>
       </c>
       <c r="AF39" s="22">
-        <f>(AA39/Z39)-1</f>
-        <v>0.69323299088674828</v>
-      </c>
-      <c r="AG39" s="23" t="s">
-        <v>109</v>
+        <f>(AD39/AA39)-1</f>
+        <v>0.51889969317193052</v>
+      </c>
+      <c r="AG39" s="22">
+        <f>(AB39/AA39)-1</f>
+        <v>1.1407440199056618</v>
+      </c>
+      <c r="AH39" s="23" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="40" ht="18">
       <c r="A40" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C40" s="17"/>
       <c r="D40" s="17"/>
@@ -4677,44 +4783,47 @@
       <c r="Y40" s="19">
         <v>1592.6400000000001</v>
       </c>
-      <c r="Z40" s="20">
-        <f>MIN(C40:Y40)</f>
+      <c r="Z40" s="19">
         <v>1592.6400000000001</v>
       </c>
-      <c r="AA40" s="21">
-        <f>MAX(C40:Y40)</f>
+      <c r="AA40" s="20">
+        <f>MIN(C40:Z40)</f>
+        <v>1592.6400000000001</v>
+      </c>
+      <c r="AB40" s="21">
+        <f>MAX(C40:Z40)</f>
         <v>1896</v>
       </c>
-      <c r="AB40" s="21">
-        <f>AVERAGE(C40:Y40)</f>
-        <v>1693.76</v>
-      </c>
       <c r="AC40" s="21">
-        <f>AVERAGE(Q40:Y40)</f>
-        <v>1693.76</v>
-      </c>
-      <c r="AD40" s="22">
-        <f>(AC40/AB40)-1</f>
+        <f>AVERAGE(C40:Z40)</f>
+        <v>1679.3142857142855</v>
+      </c>
+      <c r="AD40" s="21">
+        <f>AVERAGE(Q40:Z40)</f>
+        <v>1679.3142857142855</v>
+      </c>
+      <c r="AE40" s="22">
+        <f>(AD40/AC40)-1</f>
         <v>0</v>
       </c>
-      <c r="AE40" s="22">
-        <f>(AC40/Z40)-1</f>
-        <v>6.3492063492063489e-002</v>
-      </c>
       <c r="AF40" s="22">
-        <f>(AA40/Z40)-1</f>
+        <f>(AD40/AA40)-1</f>
+        <v>5.4421768707482832e-002</v>
+      </c>
+      <c r="AG40" s="22">
+        <f>(AB40/AA40)-1</f>
         <v>0.19047619047619047</v>
       </c>
-      <c r="AG40" s="23" t="s">
-        <v>109</v>
+      <c r="AH40" s="23" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="41" ht="18">
       <c r="A41" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C41" s="17"/>
       <c r="D41" s="17"/>
@@ -4746,13 +4855,13 @@
         <v>1628.6199999999999</v>
       </c>
       <c r="T41" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="U41" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="V41" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="W41" s="19">
         <v>1985.76</v>
@@ -4763,44 +4872,47 @@
       <c r="Y41" s="19">
         <v>1985.76</v>
       </c>
-      <c r="Z41" s="20">
-        <f>MIN(C41:Y41)</f>
+      <c r="Z41" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA41" s="20">
+        <f>MIN(C41:Z41)</f>
         <v>1480.5599999999999</v>
       </c>
-      <c r="AA41" s="21">
-        <f>MAX(C41:Y41)</f>
+      <c r="AB41" s="21">
+        <f>MAX(C41:Z41)</f>
         <v>1985.76</v>
       </c>
-      <c r="AB41" s="21">
-        <f>AVERAGE(C41:Y41)</f>
+      <c r="AC41" s="21">
+        <f>AVERAGE(C41:Z41)</f>
         <v>1714.7644444444443</v>
       </c>
-      <c r="AC41" s="21">
-        <f>AVERAGE(Q41:Y41)</f>
+      <c r="AD41" s="21">
+        <f>AVERAGE(Q41:Z41)</f>
         <v>1807.1899999999998</v>
       </c>
-      <c r="AD41" s="22">
-        <f>(AC41/AB41)-1</f>
+      <c r="AE41" s="22">
+        <f>(AD41/AC41)-1</f>
         <v>5.389985537372155e-002</v>
       </c>
-      <c r="AE41" s="22">
-        <f>(AC41/Z41)-1</f>
+      <c r="AF41" s="22">
+        <f>(AD41/AA41)-1</f>
         <v>0.22061247095693504</v>
       </c>
-      <c r="AF41" s="22">
-        <f>(AA41/Z41)-1</f>
+      <c r="AG41" s="22">
+        <f>(AB41/AA41)-1</f>
         <v>0.34122224023342529</v>
       </c>
-      <c r="AG41" s="23" t="s">
-        <v>109</v>
+      <c r="AH41" s="23" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="42" ht="18">
       <c r="A42" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C42" s="17"/>
       <c r="D42" s="17">
@@ -4827,41 +4939,42 @@
       <c r="W42" s="17"/>
       <c r="X42" s="17"/>
       <c r="Y42" s="17"/>
-      <c r="Z42" s="20">
-        <f>MIN(C42:Y42)</f>
+      <c r="Z42" s="17"/>
+      <c r="AA42" s="20">
+        <f>MIN(C42:Z42)</f>
         <v>339.45999999999998</v>
       </c>
-      <c r="AA42" s="21">
-        <f>MAX(C42:Y42)</f>
+      <c r="AB42" s="21">
+        <f>MAX(C42:Z42)</f>
         <v>339.45999999999998</v>
       </c>
-      <c r="AB42" s="21">
-        <f>AVERAGE(C42:Y42)</f>
+      <c r="AC42" s="21">
+        <f>AVERAGE(C42:Z42)</f>
         <v>339.45999999999998</v>
       </c>
-      <c r="AC42" s="21" t="e">
-        <f>AVERAGE(Q42:Y42)</f>
+      <c r="AD42" s="21" t="e">
+        <f>AVERAGE(Q42:Z42)</f>
         <v>#NUM!</v>
       </c>
-      <c r="AD42" s="22" t="e">
-        <f>(AC42/AB42)-1</f>
+      <c r="AE42" s="22" t="e">
+        <f>(AD42/AC42)-1</f>
         <v>#NUM!</v>
       </c>
-      <c r="AE42" s="22" t="e">
-        <f>(AC42/Z42)-1</f>
+      <c r="AF42" s="22" t="e">
+        <f>(AD42/AA42)-1</f>
         <v>#NUM!</v>
       </c>
-      <c r="AF42" s="22">
-        <f>(AA42/Z42)-1</f>
+      <c r="AG42" s="22">
+        <f>(AB42/AA42)-1</f>
         <v>0</v>
       </c>
     </row>
     <row r="43" ht="18">
       <c r="A43" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C43" s="17"/>
       <c r="D43" s="17"/>
@@ -4924,44 +5037,47 @@
       <c r="Y43" s="17">
         <v>378.99000000000001</v>
       </c>
-      <c r="Z43" s="20">
-        <f>MIN(C43:Y43)</f>
+      <c r="Z43" s="17">
         <v>378.99000000000001</v>
       </c>
-      <c r="AA43" s="21">
-        <f>MAX(C43:Y43)</f>
+      <c r="AA43" s="20">
+        <f>MIN(C43:Z43)</f>
         <v>378.99000000000001</v>
       </c>
       <c r="AB43" s="21">
-        <f>AVERAGE(C43:Y43)</f>
+        <f>MAX(C43:Z43)</f>
+        <v>378.99000000000001</v>
+      </c>
+      <c r="AC43" s="21">
+        <f>AVERAGE(C43:Z43)</f>
         <v>378.9899999999999</v>
       </c>
-      <c r="AC43" s="21">
-        <f>AVERAGE(Q43:Y43)</f>
-        <v>378.99000000000001</v>
-      </c>
-      <c r="AD43" s="22">
-        <f>(AC43/AB43)-1</f>
+      <c r="AD43" s="21">
+        <f>AVERAGE(Q43:Z43)</f>
+        <v>378.98999999999995</v>
+      </c>
+      <c r="AE43" s="22">
+        <f>(AD43/AC43)-1</f>
         <v>2.2204460492503131e-016</v>
       </c>
-      <c r="AE43" s="22">
-        <f>(AC43/Z43)-1</f>
+      <c r="AF43" s="22">
+        <f>(AD43/AA43)-1</f>
+        <v>-1.1102230246251565e-016</v>
+      </c>
+      <c r="AG43" s="22">
+        <f>(AB43/AA43)-1</f>
         <v>0</v>
       </c>
-      <c r="AF43" s="22">
-        <f>(AA43/Z43)-1</f>
-        <v>0</v>
-      </c>
-      <c r="AG43" s="23" t="s">
-        <v>120</v>
+      <c r="AH43" s="23" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="44" ht="18">
       <c r="A44" s="26" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B44" s="27" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C44" s="29"/>
       <c r="D44" s="29"/>
@@ -5024,44 +5140,47 @@
       <c r="Y44" s="30">
         <v>191.19</v>
       </c>
-      <c r="Z44" s="20">
-        <f>MIN(C44:Y44)</f>
+      <c r="Z44" s="30">
+        <v>191.19</v>
+      </c>
+      <c r="AA44" s="20">
+        <f>MIN(C44:Z44)</f>
         <v>88.329999999999998</v>
       </c>
-      <c r="AA44" s="21">
-        <f>MAX(C44:Y44)</f>
+      <c r="AB44" s="21">
+        <f>MAX(C44:Z44)</f>
         <v>191.19</v>
       </c>
-      <c r="AB44" s="21">
-        <f>AVERAGE(C44:Y44)</f>
-        <v>107.45789473684212</v>
-      </c>
       <c r="AC44" s="21">
-        <f>AVERAGE(Q44:Y44)</f>
-        <v>128.71111111111111</v>
-      </c>
-      <c r="AD44" s="22">
-        <f>(AC44/AB44)-1</f>
-        <v>0.19778180492291253</v>
+        <f>AVERAGE(C44:Z44)</f>
+        <v>111.64450000000002</v>
+      </c>
+      <c r="AD44" s="21">
+        <f>AVERAGE(Q44:Z44)</f>
+        <v>134.959</v>
       </c>
       <c r="AE44" s="22">
-        <f>(AC44/Z44)-1</f>
-        <v>0.4571619054807099</v>
+        <f>(AD44/AC44)-1</f>
+        <v>0.20882802108478238</v>
       </c>
       <c r="AF44" s="22">
-        <f>(AA44/Z44)-1</f>
+        <f>(AD44/AA44)-1</f>
+        <v>0.52789539227895399</v>
+      </c>
+      <c r="AG44" s="22">
+        <f>(AB44/AA44)-1</f>
         <v>1.1644967734631497</v>
       </c>
-      <c r="AG44" s="23" t="s">
-        <v>123</v>
+      <c r="AH44" s="23" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="45" ht="18">
       <c r="A45" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C45" s="17"/>
       <c r="D45" s="17">
@@ -5126,44 +5245,47 @@
       <c r="Y45" s="36">
         <v>40.039999999999999</v>
       </c>
-      <c r="Z45" s="20">
-        <f>MIN(C45:Y45)</f>
+      <c r="Z45" s="36">
+        <v>39.899999999999999</v>
+      </c>
+      <c r="AA45" s="20">
+        <f>MIN(C45:Z45)</f>
         <v>29.989999999999998</v>
       </c>
-      <c r="AA45" s="21">
-        <f>MAX(C45:Y45)</f>
+      <c r="AB45" s="21">
+        <f>MAX(C45:Z45)</f>
         <v>44.979999999999997</v>
       </c>
-      <c r="AB45" s="21">
-        <f>AVERAGE(C45:Y45)</f>
-        <v>36.602500000000006</v>
-      </c>
       <c r="AC45" s="21">
-        <f>AVERAGE(Q45:Y45)</f>
-        <v>36.745555555555562</v>
-      </c>
-      <c r="AD45" s="22">
-        <f>(AC45/AB45)-1</f>
-        <v>3.9083547723668399e-003</v>
+        <f>AVERAGE(C45:Z45)</f>
+        <v>36.759523809523813</v>
+      </c>
+      <c r="AD45" s="21">
+        <f>AVERAGE(Q45:Z45)</f>
+        <v>37.061</v>
       </c>
       <c r="AE45" s="22">
-        <f>(AC45/Z45)-1</f>
-        <v>0.22526027194249965</v>
+        <f>(AD45/AC45)-1</f>
+        <v>8.2013083748946336e-003</v>
       </c>
       <c r="AF45" s="22">
-        <f>(AA45/Z45)-1</f>
+        <f>(AD45/AA45)-1</f>
+        <v>0.23577859286428815</v>
+      </c>
+      <c r="AG45" s="22">
+        <f>(AB45/AA45)-1</f>
         <v>0.49983327775925313</v>
       </c>
-      <c r="AG45" s="23" t="s">
-        <v>126</v>
+      <c r="AH45" s="23" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="46" ht="18">
       <c r="A46" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C46" s="17"/>
       <c r="D46" s="17">
@@ -5228,44 +5350,47 @@
       <c r="Y46" s="36">
         <v>30.989999999999998</v>
       </c>
-      <c r="Z46" s="20">
-        <f>MIN(C46:Y46)</f>
+      <c r="Z46" s="36">
+        <v>30.989999999999998</v>
+      </c>
+      <c r="AA46" s="20">
+        <f>MIN(C46:Z46)</f>
         <v>25.989999999999998</v>
       </c>
-      <c r="AA46" s="21">
-        <f>MAX(C46:Y46)</f>
+      <c r="AB46" s="21">
+        <f>MAX(C46:Z46)</f>
         <v>42</v>
       </c>
-      <c r="AB46" s="21">
-        <f>AVERAGE(C46:Y46)</f>
-        <v>31.887999999999998</v>
-      </c>
       <c r="AC46" s="21">
-        <f>AVERAGE(Q46:Y46)</f>
-        <v>32.615555555555567</v>
-      </c>
-      <c r="AD46" s="22">
-        <f>(AC46/AB46)-1</f>
-        <v>2.2815966995596071e-002</v>
+        <f>AVERAGE(C46:Z46)</f>
+        <v>31.845238095238095</v>
+      </c>
+      <c r="AD46" s="21">
+        <f>AVERAGE(Q46:Z46)</f>
+        <v>32.45300000000001</v>
       </c>
       <c r="AE46" s="22">
-        <f>(AC46/Z46)-1</f>
-        <v>0.25492710871702839</v>
+        <f>(AD46/AC46)-1</f>
+        <v>1.9084859813084387e-002</v>
       </c>
       <c r="AF46" s="22">
-        <f>(AA46/Z46)-1</f>
+        <f>(AD46/AA46)-1</f>
+        <v>0.24867256637168178</v>
+      </c>
+      <c r="AG46" s="22">
+        <f>(AB46/AA46)-1</f>
         <v>0.61600615621392851</v>
       </c>
-      <c r="AG46" s="23" t="s">
-        <v>129</v>
+      <c r="AH46" s="23" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="47" ht="18">
       <c r="A47" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C47" s="17"/>
       <c r="D47" s="17">
@@ -5330,44 +5455,47 @@
       <c r="Y47" s="36">
         <v>28.899999999999999</v>
       </c>
-      <c r="Z47" s="20">
-        <f>MIN(C47:Y47)</f>
+      <c r="Z47" s="36">
+        <v>28.899999999999999</v>
+      </c>
+      <c r="AA47" s="20">
+        <f>MIN(C47:Z47)</f>
         <v>21.690000000000001</v>
       </c>
-      <c r="AA47" s="21">
-        <f>MAX(C47:Y47)</f>
+      <c r="AB47" s="21">
+        <f>MAX(C47:Z47)</f>
         <v>43.990000000000002</v>
       </c>
-      <c r="AB47" s="21">
-        <f>AVERAGE(C47:Y47)</f>
-        <v>29.413999999999994</v>
-      </c>
       <c r="AC47" s="21">
-        <f>AVERAGE(Q47:Y47)</f>
-        <v>28.052222222222227</v>
-      </c>
-      <c r="AD47" s="22">
-        <f>(AC47/AB47)-1</f>
-        <v>-4.6296925878077322e-002</v>
+        <f>AVERAGE(C47:Z47)</f>
+        <v>29.389523809523801</v>
+      </c>
+      <c r="AD47" s="21">
+        <f>AVERAGE(Q47:Z47)</f>
+        <v>28.137</v>
       </c>
       <c r="AE47" s="22">
-        <f>(AC47/Z47)-1</f>
-        <v>0.29332513703191454</v>
+        <f>(AD47/AC47)-1</f>
+        <v>-4.2618036877409837e-002</v>
       </c>
       <c r="AF47" s="22">
-        <f>(AA47/Z47)-1</f>
+        <f>(AD47/AA47)-1</f>
+        <v>0.29723374827109272</v>
+      </c>
+      <c r="AG47" s="22">
+        <f>(AB47/AA47)-1</f>
         <v>1.0281235592438911</v>
       </c>
-      <c r="AG47" s="23" t="s">
-        <v>132</v>
+      <c r="AH47" s="23" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="48" ht="54">
       <c r="A48" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C48" s="17"/>
       <c r="D48" s="17"/>
@@ -5388,10 +5516,10 @@
         <v>1714.0799999999999</v>
       </c>
       <c r="K48" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L48" s="17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M48" s="25">
         <v>1449.28</v>
@@ -5432,44 +5560,47 @@
       <c r="Y48" s="18">
         <v>1820.77</v>
       </c>
-      <c r="Z48" s="20">
-        <f>MIN(C48:Y48)</f>
+      <c r="Z48" s="18">
+        <v>1820.77</v>
+      </c>
+      <c r="AA48" s="20">
+        <f>MIN(C48:Z48)</f>
         <v>1449.28</v>
       </c>
-      <c r="AA48" s="21">
-        <f>MAX(C48:Y48)</f>
+      <c r="AB48" s="21">
+        <f>MAX(C48:Z48)</f>
         <v>1820.77</v>
       </c>
-      <c r="AB48" s="21">
-        <f>AVERAGE(C48:Y48)</f>
-        <v>1698.8299999999999</v>
-      </c>
       <c r="AC48" s="21">
-        <f>AVERAGE(Q48:Y48)</f>
-        <v>1677.4388888888889</v>
-      </c>
-      <c r="AD48" s="22">
-        <f>(AC48/AB48)-1</f>
-        <v>-1.2591672569421952e-002</v>
+        <f>AVERAGE(C48:Z48)</f>
+        <v>1705.247894736842</v>
+      </c>
+      <c r="AD48" s="21">
+        <f>AVERAGE(Q48:Z48)</f>
+        <v>1691.7720000000002</v>
       </c>
       <c r="AE48" s="22">
-        <f>(AC48/Z48)-1</f>
-        <v>0.15742912956011867</v>
+        <f>(AD48/AC48)-1</f>
+        <v>-7.9026015973597818e-003</v>
       </c>
       <c r="AF48" s="22">
-        <f>(AA48/Z48)-1</f>
+        <f>(AD48/AA48)-1</f>
+        <v>0.16731894457937746</v>
+      </c>
+      <c r="AG48" s="22">
+        <f>(AB48/AA48)-1</f>
         <v>0.25632727975270475</v>
       </c>
-      <c r="AG48" s="1" t="s">
-        <v>134</v>
+      <c r="AH48" s="1" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="49" ht="18">
       <c r="A49" s="26" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B49" s="27" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C49" s="29"/>
       <c r="D49" s="29"/>
@@ -5532,44 +5663,47 @@
       <c r="Y49" s="36">
         <v>43.990000000000002</v>
       </c>
-      <c r="Z49" s="20">
-        <f>MIN(C49:Y49)</f>
+      <c r="Z49" s="36">
+        <v>36.990000000000002</v>
+      </c>
+      <c r="AA49" s="20">
+        <f>MIN(C49:Z49)</f>
         <v>30.989999999999998</v>
       </c>
-      <c r="AA49" s="21">
-        <f>MAX(C49:Y49)</f>
+      <c r="AB49" s="21">
+        <f>MAX(C49:Z49)</f>
         <v>43.990000000000002</v>
       </c>
-      <c r="AB49" s="21">
-        <f>AVERAGE(C49:Y49)</f>
-        <v>37.268421052631574</v>
-      </c>
       <c r="AC49" s="21">
-        <f>AVERAGE(Q49:Y49)</f>
-        <v>38.57</v>
-      </c>
-      <c r="AD49" s="22">
-        <f>(AC49/AB49)-1</f>
-        <v>3.4924445699760165e-002</v>
+        <f>AVERAGE(C49:Z49)</f>
+        <v>37.254499999999993</v>
+      </c>
+      <c r="AD49" s="21">
+        <f>AVERAGE(Q49:Z49)</f>
+        <v>38.411999999999999</v>
       </c>
       <c r="AE49" s="22">
-        <f>(AC49/Z49)-1</f>
-        <v>0.24459503065505017</v>
+        <f>(AD49/AC49)-1</f>
+        <v>3.1070072071830435e-002</v>
       </c>
       <c r="AF49" s="22">
-        <f>(AA49/Z49)-1</f>
+        <f>(AD49/AA49)-1</f>
+        <v>0.23949661181026149</v>
+      </c>
+      <c r="AG49" s="22">
+        <f>(AB49/AA49)-1</f>
         <v>0.41949015811552126</v>
       </c>
-      <c r="AG49" s="23" t="s">
-        <v>137</v>
+      <c r="AH49" s="23" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="50" ht="18">
       <c r="A50" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C50" s="17"/>
       <c r="D50" s="17"/>
@@ -5632,44 +5766,47 @@
       <c r="Y50" s="17">
         <v>85.209999999999994</v>
       </c>
-      <c r="Z50" s="20">
-        <f>MIN(C50:Y50)</f>
+      <c r="Z50" s="17">
+        <v>85.209999999999994</v>
+      </c>
+      <c r="AA50" s="20">
+        <f>MIN(C50:Z50)</f>
         <v>81.689999999999998</v>
       </c>
-      <c r="AA50" s="21">
-        <f>MAX(C50:Y50)</f>
+      <c r="AB50" s="21">
+        <f>MAX(C50:Z50)</f>
         <v>93.280000000000001</v>
       </c>
-      <c r="AB50" s="21">
-        <f>AVERAGE(C50:Y50)</f>
-        <v>88.041052631578964</v>
-      </c>
       <c r="AC50" s="21">
-        <f>AVERAGE(Q50:Y50)</f>
-        <v>85.351111111111123</v>
-      </c>
-      <c r="AD50" s="22">
-        <f>(AC50/AB50)-1</f>
-        <v>-3.0553263961124011e-002</v>
+        <f>AVERAGE(C50:Z50)</f>
+        <v>87.899500000000018</v>
+      </c>
+      <c r="AD50" s="21">
+        <f>AVERAGE(Q50:Z50)</f>
+        <v>85.337000000000018</v>
       </c>
       <c r="AE50" s="22">
-        <f>(AC50/Z50)-1</f>
-        <v>4.4817127079338048e-002</v>
+        <f>(AD50/AC50)-1</f>
+        <v>-2.9152611789600602e-002</v>
       </c>
       <c r="AF50" s="22">
-        <f>(AA50/Z50)-1</f>
+        <f>(AD50/AA50)-1</f>
+        <v>4.4644387317909429e-002</v>
+      </c>
+      <c r="AG50" s="22">
+        <f>(AB50/AA50)-1</f>
         <v>0.1418778308238462</v>
       </c>
-      <c r="AG50" s="1" t="s">
-        <v>140</v>
+      <c r="AH50" s="1" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="51" ht="18">
       <c r="A51" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C51" s="17"/>
       <c r="D51" s="17"/>
@@ -5734,44 +5871,47 @@
       <c r="Y51" s="34">
         <v>298.80000000000001</v>
       </c>
-      <c r="Z51" s="20">
-        <f>MIN(C51:Y51)</f>
+      <c r="Z51" s="34">
         <v>298.80000000000001</v>
       </c>
-      <c r="AA51" s="21">
-        <f>MAX(C51:Y51)</f>
+      <c r="AA51" s="20">
+        <f>MIN(C51:Z51)</f>
+        <v>298.80000000000001</v>
+      </c>
+      <c r="AB51" s="21">
+        <f>MAX(C51:Z51)</f>
         <v>309.05000000000001</v>
       </c>
-      <c r="AB51" s="21">
-        <f>AVERAGE(C51:Y51)</f>
-        <v>307.5125000000001</v>
-      </c>
       <c r="AC51" s="21">
-        <f>AVERAGE(Q51:Y51)</f>
-        <v>305.63333333333338</v>
-      </c>
-      <c r="AD51" s="22">
-        <f>(AC51/AB51)-1</f>
-        <v>-6.1108627020584061e-003</v>
+        <f>AVERAGE(C51:Z51)</f>
+        <v>307.09761904761916</v>
+      </c>
+      <c r="AD51" s="21">
+        <f>AVERAGE(Q51:Z51)</f>
+        <v>304.95000000000005</v>
       </c>
       <c r="AE51" s="22">
-        <f>(AC51/Z51)-1</f>
-        <v>2.2869254796965777e-002</v>
+        <f>(AD51/AC51)-1</f>
+        <v>-6.993278079717391e-003</v>
       </c>
       <c r="AF51" s="22">
-        <f>(AA51/Z51)-1</f>
+        <f>(AD51/AA51)-1</f>
+        <v>2.058232931726911e-002</v>
+      </c>
+      <c r="AG51" s="22">
+        <f>(AB51/AA51)-1</f>
         <v>3.4303882195448443e-002</v>
       </c>
-      <c r="AG51" s="23" t="s">
-        <v>143</v>
+      <c r="AH51" s="23" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="52" ht="18">
       <c r="A52" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C52" s="17"/>
       <c r="D52" s="17"/>
@@ -5834,41 +5974,44 @@
       <c r="Y52" s="25">
         <v>100.44</v>
       </c>
-      <c r="Z52" s="20">
-        <f>MIN(C52:Y52)</f>
+      <c r="Z52" s="25">
         <v>100.44</v>
       </c>
-      <c r="AA52" s="21">
-        <f>MAX(C52:Y52)</f>
+      <c r="AA52" s="20">
+        <f>MIN(C52:Z52)</f>
+        <v>100.44</v>
+      </c>
+      <c r="AB52" s="21">
+        <f>MAX(C52:Z52)</f>
         <v>108.98999999999999</v>
       </c>
-      <c r="AB52" s="21">
-        <f>AVERAGE(C52:Y52)</f>
-        <v>108.53999999999999</v>
-      </c>
       <c r="AC52" s="21">
-        <f>AVERAGE(Q52:Y52)</f>
-        <v>108.03999999999999</v>
-      </c>
-      <c r="AD52" s="22">
-        <f>(AC52/AB52)-1</f>
-        <v>-4.6065966463976205e-003</v>
+        <f>AVERAGE(C52:Z52)</f>
+        <v>108.13499999999999</v>
+      </c>
+      <c r="AD52" s="21">
+        <f>AVERAGE(Q52:Z52)</f>
+        <v>107.28</v>
       </c>
       <c r="AE52" s="22">
-        <f>(AC52/Z52)-1</f>
-        <v>7.5667064914376692e-002</v>
+        <f>(AD52/AC52)-1</f>
+        <v>-7.9067831876820094e-003</v>
       </c>
       <c r="AF52" s="22">
-        <f>(AA52/Z52)-1</f>
+        <f>(AD52/AA52)-1</f>
+        <v>6.8100358422939156e-002</v>
+      </c>
+      <c r="AG52" s="22">
+        <f>(AB52/AA52)-1</f>
         <v>8.5125448028673834e-002</v>
       </c>
-      <c r="AG52" s="38" t="s">
-        <v>145</v>
+      <c r="AH52" s="38" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="53" ht="18">
       <c r="B53" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="O53" s="17">
         <v>1.49</v>
@@ -5903,92 +6046,95 @@
       <c r="Y53" s="17">
         <v>1.99</v>
       </c>
-      <c r="Z53" s="20">
-        <f>MIN(C53:Y53)</f>
+      <c r="Z53" s="17">
+        <v>1.99</v>
+      </c>
+      <c r="AA53" s="20">
+        <f>MIN(C53:Z53)</f>
         <v>1.49</v>
       </c>
-      <c r="AA53" s="21">
-        <f>MAX(C53:Y53)</f>
+      <c r="AB53" s="21">
+        <f>MAX(C53:Z53)</f>
         <v>1.99</v>
       </c>
-      <c r="AB53" s="21">
-        <f>AVERAGE(C53:Y53)</f>
-        <v>1.7627272727272725</v>
-      </c>
       <c r="AC53" s="21">
-        <f>AVERAGE(Q53:Y53)</f>
-        <v>1.8233333333333333</v>
-      </c>
-      <c r="AD53" s="22">
-        <f>(AC53/AB53)-1</f>
-        <v>3.4381983840467756e-002</v>
+        <f>AVERAGE(C53:Z53)</f>
+        <v>1.7816666666666663</v>
+      </c>
+      <c r="AD53" s="21">
+        <f>AVERAGE(Q53:Z53)</f>
+        <v>1.8399999999999999</v>
       </c>
       <c r="AE53" s="22">
-        <f>(AC53/Z53)-1</f>
-        <v>0.22371364653243853</v>
+        <f>(AD53/AC53)-1</f>
+        <v>3.2740879326473404e-002</v>
       </c>
       <c r="AF53" s="22">
-        <f>(AA53/Z53)-1</f>
+        <f>(AD53/AA53)-1</f>
+        <v>0.2348993288590604</v>
+      </c>
+      <c r="AG53" s="22">
+        <f>(AB53/AA53)-1</f>
         <v>0.33557046979865768</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="Z1:Z6"/>
     <mergeCell ref="AA1:AA6"/>
     <mergeCell ref="AB1:AB6"/>
     <mergeCell ref="AC1:AC6"/>
     <mergeCell ref="AD1:AD6"/>
     <mergeCell ref="AE1:AE6"/>
     <mergeCell ref="AF1:AF6"/>
+    <mergeCell ref="AG1:AG6"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="AG8"/>
-    <hyperlink r:id="rId2" ref="AG9"/>
-    <hyperlink r:id="rId3" ref="AG10"/>
-    <hyperlink r:id="rId4" ref="AG11"/>
-    <hyperlink r:id="rId5" ref="AG12"/>
-    <hyperlink r:id="rId6" ref="AG13"/>
-    <hyperlink r:id="rId7" ref="AG14"/>
-    <hyperlink r:id="rId8" ref="AG15"/>
-    <hyperlink r:id="rId9" ref="AG16"/>
-    <hyperlink r:id="rId10" ref="AG17"/>
-    <hyperlink r:id="rId11" ref="AG18"/>
-    <hyperlink r:id="rId12" ref="AG19"/>
-    <hyperlink r:id="rId13" ref="AG20"/>
-    <hyperlink r:id="rId14" ref="AG21"/>
-    <hyperlink r:id="rId15" ref="AG22"/>
-    <hyperlink r:id="rId16" ref="AG23"/>
-    <hyperlink r:id="rId17" ref="AG24"/>
-    <hyperlink r:id="rId18" ref="AG25"/>
-    <hyperlink r:id="rId19" ref="AG26"/>
-    <hyperlink r:id="rId20" ref="AG27"/>
-    <hyperlink r:id="rId21" ref="AG28"/>
-    <hyperlink r:id="rId22" ref="AG29"/>
-    <hyperlink r:id="rId23" ref="AG30"/>
-    <hyperlink r:id="rId24" ref="AG31"/>
-    <hyperlink r:id="rId25" ref="AG32"/>
-    <hyperlink r:id="rId26" ref="AG33"/>
-    <hyperlink r:id="rId27" ref="AG34"/>
-    <hyperlink r:id="rId28" ref="AG35"/>
-    <hyperlink r:id="rId29" ref="AG36"/>
-    <hyperlink r:id="rId29" ref="AG37"/>
-    <hyperlink r:id="rId29" ref="AG38"/>
-    <hyperlink r:id="rId29" ref="AG39"/>
-    <hyperlink r:id="rId29" ref="AG40"/>
-    <hyperlink r:id="rId29" ref="AG41"/>
-    <hyperlink r:id="rId30" ref="AG43"/>
-    <hyperlink r:id="rId31" ref="AG44"/>
-    <hyperlink r:id="rId32" ref="AG45"/>
-    <hyperlink r:id="rId33" ref="AG46"/>
-    <hyperlink r:id="rId34" ref="AG47"/>
-    <hyperlink r:id="rId35" ref="AG49"/>
-    <hyperlink r:id="rId36" ref="AG51"/>
-    <hyperlink r:id="rId37" ref="AG52"/>
+    <hyperlink r:id="rId1" ref="AH8"/>
+    <hyperlink r:id="rId2" ref="AH9"/>
+    <hyperlink r:id="rId3" ref="AH10"/>
+    <hyperlink r:id="rId4" ref="AH11"/>
+    <hyperlink r:id="rId5" ref="AH12"/>
+    <hyperlink r:id="rId6" ref="AH13"/>
+    <hyperlink r:id="rId7" ref="AH14"/>
+    <hyperlink r:id="rId8" ref="AH15"/>
+    <hyperlink r:id="rId9" ref="AH16"/>
+    <hyperlink r:id="rId10" ref="AH17"/>
+    <hyperlink r:id="rId11" ref="AH18"/>
+    <hyperlink r:id="rId12" ref="AH19"/>
+    <hyperlink r:id="rId13" ref="AH20"/>
+    <hyperlink r:id="rId14" ref="AH21"/>
+    <hyperlink r:id="rId15" ref="AH22"/>
+    <hyperlink r:id="rId16" ref="AH23"/>
+    <hyperlink r:id="rId17" ref="AH24"/>
+    <hyperlink r:id="rId18" ref="AH25"/>
+    <hyperlink r:id="rId19" ref="AH26"/>
+    <hyperlink r:id="rId20" ref="AH27"/>
+    <hyperlink r:id="rId21" ref="AH28"/>
+    <hyperlink r:id="rId22" ref="AH29"/>
+    <hyperlink r:id="rId23" ref="AH30"/>
+    <hyperlink r:id="rId24" ref="AH31"/>
+    <hyperlink r:id="rId25" ref="AH32"/>
+    <hyperlink r:id="rId26" ref="AH33"/>
+    <hyperlink r:id="rId27" ref="AH34"/>
+    <hyperlink r:id="rId28" ref="AH35"/>
+    <hyperlink r:id="rId29" ref="AH36"/>
+    <hyperlink r:id="rId29" ref="AH37"/>
+    <hyperlink r:id="rId29" ref="AH38"/>
+    <hyperlink r:id="rId29" ref="AH39"/>
+    <hyperlink r:id="rId29" ref="AH40"/>
+    <hyperlink r:id="rId29" ref="AH41"/>
+    <hyperlink r:id="rId30" ref="AH43"/>
+    <hyperlink r:id="rId31" ref="AH44"/>
+    <hyperlink r:id="rId32" ref="AH45"/>
+    <hyperlink r:id="rId33" ref="AH46"/>
+    <hyperlink r:id="rId34" ref="AH47"/>
+    <hyperlink r:id="rId35" ref="AH49"/>
+    <hyperlink r:id="rId36" ref="AH51"/>
+    <hyperlink r:id="rId37" ref="AH52"/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.25196850393700787" right="0.25196850393700787" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="34" firstPageNumber="1" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="1" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <pageSetup paperSize="9" scale="32" firstPageNumber="1" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="1" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/analyse-prix-composants.xlsx
+++ b/analyse-prix-composants.xlsx
@@ -10,7 +10,7 @@
   </sheets>
   <definedNames>
     <definedName name="Print_Titles" localSheetId="0">Feuille1!$3:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Feuille1!$A$1:$AJ$57</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Feuille1!$A$1:$AK$58</definedName>
   </definedNames>
   <calcPr/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="171">
   <si>
     <t xml:space="preserve">Le prix des composants IT</t>
   </si>
@@ -141,6 +141,9 @@
     <t xml:space="preserve">2 mai 2026</t>
   </si>
   <si>
+    <t xml:space="preserve">9 mai 2026</t>
+  </si>
+  <si>
     <t>Min</t>
   </si>
   <si>
@@ -292,7 +295,13 @@
     <t xml:space="preserve">ASRock Intel Arc Pro B60 Creator 24GB</t>
   </si>
   <si>
-    <t>https://www.materiel.net/produit/202601060101.html</t>
+    <t>https://www.amazon.fr/dp/B0GVGFW7MB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASRock Intel Arc Pro B70 Creator 32GB</t>
+  </si>
+  <si>
+    <t>https://www.amazon.fr/dp/B0GXHLFV2G</t>
   </si>
   <si>
     <t xml:space="preserve">PNY nVidia T400 2GB (30W)</t>
@@ -1403,12 +1412,12 @@
     <col bestFit="1" min="12" max="12" style="4" width="11.7109375"/>
     <col bestFit="1" min="13" max="13" style="4" width="13.00390625"/>
     <col bestFit="1" min="14" max="15" style="4" width="14.140625"/>
-    <col customWidth="1" min="16" max="29" style="1" width="12.7109375"/>
-    <col customWidth="1" min="30" max="33" style="2" width="12.7109375"/>
-    <col customWidth="1" min="34" max="34" style="2" width="14.140625"/>
-    <col customWidth="1" min="35" max="36" style="2" width="12.7109375"/>
-    <col customWidth="1" min="37" max="37" style="5" width="42.28125"/>
-    <col min="38" max="16384" style="1" width="9.140625"/>
+    <col customWidth="1" min="16" max="30" style="1" width="12.7109375"/>
+    <col customWidth="1" min="31" max="34" style="2" width="12.7109375"/>
+    <col customWidth="1" min="35" max="35" style="2" width="14.140625"/>
+    <col customWidth="1" min="36" max="37" style="2" width="12.7109375"/>
+    <col customWidth="1" min="38" max="38" style="5" width="42.28125"/>
+    <col min="39" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" ht="57.75" customHeight="1">
@@ -1430,28 +1439,29 @@
       <c r="AA1" s="1"/>
       <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
-      <c r="AD1" s="7" t="s">
+      <c r="AD1" s="1"/>
+      <c r="AE1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="AE1" s="7" t="s">
+      <c r="AF1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="AF1" s="7" t="s">
+      <c r="AG1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="AG1" s="7" t="s">
+      <c r="AH1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="AH1" s="7" t="s">
+      <c r="AI1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="AI1" s="7" t="s">
+      <c r="AJ1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="AJ1" s="7" t="s">
+      <c r="AK1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="AK1" s="5"/>
+      <c r="AL1" s="5"/>
     </row>
     <row r="2" ht="39.75" customHeight="1">
       <c r="A2" s="2"/>
@@ -1472,13 +1482,14 @@
       <c r="AA2" s="1"/>
       <c r="AB2" s="1"/>
       <c r="AC2" s="1"/>
-      <c r="AD2" s="7"/>
+      <c r="AD2" s="1"/>
       <c r="AE2" s="7"/>
       <c r="AF2" s="7"/>
       <c r="AG2" s="7"/>
       <c r="AH2" s="7"/>
       <c r="AI2" s="7"/>
       <c r="AJ2" s="7"/>
+      <c r="AK2" s="7"/>
     </row>
     <row r="3" ht="18">
       <c r="A3" s="9" t="s">
@@ -1568,7 +1579,7 @@
       <c r="AC3" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="AD3" s="12" t="s">
+      <c r="AD3" s="11" t="s">
         <v>38</v>
       </c>
       <c r="AE3" s="12" t="s">
@@ -1589,16 +1600,19 @@
       <c r="AJ3" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="AK3" s="5" t="s">
+      <c r="AK3" s="12" t="s">
         <v>45</v>
+      </c>
+      <c r="AL3" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="4" ht="36">
       <c r="A4" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C4" s="14">
         <v>171.88</v>
@@ -1625,7 +1639,7 @@
         <v>341.57999999999998</v>
       </c>
       <c r="M4" s="16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N4" s="17">
         <v>321.14999999999998</v>
@@ -1675,48 +1689,51 @@
       <c r="AC4" s="18">
         <v>450.54000000000002</v>
       </c>
-      <c r="AD4" s="19">
-        <f>MIN(C4:AC4)</f>
+      <c r="AD4" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE4" s="19">
+        <f>MIN(C4:AD4)</f>
         <v>171.88</v>
       </c>
-      <c r="AE4" s="20">
-        <f>MAX(C4:AC4)</f>
+      <c r="AF4" s="20">
+        <f>MAX(C4:AD4)</f>
         <v>450.54000000000002</v>
       </c>
-      <c r="AF4" s="20">
-        <f>AVERAGE(C4:AC4)</f>
+      <c r="AG4" s="20">
+        <f>AVERAGE(C4:AD4)</f>
         <v>360.5704347826088</v>
       </c>
-      <c r="AG4" s="20">
-        <f>AVERAGE(Q4:AC4)</f>
+      <c r="AH4" s="20">
+        <f>AVERAGE(Q4:AD4)</f>
         <v>393.24846153846153</v>
       </c>
-      <c r="AH4" s="21">
-        <f>(AG4/AF4)-1</f>
+      <c r="AI4" s="21">
+        <f>(AH4/AG4)-1</f>
         <v>9.0628691660631144e-002</v>
       </c>
-      <c r="AI4" s="21">
-        <f>(AG4/AD4)-1</f>
+      <c r="AJ4" s="21">
+        <f>(AH4/AE4)-1</f>
         <v>1.2879244911476699</v>
       </c>
-      <c r="AJ4" s="21">
-        <f>(AE4/AD4)-1</f>
+      <c r="AK4" s="21">
+        <f>(AF4/AE4)-1</f>
         <v>1.6212473818943449</v>
       </c>
-      <c r="AK4" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="AL4" s="23">
+      <c r="AL4" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="AM4" s="23">
         <f>C2*1</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" ht="36">
       <c r="A5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C5" s="15"/>
       <c r="D5" s="24">
@@ -1728,7 +1745,7 @@
         <v>686</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="I5" s="16">
         <v>613.99000000000001</v>
@@ -1793,44 +1810,47 @@
       <c r="AC5" s="17">
         <v>978.75</v>
       </c>
-      <c r="AD5" s="19">
-        <f>MIN(C5:AC5)</f>
+      <c r="AD5" s="17">
+        <v>978.75</v>
+      </c>
+      <c r="AE5" s="19">
+        <f>MIN(C5:AD5)</f>
         <v>200.47999999999999</v>
       </c>
-      <c r="AE5" s="20">
-        <f>MAX(C5:AC5)</f>
+      <c r="AF5" s="20">
+        <f>MAX(C5:AD5)</f>
         <v>978.75</v>
       </c>
-      <c r="AF5" s="20">
-        <f>AVERAGE(C5:AC5)</f>
-        <v>839.45086956521754</v>
-      </c>
       <c r="AG5" s="20">
-        <f>AVERAGE(Q5:AC5)</f>
-        <v>919.16923076923081</v>
-      </c>
-      <c r="AH5" s="21">
-        <f>(AG5/AF5)-1</f>
-        <v>9.4964892043416738e-002</v>
+        <f>AVERAGE(C5:AD5)</f>
+        <v>845.25500000000011</v>
+      </c>
+      <c r="AH5" s="20">
+        <f>AVERAGE(Q5:AD5)</f>
+        <v>923.42500000000007</v>
       </c>
       <c r="AI5" s="21">
-        <f>(AG5/AD5)-1</f>
-        <v>3.5848425317699064</v>
+        <f>(AH5/AG5)-1</f>
+        <v>9.2480967282062787e-002</v>
       </c>
       <c r="AJ5" s="21">
-        <f>(AE5/AD5)-1</f>
+        <f>(AH5/AE5)-1</f>
+        <v>3.6060704309656826</v>
+      </c>
+      <c r="AK5" s="21">
+        <f>(AF5/AE5)-1</f>
         <v>3.8820331205107745</v>
       </c>
-      <c r="AK5" s="22" t="s">
-        <v>51</v>
+      <c r="AL5" s="22" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="6" ht="36">
       <c r="A6" s="25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C6" s="27"/>
       <c r="D6" s="24">
@@ -1907,44 +1927,47 @@
       <c r="AC6" s="17">
         <v>703</v>
       </c>
-      <c r="AD6" s="19">
-        <f>MIN(C6:AC6)</f>
+      <c r="AD6" s="17">
+        <v>714.80999999999995</v>
+      </c>
+      <c r="AE6" s="19">
+        <f>MIN(C6:AD6)</f>
         <v>284.13</v>
       </c>
-      <c r="AE6" s="20">
-        <f>MAX(C6:AC6)</f>
+      <c r="AF6" s="20">
+        <f>MAX(C6:AD6)</f>
         <v>717.78999999999996</v>
       </c>
-      <c r="AF6" s="20">
-        <f>AVERAGE(C6:AC6)</f>
-        <v>621.07208333333324</v>
-      </c>
       <c r="AG6" s="20">
-        <f>AVERAGE(Q6:AC6)</f>
-        <v>678.5276923076924</v>
-      </c>
-      <c r="AH6" s="21">
-        <f>(AG6/AF6)-1</f>
-        <v>9.2510371205209108e-002</v>
+        <f>AVERAGE(C6:AD6)</f>
+        <v>624.82159999999988</v>
+      </c>
+      <c r="AH6" s="20">
+        <f>AVERAGE(Q6:AD6)</f>
+        <v>681.11928571428575</v>
       </c>
       <c r="AI6" s="21">
-        <f>(AG6/AD6)-1</f>
-        <v>1.3880888758937542</v>
+        <f>(AH6/AG6)-1</f>
+        <v>9.0102015862265183e-002</v>
       </c>
       <c r="AJ6" s="21">
-        <f>(AE6/AD6)-1</f>
+        <f>(AH6/AE6)-1</f>
+        <v>1.3972100296142109</v>
+      </c>
+      <c r="AK6" s="21">
+        <f>(AF6/AE6)-1</f>
         <v>1.5262731848097699</v>
       </c>
-      <c r="AK6" s="22" t="s">
-        <v>53</v>
+      <c r="AL6" s="22" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="7" ht="36">
       <c r="A7" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C7" s="15"/>
       <c r="D7" s="15"/>
@@ -2015,44 +2038,47 @@
       <c r="AC7" s="17">
         <v>795.28999999999996</v>
       </c>
-      <c r="AD7" s="19">
-        <f>MIN(C7:AC7)</f>
+      <c r="AD7" s="18">
+        <v>887.78999999999996</v>
+      </c>
+      <c r="AE7" s="19">
+        <f>MIN(C7:AD7)</f>
         <v>685.71000000000004</v>
       </c>
-      <c r="AE7" s="20">
-        <f>MAX(C7:AC7)</f>
+      <c r="AF7" s="20">
+        <f>MAX(C7:AD7)</f>
         <v>887.78999999999996</v>
       </c>
-      <c r="AF7" s="20">
-        <f>AVERAGE(C7:AC7)</f>
-        <v>794.62333333333333</v>
-      </c>
       <c r="AG7" s="20">
-        <f>AVERAGE(Q7:AC7)</f>
-        <v>814.62307692307706</v>
-      </c>
-      <c r="AH7" s="21">
-        <f>(AG7/AF7)-1</f>
-        <v>2.5168835032628012e-002</v>
+        <f>AVERAGE(C7:AD7)</f>
+        <v>798.85818181818183</v>
+      </c>
+      <c r="AH7" s="20">
+        <f>AVERAGE(Q7:AD7)</f>
+        <v>819.84928571428588</v>
       </c>
       <c r="AI7" s="21">
-        <f>(AG7/AD7)-1</f>
-        <v>0.18799941217581351</v>
+        <f>(AH7/AG7)-1</f>
+        <v>2.6276383435579032e-002</v>
       </c>
       <c r="AJ7" s="21">
-        <f>(AE7/AD7)-1</f>
+        <f>(AH7/AE7)-1</f>
+        <v>0.19562101429800616</v>
+      </c>
+      <c r="AK7" s="21">
+        <f>(AF7/AE7)-1</f>
         <v>0.29470184188651172</v>
       </c>
-      <c r="AK7" s="22" t="s">
-        <v>55</v>
+      <c r="AL7" s="22" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="8" ht="18">
       <c r="A8" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C8" s="15"/>
       <c r="D8" s="16">
@@ -2129,45 +2155,48 @@
       <c r="AC8" s="17">
         <v>556.89999999999998</v>
       </c>
-      <c r="AD8" s="19">
-        <f>MIN(C8:AC8)</f>
+      <c r="AD8" s="17">
+        <v>557.98000000000002</v>
+      </c>
+      <c r="AE8" s="19">
+        <f>MIN(C8:AD8)</f>
         <v>465</v>
       </c>
-      <c r="AE8" s="20">
-        <f>MAX(C8:AC8)</f>
+      <c r="AF8" s="20">
+        <f>MAX(C8:AD8)</f>
         <v>623.12</v>
       </c>
-      <c r="AF8" s="20">
-        <f>AVERAGE(C8:AC8)</f>
-        <v>553.70666666666648</v>
-      </c>
       <c r="AG8" s="20">
-        <f>AVERAGE(Q8:AC8)</f>
-        <v>547.38769230769219</v>
-      </c>
-      <c r="AH8" s="21">
-        <f>(AG8/AF8)-1</f>
-        <v>-1.1412133426196069e-002</v>
+        <f>AVERAGE(C8:AD8)</f>
+        <v>553.8775999999998</v>
+      </c>
+      <c r="AH8" s="20">
+        <f>AVERAGE(Q8:AD8)</f>
+        <v>548.14428571428562</v>
       </c>
       <c r="AI8" s="21">
-        <f>(AG8/AD8)-1</f>
-        <v>0.17717783291976819</v>
+        <f>(AH8/AG8)-1</f>
+        <v>-1.0351229740495405e-002</v>
       </c>
       <c r="AJ8" s="21">
-        <f>(AE8/AD8)-1</f>
+        <f>(AH8/AE8)-1</f>
+        <v>0.17880491551459277</v>
+      </c>
+      <c r="AK8" s="21">
+        <f>(AF8/AE8)-1</f>
         <v>0.34004301075268817</v>
       </c>
-      <c r="AK8" s="22" t="s">
-        <v>58</v>
-      </c>
-      <c r="AL8" s="1"/>
+      <c r="AL8" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="AM8" s="1"/>
     </row>
     <row r="9" ht="18">
       <c r="A9" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C9" s="15"/>
       <c r="D9" s="16"/>
@@ -2242,44 +2271,47 @@
       <c r="AC9" s="17">
         <v>169</v>
       </c>
-      <c r="AD9" s="19">
-        <f>MIN(C9:AC9)</f>
+      <c r="AD9" s="17">
+        <v>159.99000000000001</v>
+      </c>
+      <c r="AE9" s="19">
+        <f>MIN(C9:AD9)</f>
         <v>122</v>
       </c>
-      <c r="AE9" s="20">
-        <f>MAX(C9:AC9)</f>
+      <c r="AF9" s="20">
+        <f>MAX(C9:AD9)</f>
         <v>169</v>
       </c>
-      <c r="AF9" s="20">
-        <f>AVERAGE(C9:AC9)</f>
-        <v>131.65217391304347</v>
-      </c>
       <c r="AG9" s="20">
-        <f>AVERAGE(Q9:AC9)</f>
-        <v>139.07692307692307</v>
-      </c>
-      <c r="AH9" s="21">
-        <f>(AG9/AF9)-1</f>
-        <v>5.6396707651661382e-002</v>
+        <f>AVERAGE(C9:AD9)</f>
+        <v>132.83291666666665</v>
+      </c>
+      <c r="AH9" s="20">
+        <f>AVERAGE(Q9:AD9)</f>
+        <v>140.57071428571427</v>
       </c>
       <c r="AI9" s="21">
-        <f>(AG9/AD9)-1</f>
-        <v>0.13997477931904156</v>
+        <f>(AH9/AG9)-1</f>
+        <v>5.8252109591668377e-002</v>
       </c>
       <c r="AJ9" s="21">
-        <f>(AE9/AD9)-1</f>
+        <f>(AH9/AE9)-1</f>
+        <v>0.15221896955503511</v>
+      </c>
+      <c r="AK9" s="21">
+        <f>(AF9/AE9)-1</f>
         <v>0.38524590163934436</v>
       </c>
-      <c r="AK9" s="29" t="s">
-        <v>61</v>
+      <c r="AL9" s="29" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="10" ht="18">
       <c r="A10" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" s="15"/>
       <c r="D10" s="16"/>
@@ -2312,44 +2344,47 @@
       <c r="AC10" s="16">
         <v>349</v>
       </c>
-      <c r="AD10" s="19">
-        <f>MIN(C10:AC10)</f>
+      <c r="AD10" s="16">
         <v>349</v>
       </c>
-      <c r="AE10" s="20">
-        <f>MAX(C10:AC10)</f>
+      <c r="AE10" s="19">
+        <f>MIN(C10:AD10)</f>
         <v>349</v>
       </c>
       <c r="AF10" s="20">
-        <f>AVERAGE(C10:AC10)</f>
+        <f>MAX(C10:AD10)</f>
         <v>349</v>
       </c>
       <c r="AG10" s="20">
-        <f>AVERAGE(Q10:AC10)</f>
+        <f>AVERAGE(C10:AD10)</f>
         <v>349</v>
       </c>
-      <c r="AH10" s="21">
-        <f>(AG10/AF10)-1</f>
+      <c r="AH10" s="20">
+        <f>AVERAGE(Q10:AD10)</f>
+        <v>349</v>
+      </c>
+      <c r="AI10" s="21">
+        <f>(AH10/AG10)-1</f>
         <v>0</v>
       </c>
-      <c r="AI10" s="21">
-        <f>(AG10/AD10)-1</f>
+      <c r="AJ10" s="21">
+        <f>(AH10/AE10)-1</f>
         <v>0</v>
       </c>
-      <c r="AJ10" s="21">
-        <f>(AE10/AD10)-1</f>
+      <c r="AK10" s="21">
+        <f>(AF10/AE10)-1</f>
         <v>0</v>
       </c>
-      <c r="AK10" s="29" t="s">
-        <v>63</v>
+      <c r="AL10" s="29" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="11" ht="18">
       <c r="A11" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C11" s="15"/>
       <c r="D11" s="16"/>
@@ -2382,44 +2417,47 @@
       <c r="AC11" s="16">
         <v>467</v>
       </c>
-      <c r="AD11" s="19">
-        <f>MIN(C11:AC11)</f>
+      <c r="AD11" s="16">
         <v>467</v>
       </c>
-      <c r="AE11" s="20">
-        <f>MAX(C11:AC11)</f>
+      <c r="AE11" s="19">
+        <f>MIN(C11:AD11)</f>
+        <v>467</v>
+      </c>
+      <c r="AF11" s="20">
+        <f>MAX(C11:AD11)</f>
         <v>515</v>
       </c>
-      <c r="AF11" s="20">
-        <f>AVERAGE(C11:AC11)</f>
-        <v>491</v>
-      </c>
       <c r="AG11" s="20">
-        <f>AVERAGE(Q11:AC11)</f>
-        <v>491</v>
-      </c>
-      <c r="AH11" s="21">
-        <f>(AG11/AF11)-1</f>
+        <f>AVERAGE(C11:AD11)</f>
+        <v>483</v>
+      </c>
+      <c r="AH11" s="20">
+        <f>AVERAGE(Q11:AD11)</f>
+        <v>483</v>
+      </c>
+      <c r="AI11" s="21">
+        <f>(AH11/AG11)-1</f>
         <v>0</v>
       </c>
-      <c r="AI11" s="21">
-        <f>(AG11/AD11)-1</f>
-        <v>5.1391862955032064e-002</v>
-      </c>
       <c r="AJ11" s="21">
-        <f>(AE11/AD11)-1</f>
+        <f>(AH11/AE11)-1</f>
+        <v>3.426124197002145e-002</v>
+      </c>
+      <c r="AK11" s="21">
+        <f>(AF11/AE11)-1</f>
         <v>0.10278372591006435</v>
       </c>
-      <c r="AK11" s="29" t="s">
-        <v>65</v>
+      <c r="AL11" s="29" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="12" ht="18">
       <c r="A12" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C12" s="15"/>
       <c r="D12" s="16"/>
@@ -2452,44 +2490,47 @@
       <c r="AC12" s="16">
         <v>179.88999999999999</v>
       </c>
-      <c r="AD12" s="19">
-        <f>MIN(C12:AC12)</f>
-        <v>173.84</v>
-      </c>
-      <c r="AE12" s="20">
-        <f>MAX(C12:AC12)</f>
+      <c r="AD12" s="16">
+        <v>165.13999999999999</v>
+      </c>
+      <c r="AE12" s="19">
+        <f>MIN(C12:AD12)</f>
+        <v>165.13999999999999</v>
+      </c>
+      <c r="AF12" s="20">
+        <f>MAX(C12:AD12)</f>
         <v>179.88999999999999</v>
       </c>
-      <c r="AF12" s="20">
-        <f>AVERAGE(C12:AC12)</f>
-        <v>176.86500000000001</v>
-      </c>
       <c r="AG12" s="20">
-        <f>AVERAGE(Q12:AC12)</f>
-        <v>176.86500000000001</v>
-      </c>
-      <c r="AH12" s="21">
-        <f>(AG12/AF12)-1</f>
+        <f>AVERAGE(C12:AD12)</f>
+        <v>172.95666666666668</v>
+      </c>
+      <c r="AH12" s="20">
+        <f>AVERAGE(Q12:AD12)</f>
+        <v>172.95666666666668</v>
+      </c>
+      <c r="AI12" s="21">
+        <f>(AH12/AG12)-1</f>
         <v>0</v>
       </c>
-      <c r="AI12" s="21">
-        <f>(AG12/AD12)-1</f>
-        <v>1.7401058444546758e-002</v>
-      </c>
       <c r="AJ12" s="21">
-        <f>(AE12/AD12)-1</f>
-        <v>3.4802116889093293e-002</v>
-      </c>
-      <c r="AK12" s="29" t="s">
-        <v>67</v>
+        <f>(AH12/AE12)-1</f>
+        <v>4.7333575552056972e-002</v>
+      </c>
+      <c r="AK12" s="21">
+        <f>(AF12/AE12)-1</f>
+        <v>8.931815429332679e-002</v>
+      </c>
+      <c r="AL12" s="29" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="13" ht="36">
       <c r="A13" s="25" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C13" s="27"/>
       <c r="D13" s="24">
@@ -2525,19 +2566,19 @@
         <v>1084.8299999999999</v>
       </c>
       <c r="P13" s="16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Q13" s="16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R13" s="16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="S13" s="30">
         <v>1426.5699999999999</v>
       </c>
       <c r="T13" s="16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="U13" s="24">
         <v>592.17999999999995</v>
@@ -2552,58 +2593,61 @@
         <v>623.23000000000002</v>
       </c>
       <c r="Y13" s="16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="Z13" s="16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AA13" s="16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AB13" s="16" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AC13" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD13" s="19">
-        <f>MIN(C13:AC13)</f>
+        <v>49</v>
+      </c>
+      <c r="AD13" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE13" s="19">
+        <f>MIN(C13:AD13)</f>
         <v>592.17999999999995</v>
       </c>
-      <c r="AE13" s="20">
-        <f>MAX(C13:AC13)</f>
+      <c r="AF13" s="20">
+        <f>MAX(C13:AD13)</f>
         <v>1426.5699999999999</v>
       </c>
-      <c r="AF13" s="20">
-        <f>AVERAGE(C13:AC13)</f>
+      <c r="AG13" s="20">
+        <f>AVERAGE(C13:AD13)</f>
         <v>853.96466666666674</v>
       </c>
-      <c r="AG13" s="20">
-        <f>AVERAGE(Q13:AC13)</f>
+      <c r="AH13" s="20">
+        <f>AVERAGE(Q13:AD13)</f>
         <v>771.42200000000003</v>
       </c>
-      <c r="AH13" s="21">
-        <f>(AG13/AF13)-1</f>
+      <c r="AI13" s="21">
+        <f>(AH13/AG13)-1</f>
         <v>-9.665817555293077e-002</v>
       </c>
-      <c r="AI13" s="21">
-        <f>(AG13/AD13)-1</f>
+      <c r="AJ13" s="21">
+        <f>(AH13/AE13)-1</f>
         <v>0.30268161707588925</v>
       </c>
-      <c r="AJ13" s="21">
-        <f>(AE13/AD13)-1</f>
+      <c r="AK13" s="21">
+        <f>(AF13/AE13)-1</f>
         <v>1.4090141511027054</v>
       </c>
-      <c r="AK13" s="22" t="s">
-        <v>70</v>
+      <c r="AL13" s="22" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="14" ht="18">
       <c r="A14" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C14" s="15"/>
       <c r="D14" s="15"/>
@@ -2672,44 +2716,47 @@
       <c r="AC14" s="17">
         <v>647.98000000000002</v>
       </c>
-      <c r="AD14" s="19">
-        <f>MIN(C14:AC14)</f>
+      <c r="AD14" s="17">
+        <v>608.89999999999998</v>
+      </c>
+      <c r="AE14" s="19">
+        <f>MIN(C14:AD14)</f>
         <v>580.98000000000002</v>
       </c>
-      <c r="AE14" s="20">
-        <f>MAX(C14:AC14)</f>
+      <c r="AF14" s="20">
+        <f>MAX(C14:AD14)</f>
         <v>709.99000000000001</v>
       </c>
-      <c r="AF14" s="20">
-        <f>AVERAGE(C14:AC14)</f>
-        <v>650.8594999999998</v>
-      </c>
       <c r="AG14" s="20">
-        <f>AVERAGE(Q14:AC14)</f>
-        <v>665.29999999999995</v>
-      </c>
-      <c r="AH14" s="21">
-        <f>(AG14/AF14)-1</f>
-        <v>2.2186816048625158e-002</v>
+        <f>AVERAGE(C14:AD14)</f>
+        <v>648.86142857142841</v>
+      </c>
+      <c r="AH14" s="20">
+        <f>AVERAGE(Q14:AD14)</f>
+        <v>661.27142857142849</v>
       </c>
       <c r="AI14" s="21">
-        <f>(AG14/AD14)-1</f>
-        <v>0.14513408378945902</v>
+        <f>(AH14/AG14)-1</f>
+        <v>1.9125809384790582e-002</v>
       </c>
       <c r="AJ14" s="21">
-        <f>(AE14/AD14)-1</f>
+        <f>(AH14/AE14)-1</f>
+        <v>0.13819998721372251</v>
+      </c>
+      <c r="AK14" s="21">
+        <f>(AF14/AE14)-1</f>
         <v>0.22205583668973117</v>
       </c>
-      <c r="AK14" s="22" t="s">
-        <v>72</v>
+      <c r="AL14" s="22" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="15" ht="18">
       <c r="A15" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C15" s="15"/>
       <c r="D15" s="15"/>
@@ -2778,44 +2825,47 @@
       <c r="AC15" s="16">
         <v>679.28999999999996</v>
       </c>
-      <c r="AD15" s="19">
-        <f>MIN(C15:AC15)</f>
+      <c r="AD15" s="16">
+        <v>675.62</v>
+      </c>
+      <c r="AE15" s="19">
+        <f>MIN(C15:AD15)</f>
         <v>622.63</v>
       </c>
-      <c r="AE15" s="20">
-        <f>MAX(C15:AC15)</f>
+      <c r="AF15" s="20">
+        <f>MAX(C15:AD15)</f>
         <v>728.61000000000001</v>
       </c>
-      <c r="AF15" s="20">
-        <f>AVERAGE(C15:AC15)</f>
-        <v>681.45299999999986</v>
-      </c>
       <c r="AG15" s="20">
-        <f>AVERAGE(Q15:AC15)</f>
-        <v>689.55384615384617</v>
-      </c>
-      <c r="AH15" s="21">
-        <f>(AG15/AF15)-1</f>
-        <v>1.1887608028501306e-002</v>
+        <f>AVERAGE(C15:AD15)</f>
+        <v>681.175238095238</v>
+      </c>
+      <c r="AH15" s="20">
+        <f>AVERAGE(Q15:AD15)</f>
+        <v>688.55857142857155</v>
       </c>
       <c r="AI15" s="21">
-        <f>(AG15/AD15)-1</f>
-        <v>0.10748573977136688</v>
+        <f>(AH15/AG15)-1</f>
+        <v>1.0839109997567542e-002</v>
       </c>
       <c r="AJ15" s="21">
-        <f>(AE15/AD15)-1</f>
+        <f>(AH15/AE15)-1</f>
+        <v>0.10588723869484529</v>
+      </c>
+      <c r="AK15" s="21">
+        <f>(AF15/AE15)-1</f>
         <v>0.17021344940012528</v>
       </c>
-      <c r="AK15" s="22" t="s">
-        <v>74</v>
+      <c r="AL15" s="22" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="16" ht="18">
       <c r="A16" s="25" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C16" s="27"/>
       <c r="D16" s="28"/>
@@ -2890,44 +2940,47 @@
       <c r="AC16" s="16">
         <v>10741.540000000001</v>
       </c>
-      <c r="AD16" s="19">
-        <f>MIN(C16:AC16)</f>
+      <c r="AD16" s="16">
+        <v>10701.66</v>
+      </c>
+      <c r="AE16" s="19">
+        <f>MIN(C16:AD16)</f>
         <v>9100</v>
       </c>
-      <c r="AE16" s="20">
-        <f>MAX(C16:AC16)</f>
+      <c r="AF16" s="20">
+        <f>MAX(C16:AD16)</f>
         <v>11315.18</v>
       </c>
-      <c r="AF16" s="20">
-        <f>AVERAGE(C16:AC16)</f>
-        <v>10003.919999999998</v>
-      </c>
       <c r="AG16" s="20">
-        <f>AVERAGE(Q16:AC16)</f>
-        <v>10669.316923076925</v>
-      </c>
-      <c r="AH16" s="21">
-        <f>(AG16/AF16)-1</f>
-        <v>6.6513618969056942e-002</v>
+        <f>AVERAGE(C16:AD16)</f>
+        <v>10032.992499999998</v>
+      </c>
+      <c r="AH16" s="20">
+        <f>AVERAGE(Q16:AD16)</f>
+        <v>10671.627142857145</v>
       </c>
       <c r="AI16" s="21">
-        <f>(AG16/AD16)-1</f>
-        <v>0.17245240912933246</v>
+        <f>(AH16/AG16)-1</f>
+        <v>6.3653455622252997e-002</v>
       </c>
       <c r="AJ16" s="21">
-        <f>(AE16/AD16)-1</f>
+        <f>(AH16/AE16)-1</f>
+        <v>0.17270627943485106</v>
+      </c>
+      <c r="AK16" s="21">
+        <f>(AF16/AE16)-1</f>
         <v>0.24342637362637376</v>
       </c>
-      <c r="AK16" s="22" t="s">
-        <v>76</v>
+      <c r="AL16" s="22" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="17" ht="36">
       <c r="A17" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C17" s="15"/>
       <c r="D17" s="15"/>
@@ -2994,44 +3047,47 @@
       <c r="AC17" s="17">
         <v>1516</v>
       </c>
-      <c r="AD17" s="19">
-        <f>MIN(C17:AC17)</f>
+      <c r="AD17" s="17">
+        <v>1478.02</v>
+      </c>
+      <c r="AE17" s="19">
+        <f>MIN(C17:AD17)</f>
         <v>1297.6199999999999</v>
       </c>
-      <c r="AE17" s="20">
-        <f>MAX(C17:AC17)</f>
+      <c r="AF17" s="20">
+        <f>MAX(C17:AD17)</f>
         <v>1697.6199999999999</v>
       </c>
-      <c r="AF17" s="20">
-        <f>AVERAGE(C17:AC17)</f>
-        <v>1540.6863157894736</v>
-      </c>
       <c r="AG17" s="20">
-        <f>AVERAGE(Q17:AC17)</f>
-        <v>1573.4238461538459</v>
-      </c>
-      <c r="AH17" s="21">
-        <f>(AG17/AF17)-1</f>
-        <v>2.1248666927762727e-002</v>
+        <f>AVERAGE(C17:AD17)</f>
+        <v>1537.5529999999999</v>
+      </c>
+      <c r="AH17" s="20">
+        <f>AVERAGE(Q17:AD17)</f>
+        <v>1566.6092857142855</v>
       </c>
       <c r="AI17" s="21">
-        <f>(AG17/AD17)-1</f>
-        <v>0.21254592727751276</v>
+        <f>(AH17/AG17)-1</f>
+        <v>1.8897745778054809e-002</v>
       </c>
       <c r="AJ17" s="21">
-        <f>(AE17/AD17)-1</f>
+        <f>(AH17/AE17)-1</f>
+        <v>0.20729434327020679</v>
+      </c>
+      <c r="AK17" s="21">
+        <f>(AF17/AE17)-1</f>
         <v>0.30825665449052875</v>
       </c>
-      <c r="AK17" s="22" t="s">
-        <v>78</v>
+      <c r="AL17" s="22" t="s">
+        <v>79</v>
       </c>
     </row>
-    <row r="18" ht="36">
+    <row r="18" ht="18">
       <c r="A18" s="25" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B18" s="26" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C18" s="27"/>
       <c r="D18" s="28"/>
@@ -3040,112 +3096,115 @@
         <v>2279</v>
       </c>
       <c r="G18" s="28" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H18" s="28" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I18" s="28" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J18" s="28" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K18" s="28" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L18" s="28" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M18" s="28" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N18" s="28" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="O18" s="28" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="P18" s="16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Q18" s="16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="R18" s="16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="S18" s="16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="T18" s="16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="U18" s="16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="V18" s="16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="W18" s="16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="X18" s="16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Y18" s="16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="Z18" s="16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AA18" s="16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AB18" s="16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="AC18" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="AD18" s="19">
-        <f>MIN(C18:AC18)</f>
+        <v>81</v>
+      </c>
+      <c r="AD18" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="AE18" s="19">
+        <f>MIN(C18:AD18)</f>
         <v>2279</v>
       </c>
-      <c r="AE18" s="20">
-        <f>MAX(C18:AC18)</f>
+      <c r="AF18" s="20">
+        <f>MAX(C18:AD18)</f>
         <v>2279</v>
       </c>
-      <c r="AF18" s="20">
-        <f>AVERAGE(C18:AC18)</f>
+      <c r="AG18" s="20">
+        <f>AVERAGE(C18:AD18)</f>
         <v>2279</v>
       </c>
-      <c r="AG18" s="20" t="e">
-        <f>AVERAGE(Q18:AC18)</f>
+      <c r="AH18" s="20" t="e">
+        <f>AVERAGE(Q18:AD18)</f>
         <v>#NUM!</v>
       </c>
-      <c r="AH18" s="21" t="e">
-        <f>(AG18/AF18)-1</f>
+      <c r="AI18" s="21" t="e">
+        <f>(AH18/AG18)-1</f>
         <v>#NUM!</v>
       </c>
-      <c r="AI18" s="21" t="e">
-        <f>(AG18/AD18)-1</f>
+      <c r="AJ18" s="21" t="e">
+        <f>(AH18/AE18)-1</f>
         <v>#NUM!</v>
       </c>
-      <c r="AJ18" s="21">
-        <f>(AE18/AD18)-1</f>
+      <c r="AK18" s="21">
+        <f>(AF18/AE18)-1</f>
         <v>0</v>
       </c>
-      <c r="AK18" s="22" t="s">
-        <v>81</v>
+      <c r="AL18" s="22" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="19" ht="36">
       <c r="A19" s="25" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B19" s="26" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C19" s="27"/>
       <c r="D19" s="28"/>
@@ -3176,44 +3235,47 @@
       <c r="AC19" s="16">
         <v>3499.9499999999998</v>
       </c>
-      <c r="AD19" s="19">
-        <f>MIN(C19:AC19)</f>
+      <c r="AD19" s="16">
+        <v>3629</v>
+      </c>
+      <c r="AE19" s="19">
+        <f>MIN(C19:AD19)</f>
         <v>3499.9499999999998</v>
       </c>
-      <c r="AE19" s="20">
-        <f>MAX(C19:AC19)</f>
-        <v>3499.9499999999998</v>
-      </c>
       <c r="AF19" s="20">
-        <f>AVERAGE(C19:AC19)</f>
-        <v>3499.9499999999998</v>
+        <f>MAX(C19:AD19)</f>
+        <v>3629</v>
       </c>
       <c r="AG19" s="20">
-        <f>AVERAGE(Q19:AC19)</f>
-        <v>3499.9499999999998</v>
-      </c>
-      <c r="AH19" s="21">
-        <f>(AG19/AF19)-1</f>
+        <f>AVERAGE(C19:AD19)</f>
+        <v>3564.4749999999999</v>
+      </c>
+      <c r="AH19" s="20">
+        <f>AVERAGE(Q19:AD19)</f>
+        <v>3564.4749999999999</v>
+      </c>
+      <c r="AI19" s="21">
+        <f>(AH19/AG19)-1</f>
         <v>0</v>
       </c>
-      <c r="AI19" s="21">
-        <f>(AG19/AD19)-1</f>
-        <v>0</v>
-      </c>
       <c r="AJ19" s="21">
-        <f>(AE19/AD19)-1</f>
-        <v>0</v>
-      </c>
-      <c r="AK19" s="29" t="s">
-        <v>83</v>
+        <f>(AH19/AE19)-1</f>
+        <v>1.8435977656823699e-002</v>
+      </c>
+      <c r="AK19" s="21">
+        <f>(AF19/AE19)-1</f>
+        <v>3.6871955313647398e-002</v>
+      </c>
+      <c r="AL19" s="29" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="20" ht="18">
       <c r="A20" s="25" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B20" s="26" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C20" s="27"/>
       <c r="D20" s="28"/>
@@ -3244,44 +3306,47 @@
       <c r="AC20" s="16">
         <v>1624.75</v>
       </c>
-      <c r="AD20" s="19">
-        <f>MIN(C20:AC20)</f>
+      <c r="AD20" s="16">
+        <v>1601.5</v>
+      </c>
+      <c r="AE20" s="19">
+        <f>MIN(C20:AD20)</f>
+        <v>1601.5</v>
+      </c>
+      <c r="AF20" s="20">
+        <f>MAX(C20:AD20)</f>
         <v>1624.75</v>
       </c>
-      <c r="AE20" s="20">
-        <f>MAX(C20:AC20)</f>
-        <v>1624.75</v>
-      </c>
-      <c r="AF20" s="20">
-        <f>AVERAGE(C20:AC20)</f>
-        <v>1624.75</v>
-      </c>
       <c r="AG20" s="20">
-        <f>AVERAGE(Q20:AC20)</f>
-        <v>1624.75</v>
-      </c>
-      <c r="AH20" s="21">
-        <f>(AG20/AF20)-1</f>
+        <f>AVERAGE(C20:AD20)</f>
+        <v>1613.125</v>
+      </c>
+      <c r="AH20" s="20">
+        <f>AVERAGE(Q20:AD20)</f>
+        <v>1613.125</v>
+      </c>
+      <c r="AI20" s="21">
+        <f>(AH20/AG20)-1</f>
         <v>0</v>
       </c>
-      <c r="AI20" s="21">
-        <f>(AG20/AD20)-1</f>
-        <v>0</v>
-      </c>
       <c r="AJ20" s="21">
-        <f>(AE20/AD20)-1</f>
-        <v>0</v>
-      </c>
-      <c r="AK20" s="29" t="s">
-        <v>85</v>
+        <f>(AH20/AE20)-1</f>
+        <v>7.2588198563845463e-003</v>
+      </c>
+      <c r="AK20" s="21">
+        <f>(AF20/AE20)-1</f>
+        <v>1.4517639712769315e-002</v>
+      </c>
+      <c r="AL20" s="29" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="21" ht="18">
       <c r="A21" s="25" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C21" s="27"/>
       <c r="D21" s="28"/>
@@ -3312,494 +3377,463 @@
       <c r="AC21" s="16">
         <v>759.95000000000005</v>
       </c>
-      <c r="AD21" s="19">
-        <f>MIN(C21:AC21)</f>
+      <c r="AD21" s="16">
+        <v>692.88999999999999</v>
+      </c>
+      <c r="AE21" s="19">
+        <f>MIN(C21:AD21)</f>
+        <v>692.88999999999999</v>
+      </c>
+      <c r="AF21" s="20">
+        <f>MAX(C21:AD21)</f>
         <v>759.95000000000005</v>
       </c>
-      <c r="AE21" s="20">
-        <f>MAX(C21:AC21)</f>
-        <v>759.95000000000005</v>
-      </c>
-      <c r="AF21" s="20">
-        <f>AVERAGE(C21:AC21)</f>
-        <v>759.95000000000005</v>
-      </c>
       <c r="AG21" s="20">
-        <f>AVERAGE(Q21:AC21)</f>
-        <v>759.95000000000005</v>
-      </c>
-      <c r="AH21" s="21">
-        <f>(AG21/AF21)-1</f>
+        <f>AVERAGE(C21:AD21)</f>
+        <v>726.42000000000007</v>
+      </c>
+      <c r="AH21" s="20">
+        <f>AVERAGE(Q21:AD21)</f>
+        <v>726.42000000000007</v>
+      </c>
+      <c r="AI21" s="21">
+        <f>(AH21/AG21)-1</f>
         <v>0</v>
       </c>
-      <c r="AI21" s="21">
-        <f>(AG21/AD21)-1</f>
-        <v>0</v>
-      </c>
       <c r="AJ21" s="21">
-        <f>(AE21/AD21)-1</f>
-        <v>0</v>
-      </c>
-      <c r="AK21" s="29" t="s">
-        <v>87</v>
+        <f>(AH21/AE21)-1</f>
+        <v>4.8391519577422271e-002</v>
+      </c>
+      <c r="AK21" s="21">
+        <f>(AF21/AE21)-1</f>
+        <v>9.6783039154844319e-002</v>
+      </c>
+      <c r="AL21" s="29" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="22" ht="18">
-      <c r="A22" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C22" s="24">
-        <v>176.69</v>
-      </c>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="24">
-        <v>150</v>
-      </c>
-      <c r="H22" s="16">
-        <v>150</v>
-      </c>
-      <c r="I22" s="16">
-        <v>199</v>
-      </c>
-      <c r="J22" s="16">
-        <v>199</v>
-      </c>
-      <c r="K22" s="16">
-        <v>199</v>
-      </c>
-      <c r="L22" s="24">
-        <v>145</v>
-      </c>
-      <c r="M22" s="24">
-        <v>150</v>
-      </c>
-      <c r="N22" s="24">
-        <v>150</v>
-      </c>
-      <c r="O22" s="24">
-        <v>148.05000000000001</v>
-      </c>
-      <c r="P22" s="18">
-        <v>219.69</v>
-      </c>
-      <c r="Q22" s="30">
-        <v>237.69999999999999</v>
-      </c>
-      <c r="R22" s="30">
-        <v>237.69999999999999</v>
-      </c>
-      <c r="S22" s="30">
-        <v>237.69999999999999</v>
-      </c>
-      <c r="T22" s="30">
-        <v>237.69999999999999</v>
-      </c>
-      <c r="U22" s="30">
-        <v>237.69999999999999</v>
-      </c>
-      <c r="V22" s="30">
-        <v>228</v>
-      </c>
-      <c r="W22" s="30">
-        <v>228</v>
-      </c>
-      <c r="X22" s="30">
-        <v>228</v>
-      </c>
-      <c r="Y22" s="30">
-        <v>260</v>
-      </c>
-      <c r="Z22" s="30">
-        <v>260</v>
-      </c>
-      <c r="AA22" s="30">
-        <v>260</v>
-      </c>
-      <c r="AB22" s="30">
-        <v>260</v>
-      </c>
-      <c r="AC22" s="30">
-        <v>260</v>
-      </c>
-      <c r="AD22" s="19">
-        <f>MIN(C22:AC22)</f>
-        <v>145</v>
-      </c>
-      <c r="AE22" s="20">
-        <f>MAX(C22:AC22)</f>
-        <v>260</v>
+      <c r="A22" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="C22" s="27"/>
+      <c r="D22" s="28"/>
+      <c r="E22" s="28"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="28"/>
+      <c r="H22" s="28"/>
+      <c r="I22" s="28"/>
+      <c r="J22" s="28"/>
+      <c r="K22" s="28"/>
+      <c r="L22" s="28"/>
+      <c r="M22" s="28"/>
+      <c r="N22" s="28"/>
+      <c r="O22" s="28"/>
+      <c r="P22" s="16"/>
+      <c r="Q22" s="16"/>
+      <c r="R22" s="16"/>
+      <c r="S22" s="16"/>
+      <c r="T22" s="16"/>
+      <c r="U22" s="16"/>
+      <c r="V22" s="16"/>
+      <c r="W22" s="16"/>
+      <c r="X22" s="16"/>
+      <c r="Y22" s="16"/>
+      <c r="Z22" s="16"/>
+      <c r="AA22" s="16"/>
+      <c r="AB22" s="16"/>
+      <c r="AC22" s="16"/>
+      <c r="AD22" s="16">
+        <v>1410.9000000000001</v>
+      </c>
+      <c r="AE22" s="19">
+        <f>MIN(C22:AD22)</f>
+        <v>1410.9000000000001</v>
       </c>
       <c r="AF22" s="20">
-        <f>AVERAGE(C22:AC22)</f>
-        <v>210.78874999999996</v>
+        <f>MAX(C22:AD22)</f>
+        <v>1410.9000000000001</v>
       </c>
       <c r="AG22" s="20">
-        <f>AVERAGE(Q22:AC22)</f>
-        <v>244.03846153846155</v>
-      </c>
-      <c r="AH22" s="21">
-        <f>(AG22/AF22)-1</f>
-        <v>0.15773949766513429</v>
+        <f>AVERAGE(C22:AD22)</f>
+        <v>1410.9000000000001</v>
+      </c>
+      <c r="AH22" s="20">
+        <f>AVERAGE(Q22:AD22)</f>
+        <v>1410.9000000000001</v>
       </c>
       <c r="AI22" s="21">
-        <f>(AG22/AD22)-1</f>
-        <v>0.68302387267904519</v>
+        <f>(AH22/AG22)-1</f>
+        <v>0</v>
       </c>
       <c r="AJ22" s="21">
-        <f>(AE22/AD22)-1</f>
-        <v>0.7931034482758621</v>
-      </c>
-      <c r="AK22" s="22" t="s">
-        <v>89</v>
+        <f>(AH22/AE22)-1</f>
+        <v>0</v>
+      </c>
+      <c r="AK22" s="21">
+        <f>(AF22/AE22)-1</f>
+        <v>0</v>
+      </c>
+      <c r="AL22" s="29" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="23" ht="18">
       <c r="A23" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C23" s="16"/>
+        <v>91</v>
+      </c>
+      <c r="C23" s="24">
+        <v>176.69</v>
+      </c>
       <c r="D23" s="16"/>
       <c r="E23" s="16"/>
       <c r="F23" s="16"/>
-      <c r="G23" s="16">
-        <v>179</v>
+      <c r="G23" s="24">
+        <v>150</v>
       </c>
       <c r="H23" s="16">
-        <v>179</v>
+        <v>150</v>
       </c>
       <c r="I23" s="16">
-        <v>180</v>
-      </c>
-      <c r="J23" s="24">
-        <v>176.91999999999999</v>
-      </c>
-      <c r="K23" s="24">
-        <v>176.91999999999999</v>
+        <v>199</v>
+      </c>
+      <c r="J23" s="16">
+        <v>199</v>
+      </c>
+      <c r="K23" s="16">
+        <v>199</v>
       </c>
       <c r="L23" s="24">
-        <v>176.91999999999999</v>
+        <v>145</v>
       </c>
       <c r="M23" s="24">
-        <v>176.91999999999999</v>
+        <v>150</v>
       </c>
       <c r="N23" s="24">
-        <v>179</v>
+        <v>150</v>
       </c>
       <c r="O23" s="24">
-        <v>180</v>
-      </c>
-      <c r="P23" s="17">
-        <v>198.90000000000001</v>
-      </c>
-      <c r="Q23" s="17">
-        <v>203.93000000000001</v>
-      </c>
-      <c r="R23" s="17">
-        <v>208.97</v>
-      </c>
-      <c r="S23" s="17">
-        <v>212.09</v>
-      </c>
-      <c r="T23" s="17">
-        <v>212.31</v>
-      </c>
-      <c r="U23" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="V23" s="18">
-        <v>229.94999999999999</v>
-      </c>
-      <c r="W23" s="18">
-        <v>229.94</v>
-      </c>
-      <c r="X23" s="18">
-        <v>230</v>
+        <v>148.05000000000001</v>
+      </c>
+      <c r="P23" s="18">
+        <v>219.69</v>
+      </c>
+      <c r="Q23" s="30">
+        <v>237.69999999999999</v>
+      </c>
+      <c r="R23" s="30">
+        <v>237.69999999999999</v>
+      </c>
+      <c r="S23" s="30">
+        <v>237.69999999999999</v>
+      </c>
+      <c r="T23" s="30">
+        <v>237.69999999999999</v>
+      </c>
+      <c r="U23" s="30">
+        <v>237.69999999999999</v>
+      </c>
+      <c r="V23" s="30">
+        <v>228</v>
+      </c>
+      <c r="W23" s="30">
+        <v>228</v>
+      </c>
+      <c r="X23" s="30">
+        <v>228</v>
       </c>
       <c r="Y23" s="30">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="Z23" s="30">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AA23" s="30">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AB23" s="30">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="AC23" s="30">
-        <v>270</v>
-      </c>
-      <c r="AD23" s="19">
-        <f>MIN(C23:AC23)</f>
-        <v>176.91999999999999</v>
-      </c>
-      <c r="AE23" s="20">
-        <f>MAX(C23:AC23)</f>
-        <v>270</v>
+        <v>260</v>
+      </c>
+      <c r="AD23" s="30">
+        <v>260</v>
+      </c>
+      <c r="AE23" s="19">
+        <f>MIN(C23:AD23)</f>
+        <v>145</v>
       </c>
       <c r="AF23" s="20">
-        <f>AVERAGE(C23:AC23)</f>
-        <v>212.76227272727274</v>
+        <f>MAX(C23:AD23)</f>
+        <v>260</v>
       </c>
       <c r="AG23" s="20">
-        <f>AVERAGE(Q23:AC23)</f>
-        <v>239.76583333333335</v>
-      </c>
-      <c r="AH23" s="21">
-        <f>(AG23/AF23)-1</f>
-        <v>0.1269189328536402</v>
+        <f>AVERAGE(C23:AD23)</f>
+        <v>212.75719999999998</v>
+      </c>
+      <c r="AH23" s="20">
+        <f>AVERAGE(Q23:AD23)</f>
+        <v>245.17857142857142</v>
       </c>
       <c r="AI23" s="21">
-        <f>(AG23/AD23)-1</f>
-        <v>0.35522175747984042</v>
+        <f>(AH23/AG23)-1</f>
+        <v>0.15238671795159653</v>
       </c>
       <c r="AJ23" s="21">
-        <f>(AE23/AD23)-1</f>
-        <v>0.52611349762604576</v>
-      </c>
-      <c r="AK23" s="22" t="s">
-        <v>91</v>
+        <f>(AH23/AE23)-1</f>
+        <v>0.69088669950738901</v>
+      </c>
+      <c r="AK23" s="21">
+        <f>(AF23/AE23)-1</f>
+        <v>0.7931034482758621</v>
+      </c>
+      <c r="AL23" s="22" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="24" ht="18">
-      <c r="A24" s="25" t="s">
-        <v>68</v>
-      </c>
-      <c r="B24" s="26" t="s">
-        <v>92</v>
-      </c>
-      <c r="C24" s="28"/>
-      <c r="D24" s="28"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="28"/>
-      <c r="G24" s="28">
+      <c r="A24" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16">
+        <v>179</v>
+      </c>
+      <c r="H24" s="16">
+        <v>179</v>
+      </c>
+      <c r="I24" s="16">
+        <v>180</v>
+      </c>
+      <c r="J24" s="24">
+        <v>176.91999999999999</v>
+      </c>
+      <c r="K24" s="24">
+        <v>176.91999999999999</v>
+      </c>
+      <c r="L24" s="24">
+        <v>176.91999999999999</v>
+      </c>
+      <c r="M24" s="24">
+        <v>176.91999999999999</v>
+      </c>
+      <c r="N24" s="24">
+        <v>179</v>
+      </c>
+      <c r="O24" s="24">
+        <v>180</v>
+      </c>
+      <c r="P24" s="17">
+        <v>198.90000000000001</v>
+      </c>
+      <c r="Q24" s="17">
+        <v>203.93000000000001</v>
+      </c>
+      <c r="R24" s="17">
+        <v>208.97</v>
+      </c>
+      <c r="S24" s="17">
+        <v>212.09</v>
+      </c>
+      <c r="T24" s="17">
+        <v>212.31</v>
+      </c>
+      <c r="U24" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="V24" s="18">
+        <v>229.94999999999999</v>
+      </c>
+      <c r="W24" s="18">
+        <v>229.94</v>
+      </c>
+      <c r="X24" s="18">
+        <v>230</v>
+      </c>
+      <c r="Y24" s="30">
+        <v>270</v>
+      </c>
+      <c r="Z24" s="30">
+        <v>270</v>
+      </c>
+      <c r="AA24" s="30">
+        <v>270</v>
+      </c>
+      <c r="AB24" s="30">
+        <v>270</v>
+      </c>
+      <c r="AC24" s="30">
+        <v>270</v>
+      </c>
+      <c r="AD24" s="30">
+        <v>270</v>
+      </c>
+      <c r="AE24" s="19">
+        <f>MIN(C24:AD24)</f>
+        <v>176.91999999999999</v>
+      </c>
+      <c r="AF24" s="20">
+        <f>MAX(C24:AD24)</f>
+        <v>270</v>
+      </c>
+      <c r="AG24" s="20">
+        <f>AVERAGE(C24:AD24)</f>
+        <v>215.25086956521741</v>
+      </c>
+      <c r="AH24" s="20">
+        <f>AVERAGE(Q24:AD24)</f>
+        <v>242.09153846153848</v>
+      </c>
+      <c r="AI24" s="21">
+        <f>(AH24/AG24)-1</f>
+        <v>0.12469482214188599</v>
+      </c>
+      <c r="AJ24" s="21">
+        <f>(AH24/AE24)-1</f>
+        <v>0.36836727595262553</v>
+      </c>
+      <c r="AK24" s="21">
+        <f>(AF24/AE24)-1</f>
+        <v>0.52611349762604576</v>
+      </c>
+      <c r="AL24" s="22" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="25" ht="18">
+      <c r="A25" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="C25" s="28"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="28"/>
+      <c r="F25" s="28"/>
+      <c r="G25" s="28">
         <v>396.77999999999997</v>
       </c>
-      <c r="H24" s="28">
+      <c r="H25" s="28">
         <v>396.77999999999997</v>
       </c>
-      <c r="I24" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="J24" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="K24" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="L24" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="M24" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="N24" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="O24" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="P24" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q24" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="R24" s="16">
+      <c r="I25" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="J25" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="K25" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="L25" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="M25" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="N25" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="O25" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="P25" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q25" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="R25" s="16">
         <v>413</v>
       </c>
-      <c r="S24" s="16">
+      <c r="S25" s="16">
         <v>453.01999999999998</v>
       </c>
-      <c r="T24" s="16">
+      <c r="T25" s="16">
         <v>408.87</v>
       </c>
-      <c r="U24" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="V24" s="16">
+      <c r="U25" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="V25" s="16">
         <v>453.04000000000002</v>
       </c>
-      <c r="W24" s="16">
+      <c r="W25" s="16">
         <v>453.04000000000002</v>
       </c>
-      <c r="X24" s="16">
+      <c r="X25" s="16">
         <v>349</v>
       </c>
-      <c r="Y24" s="16">
+      <c r="Y25" s="16">
         <v>349</v>
       </c>
-      <c r="Z24" s="16">
+      <c r="Z25" s="16">
         <v>349</v>
       </c>
-      <c r="AA24" s="16">
+      <c r="AA25" s="16">
         <v>349</v>
       </c>
-      <c r="AB24" s="16">
+      <c r="AB25" s="16">
         <v>349</v>
       </c>
-      <c r="AC24" s="16">
+      <c r="AC25" s="16">
         <v>349</v>
       </c>
-      <c r="AD24" s="19">
-        <f>MIN(C24:AC24)</f>
+      <c r="AD25" s="16">
         <v>349</v>
       </c>
-      <c r="AE24" s="20">
-        <f>MAX(C24:AC24)</f>
+      <c r="AE25" s="19">
+        <f>MIN(C25:AD25)</f>
+        <v>349</v>
+      </c>
+      <c r="AF25" s="20">
+        <f>MAX(C25:AD25)</f>
         <v>453.04000000000002</v>
       </c>
-      <c r="AF24" s="20">
-        <f>AVERAGE(C24:AC24)</f>
-        <v>389.88692307692304</v>
-      </c>
-      <c r="AG24" s="20">
-        <f>AVERAGE(Q24:AC24)</f>
-        <v>388.6336363636363</v>
-      </c>
-      <c r="AH24" s="21">
-        <f>(AG24/AF24)-1</f>
-        <v>-3.2144876863168248e-003</v>
-      </c>
-      <c r="AI24" s="21">
-        <f>(AG24/AD24)-1</f>
-        <v>0.11356342797603514</v>
-      </c>
-      <c r="AJ24" s="21">
-        <f>(AE24/AD24)-1</f>
+      <c r="AG25" s="20">
+        <f>AVERAGE(C25:AD25)</f>
+        <v>386.96642857142854</v>
+      </c>
+      <c r="AH25" s="20">
+        <f>AVERAGE(Q25:AD25)</f>
+        <v>385.33083333333326</v>
+      </c>
+      <c r="AI25" s="21">
+        <f>(AH25/AG25)-1</f>
+        <v>-4.2267109426867844e-003</v>
+      </c>
+      <c r="AJ25" s="21">
+        <f>(AH25/AE25)-1</f>
+        <v>0.10409980897803228</v>
+      </c>
+      <c r="AK25" s="21">
+        <f>(AF25/AE25)-1</f>
         <v>0.29810888252148993</v>
       </c>
-      <c r="AK24" s="29" t="s">
-        <v>93</v>
+      <c r="AL25" s="29" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="25" ht="54">
-      <c r="A25" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16">
-        <v>550</v>
-      </c>
-      <c r="H25" s="16">
-        <v>550</v>
-      </c>
-      <c r="I25" s="16">
-        <v>550</v>
-      </c>
-      <c r="J25" s="16">
-        <v>550</v>
-      </c>
-      <c r="K25" s="16">
-        <v>550</v>
-      </c>
-      <c r="L25" s="16">
-        <v>550</v>
-      </c>
-      <c r="M25" s="16">
-        <v>550</v>
-      </c>
-      <c r="N25" s="16">
-        <v>550</v>
-      </c>
-      <c r="O25" s="16">
-        <v>550</v>
-      </c>
-      <c r="P25" s="16">
-        <v>550</v>
-      </c>
-      <c r="Q25" s="16">
-        <v>580</v>
-      </c>
-      <c r="R25" s="16">
-        <v>600</v>
-      </c>
-      <c r="S25" s="16">
-        <v>600</v>
-      </c>
-      <c r="T25" s="16">
-        <v>600</v>
-      </c>
-      <c r="U25" s="16">
-        <v>600</v>
-      </c>
-      <c r="V25" s="16">
-        <v>600</v>
-      </c>
-      <c r="W25" s="16">
-        <v>600</v>
-      </c>
-      <c r="X25" s="16">
-        <v>600</v>
-      </c>
-      <c r="Y25" s="16">
-        <v>600</v>
-      </c>
-      <c r="Z25" s="16">
-        <v>600</v>
-      </c>
-      <c r="AA25" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="AB25" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="AC25" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD25" s="19">
-        <f>MIN(C25:AC25)</f>
-        <v>550</v>
-      </c>
-      <c r="AE25" s="20">
-        <f>MAX(C25:AC25)</f>
-        <v>600</v>
-      </c>
-      <c r="AF25" s="20">
-        <f>AVERAGE(C25:AC25)</f>
-        <v>574</v>
-      </c>
-      <c r="AG25" s="20">
-        <f>AVERAGE(Q25:AC25)</f>
-        <v>598</v>
-      </c>
-      <c r="AH25" s="21">
-        <f>(AG25/AF25)-1</f>
-        <v>4.1811846689895571e-002</v>
-      </c>
-      <c r="AI25" s="21">
-        <f>(AG25/AD25)-1</f>
-        <v>8.7272727272727169e-002</v>
-      </c>
-      <c r="AJ25" s="21">
-        <f>(AE25/AD25)-1</f>
-        <v>9.0909090909090828e-002</v>
-      </c>
-      <c r="AK25" s="22" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="26" ht="36">
+    <row r="26" ht="54">
       <c r="A26" s="2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C26" s="16"/>
       <c r="D26" s="16"/>
@@ -3865,50 +3899,53 @@
       <c r="Z26" s="16">
         <v>600</v>
       </c>
-      <c r="AA26" s="16">
-        <v>800</v>
-      </c>
-      <c r="AB26" s="16">
-        <v>800</v>
-      </c>
-      <c r="AC26" s="24">
-        <v>599.99000000000001</v>
-      </c>
-      <c r="AD26" s="19">
-        <f>MIN(C26:AC26)</f>
+      <c r="AA26" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="AB26" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC26" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD26" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE26" s="19">
+        <f>MIN(C26:AD26)</f>
         <v>550</v>
       </c>
-      <c r="AE26" s="20">
-        <f>MAX(C26:AC26)</f>
-        <v>800</v>
-      </c>
       <c r="AF26" s="20">
-        <f>AVERAGE(C26:AC26)</f>
-        <v>594.78217391304349</v>
+        <f>MAX(C26:AD26)</f>
+        <v>600</v>
       </c>
       <c r="AG26" s="20">
-        <f>AVERAGE(Q26:AC26)</f>
-        <v>629.23000000000002</v>
-      </c>
-      <c r="AH26" s="21">
-        <f>(AG26/AF26)-1</f>
-        <v>5.7916709003442257e-002</v>
+        <f>AVERAGE(C26:AD26)</f>
+        <v>574</v>
+      </c>
+      <c r="AH26" s="20">
+        <f>AVERAGE(Q26:AD26)</f>
+        <v>598</v>
       </c>
       <c r="AI26" s="21">
-        <f>(AG26/AD26)-1</f>
-        <v>0.14405454545454544</v>
+        <f>(AH26/AG26)-1</f>
+        <v>4.1811846689895571e-002</v>
       </c>
       <c r="AJ26" s="21">
-        <f>(AE26/AD26)-1</f>
-        <v>0.45454545454545459</v>
-      </c>
-      <c r="AK26" s="29" t="s">
-        <v>98</v>
+        <f>(AH26/AE26)-1</f>
+        <v>8.7272727272727169e-002</v>
+      </c>
+      <c r="AK26" s="21">
+        <f>(AF26/AE26)-1</f>
+        <v>9.0909090909090828e-002</v>
+      </c>
+      <c r="AL26" s="22" t="s">
+        <v>99</v>
       </c>
     </row>
-    <row r="27" ht="18">
+    <row r="27" ht="36">
       <c r="A27" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>100</v>
@@ -3917,767 +3954,796 @@
       <c r="D27" s="16"/>
       <c r="E27" s="16"/>
       <c r="F27" s="16"/>
-      <c r="G27" s="24">
-        <v>329</v>
+      <c r="G27" s="16">
+        <v>550</v>
       </c>
       <c r="H27" s="16">
-        <v>329</v>
+        <v>550</v>
       </c>
       <c r="I27" s="16">
-        <v>329</v>
+        <v>550</v>
       </c>
       <c r="J27" s="16">
-        <v>472</v>
+        <v>550</v>
       </c>
       <c r="K27" s="16">
-        <v>480</v>
+        <v>550</v>
       </c>
       <c r="L27" s="16">
-        <v>479</v>
+        <v>550</v>
       </c>
       <c r="M27" s="16">
-        <v>479</v>
+        <v>550</v>
       </c>
       <c r="N27" s="16">
-        <v>478</v>
-      </c>
-      <c r="O27" s="17">
-        <v>529.95000000000005</v>
-      </c>
-      <c r="P27" s="17">
-        <v>529.95000000000005</v>
-      </c>
-      <c r="Q27" s="17">
-        <v>472</v>
-      </c>
-      <c r="R27" s="17">
-        <v>529.95000000000005</v>
-      </c>
-      <c r="S27" s="17">
-        <v>529.95000000000005</v>
-      </c>
-      <c r="T27" s="17">
-        <v>529.95000000000005</v>
-      </c>
-      <c r="U27" s="17">
-        <v>518</v>
-      </c>
-      <c r="V27" s="17">
-        <v>518</v>
-      </c>
-      <c r="W27" s="18">
-        <v>549</v>
-      </c>
-      <c r="X27" s="18">
-        <v>549</v>
-      </c>
-      <c r="Y27" s="18">
-        <v>549</v>
-      </c>
-      <c r="Z27" s="18">
-        <v>549</v>
-      </c>
-      <c r="AA27" s="30">
-        <v>969.95000000000005</v>
-      </c>
-      <c r="AB27" s="32">
-        <v>549</v>
-      </c>
-      <c r="AC27" s="32">
-        <v>549</v>
-      </c>
-      <c r="AD27" s="19">
-        <f>MIN(C27:AC27)</f>
-        <v>329</v>
-      </c>
-      <c r="AE27" s="20">
-        <f>MAX(C27:AC27)</f>
-        <v>969.95000000000005</v>
+        <v>550</v>
+      </c>
+      <c r="O27" s="16">
+        <v>550</v>
+      </c>
+      <c r="P27" s="16">
+        <v>550</v>
+      </c>
+      <c r="Q27" s="16">
+        <v>580</v>
+      </c>
+      <c r="R27" s="16">
+        <v>600</v>
+      </c>
+      <c r="S27" s="16">
+        <v>600</v>
+      </c>
+      <c r="T27" s="16">
+        <v>600</v>
+      </c>
+      <c r="U27" s="16">
+        <v>600</v>
+      </c>
+      <c r="V27" s="16">
+        <v>600</v>
+      </c>
+      <c r="W27" s="16">
+        <v>600</v>
+      </c>
+      <c r="X27" s="16">
+        <v>600</v>
+      </c>
+      <c r="Y27" s="16">
+        <v>600</v>
+      </c>
+      <c r="Z27" s="16">
+        <v>600</v>
+      </c>
+      <c r="AA27" s="16">
+        <v>800</v>
+      </c>
+      <c r="AB27" s="16">
+        <v>800</v>
+      </c>
+      <c r="AC27" s="24">
+        <v>599.99000000000001</v>
+      </c>
+      <c r="AD27" s="24">
+        <v>599.99000000000001</v>
+      </c>
+      <c r="AE27" s="19">
+        <f>MIN(C27:AD27)</f>
+        <v>550</v>
       </c>
       <c r="AF27" s="20">
-        <f>AVERAGE(C27:AC27)</f>
-        <v>512.89999999999998</v>
+        <f>MAX(C27:AD27)</f>
+        <v>800</v>
       </c>
       <c r="AG27" s="20">
-        <f>AVERAGE(Q27:AC27)</f>
-        <v>566.29230769230776</v>
-      </c>
-      <c r="AH27" s="21">
-        <f>(AG27/AF27)-1</f>
-        <v>0.10409886467597551</v>
+        <f>AVERAGE(C27:AD27)</f>
+        <v>594.99916666666661</v>
+      </c>
+      <c r="AH27" s="20">
+        <f>AVERAGE(Q27:AD27)</f>
+        <v>627.14142857142849</v>
       </c>
       <c r="AI27" s="21">
-        <f>(AG27/AD27)-1</f>
-        <v>0.72125321487023641</v>
+        <f>(AH27/AG27)-1</f>
+        <v>5.4020683902518352e-002</v>
       </c>
       <c r="AJ27" s="21">
-        <f>(AE27/AD27)-1</f>
-        <v>1.9481762917933132</v>
-      </c>
-      <c r="AK27" s="22" t="s">
+        <f>(AH27/AE27)-1</f>
+        <v>0.14025714285714264</v>
+      </c>
+      <c r="AK27" s="21">
+        <f>(AF27/AE27)-1</f>
+        <v>0.45454545454545459</v>
+      </c>
+      <c r="AL27" s="29" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="28" ht="18">
       <c r="A28" s="2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C28" s="16"/>
       <c r="D28" s="16"/>
       <c r="E28" s="16"/>
       <c r="F28" s="16"/>
       <c r="G28" s="24">
+        <v>329</v>
+      </c>
+      <c r="H28" s="16">
+        <v>329</v>
+      </c>
+      <c r="I28" s="16">
+        <v>329</v>
+      </c>
+      <c r="J28" s="16">
+        <v>472</v>
+      </c>
+      <c r="K28" s="16">
+        <v>480</v>
+      </c>
+      <c r="L28" s="16">
+        <v>479</v>
+      </c>
+      <c r="M28" s="16">
+        <v>479</v>
+      </c>
+      <c r="N28" s="16">
+        <v>478</v>
+      </c>
+      <c r="O28" s="17">
+        <v>529.95000000000005</v>
+      </c>
+      <c r="P28" s="17">
+        <v>529.95000000000005</v>
+      </c>
+      <c r="Q28" s="17">
+        <v>472</v>
+      </c>
+      <c r="R28" s="17">
+        <v>529.95000000000005</v>
+      </c>
+      <c r="S28" s="17">
+        <v>529.95000000000005</v>
+      </c>
+      <c r="T28" s="17">
+        <v>529.95000000000005</v>
+      </c>
+      <c r="U28" s="17">
+        <v>518</v>
+      </c>
+      <c r="V28" s="17">
+        <v>518</v>
+      </c>
+      <c r="W28" s="18">
+        <v>549</v>
+      </c>
+      <c r="X28" s="18">
+        <v>549</v>
+      </c>
+      <c r="Y28" s="18">
+        <v>549</v>
+      </c>
+      <c r="Z28" s="18">
+        <v>549</v>
+      </c>
+      <c r="AA28" s="30">
+        <v>969.95000000000005</v>
+      </c>
+      <c r="AB28" s="32">
+        <v>549</v>
+      </c>
+      <c r="AC28" s="32">
+        <v>549</v>
+      </c>
+      <c r="AD28" s="30">
+        <v>688</v>
+      </c>
+      <c r="AE28" s="19">
+        <f>MIN(C28:AD28)</f>
+        <v>329</v>
+      </c>
+      <c r="AF28" s="20">
+        <f>MAX(C28:AD28)</f>
+        <v>969.95000000000005</v>
+      </c>
+      <c r="AG28" s="20">
+        <f>AVERAGE(C28:AD28)</f>
+        <v>520.19583333333333</v>
+      </c>
+      <c r="AH28" s="20">
+        <f>AVERAGE(Q28:AD28)</f>
+        <v>574.98571428571427</v>
+      </c>
+      <c r="AI28" s="21">
+        <f>(AH28/AG28)-1</f>
+        <v>0.10532548982812107</v>
+      </c>
+      <c r="AJ28" s="21">
+        <f>(AH28/AE28)-1</f>
+        <v>0.74767694311767263</v>
+      </c>
+      <c r="AK28" s="21">
+        <f>(AF28/AE28)-1</f>
+        <v>1.9481762917933132</v>
+      </c>
+      <c r="AL28" s="22" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="29" ht="18">
+      <c r="A29" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="24">
         <v>371.14999999999998</v>
       </c>
-      <c r="H28" s="16">
+      <c r="H29" s="16">
         <v>371.14999999999998</v>
       </c>
-      <c r="I28" s="16">
+      <c r="I29" s="16">
         <v>371.14999999999998</v>
       </c>
-      <c r="J28" s="16">
+      <c r="J29" s="16">
         <v>435.13999999999999</v>
       </c>
-      <c r="K28" s="16">
+      <c r="K29" s="16">
         <v>436.93000000000001</v>
       </c>
-      <c r="L28" s="16">
+      <c r="L29" s="16">
         <v>434.66000000000003</v>
       </c>
-      <c r="M28" s="16">
+      <c r="M29" s="16">
         <v>436.93000000000001</v>
       </c>
-      <c r="N28" s="16">
+      <c r="N29" s="16">
         <v>435.14999999999998</v>
       </c>
-      <c r="O28" s="17">
+      <c r="O29" s="17">
         <v>463.79000000000002</v>
       </c>
-      <c r="P28" s="17">
+      <c r="P29" s="17">
         <v>462.67000000000002</v>
       </c>
-      <c r="Q28" s="17">
+      <c r="Q29" s="17">
         <v>473</v>
       </c>
-      <c r="R28" s="17">
+      <c r="R29" s="17">
         <v>504.73000000000002</v>
       </c>
-      <c r="S28" s="18">
+      <c r="S29" s="18">
         <v>513.71000000000004</v>
       </c>
-      <c r="T28" s="17">
+      <c r="T29" s="17">
         <v>476.07999999999998</v>
       </c>
-      <c r="U28" s="17">
+      <c r="U29" s="17">
         <v>475.56</v>
       </c>
-      <c r="V28" s="17">
+      <c r="V29" s="17">
         <v>435.14999999999998</v>
       </c>
-      <c r="W28" s="17">
+      <c r="W29" s="17">
         <v>483.99000000000001</v>
       </c>
-      <c r="X28" s="17">
+      <c r="X29" s="17">
         <v>435.14999999999998</v>
       </c>
-      <c r="Y28" s="17">
+      <c r="Y29" s="17">
         <v>472.97000000000003</v>
       </c>
-      <c r="Z28" s="17">
+      <c r="Z29" s="17">
         <v>435.14999999999998</v>
       </c>
-      <c r="AA28" s="17">
+      <c r="AA29" s="17">
         <v>435.14999999999998</v>
       </c>
-      <c r="AB28" s="17">
+      <c r="AB29" s="17">
         <v>435.14999999999998</v>
       </c>
-      <c r="AC28" s="30">
+      <c r="AC29" s="30">
         <v>648</v>
       </c>
-      <c r="AD28" s="19">
-        <f>MIN(C28:AC28)</f>
+      <c r="AD29" s="30">
+        <v>673.37</v>
+      </c>
+      <c r="AE29" s="19">
+        <f>MIN(C29:AD29)</f>
         <v>371.14999999999998</v>
       </c>
-      <c r="AE28" s="20">
-        <f>MAX(C28:AC28)</f>
-        <v>648</v>
-      </c>
-      <c r="AF28" s="20">
-        <f>AVERAGE(C28:AC28)</f>
-        <v>454.02217391304333</v>
-      </c>
-      <c r="AG28" s="20">
-        <f>AVERAGE(Q28:AC28)</f>
-        <v>478.75307692307683</v>
-      </c>
-      <c r="AH28" s="21">
-        <f>(AG28/AF28)-1</f>
-        <v>5.4470694232590766e-002</v>
-      </c>
-      <c r="AI28" s="21">
-        <f>(AG28/AD28)-1</f>
-        <v>0.28991803023865526</v>
-      </c>
-      <c r="AJ28" s="21">
-        <f>(AE28/AD28)-1</f>
-        <v>0.74592482823656225</v>
-      </c>
-      <c r="AK28" s="22" t="s">
-        <v>103</v>
+      <c r="AF29" s="20">
+        <f>MAX(C29:AD29)</f>
+        <v>673.37</v>
+      </c>
+      <c r="AG29" s="20">
+        <f>AVERAGE(C29:AD29)</f>
+        <v>463.16166666666658</v>
+      </c>
+      <c r="AH29" s="20">
+        <f>AVERAGE(Q29:AD29)</f>
+        <v>492.65428571428566</v>
+      </c>
+      <c r="AI29" s="21">
+        <f>(AH29/AG29)-1</f>
+        <v>6.3676727091589447e-002</v>
+      </c>
+      <c r="AJ29" s="21">
+        <f>(AH29/AE29)-1</f>
+        <v>0.32737245241623514</v>
+      </c>
+      <c r="AK29" s="21">
+        <f>(AF29/AE29)-1</f>
+        <v>0.8142799407247745</v>
+      </c>
+      <c r="AL29" s="22" t="s">
+        <v>106</v>
       </c>
     </row>
-    <row r="29" ht="36">
-      <c r="A29" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="B29" s="26" t="s">
-        <v>105</v>
-      </c>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28">
+    <row r="30" ht="36">
+      <c r="A30" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>108</v>
+      </c>
+      <c r="C30" s="28"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="28">
         <v>433.49000000000001</v>
       </c>
-      <c r="F29" s="24">
+      <c r="F30" s="24">
         <v>396</v>
       </c>
-      <c r="G29" s="28">
+      <c r="G30" s="28">
         <v>541.24000000000001</v>
       </c>
-      <c r="H29" s="28">
+      <c r="H30" s="28">
         <v>531.65999999999997</v>
       </c>
-      <c r="I29" s="28">
+      <c r="I30" s="28">
         <v>524.17999999999995</v>
       </c>
-      <c r="J29" s="28">
+      <c r="J30" s="28">
         <v>519.91999999999996</v>
       </c>
-      <c r="K29" s="28">
+      <c r="K30" s="28">
         <v>519.74000000000001</v>
       </c>
-      <c r="L29" s="28">
+      <c r="L30" s="28">
         <v>429.80000000000001</v>
       </c>
-      <c r="M29" s="28">
+      <c r="M30" s="28">
         <v>534.13</v>
       </c>
-      <c r="N29" s="28">
+      <c r="N30" s="28">
         <v>525.30999999999995</v>
       </c>
-      <c r="O29" s="28">
+      <c r="O30" s="28">
         <v>524.61000000000001</v>
       </c>
-      <c r="P29" s="16">
+      <c r="P30" s="16">
         <v>568.66999999999996</v>
       </c>
-      <c r="Q29" s="16">
+      <c r="Q30" s="16">
         <v>559.30999999999995</v>
       </c>
-      <c r="R29" s="16">
+      <c r="R30" s="16">
         <v>557.15999999999997</v>
       </c>
-      <c r="S29" s="16">
+      <c r="S30" s="16">
         <v>557.15999999999997</v>
       </c>
-      <c r="T29" s="16">
+      <c r="T30" s="16">
         <v>559.45000000000005</v>
       </c>
-      <c r="U29" s="16">
+      <c r="U30" s="16">
         <v>492.13999999999999</v>
       </c>
-      <c r="V29" s="30">
+      <c r="V30" s="30">
         <v>609.25</v>
       </c>
-      <c r="W29" s="32">
+      <c r="W30" s="32">
         <v>587.11000000000001</v>
       </c>
-      <c r="X29" s="32">
+      <c r="X30" s="32">
         <v>587.11000000000001</v>
       </c>
-      <c r="Y29" s="30">
+      <c r="Y30" s="30">
         <v>619.59000000000003</v>
       </c>
-      <c r="Z29" s="30">
+      <c r="Z30" s="30">
         <v>619.58000000000004</v>
       </c>
-      <c r="AA29" s="30">
+      <c r="AA30" s="30">
         <v>619.58000000000004</v>
       </c>
-      <c r="AB29" s="30">
+      <c r="AB30" s="30">
         <v>619.59000000000003</v>
       </c>
-      <c r="AC29" s="30">
+      <c r="AC30" s="30">
         <v>619.59000000000003</v>
       </c>
-      <c r="AD29" s="19">
-        <f>MIN(C29:AC29)</f>
+      <c r="AD30" s="30">
+        <v>619.59000000000003</v>
+      </c>
+      <c r="AE30" s="19">
+        <f>MIN(C30:AD30)</f>
         <v>396</v>
       </c>
-      <c r="AE29" s="20">
-        <f>MAX(C29:AC29)</f>
+      <c r="AF30" s="20">
+        <f>MAX(C30:AD30)</f>
         <v>619.59000000000003</v>
       </c>
-      <c r="AF29" s="20">
-        <f>AVERAGE(C29:AC29)</f>
-        <v>546.21480000000008</v>
-      </c>
-      <c r="AG29" s="20">
-        <f>AVERAGE(Q29:AC29)</f>
-        <v>585.12461538461537</v>
-      </c>
-      <c r="AH29" s="21">
-        <f>(AG29/AF29)-1</f>
-        <v>7.1235373674633617e-002</v>
-      </c>
-      <c r="AI29" s="21">
-        <f>(AG29/AD29)-1</f>
-        <v>0.47758741258741244</v>
-      </c>
-      <c r="AJ29" s="21">
-        <f>(AE29/AD29)-1</f>
+      <c r="AG30" s="20">
+        <f>AVERAGE(C30:AD30)</f>
+        <v>549.03692307692313</v>
+      </c>
+      <c r="AH30" s="20">
+        <f>AVERAGE(Q30:AD30)</f>
+        <v>587.58642857142854</v>
+      </c>
+      <c r="AI30" s="21">
+        <f>(AH30/AG30)-1</f>
+        <v>7.0212956313512542e-002</v>
+      </c>
+      <c r="AJ30" s="21">
+        <f>(AH30/AE30)-1</f>
+        <v>0.48380411255411238</v>
+      </c>
+      <c r="AK30" s="21">
+        <f>(AF30/AE30)-1</f>
         <v>0.56462121212121219</v>
       </c>
-      <c r="AK29" s="22" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="30" ht="18">
-      <c r="A30" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C30" s="16"/>
-      <c r="D30" s="24">
-        <v>381.82999999999998</v>
-      </c>
-      <c r="E30" s="16"/>
-      <c r="F30" s="16"/>
-      <c r="G30" s="16">
-        <v>931.41999999999996</v>
-      </c>
-      <c r="H30" s="16">
-        <v>902.87</v>
-      </c>
-      <c r="I30" s="16">
-        <v>902.87</v>
-      </c>
-      <c r="J30" s="17">
-        <v>990.46000000000004</v>
-      </c>
-      <c r="K30" s="17">
-        <v>984.66999999999996</v>
-      </c>
-      <c r="L30" s="17">
-        <v>1020.16</v>
-      </c>
-      <c r="M30" s="17">
-        <v>1153.71</v>
-      </c>
-      <c r="N30" s="17">
-        <v>988.74000000000001</v>
-      </c>
-      <c r="O30" s="18">
-        <v>1543.1300000000001</v>
-      </c>
-      <c r="P30" s="18">
-        <v>1552.5699999999999</v>
-      </c>
-      <c r="Q30" s="18">
-        <v>1542.1700000000001</v>
-      </c>
-      <c r="R30" s="18">
-        <v>1398</v>
-      </c>
-      <c r="S30" s="18">
-        <v>1534.8399999999999</v>
-      </c>
-      <c r="T30" s="33">
-        <v>370</v>
-      </c>
-      <c r="U30" s="30">
-        <v>1655.4000000000001</v>
-      </c>
-      <c r="V30" s="34">
-        <v>700</v>
-      </c>
-      <c r="W30" s="30">
-        <v>1678.0799999999999</v>
-      </c>
-      <c r="X30" s="30">
-        <v>1565.48</v>
-      </c>
-      <c r="Y30" s="30">
-        <v>1592.45</v>
-      </c>
-      <c r="Z30" s="30">
-        <v>1561.8099999999999</v>
-      </c>
-      <c r="AA30" s="30">
-        <v>1445.73</v>
-      </c>
-      <c r="AB30" s="30">
-        <v>1422.1300000000001</v>
-      </c>
-      <c r="AC30" s="30">
-        <v>1445.73</v>
-      </c>
-      <c r="AD30" s="19">
-        <f>MIN(C30:AC30)</f>
-        <v>370</v>
-      </c>
-      <c r="AE30" s="20">
-        <f>MAX(C30:AC30)</f>
-        <v>1678.0799999999999</v>
-      </c>
-      <c r="AF30" s="20">
-        <f>AVERAGE(C30:AC30)</f>
-        <v>1219.34375</v>
-      </c>
-      <c r="AG30" s="20">
-        <f>AVERAGE(Q30:AC30)</f>
-        <v>1377.8323076923077</v>
-      </c>
-      <c r="AH30" s="21">
-        <f>(AG30/AF30)-1</f>
-        <v>0.12997857059775608</v>
-      </c>
-      <c r="AI30" s="21">
-        <f>(AG30/AD30)-1</f>
-        <v>2.7238711018711022</v>
-      </c>
-      <c r="AJ30" s="21">
-        <f>(AE30/AD30)-1</f>
-        <v>3.535351351351351</v>
-      </c>
-      <c r="AK30" s="22" t="s">
-        <v>108</v>
+      <c r="AL30" s="22" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="31" ht="18">
       <c r="A31" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C31" s="16"/>
-      <c r="D31" s="16"/>
+      <c r="D31" s="24">
+        <v>381.82999999999998</v>
+      </c>
       <c r="E31" s="16"/>
       <c r="F31" s="16"/>
-      <c r="G31" s="16"/>
-      <c r="H31" s="16"/>
-      <c r="I31" s="16"/>
-      <c r="J31" s="16"/>
-      <c r="K31" s="16">
-        <v>109.98999999999999</v>
-      </c>
-      <c r="L31" s="16">
-        <v>109.98999999999999</v>
+      <c r="G31" s="16">
+        <v>931.41999999999996</v>
+      </c>
+      <c r="H31" s="16">
+        <v>902.87</v>
+      </c>
+      <c r="I31" s="16">
+        <v>902.87</v>
+      </c>
+      <c r="J31" s="17">
+        <v>990.46000000000004</v>
+      </c>
+      <c r="K31" s="17">
+        <v>984.66999999999996</v>
+      </c>
+      <c r="L31" s="17">
+        <v>1020.16</v>
       </c>
       <c r="M31" s="17">
-        <v>165.72999999999999</v>
+        <v>1153.71</v>
       </c>
       <c r="N31" s="17">
-        <v>124.98999999999999</v>
-      </c>
-      <c r="O31" s="17">
-        <v>134.99000000000001</v>
-      </c>
-      <c r="P31" s="17">
-        <v>139.99000000000001</v>
-      </c>
-      <c r="Q31" s="17">
-        <v>149.99000000000001</v>
-      </c>
-      <c r="R31" s="17">
-        <v>149.99000000000001</v>
-      </c>
-      <c r="S31" s="17">
-        <v>149.99000000000001</v>
-      </c>
-      <c r="T31" s="18">
-        <v>159.99000000000001</v>
-      </c>
-      <c r="U31" s="18">
-        <v>159.99000000000001</v>
-      </c>
-      <c r="V31" s="18">
-        <v>164.99000000000001</v>
-      </c>
-      <c r="W31" s="18">
-        <v>164.99000000000001</v>
-      </c>
-      <c r="X31" s="18">
-        <v>164.99000000000001</v>
-      </c>
-      <c r="Y31" s="18">
-        <v>166.99000000000001</v>
-      </c>
-      <c r="Z31" s="18">
-        <v>166.99000000000001</v>
-      </c>
-      <c r="AA31" s="18">
-        <v>169.99000000000001</v>
-      </c>
-      <c r="AB31" s="18">
-        <v>169.99000000000001</v>
-      </c>
-      <c r="AC31" s="18">
-        <v>169.97</v>
-      </c>
-      <c r="AD31" s="19">
-        <f>MIN(C31:AC31)</f>
-        <v>109.98999999999999</v>
-      </c>
-      <c r="AE31" s="20">
-        <f>MAX(C31:AC31)</f>
-        <v>169.99000000000001</v>
+        <v>988.74000000000001</v>
+      </c>
+      <c r="O31" s="18">
+        <v>1543.1300000000001</v>
+      </c>
+      <c r="P31" s="18">
+        <v>1552.5699999999999</v>
+      </c>
+      <c r="Q31" s="18">
+        <v>1542.1700000000001</v>
+      </c>
+      <c r="R31" s="18">
+        <v>1398</v>
+      </c>
+      <c r="S31" s="18">
+        <v>1534.8399999999999</v>
+      </c>
+      <c r="T31" s="33">
+        <v>370</v>
+      </c>
+      <c r="U31" s="30">
+        <v>1655.4000000000001</v>
+      </c>
+      <c r="V31" s="34">
+        <v>700</v>
+      </c>
+      <c r="W31" s="30">
+        <v>1678.0799999999999</v>
+      </c>
+      <c r="X31" s="30">
+        <v>1565.48</v>
+      </c>
+      <c r="Y31" s="30">
+        <v>1592.45</v>
+      </c>
+      <c r="Z31" s="30">
+        <v>1561.8099999999999</v>
+      </c>
+      <c r="AA31" s="30">
+        <v>1445.73</v>
+      </c>
+      <c r="AB31" s="30">
+        <v>1422.1300000000001</v>
+      </c>
+      <c r="AC31" s="30">
+        <v>1445.73</v>
+      </c>
+      <c r="AD31" s="30">
+        <v>1500</v>
+      </c>
+      <c r="AE31" s="19">
+        <f>MIN(C31:AD31)</f>
+        <v>370</v>
       </c>
       <c r="AF31" s="20">
-        <f>AVERAGE(C31:AC31)</f>
-        <v>152.34368421052628</v>
+        <f>MAX(C31:AD31)</f>
+        <v>1678.0799999999999</v>
       </c>
       <c r="AG31" s="20">
-        <f>AVERAGE(Q31:AC31)</f>
-        <v>162.21923076923076</v>
-      </c>
-      <c r="AH31" s="21">
-        <f>(AG31/AF31)-1</f>
-        <v>6.4824128482131815e-002</v>
+        <f>AVERAGE(C31:AD31)</f>
+        <v>1230.5699999999999</v>
+      </c>
+      <c r="AH31" s="20">
+        <f>AVERAGE(Q31:AD31)</f>
+        <v>1386.5585714285714</v>
       </c>
       <c r="AI31" s="21">
-        <f>(AG31/AD31)-1</f>
-        <v>0.47485435738913329</v>
+        <f>(AH31/AG31)-1</f>
+        <v>0.12676123376042936</v>
       </c>
       <c r="AJ31" s="21">
-        <f>(AE31/AD31)-1</f>
-        <v>0.54550413673970377</v>
-      </c>
-      <c r="AK31" s="22" t="s">
-        <v>110</v>
+        <f>(AH31/AE31)-1</f>
+        <v>2.7474555984555984</v>
+      </c>
+      <c r="AK31" s="21">
+        <f>(AF31/AE31)-1</f>
+        <v>3.535351351351351</v>
+      </c>
+      <c r="AL31" s="22" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="32" ht="18">
-      <c r="A32" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="B32" s="26" t="s">
-        <v>111</v>
-      </c>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="28"/>
-      <c r="J32" s="28"/>
-      <c r="K32" s="28">
-        <v>69</v>
-      </c>
-      <c r="L32" s="28">
-        <v>68</v>
-      </c>
-      <c r="M32" s="28">
-        <v>80.060000000000002</v>
-      </c>
-      <c r="N32" s="28">
-        <v>74.560000000000002</v>
-      </c>
-      <c r="O32" s="28">
-        <v>76.189999999999998</v>
-      </c>
-      <c r="P32" s="16">
-        <v>74.989999999999995</v>
-      </c>
-      <c r="Q32" s="16">
-        <v>77.319999999999993</v>
-      </c>
-      <c r="R32" s="16">
-        <v>83</v>
-      </c>
-      <c r="S32" s="16">
-        <v>83</v>
-      </c>
-      <c r="T32" s="16">
-        <v>83</v>
-      </c>
-      <c r="U32" s="16">
-        <v>81</v>
-      </c>
-      <c r="V32" s="17">
-        <v>85.700000000000003</v>
-      </c>
-      <c r="W32" s="17">
-        <v>82</v>
-      </c>
-      <c r="X32" s="17">
-        <v>82.890000000000001</v>
-      </c>
-      <c r="Y32" s="17">
-        <v>81.480000000000004</v>
-      </c>
-      <c r="Z32" s="17">
-        <v>81.480000000000004</v>
-      </c>
-      <c r="AA32" s="17">
-        <v>76.340000000000003</v>
-      </c>
-      <c r="AB32" s="17">
-        <v>81.900000000000006</v>
-      </c>
-      <c r="AC32" s="17">
-        <v>80.019999999999996</v>
-      </c>
-      <c r="AD32" s="19">
-        <f>MIN(C32:AC32)</f>
-        <v>68</v>
-      </c>
-      <c r="AE32" s="20">
-        <f>MAX(C32:AC32)</f>
-        <v>85.700000000000003</v>
+      <c r="A32" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C32" s="16"/>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="16"/>
+      <c r="G32" s="16"/>
+      <c r="H32" s="16"/>
+      <c r="I32" s="16"/>
+      <c r="J32" s="16"/>
+      <c r="K32" s="16">
+        <v>109.98999999999999</v>
+      </c>
+      <c r="L32" s="16">
+        <v>109.98999999999999</v>
+      </c>
+      <c r="M32" s="17">
+        <v>165.72999999999999</v>
+      </c>
+      <c r="N32" s="17">
+        <v>124.98999999999999</v>
+      </c>
+      <c r="O32" s="17">
+        <v>134.99000000000001</v>
+      </c>
+      <c r="P32" s="17">
+        <v>139.99000000000001</v>
+      </c>
+      <c r="Q32" s="17">
+        <v>149.99000000000001</v>
+      </c>
+      <c r="R32" s="17">
+        <v>149.99000000000001</v>
+      </c>
+      <c r="S32" s="17">
+        <v>149.99000000000001</v>
+      </c>
+      <c r="T32" s="18">
+        <v>159.99000000000001</v>
+      </c>
+      <c r="U32" s="18">
+        <v>159.99000000000001</v>
+      </c>
+      <c r="V32" s="18">
+        <v>164.99000000000001</v>
+      </c>
+      <c r="W32" s="18">
+        <v>164.99000000000001</v>
+      </c>
+      <c r="X32" s="18">
+        <v>164.99000000000001</v>
+      </c>
+      <c r="Y32" s="18">
+        <v>166.99000000000001</v>
+      </c>
+      <c r="Z32" s="18">
+        <v>166.99000000000001</v>
+      </c>
+      <c r="AA32" s="18">
+        <v>169.99000000000001</v>
+      </c>
+      <c r="AB32" s="18">
+        <v>169.99000000000001</v>
+      </c>
+      <c r="AC32" s="18">
+        <v>169.97</v>
+      </c>
+      <c r="AD32" s="18">
+        <v>169</v>
+      </c>
+      <c r="AE32" s="19">
+        <f>MIN(C32:AD32)</f>
+        <v>109.98999999999999</v>
       </c>
       <c r="AF32" s="20">
-        <f>AVERAGE(C32:AC32)</f>
-        <v>79.048947368421054</v>
+        <f>MAX(C32:AD32)</f>
+        <v>169.99000000000001</v>
       </c>
       <c r="AG32" s="20">
-        <f>AVERAGE(Q32:AC32)</f>
-        <v>81.471538461538472</v>
-      </c>
-      <c r="AH32" s="21">
-        <f>(AG32/AF32)-1</f>
-        <v>3.064672173086036e-002</v>
+        <f>AVERAGE(C32:AD32)</f>
+        <v>153.17649999999998</v>
+      </c>
+      <c r="AH32" s="20">
+        <f>AVERAGE(Q32:AD32)</f>
+        <v>162.70357142857142</v>
       </c>
       <c r="AI32" s="21">
-        <f>(AG32/AD32)-1</f>
-        <v>0.19811085972850684</v>
+        <f>(AH32/AG32)-1</f>
+        <v>6.2196690932169396e-002</v>
       </c>
       <c r="AJ32" s="21">
-        <f>(AE32/AD32)-1</f>
-        <v>0.26029411764705879</v>
-      </c>
-      <c r="AK32" s="22" t="s">
-        <v>112</v>
+        <f>(AH32/AE32)-1</f>
+        <v>0.47925785461015935</v>
+      </c>
+      <c r="AK32" s="21">
+        <f>(AF32/AE32)-1</f>
+        <v>0.54550413673970377</v>
+      </c>
+      <c r="AL32" s="22" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="33" ht="18">
-      <c r="A33" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C33" s="16"/>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
-      <c r="F33" s="16"/>
-      <c r="G33" s="16"/>
-      <c r="H33" s="16"/>
-      <c r="I33" s="16"/>
-      <c r="J33" s="16"/>
-      <c r="K33" s="16">
-        <v>69.989999999999995</v>
-      </c>
-      <c r="L33" s="16">
-        <v>55</v>
-      </c>
-      <c r="M33" s="16">
-        <v>55</v>
-      </c>
-      <c r="N33" s="17">
-        <v>84.590000000000003</v>
-      </c>
-      <c r="O33" s="17">
-        <v>82.590000000000003</v>
-      </c>
-      <c r="P33" s="17">
-        <v>82.590000000000003</v>
-      </c>
-      <c r="Q33" s="17">
-        <v>80.769999999999996</v>
-      </c>
-      <c r="R33" s="17">
-        <v>82.590000000000003</v>
-      </c>
-      <c r="S33" s="30">
-        <v>108</v>
-      </c>
-      <c r="T33" s="30">
-        <v>104.5</v>
-      </c>
-      <c r="U33" s="30">
-        <v>111</v>
-      </c>
-      <c r="V33" s="33">
-        <v>65.530000000000001</v>
-      </c>
-      <c r="W33" s="32">
-        <v>99.989999999999995</v>
-      </c>
-      <c r="X33" s="30">
+      <c r="A33" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="Y33" s="32">
-        <v>99.900000000000006</v>
-      </c>
-      <c r="Z33" s="32">
-        <v>99.900000000000006</v>
-      </c>
-      <c r="AA33" s="30">
-        <v>104.98999999999999</v>
-      </c>
-      <c r="AB33" s="32">
-        <v>97</v>
-      </c>
-      <c r="AC33" s="32">
-        <v>97</v>
-      </c>
-      <c r="AD33" s="19">
-        <f>MIN(C33:AC33)</f>
-        <v>55</v>
-      </c>
-      <c r="AE33" s="20">
-        <f>MAX(C33:AC33)</f>
-        <v>111</v>
+      <c r="B33" s="26" t="s">
+        <v>114</v>
+      </c>
+      <c r="C33" s="28"/>
+      <c r="D33" s="28"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="28"/>
+      <c r="G33" s="28"/>
+      <c r="H33" s="28"/>
+      <c r="I33" s="28"/>
+      <c r="J33" s="28"/>
+      <c r="K33" s="28">
+        <v>69</v>
+      </c>
+      <c r="L33" s="28">
+        <v>68</v>
+      </c>
+      <c r="M33" s="28">
+        <v>80.060000000000002</v>
+      </c>
+      <c r="N33" s="28">
+        <v>74.560000000000002</v>
+      </c>
+      <c r="O33" s="28">
+        <v>76.189999999999998</v>
+      </c>
+      <c r="P33" s="16">
+        <v>74.989999999999995</v>
+      </c>
+      <c r="Q33" s="16">
+        <v>77.319999999999993</v>
+      </c>
+      <c r="R33" s="16">
+        <v>83</v>
+      </c>
+      <c r="S33" s="16">
+        <v>83</v>
+      </c>
+      <c r="T33" s="16">
+        <v>83</v>
+      </c>
+      <c r="U33" s="16">
+        <v>81</v>
+      </c>
+      <c r="V33" s="17">
+        <v>85.700000000000003</v>
+      </c>
+      <c r="W33" s="17">
+        <v>82</v>
+      </c>
+      <c r="X33" s="17">
+        <v>82.890000000000001</v>
+      </c>
+      <c r="Y33" s="17">
+        <v>81.480000000000004</v>
+      </c>
+      <c r="Z33" s="17">
+        <v>81.480000000000004</v>
+      </c>
+      <c r="AA33" s="17">
+        <v>76.340000000000003</v>
+      </c>
+      <c r="AB33" s="17">
+        <v>81.900000000000006</v>
+      </c>
+      <c r="AC33" s="17">
+        <v>80.019999999999996</v>
+      </c>
+      <c r="AD33" s="17">
+        <v>80.019999999999996</v>
+      </c>
+      <c r="AE33" s="19">
+        <f>MIN(C33:AD33)</f>
+        <v>68</v>
       </c>
       <c r="AF33" s="20">
-        <f>AVERAGE(C33:AC33)</f>
-        <v>88.838421052631588</v>
+        <f>MAX(C33:AD33)</f>
+        <v>85.700000000000003</v>
       </c>
       <c r="AG33" s="20">
-        <f>AVERAGE(Q33:AC33)</f>
-        <v>96.782307692307683</v>
-      </c>
-      <c r="AH33" s="21">
-        <f>(AG33/AF33)-1</f>
-        <v>8.9419493790527937e-002</v>
+        <f>AVERAGE(C33:AD33)</f>
+        <v>79.097499999999997</v>
+      </c>
+      <c r="AH33" s="20">
+        <f>AVERAGE(Q33:AD33)</f>
+        <v>81.367857142857147</v>
       </c>
       <c r="AI33" s="21">
-        <f>(AG33/AD33)-1</f>
-        <v>0.75967832167832161</v>
+        <f>(AH33/AG33)-1</f>
+        <v>2.8703273085206815e-002</v>
       </c>
       <c r="AJ33" s="21">
-        <f>(AE33/AD33)-1</f>
-        <v>1.0181818181818181</v>
-      </c>
-      <c r="AK33" s="22" t="s">
-        <v>114</v>
+        <f>(AH33/AE33)-1</f>
+        <v>0.19658613445378159</v>
+      </c>
+      <c r="AK33" s="21">
+        <f>(AF33/AE33)-1</f>
+        <v>0.26029411764705879</v>
+      </c>
+      <c r="AL33" s="22" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="34" ht="18">
       <c r="A34" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C34" s="16"/>
       <c r="D34" s="16"/>
@@ -4687,301 +4753,314 @@
       <c r="H34" s="16"/>
       <c r="I34" s="16"/>
       <c r="J34" s="16"/>
-      <c r="K34" s="16"/>
+      <c r="K34" s="16">
+        <v>69.989999999999995</v>
+      </c>
       <c r="L34" s="16">
-        <v>68.859999999999999</v>
+        <v>55</v>
       </c>
       <c r="M34" s="16">
-        <v>47.359999999999999</v>
-      </c>
-      <c r="N34" s="16">
-        <v>47.359999999999999</v>
-      </c>
-      <c r="O34" s="16">
         <v>55</v>
       </c>
-      <c r="P34" s="16">
-        <v>53.869999999999997</v>
-      </c>
-      <c r="Q34" s="16">
-        <v>53.869999999999997</v>
+      <c r="N34" s="17">
+        <v>84.590000000000003</v>
+      </c>
+      <c r="O34" s="17">
+        <v>82.590000000000003</v>
+      </c>
+      <c r="P34" s="17">
+        <v>82.590000000000003</v>
+      </c>
+      <c r="Q34" s="17">
+        <v>80.769999999999996</v>
       </c>
       <c r="R34" s="17">
-        <v>83.909999999999997</v>
-      </c>
-      <c r="S34" s="17">
-        <v>90.579999999999998</v>
-      </c>
-      <c r="T34" s="18">
-        <v>100.68000000000001</v>
-      </c>
-      <c r="U34" s="18">
-        <v>92.530000000000001</v>
-      </c>
-      <c r="V34" s="17">
-        <v>89.090000000000003</v>
-      </c>
-      <c r="W34" s="17">
-        <v>86.700000000000003</v>
-      </c>
-      <c r="X34" s="17">
-        <v>86.700000000000003</v>
-      </c>
-      <c r="Y34" s="17">
-        <v>89.700000000000003</v>
-      </c>
-      <c r="Z34" s="18">
-        <v>91</v>
-      </c>
-      <c r="AA34" s="18">
-        <v>91</v>
-      </c>
-      <c r="AB34" s="16">
-        <v>61.579999999999998</v>
-      </c>
-      <c r="AC34" s="16">
-        <v>89.700000000000003</v>
-      </c>
-      <c r="AD34" s="19">
-        <f>MIN(C34:AC34)</f>
-        <v>47.359999999999999</v>
-      </c>
-      <c r="AE34" s="20">
-        <f>MAX(C34:AC34)</f>
-        <v>100.68000000000001</v>
+        <v>82.590000000000003</v>
+      </c>
+      <c r="S34" s="30">
+        <v>108</v>
+      </c>
+      <c r="T34" s="30">
+        <v>104.5</v>
+      </c>
+      <c r="U34" s="30">
+        <v>111</v>
+      </c>
+      <c r="V34" s="33">
+        <v>65.530000000000001</v>
+      </c>
+      <c r="W34" s="32">
+        <v>99.989999999999995</v>
+      </c>
+      <c r="X34" s="30">
+        <v>107</v>
+      </c>
+      <c r="Y34" s="32">
+        <v>99.900000000000006</v>
+      </c>
+      <c r="Z34" s="32">
+        <v>99.900000000000006</v>
+      </c>
+      <c r="AA34" s="30">
+        <v>104.98999999999999</v>
+      </c>
+      <c r="AB34" s="32">
+        <v>97</v>
+      </c>
+      <c r="AC34" s="32">
+        <v>97</v>
+      </c>
+      <c r="AD34" s="32">
+        <v>97</v>
+      </c>
+      <c r="AE34" s="19">
+        <f>MIN(C34:AD34)</f>
+        <v>55</v>
       </c>
       <c r="AF34" s="20">
-        <f>AVERAGE(C34:AC34)</f>
-        <v>76.638333333333335</v>
+        <f>MAX(C34:AD34)</f>
+        <v>111</v>
       </c>
       <c r="AG34" s="20">
-        <f>AVERAGE(Q34:AC34)</f>
-        <v>85.156923076923093</v>
-      </c>
-      <c r="AH34" s="21">
-        <f>(AG34/AF34)-1</f>
-        <v>0.11115311846016684</v>
+        <f>AVERAGE(C34:AD34)</f>
+        <v>89.246500000000012</v>
+      </c>
+      <c r="AH34" s="20">
+        <f>AVERAGE(Q34:AD34)</f>
+        <v>96.797857142857126</v>
       </c>
       <c r="AI34" s="21">
-        <f>(AG34/AD34)-1</f>
-        <v>0.79807692307692335</v>
+        <f>(AH34/AG34)-1</f>
+        <v>8.4612361749279996e-002</v>
       </c>
       <c r="AJ34" s="21">
-        <f>(AE34/AD34)-1</f>
-        <v>1.1258445945945947</v>
-      </c>
-      <c r="AK34" s="22" t="s">
-        <v>116</v>
+        <f>(AH34/AE34)-1</f>
+        <v>0.75996103896103873</v>
+      </c>
+      <c r="AK34" s="21">
+        <f>(AF34/AE34)-1</f>
+        <v>1.0181818181818181</v>
+      </c>
+      <c r="AL34" s="22" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="35" ht="18">
-      <c r="A35" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="B35" s="26" t="s">
-        <v>117</v>
-      </c>
-      <c r="C35" s="28"/>
-      <c r="D35" s="28"/>
-      <c r="E35" s="28"/>
-      <c r="F35" s="28"/>
-      <c r="G35" s="28"/>
-      <c r="H35" s="28"/>
-      <c r="I35" s="28"/>
-      <c r="J35" s="28"/>
-      <c r="K35" s="28"/>
-      <c r="L35" s="28">
-        <v>92.5</v>
-      </c>
-      <c r="M35" s="28">
-        <v>110.91</v>
-      </c>
-      <c r="N35" s="28">
-        <v>107.04000000000001</v>
-      </c>
-      <c r="O35" s="28">
-        <v>112</v>
+      <c r="A35" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C35" s="16"/>
+      <c r="D35" s="16"/>
+      <c r="E35" s="16"/>
+      <c r="F35" s="16"/>
+      <c r="G35" s="16"/>
+      <c r="H35" s="16"/>
+      <c r="I35" s="16"/>
+      <c r="J35" s="16"/>
+      <c r="K35" s="16"/>
+      <c r="L35" s="16">
+        <v>68.859999999999999</v>
+      </c>
+      <c r="M35" s="16">
+        <v>47.359999999999999</v>
+      </c>
+      <c r="N35" s="16">
+        <v>47.359999999999999</v>
+      </c>
+      <c r="O35" s="16">
+        <v>55</v>
       </c>
       <c r="P35" s="16">
-        <v>107.04000000000001</v>
+        <v>53.869999999999997</v>
       </c>
       <c r="Q35" s="16">
-        <v>111.43000000000001</v>
-      </c>
-      <c r="R35" s="16">
-        <v>111.43000000000001</v>
+        <v>53.869999999999997</v>
+      </c>
+      <c r="R35" s="17">
+        <v>83.909999999999997</v>
       </c>
       <c r="S35" s="17">
-        <v>132.33000000000001</v>
-      </c>
-      <c r="T35" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="U35" s="17">
-        <v>156</v>
+        <v>90.579999999999998</v>
+      </c>
+      <c r="T35" s="18">
+        <v>100.68000000000001</v>
+      </c>
+      <c r="U35" s="18">
+        <v>92.530000000000001</v>
       </c>
       <c r="V35" s="17">
-        <v>156</v>
+        <v>89.090000000000003</v>
       </c>
       <c r="W35" s="17">
-        <v>156</v>
+        <v>86.700000000000003</v>
       </c>
       <c r="X35" s="17">
-        <v>156</v>
+        <v>86.700000000000003</v>
       </c>
       <c r="Y35" s="17">
-        <v>151.22</v>
-      </c>
-      <c r="Z35" s="17">
-        <v>151.22</v>
-      </c>
-      <c r="AA35" s="17">
-        <v>149.30000000000001</v>
-      </c>
-      <c r="AB35" s="17">
-        <v>159.99000000000001</v>
-      </c>
-      <c r="AC35" s="17">
-        <v>154.27000000000001</v>
-      </c>
-      <c r="AD35" s="19">
-        <f>MIN(C35:AC35)</f>
-        <v>92.5</v>
-      </c>
-      <c r="AE35" s="20">
-        <f>MAX(C35:AC35)</f>
-        <v>159.99000000000001</v>
+        <v>89.700000000000003</v>
+      </c>
+      <c r="Z35" s="18">
+        <v>91</v>
+      </c>
+      <c r="AA35" s="18">
+        <v>91</v>
+      </c>
+      <c r="AB35" s="16">
+        <v>61.579999999999998</v>
+      </c>
+      <c r="AC35" s="16">
+        <v>89.700000000000003</v>
+      </c>
+      <c r="AD35" s="16">
+        <v>89.700000000000003</v>
+      </c>
+      <c r="AE35" s="19">
+        <f>MIN(C35:AD35)</f>
+        <v>47.359999999999999</v>
       </c>
       <c r="AF35" s="20">
-        <f>AVERAGE(C35:AC35)</f>
-        <v>133.80470588235295</v>
+        <f>MAX(C35:AD35)</f>
+        <v>100.68000000000001</v>
       </c>
       <c r="AG35" s="20">
-        <f>AVERAGE(Q35:AC35)</f>
-        <v>145.4325</v>
-      </c>
-      <c r="AH35" s="21">
-        <f>(AG35/AF35)-1</f>
-        <v>8.6901234459352494e-002</v>
+        <f>AVERAGE(C35:AD35)</f>
+        <v>77.32578947368421</v>
+      </c>
+      <c r="AH35" s="20">
+        <f>AVERAGE(Q35:AD35)</f>
+        <v>85.481428571428594</v>
       </c>
       <c r="AI35" s="21">
-        <f>(AG35/AD35)-1</f>
-        <v>0.57224324324324338</v>
+        <f>(AH35/AG35)-1</f>
+        <v>0.10547113910191563</v>
       </c>
       <c r="AJ35" s="21">
-        <f>(AE35/AD35)-1</f>
-        <v>0.72962162162162181</v>
-      </c>
-      <c r="AK35" s="22" t="s">
-        <v>118</v>
+        <f>(AH35/AE35)-1</f>
+        <v>0.80492881274131323</v>
+      </c>
+      <c r="AK35" s="21">
+        <f>(AF35/AE35)-1</f>
+        <v>1.1258445945945947</v>
+      </c>
+      <c r="AL35" s="22" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="36" ht="18">
-      <c r="A36" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C36" s="16"/>
-      <c r="D36" s="16"/>
-      <c r="E36" s="16"/>
-      <c r="F36" s="16"/>
-      <c r="G36" s="16"/>
-      <c r="H36" s="16"/>
-      <c r="I36" s="16"/>
-      <c r="J36" s="16"/>
-      <c r="K36" s="16"/>
-      <c r="L36" s="16"/>
-      <c r="M36" s="16">
-        <v>148.88</v>
-      </c>
-      <c r="N36" s="16">
-        <v>165.36000000000001</v>
-      </c>
-      <c r="O36" s="18">
-        <v>241.99000000000001</v>
-      </c>
-      <c r="P36" s="17">
-        <v>224.84999999999999</v>
-      </c>
-      <c r="Q36" s="17">
-        <v>224.84999999999999</v>
-      </c>
-      <c r="R36" s="18">
-        <v>257.87</v>
+      <c r="A36" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>120</v>
+      </c>
+      <c r="C36" s="28"/>
+      <c r="D36" s="28"/>
+      <c r="E36" s="28"/>
+      <c r="F36" s="28"/>
+      <c r="G36" s="28"/>
+      <c r="H36" s="28"/>
+      <c r="I36" s="28"/>
+      <c r="J36" s="28"/>
+      <c r="K36" s="28"/>
+      <c r="L36" s="28">
+        <v>92.5</v>
+      </c>
+      <c r="M36" s="28">
+        <v>110.91</v>
+      </c>
+      <c r="N36" s="28">
+        <v>107.04000000000001</v>
+      </c>
+      <c r="O36" s="28">
+        <v>112</v>
+      </c>
+      <c r="P36" s="16">
+        <v>107.04000000000001</v>
+      </c>
+      <c r="Q36" s="16">
+        <v>111.43000000000001</v>
+      </c>
+      <c r="R36" s="16">
+        <v>111.43000000000001</v>
       </c>
       <c r="S36" s="17">
-        <v>239.99000000000001</v>
-      </c>
-      <c r="T36" s="16">
-        <v>210.08000000000001</v>
+        <v>132.33000000000001</v>
+      </c>
+      <c r="T36" s="16" t="s">
+        <v>49</v>
       </c>
       <c r="U36" s="17">
-        <v>238.24000000000001</v>
+        <v>156</v>
       </c>
       <c r="V36" s="17">
-        <v>238.24000000000001</v>
+        <v>156</v>
       </c>
       <c r="W36" s="17">
-        <v>235.97999999999999</v>
+        <v>156</v>
       </c>
       <c r="X36" s="17">
-        <v>238.24000000000001</v>
+        <v>156</v>
       </c>
       <c r="Y36" s="17">
-        <v>221.25</v>
-      </c>
-      <c r="Z36" s="16">
-        <v>209.99000000000001</v>
-      </c>
-      <c r="AA36" s="16">
-        <v>199.99000000000001</v>
-      </c>
-      <c r="AB36" s="16">
-        <v>190.90000000000001</v>
-      </c>
-      <c r="AC36" s="16">
-        <v>199.5</v>
-      </c>
-      <c r="AD36" s="19">
-        <f>MIN(C36:AC36)</f>
-        <v>148.88</v>
-      </c>
-      <c r="AE36" s="20">
-        <f>MAX(C36:AC36)</f>
-        <v>257.87</v>
+        <v>151.22</v>
+      </c>
+      <c r="Z36" s="17">
+        <v>151.22</v>
+      </c>
+      <c r="AA36" s="17">
+        <v>149.30000000000001</v>
+      </c>
+      <c r="AB36" s="17">
+        <v>159.99000000000001</v>
+      </c>
+      <c r="AC36" s="17">
+        <v>154.27000000000001</v>
+      </c>
+      <c r="AD36" s="16">
+        <v>121.06</v>
+      </c>
+      <c r="AE36" s="19">
+        <f>MIN(C36:AD36)</f>
+        <v>92.5</v>
       </c>
       <c r="AF36" s="20">
-        <f>AVERAGE(C36:AC36)</f>
-        <v>216.83529411764707</v>
+        <f>MAX(C36:AD36)</f>
+        <v>159.99000000000001</v>
       </c>
       <c r="AG36" s="20">
-        <f>AVERAGE(Q36:AC36)</f>
-        <v>223.47076923076926</v>
-      </c>
-      <c r="AH36" s="21">
-        <f>(AG36/AF36)-1</f>
-        <v>3.060145323723007e-002</v>
+        <f>AVERAGE(C36:AD36)</f>
+        <v>133.09666666666669</v>
+      </c>
+      <c r="AH36" s="20">
+        <f>AVERAGE(Q36:AD36)</f>
+        <v>143.55769230769232</v>
       </c>
       <c r="AI36" s="21">
-        <f>(AG36/AD36)-1</f>
-        <v>0.50101268962096501</v>
+        <f>(AH36/AG36)-1</f>
+        <v>7.8597202341849082e-002</v>
       </c>
       <c r="AJ36" s="21">
-        <f>(AE36/AD36)-1</f>
-        <v>0.73206609349811935</v>
-      </c>
-      <c r="AK36" s="22" t="s">
-        <v>120</v>
+        <f>(AH36/AE36)-1</f>
+        <v>0.55197505197505214</v>
+      </c>
+      <c r="AK36" s="21">
+        <f>(AF36/AE36)-1</f>
+        <v>0.72962162162162181</v>
+      </c>
+      <c r="AL36" s="22" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="37" ht="18">
       <c r="A37" s="2" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C37" s="16"/>
       <c r="D37" s="16"/>
@@ -4993,258 +5072,287 @@
       <c r="J37" s="16"/>
       <c r="K37" s="16"/>
       <c r="L37" s="16"/>
-      <c r="M37" s="16"/>
-      <c r="N37" s="16"/>
-      <c r="O37" s="16">
-        <v>155</v>
-      </c>
-      <c r="P37" s="16">
-        <v>153.44</v>
-      </c>
-      <c r="Q37" s="16">
-        <v>144.94999999999999</v>
-      </c>
-      <c r="R37" s="16">
-        <v>152.5</v>
-      </c>
-      <c r="S37" s="16">
-        <v>148.87</v>
+      <c r="M37" s="16">
+        <v>148.88</v>
+      </c>
+      <c r="N37" s="16">
+        <v>165.36000000000001</v>
+      </c>
+      <c r="O37" s="18">
+        <v>241.99000000000001</v>
+      </c>
+      <c r="P37" s="17">
+        <v>224.84999999999999</v>
+      </c>
+      <c r="Q37" s="17">
+        <v>224.84999999999999</v>
+      </c>
+      <c r="R37" s="18">
+        <v>257.87</v>
+      </c>
+      <c r="S37" s="17">
+        <v>239.99000000000001</v>
       </c>
       <c r="T37" s="16">
-        <v>147.44999999999999</v>
+        <v>210.08000000000001</v>
       </c>
       <c r="U37" s="17">
-        <v>162.63999999999999</v>
+        <v>238.24000000000001</v>
       </c>
       <c r="V37" s="17">
-        <v>164.93000000000001</v>
+        <v>238.24000000000001</v>
       </c>
       <c r="W37" s="17">
-        <v>161.65000000000001</v>
+        <v>235.97999999999999</v>
       </c>
       <c r="X37" s="17">
-        <v>164.38999999999999</v>
+        <v>238.24000000000001</v>
       </c>
       <c r="Y37" s="17">
-        <v>168.28999999999999</v>
-      </c>
-      <c r="Z37" s="17">
-        <v>149.88999999999999</v>
-      </c>
-      <c r="AA37" s="17">
-        <v>148.5</v>
-      </c>
-      <c r="AB37" s="17">
-        <v>148.69</v>
-      </c>
-      <c r="AC37" s="17">
-        <v>149</v>
-      </c>
-      <c r="AD37" s="19">
-        <f>MIN(C37:AC37)</f>
-        <v>144.94999999999999</v>
-      </c>
-      <c r="AE37" s="20">
-        <f>MAX(C37:AC37)</f>
-        <v>168.28999999999999</v>
+        <v>221.25</v>
+      </c>
+      <c r="Z37" s="16">
+        <v>209.99000000000001</v>
+      </c>
+      <c r="AA37" s="16">
+        <v>199.99000000000001</v>
+      </c>
+      <c r="AB37" s="16">
+        <v>190.90000000000001</v>
+      </c>
+      <c r="AC37" s="16">
+        <v>199.5</v>
+      </c>
+      <c r="AD37" s="16">
+        <v>199.5</v>
+      </c>
+      <c r="AE37" s="19">
+        <f>MIN(C37:AD37)</f>
+        <v>148.88</v>
       </c>
       <c r="AF37" s="20">
-        <f>AVERAGE(C37:AC37)</f>
-        <v>154.67933333333335</v>
+        <f>MAX(C37:AD37)</f>
+        <v>257.87</v>
       </c>
       <c r="AG37" s="20">
-        <f>AVERAGE(Q37:AC37)</f>
-        <v>154.75</v>
-      </c>
-      <c r="AH37" s="21">
-        <f>(AG37/AF37)-1</f>
-        <v>4.568591365361474e-004</v>
+        <f>AVERAGE(C37:AD37)</f>
+        <v>215.87222222222223</v>
+      </c>
+      <c r="AH37" s="20">
+        <f>AVERAGE(Q37:AD37)</f>
+        <v>221.75857142857146</v>
       </c>
       <c r="AI37" s="21">
-        <f>(AG37/AD37)-1</f>
-        <v>6.7609520524318789e-002</v>
+        <f>(AH37/AG37)-1</f>
+        <v>2.7267747307894608e-002</v>
       </c>
       <c r="AJ37" s="21">
-        <f>(AE37/AD37)-1</f>
-        <v>0.16102104173853049</v>
-      </c>
-      <c r="AK37" s="22" t="s">
-        <v>122</v>
+        <f>(AH37/AE37)-1</f>
+        <v>0.48951216703769118</v>
+      </c>
+      <c r="AK37" s="21">
+        <f>(AF37/AE37)-1</f>
+        <v>0.73206609349811935</v>
+      </c>
+      <c r="AL37" s="22" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="38" ht="18">
-      <c r="A38" s="25" t="s">
-        <v>104</v>
-      </c>
-      <c r="B38" s="26" t="s">
-        <v>123</v>
-      </c>
-      <c r="C38" s="28"/>
-      <c r="D38" s="28"/>
-      <c r="E38" s="28"/>
-      <c r="F38" s="28"/>
-      <c r="G38" s="28"/>
-      <c r="H38" s="28"/>
-      <c r="I38" s="28"/>
-      <c r="J38" s="28"/>
-      <c r="K38" s="28"/>
-      <c r="L38" s="28"/>
-      <c r="M38" s="28"/>
-      <c r="N38" s="28"/>
-      <c r="O38" s="18">
-        <v>199.93000000000001</v>
+      <c r="A38" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C38" s="16"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="16"/>
+      <c r="G38" s="16"/>
+      <c r="H38" s="16"/>
+      <c r="I38" s="16"/>
+      <c r="J38" s="16"/>
+      <c r="K38" s="16"/>
+      <c r="L38" s="16"/>
+      <c r="M38" s="16"/>
+      <c r="N38" s="16"/>
+      <c r="O38" s="16">
+        <v>155</v>
       </c>
       <c r="P38" s="16">
-        <v>161.90000000000001</v>
+        <v>153.44</v>
       </c>
       <c r="Q38" s="16">
-        <v>175.99000000000001</v>
-      </c>
-      <c r="R38" s="24">
-        <v>144</v>
-      </c>
-      <c r="S38" s="18">
-        <v>199.40000000000001</v>
-      </c>
-      <c r="T38" s="18">
-        <v>189.99000000000001</v>
-      </c>
-      <c r="U38" s="18">
-        <v>199.94999999999999</v>
+        <v>144.94999999999999</v>
+      </c>
+      <c r="R38" s="16">
+        <v>152.5</v>
+      </c>
+      <c r="S38" s="16">
+        <v>148.87</v>
+      </c>
+      <c r="T38" s="16">
+        <v>147.44999999999999</v>
+      </c>
+      <c r="U38" s="17">
+        <v>162.63999999999999</v>
       </c>
       <c r="V38" s="17">
-        <v>169</v>
-      </c>
-      <c r="W38" s="18">
-        <v>181.33000000000001</v>
+        <v>164.93000000000001</v>
+      </c>
+      <c r="W38" s="17">
+        <v>161.65000000000001</v>
       </c>
       <c r="X38" s="17">
-        <v>169</v>
+        <v>164.38999999999999</v>
       </c>
       <c r="Y38" s="17">
-        <v>159</v>
-      </c>
-      <c r="Z38" s="18">
-        <v>195.22999999999999</v>
-      </c>
-      <c r="AA38" s="18">
-        <v>189.99000000000001</v>
-      </c>
-      <c r="AB38" s="18">
-        <v>191.28999999999999</v>
-      </c>
-      <c r="AC38" s="18">
-        <v>179.09</v>
-      </c>
-      <c r="AD38" s="19">
-        <f>MIN(C38:AC38)</f>
-        <v>144</v>
-      </c>
-      <c r="AE38" s="20">
-        <f>MAX(C38:AC38)</f>
-        <v>199.94999999999999</v>
+        <v>168.28999999999999</v>
+      </c>
+      <c r="Z38" s="17">
+        <v>149.88999999999999</v>
+      </c>
+      <c r="AA38" s="17">
+        <v>148.5</v>
+      </c>
+      <c r="AB38" s="17">
+        <v>148.69</v>
+      </c>
+      <c r="AC38" s="17">
+        <v>149</v>
+      </c>
+      <c r="AD38" s="17">
+        <v>148.28999999999999</v>
+      </c>
+      <c r="AE38" s="19">
+        <f>MIN(C38:AD38)</f>
+        <v>144.94999999999999</v>
       </c>
       <c r="AF38" s="20">
-        <f>AVERAGE(C38:AC38)</f>
-        <v>180.33933333333334</v>
+        <f>MAX(C38:AD38)</f>
+        <v>168.28999999999999</v>
       </c>
       <c r="AG38" s="20">
-        <f>AVERAGE(Q38:AC38)</f>
-        <v>180.25076923076924</v>
-      </c>
-      <c r="AH38" s="21">
-        <f>(AG38/AF38)-1</f>
-        <v>-4.9109698326543771e-004</v>
+        <f>AVERAGE(C38:AD38)</f>
+        <v>154.28</v>
+      </c>
+      <c r="AH38" s="20">
+        <f>AVERAGE(Q38:AD38)</f>
+        <v>154.28857142857143</v>
       </c>
       <c r="AI38" s="21">
-        <f>(AG38/AD38)-1</f>
-        <v>0.25174145299145301</v>
+        <f>(AH38/AG38)-1</f>
+        <v>5.5557613244827664e-005</v>
       </c>
       <c r="AJ38" s="21">
-        <f>(AE38/AD38)-1</f>
-        <v>0.38854166666666656</v>
-      </c>
-      <c r="AK38" s="22" t="s">
-        <v>124</v>
+        <f>(AH38/AE38)-1</f>
+        <v>6.4426156802838586e-002</v>
+      </c>
+      <c r="AK38" s="21">
+        <f>(AF38/AE38)-1</f>
+        <v>0.16102104173853049</v>
+      </c>
+      <c r="AL38" s="22" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="39" ht="18">
-      <c r="A39" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="B39" s="3" t="s">
+      <c r="A39" s="25" t="s">
+        <v>107</v>
+      </c>
+      <c r="B39" s="26" t="s">
         <v>126</v>
       </c>
-      <c r="C39" s="16"/>
-      <c r="D39" s="16"/>
-      <c r="E39" s="16"/>
-      <c r="F39" s="16"/>
-      <c r="G39" s="24">
-        <v>30731.380000000001</v>
-      </c>
-      <c r="H39" s="17">
-        <v>32127.290000000001</v>
-      </c>
-      <c r="I39" s="17">
-        <v>32790.889999999999</v>
-      </c>
-      <c r="J39" s="17">
-        <v>31941.080000000002</v>
-      </c>
-      <c r="K39" s="17">
-        <v>31941.080000000002</v>
-      </c>
-      <c r="L39" s="17">
-        <v>31941.080000000002</v>
-      </c>
-      <c r="M39" s="16" t="s">
-        <v>80</v>
-      </c>
-      <c r="N39" s="17"/>
-      <c r="O39" s="16"/>
-      <c r="P39" s="16"/>
-      <c r="Q39" s="16"/>
-      <c r="R39" s="16"/>
-      <c r="S39" s="16"/>
-      <c r="T39" s="16"/>
-      <c r="U39" s="16"/>
-      <c r="V39" s="16"/>
-      <c r="W39" s="16"/>
-      <c r="X39" s="16"/>
-      <c r="Y39" s="16"/>
-      <c r="Z39" s="16"/>
-      <c r="AA39" s="16"/>
-      <c r="AB39" s="16"/>
-      <c r="AC39" s="16"/>
-      <c r="AD39" s="19">
-        <f>MIN(C39:AC39)</f>
-        <v>30731.380000000001</v>
-      </c>
-      <c r="AE39" s="20">
-        <f>MAX(C39:AC39)</f>
-        <v>32790.889999999999</v>
+      <c r="C39" s="28"/>
+      <c r="D39" s="28"/>
+      <c r="E39" s="28"/>
+      <c r="F39" s="28"/>
+      <c r="G39" s="28"/>
+      <c r="H39" s="28"/>
+      <c r="I39" s="28"/>
+      <c r="J39" s="28"/>
+      <c r="K39" s="28"/>
+      <c r="L39" s="28"/>
+      <c r="M39" s="28"/>
+      <c r="N39" s="28"/>
+      <c r="O39" s="18">
+        <v>199.93000000000001</v>
+      </c>
+      <c r="P39" s="16">
+        <v>161.90000000000001</v>
+      </c>
+      <c r="Q39" s="16">
+        <v>175.99000000000001</v>
+      </c>
+      <c r="R39" s="24">
+        <v>144</v>
+      </c>
+      <c r="S39" s="18">
+        <v>199.40000000000001</v>
+      </c>
+      <c r="T39" s="18">
+        <v>189.99000000000001</v>
+      </c>
+      <c r="U39" s="18">
+        <v>199.94999999999999</v>
+      </c>
+      <c r="V39" s="17">
+        <v>169</v>
+      </c>
+      <c r="W39" s="18">
+        <v>181.33000000000001</v>
+      </c>
+      <c r="X39" s="17">
+        <v>169</v>
+      </c>
+      <c r="Y39" s="17">
+        <v>159</v>
+      </c>
+      <c r="Z39" s="18">
+        <v>195.22999999999999</v>
+      </c>
+      <c r="AA39" s="18">
+        <v>189.99000000000001</v>
+      </c>
+      <c r="AB39" s="18">
+        <v>191.28999999999999</v>
+      </c>
+      <c r="AC39" s="18">
+        <v>179.09</v>
+      </c>
+      <c r="AD39" s="18">
+        <v>189.99000000000001</v>
+      </c>
+      <c r="AE39" s="19">
+        <f>MIN(C39:AD39)</f>
+        <v>144</v>
       </c>
       <c r="AF39" s="20">
-        <f>AVERAGE(C39:AC39)</f>
-        <v>31912.133333333331</v>
-      </c>
-      <c r="AG39" s="20" t="e">
-        <f>AVERAGE(Q39:AC39)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AH39" s="21" t="e">
-        <f>(AG39/AF39)-1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AI39" s="21" t="e">
-        <f>(AG39/AD39)-1</f>
-        <v>#NUM!</v>
+        <f>MAX(C39:AD39)</f>
+        <v>199.94999999999999</v>
+      </c>
+      <c r="AG39" s="20">
+        <f>AVERAGE(C39:AD39)</f>
+        <v>180.9425</v>
+      </c>
+      <c r="AH39" s="20">
+        <f>AVERAGE(Q39:AD39)</f>
+        <v>180.94642857142858</v>
+      </c>
+      <c r="AI39" s="21">
+        <f>(AH39/AG39)-1</f>
+        <v>2.1711711889693674e-005</v>
       </c>
       <c r="AJ39" s="21">
-        <f>(AE39/AD39)-1</f>
-        <v>6.7016515366377982e-002</v>
-      </c>
-      <c r="AK39" s="22" t="s">
+        <f>(AH39/AE39)-1</f>
+        <v>0.25657242063492069</v>
+      </c>
+      <c r="AK39" s="21">
+        <f>(AF39/AE39)-1</f>
+        <v>0.38854166666666656</v>
+      </c>
+      <c r="AL39" s="22" t="s">
         <v>127</v>
       </c>
     </row>
@@ -5259,99 +5367,82 @@
       <c r="D40" s="16"/>
       <c r="E40" s="16"/>
       <c r="F40" s="16"/>
-      <c r="G40" s="24"/>
-      <c r="H40" s="17"/>
-      <c r="I40" s="17"/>
-      <c r="J40" s="17"/>
-      <c r="K40" s="17"/>
-      <c r="L40" s="17"/>
-      <c r="M40" s="17"/>
-      <c r="N40" s="17">
-        <v>642.82000000000005</v>
-      </c>
-      <c r="O40" s="17">
-        <v>642.82000000000005</v>
-      </c>
-      <c r="P40" s="18">
-        <v>721.67999999999995</v>
-      </c>
-      <c r="Q40" s="18">
-        <v>721.67999999999995</v>
-      </c>
-      <c r="R40" s="18">
-        <v>721.67999999999995</v>
-      </c>
-      <c r="S40" s="18">
-        <v>721.67999999999995</v>
-      </c>
-      <c r="T40" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="U40" s="18">
-        <v>1164</v>
-      </c>
-      <c r="V40" s="18">
-        <v>1150.8</v>
-      </c>
-      <c r="W40" s="18">
-        <v>1150.8</v>
-      </c>
-      <c r="X40" s="18">
-        <v>1150.8</v>
-      </c>
-      <c r="Y40" s="18">
-        <v>1150.8</v>
-      </c>
-      <c r="Z40" s="30">
-        <v>1360.8</v>
-      </c>
-      <c r="AA40" s="30">
-        <v>1360.8</v>
-      </c>
-      <c r="AB40" s="35" t="s">
-        <v>48</v>
-      </c>
-      <c r="AC40" s="30">
-        <v>1360.8</v>
-      </c>
-      <c r="AD40" s="19">
-        <f>MIN(C40:AC40)</f>
-        <v>642.82000000000005</v>
-      </c>
-      <c r="AE40" s="20">
-        <f>MAX(C40:AC40)</f>
-        <v>1360.8</v>
+      <c r="G40" s="24">
+        <v>30731.380000000001</v>
+      </c>
+      <c r="H40" s="17">
+        <v>32127.290000000001</v>
+      </c>
+      <c r="I40" s="17">
+        <v>32790.889999999999</v>
+      </c>
+      <c r="J40" s="17">
+        <v>31941.080000000002</v>
+      </c>
+      <c r="K40" s="17">
+        <v>31941.080000000002</v>
+      </c>
+      <c r="L40" s="17">
+        <v>31941.080000000002</v>
+      </c>
+      <c r="M40" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="N40" s="17"/>
+      <c r="O40" s="16"/>
+      <c r="P40" s="16"/>
+      <c r="Q40" s="16"/>
+      <c r="R40" s="16"/>
+      <c r="S40" s="16"/>
+      <c r="T40" s="16"/>
+      <c r="U40" s="16"/>
+      <c r="V40" s="16"/>
+      <c r="W40" s="16"/>
+      <c r="X40" s="16"/>
+      <c r="Y40" s="16"/>
+      <c r="Z40" s="16"/>
+      <c r="AA40" s="16"/>
+      <c r="AB40" s="16"/>
+      <c r="AC40" s="16"/>
+      <c r="AD40" s="16"/>
+      <c r="AE40" s="19">
+        <f>MIN(C40:AD40)</f>
+        <v>30731.380000000001</v>
       </c>
       <c r="AF40" s="20">
-        <f>AVERAGE(C40:AC40)</f>
-        <v>1001.5685714285712</v>
+        <f>MAX(C40:AD40)</f>
+        <v>32790.889999999999</v>
       </c>
       <c r="AG40" s="20">
-        <f>AVERAGE(Q40:AC40)</f>
-        <v>1092.24</v>
-      </c>
-      <c r="AH40" s="21">
-        <f>(AG40/AF40)-1</f>
-        <v>9.0529426699263338e-002</v>
-      </c>
-      <c r="AI40" s="21">
-        <f>(AG40/AD40)-1</f>
-        <v>0.69913817242774012</v>
-      </c>
-      <c r="AJ40" s="21">
-        <f>(AE40/AD40)-1</f>
-        <v>1.1169223110668614</v>
-      </c>
-      <c r="AK40" s="22" t="s">
+        <f>AVERAGE(C40:AD40)</f>
+        <v>31912.133333333331</v>
+      </c>
+      <c r="AH40" s="20" t="e">
+        <f>AVERAGE(Q40:AD40)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AI40" s="21" t="e">
+        <f>(AH40/AG40)-1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AJ40" s="21" t="e">
+        <f>(AH40/AE40)-1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AK40" s="21">
+        <f>(AF40/AE40)-1</f>
+        <v>6.7016515366377982e-002</v>
+      </c>
+      <c r="AL40" s="22" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="41" ht="18">
       <c r="A41" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C41" s="16"/>
       <c r="D41" s="16"/>
@@ -5365,91 +5456,94 @@
       <c r="L41" s="17"/>
       <c r="M41" s="17"/>
       <c r="N41" s="17">
-        <v>1151.71</v>
+        <v>642.82000000000005</v>
       </c>
       <c r="O41" s="17">
-        <v>1151.71</v>
+        <v>642.82000000000005</v>
       </c>
       <c r="P41" s="18">
-        <v>1279.6800000000001</v>
+        <v>721.67999999999995</v>
       </c>
       <c r="Q41" s="18">
-        <v>1279.6800000000001</v>
+        <v>721.67999999999995</v>
       </c>
       <c r="R41" s="18">
-        <v>1279.6800000000001</v>
+        <v>721.67999999999995</v>
       </c>
       <c r="S41" s="18">
-        <v>1279.6800000000001</v>
-      </c>
-      <c r="T41" s="30">
-        <v>2064</v>
-      </c>
-      <c r="U41" s="30">
-        <v>2064</v>
-      </c>
-      <c r="V41" s="30">
-        <v>2016</v>
-      </c>
-      <c r="W41" s="30">
-        <v>2016</v>
-      </c>
-      <c r="X41" s="30">
-        <v>2016</v>
-      </c>
-      <c r="Y41" s="30">
-        <v>2016</v>
+        <v>721.67999999999995</v>
+      </c>
+      <c r="T41" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="U41" s="18">
+        <v>1164</v>
+      </c>
+      <c r="V41" s="18">
+        <v>1150.8</v>
+      </c>
+      <c r="W41" s="18">
+        <v>1150.8</v>
+      </c>
+      <c r="X41" s="18">
+        <v>1150.8</v>
+      </c>
+      <c r="Y41" s="18">
+        <v>1150.8</v>
       </c>
       <c r="Z41" s="30">
-        <v>2171.4000000000001</v>
+        <v>1360.8</v>
       </c>
       <c r="AA41" s="30">
-        <v>2171.4000000000001</v>
+        <v>1360.8</v>
       </c>
       <c r="AB41" s="35" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AC41" s="30">
-        <v>2171.4000000000001</v>
-      </c>
-      <c r="AD41" s="19">
-        <f>MIN(C41:AC41)</f>
-        <v>1151.71</v>
-      </c>
-      <c r="AE41" s="20">
-        <f>MAX(C41:AC41)</f>
-        <v>2171.4000000000001</v>
+        <v>1360.8</v>
+      </c>
+      <c r="AD41" s="30">
+        <v>1360.8</v>
+      </c>
+      <c r="AE41" s="19">
+        <f>MIN(C41:AD41)</f>
+        <v>642.82000000000005</v>
       </c>
       <c r="AF41" s="20">
-        <f>AVERAGE(C41:AC41)</f>
-        <v>1741.8893333333335</v>
+        <f>MAX(C41:AD41)</f>
+        <v>1360.8</v>
       </c>
       <c r="AG41" s="20">
-        <f>AVERAGE(Q41:AC41)</f>
-        <v>1878.7700000000004</v>
-      </c>
-      <c r="AH41" s="21">
-        <f>(AG41/AF41)-1</f>
-        <v>7.8581723905919887e-002</v>
+        <f>AVERAGE(C41:AD41)</f>
+        <v>1025.517333333333</v>
+      </c>
+      <c r="AH41" s="20">
+        <f>AVERAGE(Q41:AD41)</f>
+        <v>1114.6199999999999</v>
       </c>
       <c r="AI41" s="21">
-        <f>(AG41/AD41)-1</f>
-        <v>0.6312873900547884</v>
+        <f>(AH41/AG41)-1</f>
+        <v>8.6885578400755392e-002</v>
       </c>
       <c r="AJ41" s="21">
-        <f>(AE41/AD41)-1</f>
-        <v>0.88537044915820817</v>
-      </c>
-      <c r="AK41" s="22" t="s">
-        <v>130</v>
+        <f>(AH41/AE41)-1</f>
+        <v>0.73395351731433345</v>
+      </c>
+      <c r="AK41" s="21">
+        <f>(AF41/AE41)-1</f>
+        <v>1.1169223110668614</v>
+      </c>
+      <c r="AL41" s="22" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="42" ht="18">
       <c r="A42" s="2" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C42" s="16"/>
       <c r="D42" s="16"/>
@@ -5463,91 +5557,94 @@
       <c r="L42" s="17"/>
       <c r="M42" s="17"/>
       <c r="N42" s="17">
-        <v>2159.8299999999999</v>
+        <v>1151.71</v>
       </c>
       <c r="O42" s="17">
-        <v>2159.8299999999999</v>
+        <v>1151.71</v>
       </c>
       <c r="P42" s="18">
-        <v>2403.1199999999999</v>
+        <v>1279.6800000000001</v>
       </c>
       <c r="Q42" s="18">
-        <v>2403.1199999999999</v>
+        <v>1279.6800000000001</v>
       </c>
       <c r="R42" s="18">
-        <v>2403.1199999999999</v>
+        <v>1279.6800000000001</v>
       </c>
       <c r="S42" s="18">
-        <v>2403.1199999999999</v>
+        <v>1279.6800000000001</v>
       </c>
       <c r="T42" s="30">
-        <v>3876</v>
-      </c>
-      <c r="U42" s="35" t="s">
-        <v>48</v>
-      </c>
-      <c r="V42" s="35" t="s">
-        <v>48</v>
-      </c>
-      <c r="W42" s="35" t="s">
-        <v>48</v>
-      </c>
-      <c r="X42" s="35" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y42" s="35" t="s">
-        <v>48</v>
-      </c>
-      <c r="Z42" s="35" t="s">
-        <v>48</v>
-      </c>
-      <c r="AA42" s="35" t="s">
-        <v>48</v>
+        <v>2064</v>
+      </c>
+      <c r="U42" s="30">
+        <v>2064</v>
+      </c>
+      <c r="V42" s="30">
+        <v>2016</v>
+      </c>
+      <c r="W42" s="30">
+        <v>2016</v>
+      </c>
+      <c r="X42" s="30">
+        <v>2016</v>
+      </c>
+      <c r="Y42" s="30">
+        <v>2016</v>
+      </c>
+      <c r="Z42" s="30">
+        <v>2171.4000000000001</v>
+      </c>
+      <c r="AA42" s="30">
+        <v>2171.4000000000001</v>
       </c>
       <c r="AB42" s="35" t="s">
-        <v>48</v>
-      </c>
-      <c r="AC42" s="35" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD42" s="19">
-        <f>MIN(C42:AC42)</f>
-        <v>2159.8299999999999</v>
-      </c>
-      <c r="AE42" s="20">
-        <f>MAX(C42:AC42)</f>
-        <v>3876</v>
+        <v>49</v>
+      </c>
+      <c r="AC42" s="30">
+        <v>2171.4000000000001</v>
+      </c>
+      <c r="AD42" s="30">
+        <v>2171.4000000000001</v>
+      </c>
+      <c r="AE42" s="19">
+        <f>MIN(C42:AD42)</f>
+        <v>1151.71</v>
       </c>
       <c r="AF42" s="20">
-        <f>AVERAGE(C42:AC42)</f>
-        <v>2544.02</v>
+        <f>MAX(C42:AD42)</f>
+        <v>2171.4000000000001</v>
       </c>
       <c r="AG42" s="20">
-        <f>AVERAGE(Q42:AC42)</f>
-        <v>2771.3400000000001</v>
-      </c>
-      <c r="AH42" s="21">
-        <f>(AG42/AF42)-1</f>
-        <v>8.9354643438337877e-002</v>
+        <f>AVERAGE(C42:AD42)</f>
+        <v>1768.7337500000003</v>
+      </c>
+      <c r="AH42" s="20">
+        <f>AVERAGE(Q42:AD42)</f>
+        <v>1901.2800000000004</v>
       </c>
       <c r="AI42" s="21">
-        <f>(AG42/AD42)-1</f>
-        <v>0.28312876476389359</v>
+        <f>(AH42/AG42)-1</f>
+        <v>7.4938497668176396e-002</v>
       </c>
       <c r="AJ42" s="21">
-        <f>(AE42/AD42)-1</f>
-        <v>0.79458568498446636</v>
-      </c>
-      <c r="AK42" s="22" t="s">
-        <v>130</v>
+        <f>(AH42/AE42)-1</f>
+        <v>0.65083224075505153</v>
+      </c>
+      <c r="AK42" s="21">
+        <f>(AF42/AE42)-1</f>
+        <v>0.88537044915820817</v>
+      </c>
+      <c r="AL42" s="22" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="43" ht="18">
       <c r="A43" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C43" s="16"/>
       <c r="D43" s="16"/>
@@ -5561,267 +5658,276 @@
       <c r="L43" s="17"/>
       <c r="M43" s="17"/>
       <c r="N43" s="17">
-        <v>1310.1800000000001</v>
+        <v>2159.8299999999999</v>
       </c>
       <c r="O43" s="17">
-        <v>1320.5999999999999</v>
+        <v>2159.8299999999999</v>
       </c>
       <c r="P43" s="18">
-        <v>1320.5999999999999</v>
+        <v>2403.1199999999999</v>
       </c>
       <c r="Q43" s="18">
-        <v>1320.5999999999999</v>
+        <v>2403.1199999999999</v>
       </c>
       <c r="R43" s="18">
-        <v>1320.5999999999999</v>
+        <v>2403.1199999999999</v>
       </c>
       <c r="S43" s="18">
-        <v>1320.5999999999999</v>
+        <v>2403.1199999999999</v>
       </c>
       <c r="T43" s="30">
-        <v>2130</v>
-      </c>
-      <c r="U43" s="30">
-        <v>2130</v>
-      </c>
-      <c r="V43" s="30">
-        <v>2218.4400000000001</v>
-      </c>
-      <c r="W43" s="30">
-        <v>2218.4400000000001</v>
-      </c>
-      <c r="X43" s="30">
-        <v>2218.4400000000001</v>
-      </c>
-      <c r="Y43" s="30">
-        <v>2218.4400000000001</v>
-      </c>
-      <c r="Z43" s="30">
-        <v>2804.7600000000002</v>
-      </c>
-      <c r="AA43" s="30">
-        <v>2804.7600000000002</v>
+        <v>3876</v>
+      </c>
+      <c r="U43" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="V43" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="W43" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="X43" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="Y43" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z43" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA43" s="35" t="s">
+        <v>49</v>
       </c>
       <c r="AB43" s="35" t="s">
-        <v>48</v>
-      </c>
-      <c r="AC43" s="30">
-        <v>2804.7600000000002</v>
-      </c>
-      <c r="AD43" s="19">
-        <f>MIN(C43:AC43)</f>
-        <v>1310.1800000000001</v>
-      </c>
-      <c r="AE43" s="20">
-        <f>MAX(C43:AC43)</f>
-        <v>2804.7600000000002</v>
+        <v>49</v>
+      </c>
+      <c r="AC43" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD43" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE43" s="19">
+        <f>MIN(C43:AD43)</f>
+        <v>2159.8299999999999</v>
       </c>
       <c r="AF43" s="20">
-        <f>AVERAGE(C43:AC43)</f>
-        <v>1964.0813333333333</v>
+        <f>MAX(C43:AD43)</f>
+        <v>3876</v>
       </c>
       <c r="AG43" s="20">
-        <f>AVERAGE(Q43:AC43)</f>
-        <v>2125.8200000000002</v>
-      </c>
-      <c r="AH43" s="21">
-        <f>(AG43/AF43)-1</f>
-        <v>8.2348253059445709e-002</v>
+        <f>AVERAGE(C43:AD43)</f>
+        <v>2544.02</v>
+      </c>
+      <c r="AH43" s="20">
+        <f>AVERAGE(Q43:AD43)</f>
+        <v>2771.3400000000001</v>
       </c>
       <c r="AI43" s="21">
-        <f>(AG43/AD43)-1</f>
-        <v>0.62254041429421925</v>
+        <f>(AH43/AG43)-1</f>
+        <v>8.9354643438337877e-002</v>
       </c>
       <c r="AJ43" s="21">
-        <f>(AE43/AD43)-1</f>
-        <v>1.1407440199056618</v>
-      </c>
-      <c r="AK43" s="22" t="s">
-        <v>130</v>
+        <f>(AH43/AE43)-1</f>
+        <v>0.28312876476389359</v>
+      </c>
+      <c r="AK43" s="21">
+        <f>(AF43/AE43)-1</f>
+        <v>0.79458568498446636</v>
+      </c>
+      <c r="AL43" s="22" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="44" ht="18">
       <c r="A44" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C44" s="16"/>
       <c r="D44" s="16"/>
       <c r="E44" s="16"/>
       <c r="F44" s="16"/>
-      <c r="G44" s="16"/>
-      <c r="H44" s="16"/>
-      <c r="I44" s="16"/>
-      <c r="J44" s="16"/>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="16"/>
-      <c r="O44" s="16"/>
-      <c r="P44" s="16"/>
-      <c r="Q44" s="16"/>
-      <c r="R44" s="16"/>
-      <c r="S44" s="16"/>
-      <c r="T44" s="18">
-        <v>1896</v>
-      </c>
-      <c r="U44" s="18">
-        <v>1896</v>
-      </c>
-      <c r="V44" s="18">
-        <v>1592.6400000000001</v>
-      </c>
-      <c r="W44" s="18">
-        <v>1592.6400000000001</v>
-      </c>
-      <c r="X44" s="18">
-        <v>1592.6400000000001</v>
-      </c>
-      <c r="Y44" s="18">
-        <v>1592.6400000000001</v>
-      </c>
-      <c r="Z44" s="18">
-        <v>1592.6400000000001</v>
-      </c>
-      <c r="AA44" s="18">
-        <v>1592.6400000000001</v>
-      </c>
-      <c r="AB44" s="18">
-        <v>1592.6400000000001</v>
-      </c>
-      <c r="AC44" s="18">
-        <v>1592.6400000000001</v>
-      </c>
-      <c r="AD44" s="19">
-        <f>MIN(C44:AC44)</f>
-        <v>1592.6400000000001</v>
-      </c>
-      <c r="AE44" s="20">
-        <f>MAX(C44:AC44)</f>
-        <v>1896</v>
+      <c r="G44" s="24"/>
+      <c r="H44" s="17"/>
+      <c r="I44" s="17"/>
+      <c r="J44" s="17"/>
+      <c r="K44" s="17"/>
+      <c r="L44" s="17"/>
+      <c r="M44" s="17"/>
+      <c r="N44" s="17">
+        <v>1310.1800000000001</v>
+      </c>
+      <c r="O44" s="17">
+        <v>1320.5999999999999</v>
+      </c>
+      <c r="P44" s="18">
+        <v>1320.5999999999999</v>
+      </c>
+      <c r="Q44" s="18">
+        <v>1320.5999999999999</v>
+      </c>
+      <c r="R44" s="18">
+        <v>1320.5999999999999</v>
+      </c>
+      <c r="S44" s="18">
+        <v>1320.5999999999999</v>
+      </c>
+      <c r="T44" s="30">
+        <v>2130</v>
+      </c>
+      <c r="U44" s="30">
+        <v>2130</v>
+      </c>
+      <c r="V44" s="30">
+        <v>2218.4400000000001</v>
+      </c>
+      <c r="W44" s="30">
+        <v>2218.4400000000001</v>
+      </c>
+      <c r="X44" s="30">
+        <v>2218.4400000000001</v>
+      </c>
+      <c r="Y44" s="30">
+        <v>2218.4400000000001</v>
+      </c>
+      <c r="Z44" s="30">
+        <v>2804.7600000000002</v>
+      </c>
+      <c r="AA44" s="30">
+        <v>2804.7600000000002</v>
+      </c>
+      <c r="AB44" s="35" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC44" s="30">
+        <v>2804.7600000000002</v>
+      </c>
+      <c r="AD44" s="30">
+        <v>2804.7600000000002</v>
+      </c>
+      <c r="AE44" s="19">
+        <f>MIN(C44:AD44)</f>
+        <v>1310.1800000000001</v>
       </c>
       <c r="AF44" s="20">
-        <f>AVERAGE(C44:AC44)</f>
-        <v>1653.3119999999999</v>
+        <f>MAX(C44:AD44)</f>
+        <v>2804.7600000000002</v>
       </c>
       <c r="AG44" s="20">
-        <f>AVERAGE(Q44:AC44)</f>
-        <v>1653.3119999999999</v>
-      </c>
-      <c r="AH44" s="21">
-        <f>(AG44/AF44)-1</f>
-        <v>0</v>
+        <f>AVERAGE(C44:AD44)</f>
+        <v>2016.6237500000002</v>
+      </c>
+      <c r="AH44" s="20">
+        <f>AVERAGE(Q44:AD44)</f>
+        <v>2178.0461538461541</v>
       </c>
       <c r="AI44" s="21">
-        <f>(AG44/AD44)-1</f>
-        <v>3.809523809523796e-002</v>
+        <f>(AH44/AG44)-1</f>
+        <v>8.0045870651951789e-002</v>
       </c>
       <c r="AJ44" s="21">
-        <f>(AE44/AD44)-1</f>
-        <v>0.19047619047619047</v>
-      </c>
-      <c r="AK44" s="22" t="s">
-        <v>130</v>
+        <f>(AH44/AE44)-1</f>
+        <v>0.66240223011048394</v>
+      </c>
+      <c r="AK44" s="21">
+        <f>(AF44/AE44)-1</f>
+        <v>1.1407440199056618</v>
+      </c>
+      <c r="AL44" s="22" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="45" ht="18">
       <c r="A45" s="2" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C45" s="16"/>
       <c r="D45" s="16"/>
       <c r="E45" s="16"/>
       <c r="F45" s="16"/>
-      <c r="G45" s="24"/>
-      <c r="H45" s="17"/>
-      <c r="I45" s="17"/>
-      <c r="J45" s="17"/>
-      <c r="K45" s="17"/>
-      <c r="L45" s="17"/>
-      <c r="M45" s="17"/>
-      <c r="N45" s="17">
-        <v>1480.5599999999999</v>
-      </c>
-      <c r="O45" s="17">
-        <v>1480.5599999999999</v>
-      </c>
-      <c r="P45" s="18">
-        <v>1628.6199999999999</v>
-      </c>
-      <c r="Q45" s="18">
-        <v>1628.6199999999999</v>
-      </c>
-      <c r="R45" s="18">
-        <v>1628.6199999999999</v>
-      </c>
-      <c r="S45" s="18">
-        <v>1628.6199999999999</v>
-      </c>
-      <c r="T45" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="U45" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="V45" s="16" t="s">
-        <v>48</v>
+      <c r="G45" s="16"/>
+      <c r="H45" s="16"/>
+      <c r="I45" s="16"/>
+      <c r="J45" s="16"/>
+      <c r="K45" s="16"/>
+      <c r="L45" s="16"/>
+      <c r="M45" s="16"/>
+      <c r="N45" s="16"/>
+      <c r="O45" s="16"/>
+      <c r="P45" s="16"/>
+      <c r="Q45" s="16"/>
+      <c r="R45" s="16"/>
+      <c r="S45" s="16"/>
+      <c r="T45" s="18">
+        <v>1896</v>
+      </c>
+      <c r="U45" s="18">
+        <v>1896</v>
+      </c>
+      <c r="V45" s="18">
+        <v>1592.6400000000001</v>
       </c>
       <c r="W45" s="18">
-        <v>1985.76</v>
+        <v>1592.6400000000001</v>
       </c>
       <c r="X45" s="18">
-        <v>1985.76</v>
+        <v>1592.6400000000001</v>
       </c>
       <c r="Y45" s="18">
-        <v>1985.76</v>
-      </c>
-      <c r="Z45" s="16" t="s">
-        <v>48</v>
+        <v>1592.6400000000001</v>
+      </c>
+      <c r="Z45" s="18">
+        <v>1592.6400000000001</v>
       </c>
       <c r="AA45" s="18">
-        <v>1985.76</v>
+        <v>1592.6400000000001</v>
       </c>
       <c r="AB45" s="18">
-        <v>1985.76</v>
-      </c>
-      <c r="AC45" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="AD45" s="19">
-        <f>MIN(C45:AC45)</f>
-        <v>1480.5599999999999</v>
-      </c>
-      <c r="AE45" s="20">
-        <f>MAX(C45:AC45)</f>
-        <v>1985.76</v>
+        <v>1592.6400000000001</v>
+      </c>
+      <c r="AC45" s="18">
+        <v>1592.6400000000001</v>
+      </c>
+      <c r="AD45" s="18">
+        <v>1592.6400000000001</v>
+      </c>
+      <c r="AE45" s="19">
+        <f>MIN(C45:AD45)</f>
+        <v>1592.6400000000001</v>
       </c>
       <c r="AF45" s="20">
-        <f>AVERAGE(C45:AC45)</f>
-        <v>1764.0363636363634</v>
+        <f>MAX(C45:AD45)</f>
+        <v>1896</v>
       </c>
       <c r="AG45" s="20">
-        <f>AVERAGE(Q45:AC45)</f>
-        <v>1851.8325</v>
-      </c>
-      <c r="AH45" s="21">
-        <f>(AG45/AF45)-1</f>
-        <v>4.9770026385768329e-002</v>
+        <f>AVERAGE(C45:AD45)</f>
+        <v>1647.7963636363636</v>
+      </c>
+      <c r="AH45" s="20">
+        <f>AVERAGE(Q45:AD45)</f>
+        <v>1647.7963636363636</v>
       </c>
       <c r="AI45" s="21">
-        <f>(AG45/AD45)-1</f>
-        <v>0.25076491327605765</v>
+        <f>(AH45/AG45)-1</f>
+        <v>0</v>
       </c>
       <c r="AJ45" s="21">
-        <f>(AE45/AD45)-1</f>
-        <v>0.34122224023342529</v>
-      </c>
-      <c r="AK45" s="22" t="s">
-        <v>130</v>
+        <f>(AH45/AE45)-1</f>
+        <v>3.463203463203457e-002</v>
+      </c>
+      <c r="AK45" s="21">
+        <f>(AF45/AE45)-1</f>
+        <v>0.19047619047619047</v>
+      </c>
+      <c r="AL45" s="22" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="46" ht="18">
@@ -5829,401 +5935,395 @@
         <v>138</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C46" s="16"/>
-      <c r="D46" s="16">
-        <v>339.45999999999998</v>
-      </c>
-      <c r="E46" s="36"/>
-      <c r="F46" s="36"/>
-      <c r="G46" s="36"/>
-      <c r="H46" s="36"/>
-      <c r="I46" s="36"/>
-      <c r="J46" s="36"/>
-      <c r="K46" s="36"/>
-      <c r="L46" s="36"/>
-      <c r="M46" s="36"/>
-      <c r="N46" s="36"/>
-      <c r="O46" s="16"/>
-      <c r="P46" s="16"/>
-      <c r="Q46" s="16"/>
-      <c r="R46" s="16"/>
-      <c r="S46" s="16"/>
-      <c r="T46" s="16"/>
-      <c r="U46" s="16"/>
-      <c r="V46" s="16"/>
-      <c r="W46" s="16"/>
-      <c r="X46" s="16"/>
-      <c r="Y46" s="16"/>
-      <c r="Z46" s="16"/>
-      <c r="AA46" s="16"/>
-      <c r="AB46" s="16"/>
-      <c r="AC46" s="16"/>
-      <c r="AD46" s="19">
-        <f>MIN(C46:AC46)</f>
-        <v>339.45999999999998</v>
-      </c>
-      <c r="AE46" s="20">
-        <f>MAX(C46:AC46)</f>
-        <v>339.45999999999998</v>
+      <c r="D46" s="16"/>
+      <c r="E46" s="16"/>
+      <c r="F46" s="16"/>
+      <c r="G46" s="24"/>
+      <c r="H46" s="17"/>
+      <c r="I46" s="17"/>
+      <c r="J46" s="17"/>
+      <c r="K46" s="17"/>
+      <c r="L46" s="17"/>
+      <c r="M46" s="17"/>
+      <c r="N46" s="17">
+        <v>1480.5599999999999</v>
+      </c>
+      <c r="O46" s="17">
+        <v>1480.5599999999999</v>
+      </c>
+      <c r="P46" s="18">
+        <v>1628.6199999999999</v>
+      </c>
+      <c r="Q46" s="18">
+        <v>1628.6199999999999</v>
+      </c>
+      <c r="R46" s="18">
+        <v>1628.6199999999999</v>
+      </c>
+      <c r="S46" s="18">
+        <v>1628.6199999999999</v>
+      </c>
+      <c r="T46" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="U46" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="V46" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="W46" s="18">
+        <v>1985.76</v>
+      </c>
+      <c r="X46" s="18">
+        <v>1985.76</v>
+      </c>
+      <c r="Y46" s="18">
+        <v>1985.76</v>
+      </c>
+      <c r="Z46" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA46" s="18">
+        <v>1985.76</v>
+      </c>
+      <c r="AB46" s="18">
+        <v>1985.76</v>
+      </c>
+      <c r="AC46" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="AD46" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE46" s="19">
+        <f>MIN(C46:AD46)</f>
+        <v>1480.5599999999999</v>
       </c>
       <c r="AF46" s="20">
-        <f>AVERAGE(C46:AC46)</f>
-        <v>339.45999999999998</v>
-      </c>
-      <c r="AG46" s="20" t="e">
-        <f>AVERAGE(Q46:AC46)</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AH46" s="21" t="e">
-        <f>(AG46/AF46)-1</f>
-        <v>#NUM!</v>
-      </c>
-      <c r="AI46" s="21" t="e">
-        <f>(AG46/AD46)-1</f>
-        <v>#NUM!</v>
+        <f>MAX(C46:AD46)</f>
+        <v>1985.76</v>
+      </c>
+      <c r="AG46" s="20">
+        <f>AVERAGE(C46:AD46)</f>
+        <v>1764.0363636363634</v>
+      </c>
+      <c r="AH46" s="20">
+        <f>AVERAGE(Q46:AD46)</f>
+        <v>1851.8325</v>
+      </c>
+      <c r="AI46" s="21">
+        <f>(AH46/AG46)-1</f>
+        <v>4.9770026385768329e-002</v>
       </c>
       <c r="AJ46" s="21">
-        <f>(AE46/AD46)-1</f>
-        <v>0</v>
+        <f>(AH46/AE46)-1</f>
+        <v>0.25076491327605765</v>
+      </c>
+      <c r="AK46" s="21">
+        <f>(AF46/AE46)-1</f>
+        <v>0.34122224023342529</v>
+      </c>
+      <c r="AL46" s="22" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="47" ht="18">
       <c r="A47" s="2" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C47" s="16"/>
-      <c r="D47" s="16"/>
-      <c r="E47" s="16"/>
-      <c r="F47" s="16"/>
-      <c r="G47" s="24">
-        <v>378.99000000000001</v>
-      </c>
-      <c r="H47" s="16">
-        <v>378.99000000000001</v>
-      </c>
-      <c r="I47" s="16">
-        <v>378.99000000000001</v>
-      </c>
-      <c r="J47" s="16">
-        <v>378.99000000000001</v>
-      </c>
-      <c r="K47" s="16">
-        <v>378.99000000000001</v>
-      </c>
-      <c r="L47" s="16">
-        <v>378.99000000000001</v>
-      </c>
-      <c r="M47" s="16">
-        <v>378.99000000000001</v>
-      </c>
-      <c r="N47" s="16">
-        <v>378.99000000000001</v>
-      </c>
-      <c r="O47" s="16">
-        <v>378.99000000000001</v>
-      </c>
-      <c r="P47" s="16">
-        <v>378.99000000000001</v>
-      </c>
-      <c r="Q47" s="16">
-        <v>378.99000000000001</v>
-      </c>
-      <c r="R47" s="16">
-        <v>378.99000000000001</v>
-      </c>
-      <c r="S47" s="16">
-        <v>378.99000000000001</v>
-      </c>
-      <c r="T47" s="16">
-        <v>378.99000000000001</v>
-      </c>
-      <c r="U47" s="16">
-        <v>378.99000000000001</v>
-      </c>
-      <c r="V47" s="16">
-        <v>378.99000000000001</v>
-      </c>
-      <c r="W47" s="16">
-        <v>378.99000000000001</v>
-      </c>
-      <c r="X47" s="16">
-        <v>378.99000000000001</v>
-      </c>
-      <c r="Y47" s="16">
-        <v>378.99000000000001</v>
-      </c>
-      <c r="Z47" s="16">
-        <v>378.99000000000001</v>
-      </c>
-      <c r="AA47" s="16">
-        <v>378.99000000000001</v>
-      </c>
-      <c r="AB47" s="16">
-        <v>378.99000000000001</v>
-      </c>
-      <c r="AC47" s="16">
-        <v>378.99000000000001</v>
-      </c>
-      <c r="AD47" s="19">
-        <f>MIN(C47:AC47)</f>
-        <v>378.99000000000001</v>
-      </c>
-      <c r="AE47" s="20">
-        <f>MAX(C47:AC47)</f>
-        <v>378.99000000000001</v>
+      <c r="D47" s="16">
+        <v>339.45999999999998</v>
+      </c>
+      <c r="E47" s="36"/>
+      <c r="F47" s="36"/>
+      <c r="G47" s="36"/>
+      <c r="H47" s="36"/>
+      <c r="I47" s="36"/>
+      <c r="J47" s="36"/>
+      <c r="K47" s="36"/>
+      <c r="L47" s="36"/>
+      <c r="M47" s="36"/>
+      <c r="N47" s="36"/>
+      <c r="O47" s="16"/>
+      <c r="P47" s="16"/>
+      <c r="Q47" s="16"/>
+      <c r="R47" s="16"/>
+      <c r="S47" s="16"/>
+      <c r="T47" s="16"/>
+      <c r="U47" s="16"/>
+      <c r="V47" s="16"/>
+      <c r="W47" s="16"/>
+      <c r="X47" s="16"/>
+      <c r="Y47" s="16"/>
+      <c r="Z47" s="16"/>
+      <c r="AA47" s="16"/>
+      <c r="AB47" s="16"/>
+      <c r="AC47" s="16"/>
+      <c r="AD47" s="16"/>
+      <c r="AE47" s="19">
+        <f>MIN(C47:AD47)</f>
+        <v>339.45999999999998</v>
       </c>
       <c r="AF47" s="20">
-        <f>AVERAGE(C47:AC47)</f>
-        <v>378.98999999999984</v>
+        <f>MAX(C47:AD47)</f>
+        <v>339.45999999999998</v>
       </c>
       <c r="AG47" s="20">
-        <f>AVERAGE(Q47:AC47)</f>
-        <v>378.9899999999999</v>
-      </c>
-      <c r="AH47" s="21">
-        <f>(AG47/AF47)-1</f>
-        <v>2.2204460492503131e-016</v>
-      </c>
-      <c r="AI47" s="21">
-        <f>(AG47/AD47)-1</f>
-        <v>-3.3306690738754696e-016</v>
-      </c>
-      <c r="AJ47" s="21">
-        <f>(AE47/AD47)-1</f>
+        <f>AVERAGE(C47:AD47)</f>
+        <v>339.45999999999998</v>
+      </c>
+      <c r="AH47" s="20" t="e">
+        <f>AVERAGE(Q47:AD47)</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AI47" s="21" t="e">
+        <f>(AH47/AG47)-1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AJ47" s="21" t="e">
+        <f>(AH47/AE47)-1</f>
+        <v>#NUM!</v>
+      </c>
+      <c r="AK47" s="21">
+        <f>(AF47/AE47)-1</f>
         <v>0</v>
-      </c>
-      <c r="AK47" s="22" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="48" ht="18">
-      <c r="A48" s="25" t="s">
-        <v>142</v>
-      </c>
-      <c r="B48" s="26" t="s">
+      <c r="A48" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="C48" s="28"/>
-      <c r="D48" s="28"/>
-      <c r="E48" s="28"/>
-      <c r="F48" s="28"/>
-      <c r="G48" s="28">
-        <v>88.329999999999998</v>
-      </c>
-      <c r="H48" s="28">
-        <v>88.329999999999998</v>
-      </c>
-      <c r="I48" s="28">
-        <v>88.329999999999998</v>
-      </c>
-      <c r="J48" s="28">
-        <v>88.329999999999998</v>
-      </c>
-      <c r="K48" s="28">
-        <v>88.329999999999998</v>
-      </c>
-      <c r="L48" s="28">
-        <v>88.329999999999998</v>
-      </c>
-      <c r="M48" s="28">
-        <v>88.329999999999998</v>
-      </c>
-      <c r="N48" s="28">
-        <v>88.329999999999998</v>
-      </c>
-      <c r="O48" s="28">
-        <v>88.329999999999998</v>
+      <c r="C48" s="16"/>
+      <c r="D48" s="16"/>
+      <c r="E48" s="16"/>
+      <c r="F48" s="16"/>
+      <c r="G48" s="24">
+        <v>378.99000000000001</v>
+      </c>
+      <c r="H48" s="16">
+        <v>378.99000000000001</v>
+      </c>
+      <c r="I48" s="16">
+        <v>378.99000000000001</v>
+      </c>
+      <c r="J48" s="16">
+        <v>378.99000000000001</v>
+      </c>
+      <c r="K48" s="16">
+        <v>378.99000000000001</v>
+      </c>
+      <c r="L48" s="16">
+        <v>378.99000000000001</v>
+      </c>
+      <c r="M48" s="16">
+        <v>378.99000000000001</v>
+      </c>
+      <c r="N48" s="16">
+        <v>378.99000000000001</v>
+      </c>
+      <c r="O48" s="16">
+        <v>378.99000000000001</v>
       </c>
       <c r="P48" s="16">
-        <v>88.329999999999998</v>
-      </c>
-      <c r="Q48" s="17">
-        <v>118.58</v>
-      </c>
-      <c r="R48" s="17">
-        <v>118.58</v>
-      </c>
-      <c r="S48" s="17">
-        <v>118.58</v>
-      </c>
-      <c r="T48" s="17">
-        <v>117.58</v>
-      </c>
-      <c r="U48" s="17">
-        <v>117.58</v>
-      </c>
-      <c r="V48" s="17">
-        <v>119.59</v>
-      </c>
-      <c r="W48" s="18">
-        <v>128.36000000000001</v>
-      </c>
-      <c r="X48" s="18">
-        <v>128.36000000000001</v>
-      </c>
-      <c r="Y48" s="30">
-        <v>191.19</v>
-      </c>
-      <c r="Z48" s="30">
-        <v>191.19</v>
-      </c>
-      <c r="AA48" s="30">
-        <v>191.19</v>
-      </c>
-      <c r="AB48" s="30">
-        <v>181.09999999999999</v>
-      </c>
-      <c r="AC48" s="30">
-        <v>181.09999999999999</v>
-      </c>
-      <c r="AD48" s="19">
-        <f>MIN(C48:AC48)</f>
-        <v>88.329999999999998</v>
-      </c>
-      <c r="AE48" s="20">
-        <f>MAX(C48:AC48)</f>
-        <v>191.19</v>
+        <v>378.99000000000001</v>
+      </c>
+      <c r="Q48" s="16">
+        <v>378.99000000000001</v>
+      </c>
+      <c r="R48" s="16">
+        <v>378.99000000000001</v>
+      </c>
+      <c r="S48" s="16">
+        <v>378.99000000000001</v>
+      </c>
+      <c r="T48" s="16">
+        <v>378.99000000000001</v>
+      </c>
+      <c r="U48" s="16">
+        <v>378.99000000000001</v>
+      </c>
+      <c r="V48" s="16">
+        <v>378.99000000000001</v>
+      </c>
+      <c r="W48" s="16">
+        <v>378.99000000000001</v>
+      </c>
+      <c r="X48" s="16">
+        <v>378.99000000000001</v>
+      </c>
+      <c r="Y48" s="16">
+        <v>378.99000000000001</v>
+      </c>
+      <c r="Z48" s="16">
+        <v>378.99000000000001</v>
+      </c>
+      <c r="AA48" s="16">
+        <v>378.99000000000001</v>
+      </c>
+      <c r="AB48" s="16">
+        <v>378.99000000000001</v>
+      </c>
+      <c r="AC48" s="16">
+        <v>378.99000000000001</v>
+      </c>
+      <c r="AD48" s="16">
+        <v>378.99000000000001</v>
+      </c>
+      <c r="AE48" s="19">
+        <f>MIN(C48:AD48)</f>
+        <v>378.99000000000001</v>
       </c>
       <c r="AF48" s="20">
-        <f>AVERAGE(C48:AC48)</f>
-        <v>121.14260869565219</v>
+        <f>MAX(C48:AD48)</f>
+        <v>378.99000000000001</v>
       </c>
       <c r="AG48" s="20">
-        <f>AVERAGE(Q48:AC48)</f>
-        <v>146.38307692307691</v>
-      </c>
-      <c r="AH48" s="21">
-        <f>(AG48/AF48)-1</f>
-        <v>0.20835334899248048</v>
+        <f>AVERAGE(C48:AD48)</f>
+        <v>378.98999999999984</v>
+      </c>
+      <c r="AH48" s="20">
+        <f>AVERAGE(Q48:AD48)</f>
+        <v>378.9899999999999</v>
       </c>
       <c r="AI48" s="21">
-        <f>(AG48/AD48)-1</f>
-        <v>0.65722944552334339</v>
+        <f>(AH48/AG48)-1</f>
+        <v>2.2204460492503131e-016</v>
       </c>
       <c r="AJ48" s="21">
-        <f>(AE48/AD48)-1</f>
-        <v>1.1644967734631497</v>
-      </c>
-      <c r="AK48" s="22" t="s">
+        <f>(AH48/AE48)-1</f>
+        <v>-3.3306690738754696e-016</v>
+      </c>
+      <c r="AK48" s="21">
+        <f>(AF48/AE48)-1</f>
+        <v>0</v>
+      </c>
+      <c r="AL48" s="22" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="49" ht="18">
-      <c r="A49" s="2" t="s">
+      <c r="A49" s="25" t="s">
         <v>145</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="B49" s="26" t="s">
         <v>146</v>
       </c>
-      <c r="C49" s="16"/>
-      <c r="D49" s="16">
-        <v>39.950000000000003</v>
-      </c>
-      <c r="E49" s="16"/>
-      <c r="F49" s="16"/>
-      <c r="G49" s="16">
-        <v>39.950000000000003</v>
-      </c>
-      <c r="H49" s="24">
-        <v>29.989999999999998</v>
-      </c>
-      <c r="I49" s="16">
-        <v>32.990000000000002</v>
-      </c>
-      <c r="J49" s="16">
-        <v>39.990000000000002</v>
-      </c>
-      <c r="K49" s="16">
-        <v>39.990000000000002</v>
-      </c>
-      <c r="L49" s="16">
-        <v>39.990000000000002</v>
-      </c>
-      <c r="M49" s="16">
-        <v>36.990000000000002</v>
-      </c>
-      <c r="N49" s="16">
-        <v>34.5</v>
-      </c>
-      <c r="O49" s="16">
-        <v>34.5</v>
+      <c r="C49" s="28"/>
+      <c r="D49" s="28"/>
+      <c r="E49" s="28"/>
+      <c r="F49" s="28"/>
+      <c r="G49" s="28">
+        <v>88.329999999999998</v>
+      </c>
+      <c r="H49" s="28">
+        <v>88.329999999999998</v>
+      </c>
+      <c r="I49" s="28">
+        <v>88.329999999999998</v>
+      </c>
+      <c r="J49" s="28">
+        <v>88.329999999999998</v>
+      </c>
+      <c r="K49" s="28">
+        <v>88.329999999999998</v>
+      </c>
+      <c r="L49" s="28">
+        <v>88.329999999999998</v>
+      </c>
+      <c r="M49" s="28">
+        <v>88.329999999999998</v>
+      </c>
+      <c r="N49" s="28">
+        <v>88.329999999999998</v>
+      </c>
+      <c r="O49" s="28">
+        <v>88.329999999999998</v>
       </c>
       <c r="P49" s="16">
-        <v>32.5</v>
-      </c>
-      <c r="Q49" s="16">
-        <v>29.989999999999998</v>
-      </c>
-      <c r="R49" s="16">
-        <v>29.989999999999998</v>
-      </c>
-      <c r="S49" s="16">
-        <v>44.979999999999997</v>
-      </c>
-      <c r="T49" s="16">
-        <v>44.979999999999997</v>
-      </c>
-      <c r="U49" s="16">
-        <v>39.990000000000002</v>
-      </c>
-      <c r="V49" s="33">
-        <v>32.990000000000002</v>
-      </c>
-      <c r="W49" s="33">
-        <v>32.990000000000002</v>
-      </c>
-      <c r="X49" s="35">
-        <v>34.759999999999998</v>
-      </c>
-      <c r="Y49" s="35">
-        <v>40.039999999999999</v>
-      </c>
-      <c r="Z49" s="35">
-        <v>39.899999999999999</v>
-      </c>
-      <c r="AA49" s="35">
-        <v>39.899999999999999</v>
-      </c>
-      <c r="AB49" s="35">
-        <v>36.170000000000002</v>
-      </c>
-      <c r="AC49" s="33">
-        <v>29.149999999999999</v>
-      </c>
-      <c r="AD49" s="19">
-        <f>MIN(C49:AC49)</f>
-        <v>29.149999999999999</v>
-      </c>
-      <c r="AE49" s="20">
-        <f>MAX(C49:AC49)</f>
-        <v>44.979999999999997</v>
+        <v>88.329999999999998</v>
+      </c>
+      <c r="Q49" s="17">
+        <v>118.58</v>
+      </c>
+      <c r="R49" s="17">
+        <v>118.58</v>
+      </c>
+      <c r="S49" s="17">
+        <v>118.58</v>
+      </c>
+      <c r="T49" s="17">
+        <v>117.58</v>
+      </c>
+      <c r="U49" s="17">
+        <v>117.58</v>
+      </c>
+      <c r="V49" s="17">
+        <v>119.59</v>
+      </c>
+      <c r="W49" s="18">
+        <v>128.36000000000001</v>
+      </c>
+      <c r="X49" s="18">
+        <v>128.36000000000001</v>
+      </c>
+      <c r="Y49" s="30">
+        <v>191.19</v>
+      </c>
+      <c r="Z49" s="30">
+        <v>191.19</v>
+      </c>
+      <c r="AA49" s="30">
+        <v>191.19</v>
+      </c>
+      <c r="AB49" s="30">
+        <v>181.09999999999999</v>
+      </c>
+      <c r="AC49" s="30">
+        <v>181.09999999999999</v>
+      </c>
+      <c r="AD49" s="30">
+        <v>173.03999999999999</v>
+      </c>
+      <c r="AE49" s="19">
+        <f>MIN(C49:AD49)</f>
+        <v>88.329999999999998</v>
       </c>
       <c r="AF49" s="20">
-        <f>AVERAGE(C49:AC49)</f>
-        <v>36.548749999999998</v>
+        <f>MAX(C49:AD49)</f>
+        <v>191.19</v>
       </c>
       <c r="AG49" s="20">
-        <f>AVERAGE(Q49:AC49)</f>
-        <v>36.60230769230769</v>
-      </c>
-      <c r="AH49" s="21">
-        <f>(AG49/AF49)-1</f>
-        <v>1.4653768544119483e-003</v>
+        <f>AVERAGE(C49:AD49)</f>
+        <v>123.30500000000001</v>
+      </c>
+      <c r="AH49" s="20">
+        <f>AVERAGE(Q49:AD49)</f>
+        <v>148.28714285714287</v>
       </c>
       <c r="AI49" s="21">
-        <f>(AG49/AD49)-1</f>
-        <v>0.25565378018208196</v>
+        <f>(AH49/AG49)-1</f>
+        <v>0.20260445932559801</v>
       </c>
       <c r="AJ49" s="21">
-        <f>(AE49/AD49)-1</f>
-        <v>0.54305317324185243</v>
-      </c>
-      <c r="AK49" s="22" t="s">
+        <f>(AH49/AE49)-1</f>
+        <v>0.67878572237227286</v>
+      </c>
+      <c r="AK49" s="21">
+        <f>(AF49/AE49)-1</f>
+        <v>1.1644967734631497</v>
+      </c>
+      <c r="AL49" s="22" t="s">
         <v>147</v>
       </c>
     </row>
@@ -6236,108 +6336,111 @@
       </c>
       <c r="C50" s="16"/>
       <c r="D50" s="16">
-        <v>31.989999999999998</v>
+        <v>39.950000000000003</v>
       </c>
       <c r="E50" s="16"/>
       <c r="F50" s="16"/>
-      <c r="G50" s="33">
-        <v>27.489999999999998</v>
-      </c>
-      <c r="H50" s="16">
+      <c r="G50" s="16">
+        <v>39.950000000000003</v>
+      </c>
+      <c r="H50" s="24">
         <v>29.989999999999998</v>
       </c>
       <c r="I50" s="16">
-        <v>35.990000000000002</v>
-      </c>
-      <c r="J50" s="33">
-        <v>25.989999999999998</v>
-      </c>
-      <c r="K50" s="33">
-        <v>25.989999999999998</v>
-      </c>
-      <c r="L50" s="33">
-        <v>25.989999999999998</v>
-      </c>
-      <c r="M50" s="33">
-        <v>25.989999999999998</v>
-      </c>
-      <c r="N50" s="17">
-        <v>36.43</v>
-      </c>
-      <c r="O50" s="18">
-        <v>42</v>
-      </c>
-      <c r="P50" s="17">
-        <v>36.369999999999997</v>
-      </c>
-      <c r="Q50" s="17">
-        <v>35.119999999999997</v>
-      </c>
-      <c r="R50" s="17">
-        <v>36.409999999999997</v>
-      </c>
-      <c r="S50" s="17">
-        <v>36.530000000000001</v>
-      </c>
-      <c r="T50" s="33">
-        <v>27.989999999999998</v>
-      </c>
-      <c r="U50" s="33">
-        <v>27.989999999999998</v>
-      </c>
-      <c r="V50" s="35">
-        <v>30.989999999999998</v>
-      </c>
-      <c r="W50" s="35">
-        <v>30.989999999999998</v>
-      </c>
-      <c r="X50" s="34">
-        <v>36.530000000000001</v>
+        <v>32.990000000000002</v>
+      </c>
+      <c r="J50" s="16">
+        <v>39.990000000000002</v>
+      </c>
+      <c r="K50" s="16">
+        <v>39.990000000000002</v>
+      </c>
+      <c r="L50" s="16">
+        <v>39.990000000000002</v>
+      </c>
+      <c r="M50" s="16">
+        <v>36.990000000000002</v>
+      </c>
+      <c r="N50" s="16">
+        <v>34.5</v>
+      </c>
+      <c r="O50" s="16">
+        <v>34.5</v>
+      </c>
+      <c r="P50" s="16">
+        <v>32.5</v>
+      </c>
+      <c r="Q50" s="16">
+        <v>29.989999999999998</v>
+      </c>
+      <c r="R50" s="16">
+        <v>29.989999999999998</v>
+      </c>
+      <c r="S50" s="16">
+        <v>44.979999999999997</v>
+      </c>
+      <c r="T50" s="16">
+        <v>44.979999999999997</v>
+      </c>
+      <c r="U50" s="16">
+        <v>39.990000000000002</v>
+      </c>
+      <c r="V50" s="33">
+        <v>32.990000000000002</v>
+      </c>
+      <c r="W50" s="33">
+        <v>32.990000000000002</v>
+      </c>
+      <c r="X50" s="35">
+        <v>34.759999999999998</v>
       </c>
       <c r="Y50" s="35">
-        <v>30.989999999999998</v>
+        <v>40.039999999999999</v>
       </c>
       <c r="Z50" s="35">
-        <v>30.989999999999998</v>
+        <v>39.899999999999999</v>
       </c>
       <c r="AA50" s="35">
-        <v>30.989999999999998</v>
+        <v>39.899999999999999</v>
       </c>
       <c r="AB50" s="35">
-        <v>36.100000000000001</v>
-      </c>
-      <c r="AC50" s="35">
-        <v>36.100000000000001</v>
-      </c>
-      <c r="AD50" s="19">
-        <f>MIN(C50:AC50)</f>
-        <v>25.989999999999998</v>
-      </c>
-      <c r="AE50" s="20">
-        <f>MAX(C50:AC50)</f>
-        <v>42</v>
+        <v>36.170000000000002</v>
+      </c>
+      <c r="AC50" s="33">
+        <v>29.149999999999999</v>
+      </c>
+      <c r="AD50" s="35">
+        <v>32.460000000000001</v>
+      </c>
+      <c r="AE50" s="19">
+        <f>MIN(C50:AD50)</f>
+        <v>29.149999999999999</v>
       </c>
       <c r="AF50" s="20">
-        <f>AVERAGE(C50:AC50)</f>
-        <v>32.164166666666667</v>
+        <f>MAX(C50:AD50)</f>
+        <v>44.979999999999997</v>
       </c>
       <c r="AG50" s="20">
-        <f>AVERAGE(Q50:AC50)</f>
-        <v>32.901538461538472</v>
-      </c>
-      <c r="AH50" s="21">
-        <f>(AG50/AF50)-1</f>
-        <v>2.2925257243987085e-002</v>
+        <f>AVERAGE(C50:AD50)</f>
+        <v>36.385199999999998</v>
+      </c>
+      <c r="AH50" s="20">
+        <f>AVERAGE(Q50:AD50)</f>
+        <v>36.306428571428569</v>
       </c>
       <c r="AI50" s="21">
-        <f>(AG50/AD50)-1</f>
-        <v>0.26593068339894099</v>
+        <f>(AH50/AG50)-1</f>
+        <v>-2.164930481938554e-003</v>
       </c>
       <c r="AJ50" s="21">
-        <f>(AE50/AD50)-1</f>
-        <v>0.61600615621392851</v>
-      </c>
-      <c r="AK50" s="22" t="s">
+        <f>(AH50/AE50)-1</f>
+        <v>0.2455035530507228</v>
+      </c>
+      <c r="AK50" s="21">
+        <f>(AF50/AE50)-1</f>
+        <v>0.54305317324185243</v>
+      </c>
+      <c r="AL50" s="22" t="s">
         <v>150</v>
       </c>
     </row>
@@ -6350,446 +6453,460 @@
       </c>
       <c r="C51" s="16"/>
       <c r="D51" s="16">
-        <v>43.990000000000002</v>
+        <v>31.989999999999998</v>
       </c>
       <c r="E51" s="16"/>
       <c r="F51" s="16"/>
-      <c r="G51" s="16">
+      <c r="G51" s="33">
+        <v>27.489999999999998</v>
+      </c>
+      <c r="H51" s="16">
+        <v>29.989999999999998</v>
+      </c>
+      <c r="I51" s="16">
+        <v>35.990000000000002</v>
+      </c>
+      <c r="J51" s="33">
+        <v>25.989999999999998</v>
+      </c>
+      <c r="K51" s="33">
+        <v>25.989999999999998</v>
+      </c>
+      <c r="L51" s="33">
+        <v>25.989999999999998</v>
+      </c>
+      <c r="M51" s="33">
+        <v>25.989999999999998</v>
+      </c>
+      <c r="N51" s="17">
+        <v>36.43</v>
+      </c>
+      <c r="O51" s="18">
+        <v>42</v>
+      </c>
+      <c r="P51" s="17">
+        <v>36.369999999999997</v>
+      </c>
+      <c r="Q51" s="17">
+        <v>35.119999999999997</v>
+      </c>
+      <c r="R51" s="17">
+        <v>36.409999999999997</v>
+      </c>
+      <c r="S51" s="17">
+        <v>36.530000000000001</v>
+      </c>
+      <c r="T51" s="33">
+        <v>27.989999999999998</v>
+      </c>
+      <c r="U51" s="33">
+        <v>27.989999999999998</v>
+      </c>
+      <c r="V51" s="35">
+        <v>30.989999999999998</v>
+      </c>
+      <c r="W51" s="35">
+        <v>30.989999999999998</v>
+      </c>
+      <c r="X51" s="34">
+        <v>36.530000000000001</v>
+      </c>
+      <c r="Y51" s="35">
+        <v>30.989999999999998</v>
+      </c>
+      <c r="Z51" s="35">
+        <v>30.989999999999998</v>
+      </c>
+      <c r="AA51" s="35">
+        <v>30.989999999999998</v>
+      </c>
+      <c r="AB51" s="35">
+        <v>36.100000000000001</v>
+      </c>
+      <c r="AC51" s="35">
+        <v>36.100000000000001</v>
+      </c>
+      <c r="AD51" s="35">
+        <v>36.140000000000001</v>
+      </c>
+      <c r="AE51" s="19">
+        <f>MIN(C51:AD51)</f>
+        <v>25.989999999999998</v>
+      </c>
+      <c r="AF51" s="20">
+        <f>MAX(C51:AD51)</f>
+        <v>42</v>
+      </c>
+      <c r="AG51" s="20">
+        <f>AVERAGE(C51:AD51)</f>
+        <v>32.3232</v>
+      </c>
+      <c r="AH51" s="20">
+        <f>AVERAGE(Q51:AD51)</f>
+        <v>33.132857142857155</v>
+      </c>
+      <c r="AI51" s="21">
+        <f>(AH51/AG51)-1</f>
+        <v>2.5048792905936201e-002</v>
+      </c>
+      <c r="AJ51" s="21">
+        <f>(AH51/AE51)-1</f>
+        <v>0.2748309789479475</v>
+      </c>
+      <c r="AK51" s="21">
+        <f>(AF51/AE51)-1</f>
+        <v>0.61600615621392851</v>
+      </c>
+      <c r="AL51" s="22" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="52" ht="18">
+      <c r="A52" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C52" s="16"/>
+      <c r="D52" s="16">
+        <v>43.990000000000002</v>
+      </c>
+      <c r="E52" s="16"/>
+      <c r="F52" s="16"/>
+      <c r="G52" s="16">
         <v>22.989999999999998</v>
       </c>
-      <c r="H51" s="24">
+      <c r="H52" s="24">
         <v>21.690000000000001</v>
       </c>
-      <c r="I51" s="16">
+      <c r="I52" s="16">
         <v>21.690000000000001</v>
       </c>
-      <c r="J51" s="16">
+      <c r="J52" s="16">
         <v>36.170000000000002</v>
       </c>
-      <c r="K51" s="16">
+      <c r="K52" s="16">
         <v>42.020000000000003</v>
       </c>
-      <c r="L51" s="16">
+      <c r="L52" s="16">
         <v>39.799999999999997</v>
       </c>
-      <c r="M51" s="16">
+      <c r="M52" s="16">
         <v>36.759999999999998</v>
       </c>
-      <c r="N51" s="16">
+      <c r="N52" s="16">
         <v>24.899999999999999</v>
       </c>
-      <c r="O51" s="16">
+      <c r="O52" s="16">
         <v>22.899999999999999</v>
       </c>
-      <c r="P51" s="16">
+      <c r="P52" s="16">
         <v>22.899999999999999</v>
       </c>
-      <c r="Q51" s="16">
+      <c r="Q52" s="16">
         <v>34.689999999999998</v>
       </c>
-      <c r="R51" s="16">
+      <c r="R52" s="16">
         <v>34.689999999999998</v>
       </c>
-      <c r="S51" s="16">
+      <c r="S52" s="16">
         <v>24.899999999999999</v>
       </c>
-      <c r="T51" s="16">
+      <c r="T52" s="16">
         <v>24.899999999999999</v>
       </c>
-      <c r="U51" s="16">
+      <c r="U52" s="16">
         <v>24.899999999999999</v>
       </c>
-      <c r="V51" s="33">
+      <c r="V52" s="33">
         <v>21.690000000000001</v>
       </c>
-      <c r="W51" s="35">
+      <c r="W52" s="35">
         <v>28.899999999999999</v>
       </c>
-      <c r="X51" s="35">
+      <c r="X52" s="35">
         <v>28.899999999999999</v>
       </c>
-      <c r="Y51" s="35">
+      <c r="Y52" s="35">
         <v>28.899999999999999</v>
       </c>
-      <c r="Z51" s="35">
+      <c r="Z52" s="35">
         <v>28.899999999999999</v>
       </c>
-      <c r="AA51" s="35">
+      <c r="AA52" s="35">
         <v>24.899999999999999</v>
       </c>
-      <c r="AB51" s="35">
+      <c r="AB52" s="35">
         <v>24.899999999999999</v>
       </c>
-      <c r="AC51" s="35">
+      <c r="AC52" s="35">
         <v>24.899999999999999</v>
       </c>
-      <c r="AD51" s="19">
-        <f>MIN(C51:AC51)</f>
+      <c r="AD52" s="32">
+        <v>34.719999999999999</v>
+      </c>
+      <c r="AE52" s="19">
+        <f>MIN(C52:AD52)</f>
         <v>21.690000000000001</v>
       </c>
-      <c r="AE51" s="20">
-        <f>MAX(C51:AC51)</f>
+      <c r="AF52" s="20">
+        <f>MAX(C52:AD52)</f>
         <v>43.990000000000002</v>
       </c>
-      <c r="AF51" s="20">
-        <f>AVERAGE(C51:AC51)</f>
-        <v>28.828333333333322</v>
-      </c>
-      <c r="AG51" s="20">
-        <f>AVERAGE(Q51:AC51)</f>
-        <v>27.389999999999993</v>
-      </c>
-      <c r="AH51" s="21">
-        <f>(AG51/AF51)-1</f>
-        <v>-4.9893045036711436e-002</v>
-      </c>
-      <c r="AI51" s="21">
-        <f>(AG51/AD51)-1</f>
-        <v>0.26279391424619614</v>
-      </c>
-      <c r="AJ51" s="21">
-        <f>(AE51/AD51)-1</f>
+      <c r="AG52" s="20">
+        <f>AVERAGE(C52:AD52)</f>
+        <v>29.063999999999993</v>
+      </c>
+      <c r="AH52" s="20">
+        <f>AVERAGE(Q52:AD52)</f>
+        <v>27.913571428571426</v>
+      </c>
+      <c r="AI52" s="21">
+        <f>(AH52/AG52)-1</f>
+        <v>-3.9582596044197893e-002</v>
+      </c>
+      <c r="AJ52" s="21">
+        <f>(AH52/AE52)-1</f>
+        <v>0.28693275373773286</v>
+      </c>
+      <c r="AK52" s="21">
+        <f>(AF52/AE52)-1</f>
         <v>1.0281235592438911</v>
       </c>
-      <c r="AK51" s="22" t="s">
-        <v>153</v>
+      <c r="AL52" s="22" t="s">
+        <v>156</v>
       </c>
     </row>
-    <row r="52" ht="54">
-      <c r="A52" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="C52" s="16"/>
-      <c r="D52" s="16"/>
-      <c r="E52" s="16"/>
-      <c r="F52" s="16">
+    <row r="53" ht="54">
+      <c r="A53" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="C53" s="16"/>
+      <c r="D53" s="16"/>
+      <c r="E53" s="16"/>
+      <c r="F53" s="16">
         <v>1714.0799999999999</v>
       </c>
-      <c r="G52" s="16">
+      <c r="G53" s="16">
         <v>1714.0799999999999</v>
       </c>
-      <c r="H52" s="16">
+      <c r="H53" s="16">
         <v>1714.0799999999999</v>
       </c>
-      <c r="I52" s="16">
+      <c r="I53" s="16">
         <v>1714.0799999999999</v>
       </c>
-      <c r="J52" s="16">
+      <c r="J53" s="16">
         <v>1714.0799999999999</v>
       </c>
-      <c r="K52" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="L52" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="M52" s="24">
+      <c r="K53" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L53" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M53" s="24">
         <v>1449.28</v>
       </c>
-      <c r="N52" s="17">
+      <c r="N53" s="17">
         <v>1820.77</v>
       </c>
-      <c r="O52" s="17">
+      <c r="O53" s="17">
         <v>1820.77</v>
       </c>
-      <c r="P52" s="17">
+      <c r="P53" s="17">
         <v>1820.77</v>
       </c>
-      <c r="Q52" s="17">
+      <c r="Q53" s="17">
         <v>1820.77</v>
       </c>
-      <c r="R52" s="16">
+      <c r="R53" s="16">
         <v>1669.97</v>
       </c>
-      <c r="S52" s="16">
+      <c r="S53" s="16">
         <v>1669.76</v>
       </c>
-      <c r="T52" s="16">
+      <c r="T53" s="16">
         <v>1669.76</v>
       </c>
-      <c r="U52" s="16">
+      <c r="U53" s="16">
         <v>1611.6900000000001</v>
       </c>
-      <c r="V52" s="16">
+      <c r="V53" s="16">
         <v>1611.4100000000001</v>
       </c>
-      <c r="W52" s="16">
+      <c r="W53" s="16">
         <v>1611.4100000000001</v>
       </c>
-      <c r="X52" s="16">
+      <c r="X53" s="16">
         <v>1611.4100000000001</v>
       </c>
-      <c r="Y52" s="17">
+      <c r="Y53" s="17">
         <v>1820.77</v>
       </c>
-      <c r="Z52" s="17">
+      <c r="Z53" s="17">
         <v>1820.77</v>
       </c>
-      <c r="AA52" s="17">
+      <c r="AA53" s="17">
         <v>1820.77</v>
       </c>
-      <c r="AB52" s="17">
+      <c r="AB53" s="17">
         <v>1820.8099999999999</v>
       </c>
-      <c r="AC52" s="17">
+      <c r="AC53" s="17">
         <v>1820.8099999999999</v>
       </c>
-      <c r="AD52" s="19">
-        <f>MIN(C52:AC52)</f>
+      <c r="AD53" s="30">
+        <v>2407.79</v>
+      </c>
+      <c r="AE53" s="19">
+        <f>MIN(C53:AD53)</f>
         <v>1449.28</v>
       </c>
-      <c r="AE52" s="20">
-        <f>MAX(C52:AC52)</f>
-        <v>1820.8099999999999</v>
-      </c>
-      <c r="AF52" s="20">
-        <f>AVERAGE(C52:AC52)</f>
-        <v>1721.004545454545</v>
-      </c>
-      <c r="AG52" s="20">
-        <f>AVERAGE(Q52:AC52)</f>
-        <v>1721.5469230769233</v>
-      </c>
-      <c r="AH52" s="21">
-        <f>(AG52/AF52)-1</f>
-        <v>3.1515176633956088e-004</v>
-      </c>
-      <c r="AI52" s="21">
-        <f>(AG52/AD52)-1</f>
-        <v>0.18786357575963475</v>
-      </c>
-      <c r="AJ52" s="21">
-        <f>(AE52/AD52)-1</f>
-        <v>0.25635487966438508</v>
-      </c>
-      <c r="AK52" s="1" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="53" ht="18">
-      <c r="A53" s="25" t="s">
-        <v>156</v>
-      </c>
-      <c r="B53" s="26" t="s">
-        <v>157</v>
-      </c>
-      <c r="C53" s="28"/>
-      <c r="D53" s="28"/>
-      <c r="E53" s="28"/>
-      <c r="F53" s="28"/>
-      <c r="G53" s="28">
-        <v>33.890000000000001</v>
-      </c>
-      <c r="H53" s="28">
-        <v>33.890000000000001</v>
-      </c>
-      <c r="I53" s="28">
-        <v>33.890000000000001</v>
-      </c>
-      <c r="J53" s="28">
-        <v>33.890000000000001</v>
-      </c>
-      <c r="K53" s="28">
-        <v>33.890000000000001</v>
-      </c>
-      <c r="L53" s="28">
-        <v>38.039999999999999</v>
-      </c>
-      <c r="M53" s="28">
-        <v>38.369999999999997</v>
-      </c>
-      <c r="N53" s="28">
-        <v>38.369999999999997</v>
-      </c>
-      <c r="O53" s="28">
-        <v>38.369999999999997</v>
-      </c>
-      <c r="P53" s="16">
-        <v>38.369999999999997</v>
-      </c>
-      <c r="Q53" s="16">
-        <v>38.369999999999997</v>
-      </c>
-      <c r="R53" s="16">
-        <v>39.390000000000001</v>
-      </c>
-      <c r="S53" s="16">
-        <v>39.390000000000001</v>
-      </c>
-      <c r="T53" s="16">
-        <v>43.210000000000001</v>
-      </c>
-      <c r="U53" s="16">
-        <v>39.899999999999999</v>
-      </c>
-      <c r="V53" s="33">
-        <v>31.989999999999998</v>
-      </c>
-      <c r="W53" s="33">
-        <v>30.989999999999998</v>
-      </c>
-      <c r="X53" s="35">
-        <v>39.899999999999999</v>
-      </c>
-      <c r="Y53" s="35">
-        <v>43.990000000000002</v>
-      </c>
-      <c r="Z53" s="35">
-        <v>36.990000000000002</v>
-      </c>
-      <c r="AA53" s="35">
-        <v>36.990000000000002</v>
-      </c>
-      <c r="AB53" s="35">
-        <v>36.990000000000002</v>
-      </c>
-      <c r="AC53" s="35">
-        <v>36.990000000000002</v>
-      </c>
-      <c r="AD53" s="19">
-        <f>MIN(C53:AC53)</f>
-        <v>30.989999999999998</v>
-      </c>
-      <c r="AE53" s="20">
-        <f>MAX(C53:AC53)</f>
-        <v>43.990000000000002</v>
-      </c>
       <c r="AF53" s="20">
-        <f>AVERAGE(C53:AC53)</f>
-        <v>37.219999999999999</v>
+        <f>MAX(C53:AD53)</f>
+        <v>2407.79</v>
       </c>
       <c r="AG53" s="20">
-        <f>AVERAGE(Q53:AC53)</f>
-        <v>38.083846153846153</v>
-      </c>
-      <c r="AH53" s="21">
-        <f>(AG53/AF53)-1</f>
-        <v>2.3209192741702189e-002</v>
+        <f>AVERAGE(C53:AD53)</f>
+        <v>1750.8647826086954</v>
+      </c>
+      <c r="AH53" s="20">
+        <f>AVERAGE(Q53:AD53)</f>
+        <v>1770.5642857142861</v>
       </c>
       <c r="AI53" s="21">
-        <f>(AG53/AD53)-1</f>
-        <v>0.22890758805570033</v>
+        <f>(AH53/AG53)-1</f>
+        <v>1.1251298958814937e-002</v>
       </c>
       <c r="AJ53" s="21">
-        <f>(AE53/AD53)-1</f>
-        <v>0.41949015811552126</v>
-      </c>
-      <c r="AK53" s="22" t="s">
+        <f>(AH53/AE53)-1</f>
+        <v>0.22168544774942456</v>
+      </c>
+      <c r="AK53" s="21">
+        <f>(AF53/AE53)-1</f>
+        <v>0.66136978361669252</v>
+      </c>
+      <c r="AL53" s="1" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="54" ht="18">
-      <c r="A54" s="2" t="s">
+      <c r="A54" s="25" t="s">
         <v>159</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="B54" s="26" t="s">
         <v>160</v>
       </c>
-      <c r="C54" s="16"/>
-      <c r="D54" s="16"/>
-      <c r="E54" s="16"/>
-      <c r="F54" s="16"/>
-      <c r="G54" s="16">
-        <v>90.739999999999995</v>
-      </c>
-      <c r="H54" s="16">
-        <v>90.739999999999995</v>
-      </c>
-      <c r="I54" s="24">
-        <v>89.950000000000003</v>
-      </c>
-      <c r="J54" s="24">
-        <v>89.950000000000003</v>
-      </c>
-      <c r="K54" s="24">
-        <v>89.950000000000003</v>
-      </c>
-      <c r="L54" s="16">
-        <v>93.280000000000001</v>
-      </c>
-      <c r="M54" s="16">
-        <v>92.060000000000002</v>
-      </c>
-      <c r="N54" s="17">
-        <v>88.049999999999997</v>
-      </c>
-      <c r="O54" s="17">
-        <v>89.950000000000003</v>
-      </c>
-      <c r="P54" s="17">
-        <v>89.950000000000003</v>
+      <c r="C54" s="28"/>
+      <c r="D54" s="28"/>
+      <c r="E54" s="28"/>
+      <c r="F54" s="28"/>
+      <c r="G54" s="28">
+        <v>33.890000000000001</v>
+      </c>
+      <c r="H54" s="28">
+        <v>33.890000000000001</v>
+      </c>
+      <c r="I54" s="28">
+        <v>33.890000000000001</v>
+      </c>
+      <c r="J54" s="28">
+        <v>33.890000000000001</v>
+      </c>
+      <c r="K54" s="28">
+        <v>33.890000000000001</v>
+      </c>
+      <c r="L54" s="28">
+        <v>38.039999999999999</v>
+      </c>
+      <c r="M54" s="28">
+        <v>38.369999999999997</v>
+      </c>
+      <c r="N54" s="28">
+        <v>38.369999999999997</v>
+      </c>
+      <c r="O54" s="28">
+        <v>38.369999999999997</v>
+      </c>
+      <c r="P54" s="16">
+        <v>38.369999999999997</v>
       </c>
       <c r="Q54" s="16">
-        <v>81.689999999999998</v>
+        <v>38.369999999999997</v>
       </c>
       <c r="R54" s="16">
-        <v>84.900000000000006</v>
-      </c>
-      <c r="S54" s="17">
-        <v>89.950000000000003</v>
-      </c>
-      <c r="T54" s="17">
-        <v>89.650000000000006</v>
+        <v>39.390000000000001</v>
+      </c>
+      <c r="S54" s="16">
+        <v>39.390000000000001</v>
+      </c>
+      <c r="T54" s="16">
+        <v>43.210000000000001</v>
       </c>
       <c r="U54" s="16">
-        <v>84.900000000000006</v>
-      </c>
-      <c r="V54" s="16">
-        <v>83.079999999999998</v>
-      </c>
-      <c r="W54" s="16">
-        <v>84.099999999999994</v>
-      </c>
-      <c r="X54" s="16">
-        <v>84.680000000000007</v>
-      </c>
-      <c r="Y54" s="16">
-        <v>85.209999999999994</v>
-      </c>
-      <c r="Z54" s="16">
-        <v>85.209999999999994</v>
-      </c>
-      <c r="AA54" s="16">
-        <v>85.150000000000006</v>
-      </c>
-      <c r="AB54" s="16">
-        <v>85.040000000000006</v>
-      </c>
-      <c r="AC54" s="17">
-        <v>109.84999999999999</v>
-      </c>
-      <c r="AD54" s="19">
-        <f>MIN(C54:AC54)</f>
-        <v>81.689999999999998</v>
-      </c>
-      <c r="AE54" s="20">
-        <f>MAX(C54:AC54)</f>
-        <v>109.84999999999999</v>
+        <v>39.899999999999999</v>
+      </c>
+      <c r="V54" s="33">
+        <v>31.989999999999998</v>
+      </c>
+      <c r="W54" s="33">
+        <v>30.989999999999998</v>
+      </c>
+      <c r="X54" s="35">
+        <v>39.899999999999999</v>
+      </c>
+      <c r="Y54" s="35">
+        <v>43.990000000000002</v>
+      </c>
+      <c r="Z54" s="35">
+        <v>36.990000000000002</v>
+      </c>
+      <c r="AA54" s="35">
+        <v>36.990000000000002</v>
+      </c>
+      <c r="AB54" s="35">
+        <v>36.990000000000002</v>
+      </c>
+      <c r="AC54" s="35">
+        <v>36.990000000000002</v>
+      </c>
+      <c r="AD54" s="35">
+        <v>36.990000000000002</v>
+      </c>
+      <c r="AE54" s="19">
+        <f>MIN(C54:AD54)</f>
+        <v>30.989999999999998</v>
       </c>
       <c r="AF54" s="20">
-        <f>AVERAGE(C54:AC54)</f>
-        <v>88.610000000000014</v>
+        <f>MAX(C54:AD54)</f>
+        <v>43.990000000000002</v>
       </c>
       <c r="AG54" s="20">
-        <f>AVERAGE(Q54:AC54)</f>
-        <v>87.185384615384621</v>
-      </c>
-      <c r="AH54" s="21">
-        <f>(AG54/AF54)-1</f>
-        <v>-1.6077365812158795e-002</v>
+        <f>AVERAGE(C54:AD54)</f>
+        <v>37.210416666666667</v>
+      </c>
+      <c r="AH54" s="20">
+        <f>AVERAGE(Q54:AD54)</f>
+        <v>38.005714285714291</v>
       </c>
       <c r="AI54" s="21">
-        <f>(AG54/AD54)-1</f>
-        <v>6.7271203517990319e-002</v>
+        <f>(AH54/AG54)-1</f>
+        <v>2.137298343557803e-002</v>
       </c>
       <c r="AJ54" s="21">
-        <f>(AE54/AD54)-1</f>
-        <v>0.34471783572040637</v>
-      </c>
-      <c r="AK54" s="1" t="s">
+        <f>(AH54/AE54)-1</f>
+        <v>0.22638639192366217</v>
+      </c>
+      <c r="AK54" s="21">
+        <f>(AF54/AE54)-1</f>
+        <v>0.41949015811552126</v>
+      </c>
+      <c r="AL54" s="22" t="s">
         <v>161</v>
       </c>
     </row>
@@ -6803,409 +6920,538 @@
       <c r="C55" s="16"/>
       <c r="D55" s="16"/>
       <c r="E55" s="16"/>
-      <c r="F55" s="16">
-        <v>309.05000000000001</v>
-      </c>
+      <c r="F55" s="16"/>
       <c r="G55" s="16">
-        <v>309.05000000000001</v>
+        <v>90.739999999999995</v>
       </c>
       <c r="H55" s="16">
-        <v>309.05000000000001</v>
-      </c>
-      <c r="I55" s="16">
-        <v>309.05000000000001</v>
-      </c>
-      <c r="J55" s="16">
-        <v>309.05000000000001</v>
-      </c>
-      <c r="K55" s="16">
-        <v>309.05000000000001</v>
+        <v>90.739999999999995</v>
+      </c>
+      <c r="I55" s="24">
+        <v>89.950000000000003</v>
+      </c>
+      <c r="J55" s="24">
+        <v>89.950000000000003</v>
+      </c>
+      <c r="K55" s="24">
+        <v>89.950000000000003</v>
       </c>
       <c r="L55" s="16">
-        <v>309.05000000000001</v>
+        <v>93.280000000000001</v>
       </c>
       <c r="M55" s="16">
-        <v>309.05000000000001</v>
-      </c>
-      <c r="N55" s="16">
-        <v>309.05000000000001</v>
-      </c>
-      <c r="O55" s="16">
-        <v>309.05000000000001</v>
-      </c>
-      <c r="P55" s="16">
-        <v>309.05000000000001</v>
+        <v>92.060000000000002</v>
+      </c>
+      <c r="N55" s="17">
+        <v>88.049999999999997</v>
+      </c>
+      <c r="O55" s="17">
+        <v>89.950000000000003</v>
+      </c>
+      <c r="P55" s="17">
+        <v>89.950000000000003</v>
       </c>
       <c r="Q55" s="16">
-        <v>309.05000000000001</v>
+        <v>81.689999999999998</v>
       </c>
       <c r="R55" s="16">
-        <v>309.05000000000001</v>
-      </c>
-      <c r="S55" s="16">
-        <v>309.05000000000001</v>
-      </c>
-      <c r="T55" s="16">
-        <v>309.05000000000001</v>
+        <v>84.900000000000006</v>
+      </c>
+      <c r="S55" s="17">
+        <v>89.950000000000003</v>
+      </c>
+      <c r="T55" s="17">
+        <v>89.650000000000006</v>
       </c>
       <c r="U55" s="16">
-        <v>309.05000000000001</v>
+        <v>84.900000000000006</v>
       </c>
       <c r="V55" s="16">
-        <v>309.05000000000001</v>
-      </c>
-      <c r="W55" s="33">
-        <v>298.80000000000001</v>
-      </c>
-      <c r="X55" s="33">
-        <v>298.80000000000001</v>
-      </c>
-      <c r="Y55" s="33">
-        <v>298.80000000000001</v>
-      </c>
-      <c r="Z55" s="33">
-        <v>298.80000000000001</v>
-      </c>
-      <c r="AA55" s="33">
-        <v>298.80000000000001</v>
-      </c>
-      <c r="AB55" s="33">
-        <v>298.80000000000001</v>
-      </c>
-      <c r="AC55" s="33">
-        <v>298.80000000000001</v>
-      </c>
-      <c r="AD55" s="19">
-        <f>MIN(C55:AC55)</f>
-        <v>298.80000000000001</v>
-      </c>
-      <c r="AE55" s="20">
-        <f>MAX(C55:AC55)</f>
-        <v>309.05000000000001</v>
+        <v>83.079999999999998</v>
+      </c>
+      <c r="W55" s="16">
+        <v>84.099999999999994</v>
+      </c>
+      <c r="X55" s="16">
+        <v>84.680000000000007</v>
+      </c>
+      <c r="Y55" s="16">
+        <v>85.209999999999994</v>
+      </c>
+      <c r="Z55" s="16">
+        <v>85.209999999999994</v>
+      </c>
+      <c r="AA55" s="16">
+        <v>85.150000000000006</v>
+      </c>
+      <c r="AB55" s="16">
+        <v>85.040000000000006</v>
+      </c>
+      <c r="AC55" s="17">
+        <v>109.84999999999999</v>
+      </c>
+      <c r="AD55" s="16">
+        <v>89.950000000000003</v>
+      </c>
+      <c r="AE55" s="19">
+        <f>MIN(C55:AD55)</f>
+        <v>81.689999999999998</v>
       </c>
       <c r="AF55" s="20">
-        <f>AVERAGE(C55:AC55)</f>
-        <v>306.06041666666675</v>
+        <f>MAX(C55:AD55)</f>
+        <v>109.84999999999999</v>
       </c>
       <c r="AG55" s="20">
-        <f>AVERAGE(Q55:AC55)</f>
-        <v>303.53076923076929</v>
-      </c>
-      <c r="AH55" s="21">
-        <f>(AG55/AF55)-1</f>
-        <v>-8.265189806143769e-003</v>
+        <f>AVERAGE(C55:AD55)</f>
+        <v>88.665833333333353</v>
+      </c>
+      <c r="AH55" s="20">
+        <f>AVERAGE(Q55:AD55)</f>
+        <v>87.382857142857148</v>
       </c>
       <c r="AI55" s="21">
-        <f>(AG55/AD55)-1</f>
-        <v>1.5832561013284119e-002</v>
+        <f>(AH55/AG55)-1</f>
+        <v>-1.4469792277854499e-002</v>
       </c>
       <c r="AJ55" s="21">
-        <f>(AE55/AD55)-1</f>
-        <v>3.4303882195448443e-002</v>
-      </c>
-      <c r="AK55" s="22" t="s">
+        <f>(AH55/AE55)-1</f>
+        <v>6.968854379798195e-002</v>
+      </c>
+      <c r="AK55" s="21">
+        <f>(AF55/AE55)-1</f>
+        <v>0.34471783572040637</v>
+      </c>
+      <c r="AL55" s="1" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="56" ht="18">
       <c r="A56" s="2" t="s">
-        <v>125</v>
+        <v>165</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C56" s="16"/>
       <c r="D56" s="16"/>
       <c r="E56" s="16"/>
-      <c r="F56" s="16"/>
+      <c r="F56" s="16">
+        <v>309.05000000000001</v>
+      </c>
       <c r="G56" s="16">
-        <v>108.98999999999999</v>
+        <v>309.05000000000001</v>
       </c>
       <c r="H56" s="16">
-        <v>108.98999999999999</v>
+        <v>309.05000000000001</v>
       </c>
       <c r="I56" s="16">
-        <v>108.98999999999999</v>
+        <v>309.05000000000001</v>
       </c>
       <c r="J56" s="16">
-        <v>108.98999999999999</v>
+        <v>309.05000000000001</v>
       </c>
       <c r="K56" s="16">
-        <v>108.98999999999999</v>
+        <v>309.05000000000001</v>
       </c>
       <c r="L56" s="16">
-        <v>108.98999999999999</v>
+        <v>309.05000000000001</v>
       </c>
       <c r="M56" s="16">
-        <v>108.98999999999999</v>
+        <v>309.05000000000001</v>
       </c>
       <c r="N56" s="16">
-        <v>108.98999999999999</v>
+        <v>309.05000000000001</v>
       </c>
       <c r="O56" s="16">
-        <v>108.98999999999999</v>
+        <v>309.05000000000001</v>
       </c>
       <c r="P56" s="16">
-        <v>108.98999999999999</v>
+        <v>309.05000000000001</v>
       </c>
       <c r="Q56" s="16">
-        <v>108.98999999999999</v>
+        <v>309.05000000000001</v>
       </c>
       <c r="R56" s="16">
-        <v>108.98999999999999</v>
+        <v>309.05000000000001</v>
       </c>
       <c r="S56" s="16">
-        <v>108.98999999999999</v>
+        <v>309.05000000000001</v>
       </c>
       <c r="T56" s="16">
-        <v>108.98999999999999</v>
+        <v>309.05000000000001</v>
       </c>
       <c r="U56" s="16">
-        <v>108.98999999999999</v>
+        <v>309.05000000000001</v>
       </c>
       <c r="V56" s="16">
-        <v>108.98999999999999</v>
-      </c>
-      <c r="W56" s="16">
-        <v>108.98999999999999</v>
-      </c>
-      <c r="X56" s="16">
-        <v>108.98999999999999</v>
-      </c>
-      <c r="Y56" s="24">
-        <v>100.44</v>
-      </c>
-      <c r="Z56" s="24">
-        <v>100.44</v>
-      </c>
-      <c r="AA56" s="24">
-        <v>100.44</v>
-      </c>
-      <c r="AB56" s="24">
-        <v>100.44</v>
-      </c>
-      <c r="AC56" s="24">
-        <v>100.44</v>
-      </c>
-      <c r="AD56" s="19">
-        <f>MIN(C56:AC56)</f>
-        <v>100.44</v>
-      </c>
-      <c r="AE56" s="20">
-        <f>MAX(C56:AC56)</f>
-        <v>108.98999999999999</v>
+        <v>309.05000000000001</v>
+      </c>
+      <c r="W56" s="33">
+        <v>298.80000000000001</v>
+      </c>
+      <c r="X56" s="33">
+        <v>298.80000000000001</v>
+      </c>
+      <c r="Y56" s="33">
+        <v>298.80000000000001</v>
+      </c>
+      <c r="Z56" s="33">
+        <v>298.80000000000001</v>
+      </c>
+      <c r="AA56" s="33">
+        <v>298.80000000000001</v>
+      </c>
+      <c r="AB56" s="33">
+        <v>298.80000000000001</v>
+      </c>
+      <c r="AC56" s="33">
+        <v>298.80000000000001</v>
+      </c>
+      <c r="AD56" s="33">
+        <v>298.80000000000001</v>
+      </c>
+      <c r="AE56" s="19">
+        <f>MIN(C56:AD56)</f>
+        <v>298.80000000000001</v>
       </c>
       <c r="AF56" s="20">
-        <f>AVERAGE(C56:AC56)</f>
-        <v>107.13130434782609</v>
+        <f>MAX(C56:AD56)</f>
+        <v>309.05000000000001</v>
       </c>
       <c r="AG56" s="20">
-        <f>AVERAGE(Q56:AC56)</f>
-        <v>105.70153846153848</v>
-      </c>
-      <c r="AH56" s="21">
-        <f>(AG56/AF56)-1</f>
-        <v>-1.3345920643750842e-002</v>
+        <f>AVERAGE(C56:AD56)</f>
+        <v>305.7700000000001</v>
+      </c>
+      <c r="AH56" s="20">
+        <f>AVERAGE(Q56:AD56)</f>
+        <v>303.19285714285718</v>
       </c>
       <c r="AI56" s="21">
-        <f>(AG56/AD56)-1</f>
-        <v>5.2384891094568786e-002</v>
+        <f>(AH56/AG56)-1</f>
+        <v>-8.4283705306044121e-003</v>
       </c>
       <c r="AJ56" s="21">
-        <f>(AE56/AD56)-1</f>
-        <v>8.5125448028673834e-002</v>
-      </c>
-      <c r="AK56" s="37" t="s">
-        <v>166</v>
+        <f>(AH56/AE56)-1</f>
+        <v>1.4701663798049491e-002</v>
+      </c>
+      <c r="AK56" s="21">
+        <f>(AF56/AE56)-1</f>
+        <v>3.4303882195448443e-002</v>
+      </c>
+      <c r="AL56" s="22" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="57" ht="18">
+      <c r="A57" s="2" t="s">
+        <v>128</v>
+      </c>
       <c r="B57" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
+      </c>
+      <c r="C57" s="16"/>
+      <c r="D57" s="16"/>
+      <c r="E57" s="16"/>
+      <c r="F57" s="16"/>
+      <c r="G57" s="16">
+        <v>108.98999999999999</v>
+      </c>
+      <c r="H57" s="16">
+        <v>108.98999999999999</v>
+      </c>
+      <c r="I57" s="16">
+        <v>108.98999999999999</v>
+      </c>
+      <c r="J57" s="16">
+        <v>108.98999999999999</v>
+      </c>
+      <c r="K57" s="16">
+        <v>108.98999999999999</v>
+      </c>
+      <c r="L57" s="16">
+        <v>108.98999999999999</v>
+      </c>
+      <c r="M57" s="16">
+        <v>108.98999999999999</v>
+      </c>
+      <c r="N57" s="16">
+        <v>108.98999999999999</v>
       </c>
       <c r="O57" s="16">
+        <v>108.98999999999999</v>
+      </c>
+      <c r="P57" s="16">
+        <v>108.98999999999999</v>
+      </c>
+      <c r="Q57" s="16">
+        <v>108.98999999999999</v>
+      </c>
+      <c r="R57" s="16">
+        <v>108.98999999999999</v>
+      </c>
+      <c r="S57" s="16">
+        <v>108.98999999999999</v>
+      </c>
+      <c r="T57" s="16">
+        <v>108.98999999999999</v>
+      </c>
+      <c r="U57" s="16">
+        <v>108.98999999999999</v>
+      </c>
+      <c r="V57" s="16">
+        <v>108.98999999999999</v>
+      </c>
+      <c r="W57" s="16">
+        <v>108.98999999999999</v>
+      </c>
+      <c r="X57" s="16">
+        <v>108.98999999999999</v>
+      </c>
+      <c r="Y57" s="24">
+        <v>100.44</v>
+      </c>
+      <c r="Z57" s="24">
+        <v>100.44</v>
+      </c>
+      <c r="AA57" s="24">
+        <v>100.44</v>
+      </c>
+      <c r="AB57" s="24">
+        <v>100.44</v>
+      </c>
+      <c r="AC57" s="16">
+        <v>108.98999999999999</v>
+      </c>
+      <c r="AD57" s="16">
+        <v>108.98999999999999</v>
+      </c>
+      <c r="AE57" s="19">
+        <f>MIN(C57:AD57)</f>
+        <v>100.44</v>
+      </c>
+      <c r="AF57" s="20">
+        <f>MAX(C57:AD57)</f>
+        <v>108.98999999999999</v>
+      </c>
+      <c r="AG57" s="20">
+        <f>AVERAGE(C57:AD57)</f>
+        <v>107.56499999999998</v>
+      </c>
+      <c r="AH57" s="20">
+        <f>AVERAGE(Q57:AD57)</f>
+        <v>106.54714285714286</v>
+      </c>
+      <c r="AI57" s="21">
+        <f>(AH57/AG57)-1</f>
+        <v>-9.4627168954318774e-003</v>
+      </c>
+      <c r="AJ57" s="21">
+        <f>(AH57/AE57)-1</f>
+        <v>6.0803891449052738e-002</v>
+      </c>
+      <c r="AK57" s="21">
+        <f>(AF57/AE57)-1</f>
+        <v>8.5125448028673834e-002</v>
+      </c>
+      <c r="AL57" s="37" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="58" ht="18">
+      <c r="B58" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="O58" s="16">
         <v>1.49</v>
       </c>
-      <c r="P57" s="16">
+      <c r="P58" s="16">
         <v>1.49</v>
       </c>
-      <c r="Q57" s="16">
+      <c r="Q58" s="16">
         <v>1.49</v>
       </c>
-      <c r="R57" s="16">
+      <c r="R58" s="16">
         <v>1.49</v>
       </c>
-      <c r="S57" s="16">
+      <c r="S58" s="16">
         <v>1.49</v>
       </c>
-      <c r="T57" s="16">
+      <c r="T58" s="16">
         <v>1.99</v>
       </c>
-      <c r="U57" s="16">
+      <c r="U58" s="16">
         <v>1.99</v>
       </c>
-      <c r="V57" s="16">
+      <c r="V58" s="16">
         <v>1.99</v>
       </c>
-      <c r="W57" s="16">
+      <c r="W58" s="16">
         <v>1.99</v>
       </c>
-      <c r="X57" s="16">
+      <c r="X58" s="16">
         <v>1.99</v>
       </c>
-      <c r="Y57" s="16">
+      <c r="Y58" s="16">
         <v>1.99</v>
       </c>
-      <c r="Z57" s="16">
+      <c r="Z58" s="16">
         <v>1.99</v>
       </c>
-      <c r="AA57" s="16">
+      <c r="AA58" s="16">
         <v>1.99</v>
       </c>
-      <c r="AB57" s="16">
+      <c r="AB58" s="16">
         <v>1.99</v>
       </c>
-      <c r="AC57" s="16">
+      <c r="AC58" s="16">
         <v>1.99</v>
       </c>
-      <c r="AD57" s="19">
-        <f>MIN(C57:AC57)</f>
+      <c r="AD58" s="16">
+        <v>1.99</v>
+      </c>
+      <c r="AE58" s="19">
+        <f>MIN(C58:AD58)</f>
         <v>1.49</v>
       </c>
-      <c r="AE57" s="20">
-        <f>MAX(C57:AC57)</f>
+      <c r="AF58" s="20">
+        <f>MAX(C58:AD58)</f>
         <v>1.99</v>
       </c>
-      <c r="AF57" s="20">
-        <f>AVERAGE(C57:AC57)</f>
-        <v>1.8233333333333328</v>
-      </c>
-      <c r="AG57" s="20">
-        <f>AVERAGE(Q57:AC57)</f>
-        <v>1.8746153846153841</v>
-      </c>
-      <c r="AH57" s="21">
-        <f>(AG57/AF57)-1</f>
-        <v>2.8125439459991686e-002</v>
-      </c>
-      <c r="AI57" s="21">
-        <f>(AG57/AD57)-1</f>
-        <v>0.25813113061435167</v>
-      </c>
-      <c r="AJ57" s="21">
-        <f>(AE57/AD57)-1</f>
+      <c r="AG58" s="20">
+        <f>AVERAGE(C58:AD58)</f>
+        <v>1.8337499999999993</v>
+      </c>
+      <c r="AH58" s="20">
+        <f>AVERAGE(Q58:AD58)</f>
+        <v>1.8828571428571423</v>
+      </c>
+      <c r="AI58" s="21">
+        <f>(AH58/AG58)-1</f>
+        <v>2.6779628006621925e-002</v>
+      </c>
+      <c r="AJ58" s="21">
+        <f>(AH58/AE58)-1</f>
+        <v>0.2636625119846594</v>
+      </c>
+      <c r="AK58" s="21">
+        <f>(AF58/AE58)-1</f>
         <v>0.33557046979865768</v>
       </c>
-    </row>
-    <row r="58" ht="14.25">
-      <c r="AA58" s="1"/>
-      <c r="AB58" s="1"/>
-      <c r="AC58" s="1"/>
-      <c r="AD58" s="2"/>
-      <c r="AE58" s="2"/>
-      <c r="AF58" s="2"/>
-      <c r="AG58" s="2"/>
-      <c r="AH58" s="2"/>
-      <c r="AI58" s="2"/>
-      <c r="AJ58" s="2"/>
     </row>
     <row r="59" ht="14.25">
       <c r="AA59" s="1"/>
       <c r="AB59" s="1"/>
       <c r="AC59" s="1"/>
-      <c r="AD59" s="2"/>
+      <c r="AD59" s="1"/>
       <c r="AE59" s="2"/>
       <c r="AF59" s="2"/>
       <c r="AG59" s="2"/>
       <c r="AH59" s="2"/>
       <c r="AI59" s="2"/>
       <c r="AJ59" s="2"/>
+      <c r="AK59" s="2"/>
     </row>
     <row r="60" ht="14.25">
       <c r="AA60" s="1"/>
       <c r="AB60" s="1"/>
       <c r="AC60" s="1"/>
-      <c r="AD60" s="2"/>
+      <c r="AD60" s="1"/>
       <c r="AE60" s="2"/>
       <c r="AF60" s="2"/>
       <c r="AG60" s="2"/>
       <c r="AH60" s="2"/>
       <c r="AI60" s="2"/>
       <c r="AJ60" s="2"/>
+      <c r="AK60" s="2"/>
     </row>
     <row r="61" ht="14.25">
       <c r="AA61" s="1"/>
       <c r="AB61" s="1"/>
       <c r="AC61" s="1"/>
-      <c r="AD61" s="2"/>
+      <c r="AD61" s="1"/>
       <c r="AE61" s="2"/>
       <c r="AF61" s="2"/>
       <c r="AG61" s="2"/>
       <c r="AH61" s="2"/>
       <c r="AI61" s="2"/>
       <c r="AJ61" s="2"/>
+      <c r="AK61" s="2"/>
+    </row>
+    <row r="62" ht="14.25">
+      <c r="AA62" s="1"/>
+      <c r="AB62" s="1"/>
+      <c r="AC62" s="1"/>
+      <c r="AD62" s="1"/>
+      <c r="AE62" s="2"/>
+      <c r="AF62" s="2"/>
+      <c r="AG62" s="2"/>
+      <c r="AH62" s="2"/>
+      <c r="AI62" s="2"/>
+      <c r="AJ62" s="2"/>
+      <c r="AK62" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="AD1:AD2"/>
     <mergeCell ref="AE1:AE2"/>
     <mergeCell ref="AF1:AF2"/>
     <mergeCell ref="AG1:AG2"/>
     <mergeCell ref="AH1:AH2"/>
     <mergeCell ref="AI1:AI2"/>
     <mergeCell ref="AJ1:AJ2"/>
+    <mergeCell ref="AK1:AK2"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="AK4"/>
-    <hyperlink r:id="rId2" ref="AK5"/>
-    <hyperlink r:id="rId3" ref="AK6"/>
-    <hyperlink r:id="rId4" ref="AK7"/>
-    <hyperlink r:id="rId5" ref="AK8"/>
-    <hyperlink r:id="rId6" ref="AK9"/>
-    <hyperlink r:id="rId7" ref="AK10"/>
-    <hyperlink r:id="rId8" ref="AK11"/>
-    <hyperlink r:id="rId9" ref="AK12"/>
-    <hyperlink r:id="rId10" ref="AK13"/>
-    <hyperlink r:id="rId11" ref="AK14"/>
-    <hyperlink r:id="rId12" ref="AK15"/>
-    <hyperlink r:id="rId13" ref="AK16"/>
-    <hyperlink r:id="rId14" ref="AK17"/>
-    <hyperlink r:id="rId15" ref="AK18"/>
-    <hyperlink r:id="rId16" ref="AK19"/>
-    <hyperlink r:id="rId17" ref="AK20"/>
-    <hyperlink r:id="rId18" ref="AK21"/>
-    <hyperlink r:id="rId19" ref="AK22"/>
-    <hyperlink r:id="rId20" ref="AK23"/>
-    <hyperlink r:id="rId21" ref="AK24"/>
-    <hyperlink r:id="rId22" ref="AK25"/>
-    <hyperlink r:id="rId23" ref="AK26"/>
-    <hyperlink r:id="rId24" ref="AK27"/>
-    <hyperlink r:id="rId25" ref="AK28"/>
-    <hyperlink r:id="rId26" ref="AK29"/>
-    <hyperlink r:id="rId27" ref="AK30"/>
-    <hyperlink r:id="rId28" ref="AK31"/>
-    <hyperlink r:id="rId29" ref="AK32"/>
-    <hyperlink r:id="rId30" ref="AK33"/>
-    <hyperlink r:id="rId31" ref="AK34"/>
-    <hyperlink r:id="rId32" ref="AK35"/>
-    <hyperlink r:id="rId33" ref="AK36"/>
-    <hyperlink r:id="rId34" ref="AK37"/>
-    <hyperlink r:id="rId35" ref="AK38"/>
-    <hyperlink r:id="rId36" ref="AK39"/>
-    <hyperlink r:id="rId37" ref="AK40"/>
-    <hyperlink r:id="rId37" ref="AK41"/>
-    <hyperlink r:id="rId37" ref="AK42"/>
-    <hyperlink r:id="rId37" ref="AK43"/>
-    <hyperlink r:id="rId37" ref="AK44"/>
-    <hyperlink r:id="rId37" ref="AK45"/>
-    <hyperlink r:id="rId38" ref="AK47"/>
-    <hyperlink r:id="rId39" ref="AK48"/>
-    <hyperlink r:id="rId40" ref="AK49"/>
-    <hyperlink r:id="rId41" ref="AK50"/>
-    <hyperlink r:id="rId42" ref="AK51"/>
-    <hyperlink r:id="rId43" ref="AK53"/>
-    <hyperlink r:id="rId44" ref="AK55"/>
-    <hyperlink r:id="rId45" ref="AK56"/>
+    <hyperlink r:id="rId1" ref="AL4"/>
+    <hyperlink r:id="rId2" ref="AL5"/>
+    <hyperlink r:id="rId3" ref="AL6"/>
+    <hyperlink r:id="rId4" ref="AL7"/>
+    <hyperlink r:id="rId5" ref="AL8"/>
+    <hyperlink r:id="rId6" ref="AL9"/>
+    <hyperlink r:id="rId7" ref="AL10"/>
+    <hyperlink r:id="rId8" ref="AL11"/>
+    <hyperlink r:id="rId9" ref="AL12"/>
+    <hyperlink r:id="rId10" ref="AL13"/>
+    <hyperlink r:id="rId11" ref="AL14"/>
+    <hyperlink r:id="rId12" ref="AL15"/>
+    <hyperlink r:id="rId13" ref="AL16"/>
+    <hyperlink r:id="rId14" ref="AL17"/>
+    <hyperlink r:id="rId15" ref="AL18"/>
+    <hyperlink r:id="rId16" ref="AL19"/>
+    <hyperlink r:id="rId17" ref="AL20"/>
+    <hyperlink r:id="rId18" ref="AL21"/>
+    <hyperlink r:id="rId19" ref="AL22"/>
+    <hyperlink r:id="rId20" ref="AL23"/>
+    <hyperlink r:id="rId21" ref="AL24"/>
+    <hyperlink r:id="rId22" ref="AL25"/>
+    <hyperlink r:id="rId23" ref="AL26"/>
+    <hyperlink r:id="rId24" ref="AL27"/>
+    <hyperlink r:id="rId25" ref="AL28"/>
+    <hyperlink r:id="rId26" ref="AL29"/>
+    <hyperlink r:id="rId27" ref="AL30"/>
+    <hyperlink r:id="rId28" ref="AL31"/>
+    <hyperlink r:id="rId29" ref="AL32"/>
+    <hyperlink r:id="rId30" ref="AL33"/>
+    <hyperlink r:id="rId31" ref="AL34"/>
+    <hyperlink r:id="rId32" ref="AL35"/>
+    <hyperlink r:id="rId33" ref="AL36"/>
+    <hyperlink r:id="rId34" ref="AL37"/>
+    <hyperlink r:id="rId35" ref="AL38"/>
+    <hyperlink r:id="rId36" ref="AL39"/>
+    <hyperlink r:id="rId37" ref="AL40"/>
+    <hyperlink r:id="rId38" ref="AL41"/>
+    <hyperlink r:id="rId38" ref="AL42"/>
+    <hyperlink r:id="rId38" ref="AL43"/>
+    <hyperlink r:id="rId38" ref="AL44"/>
+    <hyperlink r:id="rId38" ref="AL45"/>
+    <hyperlink r:id="rId38" ref="AL46"/>
+    <hyperlink r:id="rId39" ref="AL48"/>
+    <hyperlink r:id="rId40" ref="AL49"/>
+    <hyperlink r:id="rId41" ref="AL50"/>
+    <hyperlink r:id="rId42" ref="AL51"/>
+    <hyperlink r:id="rId43" ref="AL52"/>
+    <hyperlink r:id="rId44" ref="AL54"/>
+    <hyperlink r:id="rId45" ref="AL56"/>
+    <hyperlink r:id="rId46" ref="AL57"/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.25196850393700787" right="0.25196850393700787" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>

--- a/analyse-prix-composants.xlsx
+++ b/analyse-prix-composants.xlsx
@@ -10,7 +10,7 @@
   </sheets>
   <definedNames>
     <definedName name="Print_Titles" localSheetId="0">Feuille1!$3:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Feuille1!$A$1:$AK$58</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Feuille1!$A$1:$AL$58</definedName>
   </definedNames>
   <calcPr/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="172">
   <si>
     <t xml:space="preserve">Le prix des composants IT</t>
   </si>
@@ -142,6 +142,9 @@
   </si>
   <si>
     <t xml:space="preserve">9 mai 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 mai 2026</t>
   </si>
   <si>
     <t>Min</t>
@@ -1412,12 +1415,12 @@
     <col bestFit="1" min="12" max="12" style="4" width="11.7109375"/>
     <col bestFit="1" min="13" max="13" style="4" width="13.00390625"/>
     <col bestFit="1" min="14" max="15" style="4" width="14.140625"/>
-    <col customWidth="1" min="16" max="30" style="1" width="12.7109375"/>
-    <col customWidth="1" min="31" max="34" style="2" width="12.7109375"/>
-    <col customWidth="1" min="35" max="35" style="2" width="14.140625"/>
-    <col customWidth="1" min="36" max="37" style="2" width="12.7109375"/>
-    <col customWidth="1" min="38" max="38" style="5" width="42.28125"/>
-    <col min="39" max="16384" style="1" width="9.140625"/>
+    <col customWidth="1" min="16" max="31" style="1" width="12.7109375"/>
+    <col customWidth="1" min="32" max="35" style="2" width="12.7109375"/>
+    <col customWidth="1" min="36" max="36" style="2" width="14.140625"/>
+    <col customWidth="1" min="37" max="38" style="2" width="12.7109375"/>
+    <col customWidth="1" min="39" max="39" style="5" width="42.28125"/>
+    <col min="40" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" ht="57.75" customHeight="1">
@@ -1440,28 +1443,29 @@
       <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
       <c r="AD1" s="1"/>
-      <c r="AE1" s="7" t="s">
+      <c r="AE1" s="1"/>
+      <c r="AF1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="AF1" s="7" t="s">
+      <c r="AG1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="AG1" s="7" t="s">
+      <c r="AH1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="AH1" s="7" t="s">
+      <c r="AI1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="AI1" s="7" t="s">
+      <c r="AJ1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="AJ1" s="7" t="s">
+      <c r="AK1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="AK1" s="7" t="s">
+      <c r="AL1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="AL1" s="5"/>
+      <c r="AM1" s="5"/>
     </row>
     <row r="2" ht="39.75" customHeight="1">
       <c r="A2" s="2"/>
@@ -1483,13 +1487,14 @@
       <c r="AB2" s="1"/>
       <c r="AC2" s="1"/>
       <c r="AD2" s="1"/>
-      <c r="AE2" s="7"/>
+      <c r="AE2" s="1"/>
       <c r="AF2" s="7"/>
       <c r="AG2" s="7"/>
       <c r="AH2" s="7"/>
       <c r="AI2" s="7"/>
       <c r="AJ2" s="7"/>
       <c r="AK2" s="7"/>
+      <c r="AL2" s="7"/>
     </row>
     <row r="3" ht="18">
       <c r="A3" s="9" t="s">
@@ -1582,7 +1587,7 @@
       <c r="AD3" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="AE3" s="12" t="s">
+      <c r="AE3" s="11" t="s">
         <v>39</v>
       </c>
       <c r="AF3" s="12" t="s">
@@ -1603,16 +1608,19 @@
       <c r="AK3" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="AL3" s="5" t="s">
+      <c r="AL3" s="12" t="s">
         <v>46</v>
+      </c>
+      <c r="AM3" s="5" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="4" ht="36">
       <c r="A4" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C4" s="14">
         <v>171.88</v>
@@ -1639,7 +1647,7 @@
         <v>341.57999999999998</v>
       </c>
       <c r="M4" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N4" s="17">
         <v>321.14999999999998</v>
@@ -1690,50 +1698,53 @@
         <v>450.54000000000002</v>
       </c>
       <c r="AD4" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="AE4" s="19">
-        <f>MIN(C4:AD4)</f>
+        <v>50</v>
+      </c>
+      <c r="AE4" s="18">
+        <v>425.05000000000001</v>
+      </c>
+      <c r="AF4" s="19">
+        <f>MIN(C4:AE4)</f>
         <v>171.88</v>
       </c>
-      <c r="AF4" s="20">
-        <f>MAX(C4:AD4)</f>
+      <c r="AG4" s="20">
+        <f>MAX(C4:AE4)</f>
         <v>450.54000000000002</v>
       </c>
-      <c r="AG4" s="20">
-        <f>AVERAGE(C4:AD4)</f>
-        <v>360.5704347826088</v>
-      </c>
       <c r="AH4" s="20">
-        <f>AVERAGE(Q4:AD4)</f>
-        <v>393.24846153846153</v>
-      </c>
-      <c r="AI4" s="21">
-        <f>(AH4/AG4)-1</f>
-        <v>9.0628691660631144e-002</v>
+        <f>AVERAGE(C4:AE4)</f>
+        <v>363.25708333333341</v>
+      </c>
+      <c r="AI4" s="20">
+        <f>AVERAGE(Q4:AE4)</f>
+        <v>395.51999999999998</v>
       </c>
       <c r="AJ4" s="21">
-        <f>(AH4/AE4)-1</f>
-        <v>1.2879244911476699</v>
+        <f>(AI4/AH4)-1</f>
+        <v>8.8815657414342386e-002</v>
       </c>
       <c r="AK4" s="21">
-        <f>(AF4/AE4)-1</f>
+        <f>(AI4/AF4)-1</f>
+        <v>1.3011403304631139</v>
+      </c>
+      <c r="AL4" s="21">
+        <f>(AG4/AF4)-1</f>
         <v>1.6212473818943449</v>
       </c>
-      <c r="AL4" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="AM4" s="23">
+      <c r="AM4" s="22" t="s">
+        <v>51</v>
+      </c>
+      <c r="AN4" s="23">
         <f>C2*1</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" ht="36">
       <c r="A5" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C5" s="15"/>
       <c r="D5" s="24">
@@ -1745,7 +1756,7 @@
         <v>686</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I5" s="16">
         <v>613.99000000000001</v>
@@ -1813,44 +1824,47 @@
       <c r="AD5" s="17">
         <v>978.75</v>
       </c>
-      <c r="AE5" s="19">
-        <f>MIN(C5:AD5)</f>
+      <c r="AE5" s="17">
+        <v>978.75</v>
+      </c>
+      <c r="AF5" s="19">
+        <f>MIN(C5:AE5)</f>
         <v>200.47999999999999</v>
       </c>
-      <c r="AF5" s="20">
-        <f>MAX(C5:AD5)</f>
+      <c r="AG5" s="20">
+        <f>MAX(C5:AE5)</f>
         <v>978.75</v>
       </c>
-      <c r="AG5" s="20">
-        <f>AVERAGE(C5:AD5)</f>
-        <v>845.25500000000011</v>
-      </c>
       <c r="AH5" s="20">
-        <f>AVERAGE(Q5:AD5)</f>
-        <v>923.42500000000007</v>
-      </c>
-      <c r="AI5" s="21">
-        <f>(AH5/AG5)-1</f>
-        <v>9.2480967282062787e-002</v>
+        <f>AVERAGE(C5:AE5)</f>
+        <v>850.59480000000008</v>
+      </c>
+      <c r="AI5" s="20">
+        <f>AVERAGE(Q5:AE5)</f>
+        <v>927.11333333333334</v>
       </c>
       <c r="AJ5" s="21">
-        <f>(AH5/AE5)-1</f>
-        <v>3.6060704309656826</v>
+        <f>(AI5/AH5)-1</f>
+        <v>8.9958853890634183e-002</v>
       </c>
       <c r="AK5" s="21">
-        <f>(AF5/AE5)-1</f>
+        <f>(AI5/AF5)-1</f>
+        <v>3.6244679436020224</v>
+      </c>
+      <c r="AL5" s="21">
+        <f>(AG5/AF5)-1</f>
         <v>3.8820331205107745</v>
       </c>
-      <c r="AL5" s="22" t="s">
-        <v>52</v>
+      <c r="AM5" s="22" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="6" ht="36">
       <c r="A6" s="25" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C6" s="27"/>
       <c r="D6" s="24">
@@ -1930,44 +1944,47 @@
       <c r="AD6" s="17">
         <v>714.80999999999995</v>
       </c>
-      <c r="AE6" s="19">
-        <f>MIN(C6:AD6)</f>
+      <c r="AE6" s="17">
+        <v>710</v>
+      </c>
+      <c r="AF6" s="19">
+        <f>MIN(C6:AE6)</f>
         <v>284.13</v>
       </c>
-      <c r="AF6" s="20">
-        <f>MAX(C6:AD6)</f>
+      <c r="AG6" s="20">
+        <f>MAX(C6:AE6)</f>
         <v>717.78999999999996</v>
       </c>
-      <c r="AG6" s="20">
-        <f>AVERAGE(C6:AD6)</f>
-        <v>624.82159999999988</v>
-      </c>
       <c r="AH6" s="20">
-        <f>AVERAGE(Q6:AD6)</f>
-        <v>681.11928571428575</v>
-      </c>
-      <c r="AI6" s="21">
-        <f>(AH6/AG6)-1</f>
-        <v>9.0102015862265183e-002</v>
+        <f>AVERAGE(C6:AE6)</f>
+        <v>628.09769230769223</v>
+      </c>
+      <c r="AI6" s="20">
+        <f>AVERAGE(Q6:AE6)</f>
+        <v>683.04466666666667</v>
       </c>
       <c r="AJ6" s="21">
-        <f>(AH6/AE6)-1</f>
-        <v>1.3972100296142109</v>
+        <f>(AI6/AH6)-1</f>
+        <v>8.7481573379284194e-002</v>
       </c>
       <c r="AK6" s="21">
-        <f>(AF6/AE6)-1</f>
+        <f>(AI6/AF6)-1</f>
+        <v>1.4039864381327796</v>
+      </c>
+      <c r="AL6" s="21">
+        <f>(AG6/AF6)-1</f>
         <v>1.5262731848097699</v>
       </c>
-      <c r="AL6" s="22" t="s">
-        <v>54</v>
+      <c r="AM6" s="22" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="7" ht="36">
       <c r="A7" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C7" s="15"/>
       <c r="D7" s="15"/>
@@ -2041,44 +2058,47 @@
       <c r="AD7" s="18">
         <v>887.78999999999996</v>
       </c>
-      <c r="AE7" s="19">
-        <f>MIN(C7:AD7)</f>
+      <c r="AE7" s="18">
+        <v>823.61000000000001</v>
+      </c>
+      <c r="AF7" s="19">
+        <f>MIN(C7:AE7)</f>
         <v>685.71000000000004</v>
       </c>
-      <c r="AF7" s="20">
-        <f>MAX(C7:AD7)</f>
+      <c r="AG7" s="20">
+        <f>MAX(C7:AE7)</f>
         <v>887.78999999999996</v>
       </c>
-      <c r="AG7" s="20">
-        <f>AVERAGE(C7:AD7)</f>
-        <v>798.85818181818183</v>
-      </c>
       <c r="AH7" s="20">
-        <f>AVERAGE(Q7:AD7)</f>
-        <v>819.84928571428588</v>
-      </c>
-      <c r="AI7" s="21">
-        <f>(AH7/AG7)-1</f>
-        <v>2.6276383435579032e-002</v>
+        <f>AVERAGE(C7:AE7)</f>
+        <v>799.93434782608699</v>
+      </c>
+      <c r="AI7" s="20">
+        <f>AVERAGE(Q7:AE7)</f>
+        <v>820.10000000000025</v>
       </c>
       <c r="AJ7" s="21">
-        <f>(AH7/AE7)-1</f>
-        <v>0.19562101429800616</v>
+        <f>(AI7/AH7)-1</f>
+        <v>2.5209134010454326e-002</v>
       </c>
       <c r="AK7" s="21">
-        <f>(AF7/AE7)-1</f>
+        <f>(AI7/AF7)-1</f>
+        <v>0.1959866415831768</v>
+      </c>
+      <c r="AL7" s="21">
+        <f>(AG7/AF7)-1</f>
         <v>0.29470184188651172</v>
       </c>
-      <c r="AL7" s="22" t="s">
-        <v>56</v>
+      <c r="AM7" s="22" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="8" ht="18">
       <c r="A8" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C8" s="15"/>
       <c r="D8" s="16">
@@ -2158,45 +2178,48 @@
       <c r="AD8" s="17">
         <v>557.98000000000002</v>
       </c>
-      <c r="AE8" s="19">
-        <f>MIN(C8:AD8)</f>
+      <c r="AE8" s="17">
+        <v>591.88</v>
+      </c>
+      <c r="AF8" s="19">
+        <f>MIN(C8:AE8)</f>
         <v>465</v>
       </c>
-      <c r="AF8" s="20">
-        <f>MAX(C8:AD8)</f>
+      <c r="AG8" s="20">
+        <f>MAX(C8:AE8)</f>
         <v>623.12</v>
       </c>
-      <c r="AG8" s="20">
-        <f>AVERAGE(C8:AD8)</f>
-        <v>553.8775999999998</v>
-      </c>
       <c r="AH8" s="20">
-        <f>AVERAGE(Q8:AD8)</f>
-        <v>548.14428571428562</v>
-      </c>
-      <c r="AI8" s="21">
-        <f>(AH8/AG8)-1</f>
-        <v>-1.0351229740495405e-002</v>
+        <f>AVERAGE(C8:AE8)</f>
+        <v>555.33923076923054</v>
+      </c>
+      <c r="AI8" s="20">
+        <f>AVERAGE(Q8:AE8)</f>
+        <v>551.05999999999983</v>
       </c>
       <c r="AJ8" s="21">
-        <f>(AH8/AE8)-1</f>
-        <v>0.17880491551459277</v>
+        <f>(AI8/AH8)-1</f>
+        <v>-7.7056158328726587e-003</v>
       </c>
       <c r="AK8" s="21">
-        <f>(AF8/AE8)-1</f>
+        <f>(AI8/AF8)-1</f>
+        <v>0.18507526881720393</v>
+      </c>
+      <c r="AL8" s="21">
+        <f>(AG8/AF8)-1</f>
         <v>0.34004301075268817</v>
       </c>
-      <c r="AL8" s="22" t="s">
-        <v>59</v>
-      </c>
-      <c r="AM8" s="1"/>
+      <c r="AM8" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="AN8" s="1"/>
     </row>
     <row r="9" ht="18">
       <c r="A9" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C9" s="15"/>
       <c r="D9" s="16"/>
@@ -2274,44 +2297,47 @@
       <c r="AD9" s="17">
         <v>159.99000000000001</v>
       </c>
-      <c r="AE9" s="19">
-        <f>MIN(C9:AD9)</f>
+      <c r="AE9" s="17">
+        <v>159.99000000000001</v>
+      </c>
+      <c r="AF9" s="19">
+        <f>MIN(C9:AE9)</f>
         <v>122</v>
       </c>
-      <c r="AF9" s="20">
-        <f>MAX(C9:AD9)</f>
+      <c r="AG9" s="20">
+        <f>MAX(C9:AE9)</f>
         <v>169</v>
       </c>
-      <c r="AG9" s="20">
-        <f>AVERAGE(C9:AD9)</f>
-        <v>132.83291666666665</v>
-      </c>
       <c r="AH9" s="20">
-        <f>AVERAGE(Q9:AD9)</f>
-        <v>140.57071428571427</v>
-      </c>
-      <c r="AI9" s="21">
-        <f>(AH9/AG9)-1</f>
-        <v>5.8252109591668377e-002</v>
+        <f>AVERAGE(C9:AE9)</f>
+        <v>133.91919999999999</v>
+      </c>
+      <c r="AI9" s="20">
+        <f>AVERAGE(Q9:AE9)</f>
+        <v>141.86533333333333</v>
       </c>
       <c r="AJ9" s="21">
-        <f>(AH9/AE9)-1</f>
-        <v>0.15221896955503511</v>
+        <f>(AI9/AH9)-1</f>
+        <v>5.9335280776269039e-002</v>
       </c>
       <c r="AK9" s="21">
-        <f>(AF9/AE9)-1</f>
+        <f>(AI9/AF9)-1</f>
+        <v>0.16283060109289615</v>
+      </c>
+      <c r="AL9" s="21">
+        <f>(AG9/AF9)-1</f>
         <v>0.38524590163934436</v>
       </c>
-      <c r="AL9" s="29" t="s">
-        <v>62</v>
+      <c r="AM9" s="29" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="10" ht="18">
       <c r="A10" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C10" s="15"/>
       <c r="D10" s="16"/>
@@ -2347,44 +2373,47 @@
       <c r="AD10" s="16">
         <v>349</v>
       </c>
-      <c r="AE10" s="19">
-        <f>MIN(C10:AD10)</f>
+      <c r="AE10" s="24">
+        <v>306.94</v>
+      </c>
+      <c r="AF10" s="19">
+        <f>MIN(C10:AE10)</f>
+        <v>306.94</v>
+      </c>
+      <c r="AG10" s="20">
+        <f>MAX(C10:AE10)</f>
         <v>349</v>
       </c>
-      <c r="AF10" s="20">
-        <f>MAX(C10:AD10)</f>
-        <v>349</v>
-      </c>
-      <c r="AG10" s="20">
-        <f>AVERAGE(C10:AD10)</f>
-        <v>349</v>
-      </c>
       <c r="AH10" s="20">
-        <f>AVERAGE(Q10:AD10)</f>
-        <v>349</v>
-      </c>
-      <c r="AI10" s="21">
-        <f>(AH10/AG10)-1</f>
+        <f>AVERAGE(C10:AE10)</f>
+        <v>338.48500000000001</v>
+      </c>
+      <c r="AI10" s="20">
+        <f>AVERAGE(Q10:AE10)</f>
+        <v>338.48500000000001</v>
+      </c>
+      <c r="AJ10" s="21">
+        <f>(AI10/AH10)-1</f>
         <v>0</v>
       </c>
-      <c r="AJ10" s="21">
-        <f>(AH10/AE10)-1</f>
-        <v>0</v>
-      </c>
       <c r="AK10" s="21">
-        <f>(AF10/AE10)-1</f>
-        <v>0</v>
-      </c>
-      <c r="AL10" s="29" t="s">
-        <v>64</v>
+        <f>(AI10/AF10)-1</f>
+        <v>0.10277252883299681</v>
+      </c>
+      <c r="AL10" s="21">
+        <f>(AG10/AF10)-1</f>
+        <v>0.13703003844399553</v>
+      </c>
+      <c r="AM10" s="29" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="11" ht="18">
       <c r="A11" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C11" s="15"/>
       <c r="D11" s="16"/>
@@ -2420,44 +2449,47 @@
       <c r="AD11" s="16">
         <v>467</v>
       </c>
-      <c r="AE11" s="19">
-        <f>MIN(C11:AD11)</f>
+      <c r="AE11" s="16">
+        <v>467.06999999999999</v>
+      </c>
+      <c r="AF11" s="19">
+        <f>MIN(C11:AE11)</f>
         <v>467</v>
       </c>
-      <c r="AF11" s="20">
-        <f>MAX(C11:AD11)</f>
+      <c r="AG11" s="20">
+        <f>MAX(C11:AE11)</f>
         <v>515</v>
       </c>
-      <c r="AG11" s="20">
-        <f>AVERAGE(C11:AD11)</f>
-        <v>483</v>
-      </c>
       <c r="AH11" s="20">
-        <f>AVERAGE(Q11:AD11)</f>
-        <v>483</v>
-      </c>
-      <c r="AI11" s="21">
-        <f>(AH11/AG11)-1</f>
+        <f>AVERAGE(C11:AE11)</f>
+        <v>479.01749999999998</v>
+      </c>
+      <c r="AI11" s="20">
+        <f>AVERAGE(Q11:AE11)</f>
+        <v>479.01749999999998</v>
+      </c>
+      <c r="AJ11" s="21">
+        <f>(AI11/AH11)-1</f>
         <v>0</v>
       </c>
-      <c r="AJ11" s="21">
-        <f>(AH11/AE11)-1</f>
-        <v>3.426124197002145e-002</v>
-      </c>
       <c r="AK11" s="21">
-        <f>(AF11/AE11)-1</f>
+        <f>(AI11/AF11)-1</f>
+        <v>2.5733404710920782e-002</v>
+      </c>
+      <c r="AL11" s="21">
+        <f>(AG11/AF11)-1</f>
         <v>0.10278372591006435</v>
       </c>
-      <c r="AL11" s="29" t="s">
-        <v>66</v>
+      <c r="AM11" s="29" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="12" ht="18">
       <c r="A12" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C12" s="15"/>
       <c r="D12" s="16"/>
@@ -2493,44 +2525,47 @@
       <c r="AD12" s="16">
         <v>165.13999999999999</v>
       </c>
-      <c r="AE12" s="19">
-        <f>MIN(C12:AD12)</f>
+      <c r="AE12" s="16">
+        <v>172.31999999999999</v>
+      </c>
+      <c r="AF12" s="19">
+        <f>MIN(C12:AE12)</f>
         <v>165.13999999999999</v>
       </c>
-      <c r="AF12" s="20">
-        <f>MAX(C12:AD12)</f>
+      <c r="AG12" s="20">
+        <f>MAX(C12:AE12)</f>
         <v>179.88999999999999</v>
       </c>
-      <c r="AG12" s="20">
-        <f>AVERAGE(C12:AD12)</f>
-        <v>172.95666666666668</v>
-      </c>
       <c r="AH12" s="20">
-        <f>AVERAGE(Q12:AD12)</f>
-        <v>172.95666666666668</v>
-      </c>
-      <c r="AI12" s="21">
-        <f>(AH12/AG12)-1</f>
+        <f>AVERAGE(C12:AE12)</f>
+        <v>172.79750000000001</v>
+      </c>
+      <c r="AI12" s="20">
+        <f>AVERAGE(Q12:AE12)</f>
+        <v>172.79750000000001</v>
+      </c>
+      <c r="AJ12" s="21">
+        <f>(AI12/AH12)-1</f>
         <v>0</v>
       </c>
-      <c r="AJ12" s="21">
-        <f>(AH12/AE12)-1</f>
-        <v>4.7333575552056972e-002</v>
-      </c>
       <c r="AK12" s="21">
-        <f>(AF12/AE12)-1</f>
+        <f>(AI12/AF12)-1</f>
+        <v>4.6369746881434137e-002</v>
+      </c>
+      <c r="AL12" s="21">
+        <f>(AG12/AF12)-1</f>
         <v>8.931815429332679e-002</v>
       </c>
-      <c r="AL12" s="29" t="s">
-        <v>68</v>
+      <c r="AM12" s="29" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="13" ht="36">
       <c r="A13" s="25" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C13" s="27"/>
       <c r="D13" s="24">
@@ -2566,19 +2601,19 @@
         <v>1084.8299999999999</v>
       </c>
       <c r="P13" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q13" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="R13" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="S13" s="30">
         <v>1426.5699999999999</v>
       </c>
       <c r="T13" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="U13" s="24">
         <v>592.17999999999995</v>
@@ -2593,61 +2628,64 @@
         <v>623.23000000000002</v>
       </c>
       <c r="Y13" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Z13" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AA13" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AB13" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AC13" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AD13" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="AE13" s="19">
-        <f>MIN(C13:AD13)</f>
+        <v>50</v>
+      </c>
+      <c r="AE13" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="AF13" s="19">
+        <f>MIN(C13:AE13)</f>
         <v>592.17999999999995</v>
       </c>
-      <c r="AF13" s="20">
-        <f>MAX(C13:AD13)</f>
+      <c r="AG13" s="20">
+        <f>MAX(C13:AE13)</f>
         <v>1426.5699999999999</v>
       </c>
-      <c r="AG13" s="20">
-        <f>AVERAGE(C13:AD13)</f>
+      <c r="AH13" s="20">
+        <f>AVERAGE(C13:AE13)</f>
         <v>853.96466666666674</v>
       </c>
-      <c r="AH13" s="20">
-        <f>AVERAGE(Q13:AD13)</f>
+      <c r="AI13" s="20">
+        <f>AVERAGE(Q13:AE13)</f>
         <v>771.42200000000003</v>
       </c>
-      <c r="AI13" s="21">
-        <f>(AH13/AG13)-1</f>
+      <c r="AJ13" s="21">
+        <f>(AI13/AH13)-1</f>
         <v>-9.665817555293077e-002</v>
       </c>
-      <c r="AJ13" s="21">
-        <f>(AH13/AE13)-1</f>
+      <c r="AK13" s="21">
+        <f>(AI13/AF13)-1</f>
         <v>0.30268161707588925</v>
       </c>
-      <c r="AK13" s="21">
-        <f>(AF13/AE13)-1</f>
+      <c r="AL13" s="21">
+        <f>(AG13/AF13)-1</f>
         <v>1.4090141511027054</v>
       </c>
-      <c r="AL13" s="22" t="s">
-        <v>71</v>
+      <c r="AM13" s="22" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="14" ht="18">
       <c r="A14" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C14" s="15"/>
       <c r="D14" s="15"/>
@@ -2719,44 +2757,47 @@
       <c r="AD14" s="17">
         <v>608.89999999999998</v>
       </c>
-      <c r="AE14" s="19">
-        <f>MIN(C14:AD14)</f>
+      <c r="AE14" s="16">
+        <v>597.99000000000001</v>
+      </c>
+      <c r="AF14" s="19">
+        <f>MIN(C14:AE14)</f>
         <v>580.98000000000002</v>
       </c>
-      <c r="AF14" s="20">
-        <f>MAX(C14:AD14)</f>
+      <c r="AG14" s="20">
+        <f>MAX(C14:AE14)</f>
         <v>709.99000000000001</v>
       </c>
-      <c r="AG14" s="20">
-        <f>AVERAGE(C14:AD14)</f>
-        <v>648.86142857142841</v>
-      </c>
       <c r="AH14" s="20">
-        <f>AVERAGE(Q14:AD14)</f>
-        <v>661.27142857142849</v>
-      </c>
-      <c r="AI14" s="21">
-        <f>(AH14/AG14)-1</f>
-        <v>1.9125809384790582e-002</v>
+        <f>AVERAGE(C14:AE14)</f>
+        <v>646.54909090909075</v>
+      </c>
+      <c r="AI14" s="20">
+        <f>AVERAGE(Q14:AE14)</f>
+        <v>657.0526666666666</v>
       </c>
       <c r="AJ14" s="21">
-        <f>(AH14/AE14)-1</f>
-        <v>0.13819998721372251</v>
+        <f>(AI14/AH14)-1</f>
+        <v>1.6245596668935214e-002</v>
       </c>
       <c r="AK14" s="21">
-        <f>(AF14/AE14)-1</f>
+        <f>(AI14/AF14)-1</f>
+        <v>0.13093852915189252</v>
+      </c>
+      <c r="AL14" s="21">
+        <f>(AG14/AF14)-1</f>
         <v>0.22205583668973117</v>
       </c>
-      <c r="AL14" s="22" t="s">
-        <v>73</v>
+      <c r="AM14" s="22" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="15" ht="18">
       <c r="A15" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C15" s="15"/>
       <c r="D15" s="15"/>
@@ -2828,44 +2869,47 @@
       <c r="AD15" s="16">
         <v>675.62</v>
       </c>
-      <c r="AE15" s="19">
-        <f>MIN(C15:AD15)</f>
+      <c r="AE15" s="16">
+        <v>675.62</v>
+      </c>
+      <c r="AF15" s="19">
+        <f>MIN(C15:AE15)</f>
         <v>622.63</v>
       </c>
-      <c r="AF15" s="20">
-        <f>MAX(C15:AD15)</f>
+      <c r="AG15" s="20">
+        <f>MAX(C15:AE15)</f>
         <v>728.61000000000001</v>
       </c>
-      <c r="AG15" s="20">
-        <f>AVERAGE(C15:AD15)</f>
-        <v>681.175238095238</v>
-      </c>
       <c r="AH15" s="20">
-        <f>AVERAGE(Q15:AD15)</f>
-        <v>688.55857142857155</v>
-      </c>
-      <c r="AI15" s="21">
-        <f>(AH15/AG15)-1</f>
-        <v>1.0839109997567542e-002</v>
+        <f>AVERAGE(C15:AE15)</f>
+        <v>680.92272727272723</v>
+      </c>
+      <c r="AI15" s="20">
+        <f>AVERAGE(Q15:AE15)</f>
+        <v>687.69600000000014</v>
       </c>
       <c r="AJ15" s="21">
-        <f>(AH15/AE15)-1</f>
-        <v>0.10588723869484529</v>
+        <f>(AI15/AH15)-1</f>
+        <v>9.9471973191460616e-003</v>
       </c>
       <c r="AK15" s="21">
-        <f>(AF15/AE15)-1</f>
+        <f>(AI15/AF15)-1</f>
+        <v>0.10450187109519327</v>
+      </c>
+      <c r="AL15" s="21">
+        <f>(AG15/AF15)-1</f>
         <v>0.17021344940012528</v>
       </c>
-      <c r="AL15" s="22" t="s">
-        <v>75</v>
+      <c r="AM15" s="22" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="16" ht="18">
       <c r="A16" s="25" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C16" s="27"/>
       <c r="D16" s="28"/>
@@ -2943,44 +2987,47 @@
       <c r="AD16" s="16">
         <v>10701.66</v>
       </c>
-      <c r="AE16" s="19">
-        <f>MIN(C16:AD16)</f>
+      <c r="AE16" s="16">
+        <v>10671.950000000001</v>
+      </c>
+      <c r="AF16" s="19">
+        <f>MIN(C16:AE16)</f>
         <v>9100</v>
       </c>
-      <c r="AF16" s="20">
-        <f>MAX(C16:AD16)</f>
+      <c r="AG16" s="20">
+        <f>MAX(C16:AE16)</f>
         <v>11315.18</v>
       </c>
-      <c r="AG16" s="20">
-        <f>AVERAGE(C16:AD16)</f>
-        <v>10032.992499999998</v>
-      </c>
       <c r="AH16" s="20">
-        <f>AVERAGE(Q16:AD16)</f>
-        <v>10671.627142857145</v>
-      </c>
-      <c r="AI16" s="21">
-        <f>(AH16/AG16)-1</f>
-        <v>6.3653455622252997e-002</v>
+        <f>AVERAGE(C16:AE16)</f>
+        <v>10058.550799999999</v>
+      </c>
+      <c r="AI16" s="20">
+        <f>AVERAGE(Q16:AE16)</f>
+        <v>10671.64866666667</v>
       </c>
       <c r="AJ16" s="21">
-        <f>(AH16/AE16)-1</f>
-        <v>0.17270627943485106</v>
+        <f>(AI16/AH16)-1</f>
+        <v>6.095290254602781e-002</v>
       </c>
       <c r="AK16" s="21">
-        <f>(AF16/AE16)-1</f>
+        <f>(AI16/AF16)-1</f>
+        <v>0.172708644688645</v>
+      </c>
+      <c r="AL16" s="21">
+        <f>(AG16/AF16)-1</f>
         <v>0.24342637362637376</v>
       </c>
-      <c r="AL16" s="22" t="s">
-        <v>77</v>
+      <c r="AM16" s="22" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="17" ht="36">
       <c r="A17" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C17" s="15"/>
       <c r="D17" s="15"/>
@@ -3050,44 +3097,47 @@
       <c r="AD17" s="17">
         <v>1478.02</v>
       </c>
-      <c r="AE17" s="19">
-        <f>MIN(C17:AD17)</f>
+      <c r="AE17" s="17">
+        <v>1379.99</v>
+      </c>
+      <c r="AF17" s="19">
+        <f>MIN(C17:AE17)</f>
         <v>1297.6199999999999</v>
       </c>
-      <c r="AF17" s="20">
-        <f>MAX(C17:AD17)</f>
+      <c r="AG17" s="20">
+        <f>MAX(C17:AE17)</f>
         <v>1697.6199999999999</v>
       </c>
-      <c r="AG17" s="20">
-        <f>AVERAGE(C17:AD17)</f>
-        <v>1537.5529999999999</v>
-      </c>
       <c r="AH17" s="20">
-        <f>AVERAGE(Q17:AD17)</f>
-        <v>1566.6092857142855</v>
-      </c>
-      <c r="AI17" s="21">
-        <f>(AH17/AG17)-1</f>
-        <v>1.8897745778054809e-002</v>
+        <f>AVERAGE(C17:AE17)</f>
+        <v>1530.05</v>
+      </c>
+      <c r="AI17" s="20">
+        <f>AVERAGE(Q17:AE17)</f>
+        <v>1554.1680000000001</v>
       </c>
       <c r="AJ17" s="21">
-        <f>(AH17/AE17)-1</f>
-        <v>0.20729434327020679</v>
+        <f>(AI17/AH17)-1</f>
+        <v>1.5762883565896724e-002</v>
       </c>
       <c r="AK17" s="21">
-        <f>(AF17/AE17)-1</f>
+        <f>(AI17/AF17)-1</f>
+        <v>0.19770657049059071</v>
+      </c>
+      <c r="AL17" s="21">
+        <f>(AG17/AF17)-1</f>
         <v>0.30825665449052875</v>
       </c>
-      <c r="AL17" s="22" t="s">
-        <v>79</v>
+      <c r="AM17" s="22" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="18" ht="18">
       <c r="A18" s="25" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B18" s="26" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C18" s="27"/>
       <c r="D18" s="28"/>
@@ -3096,115 +3146,118 @@
         <v>2279</v>
       </c>
       <c r="G18" s="28" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H18" s="28" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I18" s="28" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J18" s="28" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K18" s="28" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L18" s="28" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M18" s="28" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N18" s="28" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="O18" s="28" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P18" s="16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Q18" s="16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R18" s="16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="S18" s="16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="T18" s="16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="U18" s="16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="V18" s="16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="W18" s="16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="X18" s="16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Y18" s="16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="Z18" s="16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AA18" s="16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AB18" s="16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AC18" s="16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AD18" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="AE18" s="19">
-        <f>MIN(C18:AD18)</f>
+        <v>82</v>
+      </c>
+      <c r="AE18" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="AF18" s="19">
+        <f>MIN(C18:AE18)</f>
         <v>2279</v>
       </c>
-      <c r="AF18" s="20">
-        <f>MAX(C18:AD18)</f>
+      <c r="AG18" s="20">
+        <f>MAX(C18:AE18)</f>
         <v>2279</v>
       </c>
-      <c r="AG18" s="20">
-        <f>AVERAGE(C18:AD18)</f>
+      <c r="AH18" s="20">
+        <f>AVERAGE(C18:AE18)</f>
         <v>2279</v>
       </c>
-      <c r="AH18" s="20" t="e">
-        <f>AVERAGE(Q18:AD18)</f>
+      <c r="AI18" s="20" t="e">
+        <f>AVERAGE(Q18:AE18)</f>
         <v>#NUM!</v>
       </c>
-      <c r="AI18" s="21" t="e">
-        <f>(AH18/AG18)-1</f>
+      <c r="AJ18" s="21" t="e">
+        <f>(AI18/AH18)-1</f>
         <v>#NUM!</v>
       </c>
-      <c r="AJ18" s="21" t="e">
-        <f>(AH18/AE18)-1</f>
+      <c r="AK18" s="21" t="e">
+        <f>(AI18/AF18)-1</f>
         <v>#NUM!</v>
       </c>
-      <c r="AK18" s="21">
-        <f>(AF18/AE18)-1</f>
+      <c r="AL18" s="21">
+        <f>(AG18/AF18)-1</f>
         <v>0</v>
       </c>
-      <c r="AL18" s="22" t="s">
-        <v>82</v>
+      <c r="AM18" s="22" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="19" ht="36">
       <c r="A19" s="25" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B19" s="26" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C19" s="27"/>
       <c r="D19" s="28"/>
@@ -3238,44 +3291,47 @@
       <c r="AD19" s="16">
         <v>3629</v>
       </c>
-      <c r="AE19" s="19">
-        <f>MIN(C19:AD19)</f>
-        <v>3499.9499999999998</v>
-      </c>
-      <c r="AF19" s="20">
-        <f>MAX(C19:AD19)</f>
+      <c r="AE19" s="16">
+        <v>3394.9499999999998</v>
+      </c>
+      <c r="AF19" s="19">
+        <f>MIN(C19:AE19)</f>
+        <v>3394.9499999999998</v>
+      </c>
+      <c r="AG19" s="20">
+        <f>MAX(C19:AE19)</f>
         <v>3629</v>
       </c>
-      <c r="AG19" s="20">
-        <f>AVERAGE(C19:AD19)</f>
-        <v>3564.4749999999999</v>
-      </c>
       <c r="AH19" s="20">
-        <f>AVERAGE(Q19:AD19)</f>
-        <v>3564.4749999999999</v>
-      </c>
-      <c r="AI19" s="21">
-        <f>(AH19/AG19)-1</f>
+        <f>AVERAGE(C19:AE19)</f>
+        <v>3507.9666666666667</v>
+      </c>
+      <c r="AI19" s="20">
+        <f>AVERAGE(Q19:AE19)</f>
+        <v>3507.9666666666667</v>
+      </c>
+      <c r="AJ19" s="21">
+        <f>(AI19/AH19)-1</f>
         <v>0</v>
       </c>
-      <c r="AJ19" s="21">
-        <f>(AH19/AE19)-1</f>
-        <v>1.8435977656823699e-002</v>
-      </c>
       <c r="AK19" s="21">
-        <f>(AF19/AE19)-1</f>
-        <v>3.6871955313647398e-002</v>
-      </c>
-      <c r="AL19" s="29" t="s">
-        <v>84</v>
+        <f>(AI19/AF19)-1</f>
+        <v>3.3289640986366997e-002</v>
+      </c>
+      <c r="AL19" s="21">
+        <f>(AG19/AF19)-1</f>
+        <v>6.8940632409902891e-002</v>
+      </c>
+      <c r="AM19" s="29" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="20" ht="18">
       <c r="A20" s="25" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B20" s="26" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C20" s="27"/>
       <c r="D20" s="28"/>
@@ -3309,44 +3365,47 @@
       <c r="AD20" s="16">
         <v>1601.5</v>
       </c>
-      <c r="AE20" s="19">
-        <f>MIN(C20:AD20)</f>
+      <c r="AE20" s="16">
+        <v>1618.97</v>
+      </c>
+      <c r="AF20" s="19">
+        <f>MIN(C20:AE20)</f>
         <v>1601.5</v>
       </c>
-      <c r="AF20" s="20">
-        <f>MAX(C20:AD20)</f>
+      <c r="AG20" s="20">
+        <f>MAX(C20:AE20)</f>
         <v>1624.75</v>
       </c>
-      <c r="AG20" s="20">
-        <f>AVERAGE(C20:AD20)</f>
-        <v>1613.125</v>
-      </c>
       <c r="AH20" s="20">
-        <f>AVERAGE(Q20:AD20)</f>
-        <v>1613.125</v>
-      </c>
-      <c r="AI20" s="21">
-        <f>(AH20/AG20)-1</f>
+        <f>AVERAGE(C20:AE20)</f>
+        <v>1615.0733333333335</v>
+      </c>
+      <c r="AI20" s="20">
+        <f>AVERAGE(Q20:AE20)</f>
+        <v>1615.0733333333335</v>
+      </c>
+      <c r="AJ20" s="21">
+        <f>(AI20/AH20)-1</f>
         <v>0</v>
       </c>
-      <c r="AJ20" s="21">
-        <f>(AH20/AE20)-1</f>
-        <v>7.2588198563845463e-003</v>
-      </c>
       <c r="AK20" s="21">
-        <f>(AF20/AE20)-1</f>
+        <f>(AI20/AF20)-1</f>
+        <v>8.4753876574046316e-003</v>
+      </c>
+      <c r="AL20" s="21">
+        <f>(AG20/AF20)-1</f>
         <v>1.4517639712769315e-002</v>
       </c>
-      <c r="AL20" s="29" t="s">
-        <v>86</v>
+      <c r="AM20" s="29" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="21" ht="18">
       <c r="A21" s="25" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C21" s="27"/>
       <c r="D21" s="28"/>
@@ -3380,44 +3439,47 @@
       <c r="AD21" s="16">
         <v>692.88999999999999</v>
       </c>
-      <c r="AE21" s="19">
-        <f>MIN(C21:AD21)</f>
+      <c r="AE21" s="16">
         <v>692.88999999999999</v>
       </c>
-      <c r="AF21" s="20">
-        <f>MAX(C21:AD21)</f>
+      <c r="AF21" s="19">
+        <f>MIN(C21:AE21)</f>
+        <v>692.88999999999999</v>
+      </c>
+      <c r="AG21" s="20">
+        <f>MAX(C21:AE21)</f>
         <v>759.95000000000005</v>
       </c>
-      <c r="AG21" s="20">
-        <f>AVERAGE(C21:AD21)</f>
-        <v>726.42000000000007</v>
-      </c>
       <c r="AH21" s="20">
-        <f>AVERAGE(Q21:AD21)</f>
-        <v>726.42000000000007</v>
-      </c>
-      <c r="AI21" s="21">
-        <f>(AH21/AG21)-1</f>
+        <f>AVERAGE(C21:AE21)</f>
+        <v>715.24333333333334</v>
+      </c>
+      <c r="AI21" s="20">
+        <f>AVERAGE(Q21:AE21)</f>
+        <v>715.24333333333334</v>
+      </c>
+      <c r="AJ21" s="21">
+        <f>(AI21/AH21)-1</f>
         <v>0</v>
       </c>
-      <c r="AJ21" s="21">
-        <f>(AH21/AE21)-1</f>
-        <v>4.8391519577422271e-002</v>
-      </c>
       <c r="AK21" s="21">
-        <f>(AF21/AE21)-1</f>
+        <f>(AI21/AF21)-1</f>
+        <v>3.2261013051614773e-002</v>
+      </c>
+      <c r="AL21" s="21">
+        <f>(AG21/AF21)-1</f>
         <v>9.6783039154844319e-002</v>
       </c>
-      <c r="AL21" s="29" t="s">
-        <v>88</v>
+      <c r="AM21" s="29" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="22" ht="18">
       <c r="A22" s="25" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B22" s="26" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C22" s="27"/>
       <c r="D22" s="28"/>
@@ -3449,44 +3511,47 @@
       <c r="AD22" s="16">
         <v>1410.9000000000001</v>
       </c>
-      <c r="AE22" s="19">
-        <f>MIN(C22:AD22)</f>
+      <c r="AE22" s="16">
+        <v>1323.99</v>
+      </c>
+      <c r="AF22" s="19">
+        <f>MIN(C22:AE22)</f>
+        <v>1323.99</v>
+      </c>
+      <c r="AG22" s="20">
+        <f>MAX(C22:AE22)</f>
         <v>1410.9000000000001</v>
       </c>
-      <c r="AF22" s="20">
-        <f>MAX(C22:AD22)</f>
-        <v>1410.9000000000001</v>
-      </c>
-      <c r="AG22" s="20">
-        <f>AVERAGE(C22:AD22)</f>
-        <v>1410.9000000000001</v>
-      </c>
       <c r="AH22" s="20">
-        <f>AVERAGE(Q22:AD22)</f>
-        <v>1410.9000000000001</v>
-      </c>
-      <c r="AI22" s="21">
-        <f>(AH22/AG22)-1</f>
+        <f>AVERAGE(C22:AE22)</f>
+        <v>1367.4450000000002</v>
+      </c>
+      <c r="AI22" s="20">
+        <f>AVERAGE(Q22:AE22)</f>
+        <v>1367.4450000000002</v>
+      </c>
+      <c r="AJ22" s="21">
+        <f>(AI22/AH22)-1</f>
         <v>0</v>
       </c>
-      <c r="AJ22" s="21">
-        <f>(AH22/AE22)-1</f>
-        <v>0</v>
-      </c>
       <c r="AK22" s="21">
-        <f>(AF22/AE22)-1</f>
-        <v>0</v>
-      </c>
-      <c r="AL22" s="29" t="s">
-        <v>90</v>
+        <f>(AI22/AF22)-1</f>
+        <v>3.2821244873450839e-002</v>
+      </c>
+      <c r="AL22" s="21">
+        <f>(AG22/AF22)-1</f>
+        <v>6.5642489746901456e-002</v>
+      </c>
+      <c r="AM22" s="29" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="23" ht="18">
       <c r="A23" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C23" s="24">
         <v>176.69</v>
@@ -3566,44 +3631,47 @@
       <c r="AD23" s="30">
         <v>260</v>
       </c>
-      <c r="AE23" s="19">
-        <f>MIN(C23:AD23)</f>
+      <c r="AE23" s="30">
+        <v>260</v>
+      </c>
+      <c r="AF23" s="19">
+        <f>MIN(C23:AE23)</f>
         <v>145</v>
       </c>
-      <c r="AF23" s="20">
-        <f>MAX(C23:AD23)</f>
+      <c r="AG23" s="20">
+        <f>MAX(C23:AE23)</f>
         <v>260</v>
       </c>
-      <c r="AG23" s="20">
-        <f>AVERAGE(C23:AD23)</f>
-        <v>212.75719999999998</v>
-      </c>
       <c r="AH23" s="20">
-        <f>AVERAGE(Q23:AD23)</f>
-        <v>245.17857142857142</v>
-      </c>
-      <c r="AI23" s="21">
-        <f>(AH23/AG23)-1</f>
-        <v>0.15238671795159653</v>
+        <f>AVERAGE(C23:AE23)</f>
+        <v>214.57423076923075</v>
+      </c>
+      <c r="AI23" s="20">
+        <f>AVERAGE(Q23:AE23)</f>
+        <v>246.16666666666666</v>
       </c>
       <c r="AJ23" s="21">
-        <f>(AH23/AE23)-1</f>
-        <v>0.69088669950738901</v>
+        <f>(AI23/AH23)-1</f>
+        <v>0.14723313132327043</v>
       </c>
       <c r="AK23" s="21">
-        <f>(AF23/AE23)-1</f>
+        <f>(AI23/AF23)-1</f>
+        <v>0.69770114942528738</v>
+      </c>
+      <c r="AL23" s="21">
+        <f>(AG23/AF23)-1</f>
         <v>0.7931034482758621</v>
       </c>
-      <c r="AL23" s="22" t="s">
-        <v>92</v>
+      <c r="AM23" s="22" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="24" ht="18">
       <c r="A24" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C24" s="16"/>
       <c r="D24" s="16"/>
@@ -3652,7 +3720,7 @@
         <v>212.31</v>
       </c>
       <c r="U24" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="V24" s="18">
         <v>229.94999999999999</v>
@@ -3681,44 +3749,47 @@
       <c r="AD24" s="30">
         <v>270</v>
       </c>
-      <c r="AE24" s="19">
-        <f>MIN(C24:AD24)</f>
+      <c r="AE24" s="30">
+        <v>270</v>
+      </c>
+      <c r="AF24" s="19">
+        <f>MIN(C24:AE24)</f>
         <v>176.91999999999999</v>
       </c>
-      <c r="AF24" s="20">
-        <f>MAX(C24:AD24)</f>
+      <c r="AG24" s="20">
+        <f>MAX(C24:AE24)</f>
         <v>270</v>
       </c>
-      <c r="AG24" s="20">
-        <f>AVERAGE(C24:AD24)</f>
-        <v>215.25086956521741</v>
-      </c>
       <c r="AH24" s="20">
-        <f>AVERAGE(Q24:AD24)</f>
-        <v>242.09153846153848</v>
-      </c>
-      <c r="AI24" s="21">
-        <f>(AH24/AG24)-1</f>
-        <v>0.12469482214188599</v>
+        <f>AVERAGE(C24:AE24)</f>
+        <v>217.53208333333336</v>
+      </c>
+      <c r="AI24" s="20">
+        <f>AVERAGE(Q24:AE24)</f>
+        <v>244.08500000000001</v>
       </c>
       <c r="AJ24" s="21">
-        <f>(AH24/AE24)-1</f>
-        <v>0.36836727595262553</v>
+        <f>(AI24/AH24)-1</f>
+        <v>0.12206436981518043</v>
       </c>
       <c r="AK24" s="21">
-        <f>(AF24/AE24)-1</f>
+        <f>(AI24/AF24)-1</f>
+        <v>0.37963486321501261</v>
+      </c>
+      <c r="AL24" s="21">
+        <f>(AG24/AF24)-1</f>
         <v>0.52611349762604576</v>
       </c>
-      <c r="AL24" s="22" t="s">
-        <v>94</v>
+      <c r="AM24" s="22" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="25" ht="18">
       <c r="A25" s="25" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B25" s="26" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C25" s="28"/>
       <c r="D25" s="28"/>
@@ -3731,31 +3802,31 @@
         <v>396.77999999999997</v>
       </c>
       <c r="I25" s="28" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J25" s="28" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K25" s="28" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L25" s="28" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M25" s="28" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N25" s="28" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O25" s="28" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="P25" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q25" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="R25" s="16">
         <v>413</v>
@@ -3767,7 +3838,7 @@
         <v>408.87</v>
       </c>
       <c r="U25" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="V25" s="16">
         <v>453.04000000000002</v>
@@ -3796,44 +3867,47 @@
       <c r="AD25" s="16">
         <v>349</v>
       </c>
-      <c r="AE25" s="19">
-        <f>MIN(C25:AD25)</f>
+      <c r="AE25" s="16">
         <v>349</v>
       </c>
-      <c r="AF25" s="20">
-        <f>MAX(C25:AD25)</f>
+      <c r="AF25" s="19">
+        <f>MIN(C25:AE25)</f>
+        <v>349</v>
+      </c>
+      <c r="AG25" s="20">
+        <f>MAX(C25:AE25)</f>
         <v>453.04000000000002</v>
       </c>
-      <c r="AG25" s="20">
-        <f>AVERAGE(C25:AD25)</f>
-        <v>386.96642857142854</v>
-      </c>
       <c r="AH25" s="20">
-        <f>AVERAGE(Q25:AD25)</f>
-        <v>385.33083333333326</v>
-      </c>
-      <c r="AI25" s="21">
-        <f>(AH25/AG25)-1</f>
-        <v>-4.2267109426867844e-003</v>
+        <f>AVERAGE(C25:AE25)</f>
+        <v>384.43533333333329</v>
+      </c>
+      <c r="AI25" s="20">
+        <f>AVERAGE(Q25:AE25)</f>
+        <v>382.53615384615381</v>
       </c>
       <c r="AJ25" s="21">
-        <f>(AH25/AE25)-1</f>
-        <v>0.10409980897803228</v>
+        <f>(AI25/AH25)-1</f>
+        <v>-4.9401793292833673e-003</v>
       </c>
       <c r="AK25" s="21">
-        <f>(AF25/AE25)-1</f>
+        <f>(AI25/AF25)-1</f>
+        <v>9.6092131364337474e-002</v>
+      </c>
+      <c r="AL25" s="21">
+        <f>(AG25/AF25)-1</f>
         <v>0.29810888252148993</v>
       </c>
-      <c r="AL25" s="29" t="s">
-        <v>96</v>
+      <c r="AM25" s="29" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="26" ht="54">
       <c r="A26" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C26" s="16"/>
       <c r="D26" s="16"/>
@@ -3900,55 +3974,58 @@
         <v>600</v>
       </c>
       <c r="AA26" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AB26" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AC26" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AD26" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="AE26" s="19">
-        <f>MIN(C26:AD26)</f>
+        <v>50</v>
+      </c>
+      <c r="AE26" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="AF26" s="19">
+        <f>MIN(C26:AE26)</f>
         <v>550</v>
       </c>
-      <c r="AF26" s="20">
-        <f>MAX(C26:AD26)</f>
+      <c r="AG26" s="20">
+        <f>MAX(C26:AE26)</f>
         <v>600</v>
       </c>
-      <c r="AG26" s="20">
-        <f>AVERAGE(C26:AD26)</f>
+      <c r="AH26" s="20">
+        <f>AVERAGE(C26:AE26)</f>
         <v>574</v>
       </c>
-      <c r="AH26" s="20">
-        <f>AVERAGE(Q26:AD26)</f>
+      <c r="AI26" s="20">
+        <f>AVERAGE(Q26:AE26)</f>
         <v>598</v>
       </c>
-      <c r="AI26" s="21">
-        <f>(AH26/AG26)-1</f>
+      <c r="AJ26" s="21">
+        <f>(AI26/AH26)-1</f>
         <v>4.1811846689895571e-002</v>
       </c>
-      <c r="AJ26" s="21">
-        <f>(AH26/AE26)-1</f>
+      <c r="AK26" s="21">
+        <f>(AI26/AF26)-1</f>
         <v>8.7272727272727169e-002</v>
       </c>
-      <c r="AK26" s="21">
-        <f>(AF26/AE26)-1</f>
+      <c r="AL26" s="21">
+        <f>(AG26/AF26)-1</f>
         <v>9.0909090909090828e-002</v>
       </c>
-      <c r="AL26" s="22" t="s">
-        <v>99</v>
+      <c r="AM26" s="22" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="27" ht="36">
       <c r="A27" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C27" s="16"/>
       <c r="D27" s="16"/>
@@ -4026,44 +4103,47 @@
       <c r="AD27" s="24">
         <v>599.99000000000001</v>
       </c>
-      <c r="AE27" s="19">
-        <f>MIN(C27:AD27)</f>
+      <c r="AE27" s="24">
+        <v>599.99000000000001</v>
+      </c>
+      <c r="AF27" s="19">
+        <f>MIN(C27:AE27)</f>
         <v>550</v>
       </c>
-      <c r="AF27" s="20">
-        <f>MAX(C27:AD27)</f>
+      <c r="AG27" s="20">
+        <f>MAX(C27:AE27)</f>
         <v>800</v>
       </c>
-      <c r="AG27" s="20">
-        <f>AVERAGE(C27:AD27)</f>
-        <v>594.99916666666661</v>
-      </c>
       <c r="AH27" s="20">
-        <f>AVERAGE(Q27:AD27)</f>
-        <v>627.14142857142849</v>
-      </c>
-      <c r="AI27" s="21">
-        <f>(AH27/AG27)-1</f>
-        <v>5.4020683902518352e-002</v>
+        <f>AVERAGE(C27:AE27)</f>
+        <v>595.19880000000001</v>
+      </c>
+      <c r="AI27" s="20">
+        <f>AVERAGE(Q27:AE27)</f>
+        <v>625.3313333333333</v>
       </c>
       <c r="AJ27" s="21">
-        <f>(AH27/AE27)-1</f>
-        <v>0.14025714285714264</v>
+        <f>(AI27/AH27)-1</f>
+        <v>5.0625998125892302e-002</v>
       </c>
       <c r="AK27" s="21">
-        <f>(AF27/AE27)-1</f>
+        <f>(AI27/AF27)-1</f>
+        <v>0.13696606060606054</v>
+      </c>
+      <c r="AL27" s="21">
+        <f>(AG27/AF27)-1</f>
         <v>0.45454545454545459</v>
       </c>
-      <c r="AL27" s="29" t="s">
-        <v>101</v>
+      <c r="AM27" s="29" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="28" ht="18">
       <c r="A28" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C28" s="16"/>
       <c r="D28" s="16"/>
@@ -4141,44 +4221,47 @@
       <c r="AD28" s="30">
         <v>688</v>
       </c>
-      <c r="AE28" s="19">
-        <f>MIN(C28:AD28)</f>
+      <c r="AE28" s="33">
         <v>329</v>
       </c>
-      <c r="AF28" s="20">
-        <f>MAX(C28:AD28)</f>
+      <c r="AF28" s="19">
+        <f>MIN(C28:AE28)</f>
+        <v>329</v>
+      </c>
+      <c r="AG28" s="20">
+        <f>MAX(C28:AE28)</f>
         <v>969.95000000000005</v>
       </c>
-      <c r="AG28" s="20">
-        <f>AVERAGE(C28:AD28)</f>
-        <v>520.19583333333333</v>
-      </c>
       <c r="AH28" s="20">
-        <f>AVERAGE(Q28:AD28)</f>
-        <v>574.98571428571427</v>
-      </c>
-      <c r="AI28" s="21">
-        <f>(AH28/AG28)-1</f>
-        <v>0.10532548982812107</v>
+        <f>AVERAGE(C28:AE28)</f>
+        <v>512.548</v>
+      </c>
+      <c r="AI28" s="20">
+        <f>AVERAGE(Q28:AE28)</f>
+        <v>558.58666666666659</v>
       </c>
       <c r="AJ28" s="21">
-        <f>(AH28/AE28)-1</f>
-        <v>0.74767694311767263</v>
+        <f>(AI28/AH28)-1</f>
+        <v>8.9823132012351259e-002</v>
       </c>
       <c r="AK28" s="21">
-        <f>(AF28/AE28)-1</f>
+        <f>(AI28/AF28)-1</f>
+        <v>0.69783181357649426</v>
+      </c>
+      <c r="AL28" s="21">
+        <f>(AG28/AF28)-1</f>
         <v>1.9481762917933132</v>
       </c>
-      <c r="AL28" s="22" t="s">
-        <v>104</v>
+      <c r="AM28" s="22" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="29" ht="18">
       <c r="A29" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C29" s="16"/>
       <c r="D29" s="16"/>
@@ -4256,44 +4339,47 @@
       <c r="AD29" s="30">
         <v>673.37</v>
       </c>
-      <c r="AE29" s="19">
-        <f>MIN(C29:AD29)</f>
+      <c r="AE29" s="30">
+        <v>765.98000000000002</v>
+      </c>
+      <c r="AF29" s="19">
+        <f>MIN(C29:AE29)</f>
         <v>371.14999999999998</v>
       </c>
-      <c r="AF29" s="20">
-        <f>MAX(C29:AD29)</f>
-        <v>673.37</v>
-      </c>
       <c r="AG29" s="20">
-        <f>AVERAGE(C29:AD29)</f>
-        <v>463.16166666666658</v>
+        <f>MAX(C29:AE29)</f>
+        <v>765.98000000000002</v>
       </c>
       <c r="AH29" s="20">
-        <f>AVERAGE(Q29:AD29)</f>
-        <v>492.65428571428566</v>
-      </c>
-      <c r="AI29" s="21">
-        <f>(AH29/AG29)-1</f>
-        <v>6.3676727091589447e-002</v>
+        <f>AVERAGE(C29:AE29)</f>
+        <v>475.2743999999999</v>
+      </c>
+      <c r="AI29" s="20">
+        <f>AVERAGE(Q29:AE29)</f>
+        <v>510.87599999999998</v>
       </c>
       <c r="AJ29" s="21">
-        <f>(AH29/AE29)-1</f>
-        <v>0.32737245241623514</v>
+        <f>(AI29/AH29)-1</f>
+        <v>7.4907463982911926e-002</v>
       </c>
       <c r="AK29" s="21">
-        <f>(AF29/AE29)-1</f>
-        <v>0.8142799407247745</v>
-      </c>
-      <c r="AL29" s="22" t="s">
-        <v>106</v>
+        <f>(AI29/AF29)-1</f>
+        <v>0.37646773541694745</v>
+      </c>
+      <c r="AL29" s="21">
+        <f>(AG29/AF29)-1</f>
+        <v>1.0638016974269164</v>
+      </c>
+      <c r="AM29" s="22" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="30" ht="36">
       <c r="A30" s="25" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B30" s="26" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C30" s="28"/>
       <c r="D30" s="28"/>
@@ -4375,44 +4461,47 @@
       <c r="AD30" s="30">
         <v>619.59000000000003</v>
       </c>
-      <c r="AE30" s="19">
-        <f>MIN(C30:AD30)</f>
+      <c r="AE30" s="30">
+        <v>684.23000000000002</v>
+      </c>
+      <c r="AF30" s="19">
+        <f>MIN(C30:AE30)</f>
         <v>396</v>
       </c>
-      <c r="AF30" s="20">
-        <f>MAX(C30:AD30)</f>
-        <v>619.59000000000003</v>
-      </c>
       <c r="AG30" s="20">
-        <f>AVERAGE(C30:AD30)</f>
-        <v>549.03692307692313</v>
+        <f>MAX(C30:AE30)</f>
+        <v>684.23000000000002</v>
       </c>
       <c r="AH30" s="20">
-        <f>AVERAGE(Q30:AD30)</f>
-        <v>587.58642857142854</v>
-      </c>
-      <c r="AI30" s="21">
-        <f>(AH30/AG30)-1</f>
-        <v>7.0212956313512542e-002</v>
+        <f>AVERAGE(C30:AE30)</f>
+        <v>554.04407407407405</v>
+      </c>
+      <c r="AI30" s="20">
+        <f>AVERAGE(Q30:AE30)</f>
+        <v>594.02933333333328</v>
       </c>
       <c r="AJ30" s="21">
-        <f>(AH30/AE30)-1</f>
-        <v>0.48380411255411238</v>
+        <f>(AI30/AH30)-1</f>
+        <v>7.2169816681250776e-002</v>
       </c>
       <c r="AK30" s="21">
-        <f>(AF30/AE30)-1</f>
-        <v>0.56462121212121219</v>
-      </c>
-      <c r="AL30" s="22" t="s">
-        <v>109</v>
+        <f>(AI30/AF30)-1</f>
+        <v>0.50007407407407389</v>
+      </c>
+      <c r="AL30" s="21">
+        <f>(AG30/AF30)-1</f>
+        <v>0.72785353535353536</v>
+      </c>
+      <c r="AM30" s="22" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="31" ht="18">
       <c r="A31" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C31" s="16"/>
       <c r="D31" s="24">
@@ -4492,44 +4581,47 @@
       <c r="AD31" s="30">
         <v>1500</v>
       </c>
-      <c r="AE31" s="19">
-        <f>MIN(C31:AD31)</f>
+      <c r="AE31" s="30">
+        <v>1932.8299999999999</v>
+      </c>
+      <c r="AF31" s="19">
+        <f>MIN(C31:AE31)</f>
         <v>370</v>
       </c>
-      <c r="AF31" s="20">
-        <f>MAX(C31:AD31)</f>
-        <v>1678.0799999999999</v>
-      </c>
       <c r="AG31" s="20">
-        <f>AVERAGE(C31:AD31)</f>
-        <v>1230.5699999999999</v>
+        <f>MAX(C31:AE31)</f>
+        <v>1932.8299999999999</v>
       </c>
       <c r="AH31" s="20">
-        <f>AVERAGE(Q31:AD31)</f>
-        <v>1386.5585714285714</v>
-      </c>
-      <c r="AI31" s="21">
-        <f>(AH31/AG31)-1</f>
-        <v>0.12676123376042936</v>
+        <f>AVERAGE(C31:AE31)</f>
+        <v>1257.5800000000002</v>
+      </c>
+      <c r="AI31" s="20">
+        <f>AVERAGE(Q31:AE31)</f>
+        <v>1422.9766666666667</v>
       </c>
       <c r="AJ31" s="21">
-        <f>(AH31/AE31)-1</f>
-        <v>2.7474555984555984</v>
+        <f>(AI31/AH31)-1</f>
+        <v>0.13151979728261143</v>
       </c>
       <c r="AK31" s="21">
-        <f>(AF31/AE31)-1</f>
-        <v>3.535351351351351</v>
-      </c>
-      <c r="AL31" s="22" t="s">
-        <v>111</v>
+        <f>(AI31/AF31)-1</f>
+        <v>2.8458828828828828</v>
+      </c>
+      <c r="AL31" s="21">
+        <f>(AG31/AF31)-1</f>
+        <v>4.2238648648648649</v>
+      </c>
+      <c r="AM31" s="22" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="32" ht="18">
       <c r="A32" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C32" s="16"/>
       <c r="D32" s="16"/>
@@ -4599,44 +4691,47 @@
       <c r="AD32" s="18">
         <v>169</v>
       </c>
-      <c r="AE32" s="19">
-        <f>MIN(C32:AD32)</f>
+      <c r="AE32" s="18">
+        <v>169</v>
+      </c>
+      <c r="AF32" s="19">
+        <f>MIN(C32:AE32)</f>
         <v>109.98999999999999</v>
       </c>
-      <c r="AF32" s="20">
-        <f>MAX(C32:AD32)</f>
+      <c r="AG32" s="20">
+        <f>MAX(C32:AE32)</f>
         <v>169.99000000000001</v>
       </c>
-      <c r="AG32" s="20">
-        <f>AVERAGE(C32:AD32)</f>
-        <v>153.17649999999998</v>
-      </c>
       <c r="AH32" s="20">
-        <f>AVERAGE(Q32:AD32)</f>
-        <v>162.70357142857142</v>
-      </c>
-      <c r="AI32" s="21">
-        <f>(AH32/AG32)-1</f>
-        <v>6.2196690932169396e-002</v>
+        <f>AVERAGE(C32:AE32)</f>
+        <v>153.92999999999998</v>
+      </c>
+      <c r="AI32" s="20">
+        <f>AVERAGE(Q32:AE32)</f>
+        <v>163.12333333333333</v>
       </c>
       <c r="AJ32" s="21">
-        <f>(AH32/AE32)-1</f>
-        <v>0.47925785461015935</v>
+        <f>(AI32/AH32)-1</f>
+        <v>5.9724117022889267e-002</v>
       </c>
       <c r="AK32" s="21">
-        <f>(AF32/AE32)-1</f>
+        <f>(AI32/AF32)-1</f>
+        <v>0.48307421886838209</v>
+      </c>
+      <c r="AL32" s="21">
+        <f>(AG32/AF32)-1</f>
         <v>0.54550413673970377</v>
       </c>
-      <c r="AL32" s="22" t="s">
-        <v>113</v>
+      <c r="AM32" s="22" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="33" ht="18">
       <c r="A33" s="25" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B33" s="26" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C33" s="28"/>
       <c r="D33" s="28"/>
@@ -4706,44 +4801,47 @@
       <c r="AD33" s="17">
         <v>80.019999999999996</v>
       </c>
-      <c r="AE33" s="19">
-        <f>MIN(C33:AD33)</f>
+      <c r="AE33" s="17">
+        <v>80.019999999999996</v>
+      </c>
+      <c r="AF33" s="19">
+        <f>MIN(C33:AE33)</f>
         <v>68</v>
       </c>
-      <c r="AF33" s="20">
-        <f>MAX(C33:AD33)</f>
+      <c r="AG33" s="20">
+        <f>MAX(C33:AE33)</f>
         <v>85.700000000000003</v>
       </c>
-      <c r="AG33" s="20">
-        <f>AVERAGE(C33:AD33)</f>
-        <v>79.097499999999997</v>
-      </c>
       <c r="AH33" s="20">
-        <f>AVERAGE(Q33:AD33)</f>
-        <v>81.367857142857147</v>
-      </c>
-      <c r="AI33" s="21">
-        <f>(AH33/AG33)-1</f>
-        <v>2.8703273085206815e-002</v>
+        <f>AVERAGE(C33:AE33)</f>
+        <v>79.141428571428577</v>
+      </c>
+      <c r="AI33" s="20">
+        <f>AVERAGE(Q33:AE33)</f>
+        <v>81.278000000000006</v>
       </c>
       <c r="AJ33" s="21">
-        <f>(AH33/AE33)-1</f>
-        <v>0.19658613445378159</v>
+        <f>(AI33/AH33)-1</f>
+        <v>2.6996877199949365e-002</v>
       </c>
       <c r="AK33" s="21">
-        <f>(AF33/AE33)-1</f>
+        <f>(AI33/AF33)-1</f>
+        <v>0.19526470588235312</v>
+      </c>
+      <c r="AL33" s="21">
+        <f>(AG33/AF33)-1</f>
         <v>0.26029411764705879</v>
       </c>
-      <c r="AL33" s="22" t="s">
-        <v>115</v>
+      <c r="AM33" s="22" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="34" ht="18">
       <c r="A34" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C34" s="16"/>
       <c r="D34" s="16"/>
@@ -4813,44 +4911,47 @@
       <c r="AD34" s="32">
         <v>97</v>
       </c>
-      <c r="AE34" s="19">
-        <f>MIN(C34:AD34)</f>
+      <c r="AE34" s="32">
+        <v>97</v>
+      </c>
+      <c r="AF34" s="19">
+        <f>MIN(C34:AE34)</f>
         <v>55</v>
       </c>
-      <c r="AF34" s="20">
-        <f>MAX(C34:AD34)</f>
+      <c r="AG34" s="20">
+        <f>MAX(C34:AE34)</f>
         <v>111</v>
       </c>
-      <c r="AG34" s="20">
-        <f>AVERAGE(C34:AD34)</f>
-        <v>89.246500000000012</v>
-      </c>
       <c r="AH34" s="20">
-        <f>AVERAGE(Q34:AD34)</f>
-        <v>96.797857142857126</v>
-      </c>
-      <c r="AI34" s="21">
-        <f>(AH34/AG34)-1</f>
-        <v>8.4612361749279996e-002</v>
+        <f>AVERAGE(C34:AE34)</f>
+        <v>89.615714285714304</v>
+      </c>
+      <c r="AI34" s="20">
+        <f>AVERAGE(Q34:AE34)</f>
+        <v>96.811333333333323</v>
       </c>
       <c r="AJ34" s="21">
-        <f>(AH34/AE34)-1</f>
-        <v>0.75996103896103873</v>
+        <f>(AI34/AH34)-1</f>
+        <v>8.0294166095444153e-002</v>
       </c>
       <c r="AK34" s="21">
-        <f>(AF34/AE34)-1</f>
+        <f>(AI34/AF34)-1</f>
+        <v>0.76020606060606033</v>
+      </c>
+      <c r="AL34" s="21">
+        <f>(AG34/AF34)-1</f>
         <v>1.0181818181818181</v>
       </c>
-      <c r="AL34" s="22" t="s">
-        <v>117</v>
+      <c r="AM34" s="22" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="35" ht="18">
       <c r="A35" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C35" s="16"/>
       <c r="D35" s="16"/>
@@ -4918,44 +5019,47 @@
       <c r="AD35" s="16">
         <v>89.700000000000003</v>
       </c>
-      <c r="AE35" s="19">
-        <f>MIN(C35:AD35)</f>
+      <c r="AE35" s="16">
+        <v>86.439999999999998</v>
+      </c>
+      <c r="AF35" s="19">
+        <f>MIN(C35:AE35)</f>
         <v>47.359999999999999</v>
       </c>
-      <c r="AF35" s="20">
-        <f>MAX(C35:AD35)</f>
+      <c r="AG35" s="20">
+        <f>MAX(C35:AE35)</f>
         <v>100.68000000000001</v>
       </c>
-      <c r="AG35" s="20">
-        <f>AVERAGE(C35:AD35)</f>
-        <v>77.32578947368421</v>
-      </c>
       <c r="AH35" s="20">
-        <f>AVERAGE(Q35:AD35)</f>
-        <v>85.481428571428594</v>
-      </c>
-      <c r="AI35" s="21">
-        <f>(AH35/AG35)-1</f>
-        <v>0.10547113910191563</v>
+        <f>AVERAGE(C35:AE35)</f>
+        <v>77.781500000000008</v>
+      </c>
+      <c r="AI35" s="20">
+        <f>AVERAGE(Q35:AE35)</f>
+        <v>85.545333333333346</v>
       </c>
       <c r="AJ35" s="21">
-        <f>(AH35/AE35)-1</f>
-        <v>0.80492881274131323</v>
+        <f>(AI35/AH35)-1</f>
+        <v>9.9815937380139719e-002</v>
       </c>
       <c r="AK35" s="21">
-        <f>(AF35/AE35)-1</f>
+        <f>(AI35/AF35)-1</f>
+        <v>0.80627815315315354</v>
+      </c>
+      <c r="AL35" s="21">
+        <f>(AG35/AF35)-1</f>
         <v>1.1258445945945947</v>
       </c>
-      <c r="AL35" s="22" t="s">
-        <v>119</v>
+      <c r="AM35" s="22" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="36" ht="18">
       <c r="A36" s="25" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B36" s="26" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C36" s="28"/>
       <c r="D36" s="28"/>
@@ -4991,7 +5095,7 @@
         <v>132.33000000000001</v>
       </c>
       <c r="T36" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="U36" s="17">
         <v>156</v>
@@ -5023,44 +5127,47 @@
       <c r="AD36" s="16">
         <v>121.06</v>
       </c>
-      <c r="AE36" s="19">
-        <f>MIN(C36:AD36)</f>
+      <c r="AE36" s="16">
+        <v>138.16</v>
+      </c>
+      <c r="AF36" s="19">
+        <f>MIN(C36:AE36)</f>
         <v>92.5</v>
       </c>
-      <c r="AF36" s="20">
-        <f>MAX(C36:AD36)</f>
+      <c r="AG36" s="20">
+        <f>MAX(C36:AE36)</f>
         <v>159.99000000000001</v>
       </c>
-      <c r="AG36" s="20">
-        <f>AVERAGE(C36:AD36)</f>
-        <v>133.09666666666669</v>
-      </c>
       <c r="AH36" s="20">
-        <f>AVERAGE(Q36:AD36)</f>
-        <v>143.55769230769232</v>
-      </c>
-      <c r="AI36" s="21">
-        <f>(AH36/AG36)-1</f>
-        <v>7.8597202341849082e-002</v>
+        <f>AVERAGE(C36:AE36)</f>
+        <v>133.36315789473684</v>
+      </c>
+      <c r="AI36" s="20">
+        <f>AVERAGE(Q36:AE36)</f>
+        <v>143.17214285714286</v>
       </c>
       <c r="AJ36" s="21">
-        <f>(AH36/AE36)-1</f>
-        <v>0.55197505197505214</v>
+        <f>(AI36/AH36)-1</f>
+        <v>7.3550935035208376e-002</v>
       </c>
       <c r="AK36" s="21">
-        <f>(AF36/AE36)-1</f>
+        <f>(AI36/AF36)-1</f>
+        <v>0.54780694980694977</v>
+      </c>
+      <c r="AL36" s="21">
+        <f>(AG36/AF36)-1</f>
         <v>0.72962162162162181</v>
       </c>
-      <c r="AL36" s="22" t="s">
-        <v>121</v>
+      <c r="AM36" s="22" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="37" ht="18">
       <c r="A37" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C37" s="16"/>
       <c r="D37" s="16"/>
@@ -5126,44 +5233,47 @@
       <c r="AD37" s="16">
         <v>199.5</v>
       </c>
-      <c r="AE37" s="19">
-        <f>MIN(C37:AD37)</f>
+      <c r="AE37" s="17">
+        <v>219.19</v>
+      </c>
+      <c r="AF37" s="19">
+        <f>MIN(C37:AE37)</f>
         <v>148.88</v>
       </c>
-      <c r="AF37" s="20">
-        <f>MAX(C37:AD37)</f>
+      <c r="AG37" s="20">
+        <f>MAX(C37:AE37)</f>
         <v>257.87</v>
       </c>
-      <c r="AG37" s="20">
-        <f>AVERAGE(C37:AD37)</f>
-        <v>215.87222222222223</v>
-      </c>
       <c r="AH37" s="20">
-        <f>AVERAGE(Q37:AD37)</f>
-        <v>221.75857142857146</v>
-      </c>
-      <c r="AI37" s="21">
-        <f>(AH37/AG37)-1</f>
-        <v>2.7267747307894608e-002</v>
+        <f>AVERAGE(C37:AE37)</f>
+        <v>216.04684210526318</v>
+      </c>
+      <c r="AI37" s="20">
+        <f>AVERAGE(Q37:AE37)</f>
+        <v>221.58733333333336</v>
       </c>
       <c r="AJ37" s="21">
-        <f>(AH37/AE37)-1</f>
-        <v>0.48951216703769118</v>
+        <f>(AI37/AH37)-1</f>
+        <v>2.5644860966635763e-002</v>
       </c>
       <c r="AK37" s="21">
-        <f>(AF37/AE37)-1</f>
+        <f>(AI37/AF37)-1</f>
+        <v>0.48836199176070227</v>
+      </c>
+      <c r="AL37" s="21">
+        <f>(AG37/AF37)-1</f>
         <v>0.73206609349811935</v>
       </c>
-      <c r="AL37" s="22" t="s">
-        <v>123</v>
+      <c r="AM37" s="22" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="38" ht="18">
       <c r="A38" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C38" s="16"/>
       <c r="D38" s="16"/>
@@ -5225,44 +5335,47 @@
       <c r="AD38" s="17">
         <v>148.28999999999999</v>
       </c>
-      <c r="AE38" s="19">
-        <f>MIN(C38:AD38)</f>
+      <c r="AE38" s="17">
+        <v>149.99000000000001</v>
+      </c>
+      <c r="AF38" s="19">
+        <f>MIN(C38:AE38)</f>
         <v>144.94999999999999</v>
       </c>
-      <c r="AF38" s="20">
-        <f>MAX(C38:AD38)</f>
+      <c r="AG38" s="20">
+        <f>MAX(C38:AE38)</f>
         <v>168.28999999999999</v>
       </c>
-      <c r="AG38" s="20">
-        <f>AVERAGE(C38:AD38)</f>
-        <v>154.28</v>
-      </c>
       <c r="AH38" s="20">
-        <f>AVERAGE(Q38:AD38)</f>
-        <v>154.28857142857143</v>
-      </c>
-      <c r="AI38" s="21">
-        <f>(AH38/AG38)-1</f>
-        <v>5.5557613244827664e-005</v>
+        <f>AVERAGE(C38:AE38)</f>
+        <v>154.02764705882353</v>
+      </c>
+      <c r="AI38" s="20">
+        <f>AVERAGE(Q38:AE38)</f>
+        <v>154.00199999999998</v>
       </c>
       <c r="AJ38" s="21">
-        <f>(AH38/AE38)-1</f>
-        <v>6.4426156802838586e-002</v>
+        <f>(AI38/AH38)-1</f>
+        <v>-1.665094501752673e-004</v>
       </c>
       <c r="AK38" s="21">
-        <f>(AF38/AE38)-1</f>
+        <f>(AI38/AF38)-1</f>
+        <v>6.2449120386339985e-002</v>
+      </c>
+      <c r="AL38" s="21">
+        <f>(AG38/AF38)-1</f>
         <v>0.16102104173853049</v>
       </c>
-      <c r="AL38" s="22" t="s">
-        <v>125</v>
+      <c r="AM38" s="22" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="39" ht="18">
       <c r="A39" s="25" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B39" s="26" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C39" s="28"/>
       <c r="D39" s="28"/>
@@ -5324,44 +5437,47 @@
       <c r="AD39" s="18">
         <v>189.99000000000001</v>
       </c>
-      <c r="AE39" s="19">
-        <f>MIN(C39:AD39)</f>
+      <c r="AE39" s="17">
+        <v>169</v>
+      </c>
+      <c r="AF39" s="19">
+        <f>MIN(C39:AE39)</f>
         <v>144</v>
       </c>
-      <c r="AF39" s="20">
-        <f>MAX(C39:AD39)</f>
+      <c r="AG39" s="20">
+        <f>MAX(C39:AE39)</f>
         <v>199.94999999999999</v>
       </c>
-      <c r="AG39" s="20">
-        <f>AVERAGE(C39:AD39)</f>
-        <v>180.9425</v>
-      </c>
       <c r="AH39" s="20">
-        <f>AVERAGE(Q39:AD39)</f>
-        <v>180.94642857142858</v>
-      </c>
-      <c r="AI39" s="21">
-        <f>(AH39/AG39)-1</f>
-        <v>2.1711711889693674e-005</v>
+        <f>AVERAGE(C39:AE39)</f>
+        <v>180.24000000000001</v>
+      </c>
+      <c r="AI39" s="20">
+        <f>AVERAGE(Q39:AE39)</f>
+        <v>180.15000000000001</v>
       </c>
       <c r="AJ39" s="21">
-        <f>(AH39/AE39)-1</f>
-        <v>0.25657242063492069</v>
+        <f>(AI39/AH39)-1</f>
+        <v>-4.9933422103864977e-004</v>
       </c>
       <c r="AK39" s="21">
-        <f>(AF39/AE39)-1</f>
+        <f>(AI39/AF39)-1</f>
+        <v>0.25104166666666661</v>
+      </c>
+      <c r="AL39" s="21">
+        <f>(AG39/AF39)-1</f>
         <v>0.38854166666666656</v>
       </c>
-      <c r="AL39" s="22" t="s">
-        <v>127</v>
+      <c r="AM39" s="22" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="40" ht="18">
       <c r="A40" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C40" s="16"/>
       <c r="D40" s="16"/>
@@ -5386,7 +5502,7 @@
         <v>31941.080000000002</v>
       </c>
       <c r="M40" s="16" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N40" s="17"/>
       <c r="O40" s="16"/>
@@ -5405,44 +5521,45 @@
       <c r="AB40" s="16"/>
       <c r="AC40" s="16"/>
       <c r="AD40" s="16"/>
-      <c r="AE40" s="19">
-        <f>MIN(C40:AD40)</f>
+      <c r="AE40" s="16"/>
+      <c r="AF40" s="19">
+        <f>MIN(C40:AE40)</f>
         <v>30731.380000000001</v>
       </c>
-      <c r="AF40" s="20">
-        <f>MAX(C40:AD40)</f>
+      <c r="AG40" s="20">
+        <f>MAX(C40:AE40)</f>
         <v>32790.889999999999</v>
       </c>
-      <c r="AG40" s="20">
-        <f>AVERAGE(C40:AD40)</f>
+      <c r="AH40" s="20">
+        <f>AVERAGE(C40:AE40)</f>
         <v>31912.133333333331</v>
       </c>
-      <c r="AH40" s="20" t="e">
-        <f>AVERAGE(Q40:AD40)</f>
+      <c r="AI40" s="20" t="e">
+        <f>AVERAGE(Q40:AE40)</f>
         <v>#NUM!</v>
       </c>
-      <c r="AI40" s="21" t="e">
-        <f>(AH40/AG40)-1</f>
+      <c r="AJ40" s="21" t="e">
+        <f>(AI40/AH40)-1</f>
         <v>#NUM!</v>
       </c>
-      <c r="AJ40" s="21" t="e">
-        <f>(AH40/AE40)-1</f>
+      <c r="AK40" s="21" t="e">
+        <f>(AI40/AF40)-1</f>
         <v>#NUM!</v>
       </c>
-      <c r="AK40" s="21">
-        <f>(AF40/AE40)-1</f>
+      <c r="AL40" s="21">
+        <f>(AG40/AF40)-1</f>
         <v>6.7016515366377982e-002</v>
       </c>
-      <c r="AL40" s="22" t="s">
-        <v>130</v>
+      <c r="AM40" s="22" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="41" ht="18">
       <c r="A41" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C41" s="16"/>
       <c r="D41" s="16"/>
@@ -5474,7 +5591,7 @@
         <v>721.67999999999995</v>
       </c>
       <c r="T41" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="U41" s="18">
         <v>1164</v>
@@ -5498,7 +5615,7 @@
         <v>1360.8</v>
       </c>
       <c r="AB41" s="35" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AC41" s="30">
         <v>1360.8</v>
@@ -5506,44 +5623,47 @@
       <c r="AD41" s="30">
         <v>1360.8</v>
       </c>
-      <c r="AE41" s="19">
-        <f>MIN(C41:AD41)</f>
+      <c r="AE41" s="30">
+        <v>1360.8</v>
+      </c>
+      <c r="AF41" s="19">
+        <f>MIN(C41:AE41)</f>
         <v>642.82000000000005</v>
       </c>
-      <c r="AF41" s="20">
-        <f>MAX(C41:AD41)</f>
+      <c r="AG41" s="20">
+        <f>MAX(C41:AE41)</f>
         <v>1360.8</v>
       </c>
-      <c r="AG41" s="20">
-        <f>AVERAGE(C41:AD41)</f>
-        <v>1025.517333333333</v>
-      </c>
       <c r="AH41" s="20">
-        <f>AVERAGE(Q41:AD41)</f>
-        <v>1114.6199999999999</v>
-      </c>
-      <c r="AI41" s="21">
-        <f>(AH41/AG41)-1</f>
-        <v>8.6885578400755392e-002</v>
+        <f>AVERAGE(C41:AE41)</f>
+        <v>1046.4724999999999</v>
+      </c>
+      <c r="AI41" s="20">
+        <f>AVERAGE(Q41:AE41)</f>
+        <v>1133.5569230769229</v>
       </c>
       <c r="AJ41" s="21">
-        <f>(AH41/AE41)-1</f>
-        <v>0.73395351731433345</v>
+        <f>(AI41/AH41)-1</f>
+        <v>8.3217115668995589e-002</v>
       </c>
       <c r="AK41" s="21">
-        <f>(AF41/AE41)-1</f>
+        <f>(AI41/AF41)-1</f>
+        <v>0.76341265529529689</v>
+      </c>
+      <c r="AL41" s="21">
+        <f>(AG41/AF41)-1</f>
         <v>1.1169223110668614</v>
       </c>
-      <c r="AL41" s="22" t="s">
-        <v>133</v>
+      <c r="AM41" s="22" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="42" ht="18">
       <c r="A42" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C42" s="16"/>
       <c r="D42" s="16"/>
@@ -5599,7 +5719,7 @@
         <v>2171.4000000000001</v>
       </c>
       <c r="AB42" s="35" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AC42" s="30">
         <v>2171.4000000000001</v>
@@ -5607,44 +5727,47 @@
       <c r="AD42" s="30">
         <v>2171.4000000000001</v>
       </c>
-      <c r="AE42" s="19">
-        <f>MIN(C42:AD42)</f>
+      <c r="AE42" s="30">
+        <v>2171.4000000000001</v>
+      </c>
+      <c r="AF42" s="19">
+        <f>MIN(C42:AE42)</f>
         <v>1151.71</v>
       </c>
-      <c r="AF42" s="20">
-        <f>MAX(C42:AD42)</f>
+      <c r="AG42" s="20">
+        <f>MAX(C42:AE42)</f>
         <v>2171.4000000000001</v>
       </c>
-      <c r="AG42" s="20">
-        <f>AVERAGE(C42:AD42)</f>
-        <v>1768.7337500000003</v>
-      </c>
       <c r="AH42" s="20">
-        <f>AVERAGE(Q42:AD42)</f>
-        <v>1901.2800000000004</v>
-      </c>
-      <c r="AI42" s="21">
-        <f>(AH42/AG42)-1</f>
-        <v>7.4938497668176396e-002</v>
+        <f>AVERAGE(C42:AE42)</f>
+        <v>1792.4200000000003</v>
+      </c>
+      <c r="AI42" s="20">
+        <f>AVERAGE(Q42:AE42)</f>
+        <v>1920.5742857142864</v>
       </c>
       <c r="AJ42" s="21">
-        <f>(AH42/AE42)-1</f>
-        <v>0.65083224075505153</v>
+        <f>(AI42/AH42)-1</f>
+        <v>7.1497911044446028e-002</v>
       </c>
       <c r="AK42" s="21">
-        <f>(AF42/AE42)-1</f>
+        <f>(AI42/AF42)-1</f>
+        <v>0.6675849699267058</v>
+      </c>
+      <c r="AL42" s="21">
+        <f>(AG42/AF42)-1</f>
         <v>0.88537044915820817</v>
       </c>
-      <c r="AL42" s="22" t="s">
-        <v>133</v>
+      <c r="AM42" s="22" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="43" ht="18">
       <c r="A43" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C43" s="16"/>
       <c r="D43" s="16"/>
@@ -5679,73 +5802,76 @@
         <v>3876</v>
       </c>
       <c r="U43" s="35" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="V43" s="35" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="W43" s="35" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="X43" s="35" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Y43" s="35" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Z43" s="35" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AA43" s="35" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AB43" s="35" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AC43" s="35" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AD43" s="35" t="s">
-        <v>49</v>
-      </c>
-      <c r="AE43" s="19">
-        <f>MIN(C43:AD43)</f>
+        <v>50</v>
+      </c>
+      <c r="AE43" s="35" t="s">
+        <v>50</v>
+      </c>
+      <c r="AF43" s="19">
+        <f>MIN(C43:AE43)</f>
         <v>2159.8299999999999</v>
       </c>
-      <c r="AF43" s="20">
-        <f>MAX(C43:AD43)</f>
+      <c r="AG43" s="20">
+        <f>MAX(C43:AE43)</f>
         <v>3876</v>
       </c>
-      <c r="AG43" s="20">
-        <f>AVERAGE(C43:AD43)</f>
+      <c r="AH43" s="20">
+        <f>AVERAGE(C43:AE43)</f>
         <v>2544.02</v>
       </c>
-      <c r="AH43" s="20">
-        <f>AVERAGE(Q43:AD43)</f>
+      <c r="AI43" s="20">
+        <f>AVERAGE(Q43:AE43)</f>
         <v>2771.3400000000001</v>
       </c>
-      <c r="AI43" s="21">
-        <f>(AH43/AG43)-1</f>
+      <c r="AJ43" s="21">
+        <f>(AI43/AH43)-1</f>
         <v>8.9354643438337877e-002</v>
       </c>
-      <c r="AJ43" s="21">
-        <f>(AH43/AE43)-1</f>
+      <c r="AK43" s="21">
+        <f>(AI43/AF43)-1</f>
         <v>0.28312876476389359</v>
       </c>
-      <c r="AK43" s="21">
-        <f>(AF43/AE43)-1</f>
+      <c r="AL43" s="21">
+        <f>(AG43/AF43)-1</f>
         <v>0.79458568498446636</v>
       </c>
-      <c r="AL43" s="22" t="s">
-        <v>133</v>
+      <c r="AM43" s="22" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="44" ht="18">
       <c r="A44" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C44" s="16"/>
       <c r="D44" s="16"/>
@@ -5801,7 +5927,7 @@
         <v>2804.7600000000002</v>
       </c>
       <c r="AB44" s="35" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AC44" s="30">
         <v>2804.7600000000002</v>
@@ -5809,44 +5935,47 @@
       <c r="AD44" s="30">
         <v>2804.7600000000002</v>
       </c>
-      <c r="AE44" s="19">
-        <f>MIN(C44:AD44)</f>
+      <c r="AE44" s="30">
+        <v>2804.7600000000002</v>
+      </c>
+      <c r="AF44" s="19">
+        <f>MIN(C44:AE44)</f>
         <v>1310.1800000000001</v>
       </c>
-      <c r="AF44" s="20">
-        <f>MAX(C44:AD44)</f>
+      <c r="AG44" s="20">
+        <f>MAX(C44:AE44)</f>
         <v>2804.7600000000002</v>
       </c>
-      <c r="AG44" s="20">
-        <f>AVERAGE(C44:AD44)</f>
-        <v>2016.6237500000002</v>
-      </c>
       <c r="AH44" s="20">
-        <f>AVERAGE(Q44:AD44)</f>
-        <v>2178.0461538461541</v>
-      </c>
-      <c r="AI44" s="21">
-        <f>(AH44/AG44)-1</f>
-        <v>8.0045870651951789e-002</v>
+        <f>AVERAGE(C44:AE44)</f>
+        <v>2062.9847058823534</v>
+      </c>
+      <c r="AI44" s="20">
+        <f>AVERAGE(Q44:AE44)</f>
+        <v>2222.8114285714291</v>
       </c>
       <c r="AJ44" s="21">
-        <f>(AH44/AE44)-1</f>
-        <v>0.66240223011048394</v>
+        <f>(AI44/AH44)-1</f>
+        <v>7.7473537362322098e-002</v>
       </c>
       <c r="AK44" s="21">
-        <f>(AF44/AE44)-1</f>
+        <f>(AI44/AF44)-1</f>
+        <v>0.6965695008101398</v>
+      </c>
+      <c r="AL44" s="21">
+        <f>(AG44/AF44)-1</f>
         <v>1.1407440199056618</v>
       </c>
-      <c r="AL44" s="22" t="s">
-        <v>133</v>
+      <c r="AM44" s="22" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="45" ht="18">
       <c r="A45" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C45" s="16"/>
       <c r="D45" s="16"/>
@@ -5898,44 +6027,47 @@
       <c r="AD45" s="18">
         <v>1592.6400000000001</v>
       </c>
-      <c r="AE45" s="19">
-        <f>MIN(C45:AD45)</f>
+      <c r="AE45" s="18">
         <v>1592.6400000000001</v>
       </c>
-      <c r="AF45" s="20">
-        <f>MAX(C45:AD45)</f>
+      <c r="AF45" s="19">
+        <f>MIN(C45:AE45)</f>
+        <v>1592.6400000000001</v>
+      </c>
+      <c r="AG45" s="20">
+        <f>MAX(C45:AE45)</f>
         <v>1896</v>
       </c>
-      <c r="AG45" s="20">
-        <f>AVERAGE(C45:AD45)</f>
-        <v>1647.7963636363636</v>
-      </c>
       <c r="AH45" s="20">
-        <f>AVERAGE(Q45:AD45)</f>
-        <v>1647.7963636363636</v>
-      </c>
-      <c r="AI45" s="21">
-        <f>(AH45/AG45)-1</f>
+        <f>AVERAGE(C45:AE45)</f>
+        <v>1643.1999999999998</v>
+      </c>
+      <c r="AI45" s="20">
+        <f>AVERAGE(Q45:AE45)</f>
+        <v>1643.1999999999998</v>
+      </c>
+      <c r="AJ45" s="21">
+        <f>(AI45/AH45)-1</f>
         <v>0</v>
       </c>
-      <c r="AJ45" s="21">
-        <f>(AH45/AE45)-1</f>
-        <v>3.463203463203457e-002</v>
-      </c>
       <c r="AK45" s="21">
-        <f>(AF45/AE45)-1</f>
+        <f>(AI45/AF45)-1</f>
+        <v>3.1746031746031633e-002</v>
+      </c>
+      <c r="AL45" s="21">
+        <f>(AG45/AF45)-1</f>
         <v>0.19047619047619047</v>
       </c>
-      <c r="AL45" s="22" t="s">
-        <v>133</v>
+      <c r="AM45" s="22" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="46" ht="18">
       <c r="A46" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C46" s="16"/>
       <c r="D46" s="16"/>
@@ -5967,13 +6099,13 @@
         <v>1628.6199999999999</v>
       </c>
       <c r="T46" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="U46" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="V46" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="W46" s="18">
         <v>1985.76</v>
@@ -5985,7 +6117,7 @@
         <v>1985.76</v>
       </c>
       <c r="Z46" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AA46" s="18">
         <v>1985.76</v>
@@ -5994,49 +6126,52 @@
         <v>1985.76</v>
       </c>
       <c r="AC46" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AD46" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="AE46" s="19">
-        <f>MIN(C46:AD46)</f>
+        <v>50</v>
+      </c>
+      <c r="AE46" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="AF46" s="19">
+        <f>MIN(C46:AE46)</f>
         <v>1480.5599999999999</v>
       </c>
-      <c r="AF46" s="20">
-        <f>MAX(C46:AD46)</f>
+      <c r="AG46" s="20">
+        <f>MAX(C46:AE46)</f>
         <v>1985.76</v>
       </c>
-      <c r="AG46" s="20">
-        <f>AVERAGE(C46:AD46)</f>
+      <c r="AH46" s="20">
+        <f>AVERAGE(C46:AE46)</f>
         <v>1764.0363636363634</v>
       </c>
-      <c r="AH46" s="20">
-        <f>AVERAGE(Q46:AD46)</f>
+      <c r="AI46" s="20">
+        <f>AVERAGE(Q46:AE46)</f>
         <v>1851.8325</v>
       </c>
-      <c r="AI46" s="21">
-        <f>(AH46/AG46)-1</f>
+      <c r="AJ46" s="21">
+        <f>(AI46/AH46)-1</f>
         <v>4.9770026385768329e-002</v>
       </c>
-      <c r="AJ46" s="21">
-        <f>(AH46/AE46)-1</f>
+      <c r="AK46" s="21">
+        <f>(AI46/AF46)-1</f>
         <v>0.25076491327605765</v>
       </c>
-      <c r="AK46" s="21">
-        <f>(AF46/AE46)-1</f>
+      <c r="AL46" s="21">
+        <f>(AG46/AF46)-1</f>
         <v>0.34122224023342529</v>
       </c>
-      <c r="AL46" s="22" t="s">
-        <v>133</v>
+      <c r="AM46" s="22" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="47" ht="18">
       <c r="A47" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C47" s="16"/>
       <c r="D47" s="16">
@@ -6068,41 +6203,42 @@
       <c r="AB47" s="16"/>
       <c r="AC47" s="16"/>
       <c r="AD47" s="16"/>
-      <c r="AE47" s="19">
-        <f>MIN(C47:AD47)</f>
+      <c r="AE47" s="16"/>
+      <c r="AF47" s="19">
+        <f>MIN(C47:AE47)</f>
         <v>339.45999999999998</v>
       </c>
-      <c r="AF47" s="20">
-        <f>MAX(C47:AD47)</f>
+      <c r="AG47" s="20">
+        <f>MAX(C47:AE47)</f>
         <v>339.45999999999998</v>
       </c>
-      <c r="AG47" s="20">
-        <f>AVERAGE(C47:AD47)</f>
+      <c r="AH47" s="20">
+        <f>AVERAGE(C47:AE47)</f>
         <v>339.45999999999998</v>
       </c>
-      <c r="AH47" s="20" t="e">
-        <f>AVERAGE(Q47:AD47)</f>
+      <c r="AI47" s="20" t="e">
+        <f>AVERAGE(Q47:AE47)</f>
         <v>#NUM!</v>
       </c>
-      <c r="AI47" s="21" t="e">
-        <f>(AH47/AG47)-1</f>
+      <c r="AJ47" s="21" t="e">
+        <f>(AI47/AH47)-1</f>
         <v>#NUM!</v>
       </c>
-      <c r="AJ47" s="21" t="e">
-        <f>(AH47/AE47)-1</f>
+      <c r="AK47" s="21" t="e">
+        <f>(AI47/AF47)-1</f>
         <v>#NUM!</v>
       </c>
-      <c r="AK47" s="21">
-        <f>(AF47/AE47)-1</f>
+      <c r="AL47" s="21">
+        <f>(AG47/AF47)-1</f>
         <v>0</v>
       </c>
     </row>
     <row r="48" ht="18">
       <c r="A48" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C48" s="16"/>
       <c r="D48" s="16"/>
@@ -6180,44 +6316,47 @@
       <c r="AD48" s="16">
         <v>378.99000000000001</v>
       </c>
-      <c r="AE48" s="19">
-        <f>MIN(C48:AD48)</f>
+      <c r="AE48" s="16">
         <v>378.99000000000001</v>
       </c>
-      <c r="AF48" s="20">
-        <f>MAX(C48:AD48)</f>
+      <c r="AF48" s="19">
+        <f>MIN(C48:AE48)</f>
         <v>378.99000000000001</v>
       </c>
       <c r="AG48" s="20">
-        <f>AVERAGE(C48:AD48)</f>
+        <f>MAX(C48:AE48)</f>
+        <v>378.99000000000001</v>
+      </c>
+      <c r="AH48" s="20">
+        <f>AVERAGE(C48:AE48)</f>
         <v>378.98999999999984</v>
       </c>
-      <c r="AH48" s="20">
-        <f>AVERAGE(Q48:AD48)</f>
+      <c r="AI48" s="20">
+        <f>AVERAGE(Q48:AE48)</f>
         <v>378.9899999999999</v>
       </c>
-      <c r="AI48" s="21">
-        <f>(AH48/AG48)-1</f>
+      <c r="AJ48" s="21">
+        <f>(AI48/AH48)-1</f>
         <v>2.2204460492503131e-016</v>
       </c>
-      <c r="AJ48" s="21">
-        <f>(AH48/AE48)-1</f>
+      <c r="AK48" s="21">
+        <f>(AI48/AF48)-1</f>
         <v>-3.3306690738754696e-016</v>
       </c>
-      <c r="AK48" s="21">
-        <f>(AF48/AE48)-1</f>
+      <c r="AL48" s="21">
+        <f>(AG48/AF48)-1</f>
         <v>0</v>
       </c>
-      <c r="AL48" s="22" t="s">
-        <v>144</v>
+      <c r="AM48" s="22" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="49" ht="18">
       <c r="A49" s="25" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B49" s="26" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C49" s="28"/>
       <c r="D49" s="28"/>
@@ -6295,44 +6434,47 @@
       <c r="AD49" s="30">
         <v>173.03999999999999</v>
       </c>
-      <c r="AE49" s="19">
-        <f>MIN(C49:AD49)</f>
+      <c r="AE49" s="30">
+        <v>173.03999999999999</v>
+      </c>
+      <c r="AF49" s="19">
+        <f>MIN(C49:AE49)</f>
         <v>88.329999999999998</v>
       </c>
-      <c r="AF49" s="20">
-        <f>MAX(C49:AD49)</f>
+      <c r="AG49" s="20">
+        <f>MAX(C49:AE49)</f>
         <v>191.19</v>
       </c>
-      <c r="AG49" s="20">
-        <f>AVERAGE(C49:AD49)</f>
-        <v>123.30500000000001</v>
-      </c>
       <c r="AH49" s="20">
-        <f>AVERAGE(Q49:AD49)</f>
-        <v>148.28714285714287</v>
-      </c>
-      <c r="AI49" s="21">
-        <f>(AH49/AG49)-1</f>
-        <v>0.20260445932559801</v>
+        <f>AVERAGE(C49:AE49)</f>
+        <v>125.29440000000001</v>
+      </c>
+      <c r="AI49" s="20">
+        <f>AVERAGE(Q49:AE49)</f>
+        <v>149.93733333333333</v>
       </c>
       <c r="AJ49" s="21">
-        <f>(AH49/AE49)-1</f>
-        <v>0.67878572237227286</v>
+        <f>(AI49/AH49)-1</f>
+        <v>0.19668024535281159</v>
       </c>
       <c r="AK49" s="21">
-        <f>(AF49/AE49)-1</f>
+        <f>(AI49/AF49)-1</f>
+        <v>0.69746782897467829</v>
+      </c>
+      <c r="AL49" s="21">
+        <f>(AG49/AF49)-1</f>
         <v>1.1644967734631497</v>
       </c>
-      <c r="AL49" s="22" t="s">
-        <v>147</v>
+      <c r="AM49" s="22" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="50" ht="18">
       <c r="A50" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C50" s="16"/>
       <c r="D50" s="16">
@@ -6412,44 +6554,47 @@
       <c r="AD50" s="35">
         <v>32.460000000000001</v>
       </c>
-      <c r="AE50" s="19">
-        <f>MIN(C50:AD50)</f>
+      <c r="AE50" s="35">
+        <v>36.189999999999998</v>
+      </c>
+      <c r="AF50" s="19">
+        <f>MIN(C50:AE50)</f>
         <v>29.149999999999999</v>
       </c>
-      <c r="AF50" s="20">
-        <f>MAX(C50:AD50)</f>
+      <c r="AG50" s="20">
+        <f>MAX(C50:AE50)</f>
         <v>44.979999999999997</v>
       </c>
-      <c r="AG50" s="20">
-        <f>AVERAGE(C50:AD50)</f>
-        <v>36.385199999999998</v>
-      </c>
       <c r="AH50" s="20">
-        <f>AVERAGE(Q50:AD50)</f>
-        <v>36.306428571428569</v>
-      </c>
-      <c r="AI50" s="21">
-        <f>(AH50/AG50)-1</f>
-        <v>-2.164930481938554e-003</v>
+        <f>AVERAGE(C50:AE50)</f>
+        <v>36.377692307692307</v>
+      </c>
+      <c r="AI50" s="20">
+        <f>AVERAGE(Q50:AE50)</f>
+        <v>36.298666666666669</v>
       </c>
       <c r="AJ50" s="21">
-        <f>(AH50/AE50)-1</f>
-        <v>0.2455035530507228</v>
+        <f>(AI50/AH50)-1</f>
+        <v>-2.1723654254155456e-003</v>
       </c>
       <c r="AK50" s="21">
-        <f>(AF50/AE50)-1</f>
+        <f>(AI50/AF50)-1</f>
+        <v>0.24523727844482579</v>
+      </c>
+      <c r="AL50" s="21">
+        <f>(AG50/AF50)-1</f>
         <v>0.54305317324185243</v>
       </c>
-      <c r="AL50" s="22" t="s">
-        <v>150</v>
+      <c r="AM50" s="22" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="51" ht="18">
       <c r="A51" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C51" s="16"/>
       <c r="D51" s="16">
@@ -6520,53 +6665,56 @@
       <c r="AA51" s="35">
         <v>30.989999999999998</v>
       </c>
-      <c r="AB51" s="35">
+      <c r="AB51" s="34">
         <v>36.100000000000001</v>
       </c>
-      <c r="AC51" s="35">
+      <c r="AC51" s="34">
         <v>36.100000000000001</v>
       </c>
-      <c r="AD51" s="35">
+      <c r="AD51" s="34">
         <v>36.140000000000001</v>
       </c>
-      <c r="AE51" s="19">
-        <f>MIN(C51:AD51)</f>
+      <c r="AE51" s="35">
+        <v>30.989999999999998</v>
+      </c>
+      <c r="AF51" s="19">
+        <f>MIN(C51:AE51)</f>
         <v>25.989999999999998</v>
       </c>
-      <c r="AF51" s="20">
-        <f>MAX(C51:AD51)</f>
+      <c r="AG51" s="20">
+        <f>MAX(C51:AE51)</f>
         <v>42</v>
       </c>
-      <c r="AG51" s="20">
-        <f>AVERAGE(C51:AD51)</f>
-        <v>32.3232</v>
-      </c>
       <c r="AH51" s="20">
-        <f>AVERAGE(Q51:AD51)</f>
-        <v>33.132857142857155</v>
-      </c>
-      <c r="AI51" s="21">
-        <f>(AH51/AG51)-1</f>
-        <v>2.5048792905936201e-002</v>
+        <f>AVERAGE(C51:AE51)</f>
+        <v>32.27192307692308</v>
+      </c>
+      <c r="AI51" s="20">
+        <f>AVERAGE(Q51:AE51)</f>
+        <v>32.990000000000009</v>
       </c>
       <c r="AJ51" s="21">
-        <f>(AH51/AE51)-1</f>
-        <v>0.2748309789479475</v>
+        <f>(AI51/AH51)-1</f>
+        <v>2.2250825318507639e-002</v>
       </c>
       <c r="AK51" s="21">
-        <f>(AF51/AE51)-1</f>
+        <f>(AI51/AF51)-1</f>
+        <v>0.26933435936898853</v>
+      </c>
+      <c r="AL51" s="21">
+        <f>(AG51/AF51)-1</f>
         <v>0.61600615621392851</v>
       </c>
-      <c r="AL51" s="22" t="s">
-        <v>153</v>
+      <c r="AM51" s="22" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="52" ht="18">
       <c r="A52" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C52" s="16"/>
       <c r="D52" s="16">
@@ -6646,44 +6794,47 @@
       <c r="AD52" s="32">
         <v>34.719999999999999</v>
       </c>
-      <c r="AE52" s="19">
-        <f>MIN(C52:AD52)</f>
+      <c r="AE52" s="32">
+        <v>34.719999999999999</v>
+      </c>
+      <c r="AF52" s="19">
+        <f>MIN(C52:AE52)</f>
         <v>21.690000000000001</v>
       </c>
-      <c r="AF52" s="20">
-        <f>MAX(C52:AD52)</f>
+      <c r="AG52" s="20">
+        <f>MAX(C52:AE52)</f>
         <v>43.990000000000002</v>
       </c>
-      <c r="AG52" s="20">
-        <f>AVERAGE(C52:AD52)</f>
-        <v>29.063999999999993</v>
-      </c>
       <c r="AH52" s="20">
-        <f>AVERAGE(Q52:AD52)</f>
-        <v>27.913571428571426</v>
-      </c>
-      <c r="AI52" s="21">
-        <f>(AH52/AG52)-1</f>
-        <v>-3.9582596044197893e-002</v>
+        <f>AVERAGE(C52:AE52)</f>
+        <v>29.281538461538453</v>
+      </c>
+      <c r="AI52" s="20">
+        <f>AVERAGE(Q52:AE52)</f>
+        <v>28.367333333333331</v>
       </c>
       <c r="AJ52" s="21">
-        <f>(AH52/AE52)-1</f>
-        <v>0.28693275373773286</v>
+        <f>(AI52/AH52)-1</f>
+        <v>-3.122121228042507e-002</v>
       </c>
       <c r="AK52" s="21">
-        <f>(AF52/AE52)-1</f>
+        <f>(AI52/AF52)-1</f>
+        <v>0.30785308129706457</v>
+      </c>
+      <c r="AL52" s="21">
+        <f>(AG52/AF52)-1</f>
         <v>1.0281235592438911</v>
       </c>
-      <c r="AL52" s="22" t="s">
-        <v>156</v>
+      <c r="AM52" s="22" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="53" ht="54">
       <c r="A53" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C53" s="16"/>
       <c r="D53" s="16"/>
@@ -6704,10 +6855,10 @@
         <v>1714.0799999999999</v>
       </c>
       <c r="K53" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L53" s="16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M53" s="24">
         <v>1449.28</v>
@@ -6763,44 +6914,47 @@
       <c r="AD53" s="30">
         <v>2407.79</v>
       </c>
-      <c r="AE53" s="19">
-        <f>MIN(C53:AD53)</f>
+      <c r="AE53" s="30">
+        <v>2407.79</v>
+      </c>
+      <c r="AF53" s="19">
+        <f>MIN(C53:AE53)</f>
         <v>1449.28</v>
       </c>
-      <c r="AF53" s="20">
-        <f>MAX(C53:AD53)</f>
+      <c r="AG53" s="20">
+        <f>MAX(C53:AE53)</f>
         <v>2407.79</v>
       </c>
-      <c r="AG53" s="20">
-        <f>AVERAGE(C53:AD53)</f>
-        <v>1750.8647826086954</v>
-      </c>
       <c r="AH53" s="20">
-        <f>AVERAGE(Q53:AD53)</f>
-        <v>1770.5642857142861</v>
-      </c>
-      <c r="AI53" s="21">
-        <f>(AH53/AG53)-1</f>
-        <v>1.1251298958814937e-002</v>
+        <f>AVERAGE(C53:AE53)</f>
+        <v>1778.2366666666665</v>
+      </c>
+      <c r="AI53" s="20">
+        <f>AVERAGE(Q53:AE53)</f>
+        <v>1813.0460000000005</v>
       </c>
       <c r="AJ53" s="21">
-        <f>(AH53/AE53)-1</f>
-        <v>0.22168544774942456</v>
+        <f>(AI53/AH53)-1</f>
+        <v>1.9575197152235546e-002</v>
       </c>
       <c r="AK53" s="21">
-        <f>(AF53/AE53)-1</f>
+        <f>(AI53/AF53)-1</f>
+        <v>0.25099773680724269</v>
+      </c>
+      <c r="AL53" s="21">
+        <f>(AG53/AF53)-1</f>
         <v>0.66136978361669252</v>
       </c>
-      <c r="AL53" s="1" t="s">
-        <v>158</v>
+      <c r="AM53" s="1" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="54" ht="18">
       <c r="A54" s="25" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B54" s="26" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C54" s="28"/>
       <c r="D54" s="28"/>
@@ -6878,44 +7032,47 @@
       <c r="AD54" s="35">
         <v>36.990000000000002</v>
       </c>
-      <c r="AE54" s="19">
-        <f>MIN(C54:AD54)</f>
+      <c r="AE54" s="35">
+        <v>36.990000000000002</v>
+      </c>
+      <c r="AF54" s="19">
+        <f>MIN(C54:AE54)</f>
         <v>30.989999999999998</v>
       </c>
-      <c r="AF54" s="20">
-        <f>MAX(C54:AD54)</f>
+      <c r="AG54" s="20">
+        <f>MAX(C54:AE54)</f>
         <v>43.990000000000002</v>
       </c>
-      <c r="AG54" s="20">
-        <f>AVERAGE(C54:AD54)</f>
-        <v>37.210416666666667</v>
-      </c>
       <c r="AH54" s="20">
-        <f>AVERAGE(Q54:AD54)</f>
-        <v>38.005714285714291</v>
-      </c>
-      <c r="AI54" s="21">
-        <f>(AH54/AG54)-1</f>
-        <v>2.137298343557803e-002</v>
+        <f>AVERAGE(C54:AE54)</f>
+        <v>37.201599999999999</v>
+      </c>
+      <c r="AI54" s="20">
+        <f>AVERAGE(Q54:AE54)</f>
+        <v>37.938000000000002</v>
       </c>
       <c r="AJ54" s="21">
-        <f>(AH54/AE54)-1</f>
-        <v>0.22638639192366217</v>
+        <f>(AI54/AH54)-1</f>
+        <v>1.9794847533439519e-002</v>
       </c>
       <c r="AK54" s="21">
-        <f>(AF54/AE54)-1</f>
+        <f>(AI54/AF54)-1</f>
+        <v>0.22420135527589569</v>
+      </c>
+      <c r="AL54" s="21">
+        <f>(AG54/AF54)-1</f>
         <v>0.41949015811552126</v>
       </c>
-      <c r="AL54" s="22" t="s">
-        <v>161</v>
+      <c r="AM54" s="22" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="55" ht="18">
       <c r="A55" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C55" s="16"/>
       <c r="D55" s="16"/>
@@ -6993,44 +7150,47 @@
       <c r="AD55" s="16">
         <v>89.950000000000003</v>
       </c>
-      <c r="AE55" s="19">
-        <f>MIN(C55:AD55)</f>
+      <c r="AE55" s="16">
+        <v>89.950000000000003</v>
+      </c>
+      <c r="AF55" s="19">
+        <f>MIN(C55:AE55)</f>
         <v>81.689999999999998</v>
       </c>
-      <c r="AF55" s="20">
-        <f>MAX(C55:AD55)</f>
+      <c r="AG55" s="20">
+        <f>MAX(C55:AE55)</f>
         <v>109.84999999999999</v>
       </c>
-      <c r="AG55" s="20">
-        <f>AVERAGE(C55:AD55)</f>
-        <v>88.665833333333353</v>
-      </c>
       <c r="AH55" s="20">
-        <f>AVERAGE(Q55:AD55)</f>
-        <v>87.382857142857148</v>
-      </c>
-      <c r="AI55" s="21">
-        <f>(AH55/AG55)-1</f>
-        <v>-1.4469792277854499e-002</v>
+        <f>AVERAGE(C55:AE55)</f>
+        <v>88.717200000000005</v>
+      </c>
+      <c r="AI55" s="20">
+        <f>AVERAGE(Q55:AE55)</f>
+        <v>87.554000000000016</v>
       </c>
       <c r="AJ55" s="21">
-        <f>(AH55/AE55)-1</f>
-        <v>6.968854379798195e-002</v>
+        <f>(AI55/AH55)-1</f>
+        <v>-1.3111324523316648e-002</v>
       </c>
       <c r="AK55" s="21">
-        <f>(AF55/AE55)-1</f>
+        <f>(AI55/AF55)-1</f>
+        <v>7.1783572040641674e-002</v>
+      </c>
+      <c r="AL55" s="21">
+        <f>(AG55/AF55)-1</f>
         <v>0.34471783572040637</v>
       </c>
-      <c r="AL55" s="1" t="s">
-        <v>164</v>
+      <c r="AM55" s="1" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="56" ht="18">
       <c r="A56" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C56" s="16"/>
       <c r="D56" s="16"/>
@@ -7110,44 +7270,47 @@
       <c r="AD56" s="33">
         <v>298.80000000000001</v>
       </c>
-      <c r="AE56" s="19">
-        <f>MIN(C56:AD56)</f>
+      <c r="AE56" s="35">
+        <v>309.05000000000001</v>
+      </c>
+      <c r="AF56" s="19">
+        <f>MIN(C56:AE56)</f>
         <v>298.80000000000001</v>
       </c>
-      <c r="AF56" s="20">
-        <f>MAX(C56:AD56)</f>
+      <c r="AG56" s="20">
+        <f>MAX(C56:AE56)</f>
         <v>309.05000000000001</v>
       </c>
-      <c r="AG56" s="20">
-        <f>AVERAGE(C56:AD56)</f>
-        <v>305.7700000000001</v>
-      </c>
       <c r="AH56" s="20">
-        <f>AVERAGE(Q56:AD56)</f>
-        <v>303.19285714285718</v>
-      </c>
-      <c r="AI56" s="21">
-        <f>(AH56/AG56)-1</f>
-        <v>-8.4283705306044121e-003</v>
+        <f>AVERAGE(C56:AE56)</f>
+        <v>305.89615384615394</v>
+      </c>
+      <c r="AI56" s="20">
+        <f>AVERAGE(Q56:AE56)</f>
+        <v>303.58333333333337</v>
       </c>
       <c r="AJ56" s="21">
-        <f>(AH56/AE56)-1</f>
-        <v>1.4701663798049491e-002</v>
+        <f>(AI56/AH56)-1</f>
+        <v>-7.5608028533230565e-003</v>
       </c>
       <c r="AK56" s="21">
-        <f>(AF56/AE56)-1</f>
+        <f>(AI56/AF56)-1</f>
+        <v>1.6008478357875999e-002</v>
+      </c>
+      <c r="AL56" s="21">
+        <f>(AG56/AF56)-1</f>
         <v>3.4303882195448443e-002</v>
       </c>
-      <c r="AL56" s="22" t="s">
-        <v>167</v>
+      <c r="AM56" s="22" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="57" ht="18">
       <c r="A57" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C57" s="16"/>
       <c r="D57" s="16"/>
@@ -7225,41 +7388,44 @@
       <c r="AD57" s="16">
         <v>108.98999999999999</v>
       </c>
-      <c r="AE57" s="19">
-        <f>MIN(C57:AD57)</f>
+      <c r="AE57" s="24">
         <v>100.44</v>
       </c>
-      <c r="AF57" s="20">
-        <f>MAX(C57:AD57)</f>
+      <c r="AF57" s="19">
+        <f>MIN(C57:AE57)</f>
+        <v>100.44</v>
+      </c>
+      <c r="AG57" s="20">
+        <f>MAX(C57:AE57)</f>
         <v>108.98999999999999</v>
       </c>
-      <c r="AG57" s="20">
-        <f>AVERAGE(C57:AD57)</f>
-        <v>107.56499999999998</v>
-      </c>
       <c r="AH57" s="20">
-        <f>AVERAGE(Q57:AD57)</f>
-        <v>106.54714285714286</v>
-      </c>
-      <c r="AI57" s="21">
-        <f>(AH57/AG57)-1</f>
-        <v>-9.4627168954318774e-003</v>
+        <f>AVERAGE(C57:AE57)</f>
+        <v>107.27999999999999</v>
+      </c>
+      <c r="AI57" s="20">
+        <f>AVERAGE(Q57:AE57)</f>
+        <v>106.14000000000001</v>
       </c>
       <c r="AJ57" s="21">
-        <f>(AH57/AE57)-1</f>
-        <v>6.0803891449052738e-002</v>
+        <f>(AI57/AH57)-1</f>
+        <v>-1.0626398210290544e-002</v>
       </c>
       <c r="AK57" s="21">
-        <f>(AF57/AE57)-1</f>
+        <f>(AI57/AF57)-1</f>
+        <v>5.675029868578263e-002</v>
+      </c>
+      <c r="AL57" s="21">
+        <f>(AG57/AF57)-1</f>
         <v>8.5125448028673834e-002</v>
       </c>
-      <c r="AL57" s="37" t="s">
-        <v>169</v>
+      <c r="AM57" s="37" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="58" ht="18">
       <c r="B58" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O58" s="16">
         <v>1.49</v>
@@ -7309,32 +7475,35 @@
       <c r="AD58" s="16">
         <v>1.99</v>
       </c>
-      <c r="AE58" s="19">
-        <f>MIN(C58:AD58)</f>
+      <c r="AE58" s="16">
+        <v>1.99</v>
+      </c>
+      <c r="AF58" s="19">
+        <f>MIN(C58:AE58)</f>
         <v>1.49</v>
       </c>
-      <c r="AF58" s="20">
-        <f>MAX(C58:AD58)</f>
+      <c r="AG58" s="20">
+        <f>MAX(C58:AE58)</f>
         <v>1.99</v>
       </c>
-      <c r="AG58" s="20">
-        <f>AVERAGE(C58:AD58)</f>
-        <v>1.8337499999999993</v>
-      </c>
       <c r="AH58" s="20">
-        <f>AVERAGE(Q58:AD58)</f>
-        <v>1.8828571428571423</v>
-      </c>
-      <c r="AI58" s="21">
-        <f>(AH58/AG58)-1</f>
-        <v>2.6779628006621925e-002</v>
+        <f>AVERAGE(C58:AE58)</f>
+        <v>1.8429411764705874</v>
+      </c>
+      <c r="AI58" s="20">
+        <f>AVERAGE(Q58:AE58)</f>
+        <v>1.8899999999999995</v>
       </c>
       <c r="AJ58" s="21">
-        <f>(AH58/AE58)-1</f>
-        <v>0.2636625119846594</v>
+        <f>(AI58/AH58)-1</f>
+        <v>2.5534631343760106e-002</v>
       </c>
       <c r="AK58" s="21">
-        <f>(AF58/AE58)-1</f>
+        <f>(AI58/AF58)-1</f>
+        <v>0.26845637583892579</v>
+      </c>
+      <c r="AL58" s="21">
+        <f>(AG58/AF58)-1</f>
         <v>0.33557046979865768</v>
       </c>
     </row>
@@ -7343,119 +7512,123 @@
       <c r="AB59" s="1"/>
       <c r="AC59" s="1"/>
       <c r="AD59" s="1"/>
-      <c r="AE59" s="2"/>
+      <c r="AE59" s="1"/>
       <c r="AF59" s="2"/>
       <c r="AG59" s="2"/>
       <c r="AH59" s="2"/>
       <c r="AI59" s="2"/>
       <c r="AJ59" s="2"/>
       <c r="AK59" s="2"/>
+      <c r="AL59" s="2"/>
     </row>
     <row r="60" ht="14.25">
       <c r="AA60" s="1"/>
       <c r="AB60" s="1"/>
       <c r="AC60" s="1"/>
       <c r="AD60" s="1"/>
-      <c r="AE60" s="2"/>
+      <c r="AE60" s="1"/>
       <c r="AF60" s="2"/>
       <c r="AG60" s="2"/>
       <c r="AH60" s="2"/>
       <c r="AI60" s="2"/>
       <c r="AJ60" s="2"/>
       <c r="AK60" s="2"/>
+      <c r="AL60" s="2"/>
     </row>
     <row r="61" ht="14.25">
       <c r="AA61" s="1"/>
       <c r="AB61" s="1"/>
       <c r="AC61" s="1"/>
       <c r="AD61" s="1"/>
-      <c r="AE61" s="2"/>
+      <c r="AE61" s="1"/>
       <c r="AF61" s="2"/>
       <c r="AG61" s="2"/>
       <c r="AH61" s="2"/>
       <c r="AI61" s="2"/>
       <c r="AJ61" s="2"/>
       <c r="AK61" s="2"/>
+      <c r="AL61" s="2"/>
     </row>
     <row r="62" ht="14.25">
       <c r="AA62" s="1"/>
       <c r="AB62" s="1"/>
       <c r="AC62" s="1"/>
       <c r="AD62" s="1"/>
-      <c r="AE62" s="2"/>
+      <c r="AE62" s="1"/>
       <c r="AF62" s="2"/>
       <c r="AG62" s="2"/>
       <c r="AH62" s="2"/>
       <c r="AI62" s="2"/>
       <c r="AJ62" s="2"/>
       <c r="AK62" s="2"/>
+      <c r="AL62" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="AE1:AE2"/>
     <mergeCell ref="AF1:AF2"/>
     <mergeCell ref="AG1:AG2"/>
     <mergeCell ref="AH1:AH2"/>
     <mergeCell ref="AI1:AI2"/>
     <mergeCell ref="AJ1:AJ2"/>
     <mergeCell ref="AK1:AK2"/>
+    <mergeCell ref="AL1:AL2"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="AL4"/>
-    <hyperlink r:id="rId2" ref="AL5"/>
-    <hyperlink r:id="rId3" ref="AL6"/>
-    <hyperlink r:id="rId4" ref="AL7"/>
-    <hyperlink r:id="rId5" ref="AL8"/>
-    <hyperlink r:id="rId6" ref="AL9"/>
-    <hyperlink r:id="rId7" ref="AL10"/>
-    <hyperlink r:id="rId8" ref="AL11"/>
-    <hyperlink r:id="rId9" ref="AL12"/>
-    <hyperlink r:id="rId10" ref="AL13"/>
-    <hyperlink r:id="rId11" ref="AL14"/>
-    <hyperlink r:id="rId12" ref="AL15"/>
-    <hyperlink r:id="rId13" ref="AL16"/>
-    <hyperlink r:id="rId14" ref="AL17"/>
-    <hyperlink r:id="rId15" ref="AL18"/>
-    <hyperlink r:id="rId16" ref="AL19"/>
-    <hyperlink r:id="rId17" ref="AL20"/>
-    <hyperlink r:id="rId18" ref="AL21"/>
-    <hyperlink r:id="rId19" ref="AL22"/>
-    <hyperlink r:id="rId20" ref="AL23"/>
-    <hyperlink r:id="rId21" ref="AL24"/>
-    <hyperlink r:id="rId22" ref="AL25"/>
-    <hyperlink r:id="rId23" ref="AL26"/>
-    <hyperlink r:id="rId24" ref="AL27"/>
-    <hyperlink r:id="rId25" ref="AL28"/>
-    <hyperlink r:id="rId26" ref="AL29"/>
-    <hyperlink r:id="rId27" ref="AL30"/>
-    <hyperlink r:id="rId28" ref="AL31"/>
-    <hyperlink r:id="rId29" ref="AL32"/>
-    <hyperlink r:id="rId30" ref="AL33"/>
-    <hyperlink r:id="rId31" ref="AL34"/>
-    <hyperlink r:id="rId32" ref="AL35"/>
-    <hyperlink r:id="rId33" ref="AL36"/>
-    <hyperlink r:id="rId34" ref="AL37"/>
-    <hyperlink r:id="rId35" ref="AL38"/>
-    <hyperlink r:id="rId36" ref="AL39"/>
-    <hyperlink r:id="rId37" ref="AL40"/>
-    <hyperlink r:id="rId38" ref="AL41"/>
-    <hyperlink r:id="rId38" ref="AL42"/>
-    <hyperlink r:id="rId38" ref="AL43"/>
-    <hyperlink r:id="rId38" ref="AL44"/>
-    <hyperlink r:id="rId38" ref="AL45"/>
-    <hyperlink r:id="rId38" ref="AL46"/>
-    <hyperlink r:id="rId39" ref="AL48"/>
-    <hyperlink r:id="rId40" ref="AL49"/>
-    <hyperlink r:id="rId41" ref="AL50"/>
-    <hyperlink r:id="rId42" ref="AL51"/>
-    <hyperlink r:id="rId43" ref="AL52"/>
-    <hyperlink r:id="rId44" ref="AL54"/>
-    <hyperlink r:id="rId45" ref="AL56"/>
-    <hyperlink r:id="rId46" ref="AL57"/>
+    <hyperlink r:id="rId1" ref="AM4"/>
+    <hyperlink r:id="rId2" ref="AM5"/>
+    <hyperlink r:id="rId3" ref="AM6"/>
+    <hyperlink r:id="rId4" ref="AM7"/>
+    <hyperlink r:id="rId5" ref="AM8"/>
+    <hyperlink r:id="rId6" ref="AM9"/>
+    <hyperlink r:id="rId7" ref="AM10"/>
+    <hyperlink r:id="rId8" ref="AM11"/>
+    <hyperlink r:id="rId9" ref="AM12"/>
+    <hyperlink r:id="rId10" ref="AM13"/>
+    <hyperlink r:id="rId11" ref="AM14"/>
+    <hyperlink r:id="rId12" ref="AM15"/>
+    <hyperlink r:id="rId13" ref="AM16"/>
+    <hyperlink r:id="rId14" ref="AM17"/>
+    <hyperlink r:id="rId15" ref="AM18"/>
+    <hyperlink r:id="rId16" ref="AM19"/>
+    <hyperlink r:id="rId17" ref="AM20"/>
+    <hyperlink r:id="rId18" ref="AM21"/>
+    <hyperlink r:id="rId19" ref="AM22"/>
+    <hyperlink r:id="rId20" ref="AM23"/>
+    <hyperlink r:id="rId21" ref="AM24"/>
+    <hyperlink r:id="rId22" ref="AM25"/>
+    <hyperlink r:id="rId23" ref="AM26"/>
+    <hyperlink r:id="rId24" ref="AM27"/>
+    <hyperlink r:id="rId25" ref="AM28"/>
+    <hyperlink r:id="rId26" ref="AM29"/>
+    <hyperlink r:id="rId27" ref="AM30"/>
+    <hyperlink r:id="rId28" ref="AM31"/>
+    <hyperlink r:id="rId29" ref="AM32"/>
+    <hyperlink r:id="rId30" ref="AM33"/>
+    <hyperlink r:id="rId31" ref="AM34"/>
+    <hyperlink r:id="rId32" ref="AM35"/>
+    <hyperlink r:id="rId33" ref="AM36"/>
+    <hyperlink r:id="rId34" ref="AM37"/>
+    <hyperlink r:id="rId35" ref="AM38"/>
+    <hyperlink r:id="rId36" ref="AM39"/>
+    <hyperlink r:id="rId37" ref="AM40"/>
+    <hyperlink r:id="rId38" ref="AM41"/>
+    <hyperlink r:id="rId38" ref="AM42"/>
+    <hyperlink r:id="rId38" ref="AM43"/>
+    <hyperlink r:id="rId38" ref="AM44"/>
+    <hyperlink r:id="rId38" ref="AM45"/>
+    <hyperlink r:id="rId38" ref="AM46"/>
+    <hyperlink r:id="rId39" ref="AM48"/>
+    <hyperlink r:id="rId40" ref="AM49"/>
+    <hyperlink r:id="rId41" ref="AM50"/>
+    <hyperlink r:id="rId42" ref="AM51"/>
+    <hyperlink r:id="rId43" ref="AM52"/>
+    <hyperlink r:id="rId44" ref="AM54"/>
+    <hyperlink r:id="rId45" ref="AM56"/>
+    <hyperlink r:id="rId46" ref="AM57"/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.25196850393700787" right="0.25196850393700787" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
-  <pageSetup paperSize="9" scale="29" firstPageNumber="1" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="1" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
+  <pageSetup paperSize="9" scale="28" firstPageNumber="1" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="landscape" usePrinterDefaults="1" blackAndWhite="0" draft="0" cellComments="none" useFirstPageNumber="1" errors="displayed" horizontalDpi="600" verticalDpi="600" copies="1"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/analyse-prix-composants.xlsx
+++ b/analyse-prix-composants.xlsx
@@ -10,7 +10,7 @@
   </sheets>
   <definedNames>
     <definedName name="Print_Titles" localSheetId="0">Feuille1!$3:$3</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Feuille1!$A$1:$AL$58</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Feuille1!$A$1:$AM$58</definedName>
   </definedNames>
   <calcPr/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="173">
   <si>
     <t xml:space="preserve">Le prix des composants IT</t>
   </si>
@@ -147,6 +147,9 @@
     <t xml:space="preserve">16 mai 2026</t>
   </si>
   <si>
+    <t xml:space="preserve">23 mai 2026</t>
+  </si>
+  <si>
     <t>Min</t>
   </si>
   <si>
@@ -217,7 +220,7 @@
     <t>CPU</t>
   </si>
   <si>
-    <t xml:space="preserve">Intel i5 12400F</t>
+    <t xml:space="preserve">Intel i5 12400F (tray)</t>
   </si>
   <si>
     <t>https://www.amazon.fr/dp/B09NPJRDGD</t>
@@ -1415,12 +1418,12 @@
     <col bestFit="1" min="12" max="12" style="4" width="11.7109375"/>
     <col bestFit="1" min="13" max="13" style="4" width="13.00390625"/>
     <col bestFit="1" min="14" max="15" style="4" width="14.140625"/>
-    <col customWidth="1" min="16" max="31" style="1" width="12.7109375"/>
-    <col customWidth="1" min="32" max="35" style="2" width="12.7109375"/>
-    <col customWidth="1" min="36" max="36" style="2" width="14.140625"/>
-    <col customWidth="1" min="37" max="38" style="2" width="12.7109375"/>
-    <col customWidth="1" min="39" max="39" style="5" width="42.28125"/>
-    <col min="40" max="16384" style="1" width="9.140625"/>
+    <col customWidth="1" min="16" max="32" style="1" width="12.7109375"/>
+    <col customWidth="1" min="33" max="36" style="2" width="12.7109375"/>
+    <col customWidth="1" min="37" max="37" style="2" width="14.140625"/>
+    <col customWidth="1" min="38" max="39" style="2" width="12.7109375"/>
+    <col customWidth="1" min="40" max="40" style="5" width="42.28125"/>
+    <col min="41" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" ht="57.75" customHeight="1">
@@ -1444,28 +1447,29 @@
       <c r="AC1" s="1"/>
       <c r="AD1" s="1"/>
       <c r="AE1" s="1"/>
-      <c r="AF1" s="7" t="s">
+      <c r="AF1" s="1"/>
+      <c r="AG1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="AG1" s="7" t="s">
+      <c r="AH1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="AH1" s="7" t="s">
+      <c r="AI1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="AI1" s="7" t="s">
+      <c r="AJ1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="AJ1" s="7" t="s">
+      <c r="AK1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="AK1" s="7" t="s">
+      <c r="AL1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="AL1" s="7" t="s">
+      <c r="AM1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="AM1" s="5"/>
+      <c r="AN1" s="5"/>
     </row>
     <row r="2" ht="39.75" customHeight="1">
       <c r="A2" s="2"/>
@@ -1488,13 +1492,14 @@
       <c r="AC2" s="1"/>
       <c r="AD2" s="1"/>
       <c r="AE2" s="1"/>
-      <c r="AF2" s="7"/>
+      <c r="AF2" s="1"/>
       <c r="AG2" s="7"/>
       <c r="AH2" s="7"/>
       <c r="AI2" s="7"/>
       <c r="AJ2" s="7"/>
       <c r="AK2" s="7"/>
       <c r="AL2" s="7"/>
+      <c r="AM2" s="7"/>
     </row>
     <row r="3" ht="18">
       <c r="A3" s="9" t="s">
@@ -1590,7 +1595,7 @@
       <c r="AE3" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="AF3" s="12" t="s">
+      <c r="AF3" s="11" t="s">
         <v>40</v>
       </c>
       <c r="AG3" s="12" t="s">
@@ -1611,16 +1616,19 @@
       <c r="AL3" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="AM3" s="5" t="s">
+      <c r="AM3" s="12" t="s">
         <v>47</v>
+      </c>
+      <c r="AN3" s="5" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="4" ht="36">
       <c r="A4" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C4" s="14">
         <v>171.88</v>
@@ -1647,7 +1655,7 @@
         <v>341.57999999999998</v>
       </c>
       <c r="M4" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N4" s="17">
         <v>321.14999999999998</v>
@@ -1698,53 +1706,56 @@
         <v>450.54000000000002</v>
       </c>
       <c r="AD4" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AE4" s="18">
         <v>425.05000000000001</v>
       </c>
-      <c r="AF4" s="19">
-        <f>MIN(C4:AE4)</f>
+      <c r="AF4" s="16">
+        <v>329.94999999999999</v>
+      </c>
+      <c r="AG4" s="19">
+        <f>MIN(C4:AF4)</f>
         <v>171.88</v>
       </c>
-      <c r="AG4" s="20">
-        <f>MAX(C4:AE4)</f>
+      <c r="AH4" s="20">
+        <f>MAX(C4:AF4)</f>
         <v>450.54000000000002</v>
       </c>
-      <c r="AH4" s="20">
-        <f>AVERAGE(C4:AE4)</f>
-        <v>363.25708333333341</v>
-      </c>
       <c r="AI4" s="20">
-        <f>AVERAGE(Q4:AE4)</f>
-        <v>395.51999999999998</v>
-      </c>
-      <c r="AJ4" s="21">
-        <f>(AI4/AH4)-1</f>
-        <v>8.8815657414342386e-002</v>
+        <f>AVERAGE(C4:AF4)</f>
+        <v>361.92480000000012</v>
+      </c>
+      <c r="AJ4" s="20">
+        <f>AVERAGE(Q4:AF4)</f>
+        <v>391.14866666666666</v>
       </c>
       <c r="AK4" s="21">
-        <f>(AI4/AF4)-1</f>
-        <v>1.3011403304631139</v>
+        <f>(AJ4/AI4)-1</f>
+        <v>8.0745687133533028e-002</v>
       </c>
       <c r="AL4" s="21">
-        <f>(AG4/AF4)-1</f>
+        <f>(AJ4/AG4)-1</f>
+        <v>1.2757078581956405</v>
+      </c>
+      <c r="AM4" s="21">
+        <f>(AH4/AG4)-1</f>
         <v>1.6212473818943449</v>
       </c>
-      <c r="AM4" s="22" t="s">
-        <v>51</v>
-      </c>
-      <c r="AN4" s="23">
+      <c r="AN4" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="AO4" s="23">
         <f>C2*1</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" ht="36">
       <c r="A5" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C5" s="15"/>
       <c r="D5" s="24">
@@ -1756,7 +1767,7 @@
         <v>686</v>
       </c>
       <c r="H5" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I5" s="16">
         <v>613.99000000000001</v>
@@ -1827,44 +1838,47 @@
       <c r="AE5" s="17">
         <v>978.75</v>
       </c>
-      <c r="AF5" s="19">
-        <f>MIN(C5:AE5)</f>
+      <c r="AF5" s="17">
+        <v>978.75</v>
+      </c>
+      <c r="AG5" s="19">
+        <f>MIN(C5:AF5)</f>
         <v>200.47999999999999</v>
       </c>
-      <c r="AG5" s="20">
-        <f>MAX(C5:AE5)</f>
+      <c r="AH5" s="20">
+        <f>MAX(C5:AF5)</f>
         <v>978.75</v>
       </c>
-      <c r="AH5" s="20">
-        <f>AVERAGE(C5:AE5)</f>
-        <v>850.59480000000008</v>
-      </c>
       <c r="AI5" s="20">
-        <f>AVERAGE(Q5:AE5)</f>
-        <v>927.11333333333334</v>
-      </c>
-      <c r="AJ5" s="21">
-        <f>(AI5/AH5)-1</f>
-        <v>8.9958853890634183e-002</v>
+        <f>AVERAGE(C5:AF5)</f>
+        <v>855.52384615384631</v>
+      </c>
+      <c r="AJ5" s="20">
+        <f>AVERAGE(Q5:AF5)</f>
+        <v>930.34062500000005</v>
       </c>
       <c r="AK5" s="21">
-        <f>(AI5/AF5)-1</f>
-        <v>3.6244679436020224</v>
+        <f>(AJ5/AI5)-1</f>
+        <v>8.7451424273566891e-002</v>
       </c>
       <c r="AL5" s="21">
-        <f>(AG5/AF5)-1</f>
+        <f>(AJ5/AG5)-1</f>
+        <v>3.6405657671588196</v>
+      </c>
+      <c r="AM5" s="21">
+        <f>(AH5/AG5)-1</f>
         <v>3.8820331205107745</v>
       </c>
-      <c r="AM5" s="22" t="s">
-        <v>53</v>
+      <c r="AN5" s="22" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="6" ht="36">
       <c r="A6" s="25" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C6" s="27"/>
       <c r="D6" s="24">
@@ -1947,44 +1961,47 @@
       <c r="AE6" s="17">
         <v>710</v>
       </c>
-      <c r="AF6" s="19">
-        <f>MIN(C6:AE6)</f>
+      <c r="AF6" s="17">
+        <v>714.99000000000001</v>
+      </c>
+      <c r="AG6" s="19">
+        <f>MIN(C6:AF6)</f>
         <v>284.13</v>
       </c>
-      <c r="AG6" s="20">
-        <f>MAX(C6:AE6)</f>
+      <c r="AH6" s="20">
+        <f>MAX(C6:AF6)</f>
         <v>717.78999999999996</v>
       </c>
-      <c r="AH6" s="20">
-        <f>AVERAGE(C6:AE6)</f>
-        <v>628.09769230769223</v>
-      </c>
       <c r="AI6" s="20">
-        <f>AVERAGE(Q6:AE6)</f>
-        <v>683.04466666666667</v>
-      </c>
-      <c r="AJ6" s="21">
-        <f>(AI6/AH6)-1</f>
-        <v>8.7481573379284194e-002</v>
+        <f>AVERAGE(C6:AF6)</f>
+        <v>631.31592592592585</v>
+      </c>
+      <c r="AJ6" s="20">
+        <f>AVERAGE(Q6:AF6)</f>
+        <v>685.04124999999999</v>
       </c>
       <c r="AK6" s="21">
-        <f>(AI6/AF6)-1</f>
-        <v>1.4039864381327796</v>
+        <f>(AJ6/AI6)-1</f>
+        <v>8.5100536621624645e-002</v>
       </c>
       <c r="AL6" s="21">
-        <f>(AG6/AF6)-1</f>
+        <f>(AJ6/AG6)-1</f>
+        <v>1.4110134445500297</v>
+      </c>
+      <c r="AM6" s="21">
+        <f>(AH6/AG6)-1</f>
         <v>1.5262731848097699</v>
       </c>
-      <c r="AM6" s="22" t="s">
-        <v>55</v>
+      <c r="AN6" s="22" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="7" ht="36">
       <c r="A7" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C7" s="15"/>
       <c r="D7" s="15"/>
@@ -2061,44 +2078,47 @@
       <c r="AE7" s="18">
         <v>823.61000000000001</v>
       </c>
-      <c r="AF7" s="19">
-        <f>MIN(C7:AE7)</f>
+      <c r="AF7" s="18">
+        <v>844.82000000000005</v>
+      </c>
+      <c r="AG7" s="19">
+        <f>MIN(C7:AF7)</f>
         <v>685.71000000000004</v>
       </c>
-      <c r="AG7" s="20">
-        <f>MAX(C7:AE7)</f>
+      <c r="AH7" s="20">
+        <f>MAX(C7:AF7)</f>
         <v>887.78999999999996</v>
       </c>
-      <c r="AH7" s="20">
-        <f>AVERAGE(C7:AE7)</f>
-        <v>799.93434782608699</v>
-      </c>
       <c r="AI7" s="20">
-        <f>AVERAGE(Q7:AE7)</f>
-        <v>820.10000000000025</v>
-      </c>
-      <c r="AJ7" s="21">
-        <f>(AI7/AH7)-1</f>
-        <v>2.5209134010454326e-002</v>
+        <f>AVERAGE(C7:AF7)</f>
+        <v>801.80458333333343</v>
+      </c>
+      <c r="AJ7" s="20">
+        <f>AVERAGE(Q7:AF7)</f>
+        <v>821.64500000000021</v>
       </c>
       <c r="AK7" s="21">
-        <f>(AI7/AF7)-1</f>
-        <v>0.1959866415831768</v>
+        <f>(AJ7/AI7)-1</f>
+        <v>2.474470348396407e-002</v>
       </c>
       <c r="AL7" s="21">
-        <f>(AG7/AF7)-1</f>
+        <f>(AJ7/AG7)-1</f>
+        <v>0.19823978066529602</v>
+      </c>
+      <c r="AM7" s="21">
+        <f>(AH7/AG7)-1</f>
         <v>0.29470184188651172</v>
       </c>
-      <c r="AM7" s="22" t="s">
-        <v>57</v>
+      <c r="AN7" s="22" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="8" ht="18">
       <c r="A8" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C8" s="15"/>
       <c r="D8" s="16">
@@ -2181,45 +2201,48 @@
       <c r="AE8" s="17">
         <v>591.88</v>
       </c>
-      <c r="AF8" s="19">
-        <f>MIN(C8:AE8)</f>
+      <c r="AF8" s="17">
+        <v>591.85000000000002</v>
+      </c>
+      <c r="AG8" s="19">
+        <f>MIN(C8:AF8)</f>
         <v>465</v>
       </c>
-      <c r="AG8" s="20">
-        <f>MAX(C8:AE8)</f>
+      <c r="AH8" s="20">
+        <f>MAX(C8:AF8)</f>
         <v>623.12</v>
       </c>
-      <c r="AH8" s="20">
-        <f>AVERAGE(C8:AE8)</f>
-        <v>555.33923076923054</v>
-      </c>
       <c r="AI8" s="20">
-        <f>AVERAGE(Q8:AE8)</f>
-        <v>551.05999999999983</v>
-      </c>
-      <c r="AJ8" s="21">
-        <f>(AI8/AH8)-1</f>
-        <v>-7.7056158328726587e-003</v>
+        <f>AVERAGE(C8:AF8)</f>
+        <v>556.69148148148133</v>
+      </c>
+      <c r="AJ8" s="20">
+        <f>AVERAGE(Q8:AF8)</f>
+        <v>553.60937499999989</v>
       </c>
       <c r="AK8" s="21">
-        <f>(AI8/AF8)-1</f>
-        <v>0.18507526881720393</v>
+        <f>(AJ8/AI8)-1</f>
+        <v>-5.5364714280866645e-003</v>
       </c>
       <c r="AL8" s="21">
-        <f>(AG8/AF8)-1</f>
+        <f>(AJ8/AG8)-1</f>
+        <v>0.19055779569892439</v>
+      </c>
+      <c r="AM8" s="21">
+        <f>(AH8/AG8)-1</f>
         <v>0.34004301075268817</v>
       </c>
-      <c r="AM8" s="22" t="s">
-        <v>60</v>
-      </c>
-      <c r="AN8" s="1"/>
+      <c r="AN8" s="22" t="s">
+        <v>61</v>
+      </c>
+      <c r="AO8" s="1"/>
     </row>
     <row r="9" ht="18">
       <c r="A9" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C9" s="15"/>
       <c r="D9" s="16"/>
@@ -2300,44 +2323,47 @@
       <c r="AE9" s="17">
         <v>159.99000000000001</v>
       </c>
-      <c r="AF9" s="19">
-        <f>MIN(C9:AE9)</f>
+      <c r="AF9" s="17">
+        <v>162.75</v>
+      </c>
+      <c r="AG9" s="19">
+        <f>MIN(C9:AF9)</f>
         <v>122</v>
       </c>
-      <c r="AG9" s="20">
-        <f>MAX(C9:AE9)</f>
+      <c r="AH9" s="20">
+        <f>MAX(C9:AF9)</f>
         <v>169</v>
       </c>
-      <c r="AH9" s="20">
-        <f>AVERAGE(C9:AE9)</f>
-        <v>133.91919999999999</v>
-      </c>
       <c r="AI9" s="20">
-        <f>AVERAGE(Q9:AE9)</f>
-        <v>141.86533333333333</v>
-      </c>
-      <c r="AJ9" s="21">
-        <f>(AI9/AH9)-1</f>
-        <v>5.9335280776269039e-002</v>
+        <f>AVERAGE(C9:AF9)</f>
+        <v>135.0280769230769</v>
+      </c>
+      <c r="AJ9" s="20">
+        <f>AVERAGE(Q9:AF9)</f>
+        <v>143.170625</v>
       </c>
       <c r="AK9" s="21">
-        <f>(AI9/AF9)-1</f>
-        <v>0.16283060109289615</v>
+        <f>(AJ9/AI9)-1</f>
+        <v>6.0302629367681604e-002</v>
       </c>
       <c r="AL9" s="21">
-        <f>(AG9/AF9)-1</f>
+        <f>(AJ9/AG9)-1</f>
+        <v>0.17352971311475418</v>
+      </c>
+      <c r="AM9" s="21">
+        <f>(AH9/AG9)-1</f>
         <v>0.38524590163934436</v>
       </c>
-      <c r="AM9" s="29" t="s">
-        <v>63</v>
+      <c r="AN9" s="29" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="10" ht="18">
       <c r="A10" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C10" s="15"/>
       <c r="D10" s="16"/>
@@ -2376,44 +2402,47 @@
       <c r="AE10" s="24">
         <v>306.94</v>
       </c>
-      <c r="AF10" s="19">
-        <f>MIN(C10:AE10)</f>
+      <c r="AF10" s="24">
+        <v>323.08999999999997</v>
+      </c>
+      <c r="AG10" s="19">
+        <f>MIN(C10:AF10)</f>
         <v>306.94</v>
       </c>
-      <c r="AG10" s="20">
-        <f>MAX(C10:AE10)</f>
+      <c r="AH10" s="20">
+        <f>MAX(C10:AF10)</f>
         <v>349</v>
       </c>
-      <c r="AH10" s="20">
-        <f>AVERAGE(C10:AE10)</f>
-        <v>338.48500000000001</v>
-      </c>
       <c r="AI10" s="20">
-        <f>AVERAGE(Q10:AE10)</f>
-        <v>338.48500000000001</v>
-      </c>
-      <c r="AJ10" s="21">
-        <f>(AI10/AH10)-1</f>
+        <f>AVERAGE(C10:AF10)</f>
+        <v>335.40600000000001</v>
+      </c>
+      <c r="AJ10" s="20">
+        <f>AVERAGE(Q10:AF10)</f>
+        <v>335.40600000000001</v>
+      </c>
+      <c r="AK10" s="21">
+        <f>(AJ10/AI10)-1</f>
         <v>0</v>
       </c>
-      <c r="AK10" s="21">
-        <f>(AI10/AF10)-1</f>
-        <v>0.10277252883299681</v>
-      </c>
       <c r="AL10" s="21">
-        <f>(AG10/AF10)-1</f>
+        <f>(AJ10/AG10)-1</f>
+        <v>9.2741252362025239e-002</v>
+      </c>
+      <c r="AM10" s="21">
+        <f>(AH10/AG10)-1</f>
         <v>0.13703003844399553</v>
       </c>
-      <c r="AM10" s="29" t="s">
-        <v>65</v>
+      <c r="AN10" s="29" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="11" ht="18">
       <c r="A11" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C11" s="15"/>
       <c r="D11" s="16"/>
@@ -2452,44 +2481,47 @@
       <c r="AE11" s="16">
         <v>467.06999999999999</v>
       </c>
-      <c r="AF11" s="19">
-        <f>MIN(C11:AE11)</f>
-        <v>467</v>
-      </c>
-      <c r="AG11" s="20">
-        <f>MAX(C11:AE11)</f>
+      <c r="AF11" s="16">
+        <v>461.06999999999999</v>
+      </c>
+      <c r="AG11" s="19">
+        <f>MIN(C11:AF11)</f>
+        <v>461.06999999999999</v>
+      </c>
+      <c r="AH11" s="20">
+        <f>MAX(C11:AF11)</f>
         <v>515</v>
       </c>
-      <c r="AH11" s="20">
-        <f>AVERAGE(C11:AE11)</f>
-        <v>479.01749999999998</v>
-      </c>
       <c r="AI11" s="20">
-        <f>AVERAGE(Q11:AE11)</f>
-        <v>479.01749999999998</v>
-      </c>
-      <c r="AJ11" s="21">
-        <f>(AI11/AH11)-1</f>
+        <f>AVERAGE(C11:AF11)</f>
+        <v>475.428</v>
+      </c>
+      <c r="AJ11" s="20">
+        <f>AVERAGE(Q11:AF11)</f>
+        <v>475.428</v>
+      </c>
+      <c r="AK11" s="21">
+        <f>(AJ11/AI11)-1</f>
         <v>0</v>
       </c>
-      <c r="AK11" s="21">
-        <f>(AI11/AF11)-1</f>
-        <v>2.5733404710920782e-002</v>
-      </c>
       <c r="AL11" s="21">
-        <f>(AG11/AF11)-1</f>
-        <v>0.10278372591006435</v>
-      </c>
-      <c r="AM11" s="29" t="s">
-        <v>67</v>
+        <f>(AJ11/AG11)-1</f>
+        <v>3.114060771683258e-002</v>
+      </c>
+      <c r="AM11" s="21">
+        <f>(AH11/AG11)-1</f>
+        <v>0.1169670548940509</v>
+      </c>
+      <c r="AN11" s="29" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="12" ht="18">
       <c r="A12" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C12" s="15"/>
       <c r="D12" s="16"/>
@@ -2528,44 +2560,47 @@
       <c r="AE12" s="16">
         <v>172.31999999999999</v>
       </c>
-      <c r="AF12" s="19">
-        <f>MIN(C12:AE12)</f>
+      <c r="AF12" s="16">
+        <v>166.75</v>
+      </c>
+      <c r="AG12" s="19">
+        <f>MIN(C12:AF12)</f>
         <v>165.13999999999999</v>
       </c>
-      <c r="AG12" s="20">
-        <f>MAX(C12:AE12)</f>
+      <c r="AH12" s="20">
+        <f>MAX(C12:AF12)</f>
         <v>179.88999999999999</v>
       </c>
-      <c r="AH12" s="20">
-        <f>AVERAGE(C12:AE12)</f>
-        <v>172.79750000000001</v>
-      </c>
       <c r="AI12" s="20">
-        <f>AVERAGE(Q12:AE12)</f>
-        <v>172.79750000000001</v>
-      </c>
-      <c r="AJ12" s="21">
-        <f>(AI12/AH12)-1</f>
+        <f>AVERAGE(C12:AF12)</f>
+        <v>171.58800000000002</v>
+      </c>
+      <c r="AJ12" s="20">
+        <f>AVERAGE(Q12:AF12)</f>
+        <v>171.58800000000002</v>
+      </c>
+      <c r="AK12" s="21">
+        <f>(AJ12/AI12)-1</f>
         <v>0</v>
       </c>
-      <c r="AK12" s="21">
-        <f>(AI12/AF12)-1</f>
-        <v>4.6369746881434137e-002</v>
-      </c>
       <c r="AL12" s="21">
-        <f>(AG12/AF12)-1</f>
+        <f>(AJ12/AG12)-1</f>
+        <v>3.9045658229381441e-002</v>
+      </c>
+      <c r="AM12" s="21">
+        <f>(AH12/AG12)-1</f>
         <v>8.931815429332679e-002</v>
       </c>
-      <c r="AM12" s="29" t="s">
-        <v>69</v>
+      <c r="AN12" s="29" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="13" ht="36">
       <c r="A13" s="25" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C13" s="27"/>
       <c r="D13" s="24">
@@ -2601,19 +2636,19 @@
         <v>1084.8299999999999</v>
       </c>
       <c r="P13" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q13" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="R13" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="S13" s="30">
         <v>1426.5699999999999</v>
       </c>
       <c r="T13" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="U13" s="24">
         <v>592.17999999999995</v>
@@ -2628,64 +2663,67 @@
         <v>623.23000000000002</v>
       </c>
       <c r="Y13" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Z13" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AA13" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB13" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AC13" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AD13" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AE13" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF13" s="19">
-        <f>MIN(C13:AE13)</f>
+        <v>51</v>
+      </c>
+      <c r="AF13" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="AG13" s="19">
+        <f>MIN(C13:AF13)</f>
         <v>592.17999999999995</v>
       </c>
-      <c r="AG13" s="20">
-        <f>MAX(C13:AE13)</f>
+      <c r="AH13" s="20">
+        <f>MAX(C13:AF13)</f>
         <v>1426.5699999999999</v>
       </c>
-      <c r="AH13" s="20">
-        <f>AVERAGE(C13:AE13)</f>
+      <c r="AI13" s="20">
+        <f>AVERAGE(C13:AF13)</f>
         <v>853.96466666666674</v>
       </c>
-      <c r="AI13" s="20">
-        <f>AVERAGE(Q13:AE13)</f>
+      <c r="AJ13" s="20">
+        <f>AVERAGE(Q13:AF13)</f>
         <v>771.42200000000003</v>
       </c>
-      <c r="AJ13" s="21">
-        <f>(AI13/AH13)-1</f>
+      <c r="AK13" s="21">
+        <f>(AJ13/AI13)-1</f>
         <v>-9.665817555293077e-002</v>
       </c>
-      <c r="AK13" s="21">
-        <f>(AI13/AF13)-1</f>
+      <c r="AL13" s="21">
+        <f>(AJ13/AG13)-1</f>
         <v>0.30268161707588925</v>
       </c>
-      <c r="AL13" s="21">
-        <f>(AG13/AF13)-1</f>
+      <c r="AM13" s="21">
+        <f>(AH13/AG13)-1</f>
         <v>1.4090141511027054</v>
       </c>
-      <c r="AM13" s="22" t="s">
-        <v>72</v>
+      <c r="AN13" s="22" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="14" ht="18">
       <c r="A14" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C14" s="15"/>
       <c r="D14" s="15"/>
@@ -2760,44 +2798,47 @@
       <c r="AE14" s="16">
         <v>597.99000000000001</v>
       </c>
-      <c r="AF14" s="19">
-        <f>MIN(C14:AE14)</f>
+      <c r="AF14" s="17">
+        <v>698.99000000000001</v>
+      </c>
+      <c r="AG14" s="19">
+        <f>MIN(C14:AF14)</f>
         <v>580.98000000000002</v>
       </c>
-      <c r="AG14" s="20">
-        <f>MAX(C14:AE14)</f>
+      <c r="AH14" s="20">
+        <f>MAX(C14:AF14)</f>
         <v>709.99000000000001</v>
       </c>
-      <c r="AH14" s="20">
-        <f>AVERAGE(C14:AE14)</f>
-        <v>646.54909090909075</v>
-      </c>
       <c r="AI14" s="20">
-        <f>AVERAGE(Q14:AE14)</f>
-        <v>657.0526666666666</v>
-      </c>
-      <c r="AJ14" s="21">
-        <f>(AI14/AH14)-1</f>
-        <v>1.6245596668935214e-002</v>
+        <f>AVERAGE(C14:AF14)</f>
+        <v>648.82913043478243</v>
+      </c>
+      <c r="AJ14" s="20">
+        <f>AVERAGE(Q14:AF14)</f>
+        <v>659.67374999999993</v>
       </c>
       <c r="AK14" s="21">
-        <f>(AI14/AF14)-1</f>
-        <v>0.13093852915189252</v>
+        <f>(AJ14/AI14)-1</f>
+        <v>1.6714137908620863e-002</v>
       </c>
       <c r="AL14" s="21">
-        <f>(AG14/AF14)-1</f>
+        <f>(AJ14/AG14)-1</f>
+        <v>0.13545001549106672</v>
+      </c>
+      <c r="AM14" s="21">
+        <f>(AH14/AG14)-1</f>
         <v>0.22205583668973117</v>
       </c>
-      <c r="AM14" s="22" t="s">
-        <v>74</v>
+      <c r="AN14" s="22" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="15" ht="18">
       <c r="A15" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C15" s="15"/>
       <c r="D15" s="15"/>
@@ -2872,44 +2913,47 @@
       <c r="AE15" s="16">
         <v>675.62</v>
       </c>
-      <c r="AF15" s="19">
-        <f>MIN(C15:AE15)</f>
+      <c r="AF15" s="16">
+        <v>668.91999999999996</v>
+      </c>
+      <c r="AG15" s="19">
+        <f>MIN(C15:AF15)</f>
         <v>622.63</v>
       </c>
-      <c r="AG15" s="20">
-        <f>MAX(C15:AE15)</f>
+      <c r="AH15" s="20">
+        <f>MAX(C15:AF15)</f>
         <v>728.61000000000001</v>
       </c>
-      <c r="AH15" s="20">
-        <f>AVERAGE(C15:AE15)</f>
-        <v>680.92272727272723</v>
-      </c>
       <c r="AI15" s="20">
-        <f>AVERAGE(Q15:AE15)</f>
-        <v>687.69600000000014</v>
-      </c>
-      <c r="AJ15" s="21">
-        <f>(AI15/AH15)-1</f>
-        <v>9.9471973191460616e-003</v>
+        <f>AVERAGE(C15:AF15)</f>
+        <v>680.40086956521736</v>
+      </c>
+      <c r="AJ15" s="20">
+        <f>AVERAGE(Q15:AF15)</f>
+        <v>686.52250000000015</v>
       </c>
       <c r="AK15" s="21">
-        <f>(AI15/AF15)-1</f>
-        <v>0.10450187109519327</v>
+        <f>(AJ15/AI15)-1</f>
+        <v>8.9970937848662391e-003</v>
       </c>
       <c r="AL15" s="21">
-        <f>(AG15/AF15)-1</f>
+        <f>(AJ15/AG15)-1</f>
+        <v>0.10261712413471913</v>
+      </c>
+      <c r="AM15" s="21">
+        <f>(AH15/AG15)-1</f>
         <v>0.17021344940012528</v>
       </c>
-      <c r="AM15" s="22" t="s">
-        <v>76</v>
+      <c r="AN15" s="22" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="16" ht="18">
       <c r="A16" s="25" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C16" s="27"/>
       <c r="D16" s="28"/>
@@ -2990,44 +3034,47 @@
       <c r="AE16" s="16">
         <v>10671.950000000001</v>
       </c>
-      <c r="AF16" s="19">
-        <f>MIN(C16:AE16)</f>
+      <c r="AF16" s="16">
+        <v>11281.15</v>
+      </c>
+      <c r="AG16" s="19">
+        <f>MIN(C16:AF16)</f>
         <v>9100</v>
       </c>
-      <c r="AG16" s="20">
-        <f>MAX(C16:AE16)</f>
+      <c r="AH16" s="20">
+        <f>MAX(C16:AF16)</f>
         <v>11315.18</v>
       </c>
-      <c r="AH16" s="20">
-        <f>AVERAGE(C16:AE16)</f>
-        <v>10058.550799999999</v>
-      </c>
       <c r="AI16" s="20">
-        <f>AVERAGE(Q16:AE16)</f>
-        <v>10671.64866666667</v>
-      </c>
-      <c r="AJ16" s="21">
-        <f>(AI16/AH16)-1</f>
-        <v>6.095290254602781e-002</v>
+        <f>AVERAGE(C16:AF16)</f>
+        <v>10105.573846153846</v>
+      </c>
+      <c r="AJ16" s="20">
+        <f>AVERAGE(Q16:AF16)</f>
+        <v>10709.742500000002</v>
       </c>
       <c r="AK16" s="21">
-        <f>(AI16/AF16)-1</f>
-        <v>0.172708644688645</v>
+        <f>(AJ16/AI16)-1</f>
+        <v>5.9785684914479331e-002</v>
       </c>
       <c r="AL16" s="21">
-        <f>(AG16/AF16)-1</f>
+        <f>(AJ16/AG16)-1</f>
+        <v>0.17689478021978045</v>
+      </c>
+      <c r="AM16" s="21">
+        <f>(AH16/AG16)-1</f>
         <v>0.24342637362637376</v>
       </c>
-      <c r="AM16" s="22" t="s">
-        <v>78</v>
+      <c r="AN16" s="22" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="17" ht="36">
       <c r="A17" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C17" s="15"/>
       <c r="D17" s="15"/>
@@ -3100,44 +3147,47 @@
       <c r="AE17" s="17">
         <v>1379.99</v>
       </c>
-      <c r="AF17" s="19">
-        <f>MIN(C17:AE17)</f>
+      <c r="AF17" s="17">
+        <v>1508.8399999999999</v>
+      </c>
+      <c r="AG17" s="19">
+        <f>MIN(C17:AF17)</f>
         <v>1297.6199999999999</v>
       </c>
-      <c r="AG17" s="20">
-        <f>MAX(C17:AE17)</f>
+      <c r="AH17" s="20">
+        <f>MAX(C17:AF17)</f>
         <v>1697.6199999999999</v>
       </c>
-      <c r="AH17" s="20">
-        <f>AVERAGE(C17:AE17)</f>
-        <v>1530.05</v>
-      </c>
       <c r="AI17" s="20">
-        <f>AVERAGE(Q17:AE17)</f>
-        <v>1554.1680000000001</v>
-      </c>
-      <c r="AJ17" s="21">
-        <f>(AI17/AH17)-1</f>
-        <v>1.5762883565896724e-002</v>
+        <f>AVERAGE(C17:AF17)</f>
+        <v>1529.0859090909091</v>
+      </c>
+      <c r="AJ17" s="20">
+        <f>AVERAGE(Q17:AF17)</f>
+        <v>1551.335</v>
       </c>
       <c r="AK17" s="21">
-        <f>(AI17/AF17)-1</f>
-        <v>0.19770657049059071</v>
+        <f>(AJ17/AI17)-1</f>
+        <v>1.4550582656483124e-002</v>
       </c>
       <c r="AL17" s="21">
-        <f>(AG17/AF17)-1</f>
+        <f>(AJ17/AG17)-1</f>
+        <v>0.19552334273516148</v>
+      </c>
+      <c r="AM17" s="21">
+        <f>(AH17/AG17)-1</f>
         <v>0.30825665449052875</v>
       </c>
-      <c r="AM17" s="22" t="s">
-        <v>80</v>
+      <c r="AN17" s="22" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="18" ht="18">
       <c r="A18" s="25" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B18" s="26" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C18" s="27"/>
       <c r="D18" s="28"/>
@@ -3146,118 +3196,121 @@
         <v>2279</v>
       </c>
       <c r="G18" s="28" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H18" s="28" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I18" s="28" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J18" s="28" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K18" s="28" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L18" s="28" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="M18" s="28" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="N18" s="28" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O18" s="28" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P18" s="16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Q18" s="16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="R18" s="16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="S18" s="16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="T18" s="16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U18" s="16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="V18" s="16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="W18" s="16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="X18" s="16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Y18" s="16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="Z18" s="16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AA18" s="16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AB18" s="16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AC18" s="16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AD18" s="16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AE18" s="16" t="s">
-        <v>82</v>
-      </c>
-      <c r="AF18" s="19">
-        <f>MIN(C18:AE18)</f>
+        <v>83</v>
+      </c>
+      <c r="AF18" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="AG18" s="19">
+        <f>MIN(C18:AF18)</f>
         <v>2279</v>
       </c>
-      <c r="AG18" s="20">
-        <f>MAX(C18:AE18)</f>
+      <c r="AH18" s="20">
+        <f>MAX(C18:AF18)</f>
         <v>2279</v>
       </c>
-      <c r="AH18" s="20">
-        <f>AVERAGE(C18:AE18)</f>
+      <c r="AI18" s="20">
+        <f>AVERAGE(C18:AF18)</f>
         <v>2279</v>
       </c>
-      <c r="AI18" s="20" t="e">
-        <f>AVERAGE(Q18:AE18)</f>
+      <c r="AJ18" s="20" t="e">
+        <f>AVERAGE(Q18:AF18)</f>
         <v>#NUM!</v>
       </c>
-      <c r="AJ18" s="21" t="e">
-        <f>(AI18/AH18)-1</f>
+      <c r="AK18" s="21" t="e">
+        <f>(AJ18/AI18)-1</f>
         <v>#NUM!</v>
       </c>
-      <c r="AK18" s="21" t="e">
-        <f>(AI18/AF18)-1</f>
+      <c r="AL18" s="21" t="e">
+        <f>(AJ18/AG18)-1</f>
         <v>#NUM!</v>
       </c>
-      <c r="AL18" s="21">
-        <f>(AG18/AF18)-1</f>
+      <c r="AM18" s="21">
+        <f>(AH18/AG18)-1</f>
         <v>0</v>
       </c>
-      <c r="AM18" s="22" t="s">
-        <v>83</v>
+      <c r="AN18" s="22" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="19" ht="36">
       <c r="A19" s="25" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B19" s="26" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C19" s="27"/>
       <c r="D19" s="28"/>
@@ -3294,44 +3347,47 @@
       <c r="AE19" s="16">
         <v>3394.9499999999998</v>
       </c>
-      <c r="AF19" s="19">
-        <f>MIN(C19:AE19)</f>
+      <c r="AF19" s="16">
+        <v>3629</v>
+      </c>
+      <c r="AG19" s="19">
+        <f>MIN(C19:AF19)</f>
         <v>3394.9499999999998</v>
       </c>
-      <c r="AG19" s="20">
-        <f>MAX(C19:AE19)</f>
+      <c r="AH19" s="20">
+        <f>MAX(C19:AF19)</f>
         <v>3629</v>
       </c>
-      <c r="AH19" s="20">
-        <f>AVERAGE(C19:AE19)</f>
-        <v>3507.9666666666667</v>
-      </c>
       <c r="AI19" s="20">
-        <f>AVERAGE(Q19:AE19)</f>
-        <v>3507.9666666666667</v>
-      </c>
-      <c r="AJ19" s="21">
-        <f>(AI19/AH19)-1</f>
+        <f>AVERAGE(C19:AF19)</f>
+        <v>3538.2249999999999</v>
+      </c>
+      <c r="AJ19" s="20">
+        <f>AVERAGE(Q19:AF19)</f>
+        <v>3538.2249999999999</v>
+      </c>
+      <c r="AK19" s="21">
+        <f>(AJ19/AI19)-1</f>
         <v>0</v>
       </c>
-      <c r="AK19" s="21">
-        <f>(AI19/AF19)-1</f>
-        <v>3.3289640986366997e-002</v>
-      </c>
       <c r="AL19" s="21">
-        <f>(AG19/AF19)-1</f>
+        <f>(AJ19/AG19)-1</f>
+        <v>4.2202388842250915e-002</v>
+      </c>
+      <c r="AM19" s="21">
+        <f>(AH19/AG19)-1</f>
         <v>6.8940632409902891e-002</v>
       </c>
-      <c r="AM19" s="29" t="s">
-        <v>85</v>
+      <c r="AN19" s="29" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="20" ht="18">
       <c r="A20" s="25" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B20" s="26" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C20" s="27"/>
       <c r="D20" s="28"/>
@@ -3368,44 +3424,47 @@
       <c r="AE20" s="16">
         <v>1618.97</v>
       </c>
-      <c r="AF20" s="19">
-        <f>MIN(C20:AE20)</f>
-        <v>1601.5</v>
-      </c>
-      <c r="AG20" s="20">
-        <f>MAX(C20:AE20)</f>
+      <c r="AF20" s="16">
+        <v>1590.98</v>
+      </c>
+      <c r="AG20" s="19">
+        <f>MIN(C20:AF20)</f>
+        <v>1590.98</v>
+      </c>
+      <c r="AH20" s="20">
+        <f>MAX(C20:AF20)</f>
         <v>1624.75</v>
       </c>
-      <c r="AH20" s="20">
-        <f>AVERAGE(C20:AE20)</f>
-        <v>1615.0733333333335</v>
-      </c>
       <c r="AI20" s="20">
-        <f>AVERAGE(Q20:AE20)</f>
-        <v>1615.0733333333335</v>
-      </c>
-      <c r="AJ20" s="21">
-        <f>(AI20/AH20)-1</f>
+        <f>AVERAGE(C20:AF20)</f>
+        <v>1609.0500000000002</v>
+      </c>
+      <c r="AJ20" s="20">
+        <f>AVERAGE(Q20:AF20)</f>
+        <v>1609.0500000000002</v>
+      </c>
+      <c r="AK20" s="21">
+        <f>(AJ20/AI20)-1</f>
         <v>0</v>
       </c>
-      <c r="AK20" s="21">
-        <f>(AI20/AF20)-1</f>
-        <v>8.4753876574046316e-003</v>
-      </c>
       <c r="AL20" s="21">
-        <f>(AG20/AF20)-1</f>
-        <v>1.4517639712769315e-002</v>
-      </c>
-      <c r="AM20" s="29" t="s">
-        <v>87</v>
+        <f>(AJ20/AG20)-1</f>
+        <v>1.1357779481828922e-002</v>
+      </c>
+      <c r="AM20" s="21">
+        <f>(AH20/AG20)-1</f>
+        <v>2.1225911073677883e-002</v>
+      </c>
+      <c r="AN20" s="29" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="21" ht="18">
       <c r="A21" s="25" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C21" s="27"/>
       <c r="D21" s="28"/>
@@ -3442,44 +3501,47 @@
       <c r="AE21" s="16">
         <v>692.88999999999999</v>
       </c>
-      <c r="AF21" s="19">
-        <f>MIN(C21:AE21)</f>
-        <v>692.88999999999999</v>
-      </c>
-      <c r="AG21" s="20">
-        <f>MAX(C21:AE21)</f>
+      <c r="AF21" s="16">
+        <v>692.62</v>
+      </c>
+      <c r="AG21" s="19">
+        <f>MIN(C21:AF21)</f>
+        <v>692.62</v>
+      </c>
+      <c r="AH21" s="20">
+        <f>MAX(C21:AF21)</f>
         <v>759.95000000000005</v>
       </c>
-      <c r="AH21" s="20">
-        <f>AVERAGE(C21:AE21)</f>
-        <v>715.24333333333334</v>
-      </c>
       <c r="AI21" s="20">
-        <f>AVERAGE(Q21:AE21)</f>
-        <v>715.24333333333334</v>
-      </c>
-      <c r="AJ21" s="21">
-        <f>(AI21/AH21)-1</f>
+        <f>AVERAGE(C21:AF21)</f>
+        <v>709.58749999999998</v>
+      </c>
+      <c r="AJ21" s="20">
+        <f>AVERAGE(Q21:AF21)</f>
+        <v>709.58749999999998</v>
+      </c>
+      <c r="AK21" s="21">
+        <f>(AJ21/AI21)-1</f>
         <v>0</v>
       </c>
-      <c r="AK21" s="21">
-        <f>(AI21/AF21)-1</f>
-        <v>3.2261013051614773e-002</v>
-      </c>
       <c r="AL21" s="21">
-        <f>(AG21/AF21)-1</f>
-        <v>9.6783039154844319e-002</v>
-      </c>
-      <c r="AM21" s="29" t="s">
-        <v>89</v>
+        <f>(AJ21/AG21)-1</f>
+        <v>2.4497559989604678e-002</v>
+      </c>
+      <c r="AM21" s="21">
+        <f>(AH21/AG21)-1</f>
+        <v>9.7210591666426094e-002</v>
+      </c>
+      <c r="AN21" s="29" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="22" ht="18">
       <c r="A22" s="25" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B22" s="26" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C22" s="27"/>
       <c r="D22" s="28"/>
@@ -3514,44 +3576,47 @@
       <c r="AE22" s="16">
         <v>1323.99</v>
       </c>
-      <c r="AF22" s="19">
-        <f>MIN(C22:AE22)</f>
+      <c r="AF22" s="16">
+        <v>1359.98</v>
+      </c>
+      <c r="AG22" s="19">
+        <f>MIN(C22:AF22)</f>
         <v>1323.99</v>
       </c>
-      <c r="AG22" s="20">
-        <f>MAX(C22:AE22)</f>
+      <c r="AH22" s="20">
+        <f>MAX(C22:AF22)</f>
         <v>1410.9000000000001</v>
       </c>
-      <c r="AH22" s="20">
-        <f>AVERAGE(C22:AE22)</f>
-        <v>1367.4450000000002</v>
-      </c>
       <c r="AI22" s="20">
-        <f>AVERAGE(Q22:AE22)</f>
-        <v>1367.4450000000002</v>
-      </c>
-      <c r="AJ22" s="21">
-        <f>(AI22/AH22)-1</f>
+        <f>AVERAGE(C22:AF22)</f>
+        <v>1364.9566666666667</v>
+      </c>
+      <c r="AJ22" s="20">
+        <f>AVERAGE(Q22:AF22)</f>
+        <v>1364.9566666666667</v>
+      </c>
+      <c r="AK22" s="21">
+        <f>(AJ22/AI22)-1</f>
         <v>0</v>
       </c>
-      <c r="AK22" s="21">
-        <f>(AI22/AF22)-1</f>
-        <v>3.2821244873450839e-002</v>
-      </c>
       <c r="AL22" s="21">
-        <f>(AG22/AF22)-1</f>
+        <f>(AJ22/AG22)-1</f>
+        <v>3.0941824837549259e-002</v>
+      </c>
+      <c r="AM22" s="21">
+        <f>(AH22/AG22)-1</f>
         <v>6.5642489746901456e-002</v>
       </c>
-      <c r="AM22" s="29" t="s">
-        <v>91</v>
+      <c r="AN22" s="29" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="23" ht="18">
       <c r="A23" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C23" s="24">
         <v>176.69</v>
@@ -3634,44 +3699,47 @@
       <c r="AE23" s="30">
         <v>260</v>
       </c>
-      <c r="AF23" s="19">
-        <f>MIN(C23:AE23)</f>
+      <c r="AF23" s="30">
+        <v>260</v>
+      </c>
+      <c r="AG23" s="19">
+        <f>MIN(C23:AF23)</f>
         <v>145</v>
       </c>
-      <c r="AG23" s="20">
-        <f>MAX(C23:AE23)</f>
+      <c r="AH23" s="20">
+        <f>MAX(C23:AF23)</f>
         <v>260</v>
       </c>
-      <c r="AH23" s="20">
-        <f>AVERAGE(C23:AE23)</f>
-        <v>214.57423076923075</v>
-      </c>
       <c r="AI23" s="20">
-        <f>AVERAGE(Q23:AE23)</f>
-        <v>246.16666666666666</v>
-      </c>
-      <c r="AJ23" s="21">
-        <f>(AI23/AH23)-1</f>
-        <v>0.14723313132327043</v>
+        <f>AVERAGE(C23:AF23)</f>
+        <v>216.25666666666663</v>
+      </c>
+      <c r="AJ23" s="20">
+        <f>AVERAGE(Q23:AF23)</f>
+        <v>247.03125</v>
       </c>
       <c r="AK23" s="21">
-        <f>(AI23/AF23)-1</f>
-        <v>0.69770114942528738</v>
+        <f>(AJ23/AI23)-1</f>
+        <v>0.14230582486859777</v>
       </c>
       <c r="AL23" s="21">
-        <f>(AG23/AF23)-1</f>
+        <f>(AJ23/AG23)-1</f>
+        <v>0.70366379310344818</v>
+      </c>
+      <c r="AM23" s="21">
+        <f>(AH23/AG23)-1</f>
         <v>0.7931034482758621</v>
       </c>
-      <c r="AM23" s="22" t="s">
-        <v>93</v>
+      <c r="AN23" s="22" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="24" ht="18">
       <c r="A24" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C24" s="16"/>
       <c r="D24" s="16"/>
@@ -3720,7 +3788,7 @@
         <v>212.31</v>
       </c>
       <c r="U24" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="V24" s="18">
         <v>229.94999999999999</v>
@@ -3752,44 +3820,47 @@
       <c r="AE24" s="30">
         <v>270</v>
       </c>
-      <c r="AF24" s="19">
-        <f>MIN(C24:AE24)</f>
+      <c r="AF24" s="30">
+        <v>270</v>
+      </c>
+      <c r="AG24" s="19">
+        <f>MIN(C24:AF24)</f>
         <v>176.91999999999999</v>
       </c>
-      <c r="AG24" s="20">
-        <f>MAX(C24:AE24)</f>
+      <c r="AH24" s="20">
+        <f>MAX(C24:AF24)</f>
         <v>270</v>
       </c>
-      <c r="AH24" s="20">
-        <f>AVERAGE(C24:AE24)</f>
-        <v>217.53208333333336</v>
-      </c>
       <c r="AI24" s="20">
-        <f>AVERAGE(Q24:AE24)</f>
-        <v>244.08500000000001</v>
-      </c>
-      <c r="AJ24" s="21">
-        <f>(AI24/AH24)-1</f>
-        <v>0.12206436981518043</v>
+        <f>AVERAGE(C24:AF24)</f>
+        <v>219.63080000000002</v>
+      </c>
+      <c r="AJ24" s="20">
+        <f>AVERAGE(Q24:AF24)</f>
+        <v>245.81266666666667</v>
       </c>
       <c r="AK24" s="21">
-        <f>(AI24/AF24)-1</f>
-        <v>0.37963486321501261</v>
+        <f>(AJ24/AI24)-1</f>
+        <v>0.11920853845028412</v>
       </c>
       <c r="AL24" s="21">
-        <f>(AG24/AF24)-1</f>
+        <f>(AJ24/AG24)-1</f>
+        <v>0.38940010550908144</v>
+      </c>
+      <c r="AM24" s="21">
+        <f>(AH24/AG24)-1</f>
         <v>0.52611349762604576</v>
       </c>
-      <c r="AM24" s="22" t="s">
-        <v>95</v>
+      <c r="AN24" s="22" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="25" ht="18">
       <c r="A25" s="25" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B25" s="26" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C25" s="28"/>
       <c r="D25" s="28"/>
@@ -3802,31 +3873,31 @@
         <v>396.77999999999997</v>
       </c>
       <c r="I25" s="28" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J25" s="28" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K25" s="28" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L25" s="28" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M25" s="28" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N25" s="28" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O25" s="28" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="P25" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Q25" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="R25" s="16">
         <v>413</v>
@@ -3838,7 +3909,7 @@
         <v>408.87</v>
       </c>
       <c r="U25" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="V25" s="16">
         <v>453.04000000000002</v>
@@ -3870,44 +3941,47 @@
       <c r="AE25" s="16">
         <v>349</v>
       </c>
-      <c r="AF25" s="19">
-        <f>MIN(C25:AE25)</f>
-        <v>349</v>
-      </c>
-      <c r="AG25" s="20">
-        <f>MAX(C25:AE25)</f>
+      <c r="AF25" s="16">
+        <v>345</v>
+      </c>
+      <c r="AG25" s="19">
+        <f>MIN(C25:AF25)</f>
+        <v>345</v>
+      </c>
+      <c r="AH25" s="20">
+        <f>MAX(C25:AF25)</f>
         <v>453.04000000000002</v>
       </c>
-      <c r="AH25" s="20">
-        <f>AVERAGE(C25:AE25)</f>
-        <v>384.43533333333329</v>
-      </c>
       <c r="AI25" s="20">
-        <f>AVERAGE(Q25:AE25)</f>
-        <v>382.53615384615381</v>
-      </c>
-      <c r="AJ25" s="21">
-        <f>(AI25/AH25)-1</f>
-        <v>-4.9401793292833673e-003</v>
+        <f>AVERAGE(C25:AF25)</f>
+        <v>381.97062499999998</v>
+      </c>
+      <c r="AJ25" s="20">
+        <f>AVERAGE(Q25:AF25)</f>
+        <v>379.85499999999996</v>
       </c>
       <c r="AK25" s="21">
-        <f>(AI25/AF25)-1</f>
-        <v>9.6092131364337474e-002</v>
+        <f>(AJ25/AI25)-1</f>
+        <v>-5.5387112556103402e-003</v>
       </c>
       <c r="AL25" s="21">
-        <f>(AG25/AF25)-1</f>
-        <v>0.29810888252148993</v>
-      </c>
-      <c r="AM25" s="29" t="s">
-        <v>97</v>
+        <f>(AJ25/AG25)-1</f>
+        <v>0.10102898550724637</v>
+      </c>
+      <c r="AM25" s="21">
+        <f>(AH25/AG25)-1</f>
+        <v>0.31315942028985511</v>
+      </c>
+      <c r="AN25" s="29" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="26" ht="54">
       <c r="A26" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C26" s="16"/>
       <c r="D26" s="16"/>
@@ -3974,58 +4048,61 @@
         <v>600</v>
       </c>
       <c r="AA26" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB26" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AC26" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AD26" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AE26" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF26" s="19">
-        <f>MIN(C26:AE26)</f>
+        <v>51</v>
+      </c>
+      <c r="AF26" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="AG26" s="19">
+        <f>MIN(C26:AF26)</f>
         <v>550</v>
       </c>
-      <c r="AG26" s="20">
-        <f>MAX(C26:AE26)</f>
+      <c r="AH26" s="20">
+        <f>MAX(C26:AF26)</f>
         <v>600</v>
       </c>
-      <c r="AH26" s="20">
-        <f>AVERAGE(C26:AE26)</f>
+      <c r="AI26" s="20">
+        <f>AVERAGE(C26:AF26)</f>
         <v>574</v>
       </c>
-      <c r="AI26" s="20">
-        <f>AVERAGE(Q26:AE26)</f>
+      <c r="AJ26" s="20">
+        <f>AVERAGE(Q26:AF26)</f>
         <v>598</v>
       </c>
-      <c r="AJ26" s="21">
-        <f>(AI26/AH26)-1</f>
+      <c r="AK26" s="21">
+        <f>(AJ26/AI26)-1</f>
         <v>4.1811846689895571e-002</v>
       </c>
-      <c r="AK26" s="21">
-        <f>(AI26/AF26)-1</f>
+      <c r="AL26" s="21">
+        <f>(AJ26/AG26)-1</f>
         <v>8.7272727272727169e-002</v>
       </c>
-      <c r="AL26" s="21">
-        <f>(AG26/AF26)-1</f>
+      <c r="AM26" s="21">
+        <f>(AH26/AG26)-1</f>
         <v>9.0909090909090828e-002</v>
       </c>
-      <c r="AM26" s="22" t="s">
-        <v>100</v>
+      <c r="AN26" s="22" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="27" ht="36">
       <c r="A27" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C27" s="16"/>
       <c r="D27" s="16"/>
@@ -4106,44 +4183,47 @@
       <c r="AE27" s="24">
         <v>599.99000000000001</v>
       </c>
-      <c r="AF27" s="19">
-        <f>MIN(C27:AE27)</f>
+      <c r="AF27" s="16">
+        <v>799.99000000000001</v>
+      </c>
+      <c r="AG27" s="19">
+        <f>MIN(C27:AF27)</f>
         <v>550</v>
       </c>
-      <c r="AG27" s="20">
-        <f>MAX(C27:AE27)</f>
+      <c r="AH27" s="20">
+        <f>MAX(C27:AF27)</f>
         <v>800</v>
       </c>
-      <c r="AH27" s="20">
-        <f>AVERAGE(C27:AE27)</f>
-        <v>595.19880000000001</v>
-      </c>
       <c r="AI27" s="20">
-        <f>AVERAGE(Q27:AE27)</f>
-        <v>625.3313333333333</v>
-      </c>
-      <c r="AJ27" s="21">
-        <f>(AI27/AH27)-1</f>
-        <v>5.0625998125892302e-002</v>
+        <f>AVERAGE(C27:AF27)</f>
+        <v>603.07538461538456</v>
+      </c>
+      <c r="AJ27" s="20">
+        <f>AVERAGE(Q27:AF27)</f>
+        <v>636.24749999999995</v>
       </c>
       <c r="AK27" s="21">
-        <f>(AI27/AF27)-1</f>
-        <v>0.13696606060606054</v>
+        <f>(AJ27/AI27)-1</f>
+        <v>5.5004923481947632e-002</v>
       </c>
       <c r="AL27" s="21">
-        <f>(AG27/AF27)-1</f>
+        <f>(AJ27/AG27)-1</f>
+        <v>0.15681363636363632</v>
+      </c>
+      <c r="AM27" s="21">
+        <f>(AH27/AG27)-1</f>
         <v>0.45454545454545459</v>
       </c>
-      <c r="AM27" s="29" t="s">
-        <v>102</v>
+      <c r="AN27" s="29" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="28" ht="18">
       <c r="A28" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C28" s="16"/>
       <c r="D28" s="16"/>
@@ -4224,44 +4304,47 @@
       <c r="AE28" s="33">
         <v>329</v>
       </c>
-      <c r="AF28" s="19">
-        <f>MIN(C28:AE28)</f>
+      <c r="AF28" s="30">
+        <v>961</v>
+      </c>
+      <c r="AG28" s="19">
+        <f>MIN(C28:AF28)</f>
         <v>329</v>
       </c>
-      <c r="AG28" s="20">
-        <f>MAX(C28:AE28)</f>
+      <c r="AH28" s="20">
+        <f>MAX(C28:AF28)</f>
         <v>969.95000000000005</v>
       </c>
-      <c r="AH28" s="20">
-        <f>AVERAGE(C28:AE28)</f>
-        <v>512.548</v>
-      </c>
       <c r="AI28" s="20">
-        <f>AVERAGE(Q28:AE28)</f>
-        <v>558.58666666666659</v>
-      </c>
-      <c r="AJ28" s="21">
-        <f>(AI28/AH28)-1</f>
-        <v>8.9823132012351259e-002</v>
+        <f>AVERAGE(C28:AF28)</f>
+        <v>529.79615384615386</v>
+      </c>
+      <c r="AJ28" s="20">
+        <f>AVERAGE(Q28:AF28)</f>
+        <v>583.73749999999995</v>
       </c>
       <c r="AK28" s="21">
-        <f>(AI28/AF28)-1</f>
-        <v>0.69783181357649426</v>
+        <f>(AJ28/AI28)-1</f>
+        <v>0.10181528454340194</v>
       </c>
       <c r="AL28" s="21">
-        <f>(AG28/AF28)-1</f>
+        <f>(AJ28/AG28)-1</f>
+        <v>0.7742781155015197</v>
+      </c>
+      <c r="AM28" s="21">
+        <f>(AH28/AG28)-1</f>
         <v>1.9481762917933132</v>
       </c>
-      <c r="AM28" s="22" t="s">
-        <v>105</v>
+      <c r="AN28" s="22" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="29" ht="18">
       <c r="A29" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C29" s="16"/>
       <c r="D29" s="16"/>
@@ -4342,44 +4425,47 @@
       <c r="AE29" s="30">
         <v>765.98000000000002</v>
       </c>
-      <c r="AF29" s="19">
-        <f>MIN(C29:AE29)</f>
+      <c r="AF29" s="30">
+        <v>783.32000000000005</v>
+      </c>
+      <c r="AG29" s="19">
+        <f>MIN(C29:AF29)</f>
         <v>371.14999999999998</v>
       </c>
-      <c r="AG29" s="20">
-        <f>MAX(C29:AE29)</f>
-        <v>765.98000000000002</v>
-      </c>
       <c r="AH29" s="20">
-        <f>AVERAGE(C29:AE29)</f>
-        <v>475.2743999999999</v>
+        <f>MAX(C29:AF29)</f>
+        <v>783.32000000000005</v>
       </c>
       <c r="AI29" s="20">
-        <f>AVERAGE(Q29:AE29)</f>
-        <v>510.87599999999998</v>
-      </c>
-      <c r="AJ29" s="21">
-        <f>(AI29/AH29)-1</f>
-        <v>7.4907463982911926e-002</v>
+        <f>AVERAGE(C29:AF29)</f>
+        <v>487.12230769230757</v>
+      </c>
+      <c r="AJ29" s="20">
+        <f>AVERAGE(Q29:AF29)</f>
+        <v>527.90374999999995</v>
       </c>
       <c r="AK29" s="21">
-        <f>(AI29/AF29)-1</f>
-        <v>0.37646773541694745</v>
+        <f>(AJ29/AI29)-1</f>
+        <v>8.371910229463797e-002</v>
       </c>
       <c r="AL29" s="21">
-        <f>(AG29/AF29)-1</f>
-        <v>1.0638016974269164</v>
-      </c>
-      <c r="AM29" s="22" t="s">
-        <v>107</v>
+        <f>(AJ29/AG29)-1</f>
+        <v>0.42234608648794292</v>
+      </c>
+      <c r="AM29" s="21">
+        <f>(AH29/AG29)-1</f>
+        <v>1.1105213525528765</v>
+      </c>
+      <c r="AN29" s="22" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="30" ht="36">
       <c r="A30" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B30" s="26" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C30" s="28"/>
       <c r="D30" s="28"/>
@@ -4464,44 +4550,47 @@
       <c r="AE30" s="30">
         <v>684.23000000000002</v>
       </c>
-      <c r="AF30" s="19">
-        <f>MIN(C30:AE30)</f>
+      <c r="AF30" s="30">
+        <v>684.35000000000002</v>
+      </c>
+      <c r="AG30" s="19">
+        <f>MIN(C30:AF30)</f>
         <v>396</v>
       </c>
-      <c r="AG30" s="20">
-        <f>MAX(C30:AE30)</f>
-        <v>684.23000000000002</v>
-      </c>
       <c r="AH30" s="20">
-        <f>AVERAGE(C30:AE30)</f>
-        <v>554.04407407407405</v>
+        <f>MAX(C30:AF30)</f>
+        <v>684.35000000000002</v>
       </c>
       <c r="AI30" s="20">
-        <f>AVERAGE(Q30:AE30)</f>
-        <v>594.02933333333328</v>
-      </c>
-      <c r="AJ30" s="21">
-        <f>(AI30/AH30)-1</f>
-        <v>7.2169816681250776e-002</v>
+        <f>AVERAGE(C30:AF30)</f>
+        <v>558.69785714285717</v>
+      </c>
+      <c r="AJ30" s="20">
+        <f>AVERAGE(Q30:AF30)</f>
+        <v>599.67437499999994</v>
       </c>
       <c r="AK30" s="21">
-        <f>(AI30/AF30)-1</f>
-        <v>0.50007407407407389</v>
+        <f>(AJ30/AI30)-1</f>
+        <v>7.3342894255392199e-002</v>
       </c>
       <c r="AL30" s="21">
-        <f>(AG30/AF30)-1</f>
-        <v>0.72785353535353536</v>
-      </c>
-      <c r="AM30" s="22" t="s">
-        <v>110</v>
+        <f>(AJ30/AG30)-1</f>
+        <v>0.51432922979797957</v>
+      </c>
+      <c r="AM30" s="21">
+        <f>(AH30/AG30)-1</f>
+        <v>0.72815656565656561</v>
+      </c>
+      <c r="AN30" s="22" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="31" ht="18">
       <c r="A31" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C31" s="16"/>
       <c r="D31" s="24">
@@ -4584,44 +4673,47 @@
       <c r="AE31" s="30">
         <v>1932.8299999999999</v>
       </c>
-      <c r="AF31" s="19">
-        <f>MIN(C31:AE31)</f>
+      <c r="AF31" s="30">
+        <v>1922.9000000000001</v>
+      </c>
+      <c r="AG31" s="19">
+        <f>MIN(C31:AF31)</f>
         <v>370</v>
       </c>
-      <c r="AG31" s="20">
-        <f>MAX(C31:AE31)</f>
+      <c r="AH31" s="20">
+        <f>MAX(C31:AF31)</f>
         <v>1932.8299999999999</v>
       </c>
-      <c r="AH31" s="20">
-        <f>AVERAGE(C31:AE31)</f>
-        <v>1257.5800000000002</v>
-      </c>
       <c r="AI31" s="20">
-        <f>AVERAGE(Q31:AE31)</f>
-        <v>1422.9766666666667</v>
-      </c>
-      <c r="AJ31" s="21">
-        <f>(AI31/AH31)-1</f>
-        <v>0.13151979728261143</v>
+        <f>AVERAGE(C31:AF31)</f>
+        <v>1282.2214814814815</v>
+      </c>
+      <c r="AJ31" s="20">
+        <f>AVERAGE(Q31:AF31)</f>
+        <v>1454.2218750000002</v>
       </c>
       <c r="AK31" s="21">
-        <f>(AI31/AF31)-1</f>
-        <v>2.8458828828828828</v>
+        <f>(AJ31/AI31)-1</f>
+        <v>0.13414249878249507</v>
       </c>
       <c r="AL31" s="21">
-        <f>(AG31/AF31)-1</f>
+        <f>(AJ31/AG31)-1</f>
+        <v>2.9303293918918922</v>
+      </c>
+      <c r="AM31" s="21">
+        <f>(AH31/AG31)-1</f>
         <v>4.2238648648648649</v>
       </c>
-      <c r="AM31" s="22" t="s">
-        <v>112</v>
+      <c r="AN31" s="22" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="32" ht="18">
       <c r="A32" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C32" s="16"/>
       <c r="D32" s="16"/>
@@ -4694,44 +4786,47 @@
       <c r="AE32" s="18">
         <v>169</v>
       </c>
-      <c r="AF32" s="19">
-        <f>MIN(C32:AE32)</f>
+      <c r="AF32" s="18">
+        <v>169.99000000000001</v>
+      </c>
+      <c r="AG32" s="19">
+        <f>MIN(C32:AF32)</f>
         <v>109.98999999999999</v>
       </c>
-      <c r="AG32" s="20">
-        <f>MAX(C32:AE32)</f>
+      <c r="AH32" s="20">
+        <f>MAX(C32:AF32)</f>
         <v>169.99000000000001</v>
       </c>
-      <c r="AH32" s="20">
-        <f>AVERAGE(C32:AE32)</f>
-        <v>153.92999999999998</v>
-      </c>
       <c r="AI32" s="20">
-        <f>AVERAGE(Q32:AE32)</f>
-        <v>163.12333333333333</v>
-      </c>
-      <c r="AJ32" s="21">
-        <f>(AI32/AH32)-1</f>
-        <v>5.9724117022889267e-002</v>
+        <f>AVERAGE(C32:AF32)</f>
+        <v>154.65999999999997</v>
+      </c>
+      <c r="AJ32" s="20">
+        <f>AVERAGE(Q32:AF32)</f>
+        <v>163.55250000000001</v>
       </c>
       <c r="AK32" s="21">
-        <f>(AI32/AF32)-1</f>
-        <v>0.48307421886838209</v>
+        <f>(AJ32/AI32)-1</f>
+        <v>5.7497090391827488e-002</v>
       </c>
       <c r="AL32" s="21">
-        <f>(AG32/AF32)-1</f>
+        <f>(AJ32/AG32)-1</f>
+        <v>0.48697608873533982</v>
+      </c>
+      <c r="AM32" s="21">
+        <f>(AH32/AG32)-1</f>
         <v>0.54550413673970377</v>
       </c>
-      <c r="AM32" s="22" t="s">
-        <v>114</v>
+      <c r="AN32" s="22" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="33" ht="18">
       <c r="A33" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B33" s="26" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C33" s="28"/>
       <c r="D33" s="28"/>
@@ -4804,44 +4899,47 @@
       <c r="AE33" s="17">
         <v>80.019999999999996</v>
       </c>
-      <c r="AF33" s="19">
-        <f>MIN(C33:AE33)</f>
+      <c r="AF33" s="17">
+        <v>80.019999999999996</v>
+      </c>
+      <c r="AG33" s="19">
+        <f>MIN(C33:AF33)</f>
         <v>68</v>
       </c>
-      <c r="AG33" s="20">
-        <f>MAX(C33:AE33)</f>
+      <c r="AH33" s="20">
+        <f>MAX(C33:AF33)</f>
         <v>85.700000000000003</v>
       </c>
-      <c r="AH33" s="20">
-        <f>AVERAGE(C33:AE33)</f>
-        <v>79.141428571428577</v>
-      </c>
       <c r="AI33" s="20">
-        <f>AVERAGE(Q33:AE33)</f>
-        <v>81.278000000000006</v>
-      </c>
-      <c r="AJ33" s="21">
-        <f>(AI33/AH33)-1</f>
-        <v>2.6996877199949365e-002</v>
+        <f>AVERAGE(C33:AF33)</f>
+        <v>79.181363636363642</v>
+      </c>
+      <c r="AJ33" s="20">
+        <f>AVERAGE(Q33:AF33)</f>
+        <v>81.199375000000003</v>
       </c>
       <c r="AK33" s="21">
-        <f>(AI33/AF33)-1</f>
-        <v>0.19526470588235312</v>
+        <f>(AJ33/AI33)-1</f>
+        <v>2.5485938495628524e-002</v>
       </c>
       <c r="AL33" s="21">
-        <f>(AG33/AF33)-1</f>
+        <f>(AJ33/AG33)-1</f>
+        <v>0.19410845588235293</v>
+      </c>
+      <c r="AM33" s="21">
+        <f>(AH33/AG33)-1</f>
         <v>0.26029411764705879</v>
       </c>
-      <c r="AM33" s="22" t="s">
-        <v>116</v>
+      <c r="AN33" s="22" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="34" ht="18">
       <c r="A34" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C34" s="16"/>
       <c r="D34" s="16"/>
@@ -4914,44 +5012,47 @@
       <c r="AE34" s="32">
         <v>97</v>
       </c>
-      <c r="AF34" s="19">
-        <f>MIN(C34:AE34)</f>
+      <c r="AF34" s="32">
+        <v>97</v>
+      </c>
+      <c r="AG34" s="19">
+        <f>MIN(C34:AF34)</f>
         <v>55</v>
       </c>
-      <c r="AG34" s="20">
-        <f>MAX(C34:AE34)</f>
+      <c r="AH34" s="20">
+        <f>MAX(C34:AF34)</f>
         <v>111</v>
       </c>
-      <c r="AH34" s="20">
-        <f>AVERAGE(C34:AE34)</f>
-        <v>89.615714285714304</v>
-      </c>
       <c r="AI34" s="20">
-        <f>AVERAGE(Q34:AE34)</f>
-        <v>96.811333333333323</v>
-      </c>
-      <c r="AJ34" s="21">
-        <f>(AI34/AH34)-1</f>
-        <v>8.0294166095444153e-002</v>
+        <f>AVERAGE(C34:AF34)</f>
+        <v>89.951363636363652</v>
+      </c>
+      <c r="AJ34" s="20">
+        <f>AVERAGE(Q34:AF34)</f>
+        <v>96.82312499999999</v>
       </c>
       <c r="AK34" s="21">
-        <f>(AI34/AF34)-1</f>
-        <v>0.76020606060606033</v>
+        <f>(AJ34/AI34)-1</f>
+        <v>7.6394187768137112e-002</v>
       </c>
       <c r="AL34" s="21">
-        <f>(AG34/AF34)-1</f>
+        <f>(AJ34/AG34)-1</f>
+        <v>0.76042045454545426</v>
+      </c>
+      <c r="AM34" s="21">
+        <f>(AH34/AG34)-1</f>
         <v>1.0181818181818181</v>
       </c>
-      <c r="AM34" s="22" t="s">
-        <v>118</v>
+      <c r="AN34" s="22" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="35" ht="18">
       <c r="A35" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C35" s="16"/>
       <c r="D35" s="16"/>
@@ -5022,44 +5123,47 @@
       <c r="AE35" s="16">
         <v>86.439999999999998</v>
       </c>
-      <c r="AF35" s="19">
-        <f>MIN(C35:AE35)</f>
+      <c r="AF35" s="18">
+        <v>99.980000000000004</v>
+      </c>
+      <c r="AG35" s="19">
+        <f>MIN(C35:AF35)</f>
         <v>47.359999999999999</v>
       </c>
-      <c r="AG35" s="20">
-        <f>MAX(C35:AE35)</f>
+      <c r="AH35" s="20">
+        <f>MAX(C35:AF35)</f>
         <v>100.68000000000001</v>
       </c>
-      <c r="AH35" s="20">
-        <f>AVERAGE(C35:AE35)</f>
-        <v>77.781500000000008</v>
-      </c>
       <c r="AI35" s="20">
-        <f>AVERAGE(Q35:AE35)</f>
-        <v>85.545333333333346</v>
-      </c>
-      <c r="AJ35" s="21">
-        <f>(AI35/AH35)-1</f>
-        <v>9.9815937380139719e-002</v>
+        <f>AVERAGE(C35:AF35)</f>
+        <v>78.838571428571441</v>
+      </c>
+      <c r="AJ35" s="20">
+        <f>AVERAGE(Q35:AF35)</f>
+        <v>86.447500000000019</v>
       </c>
       <c r="AK35" s="21">
-        <f>(AI35/AF35)-1</f>
-        <v>0.80627815315315354</v>
+        <f>(AJ35/AI35)-1</f>
+        <v>9.65127656875715e-002</v>
       </c>
       <c r="AL35" s="21">
-        <f>(AG35/AF35)-1</f>
+        <f>(AJ35/AG35)-1</f>
+        <v>0.82532728040540593</v>
+      </c>
+      <c r="AM35" s="21">
+        <f>(AH35/AG35)-1</f>
         <v>1.1258445945945947</v>
       </c>
-      <c r="AM35" s="22" t="s">
-        <v>120</v>
+      <c r="AN35" s="22" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="36" ht="18">
       <c r="A36" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B36" s="26" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C36" s="28"/>
       <c r="D36" s="28"/>
@@ -5095,7 +5199,7 @@
         <v>132.33000000000001</v>
       </c>
       <c r="T36" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="U36" s="17">
         <v>156</v>
@@ -5130,44 +5234,47 @@
       <c r="AE36" s="16">
         <v>138.16</v>
       </c>
-      <c r="AF36" s="19">
-        <f>MIN(C36:AE36)</f>
+      <c r="AF36" s="18">
+        <v>165.81999999999999</v>
+      </c>
+      <c r="AG36" s="19">
+        <f>MIN(C36:AF36)</f>
         <v>92.5</v>
       </c>
-      <c r="AG36" s="20">
-        <f>MAX(C36:AE36)</f>
-        <v>159.99000000000001</v>
-      </c>
       <c r="AH36" s="20">
-        <f>AVERAGE(C36:AE36)</f>
-        <v>133.36315789473684</v>
+        <f>MAX(C36:AF36)</f>
+        <v>165.81999999999999</v>
       </c>
       <c r="AI36" s="20">
-        <f>AVERAGE(Q36:AE36)</f>
-        <v>143.17214285714286</v>
-      </c>
-      <c r="AJ36" s="21">
-        <f>(AI36/AH36)-1</f>
-        <v>7.3550935035208376e-002</v>
+        <f>AVERAGE(C36:AF36)</f>
+        <v>134.98600000000002</v>
+      </c>
+      <c r="AJ36" s="20">
+        <f>AVERAGE(Q36:AF36)</f>
+        <v>144.68199999999999</v>
       </c>
       <c r="AK36" s="21">
-        <f>(AI36/AF36)-1</f>
-        <v>0.54780694980694977</v>
+        <f>(AJ36/AI36)-1</f>
+        <v>7.1829671225163816e-002</v>
       </c>
       <c r="AL36" s="21">
-        <f>(AG36/AF36)-1</f>
-        <v>0.72962162162162181</v>
-      </c>
-      <c r="AM36" s="22" t="s">
-        <v>122</v>
+        <f>(AJ36/AG36)-1</f>
+        <v>0.56412972972972963</v>
+      </c>
+      <c r="AM36" s="21">
+        <f>(AH36/AG36)-1</f>
+        <v>0.79264864864864859</v>
+      </c>
+      <c r="AN36" s="22" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="37" ht="18">
       <c r="A37" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C37" s="16"/>
       <c r="D37" s="16"/>
@@ -5236,44 +5343,47 @@
       <c r="AE37" s="17">
         <v>219.19</v>
       </c>
-      <c r="AF37" s="19">
-        <f>MIN(C37:AE37)</f>
+      <c r="AF37" s="18">
+        <v>269</v>
+      </c>
+      <c r="AG37" s="19">
+        <f>MIN(C37:AF37)</f>
         <v>148.88</v>
       </c>
-      <c r="AG37" s="20">
-        <f>MAX(C37:AE37)</f>
-        <v>257.87</v>
-      </c>
       <c r="AH37" s="20">
-        <f>AVERAGE(C37:AE37)</f>
-        <v>216.04684210526318</v>
+        <f>MAX(C37:AF37)</f>
+        <v>269</v>
       </c>
       <c r="AI37" s="20">
-        <f>AVERAGE(Q37:AE37)</f>
-        <v>221.58733333333336</v>
-      </c>
-      <c r="AJ37" s="21">
-        <f>(AI37/AH37)-1</f>
-        <v>2.5644860966635763e-002</v>
+        <f>AVERAGE(C37:AF37)</f>
+        <v>218.69450000000001</v>
+      </c>
+      <c r="AJ37" s="20">
+        <f>AVERAGE(Q37:AF37)</f>
+        <v>224.55062500000003</v>
       </c>
       <c r="AK37" s="21">
-        <f>(AI37/AF37)-1</f>
-        <v>0.48836199176070227</v>
+        <f>(AJ37/AI37)-1</f>
+        <v>2.6777651015457815e-002</v>
       </c>
       <c r="AL37" s="21">
-        <f>(AG37/AF37)-1</f>
-        <v>0.73206609349811935</v>
-      </c>
-      <c r="AM37" s="22" t="s">
-        <v>124</v>
+        <f>(AJ37/AG37)-1</f>
+        <v>0.50826588527673322</v>
+      </c>
+      <c r="AM37" s="21">
+        <f>(AH37/AG37)-1</f>
+        <v>0.80682428801719519</v>
+      </c>
+      <c r="AN37" s="22" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="38" ht="18">
       <c r="A38" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C38" s="16"/>
       <c r="D38" s="16"/>
@@ -5338,44 +5448,47 @@
       <c r="AE38" s="17">
         <v>149.99000000000001</v>
       </c>
-      <c r="AF38" s="19">
-        <f>MIN(C38:AE38)</f>
+      <c r="AF38" s="18">
+        <v>169</v>
+      </c>
+      <c r="AG38" s="19">
+        <f>MIN(C38:AF38)</f>
         <v>144.94999999999999</v>
       </c>
-      <c r="AG38" s="20">
-        <f>MAX(C38:AE38)</f>
-        <v>168.28999999999999</v>
-      </c>
       <c r="AH38" s="20">
-        <f>AVERAGE(C38:AE38)</f>
-        <v>154.02764705882353</v>
+        <f>MAX(C38:AF38)</f>
+        <v>169</v>
       </c>
       <c r="AI38" s="20">
-        <f>AVERAGE(Q38:AE38)</f>
-        <v>154.00199999999998</v>
-      </c>
-      <c r="AJ38" s="21">
-        <f>(AI38/AH38)-1</f>
-        <v>-1.665094501752673e-004</v>
+        <f>AVERAGE(C38:AF38)</f>
+        <v>154.85944444444445</v>
+      </c>
+      <c r="AJ38" s="20">
+        <f>AVERAGE(Q38:AF38)</f>
+        <v>154.93937499999998</v>
       </c>
       <c r="AK38" s="21">
-        <f>(AI38/AF38)-1</f>
-        <v>6.2449120386339985e-002</v>
+        <f>(AJ38/AI38)-1</f>
+        <v>5.1614905272501233e-004</v>
       </c>
       <c r="AL38" s="21">
-        <f>(AG38/AF38)-1</f>
-        <v>0.16102104173853049</v>
-      </c>
-      <c r="AM38" s="22" t="s">
-        <v>126</v>
+        <f>(AJ38/AG38)-1</f>
+        <v>6.8916005519144452e-002</v>
+      </c>
+      <c r="AM38" s="21">
+        <f>(AH38/AG38)-1</f>
+        <v>0.1659192825112108</v>
+      </c>
+      <c r="AN38" s="22" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="39" ht="18">
       <c r="A39" s="25" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B39" s="26" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C39" s="28"/>
       <c r="D39" s="28"/>
@@ -5440,44 +5553,47 @@
       <c r="AE39" s="17">
         <v>169</v>
       </c>
-      <c r="AF39" s="19">
-        <f>MIN(C39:AE39)</f>
+      <c r="AF39" s="17">
+        <v>159.99000000000001</v>
+      </c>
+      <c r="AG39" s="19">
+        <f>MIN(C39:AF39)</f>
         <v>144</v>
       </c>
-      <c r="AG39" s="20">
-        <f>MAX(C39:AE39)</f>
+      <c r="AH39" s="20">
+        <f>MAX(C39:AF39)</f>
         <v>199.94999999999999</v>
       </c>
-      <c r="AH39" s="20">
-        <f>AVERAGE(C39:AE39)</f>
-        <v>180.24000000000001</v>
-      </c>
       <c r="AI39" s="20">
-        <f>AVERAGE(Q39:AE39)</f>
-        <v>180.15000000000001</v>
-      </c>
-      <c r="AJ39" s="21">
-        <f>(AI39/AH39)-1</f>
-        <v>-4.9933422103864977e-004</v>
+        <f>AVERAGE(C39:AF39)</f>
+        <v>179.11499999999998</v>
+      </c>
+      <c r="AJ39" s="20">
+        <f>AVERAGE(Q39:AF39)</f>
+        <v>178.88999999999999</v>
       </c>
       <c r="AK39" s="21">
-        <f>(AI39/AF39)-1</f>
-        <v>0.25104166666666661</v>
+        <f>(AJ39/AI39)-1</f>
+        <v>-1.2561761996482401e-003</v>
       </c>
       <c r="AL39" s="21">
-        <f>(AG39/AF39)-1</f>
+        <f>(AJ39/AG39)-1</f>
+        <v>0.24229166666666657</v>
+      </c>
+      <c r="AM39" s="21">
+        <f>(AH39/AG39)-1</f>
         <v>0.38854166666666656</v>
       </c>
-      <c r="AM39" s="22" t="s">
-        <v>128</v>
+      <c r="AN39" s="22" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="40" ht="18">
       <c r="A40" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C40" s="16"/>
       <c r="D40" s="16"/>
@@ -5502,7 +5618,7 @@
         <v>31941.080000000002</v>
       </c>
       <c r="M40" s="16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="N40" s="17"/>
       <c r="O40" s="16"/>
@@ -5522,44 +5638,45 @@
       <c r="AC40" s="16"/>
       <c r="AD40" s="16"/>
       <c r="AE40" s="16"/>
-      <c r="AF40" s="19">
-        <f>MIN(C40:AE40)</f>
+      <c r="AF40" s="16"/>
+      <c r="AG40" s="19">
+        <f>MIN(C40:AF40)</f>
         <v>30731.380000000001</v>
       </c>
-      <c r="AG40" s="20">
-        <f>MAX(C40:AE40)</f>
+      <c r="AH40" s="20">
+        <f>MAX(C40:AF40)</f>
         <v>32790.889999999999</v>
       </c>
-      <c r="AH40" s="20">
-        <f>AVERAGE(C40:AE40)</f>
+      <c r="AI40" s="20">
+        <f>AVERAGE(C40:AF40)</f>
         <v>31912.133333333331</v>
       </c>
-      <c r="AI40" s="20" t="e">
-        <f>AVERAGE(Q40:AE40)</f>
+      <c r="AJ40" s="20" t="e">
+        <f>AVERAGE(Q40:AF40)</f>
         <v>#NUM!</v>
       </c>
-      <c r="AJ40" s="21" t="e">
-        <f>(AI40/AH40)-1</f>
+      <c r="AK40" s="21" t="e">
+        <f>(AJ40/AI40)-1</f>
         <v>#NUM!</v>
       </c>
-      <c r="AK40" s="21" t="e">
-        <f>(AI40/AF40)-1</f>
+      <c r="AL40" s="21" t="e">
+        <f>(AJ40/AG40)-1</f>
         <v>#NUM!</v>
       </c>
-      <c r="AL40" s="21">
-        <f>(AG40/AF40)-1</f>
+      <c r="AM40" s="21">
+        <f>(AH40/AG40)-1</f>
         <v>6.7016515366377982e-002</v>
       </c>
-      <c r="AM40" s="22" t="s">
-        <v>131</v>
+      <c r="AN40" s="22" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="41" ht="18">
       <c r="A41" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C41" s="16"/>
       <c r="D41" s="16"/>
@@ -5591,7 +5708,7 @@
         <v>721.67999999999995</v>
       </c>
       <c r="T41" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="U41" s="18">
         <v>1164</v>
@@ -5615,7 +5732,7 @@
         <v>1360.8</v>
       </c>
       <c r="AB41" s="35" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AC41" s="30">
         <v>1360.8</v>
@@ -5626,44 +5743,47 @@
       <c r="AE41" s="30">
         <v>1360.8</v>
       </c>
-      <c r="AF41" s="19">
-        <f>MIN(C41:AE41)</f>
+      <c r="AF41" s="30">
+        <v>1360.8</v>
+      </c>
+      <c r="AG41" s="19">
+        <f>MIN(C41:AF41)</f>
         <v>642.82000000000005</v>
       </c>
-      <c r="AG41" s="20">
-        <f>MAX(C41:AE41)</f>
+      <c r="AH41" s="20">
+        <f>MAX(C41:AF41)</f>
         <v>1360.8</v>
       </c>
-      <c r="AH41" s="20">
-        <f>AVERAGE(C41:AE41)</f>
-        <v>1046.4724999999999</v>
-      </c>
       <c r="AI41" s="20">
-        <f>AVERAGE(Q41:AE41)</f>
-        <v>1133.5569230769229</v>
-      </c>
-      <c r="AJ41" s="21">
-        <f>(AI41/AH41)-1</f>
-        <v>8.3217115668995589e-002</v>
+        <f>AVERAGE(C41:AF41)</f>
+        <v>1064.9623529411763</v>
+      </c>
+      <c r="AJ41" s="20">
+        <f>AVERAGE(Q41:AF41)</f>
+        <v>1149.7885714285712</v>
       </c>
       <c r="AK41" s="21">
-        <f>(AI41/AF41)-1</f>
-        <v>0.76341265529529689</v>
+        <f>(AJ41/AI41)-1</f>
+        <v>7.9651847084664329e-002</v>
       </c>
       <c r="AL41" s="21">
-        <f>(AG41/AF41)-1</f>
+        <f>(AJ41/AG41)-1</f>
+        <v>0.78866334499326585</v>
+      </c>
+      <c r="AM41" s="21">
+        <f>(AH41/AG41)-1</f>
         <v>1.1169223110668614</v>
       </c>
-      <c r="AM41" s="22" t="s">
-        <v>134</v>
+      <c r="AN41" s="22" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="42" ht="18">
       <c r="A42" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C42" s="16"/>
       <c r="D42" s="16"/>
@@ -5719,7 +5839,7 @@
         <v>2171.4000000000001</v>
       </c>
       <c r="AB42" s="35" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AC42" s="30">
         <v>2171.4000000000001</v>
@@ -5730,44 +5850,47 @@
       <c r="AE42" s="30">
         <v>2171.4000000000001</v>
       </c>
-      <c r="AF42" s="19">
-        <f>MIN(C42:AE42)</f>
+      <c r="AF42" s="30">
+        <v>2171.4000000000001</v>
+      </c>
+      <c r="AG42" s="19">
+        <f>MIN(C42:AF42)</f>
         <v>1151.71</v>
       </c>
-      <c r="AG42" s="20">
-        <f>MAX(C42:AE42)</f>
+      <c r="AH42" s="20">
+        <f>MAX(C42:AF42)</f>
         <v>2171.4000000000001</v>
       </c>
-      <c r="AH42" s="20">
-        <f>AVERAGE(C42:AE42)</f>
-        <v>1792.4200000000003</v>
-      </c>
       <c r="AI42" s="20">
-        <f>AVERAGE(Q42:AE42)</f>
-        <v>1920.5742857142864</v>
-      </c>
-      <c r="AJ42" s="21">
-        <f>(AI42/AH42)-1</f>
-        <v>7.1497911044446028e-002</v>
+        <f>AVERAGE(C42:AF42)</f>
+        <v>1813.474444444445</v>
+      </c>
+      <c r="AJ42" s="20">
+        <f>AVERAGE(Q42:AF42)</f>
+        <v>1937.2960000000007</v>
       </c>
       <c r="AK42" s="21">
-        <f>(AI42/AF42)-1</f>
-        <v>0.6675849699267058</v>
+        <f>(AJ42/AI42)-1</f>
+        <v>6.8278632728948185e-002</v>
       </c>
       <c r="AL42" s="21">
-        <f>(AG42/AF42)-1</f>
+        <f>(AJ42/AG42)-1</f>
+        <v>0.68210400187547271</v>
+      </c>
+      <c r="AM42" s="21">
+        <f>(AH42/AG42)-1</f>
         <v>0.88537044915820817</v>
       </c>
-      <c r="AM42" s="22" t="s">
-        <v>134</v>
+      <c r="AN42" s="22" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="43" ht="18">
       <c r="A43" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C43" s="16"/>
       <c r="D43" s="16"/>
@@ -5802,76 +5925,79 @@
         <v>3876</v>
       </c>
       <c r="U43" s="35" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="V43" s="35" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="W43" s="35" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="X43" s="35" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Y43" s="35" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="Z43" s="35" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AA43" s="35" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AB43" s="35" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AC43" s="35" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AD43" s="35" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AE43" s="35" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF43" s="19">
-        <f>MIN(C43:AE43)</f>
+        <v>51</v>
+      </c>
+      <c r="AF43" s="30">
+        <v>4082.4000000000001</v>
+      </c>
+      <c r="AG43" s="19">
+        <f>MIN(C43:AF43)</f>
         <v>2159.8299999999999</v>
       </c>
-      <c r="AG43" s="20">
-        <f>MAX(C43:AE43)</f>
-        <v>3876</v>
-      </c>
       <c r="AH43" s="20">
-        <f>AVERAGE(C43:AE43)</f>
-        <v>2544.02</v>
+        <f>MAX(C43:AF43)</f>
+        <v>4082.4000000000001</v>
       </c>
       <c r="AI43" s="20">
-        <f>AVERAGE(Q43:AE43)</f>
-        <v>2771.3400000000001</v>
-      </c>
-      <c r="AJ43" s="21">
-        <f>(AI43/AH43)-1</f>
-        <v>8.9354643438337877e-002</v>
+        <f>AVERAGE(C43:AF43)</f>
+        <v>2736.3175000000001</v>
+      </c>
+      <c r="AJ43" s="20">
+        <f>AVERAGE(Q43:AF43)</f>
+        <v>3033.5520000000001</v>
       </c>
       <c r="AK43" s="21">
-        <f>(AI43/AF43)-1</f>
-        <v>0.28312876476389359</v>
+        <f>(AJ43/AI43)-1</f>
+        <v>0.10862573513490292</v>
       </c>
       <c r="AL43" s="21">
-        <f>(AG43/AF43)-1</f>
-        <v>0.79458568498446636</v>
-      </c>
-      <c r="AM43" s="22" t="s">
-        <v>134</v>
+        <f>(AJ43/AG43)-1</f>
+        <v>0.40453276415273431</v>
+      </c>
+      <c r="AM43" s="21">
+        <f>(AH43/AG43)-1</f>
+        <v>0.89014876170809742</v>
+      </c>
+      <c r="AN43" s="22" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="44" ht="18">
       <c r="A44" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C44" s="16"/>
       <c r="D44" s="16"/>
@@ -5927,7 +6053,7 @@
         <v>2804.7600000000002</v>
       </c>
       <c r="AB44" s="35" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AC44" s="30">
         <v>2804.7600000000002</v>
@@ -5938,44 +6064,47 @@
       <c r="AE44" s="30">
         <v>2804.7600000000002</v>
       </c>
-      <c r="AF44" s="19">
-        <f>MIN(C44:AE44)</f>
+      <c r="AF44" s="30">
+        <v>2804.7600000000002</v>
+      </c>
+      <c r="AG44" s="19">
+        <f>MIN(C44:AF44)</f>
         <v>1310.1800000000001</v>
       </c>
-      <c r="AG44" s="20">
-        <f>MAX(C44:AE44)</f>
+      <c r="AH44" s="20">
+        <f>MAX(C44:AF44)</f>
         <v>2804.7600000000002</v>
       </c>
-      <c r="AH44" s="20">
-        <f>AVERAGE(C44:AE44)</f>
-        <v>2062.9847058823534</v>
-      </c>
       <c r="AI44" s="20">
-        <f>AVERAGE(Q44:AE44)</f>
-        <v>2222.8114285714291</v>
-      </c>
-      <c r="AJ44" s="21">
-        <f>(AI44/AH44)-1</f>
-        <v>7.7473537362322098e-002</v>
+        <f>AVERAGE(C44:AF44)</f>
+        <v>2104.1944444444448</v>
+      </c>
+      <c r="AJ44" s="20">
+        <f>AVERAGE(Q44:AF44)</f>
+        <v>2261.6080000000006</v>
       </c>
       <c r="AK44" s="21">
-        <f>(AI44/AF44)-1</f>
-        <v>0.6965695008101398</v>
+        <f>(AJ44/AI44)-1</f>
+        <v>7.4809415057227158e-002</v>
       </c>
       <c r="AL44" s="21">
-        <f>(AG44/AF44)-1</f>
+        <f>(AJ44/AG44)-1</f>
+        <v>0.72618113541650797</v>
+      </c>
+      <c r="AM44" s="21">
+        <f>(AH44/AG44)-1</f>
         <v>1.1407440199056618</v>
       </c>
-      <c r="AM44" s="22" t="s">
-        <v>134</v>
+      <c r="AN44" s="22" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="45" ht="18">
       <c r="A45" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C45" s="16"/>
       <c r="D45" s="16"/>
@@ -6030,44 +6159,47 @@
       <c r="AE45" s="18">
         <v>1592.6400000000001</v>
       </c>
-      <c r="AF45" s="19">
-        <f>MIN(C45:AE45)</f>
+      <c r="AF45" s="18">
         <v>1592.6400000000001</v>
       </c>
-      <c r="AG45" s="20">
-        <f>MAX(C45:AE45)</f>
+      <c r="AG45" s="19">
+        <f>MIN(C45:AF45)</f>
+        <v>1592.6400000000001</v>
+      </c>
+      <c r="AH45" s="20">
+        <f>MAX(C45:AF45)</f>
         <v>1896</v>
       </c>
-      <c r="AH45" s="20">
-        <f>AVERAGE(C45:AE45)</f>
-        <v>1643.1999999999998</v>
-      </c>
       <c r="AI45" s="20">
-        <f>AVERAGE(Q45:AE45)</f>
-        <v>1643.1999999999998</v>
-      </c>
-      <c r="AJ45" s="21">
-        <f>(AI45/AH45)-1</f>
+        <f>AVERAGE(C45:AF45)</f>
+        <v>1639.310769230769</v>
+      </c>
+      <c r="AJ45" s="20">
+        <f>AVERAGE(Q45:AF45)</f>
+        <v>1639.310769230769</v>
+      </c>
+      <c r="AK45" s="21">
+        <f>(AJ45/AI45)-1</f>
         <v>0</v>
       </c>
-      <c r="AK45" s="21">
-        <f>(AI45/AF45)-1</f>
-        <v>3.1746031746031633e-002</v>
-      </c>
       <c r="AL45" s="21">
-        <f>(AG45/AF45)-1</f>
+        <f>(AJ45/AG45)-1</f>
+        <v>2.9304029304028978e-002</v>
+      </c>
+      <c r="AM45" s="21">
+        <f>(AH45/AG45)-1</f>
         <v>0.19047619047619047</v>
       </c>
-      <c r="AM45" s="22" t="s">
-        <v>134</v>
+      <c r="AN45" s="22" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="46" ht="18">
       <c r="A46" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C46" s="16"/>
       <c r="D46" s="16"/>
@@ -6099,13 +6231,13 @@
         <v>1628.6199999999999</v>
       </c>
       <c r="T46" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="U46" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="V46" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="W46" s="18">
         <v>1985.76</v>
@@ -6117,7 +6249,7 @@
         <v>1985.76</v>
       </c>
       <c r="Z46" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AA46" s="18">
         <v>1985.76</v>
@@ -6126,52 +6258,55 @@
         <v>1985.76</v>
       </c>
       <c r="AC46" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AD46" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AE46" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF46" s="19">
-        <f>MIN(C46:AE46)</f>
+        <v>51</v>
+      </c>
+      <c r="AF46" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="AG46" s="19">
+        <f>MIN(C46:AF46)</f>
         <v>1480.5599999999999</v>
       </c>
-      <c r="AG46" s="20">
-        <f>MAX(C46:AE46)</f>
+      <c r="AH46" s="20">
+        <f>MAX(C46:AF46)</f>
         <v>1985.76</v>
       </c>
-      <c r="AH46" s="20">
-        <f>AVERAGE(C46:AE46)</f>
+      <c r="AI46" s="20">
+        <f>AVERAGE(C46:AF46)</f>
         <v>1764.0363636363634</v>
       </c>
-      <c r="AI46" s="20">
-        <f>AVERAGE(Q46:AE46)</f>
+      <c r="AJ46" s="20">
+        <f>AVERAGE(Q46:AF46)</f>
         <v>1851.8325</v>
       </c>
-      <c r="AJ46" s="21">
-        <f>(AI46/AH46)-1</f>
+      <c r="AK46" s="21">
+        <f>(AJ46/AI46)-1</f>
         <v>4.9770026385768329e-002</v>
       </c>
-      <c r="AK46" s="21">
-        <f>(AI46/AF46)-1</f>
+      <c r="AL46" s="21">
+        <f>(AJ46/AG46)-1</f>
         <v>0.25076491327605765</v>
       </c>
-      <c r="AL46" s="21">
-        <f>(AG46/AF46)-1</f>
+      <c r="AM46" s="21">
+        <f>(AH46/AG46)-1</f>
         <v>0.34122224023342529</v>
       </c>
-      <c r="AM46" s="22" t="s">
-        <v>134</v>
+      <c r="AN46" s="22" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="47" ht="18">
       <c r="A47" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C47" s="16"/>
       <c r="D47" s="16">
@@ -6204,41 +6339,42 @@
       <c r="AC47" s="16"/>
       <c r="AD47" s="16"/>
       <c r="AE47" s="16"/>
-      <c r="AF47" s="19">
-        <f>MIN(C47:AE47)</f>
+      <c r="AF47" s="16"/>
+      <c r="AG47" s="19">
+        <f>MIN(C47:AF47)</f>
         <v>339.45999999999998</v>
       </c>
-      <c r="AG47" s="20">
-        <f>MAX(C47:AE47)</f>
+      <c r="AH47" s="20">
+        <f>MAX(C47:AF47)</f>
         <v>339.45999999999998</v>
       </c>
-      <c r="AH47" s="20">
-        <f>AVERAGE(C47:AE47)</f>
+      <c r="AI47" s="20">
+        <f>AVERAGE(C47:AF47)</f>
         <v>339.45999999999998</v>
       </c>
-      <c r="AI47" s="20" t="e">
-        <f>AVERAGE(Q47:AE47)</f>
+      <c r="AJ47" s="20" t="e">
+        <f>AVERAGE(Q47:AF47)</f>
         <v>#NUM!</v>
       </c>
-      <c r="AJ47" s="21" t="e">
-        <f>(AI47/AH47)-1</f>
+      <c r="AK47" s="21" t="e">
+        <f>(AJ47/AI47)-1</f>
         <v>#NUM!</v>
       </c>
-      <c r="AK47" s="21" t="e">
-        <f>(AI47/AF47)-1</f>
+      <c r="AL47" s="21" t="e">
+        <f>(AJ47/AG47)-1</f>
         <v>#NUM!</v>
       </c>
-      <c r="AL47" s="21">
-        <f>(AG47/AF47)-1</f>
+      <c r="AM47" s="21">
+        <f>(AH47/AG47)-1</f>
         <v>0</v>
       </c>
     </row>
     <row r="48" ht="18">
       <c r="A48" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C48" s="16"/>
       <c r="D48" s="16"/>
@@ -6319,44 +6455,47 @@
       <c r="AE48" s="16">
         <v>378.99000000000001</v>
       </c>
-      <c r="AF48" s="19">
-        <f>MIN(C48:AE48)</f>
+      <c r="AF48" s="16">
         <v>378.99000000000001</v>
       </c>
-      <c r="AG48" s="20">
-        <f>MAX(C48:AE48)</f>
+      <c r="AG48" s="19">
+        <f>MIN(C48:AF48)</f>
         <v>378.99000000000001</v>
       </c>
       <c r="AH48" s="20">
-        <f>AVERAGE(C48:AE48)</f>
+        <f>MAX(C48:AF48)</f>
+        <v>378.99000000000001</v>
+      </c>
+      <c r="AI48" s="20">
+        <f>AVERAGE(C48:AF48)</f>
         <v>378.98999999999984</v>
       </c>
-      <c r="AI48" s="20">
-        <f>AVERAGE(Q48:AE48)</f>
+      <c r="AJ48" s="20">
+        <f>AVERAGE(Q48:AF48)</f>
         <v>378.9899999999999</v>
       </c>
-      <c r="AJ48" s="21">
-        <f>(AI48/AH48)-1</f>
+      <c r="AK48" s="21">
+        <f>(AJ48/AI48)-1</f>
         <v>2.2204460492503131e-016</v>
       </c>
-      <c r="AK48" s="21">
-        <f>(AI48/AF48)-1</f>
+      <c r="AL48" s="21">
+        <f>(AJ48/AG48)-1</f>
         <v>-3.3306690738754696e-016</v>
       </c>
-      <c r="AL48" s="21">
-        <f>(AG48/AF48)-1</f>
+      <c r="AM48" s="21">
+        <f>(AH48/AG48)-1</f>
         <v>0</v>
       </c>
-      <c r="AM48" s="22" t="s">
-        <v>145</v>
+      <c r="AN48" s="22" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="49" ht="18">
       <c r="A49" s="25" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B49" s="26" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C49" s="28"/>
       <c r="D49" s="28"/>
@@ -6437,44 +6576,47 @@
       <c r="AE49" s="30">
         <v>173.03999999999999</v>
       </c>
-      <c r="AF49" s="19">
-        <f>MIN(C49:AE49)</f>
+      <c r="AF49" s="30">
+        <v>173.03999999999999</v>
+      </c>
+      <c r="AG49" s="19">
+        <f>MIN(C49:AF49)</f>
         <v>88.329999999999998</v>
       </c>
-      <c r="AG49" s="20">
-        <f>MAX(C49:AE49)</f>
+      <c r="AH49" s="20">
+        <f>MAX(C49:AF49)</f>
         <v>191.19</v>
       </c>
-      <c r="AH49" s="20">
-        <f>AVERAGE(C49:AE49)</f>
-        <v>125.29440000000001</v>
-      </c>
       <c r="AI49" s="20">
-        <f>AVERAGE(Q49:AE49)</f>
-        <v>149.93733333333333</v>
-      </c>
-      <c r="AJ49" s="21">
-        <f>(AI49/AH49)-1</f>
-        <v>0.19668024535281159</v>
+        <f>AVERAGE(C49:AF49)</f>
+        <v>127.13076923076923</v>
+      </c>
+      <c r="AJ49" s="20">
+        <f>AVERAGE(Q49:AF49)</f>
+        <v>151.38124999999999</v>
       </c>
       <c r="AK49" s="21">
-        <f>(AI49/AF49)-1</f>
-        <v>0.69746782897467829</v>
+        <f>(AJ49/AI49)-1</f>
+        <v>0.19075225388757788</v>
       </c>
       <c r="AL49" s="21">
-        <f>(AG49/AF49)-1</f>
+        <f>(AJ49/AG49)-1</f>
+        <v>0.71381467225178308</v>
+      </c>
+      <c r="AM49" s="21">
+        <f>(AH49/AG49)-1</f>
         <v>1.1644967734631497</v>
       </c>
-      <c r="AM49" s="22" t="s">
-        <v>148</v>
+      <c r="AN49" s="22" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="50" ht="18">
       <c r="A50" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C50" s="16"/>
       <c r="D50" s="16">
@@ -6557,44 +6699,47 @@
       <c r="AE50" s="35">
         <v>36.189999999999998</v>
       </c>
-      <c r="AF50" s="19">
-        <f>MIN(C50:AE50)</f>
+      <c r="AF50" s="35">
+        <v>36.420000000000002</v>
+      </c>
+      <c r="AG50" s="19">
+        <f>MIN(C50:AF50)</f>
         <v>29.149999999999999</v>
       </c>
-      <c r="AG50" s="20">
-        <f>MAX(C50:AE50)</f>
+      <c r="AH50" s="20">
+        <f>MAX(C50:AF50)</f>
         <v>44.979999999999997</v>
       </c>
-      <c r="AH50" s="20">
-        <f>AVERAGE(C50:AE50)</f>
-        <v>36.377692307692307</v>
-      </c>
       <c r="AI50" s="20">
-        <f>AVERAGE(Q50:AE50)</f>
-        <v>36.298666666666669</v>
-      </c>
-      <c r="AJ50" s="21">
-        <f>(AI50/AH50)-1</f>
-        <v>-2.1723654254155456e-003</v>
+        <f>AVERAGE(C50:AF50)</f>
+        <v>36.379259259259257</v>
+      </c>
+      <c r="AJ50" s="20">
+        <f>AVERAGE(Q50:AF50)</f>
+        <v>36.306249999999999</v>
       </c>
       <c r="AK50" s="21">
-        <f>(AI50/AF50)-1</f>
-        <v>0.24523727844482579</v>
+        <f>(AJ50/AI50)-1</f>
+        <v>-2.0068924091871665e-003</v>
       </c>
       <c r="AL50" s="21">
-        <f>(AG50/AF50)-1</f>
+        <f>(AJ50/AG50)-1</f>
+        <v>0.2454974271012007</v>
+      </c>
+      <c r="AM50" s="21">
+        <f>(AH50/AG50)-1</f>
         <v>0.54305317324185243</v>
       </c>
-      <c r="AM50" s="22" t="s">
-        <v>151</v>
+      <c r="AN50" s="22" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="51" ht="18">
       <c r="A51" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C51" s="16"/>
       <c r="D51" s="16">
@@ -6677,44 +6822,47 @@
       <c r="AE51" s="35">
         <v>30.989999999999998</v>
       </c>
-      <c r="AF51" s="19">
-        <f>MIN(C51:AE51)</f>
+      <c r="AF51" s="35">
+        <v>30.989999999999998</v>
+      </c>
+      <c r="AG51" s="19">
+        <f>MIN(C51:AF51)</f>
         <v>25.989999999999998</v>
       </c>
-      <c r="AG51" s="20">
-        <f>MAX(C51:AE51)</f>
+      <c r="AH51" s="20">
+        <f>MAX(C51:AF51)</f>
         <v>42</v>
       </c>
-      <c r="AH51" s="20">
-        <f>AVERAGE(C51:AE51)</f>
-        <v>32.27192307692308</v>
-      </c>
       <c r="AI51" s="20">
-        <f>AVERAGE(Q51:AE51)</f>
-        <v>32.990000000000009</v>
-      </c>
-      <c r="AJ51" s="21">
-        <f>(AI51/AH51)-1</f>
-        <v>2.2250825318507639e-002</v>
+        <f>AVERAGE(C51:AF51)</f>
+        <v>32.224444444444444</v>
+      </c>
+      <c r="AJ51" s="20">
+        <f>AVERAGE(Q51:AF51)</f>
+        <v>32.865000000000009</v>
       </c>
       <c r="AK51" s="21">
-        <f>(AI51/AF51)-1</f>
-        <v>0.26933435936898853</v>
+        <f>(AJ51/AI51)-1</f>
+        <v>1.9877939452451754e-002</v>
       </c>
       <c r="AL51" s="21">
-        <f>(AG51/AF51)-1</f>
+        <f>(AJ51/AG51)-1</f>
+        <v>0.26452481723739951</v>
+      </c>
+      <c r="AM51" s="21">
+        <f>(AH51/AG51)-1</f>
         <v>0.61600615621392851</v>
       </c>
-      <c r="AM51" s="22" t="s">
-        <v>154</v>
+      <c r="AN51" s="22" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="52" ht="18">
       <c r="A52" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C52" s="16"/>
       <c r="D52" s="16">
@@ -6797,44 +6945,47 @@
       <c r="AE52" s="32">
         <v>34.719999999999999</v>
       </c>
-      <c r="AF52" s="19">
-        <f>MIN(C52:AE52)</f>
+      <c r="AF52" s="32">
+        <v>34.719999999999999</v>
+      </c>
+      <c r="AG52" s="19">
+        <f>MIN(C52:AF52)</f>
         <v>21.690000000000001</v>
       </c>
-      <c r="AG52" s="20">
-        <f>MAX(C52:AE52)</f>
+      <c r="AH52" s="20">
+        <f>MAX(C52:AF52)</f>
         <v>43.990000000000002</v>
       </c>
-      <c r="AH52" s="20">
-        <f>AVERAGE(C52:AE52)</f>
-        <v>29.281538461538453</v>
-      </c>
       <c r="AI52" s="20">
-        <f>AVERAGE(Q52:AE52)</f>
-        <v>28.367333333333331</v>
-      </c>
-      <c r="AJ52" s="21">
-        <f>(AI52/AH52)-1</f>
-        <v>-3.122121228042507e-002</v>
+        <f>AVERAGE(C52:AF52)</f>
+        <v>29.482962962962958</v>
+      </c>
+      <c r="AJ52" s="20">
+        <f>AVERAGE(Q52:AF52)</f>
+        <v>28.764375000000001</v>
       </c>
       <c r="AK52" s="21">
-        <f>(AI52/AF52)-1</f>
-        <v>0.30785308129706457</v>
+        <f>(AJ52/AI52)-1</f>
+        <v>-2.4372990050750998e-002</v>
       </c>
       <c r="AL52" s="21">
-        <f>(AG52/AF52)-1</f>
+        <f>(AJ52/AG52)-1</f>
+        <v>0.3261583679114799</v>
+      </c>
+      <c r="AM52" s="21">
+        <f>(AH52/AG52)-1</f>
         <v>1.0281235592438911</v>
       </c>
-      <c r="AM52" s="22" t="s">
-        <v>157</v>
+      <c r="AN52" s="22" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="53" ht="54">
       <c r="A53" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C53" s="16"/>
       <c r="D53" s="16"/>
@@ -6855,10 +7006,10 @@
         <v>1714.0799999999999</v>
       </c>
       <c r="K53" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L53" s="16" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M53" s="24">
         <v>1449.28</v>
@@ -6917,44 +7068,47 @@
       <c r="AE53" s="30">
         <v>2407.79</v>
       </c>
-      <c r="AF53" s="19">
-        <f>MIN(C53:AE53)</f>
+      <c r="AF53" s="30">
+        <v>2407.79</v>
+      </c>
+      <c r="AG53" s="19">
+        <f>MIN(C53:AF53)</f>
         <v>1449.28</v>
       </c>
-      <c r="AG53" s="20">
-        <f>MAX(C53:AE53)</f>
+      <c r="AH53" s="20">
+        <f>MAX(C53:AF53)</f>
         <v>2407.79</v>
       </c>
-      <c r="AH53" s="20">
-        <f>AVERAGE(C53:AE53)</f>
-        <v>1778.2366666666665</v>
-      </c>
       <c r="AI53" s="20">
-        <f>AVERAGE(Q53:AE53)</f>
-        <v>1813.0460000000005</v>
-      </c>
-      <c r="AJ53" s="21">
-        <f>(AI53/AH53)-1</f>
-        <v>1.9575197152235546e-002</v>
+        <f>AVERAGE(C53:AF53)</f>
+        <v>1803.4187999999997</v>
+      </c>
+      <c r="AJ53" s="20">
+        <f>AVERAGE(Q53:AF53)</f>
+        <v>1850.2175000000004</v>
       </c>
       <c r="AK53" s="21">
-        <f>(AI53/AF53)-1</f>
-        <v>0.25099773680724269</v>
+        <f>(AJ53/AI53)-1</f>
+        <v>2.5949990096588049e-002</v>
       </c>
       <c r="AL53" s="21">
-        <f>(AG53/AF53)-1</f>
+        <f>(AJ53/AG53)-1</f>
+        <v>0.27664598973283328</v>
+      </c>
+      <c r="AM53" s="21">
+        <f>(AH53/AG53)-1</f>
         <v>0.66136978361669252</v>
       </c>
-      <c r="AM53" s="1" t="s">
-        <v>159</v>
+      <c r="AN53" s="1" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="54" ht="18">
       <c r="A54" s="25" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B54" s="26" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C54" s="28"/>
       <c r="D54" s="28"/>
@@ -7035,44 +7189,47 @@
       <c r="AE54" s="35">
         <v>36.990000000000002</v>
       </c>
-      <c r="AF54" s="19">
-        <f>MIN(C54:AE54)</f>
+      <c r="AF54" s="35">
+        <v>35.689999999999998</v>
+      </c>
+      <c r="AG54" s="19">
+        <f>MIN(C54:AF54)</f>
         <v>30.989999999999998</v>
       </c>
-      <c r="AG54" s="20">
-        <f>MAX(C54:AE54)</f>
+      <c r="AH54" s="20">
+        <f>MAX(C54:AF54)</f>
         <v>43.990000000000002</v>
       </c>
-      <c r="AH54" s="20">
-        <f>AVERAGE(C54:AE54)</f>
-        <v>37.201599999999999</v>
-      </c>
       <c r="AI54" s="20">
-        <f>AVERAGE(Q54:AE54)</f>
-        <v>37.938000000000002</v>
-      </c>
-      <c r="AJ54" s="21">
-        <f>(AI54/AH54)-1</f>
-        <v>1.9794847533439519e-002</v>
+        <f>AVERAGE(C54:AF54)</f>
+        <v>37.143461538461537</v>
+      </c>
+      <c r="AJ54" s="20">
+        <f>AVERAGE(Q54:AF54)</f>
+        <v>37.797499999999999</v>
       </c>
       <c r="AK54" s="21">
-        <f>(AI54/AF54)-1</f>
-        <v>0.22420135527589569</v>
+        <f>(AJ54/AI54)-1</f>
+        <v>1.7608441282760179e-002</v>
       </c>
       <c r="AL54" s="21">
-        <f>(AG54/AF54)-1</f>
+        <f>(AJ54/AG54)-1</f>
+        <v>0.21966763472087769</v>
+      </c>
+      <c r="AM54" s="21">
+        <f>(AH54/AG54)-1</f>
         <v>0.41949015811552126</v>
       </c>
-      <c r="AM54" s="22" t="s">
-        <v>162</v>
+      <c r="AN54" s="22" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="55" ht="18">
       <c r="A55" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C55" s="16"/>
       <c r="D55" s="16"/>
@@ -7153,44 +7310,47 @@
       <c r="AE55" s="16">
         <v>89.950000000000003</v>
       </c>
-      <c r="AF55" s="19">
-        <f>MIN(C55:AE55)</f>
+      <c r="AF55" s="16">
+        <v>89.950000000000003</v>
+      </c>
+      <c r="AG55" s="19">
+        <f>MIN(C55:AF55)</f>
         <v>81.689999999999998</v>
       </c>
-      <c r="AG55" s="20">
-        <f>MAX(C55:AE55)</f>
+      <c r="AH55" s="20">
+        <f>MAX(C55:AF55)</f>
         <v>109.84999999999999</v>
       </c>
-      <c r="AH55" s="20">
-        <f>AVERAGE(C55:AE55)</f>
-        <v>88.717200000000005</v>
-      </c>
       <c r="AI55" s="20">
-        <f>AVERAGE(Q55:AE55)</f>
-        <v>87.554000000000016</v>
-      </c>
-      <c r="AJ55" s="21">
-        <f>(AI55/AH55)-1</f>
-        <v>-1.3111324523316648e-002</v>
+        <f>AVERAGE(C55:AF55)</f>
+        <v>88.764615384615382</v>
+      </c>
+      <c r="AJ55" s="20">
+        <f>AVERAGE(Q55:AF55)</f>
+        <v>87.703750000000014</v>
       </c>
       <c r="AK55" s="21">
-        <f>(AI55/AF55)-1</f>
-        <v>7.1783572040641674e-002</v>
+        <f>(AJ55/AI55)-1</f>
+        <v>-1.1951444615837747e-002</v>
       </c>
       <c r="AL55" s="21">
-        <f>(AG55/AF55)-1</f>
+        <f>(AJ55/AG55)-1</f>
+        <v>7.3616721752968628e-002</v>
+      </c>
+      <c r="AM55" s="21">
+        <f>(AH55/AG55)-1</f>
         <v>0.34471783572040637</v>
       </c>
-      <c r="AM55" s="1" t="s">
-        <v>165</v>
+      <c r="AN55" s="1" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="56" ht="18">
       <c r="A56" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C56" s="16"/>
       <c r="D56" s="16"/>
@@ -7273,44 +7433,47 @@
       <c r="AE56" s="35">
         <v>309.05000000000001</v>
       </c>
-      <c r="AF56" s="19">
-        <f>MIN(C56:AE56)</f>
+      <c r="AF56" s="35">
+        <v>309.05000000000001</v>
+      </c>
+      <c r="AG56" s="19">
+        <f>MIN(C56:AF56)</f>
         <v>298.80000000000001</v>
       </c>
-      <c r="AG56" s="20">
-        <f>MAX(C56:AE56)</f>
+      <c r="AH56" s="20">
+        <f>MAX(C56:AF56)</f>
         <v>309.05000000000001</v>
       </c>
-      <c r="AH56" s="20">
-        <f>AVERAGE(C56:AE56)</f>
-        <v>305.89615384615394</v>
-      </c>
       <c r="AI56" s="20">
-        <f>AVERAGE(Q56:AE56)</f>
-        <v>303.58333333333337</v>
-      </c>
-      <c r="AJ56" s="21">
-        <f>(AI56/AH56)-1</f>
-        <v>-7.5608028533230565e-003</v>
+        <f>AVERAGE(C56:AF56)</f>
+        <v>306.01296296296306</v>
+      </c>
+      <c r="AJ56" s="20">
+        <f>AVERAGE(Q56:AF56)</f>
+        <v>303.92500000000007</v>
       </c>
       <c r="AK56" s="21">
-        <f>(AI56/AF56)-1</f>
-        <v>1.6008478357875999e-002</v>
+        <f>(AJ56/AI56)-1</f>
+        <v>-6.8231193304568727e-003</v>
       </c>
       <c r="AL56" s="21">
-        <f>(AG56/AF56)-1</f>
+        <f>(AJ56/AG56)-1</f>
+        <v>1.7151941097724333e-002</v>
+      </c>
+      <c r="AM56" s="21">
+        <f>(AH56/AG56)-1</f>
         <v>3.4303882195448443e-002</v>
       </c>
-      <c r="AM56" s="22" t="s">
-        <v>168</v>
+      <c r="AN56" s="22" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="57" ht="18">
       <c r="A57" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C57" s="16"/>
       <c r="D57" s="16"/>
@@ -7391,41 +7554,44 @@
       <c r="AE57" s="24">
         <v>100.44</v>
       </c>
-      <c r="AF57" s="19">
-        <f>MIN(C57:AE57)</f>
+      <c r="AF57" s="24">
         <v>100.44</v>
       </c>
-      <c r="AG57" s="20">
-        <f>MAX(C57:AE57)</f>
+      <c r="AG57" s="19">
+        <f>MIN(C57:AF57)</f>
+        <v>100.44</v>
+      </c>
+      <c r="AH57" s="20">
+        <f>MAX(C57:AF57)</f>
         <v>108.98999999999999</v>
       </c>
-      <c r="AH57" s="20">
-        <f>AVERAGE(C57:AE57)</f>
-        <v>107.27999999999999</v>
-      </c>
       <c r="AI57" s="20">
-        <f>AVERAGE(Q57:AE57)</f>
-        <v>106.14000000000001</v>
-      </c>
-      <c r="AJ57" s="21">
-        <f>(AI57/AH57)-1</f>
-        <v>-1.0626398210290544e-002</v>
+        <f>AVERAGE(C57:AF57)</f>
+        <v>107.01692307692306</v>
+      </c>
+      <c r="AJ57" s="20">
+        <f>AVERAGE(Q57:AF57)</f>
+        <v>105.78375000000001</v>
       </c>
       <c r="AK57" s="21">
-        <f>(AI57/AF57)-1</f>
-        <v>5.675029868578263e-002</v>
+        <f>(AJ57/AI57)-1</f>
+        <v>-1.1523159529046256e-002</v>
       </c>
       <c r="AL57" s="21">
-        <f>(AG57/AF57)-1</f>
+        <f>(AJ57/AG57)-1</f>
+        <v>5.3203405017921312e-002</v>
+      </c>
+      <c r="AM57" s="21">
+        <f>(AH57/AG57)-1</f>
         <v>8.5125448028673834e-002</v>
       </c>
-      <c r="AM57" s="37" t="s">
-        <v>170</v>
+      <c r="AN57" s="37" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="58" ht="18">
       <c r="B58" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O58" s="16">
         <v>1.49</v>
@@ -7478,32 +7644,35 @@
       <c r="AE58" s="16">
         <v>1.99</v>
       </c>
-      <c r="AF58" s="19">
-        <f>MIN(C58:AE58)</f>
+      <c r="AF58" s="16">
+        <v>1.99</v>
+      </c>
+      <c r="AG58" s="19">
+        <f>MIN(C58:AF58)</f>
         <v>1.49</v>
       </c>
-      <c r="AG58" s="20">
-        <f>MAX(C58:AE58)</f>
+      <c r="AH58" s="20">
+        <f>MAX(C58:AF58)</f>
         <v>1.99</v>
       </c>
-      <c r="AH58" s="20">
-        <f>AVERAGE(C58:AE58)</f>
-        <v>1.8429411764705874</v>
-      </c>
       <c r="AI58" s="20">
-        <f>AVERAGE(Q58:AE58)</f>
-        <v>1.8899999999999995</v>
-      </c>
-      <c r="AJ58" s="21">
-        <f>(AI58/AH58)-1</f>
-        <v>2.5534631343760106e-002</v>
+        <f>AVERAGE(C58:AF58)</f>
+        <v>1.8511111111111103</v>
+      </c>
+      <c r="AJ58" s="20">
+        <f>AVERAGE(Q58:AF58)</f>
+        <v>1.8962499999999993</v>
       </c>
       <c r="AK58" s="21">
-        <f>(AI58/AF58)-1</f>
-        <v>0.26845637583892579</v>
+        <f>(AJ58/AI58)-1</f>
+        <v>2.4384753901560696e-002</v>
       </c>
       <c r="AL58" s="21">
-        <f>(AG58/AF58)-1</f>
+        <f>(AJ58/AG58)-1</f>
+        <v>0.27265100671140896</v>
+      </c>
+      <c r="AM58" s="21">
+        <f>(AH58/AG58)-1</f>
         <v>0.33557046979865768</v>
       </c>
     </row>
@@ -7513,13 +7682,14 @@
       <c r="AC59" s="1"/>
       <c r="AD59" s="1"/>
       <c r="AE59" s="1"/>
-      <c r="AF59" s="2"/>
+      <c r="AF59" s="1"/>
       <c r="AG59" s="2"/>
       <c r="AH59" s="2"/>
       <c r="AI59" s="2"/>
       <c r="AJ59" s="2"/>
       <c r="AK59" s="2"/>
       <c r="AL59" s="2"/>
+      <c r="AM59" s="2"/>
     </row>
     <row r="60" ht="14.25">
       <c r="AA60" s="1"/>
@@ -7527,13 +7697,14 @@
       <c r="AC60" s="1"/>
       <c r="AD60" s="1"/>
       <c r="AE60" s="1"/>
-      <c r="AF60" s="2"/>
+      <c r="AF60" s="1"/>
       <c r="AG60" s="2"/>
       <c r="AH60" s="2"/>
       <c r="AI60" s="2"/>
       <c r="AJ60" s="2"/>
       <c r="AK60" s="2"/>
       <c r="AL60" s="2"/>
+      <c r="AM60" s="2"/>
     </row>
     <row r="61" ht="14.25">
       <c r="AA61" s="1"/>
@@ -7541,13 +7712,14 @@
       <c r="AC61" s="1"/>
       <c r="AD61" s="1"/>
       <c r="AE61" s="1"/>
-      <c r="AF61" s="2"/>
+      <c r="AF61" s="1"/>
       <c r="AG61" s="2"/>
       <c r="AH61" s="2"/>
       <c r="AI61" s="2"/>
       <c r="AJ61" s="2"/>
       <c r="AK61" s="2"/>
       <c r="AL61" s="2"/>
+      <c r="AM61" s="2"/>
     </row>
     <row r="62" ht="14.25">
       <c r="AA62" s="1"/>
@@ -7555,76 +7727,77 @@
       <c r="AC62" s="1"/>
       <c r="AD62" s="1"/>
       <c r="AE62" s="1"/>
-      <c r="AF62" s="2"/>
+      <c r="AF62" s="1"/>
       <c r="AG62" s="2"/>
       <c r="AH62" s="2"/>
       <c r="AI62" s="2"/>
       <c r="AJ62" s="2"/>
       <c r="AK62" s="2"/>
       <c r="AL62" s="2"/>
+      <c r="AM62" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="AF1:AF2"/>
     <mergeCell ref="AG1:AG2"/>
     <mergeCell ref="AH1:AH2"/>
     <mergeCell ref="AI1:AI2"/>
     <mergeCell ref="AJ1:AJ2"/>
     <mergeCell ref="AK1:AK2"/>
     <mergeCell ref="AL1:AL2"/>
+    <mergeCell ref="AM1:AM2"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink r:id="rId1" ref="AM4"/>
-    <hyperlink r:id="rId2" ref="AM5"/>
-    <hyperlink r:id="rId3" ref="AM6"/>
-    <hyperlink r:id="rId4" ref="AM7"/>
-    <hyperlink r:id="rId5" ref="AM8"/>
-    <hyperlink r:id="rId6" ref="AM9"/>
-    <hyperlink r:id="rId7" ref="AM10"/>
-    <hyperlink r:id="rId8" ref="AM11"/>
-    <hyperlink r:id="rId9" ref="AM12"/>
-    <hyperlink r:id="rId10" ref="AM13"/>
-    <hyperlink r:id="rId11" ref="AM14"/>
-    <hyperlink r:id="rId12" ref="AM15"/>
-    <hyperlink r:id="rId13" ref="AM16"/>
-    <hyperlink r:id="rId14" ref="AM17"/>
-    <hyperlink r:id="rId15" ref="AM18"/>
-    <hyperlink r:id="rId16" ref="AM19"/>
-    <hyperlink r:id="rId17" ref="AM20"/>
-    <hyperlink r:id="rId18" ref="AM21"/>
-    <hyperlink r:id="rId19" ref="AM22"/>
-    <hyperlink r:id="rId20" ref="AM23"/>
-    <hyperlink r:id="rId21" ref="AM24"/>
-    <hyperlink r:id="rId22" ref="AM25"/>
-    <hyperlink r:id="rId23" ref="AM26"/>
-    <hyperlink r:id="rId24" ref="AM27"/>
-    <hyperlink r:id="rId25" ref="AM28"/>
-    <hyperlink r:id="rId26" ref="AM29"/>
-    <hyperlink r:id="rId27" ref="AM30"/>
-    <hyperlink r:id="rId28" ref="AM31"/>
-    <hyperlink r:id="rId29" ref="AM32"/>
-    <hyperlink r:id="rId30" ref="AM33"/>
-    <hyperlink r:id="rId31" ref="AM34"/>
-    <hyperlink r:id="rId32" ref="AM35"/>
-    <hyperlink r:id="rId33" ref="AM36"/>
-    <hyperlink r:id="rId34" ref="AM37"/>
-    <hyperlink r:id="rId35" ref="AM38"/>
-    <hyperlink r:id="rId36" ref="AM39"/>
-    <hyperlink r:id="rId37" ref="AM40"/>
-    <hyperlink r:id="rId38" ref="AM41"/>
-    <hyperlink r:id="rId38" ref="AM42"/>
-    <hyperlink r:id="rId38" ref="AM43"/>
-    <hyperlink r:id="rId38" ref="AM44"/>
-    <hyperlink r:id="rId38" ref="AM45"/>
-    <hyperlink r:id="rId38" ref="AM46"/>
-    <hyperlink r:id="rId39" ref="AM48"/>
-    <hyperlink r:id="rId40" ref="AM49"/>
-    <hyperlink r:id="rId41" ref="AM50"/>
-    <hyperlink r:id="rId42" ref="AM51"/>
-    <hyperlink r:id="rId43" ref="AM52"/>
-    <hyperlink r:id="rId44" ref="AM54"/>
-    <hyperlink r:id="rId45" ref="AM56"/>
-    <hyperlink r:id="rId46" ref="AM57"/>
+    <hyperlink r:id="rId1" ref="AN4"/>
+    <hyperlink r:id="rId2" ref="AN5"/>
+    <hyperlink r:id="rId3" ref="AN6"/>
+    <hyperlink r:id="rId4" ref="AN7"/>
+    <hyperlink r:id="rId5" ref="AN8"/>
+    <hyperlink r:id="rId6" ref="AN9"/>
+    <hyperlink r:id="rId7" ref="AN10"/>
+    <hyperlink r:id="rId8" ref="AN11"/>
+    <hyperlink r:id="rId9" ref="AN12"/>
+    <hyperlink r:id="rId10" ref="AN13"/>
+    <hyperlink r:id="rId11" ref="AN14"/>
+    <hyperlink r:id="rId12" ref="AN15"/>
+    <hyperlink r:id="rId13" ref="AN16"/>
+    <hyperlink r:id="rId14" ref="AN17"/>
+    <hyperlink r:id="rId15" ref="AN18"/>
+    <hyperlink r:id="rId16" ref="AN19"/>
+    <hyperlink r:id="rId17" ref="AN20"/>
+    <hyperlink r:id="rId18" ref="AN21"/>
+    <hyperlink r:id="rId19" ref="AN22"/>
+    <hyperlink r:id="rId20" ref="AN23"/>
+    <hyperlink r:id="rId21" ref="AN24"/>
+    <hyperlink r:id="rId22" ref="AN25"/>
+    <hyperlink r:id="rId23" ref="AN26"/>
+    <hyperlink r:id="rId24" ref="AN27"/>
+    <hyperlink r:id="rId25" ref="AN28"/>
+    <hyperlink r:id="rId26" ref="AN29"/>
+    <hyperlink r:id="rId27" ref="AN30"/>
+    <hyperlink r:id="rId28" ref="AN31"/>
+    <hyperlink r:id="rId29" ref="AN32"/>
+    <hyperlink r:id="rId30" ref="AN33"/>
+    <hyperlink r:id="rId31" ref="AN34"/>
+    <hyperlink r:id="rId32" ref="AN35"/>
+    <hyperlink r:id="rId33" ref="AN36"/>
+    <hyperlink r:id="rId34" ref="AN37"/>
+    <hyperlink r:id="rId35" ref="AN38"/>
+    <hyperlink r:id="rId36" ref="AN39"/>
+    <hyperlink r:id="rId37" ref="AN40"/>
+    <hyperlink r:id="rId38" ref="AN41"/>
+    <hyperlink r:id="rId38" ref="AN42"/>
+    <hyperlink r:id="rId38" ref="AN43"/>
+    <hyperlink r:id="rId38" ref="AN44"/>
+    <hyperlink r:id="rId38" ref="AN45"/>
+    <hyperlink r:id="rId38" ref="AN46"/>
+    <hyperlink r:id="rId39" ref="AN48"/>
+    <hyperlink r:id="rId40" ref="AN49"/>
+    <hyperlink r:id="rId41" ref="AN50"/>
+    <hyperlink r:id="rId42" ref="AN51"/>
+    <hyperlink r:id="rId43" ref="AN52"/>
+    <hyperlink r:id="rId44" ref="AN54"/>
+    <hyperlink r:id="rId45" ref="AN56"/>
+    <hyperlink r:id="rId46" ref="AN57"/>
   </hyperlinks>
   <printOptions headings="0" gridLines="0"/>
   <pageMargins left="0.25196850393700787" right="0.25196850393700787" top="0.75196850393700787" bottom="0.75196850393700787" header="0.29999999999999999" footer="0.29999999999999999"/>
